--- a/src/main/resources/InesModResources/杀戮尖塔自制--伊内丝v0.2.xlsx
+++ b/src/main/resources/InesModResources/杀戮尖塔自制--伊内丝v0.2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\myC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\myMod\InesMod\InesMod\src\main\resources\InesModResources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BE77195-F416-4541-9F8B-4181A09275B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFABF430-5FEC-4544-9A1E-264FDB002D1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{7A3E14A4-2175-4856-859A-887D335814F1}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="887" uniqueCount="641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="647">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1977,18 +1977,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>偷取不少于4层时，偷取额外使目标获得1层易伤。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>偷取不少于3层时，偷取额外使目标获得1层易伤。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>判断偷取层数早于攻击牌最终消耗偷取。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>下回合开始时，抽3张牌且这些牌在1回合内耗能变为0。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2126,14 +2114,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>如果本回合你尚未出牌，造成14点伤害。抽1张牌。消耗。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>如果本回合你尚未出牌，造成10点伤害。抽1张牌。消耗。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>从列表中删除此牌并使用一个能力记录一个copy，下回合将copy加入手牌。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2142,10 +2122,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>借鉴原本双倍伤害的能力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>需要测试影哨塞不下时是丢弃还是消耗。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2159,10 +2135,6 @@
   </si>
   <si>
     <t>必须有1点情报才能打出。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>StealsPower消耗时，直接添加获得情报的action</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2386,14 +2358,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>造成14点伤害。消耗所有偷取，每层额外给予1层易伤。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>造成8点伤害。消耗所有偷取，每层额外给予1层易伤。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>现在与接下来3个回合开始时，增加1张小刀到你的手牌。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2419,6 +2383,70 @@
   </si>
   <si>
     <t>下一张打出的攻击牌造成2倍伤害，随后失去所有格挡并结束你的回合。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果本回合你尚未出牌，造成10点伤害，抽1张牌。消耗。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果本回合你尚未出牌，造成10点伤害，抽2张牌。消耗。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成8点伤害。消耗所有偷取，每层额外给予1层虚弱。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成14点伤害。消耗所有偷取，每层额外给予1层虚弱。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每消耗1张影哨，对所有敌人造成3点伤害。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拥有4层偷取时，偷取额外使目标获得1层易伤。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拥有3层偷取时，偷取额外使目标获得1层易伤。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>偷取触发时，消耗数+剩下数&gt;n 且拥有此power，即触发
+不可叠加。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不可叠加。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不可叠加。重复触发时第二个无效。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>借鉴原本双倍伤害的能力
+不可叠加。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">StealsPower消耗时，直接添加获得情报的action。
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不能获得
+隐匿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你不能获得隐匿。持续x回合。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>No Invisibility</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2700,27 +2728,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2732,10 +2739,46 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2744,31 +2787,16 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3092,7 +3120,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42CD751D-9911-4397-9269-1058B93A73AF}">
-  <dimension ref="A1:L235"/>
+  <dimension ref="A1:L236"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="3" width="9.1328125" customWidth="1"/>
@@ -3104,10 +3132,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="26" t="s">
         <v>321</v>
       </c>
-      <c r="B1" s="27"/>
+      <c r="B1" s="26"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -3159,16 +3187,16 @@
       <c r="B6" s="2"/>
     </row>
     <row r="8" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="34" t="s">
+      <c r="A8" s="27" t="s">
         <v>108</v>
       </c>
-      <c r="B8" s="35"/>
-      <c r="C8" s="35"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="35"/>
-      <c r="G8" s="35"/>
-      <c r="H8" s="36"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="29"/>
     </row>
     <row r="9" spans="1:8" ht="25.7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
@@ -3177,11 +3205,11 @@
       <c r="B9" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="C9" s="34" t="s">
+      <c r="C9" s="27" t="s">
         <v>244</v>
       </c>
-      <c r="D9" s="35"/>
-      <c r="E9" s="36"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="29"/>
       <c r="F9" s="8" t="s">
         <v>2</v>
       </c>
@@ -3199,17 +3227,17 @@
       <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="35" t="s">
+      <c r="C10" s="28" t="s">
         <v>246</v>
       </c>
-      <c r="D10" s="35"/>
-      <c r="E10" s="36"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="29"/>
       <c r="F10" s="9" t="s">
         <v>264</v>
       </c>
       <c r="G10" s="10"/>
       <c r="H10" s="17" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
@@ -3219,19 +3247,19 @@
       <c r="B11" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="C11" s="34" t="s">
+      <c r="C11" s="27" t="s">
         <v>250</v>
       </c>
-      <c r="D11" s="35"/>
-      <c r="E11" s="36"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="29"/>
       <c r="F11" s="9" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="G11" s="10" t="s">
         <v>252</v>
       </c>
       <c r="H11" s="17" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
@@ -3241,11 +3269,11 @@
       <c r="B12" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="C12" s="34" t="s">
+      <c r="C12" s="27" t="s">
         <v>506</v>
       </c>
-      <c r="D12" s="35"/>
-      <c r="E12" s="36"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="29"/>
       <c r="F12" s="9" t="s">
         <v>258</v>
       </c>
@@ -3264,8 +3292,8 @@
       <c r="C13" s="23" t="s">
         <v>487</v>
       </c>
-      <c r="D13" s="35"/>
-      <c r="E13" s="36"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="29"/>
       <c r="F13" s="9" t="s">
         <v>239</v>
       </c>
@@ -3281,11 +3309,11 @@
       <c r="B14" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C14" s="35" t="s">
+      <c r="C14" s="28" t="s">
         <v>317</v>
       </c>
-      <c r="D14" s="35"/>
-      <c r="E14" s="36"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="29"/>
       <c r="F14" s="9" t="s">
         <v>257</v>
       </c>
@@ -3298,16 +3326,16 @@
     <row r="16" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="17" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="27" t="s">
+      <c r="A18" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="B18" s="27"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="27"/>
-      <c r="F18" s="27"/>
-      <c r="G18" s="27"/>
-      <c r="H18" s="27"/>
+      <c r="B18" s="26"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="26"/>
     </row>
     <row r="19" spans="1:8" ht="25.7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
@@ -3316,12 +3344,12 @@
       <c r="B19" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="C19" s="34" t="s">
+      <c r="C19" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="D19" s="35"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="36"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="29"/>
       <c r="G19" s="1" t="s">
         <v>3</v>
       </c>
@@ -3343,7 +3371,7 @@
       <c r="E20" s="24"/>
       <c r="F20" s="25"/>
       <c r="G20" s="5" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="H20" s="16" t="s">
         <v>485</v>
@@ -3357,13 +3385,13 @@
         <v>496</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="D21" s="24"/>
       <c r="E21" s="24"/>
       <c r="F21" s="25"/>
       <c r="G21" s="5" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="H21" s="16" t="s">
         <v>486</v>
@@ -3371,22 +3399,22 @@
     </row>
     <row r="22" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="19" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>498</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="D22" s="24"/>
       <c r="E22" s="24"/>
       <c r="F22" s="25"/>
       <c r="G22" s="5" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
     </row>
     <row r="23" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
@@ -3397,13 +3425,13 @@
         <v>496</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="D23" s="24"/>
       <c r="E23" s="24"/>
       <c r="F23" s="25"/>
       <c r="G23" s="4" t="s">
-        <v>590</v>
+        <v>583</v>
       </c>
       <c r="H23" s="16" t="s">
         <v>484</v>
@@ -3423,7 +3451,7 @@
       <c r="E24" s="24"/>
       <c r="F24" s="25"/>
       <c r="G24" s="5" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
       <c r="H24" s="16" t="s">
         <v>523</v>
@@ -3450,208 +3478,223 @@
       </c>
     </row>
     <row r="26" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="1" t="s">
-        <v>504</v>
+      <c r="A26" s="20" t="s">
+        <v>644</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>498</v>
       </c>
       <c r="C26" s="23" t="s">
-        <v>505</v>
+        <v>645</v>
       </c>
       <c r="D26" s="24"/>
       <c r="E26" s="24"/>
       <c r="F26" s="25"/>
-      <c r="G26" s="4" t="s">
-        <v>617</v>
-      </c>
+      <c r="G26" s="4"/>
       <c r="H26" s="16" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="C27" s="23" t="s">
+        <v>505</v>
+      </c>
+      <c r="D27" s="24"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="H27" s="16" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="28" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="29" spans="1:8" ht="21.7" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="30" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="27" t="s">
-        <v>544</v>
-      </c>
-      <c r="B30" s="27"/>
-      <c r="C30" s="27"/>
-      <c r="D30" s="27"/>
-      <c r="E30" s="27"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="27"/>
-      <c r="H30" s="27"/>
-    </row>
-    <row r="31" spans="1:8" ht="25.7" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="1" t="s">
+    <row r="29" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="30" spans="1:8" ht="21.7" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="31" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="26" t="s">
+        <v>541</v>
+      </c>
+      <c r="B31" s="26"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="26"/>
+      <c r="H31" s="26"/>
+    </row>
+    <row r="32" spans="1:8" ht="25.7" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B32" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="C31" s="34" t="s">
+      <c r="C32" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="D31" s="35"/>
-      <c r="E31" s="35"/>
-      <c r="F31" s="36"/>
-      <c r="G31" s="1" t="s">
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H31" s="1" t="s">
+      <c r="H32" s="1" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="19" t="s">
+    <row r="33" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="19" t="s">
         <v>8</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="C32" s="23" t="s">
-        <v>545</v>
-      </c>
-      <c r="D32" s="24"/>
-      <c r="E32" s="24"/>
-      <c r="F32" s="25"/>
-      <c r="G32" s="5"/>
-      <c r="H32" s="16" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="19" t="s">
-        <v>219</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>496</v>
       </c>
       <c r="C33" s="23" t="s">
-        <v>555</v>
+        <v>542</v>
       </c>
       <c r="D33" s="24"/>
       <c r="E33" s="24"/>
       <c r="F33" s="25"/>
       <c r="G33" s="5"/>
       <c r="H33" s="16" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="34" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="19" t="s">
-        <v>305</v>
+        <v>219</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>496</v>
       </c>
       <c r="C34" s="23" t="s">
-        <v>589</v>
+        <v>552</v>
       </c>
       <c r="D34" s="24"/>
       <c r="E34" s="24"/>
       <c r="F34" s="25"/>
       <c r="G34" s="5"/>
       <c r="H34" s="16" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="35" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="1" t="s">
-        <v>548</v>
+      <c r="A35" s="19" t="s">
+        <v>305</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>496</v>
       </c>
       <c r="C35" s="23" t="s">
-        <v>549</v>
+        <v>582</v>
       </c>
       <c r="D35" s="24"/>
       <c r="E35" s="24"/>
       <c r="F35" s="25"/>
       <c r="G35" s="5"/>
       <c r="H35" s="16" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
+        <v>484</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="C36" s="23" t="s">
+        <v>546</v>
+      </c>
+      <c r="D36" s="24"/>
+      <c r="E36" s="24"/>
+      <c r="F36" s="25"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="16" t="s">
+        <v>547</v>
+      </c>
+    </row>
     <row r="37" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="38" spans="1:8" s="3" customFormat="1" ht="23.35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A38"/>
-      <c r="B38"/>
-      <c r="C38"/>
-      <c r="D38"/>
-      <c r="E38"/>
-      <c r="F38"/>
-      <c r="G38"/>
-      <c r="H38" s="11"/>
-    </row>
-    <row r="39" spans="1:8" s="3" customFormat="1" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="27" t="s">
-        <v>551</v>
-      </c>
-      <c r="B39" s="27"/>
-      <c r="C39" s="27"/>
-      <c r="D39" s="27"/>
-      <c r="E39" s="27"/>
-      <c r="F39" s="27"/>
-      <c r="G39" s="27"/>
-      <c r="H39" s="27"/>
-    </row>
-    <row r="40" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="1" t="s">
+    <row r="38" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="39" spans="1:8" s="3" customFormat="1" ht="23.35" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A39"/>
+      <c r="B39"/>
+      <c r="C39"/>
+      <c r="D39"/>
+      <c r="E39"/>
+      <c r="F39"/>
+      <c r="G39"/>
+      <c r="H39" s="11"/>
+    </row>
+    <row r="40" spans="1:8" s="3" customFormat="1" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="26" t="s">
+        <v>548</v>
+      </c>
+      <c r="B40" s="26"/>
+      <c r="C40" s="26"/>
+      <c r="D40" s="26"/>
+      <c r="E40" s="26"/>
+      <c r="F40" s="26"/>
+      <c r="G40" s="26"/>
+      <c r="H40" s="26"/>
+    </row>
+    <row r="41" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A41" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B41" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D40" s="1" t="s">
+      <c r="C41" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="E41" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F40" s="1" t="s">
+      <c r="F41" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G40" s="1" t="s">
+      <c r="G41" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H40" s="1" t="s">
+      <c r="H41" s="1" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="41" spans="1:8" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="22">
-        <v>1</v>
-      </c>
-      <c r="B41" s="21" t="s">
+    <row r="42" spans="1:8" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="22">
+        <v>1</v>
+      </c>
+      <c r="B42" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C42" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="D41" s="6" t="s">
+      <c r="D42" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="E42" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="F41" s="5" t="s">
+      <c r="F42" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="G41" s="4"/>
-      <c r="H41" s="16" t="s">
+      <c r="G42" s="4"/>
+      <c r="H42" s="16" t="s">
         <v>326</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="H42" s="2"/>
     </row>
     <row r="43" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="H43" s="2"/>
@@ -3660,123 +3703,98 @@
       <c r="H44" s="2"/>
     </row>
     <row r="45" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="27" t="s">
+      <c r="H45" s="2"/>
+    </row>
+    <row r="46" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A46" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="B45" s="27"/>
-      <c r="C45" s="27"/>
-      <c r="D45" s="27"/>
-      <c r="E45" s="27"/>
-      <c r="F45" s="27"/>
-      <c r="G45" s="27"/>
-      <c r="H45" s="27"/>
-    </row>
-    <row r="46" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="27" t="s">
-        <v>571</v>
-      </c>
-      <c r="B46" s="27"/>
-      <c r="C46" s="27"/>
-      <c r="D46" s="27"/>
-      <c r="E46" s="27"/>
-      <c r="F46" s="27"/>
-      <c r="G46" s="27"/>
-      <c r="H46" s="27"/>
-    </row>
-    <row r="47" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="1" t="s">
+      <c r="B46" s="26"/>
+      <c r="C46" s="26"/>
+      <c r="D46" s="26"/>
+      <c r="E46" s="26"/>
+      <c r="F46" s="26"/>
+      <c r="G46" s="26"/>
+      <c r="H46" s="26"/>
+    </row>
+    <row r="47" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A47" s="26" t="s">
+        <v>566</v>
+      </c>
+      <c r="B47" s="26"/>
+      <c r="C47" s="26"/>
+      <c r="D47" s="26"/>
+      <c r="E47" s="26"/>
+      <c r="F47" s="26"/>
+      <c r="G47" s="26"/>
+      <c r="H47" s="26"/>
+    </row>
+    <row r="48" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B48" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C47" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D47" s="1" t="s">
+      <c r="C48" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D48" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E47" s="1" t="s">
+      <c r="E48" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F47" s="1" t="s">
+      <c r="F48" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G47" s="1" t="s">
+      <c r="G48" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H47" s="1" t="s">
+      <c r="H48" s="1" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="38">
-        <v>1</v>
-      </c>
-      <c r="B48" s="37" t="s">
+    <row r="49" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A49" s="49">
+        <v>1</v>
+      </c>
+      <c r="B49" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="C48" s="27" t="s">
+      <c r="C49" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="D48" s="6" t="s">
+      <c r="D49" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E48" s="1">
-        <v>1</v>
-      </c>
-      <c r="F48" s="5" t="s">
+      <c r="E49" s="1">
+        <v>1</v>
+      </c>
+      <c r="F49" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G48" s="26"/>
-      <c r="H48" s="15" t="s">
+      <c r="G49" s="34"/>
+      <c r="H49" s="15" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="38"/>
-      <c r="B49" s="37"/>
-      <c r="C49" s="27"/>
-      <c r="D49" s="6" t="s">
+    <row r="50" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A50" s="49"/>
+      <c r="B50" s="48"/>
+      <c r="C50" s="26"/>
+      <c r="D50" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E49" s="1">
-        <v>1</v>
-      </c>
-      <c r="F49" s="5" t="s">
+      <c r="E50" s="1">
+        <v>1</v>
+      </c>
+      <c r="F50" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G49" s="26"/>
-      <c r="H49" s="15" t="s">
+      <c r="G50" s="34"/>
+      <c r="H50" s="15" t="s">
         <v>393</v>
-      </c>
-      <c r="I49" s="2"/>
-      <c r="J49" s="2"/>
-      <c r="K49" s="2"/>
-      <c r="L49" s="2"/>
-    </row>
-    <row r="50" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="39">
-        <v>2</v>
-      </c>
-      <c r="B50" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="C50" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="D50" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E50" s="1">
-        <v>1</v>
-      </c>
-      <c r="F50" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G50" s="26"/>
-      <c r="H50" s="15" t="s">
-        <v>329</v>
       </c>
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
@@ -3784,21 +3802,27 @@
       <c r="L50" s="2"/>
     </row>
     <row r="51" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="40"/>
-      <c r="B51" s="37"/>
-      <c r="C51" s="27"/>
+      <c r="A51" s="44">
+        <v>2</v>
+      </c>
+      <c r="B51" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="C51" s="26" t="s">
+        <v>14</v>
+      </c>
       <c r="D51" s="6" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E51" s="1">
         <v>1</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G51" s="26"/>
+        <v>23</v>
+      </c>
+      <c r="G51" s="34"/>
       <c r="H51" s="15" t="s">
-        <v>394</v>
+        <v>329</v>
       </c>
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
@@ -3806,27 +3830,21 @@
       <c r="L51" s="2"/>
     </row>
     <row r="52" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="39">
-        <v>3</v>
-      </c>
-      <c r="B52" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="C52" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>13</v>
+      <c r="A52" s="45"/>
+      <c r="B52" s="48"/>
+      <c r="C52" s="26"/>
+      <c r="D52" s="6" t="s">
+        <v>19</v>
       </c>
       <c r="E52" s="1">
         <v>1</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>541</v>
-      </c>
-      <c r="G52" s="26"/>
+        <v>24</v>
+      </c>
+      <c r="G52" s="34"/>
       <c r="H52" s="15" t="s">
-        <v>495</v>
+        <v>394</v>
       </c>
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
@@ -3834,21 +3852,27 @@
       <c r="L52" s="2"/>
     </row>
     <row r="53" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="40"/>
-      <c r="B53" s="37"/>
-      <c r="C53" s="27"/>
+      <c r="A53" s="44">
+        <v>3</v>
+      </c>
+      <c r="B53" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="C53" s="26" t="s">
+        <v>14</v>
+      </c>
       <c r="D53" s="5" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E53" s="1">
         <v>1</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>567</v>
-      </c>
-      <c r="G53" s="26"/>
+        <v>538</v>
+      </c>
+      <c r="G53" s="34"/>
       <c r="H53" s="15" t="s">
-        <v>395</v>
+        <v>495</v>
       </c>
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
@@ -3856,79 +3880,71 @@
       <c r="L53" s="2"/>
     </row>
     <row r="54" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="39">
-        <v>4</v>
-      </c>
-      <c r="B54" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="C54" s="27" t="s">
-        <v>6</v>
-      </c>
+      <c r="A54" s="45"/>
+      <c r="B54" s="48"/>
+      <c r="C54" s="26"/>
       <c r="D54" s="5" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E54" s="1">
         <v>1</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>508</v>
-      </c>
-      <c r="G54" s="26"/>
+        <v>564</v>
+      </c>
+      <c r="G54" s="34"/>
       <c r="H54" s="15" t="s">
-        <v>323</v>
+        <v>395</v>
       </c>
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
       <c r="L54" s="2"/>
     </row>
-    <row r="55" spans="1:12" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="40"/>
-      <c r="B55" s="37"/>
-      <c r="C55" s="27"/>
+    <row r="55" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A55" s="44">
+        <v>4</v>
+      </c>
+      <c r="B55" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="C55" s="26" t="s">
+        <v>6</v>
+      </c>
       <c r="D55" s="5" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E55" s="1">
         <v>1</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>561</v>
-      </c>
-      <c r="G55" s="26"/>
+        <v>508</v>
+      </c>
+      <c r="G55" s="34"/>
       <c r="H55" s="15" t="s">
-        <v>461</v>
+        <v>323</v>
       </c>
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
       <c r="K55" s="2"/>
       <c r="L55" s="2"/>
     </row>
-    <row r="56" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="39">
-        <v>5</v>
-      </c>
-      <c r="B56" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="C56" s="27" t="s">
-        <v>6</v>
-      </c>
+    <row r="56" spans="1:12" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A56" s="45"/>
+      <c r="B56" s="48"/>
+      <c r="C56" s="26"/>
       <c r="D56" s="5" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E56" s="1">
         <v>1</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>537</v>
-      </c>
-      <c r="G56" s="26" t="s">
-        <v>538</v>
-      </c>
+        <v>558</v>
+      </c>
+      <c r="G56" s="34"/>
       <c r="H56" s="15" t="s">
-        <v>330</v>
+        <v>461</v>
       </c>
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
@@ -3936,21 +3952,29 @@
       <c r="L56" s="2"/>
     </row>
     <row r="57" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="40"/>
-      <c r="B57" s="28"/>
-      <c r="C57" s="27"/>
+      <c r="A57" s="44">
+        <v>5</v>
+      </c>
+      <c r="B57" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="C57" s="26" t="s">
+        <v>6</v>
+      </c>
       <c r="D57" s="5" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="E57" s="1">
         <v>1</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>592</v>
-      </c>
-      <c r="G57" s="26"/>
+        <v>534</v>
+      </c>
+      <c r="G57" s="34" t="s">
+        <v>535</v>
+      </c>
       <c r="H57" s="15" t="s">
-        <v>396</v>
+        <v>330</v>
       </c>
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
@@ -3958,27 +3982,21 @@
       <c r="L57" s="2"/>
     </row>
     <row r="58" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="39">
-        <v>6</v>
-      </c>
-      <c r="B58" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="C58" s="27" t="s">
-        <v>6</v>
-      </c>
+      <c r="A58" s="45"/>
+      <c r="B58" s="35"/>
+      <c r="C58" s="26"/>
       <c r="D58" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E58" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>637</v>
-      </c>
-      <c r="G58" s="26"/>
+        <v>585</v>
+      </c>
+      <c r="G58" s="34"/>
       <c r="H58" s="15" t="s">
-        <v>331</v>
+        <v>396</v>
       </c>
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
@@ -3986,21 +4004,27 @@
       <c r="L58" s="2"/>
     </row>
     <row r="59" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A59" s="40"/>
-      <c r="B59" s="28"/>
-      <c r="C59" s="27"/>
+      <c r="A59" s="44">
+        <v>6</v>
+      </c>
+      <c r="B59" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="C59" s="26" t="s">
+        <v>6</v>
+      </c>
       <c r="D59" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E59" s="1">
         <v>0</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>636</v>
-      </c>
-      <c r="G59" s="26"/>
+        <v>628</v>
+      </c>
+      <c r="G59" s="34"/>
       <c r="H59" s="15" t="s">
-        <v>397</v>
+        <v>331</v>
       </c>
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
@@ -4008,27 +4032,21 @@
       <c r="L59" s="2"/>
     </row>
     <row r="60" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="39">
-        <v>7</v>
-      </c>
-      <c r="B60" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="C60" s="27" t="s">
-        <v>6</v>
-      </c>
+      <c r="A60" s="45"/>
+      <c r="B60" s="35"/>
+      <c r="C60" s="26"/>
       <c r="D60" s="5" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="E60" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="G60" s="26"/>
+        <v>627</v>
+      </c>
+      <c r="G60" s="34"/>
       <c r="H60" s="15" t="s">
-        <v>332</v>
+        <v>397</v>
       </c>
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
@@ -4036,21 +4054,27 @@
       <c r="L60" s="2"/>
     </row>
     <row r="61" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="40"/>
-      <c r="B61" s="28"/>
-      <c r="C61" s="27"/>
+      <c r="A61" s="44">
+        <v>7</v>
+      </c>
+      <c r="B61" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="26" t="s">
+        <v>6</v>
+      </c>
       <c r="D61" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E61" s="1">
         <v>1</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="G61" s="26"/>
+        <v>148</v>
+      </c>
+      <c r="G61" s="34"/>
       <c r="H61" s="15" t="s">
-        <v>398</v>
+        <v>332</v>
       </c>
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
@@ -4058,29 +4082,21 @@
       <c r="L61" s="2"/>
     </row>
     <row r="62" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="39">
-        <v>8</v>
-      </c>
-      <c r="B62" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="C62" s="27" t="s">
-        <v>6</v>
-      </c>
+      <c r="A62" s="45"/>
+      <c r="B62" s="35"/>
+      <c r="C62" s="26"/>
       <c r="D62" s="5" t="s">
-        <v>197</v>
+        <v>38</v>
       </c>
       <c r="E62" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>638</v>
-      </c>
-      <c r="G62" s="26" t="s">
-        <v>607</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="G62" s="34"/>
       <c r="H62" s="15" t="s">
-        <v>333</v>
+        <v>398</v>
       </c>
       <c r="I62" s="2"/>
       <c r="J62" s="2"/>
@@ -4088,21 +4104,29 @@
       <c r="L62" s="2"/>
     </row>
     <row r="63" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="40"/>
-      <c r="B63" s="28"/>
-      <c r="C63" s="27"/>
+      <c r="A63" s="44">
+        <v>8</v>
+      </c>
+      <c r="B63" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="C63" s="26" t="s">
+        <v>6</v>
+      </c>
       <c r="D63" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E63" s="1">
         <v>0</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>639</v>
-      </c>
-      <c r="G63" s="26"/>
+        <v>629</v>
+      </c>
+      <c r="G63" s="34" t="s">
+        <v>600</v>
+      </c>
       <c r="H63" s="15" t="s">
-        <v>399</v>
+        <v>333</v>
       </c>
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
@@ -4110,95 +4134,95 @@
       <c r="L63" s="2"/>
     </row>
     <row r="64" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A64" s="39">
+      <c r="A64" s="45"/>
+      <c r="B64" s="35"/>
+      <c r="C64" s="26"/>
+      <c r="D64" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="E64" s="1">
+        <v>0</v>
+      </c>
+      <c r="F64" s="5" t="s">
+        <v>630</v>
+      </c>
+      <c r="G64" s="34"/>
+      <c r="H64" s="15" t="s">
+        <v>399</v>
+      </c>
+      <c r="I64" s="2"/>
+      <c r="J64" s="2"/>
+      <c r="K64" s="2"/>
+      <c r="L64" s="2"/>
+    </row>
+    <row r="65" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A65" s="44">
         <v>9</v>
       </c>
-      <c r="B64" s="28" t="s">
+      <c r="B65" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="C64" s="27" t="s">
+      <c r="C65" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="D64" s="5" t="s">
+      <c r="D65" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="E64" s="1">
-        <v>1</v>
-      </c>
-      <c r="F64" s="5" t="s">
-        <v>604</v>
-      </c>
-      <c r="G64" s="26" t="s">
-        <v>608</v>
-      </c>
-      <c r="H64" s="15" t="s">
+      <c r="E65" s="1">
+        <v>1</v>
+      </c>
+      <c r="F65" s="5" t="s">
+        <v>597</v>
+      </c>
+      <c r="G65" s="34" t="s">
+        <v>601</v>
+      </c>
+      <c r="H65" s="15" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A65" s="40"/>
-      <c r="B65" s="28"/>
-      <c r="C65" s="27"/>
-      <c r="D65" s="5" t="s">
+    <row r="66" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A66" s="45"/>
+      <c r="B66" s="35"/>
+      <c r="C66" s="26"/>
+      <c r="D66" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="E65" s="1">
-        <v>1</v>
-      </c>
-      <c r="F65" s="5" t="s">
-        <v>605</v>
-      </c>
-      <c r="G65" s="26"/>
-      <c r="H65" s="15" t="s">
+      <c r="E66" s="1">
+        <v>1</v>
+      </c>
+      <c r="F66" s="5" t="s">
+        <v>598</v>
+      </c>
+      <c r="G66" s="34"/>
+      <c r="H66" s="15" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A66" s="39">
+    <row r="67" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A67" s="44">
         <v>10</v>
       </c>
-      <c r="B66" s="28" t="s">
+      <c r="B67" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="C66" s="27" t="s">
+      <c r="C67" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="D66" s="5" t="s">
+      <c r="D67" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="E66" s="1">
-        <v>1</v>
-      </c>
-      <c r="F66" s="5" t="s">
-        <v>584</v>
-      </c>
-      <c r="G66" s="26" t="s">
-        <v>609</v>
-      </c>
-      <c r="H66" s="15" t="s">
+      <c r="E67" s="1">
+        <v>1</v>
+      </c>
+      <c r="F67" s="5" t="s">
+        <v>577</v>
+      </c>
+      <c r="G67" s="34" t="s">
+        <v>602</v>
+      </c>
+      <c r="H67" s="15" t="s">
         <v>335</v>
-      </c>
-      <c r="I66" s="2"/>
-      <c r="J66" s="2"/>
-      <c r="K66" s="2"/>
-      <c r="L66" s="2"/>
-    </row>
-    <row r="67" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A67" s="40"/>
-      <c r="B67" s="28"/>
-      <c r="C67" s="27"/>
-      <c r="D67" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="E67" s="1">
-        <v>1</v>
-      </c>
-      <c r="F67" s="5" t="s">
-        <v>583</v>
-      </c>
-      <c r="G67" s="26"/>
-      <c r="H67" s="15" t="s">
-        <v>401</v>
       </c>
       <c r="I67" s="2"/>
       <c r="J67" s="2"/>
@@ -4206,81 +4230,73 @@
       <c r="L67" s="2"/>
     </row>
     <row r="68" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A68" s="32">
-        <v>11</v>
-      </c>
-      <c r="B68" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="C68" s="27" t="s">
-        <v>6</v>
-      </c>
+      <c r="A68" s="45"/>
+      <c r="B68" s="35"/>
+      <c r="C68" s="26"/>
       <c r="D68" s="5" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="E68" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>569</v>
-      </c>
-      <c r="G68" s="26" t="s">
-        <v>607</v>
-      </c>
+        <v>576</v>
+      </c>
+      <c r="G68" s="34"/>
       <c r="H68" s="15" t="s">
-        <v>336</v>
+        <v>401</v>
       </c>
       <c r="I68" s="2"/>
       <c r="J68" s="2"/>
       <c r="K68" s="2"/>
       <c r="L68" s="2"/>
     </row>
-    <row r="69" spans="1:12" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A69" s="33"/>
-      <c r="B69" s="28"/>
-      <c r="C69" s="27"/>
+    <row r="69" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A69" s="30">
+        <v>11</v>
+      </c>
+      <c r="B69" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="C69" s="26" t="s">
+        <v>6</v>
+      </c>
       <c r="D69" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E69" s="1">
         <v>0</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>568</v>
-      </c>
-      <c r="G69" s="26"/>
+        <v>632</v>
+      </c>
+      <c r="G69" s="34" t="s">
+        <v>600</v>
+      </c>
       <c r="H69" s="15" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="I69" s="2"/>
       <c r="J69" s="2"/>
       <c r="K69" s="2"/>
       <c r="L69" s="2"/>
     </row>
-    <row r="70" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A70" s="32">
-        <v>12</v>
-      </c>
-      <c r="B70" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="C70" s="27" t="s">
-        <v>6</v>
-      </c>
+    <row r="70" spans="1:12" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A70" s="31"/>
+      <c r="B70" s="35"/>
+      <c r="C70" s="26"/>
       <c r="D70" s="5" t="s">
-        <v>35</v>
+        <v>159</v>
       </c>
       <c r="E70" s="1">
         <v>0</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>564</v>
-      </c>
-      <c r="G70" s="26" t="s">
-        <v>607</v>
-      </c>
+        <v>633</v>
+      </c>
+      <c r="G70" s="34"/>
       <c r="H70" s="15" t="s">
-        <v>337</v>
+        <v>402</v>
       </c>
       <c r="I70" s="2"/>
       <c r="J70" s="2"/>
@@ -4288,21 +4304,29 @@
       <c r="L70" s="2"/>
     </row>
     <row r="71" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A71" s="33"/>
-      <c r="B71" s="31"/>
-      <c r="C71" s="27"/>
+      <c r="A71" s="30">
+        <v>12</v>
+      </c>
+      <c r="B71" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="C71" s="26" t="s">
+        <v>6</v>
+      </c>
       <c r="D71" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E71" s="1">
         <v>0</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>565</v>
-      </c>
-      <c r="G71" s="26"/>
+        <v>561</v>
+      </c>
+      <c r="G71" s="34" t="s">
+        <v>600</v>
+      </c>
       <c r="H71" s="15" t="s">
-        <v>403</v>
+        <v>337</v>
       </c>
       <c r="I71" s="2"/>
       <c r="J71" s="2"/>
@@ -4310,27 +4334,21 @@
       <c r="L71" s="2"/>
     </row>
     <row r="72" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A72" s="32">
-        <v>13</v>
-      </c>
-      <c r="B72" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="C72" s="27" t="s">
-        <v>6</v>
-      </c>
+      <c r="A72" s="31"/>
+      <c r="B72" s="36"/>
+      <c r="C72" s="26"/>
       <c r="D72" s="5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E72" s="1">
         <v>0</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>581</v>
-      </c>
-      <c r="G72" s="26"/>
+        <v>562</v>
+      </c>
+      <c r="G72" s="34"/>
       <c r="H72" s="15" t="s">
-        <v>338</v>
+        <v>403</v>
       </c>
       <c r="I72" s="2"/>
       <c r="J72" s="2"/>
@@ -4338,21 +4356,27 @@
       <c r="L72" s="2"/>
     </row>
     <row r="73" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A73" s="33"/>
-      <c r="B73" s="31"/>
-      <c r="C73" s="27"/>
+      <c r="A73" s="30">
+        <v>13</v>
+      </c>
+      <c r="B73" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="C73" s="26" t="s">
+        <v>6</v>
+      </c>
       <c r="D73" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E73" s="1">
         <v>0</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>582</v>
-      </c>
-      <c r="G73" s="26"/>
+        <v>574</v>
+      </c>
+      <c r="G73" s="34"/>
       <c r="H73" s="15" t="s">
-        <v>404</v>
+        <v>338</v>
       </c>
       <c r="I73" s="2"/>
       <c r="J73" s="2"/>
@@ -4360,29 +4384,21 @@
       <c r="L73" s="2"/>
     </row>
     <row r="74" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A74" s="39">
-        <v>14</v>
-      </c>
-      <c r="B74" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="C74" s="27" t="s">
-        <v>6</v>
-      </c>
+      <c r="A74" s="31"/>
+      <c r="B74" s="36"/>
+      <c r="C74" s="26"/>
       <c r="D74" s="5" t="s">
-        <v>127</v>
+        <v>34</v>
       </c>
       <c r="E74" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>509</v>
-      </c>
-      <c r="G74" s="26" t="s">
-        <v>607</v>
-      </c>
+        <v>575</v>
+      </c>
+      <c r="G74" s="34"/>
       <c r="H74" s="15" t="s">
-        <v>339</v>
+        <v>404</v>
       </c>
       <c r="I74" s="2"/>
       <c r="J74" s="2"/>
@@ -4390,3242 +4406,3645 @@
       <c r="L74" s="2"/>
     </row>
     <row r="75" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A75" s="40"/>
-      <c r="B75" s="31"/>
-      <c r="C75" s="27"/>
+      <c r="A75" s="44">
+        <v>14</v>
+      </c>
+      <c r="B75" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="C75" s="26" t="s">
+        <v>6</v>
+      </c>
       <c r="D75" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="E75" s="1">
+        <v>1</v>
+      </c>
+      <c r="F75" s="5" t="s">
+        <v>509</v>
+      </c>
+      <c r="G75" s="34" t="s">
+        <v>600</v>
+      </c>
+      <c r="H75" s="15" t="s">
+        <v>339</v>
+      </c>
+      <c r="I75" s="2"/>
+      <c r="J75" s="2"/>
+      <c r="K75" s="2"/>
+      <c r="L75" s="2"/>
+    </row>
+    <row r="76" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A76" s="45"/>
+      <c r="B76" s="36"/>
+      <c r="C76" s="26"/>
+      <c r="D76" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="E75" s="1">
-        <v>1</v>
-      </c>
-      <c r="F75" s="5" t="s">
+      <c r="E76" s="1">
+        <v>1</v>
+      </c>
+      <c r="F76" s="5" t="s">
         <v>510</v>
       </c>
-      <c r="G75" s="26"/>
-      <c r="H75" s="15" t="s">
+      <c r="G76" s="34"/>
+      <c r="H76" s="15" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A76" s="32">
+    <row r="77" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A77" s="30">
         <v>15</v>
       </c>
-      <c r="B76" s="31" t="s">
+      <c r="B77" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C76" s="27" t="s">
+      <c r="C77" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="D76" s="5" t="s">
+      <c r="D77" s="5" t="s">
         <v>125</v>
-      </c>
-      <c r="E76" s="1">
-        <v>2</v>
-      </c>
-      <c r="F76" s="5" t="s">
-        <v>633</v>
-      </c>
-      <c r="G76" s="26" t="s">
-        <v>566</v>
-      </c>
-      <c r="H76" s="15" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A77" s="33"/>
-      <c r="B77" s="31"/>
-      <c r="C77" s="27"/>
-      <c r="D77" s="5" t="s">
-        <v>126</v>
       </c>
       <c r="E77" s="1">
         <v>2</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>632</v>
-      </c>
-      <c r="G77" s="26"/>
+        <v>634</v>
+      </c>
+      <c r="G77" s="34" t="s">
+        <v>563</v>
+      </c>
       <c r="H77" s="15" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
     </row>
     <row r="78" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A78" s="32">
-        <v>16</v>
-      </c>
-      <c r="B78" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="C78" s="46" t="s">
-        <v>6</v>
-      </c>
+      <c r="A78" s="31"/>
+      <c r="B78" s="36"/>
+      <c r="C78" s="26"/>
       <c r="D78" s="5" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E78" s="1">
         <v>2</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>578</v>
-      </c>
-      <c r="G78" s="26" t="s">
-        <v>580</v>
-      </c>
+        <v>635</v>
+      </c>
+      <c r="G78" s="34"/>
       <c r="H78" s="15" t="s">
-        <v>618</v>
+        <v>406</v>
       </c>
     </row>
     <row r="79" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A79" s="33"/>
-      <c r="B79" s="31"/>
-      <c r="C79" s="47"/>
+      <c r="A79" s="30">
+        <v>16</v>
+      </c>
+      <c r="B79" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="C79" s="37" t="s">
+        <v>6</v>
+      </c>
       <c r="D79" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E79" s="1">
         <v>2</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>579</v>
-      </c>
-      <c r="G79" s="26"/>
+        <v>571</v>
+      </c>
+      <c r="G79" s="34" t="s">
+        <v>573</v>
+      </c>
       <c r="H79" s="15" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
     </row>
     <row r="80" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A80" s="32">
+      <c r="A80" s="31"/>
+      <c r="B80" s="36"/>
+      <c r="C80" s="38"/>
+      <c r="D80" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="E80" s="1">
+        <v>2</v>
+      </c>
+      <c r="F80" s="5" t="s">
+        <v>572</v>
+      </c>
+      <c r="G80" s="34"/>
+      <c r="H80" s="15" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A81" s="30">
         <v>17</v>
       </c>
-      <c r="B80" s="31" t="s">
+      <c r="B81" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C80" s="27" t="s">
+      <c r="C81" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="D80" s="5" t="s">
+      <c r="D81" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E80" s="1">
-        <v>1</v>
-      </c>
-      <c r="F80" s="5" t="s">
+      <c r="E81" s="1">
+        <v>1</v>
+      </c>
+      <c r="F81" s="5" t="s">
         <v>526</v>
       </c>
-      <c r="G80" s="26" t="s">
+      <c r="G81" s="34" t="s">
         <v>230</v>
       </c>
-      <c r="H80" s="15" t="s">
+      <c r="H81" s="15" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A81" s="33"/>
-      <c r="B81" s="31"/>
-      <c r="C81" s="27"/>
-      <c r="D81" s="5" t="s">
+    <row r="82" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A82" s="31"/>
+      <c r="B82" s="36"/>
+      <c r="C82" s="26"/>
+      <c r="D82" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E81" s="1">
-        <v>1</v>
-      </c>
-      <c r="F81" s="5" t="s">
+      <c r="E82" s="1">
+        <v>1</v>
+      </c>
+      <c r="F82" s="5" t="s">
         <v>527</v>
       </c>
-      <c r="G81" s="26"/>
-      <c r="H81" s="15" t="s">
+      <c r="G82" s="34"/>
+      <c r="H82" s="15" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A82" s="32">
+    <row r="83" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A83" s="30">
         <v>18</v>
       </c>
-      <c r="B82" s="31" t="s">
+      <c r="B83" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C82" s="43" t="s">
+      <c r="C83" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="D82" s="5" t="s">
+      <c r="D83" s="5" t="s">
         <v>41</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F82" s="5" t="s">
-        <v>511</v>
-      </c>
-      <c r="G82" s="26" t="s">
-        <v>524</v>
-      </c>
-      <c r="H82" s="15" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A83" s="33"/>
-      <c r="B83" s="31"/>
-      <c r="C83" s="43"/>
-      <c r="D83" s="5" t="s">
-        <v>42</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F83" s="5" t="s">
+        <v>511</v>
+      </c>
+      <c r="G83" s="34" t="s">
+        <v>524</v>
+      </c>
+      <c r="H83" s="15" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A84" s="31"/>
+      <c r="B84" s="36"/>
+      <c r="C84" s="33"/>
+      <c r="D84" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F84" s="5" t="s">
         <v>512</v>
       </c>
-      <c r="G83" s="26"/>
-      <c r="H83" s="15" t="s">
+      <c r="G84" s="34"/>
+      <c r="H84" s="15" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A84" s="32">
+    <row r="85" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A85" s="30">
         <v>19</v>
       </c>
-      <c r="B84" s="31" t="s">
+      <c r="B85" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C84" s="27" t="s">
+      <c r="C85" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="D84" s="5" t="s">
+      <c r="D85" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="E84" s="1">
-        <v>1</v>
-      </c>
-      <c r="F84" s="5" t="s">
+      <c r="E85" s="1">
+        <v>1</v>
+      </c>
+      <c r="F85" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="G84" s="26"/>
-      <c r="H84" s="15" t="s">
+      <c r="G85" s="34"/>
+      <c r="H85" s="15" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="85" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A85" s="33"/>
-      <c r="B85" s="31"/>
-      <c r="C85" s="27"/>
-      <c r="D85" s="5" t="s">
+    <row r="86" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A86" s="31"/>
+      <c r="B86" s="36"/>
+      <c r="C86" s="26"/>
+      <c r="D86" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="E85" s="1">
-        <v>1</v>
-      </c>
-      <c r="F85" s="5" t="s">
+      <c r="E86" s="1">
+        <v>1</v>
+      </c>
+      <c r="F86" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="G85" s="26"/>
-      <c r="H85" s="15" t="s">
+      <c r="G86" s="34"/>
+      <c r="H86" s="15" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A86" s="32">
+    <row r="87" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A87" s="30">
         <v>20</v>
       </c>
-      <c r="B86" s="29" t="s">
+      <c r="B87" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="C86" s="27" t="s">
+      <c r="C87" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="D86" s="5" t="s">
+      <c r="D87" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="E86" s="1">
-        <v>1</v>
-      </c>
-      <c r="F86" s="5" t="s">
+      <c r="E87" s="1">
+        <v>1</v>
+      </c>
+      <c r="F87" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="G86" s="26" t="s">
+      <c r="G87" s="34" t="s">
         <v>287</v>
       </c>
-      <c r="H86" s="15" t="s">
+      <c r="H87" s="15" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A87" s="33"/>
-      <c r="B87" s="29"/>
-      <c r="C87" s="27"/>
-      <c r="D87" s="5" t="s">
+    <row r="88" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A88" s="31"/>
+      <c r="B88" s="32"/>
+      <c r="C88" s="26"/>
+      <c r="D88" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="E87" s="1">
-        <v>1</v>
-      </c>
-      <c r="F87" s="5" t="s">
+      <c r="E88" s="1">
+        <v>1</v>
+      </c>
+      <c r="F88" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="G87" s="26"/>
-      <c r="H87" s="15" t="s">
+      <c r="G88" s="34"/>
+      <c r="H88" s="15" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A88" s="32">
+    <row r="89" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A89" s="30">
         <v>21</v>
       </c>
-      <c r="B88" s="29" t="s">
+      <c r="B89" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="C88" s="27" t="s">
+      <c r="C89" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="D88" s="5" t="s">
+      <c r="D89" s="5" t="s">
         <v>129</v>
-      </c>
-      <c r="E88" s="1">
-        <v>0</v>
-      </c>
-      <c r="F88" s="5" t="s">
-        <v>587</v>
-      </c>
-      <c r="G88" s="26" t="s">
-        <v>591</v>
-      </c>
-      <c r="H88" s="15" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A89" s="33"/>
-      <c r="B89" s="29"/>
-      <c r="C89" s="27"/>
-      <c r="D89" s="5" t="s">
-        <v>130</v>
       </c>
       <c r="E89" s="1">
         <v>0</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>588</v>
-      </c>
-      <c r="G89" s="26"/>
+        <v>580</v>
+      </c>
+      <c r="G89" s="34" t="s">
+        <v>584</v>
+      </c>
       <c r="H89" s="15" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A90" s="31"/>
+      <c r="B90" s="32"/>
+      <c r="C90" s="26"/>
+      <c r="D90" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="E90" s="1">
+        <v>0</v>
+      </c>
+      <c r="F90" s="5" t="s">
+        <v>581</v>
+      </c>
+      <c r="G90" s="34"/>
+      <c r="H90" s="15" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A90" s="32">
+    <row r="91" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A91" s="30">
         <v>22</v>
       </c>
-      <c r="B90" s="29" t="s">
+      <c r="B91" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="C90" s="27" t="s">
+      <c r="C91" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="D90" s="5" t="s">
+      <c r="D91" s="5" t="s">
         <v>182</v>
-      </c>
-      <c r="E90" s="1">
-        <v>2</v>
-      </c>
-      <c r="F90" s="5" t="s">
-        <v>539</v>
-      </c>
-      <c r="G90" s="26" t="s">
-        <v>530</v>
-      </c>
-      <c r="H90" s="15" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A91" s="33"/>
-      <c r="B91" s="29"/>
-      <c r="C91" s="27"/>
-      <c r="D91" s="5" t="s">
-        <v>183</v>
       </c>
       <c r="E91" s="1">
         <v>2</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>540</v>
-      </c>
-      <c r="G91" s="26"/>
+        <v>536</v>
+      </c>
+      <c r="G91" s="34" t="s">
+        <v>530</v>
+      </c>
       <c r="H91" s="15" t="s">
-        <v>411</v>
+        <v>345</v>
       </c>
     </row>
     <row r="92" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A92" s="32">
-        <v>23</v>
-      </c>
-      <c r="B92" s="29" t="s">
-        <v>29</v>
-      </c>
-      <c r="C92" s="27" t="s">
-        <v>6</v>
-      </c>
+      <c r="A92" s="31"/>
+      <c r="B92" s="32"/>
+      <c r="C92" s="26"/>
       <c r="D92" s="5" t="s">
-        <v>30</v>
+        <v>183</v>
       </c>
       <c r="E92" s="1">
         <v>2</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>546</v>
-      </c>
-      <c r="G92" s="26" t="s">
-        <v>304</v>
-      </c>
+        <v>537</v>
+      </c>
+      <c r="G92" s="34"/>
       <c r="H92" s="15" t="s">
-        <v>346</v>
+        <v>411</v>
       </c>
     </row>
     <row r="93" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A93" s="33"/>
-      <c r="B93" s="29"/>
-      <c r="C93" s="27"/>
+      <c r="A93" s="30">
+        <v>23</v>
+      </c>
+      <c r="B93" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="C93" s="26" t="s">
+        <v>6</v>
+      </c>
       <c r="D93" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E93" s="1">
         <v>2</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>547</v>
-      </c>
-      <c r="G93" s="26"/>
+        <v>543</v>
+      </c>
+      <c r="G93" s="34" t="s">
+        <v>304</v>
+      </c>
       <c r="H93" s="15" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A94" s="31"/>
+      <c r="B94" s="32"/>
+      <c r="C94" s="26"/>
+      <c r="D94" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E94" s="1">
+        <v>2</v>
+      </c>
+      <c r="F94" s="5" t="s">
+        <v>544</v>
+      </c>
+      <c r="G94" s="34"/>
+      <c r="H94" s="15" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A94" s="32">
+    <row r="95" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A95" s="30">
         <v>24</v>
       </c>
-      <c r="B94" s="29" t="s">
+      <c r="B95" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="C94" s="27" t="s">
+      <c r="C95" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="D94" s="5" t="s">
+      <c r="D95" s="5" t="s">
         <v>170</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F94" s="5" t="s">
-        <v>585</v>
-      </c>
-      <c r="G94" s="26" t="s">
-        <v>211</v>
-      </c>
-      <c r="H94" s="15" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A95" s="33"/>
-      <c r="B95" s="29"/>
-      <c r="C95" s="27"/>
-      <c r="D95" s="5" t="s">
-        <v>173</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>586</v>
-      </c>
-      <c r="G95" s="26"/>
+        <v>578</v>
+      </c>
+      <c r="G95" s="34" t="s">
+        <v>211</v>
+      </c>
       <c r="H95" s="15" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A96" s="31"/>
+      <c r="B96" s="32"/>
+      <c r="C96" s="26"/>
+      <c r="D96" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F96" s="5" t="s">
+        <v>579</v>
+      </c>
+      <c r="G96" s="34"/>
+      <c r="H96" s="15" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A96" s="32">
+    <row r="97" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A97" s="30">
         <v>25</v>
       </c>
-      <c r="B96" s="28" t="s">
+      <c r="B97" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="C96" s="27" t="s">
+      <c r="C97" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="D96" s="5" t="s">
+      <c r="D97" s="5" t="s">
         <v>150</v>
-      </c>
-      <c r="E96" s="1">
-        <v>0</v>
-      </c>
-      <c r="F96" s="5" t="s">
-        <v>574</v>
-      </c>
-      <c r="G96" s="26"/>
-      <c r="H96" s="15" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A97" s="33"/>
-      <c r="B97" s="28"/>
-      <c r="C97" s="27"/>
-      <c r="D97" s="5" t="s">
-        <v>151</v>
       </c>
       <c r="E97" s="1">
         <v>0</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>575</v>
-      </c>
-      <c r="G97" s="26"/>
+        <v>568</v>
+      </c>
+      <c r="G97" s="34"/>
       <c r="H97" s="15" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A98" s="31"/>
+      <c r="B98" s="35"/>
+      <c r="C98" s="26"/>
+      <c r="D98" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E98" s="1">
+        <v>0</v>
+      </c>
+      <c r="F98" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="G98" s="34"/>
+      <c r="H98" s="15" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A98" s="32">
+    <row r="99" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A99" s="30">
         <v>26</v>
       </c>
-      <c r="B98" s="28" t="s">
+      <c r="B99" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="C98" s="43" t="s">
+      <c r="C99" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="D98" s="5" t="s">
+      <c r="D99" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="E98" s="1">
-        <v>1</v>
-      </c>
-      <c r="F98" s="5" t="s">
+      <c r="E99" s="1">
+        <v>1</v>
+      </c>
+      <c r="F99" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="G98" s="26"/>
-      <c r="H98" s="15" t="s">
+      <c r="G99" s="34"/>
+      <c r="H99" s="15" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="99" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A99" s="33"/>
-      <c r="B99" s="28"/>
-      <c r="C99" s="43"/>
-      <c r="D99" s="5" t="s">
+    <row r="100" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A100" s="31"/>
+      <c r="B100" s="35"/>
+      <c r="C100" s="33"/>
+      <c r="D100" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="E99" s="1">
-        <v>1</v>
-      </c>
-      <c r="F99" s="5" t="s">
+      <c r="E100" s="1">
+        <v>1</v>
+      </c>
+      <c r="F100" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="G99" s="26"/>
-      <c r="H99" s="15" t="s">
+      <c r="G100" s="34"/>
+      <c r="H100" s="15" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A100" s="32">
+    <row r="101" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A101" s="30">
         <v>27</v>
       </c>
-      <c r="B100" s="28" t="s">
+      <c r="B101" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="C100" s="27" t="s">
+      <c r="C101" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="D100" s="5" t="s">
+      <c r="D101" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E100" s="1">
-        <v>1</v>
-      </c>
-      <c r="F100" s="5" t="s">
+      <c r="E101" s="1">
+        <v>1</v>
+      </c>
+      <c r="F101" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="G100" s="26"/>
-      <c r="H100" s="15" t="s">
+      <c r="G101" s="34"/>
+      <c r="H101" s="15" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="101" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A101" s="33"/>
-      <c r="B101" s="28"/>
-      <c r="C101" s="27"/>
-      <c r="D101" s="5" t="s">
+    <row r="102" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A102" s="31"/>
+      <c r="B102" s="35"/>
+      <c r="C102" s="26"/>
+      <c r="D102" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E101" s="1">
-        <v>1</v>
-      </c>
-      <c r="F101" s="5" t="s">
+      <c r="E102" s="1">
+        <v>1</v>
+      </c>
+      <c r="F102" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="G101" s="26"/>
-      <c r="H101" s="15" t="s">
+      <c r="G102" s="34"/>
+      <c r="H102" s="15" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A102" s="32">
+    <row r="103" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A103" s="30">
         <v>28</v>
       </c>
-      <c r="B102" s="28" t="s">
+      <c r="B103" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="C102" s="27" t="s">
+      <c r="C103" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="D102" s="5" t="s">
+      <c r="D103" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="E102" s="1">
-        <v>1</v>
-      </c>
-      <c r="F102" s="5" t="s">
-        <v>634</v>
-      </c>
-      <c r="G102" s="26"/>
-      <c r="H102" s="15" t="s">
+      <c r="E103" s="1">
+        <v>1</v>
+      </c>
+      <c r="F103" s="5" t="s">
+        <v>625</v>
+      </c>
+      <c r="G103" s="34"/>
+      <c r="H103" s="15" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="103" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A103" s="33"/>
-      <c r="B103" s="28"/>
-      <c r="C103" s="27"/>
-      <c r="D103" s="5" t="s">
+    <row r="104" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A104" s="31"/>
+      <c r="B104" s="35"/>
+      <c r="C104" s="26"/>
+      <c r="D104" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E103" s="1">
-        <v>1</v>
-      </c>
-      <c r="F103" s="5" t="s">
-        <v>635</v>
-      </c>
-      <c r="G103" s="26"/>
-      <c r="H103" s="15" t="s">
+      <c r="E104" s="1">
+        <v>1</v>
+      </c>
+      <c r="F104" s="5" t="s">
+        <v>626</v>
+      </c>
+      <c r="G104" s="34"/>
+      <c r="H104" s="15" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="104" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A104" s="32">
+    <row r="105" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A105" s="30">
         <v>29</v>
       </c>
-      <c r="B104" s="28" t="s">
+      <c r="B105" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="C104" s="27" t="s">
+      <c r="C105" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="D104" s="5" t="s">
+      <c r="D105" s="5" t="s">
         <v>156</v>
-      </c>
-      <c r="E104" s="1">
-        <v>0</v>
-      </c>
-      <c r="F104" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="G104" s="26" t="s">
-        <v>570</v>
-      </c>
-      <c r="H104" s="15" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A105" s="33"/>
-      <c r="B105" s="28"/>
-      <c r="C105" s="27"/>
-      <c r="D105" s="5" t="s">
-        <v>157</v>
       </c>
       <c r="E105" s="1">
         <v>0</v>
       </c>
       <c r="F105" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="G105" s="34" t="s">
+        <v>565</v>
+      </c>
+      <c r="H105" s="15" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A106" s="31"/>
+      <c r="B106" s="35"/>
+      <c r="C106" s="26"/>
+      <c r="D106" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="E106" s="1">
+        <v>0</v>
+      </c>
+      <c r="F106" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="G105" s="26"/>
-      <c r="H105" s="15" t="s">
+      <c r="G106" s="34"/>
+      <c r="H106" s="15" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="106" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A106" s="32">
+    <row r="107" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A107" s="30">
         <v>30</v>
       </c>
-      <c r="B106" s="28" t="s">
+      <c r="B107" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="C106" s="27" t="s">
+      <c r="C107" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="D106" s="5" t="s">
+      <c r="D107" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E106" s="1">
-        <v>1</v>
-      </c>
-      <c r="F106" s="5" t="s">
+      <c r="E107" s="1">
+        <v>1</v>
+      </c>
+      <c r="F107" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="G106" s="26" t="s">
+      <c r="G107" s="34" t="s">
         <v>231</v>
       </c>
-      <c r="H106" s="15" t="s">
+      <c r="H107" s="15" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="107" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A107" s="33"/>
-      <c r="B107" s="28"/>
-      <c r="C107" s="27"/>
-      <c r="D107" s="5" t="s">
+    <row r="108" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A108" s="31"/>
+      <c r="B108" s="35"/>
+      <c r="C108" s="26"/>
+      <c r="D108" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E107" s="1">
-        <v>1</v>
-      </c>
-      <c r="F107" s="5" t="s">
+      <c r="E108" s="1">
+        <v>1</v>
+      </c>
+      <c r="F108" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="G107" s="26"/>
-      <c r="H107" s="15" t="s">
+      <c r="G108" s="34"/>
+      <c r="H108" s="15" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="108" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A108" s="32">
+    <row r="109" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A109" s="30">
         <v>31</v>
       </c>
-      <c r="B108" s="41" t="s">
+      <c r="B109" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="C108" s="46" t="s">
+      <c r="C109" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="D108" s="5" t="s">
+      <c r="D109" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="E108" s="1">
-        <v>1</v>
-      </c>
-      <c r="F108" s="5" t="s">
-        <v>593</v>
-      </c>
-      <c r="G108" s="44" t="s">
+      <c r="E109" s="1">
+        <v>1</v>
+      </c>
+      <c r="F109" s="5" t="s">
+        <v>586</v>
+      </c>
+      <c r="G109" s="46" t="s">
         <v>281</v>
       </c>
-      <c r="H108" s="15" t="s">
+      <c r="H109" s="15" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="109" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A109" s="33"/>
-      <c r="B109" s="42"/>
-      <c r="C109" s="47"/>
-      <c r="D109" s="5" t="s">
+    <row r="110" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A110" s="31"/>
+      <c r="B110" s="40"/>
+      <c r="C110" s="38"/>
+      <c r="D110" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="E109" s="1">
-        <v>1</v>
-      </c>
-      <c r="F109" s="5" t="s">
-        <v>594</v>
-      </c>
-      <c r="G109" s="45"/>
-      <c r="H109" s="15" t="s">
+      <c r="E110" s="1">
+        <v>1</v>
+      </c>
+      <c r="F110" s="5" t="s">
+        <v>587</v>
+      </c>
+      <c r="G110" s="47"/>
+      <c r="H110" s="15" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="110" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A110" s="32">
+    <row r="111" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A111" s="30">
         <v>32</v>
       </c>
-      <c r="B110" s="28" t="s">
+      <c r="B111" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="C110" s="43" t="s">
+      <c r="C111" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="D110" s="5" t="s">
+      <c r="D111" s="5" t="s">
         <v>236</v>
-      </c>
-      <c r="E110" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F110" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="G110" s="26"/>
-      <c r="H110" s="15" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A111" s="33"/>
-      <c r="B111" s="28"/>
-      <c r="C111" s="43"/>
-      <c r="D111" s="5" t="s">
-        <v>52</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F111" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="G111" s="34"/>
+      <c r="H111" s="15" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A112" s="31"/>
+      <c r="B112" s="35"/>
+      <c r="C112" s="33"/>
+      <c r="D112" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F112" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="G111" s="26"/>
-      <c r="H111" s="15" t="s">
+      <c r="G112" s="34"/>
+      <c r="H112" s="15" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="112" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A112" s="32">
+    <row r="113" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A113" s="30">
         <v>33</v>
       </c>
-      <c r="B112" s="28" t="s">
+      <c r="B113" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="C112" s="27" t="s">
+      <c r="C113" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="D112" s="5" t="s">
+      <c r="D113" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="E112" s="1">
-        <v>1</v>
-      </c>
-      <c r="F112" s="5" t="s">
-        <v>610</v>
-      </c>
-      <c r="G112" s="26"/>
-      <c r="H112" s="15" t="s">
+      <c r="E113" s="1">
+        <v>1</v>
+      </c>
+      <c r="F113" s="5" t="s">
+        <v>603</v>
+      </c>
+      <c r="G113" s="34"/>
+      <c r="H113" s="15" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="113" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A113" s="33"/>
-      <c r="B113" s="28"/>
-      <c r="C113" s="27"/>
-      <c r="D113" s="5" t="s">
+    <row r="114" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A114" s="31"/>
+      <c r="B114" s="35"/>
+      <c r="C114" s="26"/>
+      <c r="D114" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="E113" s="1">
-        <v>1</v>
-      </c>
-      <c r="F113" s="5" t="s">
-        <v>611</v>
-      </c>
-      <c r="G113" s="26"/>
-      <c r="H113" s="15" t="s">
+      <c r="E114" s="1">
+        <v>1</v>
+      </c>
+      <c r="F114" s="5" t="s">
+        <v>604</v>
+      </c>
+      <c r="G114" s="34"/>
+      <c r="H114" s="15" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="114" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A114" s="32">
+    <row r="115" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A115" s="30">
         <v>34</v>
       </c>
-      <c r="B114" s="28" t="s">
+      <c r="B115" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="C114" s="27" t="s">
+      <c r="C115" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="D114" s="5" t="s">
+      <c r="D115" s="5" t="s">
         <v>77</v>
-      </c>
-      <c r="E114" s="1">
-        <v>0</v>
-      </c>
-      <c r="F114" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="G114" s="26" t="s">
-        <v>231</v>
-      </c>
-      <c r="H114" s="15" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A115" s="33"/>
-      <c r="B115" s="28"/>
-      <c r="C115" s="27"/>
-      <c r="D115" s="5" t="s">
-        <v>78</v>
       </c>
       <c r="E115" s="1">
         <v>0</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="G115" s="26"/>
+        <v>209</v>
+      </c>
+      <c r="G115" s="34" t="s">
+        <v>231</v>
+      </c>
       <c r="H115" s="15" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="116" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A116" s="32">
-        <v>35</v>
-      </c>
-      <c r="B116" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="C116" s="27" t="s">
-        <v>14</v>
-      </c>
+      <c r="A116" s="31"/>
+      <c r="B116" s="35"/>
+      <c r="C116" s="26"/>
       <c r="D116" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E116" s="1">
         <v>0</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="G116" s="26" t="s">
-        <v>231</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="G116" s="34"/>
       <c r="H116" s="15" t="s">
-        <v>357</v>
+        <v>469</v>
       </c>
     </row>
     <row r="117" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A117" s="33"/>
-      <c r="B117" s="28"/>
-      <c r="C117" s="27"/>
+      <c r="A117" s="30">
+        <v>35</v>
+      </c>
+      <c r="B117" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="C117" s="26" t="s">
+        <v>14</v>
+      </c>
       <c r="D117" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E117" s="1">
         <v>0</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="G117" s="26"/>
+        <v>210</v>
+      </c>
+      <c r="G117" s="34" t="s">
+        <v>231</v>
+      </c>
       <c r="H117" s="15" t="s">
-        <v>423</v>
+        <v>357</v>
       </c>
     </row>
     <row r="118" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A118" s="32">
-        <v>36</v>
-      </c>
-      <c r="B118" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="C118" s="27" t="s">
-        <v>14</v>
-      </c>
+      <c r="A118" s="31"/>
+      <c r="B118" s="35"/>
+      <c r="C118" s="26"/>
       <c r="D118" s="5" t="s">
-        <v>121</v>
+        <v>80</v>
       </c>
       <c r="E118" s="1">
         <v>0</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>513</v>
-      </c>
-      <c r="G118" s="26" t="s">
-        <v>262</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="G118" s="34"/>
       <c r="H118" s="15" t="s">
-        <v>358</v>
+        <v>423</v>
       </c>
     </row>
     <row r="119" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A119" s="33"/>
-      <c r="B119" s="28"/>
-      <c r="C119" s="27"/>
+      <c r="A119" s="30">
+        <v>36</v>
+      </c>
+      <c r="B119" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="C119" s="26" t="s">
+        <v>14</v>
+      </c>
       <c r="D119" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E119" s="1">
         <v>0</v>
       </c>
       <c r="F119" s="5" t="s">
+        <v>513</v>
+      </c>
+      <c r="G119" s="34" t="s">
+        <v>262</v>
+      </c>
+      <c r="H119" s="15" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A120" s="31"/>
+      <c r="B120" s="35"/>
+      <c r="C120" s="26"/>
+      <c r="D120" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="E120" s="1">
+        <v>0</v>
+      </c>
+      <c r="F120" s="5" t="s">
         <v>514</v>
       </c>
-      <c r="G119" s="26"/>
-      <c r="H119" s="15" t="s">
+      <c r="G120" s="34"/>
+      <c r="H120" s="15" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="120" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A120" s="32">
+    <row r="121" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A121" s="30">
         <v>37</v>
       </c>
-      <c r="B120" s="41" t="s">
+      <c r="B121" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="C120" s="27" t="s">
+      <c r="C121" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="D120" s="5" t="s">
+      <c r="D121" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="E120" s="1">
+      <c r="E121" s="1">
         <v>2</v>
-      </c>
-      <c r="F120" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="G120" s="26"/>
-      <c r="H120" s="15" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A121" s="33"/>
-      <c r="B121" s="42"/>
-      <c r="C121" s="27"/>
-      <c r="D121" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="E121" s="1">
-        <v>1</v>
       </c>
       <c r="F121" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="G121" s="26"/>
+      <c r="G121" s="34"/>
       <c r="H121" s="15" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A122" s="31"/>
+      <c r="B122" s="40"/>
+      <c r="C122" s="26"/>
+      <c r="D122" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="E122" s="1">
+        <v>1</v>
+      </c>
+      <c r="F122" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="G122" s="34"/>
+      <c r="H122" s="15" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="122" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A122" s="32">
+    <row r="123" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A123" s="30">
         <v>38</v>
       </c>
-      <c r="B122" s="41" t="s">
+      <c r="B123" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="C122" s="27" t="s">
+      <c r="C123" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="D122" s="5" t="s">
+      <c r="D123" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E122" s="1">
-        <v>1</v>
-      </c>
-      <c r="F122" s="5" t="s">
+      <c r="E123" s="1">
+        <v>1</v>
+      </c>
+      <c r="F123" s="5" t="s">
         <v>520</v>
       </c>
-      <c r="G122" s="26"/>
-      <c r="H122" s="15" t="s">
+      <c r="G123" s="34"/>
+      <c r="H123" s="15" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="123" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A123" s="33"/>
-      <c r="B123" s="42"/>
-      <c r="C123" s="27"/>
-      <c r="D123" s="5" t="s">
+    <row r="124" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A124" s="31"/>
+      <c r="B124" s="40"/>
+      <c r="C124" s="26"/>
+      <c r="D124" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E123" s="1">
-        <v>1</v>
-      </c>
-      <c r="F123" s="5" t="s">
+      <c r="E124" s="1">
+        <v>1</v>
+      </c>
+      <c r="F124" s="5" t="s">
         <v>521</v>
       </c>
-      <c r="G123" s="26"/>
-      <c r="H123" s="15" t="s">
+      <c r="G124" s="34"/>
+      <c r="H124" s="15" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="124" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A124" s="32">
+    <row r="125" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A125" s="30">
         <v>39</v>
       </c>
-      <c r="B124" s="41" t="s">
+      <c r="B125" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="C124" s="27" t="s">
+      <c r="C125" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="D124" s="5" t="s">
+      <c r="D125" s="5" t="s">
         <v>133</v>
-      </c>
-      <c r="E124" s="1">
-        <v>0</v>
-      </c>
-      <c r="F124" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="G124" s="26" t="s">
-        <v>573</v>
-      </c>
-      <c r="H124" s="15" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A125" s="33"/>
-      <c r="B125" s="42"/>
-      <c r="C125" s="27"/>
-      <c r="D125" s="5" t="s">
-        <v>134</v>
       </c>
       <c r="E125" s="1">
         <v>0</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>622</v>
-      </c>
-      <c r="G125" s="26"/>
+        <v>237</v>
+      </c>
+      <c r="G125" s="34" t="s">
+        <v>567</v>
+      </c>
       <c r="H125" s="15" t="s">
-        <v>621</v>
+        <v>613</v>
       </c>
     </row>
     <row r="126" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A126" s="32">
+      <c r="A126" s="31"/>
+      <c r="B126" s="40"/>
+      <c r="C126" s="26"/>
+      <c r="D126" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="E126" s="1">
+        <v>0</v>
+      </c>
+      <c r="F126" s="5" t="s">
+        <v>615</v>
+      </c>
+      <c r="G126" s="34"/>
+      <c r="H126" s="15" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A127" s="30">
         <v>40</v>
       </c>
-      <c r="B126" s="41" t="s">
+      <c r="B127" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="C126" s="27" t="s">
+      <c r="C127" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="D126" s="5" t="s">
+      <c r="D127" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="E126" s="1">
-        <v>1</v>
-      </c>
-      <c r="F126" s="5" t="s">
+      <c r="E127" s="1">
+        <v>1</v>
+      </c>
+      <c r="F127" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="G126" s="26"/>
-      <c r="H126" s="15" t="s">
+      <c r="G127" s="34"/>
+      <c r="H127" s="15" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="127" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A127" s="33"/>
-      <c r="B127" s="42"/>
-      <c r="C127" s="27"/>
-      <c r="D127" s="5" t="s">
+    <row r="128" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A128" s="31"/>
+      <c r="B128" s="40"/>
+      <c r="C128" s="26"/>
+      <c r="D128" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="E127" s="1">
-        <v>1</v>
-      </c>
-      <c r="F127" s="5" t="s">
-        <v>534</v>
-      </c>
-      <c r="G127" s="26"/>
-      <c r="H127" s="15" t="s">
+      <c r="E128" s="1">
+        <v>1</v>
+      </c>
+      <c r="F128" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="G128" s="34"/>
+      <c r="H128" s="15" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="128" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A128" s="32">
+    <row r="129" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A129" s="30">
         <v>41</v>
       </c>
-      <c r="B128" s="41" t="s">
+      <c r="B129" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="C128" s="30" t="s">
+      <c r="C129" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="D128" s="5" t="s">
+      <c r="D129" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E128" s="1">
-        <v>1</v>
-      </c>
-      <c r="F128" s="5" t="s">
+      <c r="E129" s="1">
+        <v>1</v>
+      </c>
+      <c r="F129" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="G128" s="26"/>
-      <c r="H128" s="15" t="s">
+      <c r="G129" s="34"/>
+      <c r="H129" s="15" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="129" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A129" s="33"/>
-      <c r="B129" s="42"/>
-      <c r="C129" s="30"/>
-      <c r="D129" s="5" t="s">
+    <row r="130" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A130" s="31"/>
+      <c r="B130" s="40"/>
+      <c r="C130" s="41"/>
+      <c r="D130" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="E129" s="1">
-        <v>1</v>
-      </c>
-      <c r="F129" s="5" t="s">
+      <c r="E130" s="1">
+        <v>1</v>
+      </c>
+      <c r="F130" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="G129" s="26"/>
-      <c r="H129" s="15" t="s">
+      <c r="G130" s="34"/>
+      <c r="H130" s="15" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="130" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A130" s="32">
+    <row r="131" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A131" s="30">
         <v>42</v>
       </c>
-      <c r="B130" s="31" t="s">
+      <c r="B131" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C130" s="27" t="s">
+      <c r="C131" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="D130" s="5" t="s">
+      <c r="D131" s="5" t="s">
         <v>50</v>
-      </c>
-      <c r="E130" s="1">
-        <v>0</v>
-      </c>
-      <c r="F130" s="5" t="s">
-        <v>626</v>
-      </c>
-      <c r="G130" s="26"/>
-      <c r="H130" s="15" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="131" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A131" s="33"/>
-      <c r="B131" s="31"/>
-      <c r="C131" s="27"/>
-      <c r="D131" s="5" t="s">
-        <v>51</v>
       </c>
       <c r="E131" s="1">
         <v>0</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>623</v>
-      </c>
-      <c r="G131" s="26"/>
+        <v>619</v>
+      </c>
+      <c r="G131" s="34"/>
       <c r="H131" s="15" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
     </row>
     <row r="132" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A132" s="32">
+      <c r="A132" s="31"/>
+      <c r="B132" s="36"/>
+      <c r="C132" s="26"/>
+      <c r="D132" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E132" s="1">
+        <v>0</v>
+      </c>
+      <c r="F132" s="5" t="s">
+        <v>616</v>
+      </c>
+      <c r="G132" s="34"/>
+      <c r="H132" s="15" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A133" s="30">
         <v>43</v>
       </c>
-      <c r="B132" s="31" t="s">
+      <c r="B133" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C132" s="27" t="s">
+      <c r="C133" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="D132" s="5" t="s">
+      <c r="D133" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="E132" s="1">
-        <v>1</v>
-      </c>
-      <c r="F132" s="5" t="s">
-        <v>640</v>
-      </c>
-      <c r="H132" s="15" t="s">
+      <c r="E133" s="1">
+        <v>1</v>
+      </c>
+      <c r="F133" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="H133" s="15" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="133" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A133" s="33"/>
-      <c r="B133" s="31"/>
-      <c r="C133" s="27"/>
-      <c r="D133" s="5" t="s">
+    <row r="134" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A134" s="31"/>
+      <c r="B134" s="36"/>
+      <c r="C134" s="26"/>
+      <c r="D134" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="E133" s="1">
+      <c r="E134" s="1">
         <v>0</v>
       </c>
-      <c r="F133" s="5" t="s">
-        <v>640</v>
-      </c>
-      <c r="H133" s="15" t="s">
+      <c r="F134" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="H134" s="15" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="134" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A134" s="32">
+    <row r="135" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A135" s="30">
         <v>44</v>
       </c>
-      <c r="B134" s="31" t="s">
+      <c r="B135" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C134" s="27" t="s">
+      <c r="C135" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="D134" s="5" t="s">
+      <c r="D135" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E134" s="1">
-        <v>1</v>
-      </c>
-      <c r="F134" s="5" t="s">
+      <c r="E135" s="1">
+        <v>1</v>
+      </c>
+      <c r="F135" s="5" t="s">
         <v>515</v>
       </c>
-      <c r="G134" s="26"/>
-      <c r="H134" s="15" t="s">
+      <c r="G135" s="34"/>
+      <c r="H135" s="15" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="135" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A135" s="33"/>
-      <c r="B135" s="31"/>
-      <c r="C135" s="27"/>
-      <c r="D135" s="5" t="s">
+    <row r="136" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A136" s="31"/>
+      <c r="B136" s="36"/>
+      <c r="C136" s="26"/>
+      <c r="D136" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="E135" s="1">
-        <v>1</v>
-      </c>
-      <c r="F135" s="5" t="s">
+      <c r="E136" s="1">
+        <v>1</v>
+      </c>
+      <c r="F136" s="5" t="s">
         <v>516</v>
       </c>
-      <c r="G135" s="26"/>
-      <c r="H135" s="15" t="s">
+      <c r="G136" s="34"/>
+      <c r="H136" s="15" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="136" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A136" s="32">
+    <row r="137" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A137" s="30">
         <v>45</v>
       </c>
-      <c r="B136" s="31" t="s">
+      <c r="B137" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C136" s="43" t="s">
+      <c r="C137" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="D136" s="5" t="s">
+      <c r="D137" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="E136" s="1">
-        <v>1</v>
-      </c>
-      <c r="F136" s="5" t="s">
+      <c r="E137" s="1">
+        <v>1</v>
+      </c>
+      <c r="F137" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="G136" s="26"/>
-      <c r="H136" s="15" t="s">
+      <c r="G137" s="34"/>
+      <c r="H137" s="15" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="137" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A137" s="33"/>
-      <c r="B137" s="31"/>
-      <c r="C137" s="43"/>
-      <c r="D137" s="5" t="s">
+    <row r="138" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A138" s="31"/>
+      <c r="B138" s="36"/>
+      <c r="C138" s="33"/>
+      <c r="D138" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="E137" s="1">
-        <v>1</v>
-      </c>
-      <c r="F137" s="5" t="s">
+      <c r="E138" s="1">
+        <v>1</v>
+      </c>
+      <c r="F138" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="G137" s="26"/>
-      <c r="H137" s="15" t="s">
+      <c r="G138" s="34"/>
+      <c r="H138" s="15" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="138" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A138" s="32">
+    <row r="139" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A139" s="30">
         <v>46</v>
       </c>
-      <c r="B138" s="31" t="s">
+      <c r="B139" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C138" s="27" t="s">
+      <c r="C139" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="D138" s="5" t="s">
+      <c r="D139" s="5" t="s">
         <v>247</v>
-      </c>
-      <c r="E138" s="1">
-        <v>0</v>
-      </c>
-      <c r="F138" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="G138" s="26" t="s">
-        <v>223</v>
-      </c>
-      <c r="H138" s="15" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="139" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A139" s="33"/>
-      <c r="B139" s="31"/>
-      <c r="C139" s="27"/>
-      <c r="D139" s="5" t="s">
-        <v>248</v>
       </c>
       <c r="E139" s="1">
         <v>0</v>
       </c>
       <c r="F139" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="G139" s="34" t="s">
+        <v>223</v>
+      </c>
+      <c r="H139" s="15" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A140" s="31"/>
+      <c r="B140" s="36"/>
+      <c r="C140" s="26"/>
+      <c r="D140" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="E140" s="1">
+        <v>0</v>
+      </c>
+      <c r="F140" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="G139" s="26"/>
-      <c r="H139" s="15" t="s">
+      <c r="G140" s="34"/>
+      <c r="H140" s="15" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="140" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A140" s="32">
+    <row r="141" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A141" s="30">
         <v>47</v>
       </c>
-      <c r="B140" s="31" t="s">
+      <c r="B141" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C140" s="27" t="s">
+      <c r="C141" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="D140" s="5" t="s">
+      <c r="D141" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="E140" s="1">
-        <v>1</v>
-      </c>
-      <c r="F140" s="5" t="s">
+      <c r="E141" s="1">
+        <v>1</v>
+      </c>
+      <c r="F141" s="5" t="s">
         <v>517</v>
       </c>
-      <c r="G140" s="26" t="s">
-        <v>607</v>
-      </c>
-      <c r="H140" s="15" t="s">
+      <c r="G141" s="34" t="s">
+        <v>600</v>
+      </c>
+      <c r="H141" s="15" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="141" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A141" s="33"/>
-      <c r="B141" s="31"/>
-      <c r="C141" s="27"/>
-      <c r="D141" s="5" t="s">
+    <row r="142" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A142" s="31"/>
+      <c r="B142" s="36"/>
+      <c r="C142" s="26"/>
+      <c r="D142" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="E141" s="1">
-        <v>1</v>
-      </c>
-      <c r="F141" s="5" t="s">
+      <c r="E142" s="1">
+        <v>1</v>
+      </c>
+      <c r="F142" s="5" t="s">
         <v>518</v>
       </c>
-      <c r="G141" s="26"/>
-      <c r="H141" s="15" t="s">
+      <c r="G142" s="34"/>
+      <c r="H142" s="15" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="142" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A142" s="32">
+    <row r="143" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A143" s="30">
         <v>48</v>
       </c>
-      <c r="B142" s="31" t="s">
+      <c r="B143" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C142" s="27" t="s">
+      <c r="C143" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="D142" s="5" t="s">
-        <v>595</v>
-      </c>
-      <c r="E142" s="1">
-        <v>1</v>
-      </c>
-      <c r="F142" s="5" t="s">
-        <v>519</v>
-      </c>
-      <c r="G142" s="26"/>
-      <c r="H142" s="15" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="143" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A143" s="33"/>
-      <c r="B143" s="31"/>
-      <c r="C143" s="27"/>
       <c r="D143" s="5" t="s">
-        <v>55</v>
+        <v>588</v>
       </c>
       <c r="E143" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F143" s="5" t="s">
         <v>519</v>
       </c>
-      <c r="G143" s="26"/>
+      <c r="G143" s="34"/>
       <c r="H143" s="15" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A144" s="31"/>
+      <c r="B144" s="36"/>
+      <c r="C144" s="26"/>
+      <c r="D144" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E144" s="1">
+        <v>0</v>
+      </c>
+      <c r="F144" s="5" t="s">
+        <v>519</v>
+      </c>
+      <c r="G144" s="34"/>
+      <c r="H144" s="15" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="144" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A144" s="32">
+    <row r="145" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A145" s="30">
         <v>49</v>
       </c>
-      <c r="B144" s="31" t="s">
+      <c r="B145" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C144" s="43" t="s">
+      <c r="C145" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="D144" s="5" t="s">
+      <c r="D145" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="E144" s="1">
-        <v>1</v>
-      </c>
-      <c r="F144" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="G144" s="26" t="s">
-        <v>607</v>
-      </c>
-      <c r="H144" s="15" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A145" s="33"/>
-      <c r="B145" s="31"/>
-      <c r="C145" s="43"/>
-      <c r="D145" s="5" t="s">
-        <v>57</v>
-      </c>
       <c r="E145" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F145" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="G145" s="26"/>
+      <c r="G145" s="34" t="s">
+        <v>600</v>
+      </c>
       <c r="H145" s="15" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A146" s="31"/>
+      <c r="B146" s="36"/>
+      <c r="C146" s="33"/>
+      <c r="D146" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E146" s="1">
+        <v>0</v>
+      </c>
+      <c r="F146" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="G146" s="34"/>
+      <c r="H146" s="15" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="146" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A146" s="32">
+    <row r="147" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A147" s="30">
         <v>50</v>
       </c>
-      <c r="B146" s="31" t="s">
+      <c r="B147" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C146" s="30" t="s">
+      <c r="C147" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="D146" s="5" t="s">
+      <c r="D147" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="E146" s="1">
-        <v>1</v>
-      </c>
-      <c r="F146" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="G146" s="26"/>
-      <c r="H146" s="15" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="147" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A147" s="33"/>
-      <c r="B147" s="31"/>
-      <c r="C147" s="30"/>
-      <c r="D147" s="5" t="s">
-        <v>59</v>
-      </c>
       <c r="E147" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F147" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="G147" s="26"/>
+      <c r="G147" s="34"/>
       <c r="H147" s="15" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
     </row>
     <row r="148" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A148" s="32">
+      <c r="A148" s="31"/>
+      <c r="B148" s="36"/>
+      <c r="C148" s="41"/>
+      <c r="D148" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E148" s="1">
+        <v>0</v>
+      </c>
+      <c r="F148" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="G148" s="34"/>
+      <c r="H148" s="15" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A149" s="30">
         <v>51</v>
       </c>
-      <c r="B148" s="31" t="s">
+      <c r="B149" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C148" s="27" t="s">
+      <c r="C149" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="D148" s="5" t="s">
+      <c r="D149" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="E148" s="1">
-        <v>1</v>
-      </c>
-      <c r="F148" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="G148" s="26"/>
-      <c r="H148" s="15" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="149" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A149" s="33"/>
-      <c r="B149" s="31"/>
-      <c r="C149" s="27"/>
-      <c r="D149" s="5" t="s">
-        <v>190</v>
-      </c>
       <c r="E149" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F149" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="G149" s="26"/>
+      <c r="G149" s="34"/>
       <c r="H149" s="15" t="s">
-        <v>432</v>
+        <v>365</v>
       </c>
     </row>
     <row r="150" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A150" s="32">
-        <v>52</v>
-      </c>
-      <c r="B150" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="C150" s="27" t="s">
-        <v>14</v>
-      </c>
+      <c r="A150" s="31"/>
+      <c r="B150" s="36"/>
+      <c r="C150" s="26"/>
       <c r="D150" s="5" t="s">
-        <v>75</v>
+        <v>190</v>
       </c>
       <c r="E150" s="1">
         <v>0</v>
       </c>
       <c r="F150" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="G150" s="26"/>
+        <v>191</v>
+      </c>
+      <c r="G150" s="34"/>
       <c r="H150" s="15" t="s">
-        <v>466</v>
+        <v>432</v>
       </c>
     </row>
     <row r="151" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A151" s="33"/>
-      <c r="B151" s="31"/>
-      <c r="C151" s="27"/>
+      <c r="A151" s="30">
+        <v>52</v>
+      </c>
+      <c r="B151" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="C151" s="26" t="s">
+        <v>14</v>
+      </c>
       <c r="D151" s="5" t="s">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="E151" s="1">
         <v>0</v>
       </c>
       <c r="F151" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="G151" s="26"/>
+        <v>76</v>
+      </c>
+      <c r="G151" s="34"/>
       <c r="H151" s="15" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="152" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A152" s="32">
-        <v>53</v>
-      </c>
-      <c r="B152" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="C152" s="27" t="s">
-        <v>14</v>
-      </c>
+      <c r="A152" s="31"/>
+      <c r="B152" s="36"/>
+      <c r="C152" s="26"/>
       <c r="D152" s="5" t="s">
-        <v>62</v>
+        <v>200</v>
       </c>
       <c r="E152" s="1">
         <v>0</v>
       </c>
       <c r="F152" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="G152" s="26" t="s">
-        <v>273</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="G152" s="34"/>
       <c r="H152" s="15" t="s">
-        <v>493</v>
+        <v>467</v>
       </c>
     </row>
     <row r="153" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A153" s="33"/>
-      <c r="B153" s="31"/>
-      <c r="C153" s="27"/>
+      <c r="A153" s="30">
+        <v>53</v>
+      </c>
+      <c r="B153" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="C153" s="26" t="s">
+        <v>14</v>
+      </c>
       <c r="D153" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E153" s="1">
         <v>0</v>
       </c>
       <c r="F153" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="G153" s="34" t="s">
+        <v>273</v>
+      </c>
+      <c r="H153" s="15" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A154" s="31"/>
+      <c r="B154" s="36"/>
+      <c r="C154" s="26"/>
+      <c r="D154" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E154" s="1">
+        <v>0</v>
+      </c>
+      <c r="F154" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="G153" s="26"/>
-      <c r="H153" s="15" t="s">
+      <c r="G154" s="34"/>
+      <c r="H154" s="15" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="154" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A154" s="32">
+    <row r="155" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A155" s="30">
         <v>54</v>
       </c>
-      <c r="B154" s="31" t="s">
+      <c r="B155" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C154" s="27" t="s">
+      <c r="C155" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="D154" s="5" t="s">
+      <c r="D155" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="E154" s="1">
-        <v>1</v>
-      </c>
-      <c r="F154" s="5" t="s">
+      <c r="E155" s="1">
+        <v>1</v>
+      </c>
+      <c r="F155" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="G154" s="26"/>
-      <c r="H154" s="15" t="s">
+      <c r="G155" s="34"/>
+      <c r="H155" s="15" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="155" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A155" s="33"/>
-      <c r="B155" s="31"/>
-      <c r="C155" s="27"/>
-      <c r="D155" s="5" t="s">
+    <row r="156" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A156" s="31"/>
+      <c r="B156" s="36"/>
+      <c r="C156" s="26"/>
+      <c r="D156" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="E155" s="1">
-        <v>1</v>
-      </c>
-      <c r="F155" s="5" t="s">
+      <c r="E156" s="1">
+        <v>1</v>
+      </c>
+      <c r="F156" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="G155" s="26"/>
-      <c r="H155" s="15" t="s">
+      <c r="G156" s="34"/>
+      <c r="H156" s="15" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="156" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A156" s="32">
+    <row r="157" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A157" s="30">
         <v>55</v>
       </c>
-      <c r="B156" s="31" t="s">
+      <c r="B157" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C156" s="27" t="s">
+      <c r="C157" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="D156" s="5" t="s">
+      <c r="D157" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="E156" s="1">
-        <v>1</v>
-      </c>
-      <c r="F156" s="5" t="s">
-        <v>630</v>
-      </c>
-      <c r="G156" s="26"/>
-      <c r="H156" s="15" t="s">
+      <c r="E157" s="1">
+        <v>1</v>
+      </c>
+      <c r="F157" s="5" t="s">
+        <v>623</v>
+      </c>
+      <c r="G157" s="34"/>
+      <c r="H157" s="15" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="157" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A157" s="33"/>
-      <c r="B157" s="31"/>
-      <c r="C157" s="27"/>
-      <c r="D157" s="5" t="s">
+    <row r="158" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A158" s="31"/>
+      <c r="B158" s="36"/>
+      <c r="C158" s="26"/>
+      <c r="D158" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="E157" s="1">
-        <v>1</v>
-      </c>
-      <c r="F157" s="5" t="s">
-        <v>631</v>
-      </c>
-      <c r="G157" s="26"/>
-      <c r="H157" s="15" t="s">
+      <c r="E158" s="1">
+        <v>1</v>
+      </c>
+      <c r="F158" s="5" t="s">
+        <v>624</v>
+      </c>
+      <c r="G158" s="34"/>
+      <c r="H158" s="15" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="158" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A158" s="32">
+    <row r="159" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A159" s="30">
         <v>56</v>
       </c>
-      <c r="B158" s="31" t="s">
+      <c r="B159" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C158" s="27" t="s">
+      <c r="C159" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="D158" s="5" t="s">
+      <c r="D159" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="E158" s="1">
-        <v>1</v>
-      </c>
-      <c r="F158" s="5" t="s">
-        <v>629</v>
-      </c>
-      <c r="G158" s="26" t="s">
-        <v>576</v>
-      </c>
-      <c r="H158" s="15" t="s">
+      <c r="E159" s="1">
+        <v>1</v>
+      </c>
+      <c r="F159" s="5" t="s">
+        <v>622</v>
+      </c>
+      <c r="G159" s="34" t="s">
+        <v>570</v>
+      </c>
+      <c r="H159" s="15" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="159" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A159" s="33"/>
-      <c r="B159" s="31"/>
-      <c r="C159" s="27"/>
-      <c r="D159" s="5" t="s">
+    <row r="160" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A160" s="31"/>
+      <c r="B160" s="36"/>
+      <c r="C160" s="26"/>
+      <c r="D160" s="5" t="s">
         <v>155</v>
-      </c>
-      <c r="E159" s="1">
-        <v>0</v>
-      </c>
-      <c r="F159" s="5" t="s">
-        <v>629</v>
-      </c>
-      <c r="G159" s="26"/>
-      <c r="H159" s="15" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="160" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A160" s="32">
-        <v>57</v>
-      </c>
-      <c r="B160" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="C160" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="D160" s="5" t="s">
-        <v>176</v>
       </c>
       <c r="E160" s="1">
         <v>0</v>
       </c>
       <c r="F160" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="G160" s="26" t="s">
-        <v>612</v>
-      </c>
+        <v>622</v>
+      </c>
+      <c r="G160" s="34"/>
       <c r="H160" s="15" t="s">
-        <v>371</v>
+        <v>437</v>
       </c>
     </row>
     <row r="161" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A161" s="33"/>
-      <c r="B161" s="31"/>
-      <c r="C161" s="27"/>
+      <c r="A161" s="30">
+        <v>57</v>
+      </c>
+      <c r="B161" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="C161" s="26" t="s">
+        <v>14</v>
+      </c>
       <c r="D161" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E161" s="1">
         <v>0</v>
       </c>
       <c r="F161" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="G161" s="26"/>
+        <v>308</v>
+      </c>
+      <c r="G161" s="34" t="s">
+        <v>605</v>
+      </c>
       <c r="H161" s="15" t="s">
-        <v>438</v>
+        <v>371</v>
       </c>
     </row>
     <row r="162" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A162" s="32">
-        <v>58</v>
-      </c>
-      <c r="B162" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="C162" s="43" t="s">
-        <v>14</v>
-      </c>
+      <c r="A162" s="31"/>
+      <c r="B162" s="36"/>
+      <c r="C162" s="26"/>
       <c r="D162" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E162" s="1">
         <v>0</v>
       </c>
       <c r="F162" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="G162" s="26"/>
+        <v>309</v>
+      </c>
+      <c r="G162" s="34"/>
       <c r="H162" s="15" t="s">
-        <v>372</v>
+        <v>438</v>
       </c>
     </row>
     <row r="163" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A163" s="33"/>
-      <c r="B163" s="31"/>
-      <c r="C163" s="43"/>
+      <c r="A163" s="30">
+        <v>58</v>
+      </c>
+      <c r="B163" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="C163" s="33" t="s">
+        <v>14</v>
+      </c>
       <c r="D163" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E163" s="1">
         <v>0</v>
       </c>
       <c r="F163" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="G163" s="34"/>
+      <c r="H163" s="15" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A164" s="31"/>
+      <c r="B164" s="36"/>
+      <c r="C164" s="33"/>
+      <c r="D164" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="E164" s="1">
+        <v>0</v>
+      </c>
+      <c r="F164" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="G163" s="26"/>
-      <c r="H163" s="15" t="s">
+      <c r="G164" s="34"/>
+      <c r="H164" s="15" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="164" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A164" s="32">
+    <row r="165" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A165" s="30">
         <v>59</v>
       </c>
-      <c r="B164" s="31" t="s">
+      <c r="B165" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C164" s="43" t="s">
+      <c r="C165" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="D164" s="5" t="s">
+      <c r="D165" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="E164" s="1">
-        <v>1</v>
-      </c>
-      <c r="F164" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="G164" s="26" t="s">
-        <v>201</v>
-      </c>
-      <c r="H164" s="15" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="165" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A165" s="33"/>
-      <c r="B165" s="31"/>
-      <c r="C165" s="43"/>
-      <c r="D165" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="E165" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F165" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="G165" s="26"/>
+      <c r="G165" s="34" t="s">
+        <v>201</v>
+      </c>
       <c r="H165" s="15" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A166" s="31"/>
+      <c r="B166" s="36"/>
+      <c r="C166" s="33"/>
+      <c r="D166" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="E166" s="1">
+        <v>0</v>
+      </c>
+      <c r="F166" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="G166" s="34"/>
+      <c r="H166" s="15" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="166" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A166" s="32">
+    <row r="167" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A167" s="30">
         <v>60</v>
       </c>
-      <c r="B166" s="31" t="s">
+      <c r="B167" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C166" s="43" t="s">
+      <c r="C167" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="D166" s="5" t="s">
+      <c r="D167" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="E166" s="1">
-        <v>1</v>
-      </c>
-      <c r="F166" s="5" t="s">
+      <c r="E167" s="1">
+        <v>1</v>
+      </c>
+      <c r="F167" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="G166" s="26"/>
-      <c r="H166" s="15" t="s">
+      <c r="G167" s="34"/>
+      <c r="H167" s="15" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="167" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A167" s="33"/>
-      <c r="B167" s="31"/>
-      <c r="C167" s="43"/>
-      <c r="D167" s="5" t="s">
+    <row r="168" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A168" s="31"/>
+      <c r="B168" s="36"/>
+      <c r="C168" s="33"/>
+      <c r="D168" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="E167" s="1">
-        <v>1</v>
-      </c>
-      <c r="F167" s="5" t="s">
+      <c r="E168" s="1">
+        <v>1</v>
+      </c>
+      <c r="F168" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="G167" s="26"/>
-      <c r="H167" s="15" t="s">
+      <c r="G168" s="34"/>
+      <c r="H168" s="15" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="168" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A168" s="32">
+    <row r="169" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A169" s="30">
         <v>61</v>
       </c>
-      <c r="B168" s="31" t="s">
+      <c r="B169" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C168" s="27" t="s">
+      <c r="C169" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="D168" s="5" t="s">
+      <c r="D169" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="E168" s="1">
-        <v>1</v>
-      </c>
-      <c r="F168" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="G168" s="26"/>
-      <c r="H168" s="15" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="169" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A169" s="33"/>
-      <c r="B169" s="31"/>
-      <c r="C169" s="27"/>
-      <c r="D169" s="5" t="s">
-        <v>84</v>
-      </c>
       <c r="E169" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F169" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="G169" s="26"/>
+      <c r="G169" s="34"/>
       <c r="H169" s="15" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A170" s="31"/>
+      <c r="B170" s="36"/>
+      <c r="C170" s="26"/>
+      <c r="D170" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E170" s="1">
+        <v>0</v>
+      </c>
+      <c r="F170" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="G170" s="34"/>
+      <c r="H170" s="15" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="170" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A170" s="32">
+    <row r="171" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A171" s="30">
         <v>62</v>
       </c>
-      <c r="B170" s="31" t="s">
+      <c r="B171" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C170" s="30" t="s">
+      <c r="C171" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="D170" s="5" t="s">
-        <v>597</v>
-      </c>
-      <c r="E170" s="1">
-        <v>1</v>
-      </c>
-      <c r="F170" s="5" t="s">
-        <v>599</v>
-      </c>
-      <c r="G170" s="26"/>
-      <c r="H170" s="15" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="171" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A171" s="33"/>
-      <c r="B171" s="31"/>
-      <c r="C171" s="30"/>
       <c r="D171" s="5" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="E171" s="1">
         <v>1</v>
       </c>
       <c r="F171" s="5" t="s">
-        <v>600</v>
-      </c>
-      <c r="G171" s="26"/>
+        <v>592</v>
+      </c>
+      <c r="G171" s="34"/>
       <c r="H171" s="15" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
     </row>
     <row r="172" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A172" s="32">
+      <c r="A172" s="31"/>
+      <c r="B172" s="36"/>
+      <c r="C172" s="41"/>
+      <c r="D172" s="5" t="s">
+        <v>589</v>
+      </c>
+      <c r="E172" s="1">
+        <v>1</v>
+      </c>
+      <c r="F172" s="5" t="s">
+        <v>593</v>
+      </c>
+      <c r="G172" s="34"/>
+      <c r="H172" s="15" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A173" s="30">
         <v>63</v>
       </c>
-      <c r="B172" s="31" t="s">
+      <c r="B173" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C172" s="43" t="s">
+      <c r="C173" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="D172" s="5" t="s">
+      <c r="D173" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="E172" s="1">
-        <v>1</v>
-      </c>
-      <c r="F172" s="5" t="s">
+      <c r="E173" s="1">
+        <v>1</v>
+      </c>
+      <c r="F173" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="G172" s="26"/>
-      <c r="H172" s="15" t="s">
+      <c r="G173" s="34"/>
+      <c r="H173" s="15" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="173" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A173" s="33"/>
-      <c r="B173" s="31"/>
-      <c r="C173" s="43"/>
-      <c r="D173" s="5" t="s">
+    <row r="174" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A174" s="31"/>
+      <c r="B174" s="36"/>
+      <c r="C174" s="33"/>
+      <c r="D174" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="E173" s="1">
-        <v>1</v>
-      </c>
-      <c r="F173" s="5" t="s">
+      <c r="E174" s="1">
+        <v>1</v>
+      </c>
+      <c r="F174" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="G173" s="26"/>
-      <c r="H173" s="15" t="s">
+      <c r="G174" s="34"/>
+      <c r="H174" s="15" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="174" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A174" s="32">
+    <row r="175" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A175" s="30">
         <v>64</v>
       </c>
-      <c r="B174" s="31" t="s">
+      <c r="B175" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C174" s="27" t="s">
+      <c r="C175" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="D174" s="5" t="s">
+      <c r="D175" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="E174" s="1">
-        <v>1</v>
-      </c>
-      <c r="F174" s="5" t="s">
-        <v>535</v>
-      </c>
-      <c r="G174" s="26" t="s">
+      <c r="E175" s="1">
+        <v>1</v>
+      </c>
+      <c r="F175" s="5" t="s">
+        <v>532</v>
+      </c>
+      <c r="G175" s="34" t="s">
         <v>115</v>
       </c>
-      <c r="H174" s="15" t="s">
+      <c r="H175" s="15" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="175" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A175" s="33"/>
-      <c r="B175" s="31"/>
-      <c r="C175" s="27"/>
-      <c r="D175" s="5" t="s">
+    <row r="176" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A176" s="31"/>
+      <c r="B176" s="36"/>
+      <c r="C176" s="26"/>
+      <c r="D176" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="E175" s="1">
-        <v>1</v>
-      </c>
-      <c r="F175" s="5" t="s">
-        <v>536</v>
-      </c>
-      <c r="G175" s="26"/>
-      <c r="H175" s="15" t="s">
+      <c r="E176" s="1">
+        <v>1</v>
+      </c>
+      <c r="F176" s="5" t="s">
+        <v>533</v>
+      </c>
+      <c r="G176" s="34"/>
+      <c r="H176" s="15" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="176" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A176" s="32">
+    <row r="177" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A177" s="30">
         <v>65</v>
       </c>
-      <c r="B176" s="29" t="s">
+      <c r="B177" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="C176" s="27" t="s">
+      <c r="C177" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="D176" s="5" t="s">
+      <c r="D177" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E176" s="1">
-        <v>1</v>
-      </c>
-      <c r="F176" s="5" t="s">
-        <v>627</v>
-      </c>
-      <c r="G176" s="26"/>
-      <c r="H176" s="15" t="s">
+      <c r="E177" s="1">
+        <v>1</v>
+      </c>
+      <c r="F177" s="5" t="s">
+        <v>620</v>
+      </c>
+      <c r="G177" s="34"/>
+      <c r="H177" s="15" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="177" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A177" s="33"/>
-      <c r="B177" s="29"/>
-      <c r="C177" s="27"/>
-      <c r="D177" s="5" t="s">
+    <row r="178" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A178" s="31"/>
+      <c r="B178" s="32"/>
+      <c r="C178" s="26"/>
+      <c r="D178" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E177" s="1">
+      <c r="E178" s="1">
         <v>0</v>
       </c>
-      <c r="F177" s="5" t="s">
-        <v>627</v>
-      </c>
-      <c r="G177" s="26"/>
-      <c r="H177" s="15" t="s">
+      <c r="F178" s="5" t="s">
+        <v>620</v>
+      </c>
+      <c r="G178" s="34"/>
+      <c r="H178" s="15" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="178" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A178" s="32">
+    <row r="179" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A179" s="30">
         <v>66</v>
       </c>
-      <c r="B178" s="29" t="s">
+      <c r="B179" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="C178" s="27" t="s">
+      <c r="C179" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="D178" s="5" t="s">
+      <c r="D179" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="E178" s="1">
-        <v>1</v>
-      </c>
-      <c r="F178" s="5" t="s">
+      <c r="E179" s="1">
+        <v>1</v>
+      </c>
+      <c r="F179" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="G178" s="26"/>
-      <c r="H178" s="15" t="s">
+      <c r="G179" s="34"/>
+      <c r="H179" s="15" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="179" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A179" s="33"/>
-      <c r="B179" s="29"/>
-      <c r="C179" s="27"/>
-      <c r="D179" s="5" t="s">
+    <row r="180" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A180" s="31"/>
+      <c r="B180" s="32"/>
+      <c r="C180" s="26"/>
+      <c r="D180" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="E179" s="1">
-        <v>1</v>
-      </c>
-      <c r="F179" s="5" t="s">
+      <c r="E180" s="1">
+        <v>1</v>
+      </c>
+      <c r="F180" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="G179" s="26"/>
-      <c r="H179" s="15" t="s">
+      <c r="G180" s="34"/>
+      <c r="H180" s="15" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="180" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A180" s="32">
+    <row r="181" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A181" s="30">
         <v>67</v>
       </c>
-      <c r="B180" s="29" t="s">
+      <c r="B181" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="C180" s="27" t="s">
+      <c r="C181" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="D180" s="5" t="s">
+      <c r="D181" s="5" t="s">
         <v>71</v>
-      </c>
-      <c r="E180" s="1">
-        <v>3</v>
-      </c>
-      <c r="F180" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="G180" s="26"/>
-      <c r="H180" s="15" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="181" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A181" s="33"/>
-      <c r="B181" s="29"/>
-      <c r="C181" s="27"/>
-      <c r="D181" s="5" t="s">
-        <v>72</v>
       </c>
       <c r="E181" s="1">
         <v>3</v>
       </c>
       <c r="F181" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="G181" s="26"/>
+        <v>213</v>
+      </c>
+      <c r="G181" s="34"/>
       <c r="H181" s="15" t="s">
-        <v>446</v>
+        <v>379</v>
       </c>
     </row>
     <row r="182" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A182" s="32">
-        <v>68</v>
-      </c>
-      <c r="B182" s="29" t="s">
-        <v>29</v>
-      </c>
-      <c r="C182" s="27" t="s">
-        <v>14</v>
-      </c>
+      <c r="A182" s="31"/>
+      <c r="B182" s="32"/>
+      <c r="C182" s="26"/>
       <c r="D182" s="5" t="s">
-        <v>232</v>
+        <v>72</v>
       </c>
       <c r="E182" s="1">
         <v>3</v>
       </c>
-      <c r="F182" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="G182" s="26"/>
+      <c r="F182" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="G182" s="34"/>
       <c r="H182" s="15" t="s">
-        <v>602</v>
+        <v>446</v>
       </c>
     </row>
     <row r="183" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A183" s="33"/>
-      <c r="B183" s="29"/>
-      <c r="C183" s="27"/>
+      <c r="A183" s="30">
+        <v>68</v>
+      </c>
+      <c r="B183" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="C183" s="26" t="s">
+        <v>14</v>
+      </c>
       <c r="D183" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E183" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F183" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="G183" s="26"/>
+      <c r="G183" s="34"/>
       <c r="H183" s="15" t="s">
-        <v>603</v>
+        <v>595</v>
       </c>
     </row>
     <row r="184" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A184" s="32">
+      <c r="A184" s="31"/>
+      <c r="B184" s="32"/>
+      <c r="C184" s="26"/>
+      <c r="D184" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="E184" s="1">
+        <v>2</v>
+      </c>
+      <c r="F184" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="G184" s="34"/>
+      <c r="H184" s="15" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A185" s="30">
         <v>69</v>
       </c>
-      <c r="B184" s="29" t="s">
+      <c r="B185" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="C184" s="27" t="s">
+      <c r="C185" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="D184" s="5" t="s">
+      <c r="D185" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="E184" s="1">
+      <c r="E185" s="1">
         <v>3</v>
       </c>
-      <c r="F184" s="5" t="s">
-        <v>628</v>
-      </c>
-      <c r="G184" s="26"/>
-      <c r="H184" s="15" t="s">
+      <c r="F185" s="5" t="s">
+        <v>621</v>
+      </c>
+      <c r="G185" s="34"/>
+      <c r="H185" s="15" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="185" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A185" s="33"/>
-      <c r="B185" s="29"/>
-      <c r="C185" s="27"/>
-      <c r="D185" s="5" t="s">
+    <row r="186" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A186" s="31"/>
+      <c r="B186" s="32"/>
+      <c r="C186" s="26"/>
+      <c r="D186" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="E185" s="1">
+      <c r="E186" s="1">
         <v>2</v>
       </c>
-      <c r="F185" s="5" t="s">
-        <v>628</v>
-      </c>
-      <c r="G185" s="26"/>
-      <c r="H185" s="15" t="s">
+      <c r="F186" s="5" t="s">
+        <v>621</v>
+      </c>
+      <c r="G186" s="34"/>
+      <c r="H186" s="15" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="186" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A186" s="32">
+    <row r="187" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A187" s="30">
         <v>70</v>
       </c>
-      <c r="B186" s="29" t="s">
+      <c r="B187" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="C186" s="43" t="s">
+      <c r="C187" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="D186" s="5" t="s">
+      <c r="D187" s="5" t="s">
         <v>479</v>
-      </c>
-      <c r="E186" s="1">
-        <v>0</v>
-      </c>
-      <c r="F186" s="5" t="s">
-        <v>476</v>
-      </c>
-      <c r="G186" s="26"/>
-      <c r="H186" s="15" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="187" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A187" s="33"/>
-      <c r="B187" s="29"/>
-      <c r="C187" s="43"/>
-      <c r="D187" s="5" t="s">
-        <v>478</v>
       </c>
       <c r="E187" s="1">
         <v>0</v>
       </c>
       <c r="F187" s="5" t="s">
-        <v>477</v>
-      </c>
-      <c r="G187" s="26"/>
+        <v>476</v>
+      </c>
+      <c r="G187" s="34"/>
       <c r="H187" s="15" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="188" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A188" s="32">
-        <v>71</v>
-      </c>
-      <c r="B188" s="29" t="s">
-        <v>29</v>
-      </c>
-      <c r="C188" s="43" t="s">
-        <v>14</v>
-      </c>
+      <c r="A188" s="31"/>
+      <c r="B188" s="32"/>
+      <c r="C188" s="33"/>
       <c r="D188" s="5" t="s">
-        <v>87</v>
+        <v>478</v>
       </c>
       <c r="E188" s="1">
         <v>0</v>
       </c>
       <c r="F188" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="G188" s="26" t="s">
-        <v>607</v>
-      </c>
+        <v>477</v>
+      </c>
+      <c r="G188" s="34"/>
       <c r="H188" s="15" t="s">
-        <v>380</v>
+        <v>481</v>
       </c>
     </row>
     <row r="189" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A189" s="33"/>
-      <c r="B189" s="29"/>
-      <c r="C189" s="43"/>
+      <c r="A189" s="30">
+        <v>71</v>
+      </c>
+      <c r="B189" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="C189" s="33" t="s">
+        <v>14</v>
+      </c>
       <c r="D189" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E189" s="1">
         <v>0</v>
       </c>
       <c r="F189" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="G189" s="34" t="s">
+        <v>600</v>
+      </c>
+      <c r="H189" s="15" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A190" s="31"/>
+      <c r="B190" s="32"/>
+      <c r="C190" s="33"/>
+      <c r="D190" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E190" s="1">
+        <v>0</v>
+      </c>
+      <c r="F190" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="G189" s="26"/>
-      <c r="H189" s="15" t="s">
+      <c r="G190" s="34"/>
+      <c r="H190" s="15" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="190" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A190" s="32">
+    <row r="191" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A191" s="30">
         <v>72</v>
       </c>
-      <c r="B190" s="29" t="s">
+      <c r="B191" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="C190" s="43" t="s">
+      <c r="C191" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="D190" s="5" t="s">
+      <c r="D191" s="5" t="s">
         <v>192</v>
-      </c>
-      <c r="E190" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F190" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="G190" s="26"/>
-      <c r="H190" s="15" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="191" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A191" s="33"/>
-      <c r="B191" s="29"/>
-      <c r="C191" s="43"/>
-      <c r="D191" s="5" t="s">
-        <v>193</v>
       </c>
       <c r="E191" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F191" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="G191" s="34"/>
+      <c r="H191" s="15" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A192" s="31"/>
+      <c r="B192" s="32"/>
+      <c r="C192" s="33"/>
+      <c r="D192" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="E192" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F192" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="G191" s="26"/>
-      <c r="H191" s="15" t="s">
+      <c r="G192" s="34"/>
+      <c r="H192" s="15" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="192" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A192" s="32">
+    <row r="193" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A193" s="30">
         <v>73</v>
       </c>
-      <c r="B192" s="29" t="s">
+      <c r="B193" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="C192" s="27" t="s">
+      <c r="C193" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="D192" s="5" t="s">
+      <c r="D193" s="5" t="s">
         <v>131</v>
-      </c>
-      <c r="E192" s="1">
-        <v>4</v>
-      </c>
-      <c r="F192" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="G192" s="26" t="s">
-        <v>222</v>
-      </c>
-      <c r="H192" s="15" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="193" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A193" s="33"/>
-      <c r="B193" s="29"/>
-      <c r="C193" s="27"/>
-      <c r="D193" s="5" t="s">
-        <v>132</v>
       </c>
       <c r="E193" s="1">
         <v>4</v>
       </c>
       <c r="F193" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="G193" s="34" t="s">
+        <v>222</v>
+      </c>
+      <c r="H193" s="15" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A194" s="31"/>
+      <c r="B194" s="32"/>
+      <c r="C194" s="26"/>
+      <c r="D194" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="E194" s="1">
+        <v>4</v>
+      </c>
+      <c r="F194" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="G193" s="26"/>
-      <c r="H193" s="15" t="s">
+      <c r="G194" s="34"/>
+      <c r="H194" s="15" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="194" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A194" s="32">
+    <row r="195" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A195" s="30">
         <v>74</v>
       </c>
-      <c r="B194" s="29" t="s">
+      <c r="B195" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="C194" s="27" t="s">
+      <c r="C195" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="D194" s="5" t="s">
+      <c r="D195" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="E194" s="1">
-        <v>1</v>
-      </c>
-      <c r="F194" s="5" t="s">
+      <c r="E195" s="1">
+        <v>1</v>
+      </c>
+      <c r="F195" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="G194" s="26" t="s">
+      <c r="G195" s="34" t="s">
         <v>143</v>
       </c>
-      <c r="H194" s="15" t="s">
+      <c r="H195" s="15" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="195" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A195" s="33"/>
-      <c r="B195" s="29"/>
-      <c r="C195" s="27"/>
-      <c r="D195" s="5" t="s">
+    <row r="196" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A196" s="31"/>
+      <c r="B196" s="32"/>
+      <c r="C196" s="26"/>
+      <c r="D196" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="E195" s="1">
-        <v>1</v>
-      </c>
-      <c r="F195" s="5" t="s">
+      <c r="E196" s="1">
+        <v>1</v>
+      </c>
+      <c r="F196" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="G195" s="26"/>
-      <c r="H195" s="15" t="s">
+      <c r="G196" s="34"/>
+      <c r="H196" s="15" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="196" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A196" s="32">
+    <row r="197" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A197" s="30">
         <v>75</v>
       </c>
-      <c r="B196" s="31" t="s">
+      <c r="B197" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C196" s="27" t="s">
+      <c r="C197" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="D196" s="5" t="s">
+      <c r="D197" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="E196" s="1">
+      <c r="E197" s="1">
         <v>2</v>
-      </c>
-      <c r="F196" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="G196" s="26" t="s">
-        <v>577</v>
-      </c>
-      <c r="H196" s="15" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="197" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A197" s="33"/>
-      <c r="B197" s="31"/>
-      <c r="C197" s="27"/>
-      <c r="D197" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="E197" s="1">
-        <v>1</v>
       </c>
       <c r="F197" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="G197" s="26"/>
+      <c r="G197" s="34" t="s">
+        <v>643</v>
+      </c>
       <c r="H197" s="15" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A198" s="31"/>
+      <c r="B198" s="36"/>
+      <c r="C198" s="26"/>
+      <c r="D198" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E198" s="1">
+        <v>1</v>
+      </c>
+      <c r="F198" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="G198" s="34"/>
+      <c r="H198" s="15" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="198" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A198" s="32">
+    <row r="199" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A199" s="30">
         <v>76</v>
       </c>
-      <c r="B198" s="31" t="s">
+      <c r="B199" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C198" s="27" t="s">
+      <c r="C199" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="D198" s="5" t="s">
+      <c r="D199" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="E198" s="1">
-        <v>1</v>
-      </c>
-      <c r="F198" s="5" t="s">
+      <c r="E199" s="1">
+        <v>1</v>
+      </c>
+      <c r="F199" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="G198" s="26" t="s">
+      <c r="G199" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="H198" s="15" t="s">
+      <c r="H199" s="15" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="199" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A199" s="33"/>
-      <c r="B199" s="31"/>
-      <c r="C199" s="27"/>
-      <c r="D199" s="5" t="s">
+    <row r="200" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A200" s="31"/>
+      <c r="B200" s="36"/>
+      <c r="C200" s="26"/>
+      <c r="D200" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="E199" s="1">
-        <v>1</v>
-      </c>
-      <c r="F199" s="5" t="s">
+      <c r="E200" s="1">
+        <v>1</v>
+      </c>
+      <c r="F200" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="G199" s="26"/>
-      <c r="H199" s="15" t="s">
+      <c r="G200" s="34"/>
+      <c r="H200" s="15" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="200" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A200" s="32">
+    <row r="201" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A201" s="30">
         <v>77</v>
       </c>
-      <c r="B200" s="31" t="s">
+      <c r="B201" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C200" s="27" t="s">
+      <c r="C201" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="D200" s="5" t="s">
+      <c r="D201" s="5" t="s">
         <v>111</v>
-      </c>
-      <c r="E200" s="1">
-        <v>2</v>
-      </c>
-      <c r="F200" s="5" t="s">
-        <v>614</v>
-      </c>
-      <c r="G200" s="26"/>
-      <c r="H200" s="15" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="201" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A201" s="33"/>
-      <c r="B201" s="31"/>
-      <c r="C201" s="27"/>
-      <c r="D201" s="5" t="s">
-        <v>112</v>
       </c>
       <c r="E201" s="1">
         <v>2</v>
       </c>
       <c r="F201" s="5" t="s">
-        <v>615</v>
-      </c>
-      <c r="G201" s="26"/>
+        <v>607</v>
+      </c>
+      <c r="G201" s="34" t="s">
+        <v>641</v>
+      </c>
       <c r="H201" s="15" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A202" s="31"/>
+      <c r="B202" s="36"/>
+      <c r="C202" s="26"/>
+      <c r="D202" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="E202" s="1">
+        <v>2</v>
+      </c>
+      <c r="F202" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="G202" s="34"/>
+      <c r="H202" s="15" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="202" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A202" s="32">
+    <row r="203" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A203" s="30">
         <v>78</v>
       </c>
-      <c r="B202" s="31" t="s">
+      <c r="B203" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C202" s="27" t="s">
+      <c r="C203" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="D202" s="5" t="s">
+      <c r="D203" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="E202" s="1">
-        <v>1</v>
-      </c>
-      <c r="F202" s="5" t="s">
+      <c r="E203" s="1">
+        <v>1</v>
+      </c>
+      <c r="F203" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="G202" s="26"/>
-      <c r="H202" s="15" t="s">
+      <c r="G203" s="34"/>
+      <c r="H203" s="15" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="203" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A203" s="33"/>
-      <c r="B203" s="31"/>
-      <c r="C203" s="27"/>
-      <c r="D203" s="5" t="s">
+    <row r="204" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A204" s="31"/>
+      <c r="B204" s="36"/>
+      <c r="C204" s="26"/>
+      <c r="D204" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="E203" s="1">
-        <v>1</v>
-      </c>
-      <c r="F203" s="5" t="s">
+      <c r="E204" s="1">
+        <v>1</v>
+      </c>
+      <c r="F204" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="G203" s="26"/>
-      <c r="H203" s="15" t="s">
+      <c r="G204" s="34"/>
+      <c r="H204" s="15" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="204" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A204" s="32">
+    <row r="205" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A205" s="30">
         <v>79</v>
       </c>
-      <c r="B204" s="31" t="s">
+      <c r="B205" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C204" s="27" t="s">
+      <c r="C205" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="D204" s="5" t="s">
+      <c r="D205" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="E204" s="1">
-        <v>1</v>
-      </c>
-      <c r="F204" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="G204" s="26"/>
-      <c r="H204" s="15" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="205" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A205" s="33"/>
-      <c r="B205" s="31"/>
-      <c r="C205" s="27"/>
-      <c r="D205" s="5" t="s">
-        <v>93</v>
-      </c>
       <c r="E205" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F205" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="G205" s="26"/>
+      <c r="G205" s="34"/>
       <c r="H205" s="15" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A206" s="31"/>
+      <c r="B206" s="36"/>
+      <c r="C206" s="26"/>
+      <c r="D206" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E206" s="1">
+        <v>0</v>
+      </c>
+      <c r="F206" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="G206" s="34"/>
+      <c r="H206" s="15" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="206" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A206" s="32">
+    <row r="207" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A207" s="30">
         <v>80</v>
       </c>
-      <c r="B206" s="31" t="s">
+      <c r="B207" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C206" s="27" t="s">
+      <c r="C207" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="D206" s="5" t="s">
+      <c r="D207" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="E206" s="1">
-        <v>1</v>
-      </c>
-      <c r="F206" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="G206" s="26" t="s">
-        <v>249</v>
-      </c>
-      <c r="H206" s="15" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="207" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A207" s="33"/>
-      <c r="B207" s="31"/>
-      <c r="C207" s="27"/>
-      <c r="D207" s="5" t="s">
-        <v>105</v>
-      </c>
       <c r="E207" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F207" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="G207" s="26"/>
+      <c r="G207" s="34" t="s">
+        <v>249</v>
+      </c>
       <c r="H207" s="15" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A208" s="31"/>
+      <c r="B208" s="36"/>
+      <c r="C208" s="26"/>
+      <c r="D208" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="E208" s="1">
+        <v>1</v>
+      </c>
+      <c r="F208" s="5" t="s">
+        <v>636</v>
+      </c>
+      <c r="G208" s="34"/>
+      <c r="H208" s="15" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="208" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A208" s="32">
+    <row r="209" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A209" s="30">
         <v>81</v>
       </c>
-      <c r="B208" s="31" t="s">
+      <c r="B209" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C208" s="27" t="s">
+      <c r="C209" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="D208" s="5" t="s">
+      <c r="D209" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="E208" s="1">
-        <v>1</v>
-      </c>
-      <c r="F208" s="5" t="s">
-        <v>531</v>
-      </c>
-      <c r="G208" s="26" t="s">
-        <v>533</v>
-      </c>
-      <c r="H208" s="15" t="s">
+      <c r="E209" s="1">
+        <v>1</v>
+      </c>
+      <c r="F209" s="5" t="s">
+        <v>637</v>
+      </c>
+      <c r="G209" s="34" t="s">
+        <v>639</v>
+      </c>
+      <c r="H209" s="15" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="209" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A209" s="33"/>
-      <c r="B209" s="31"/>
-      <c r="C209" s="27"/>
-      <c r="D209" s="5" t="s">
+    <row r="210" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A210" s="31"/>
+      <c r="B210" s="36"/>
+      <c r="C210" s="26"/>
+      <c r="D210" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="E209" s="1">
-        <v>1</v>
-      </c>
-      <c r="F209" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="G209" s="26"/>
-      <c r="H209" s="15" t="s">
+      <c r="E210" s="1">
+        <v>1</v>
+      </c>
+      <c r="F210" s="5" t="s">
+        <v>638</v>
+      </c>
+      <c r="G210" s="34"/>
+      <c r="H210" s="15" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="210" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A210" s="32">
+    <row r="211" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A211" s="30">
         <v>82</v>
       </c>
-      <c r="B210" s="48" t="s">
+      <c r="B211" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="C210" s="27" t="s">
+      <c r="C211" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="D210" s="5" t="s">
+      <c r="D211" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="E210" s="1">
-        <v>1</v>
-      </c>
-      <c r="F210" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="G210" s="26"/>
-      <c r="H210" s="15" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="211" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A211" s="33"/>
-      <c r="B211" s="49"/>
-      <c r="C211" s="27"/>
-      <c r="D211" s="5" t="s">
-        <v>181</v>
-      </c>
       <c r="E211" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F211" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="G211" s="26"/>
+      <c r="G211" s="34"/>
       <c r="H211" s="15" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A212" s="31"/>
+      <c r="B212" s="43"/>
+      <c r="C212" s="26"/>
+      <c r="D212" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="E212" s="1">
+        <v>0</v>
+      </c>
+      <c r="F212" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="G212" s="34"/>
+      <c r="H212" s="15" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="212" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A212" s="32">
+    <row r="213" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A213" s="30">
         <v>83</v>
       </c>
-      <c r="B212" s="29" t="s">
+      <c r="B213" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="C212" s="27" t="s">
+      <c r="C213" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="D212" s="5" t="s">
+      <c r="D213" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="E212" s="1">
+      <c r="E213" s="1">
         <v>2</v>
       </c>
-      <c r="F212" s="5" t="s">
+      <c r="F213" s="5" t="s">
+        <v>599</v>
+      </c>
+      <c r="G213" s="34" t="s">
+        <v>642</v>
+      </c>
+      <c r="H213" s="15" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A214" s="31"/>
+      <c r="B214" s="32"/>
+      <c r="C214" s="26"/>
+      <c r="D214" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="E214" s="1">
+        <v>1</v>
+      </c>
+      <c r="F214" s="5" t="s">
         <v>606</v>
       </c>
-      <c r="G212" s="26" t="s">
-        <v>572</v>
-      </c>
-      <c r="H212" s="15" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="213" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A213" s="33"/>
-      <c r="B213" s="29"/>
-      <c r="C213" s="27"/>
-      <c r="D213" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="E213" s="1">
-        <v>1</v>
-      </c>
-      <c r="F213" s="5" t="s">
-        <v>613</v>
-      </c>
-      <c r="G213" s="26"/>
-      <c r="H213" s="15" t="s">
+      <c r="G214" s="34"/>
+      <c r="H214" s="15" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="214" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A214" s="32">
+    <row r="215" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A215" s="30">
         <v>84</v>
       </c>
-      <c r="B214" s="29" t="s">
+      <c r="B215" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="C214" s="27" t="s">
+      <c r="C215" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="D214" s="5" t="s">
+      <c r="D215" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="E214" s="1">
-        <v>2</v>
-      </c>
-      <c r="F214" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="G214" s="26" t="s">
-        <v>316</v>
-      </c>
-      <c r="H214" s="15" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="215" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A215" s="33"/>
-      <c r="B215" s="29"/>
-      <c r="C215" s="27"/>
-      <c r="D215" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="E215" s="1">
         <v>2</v>
       </c>
       <c r="F215" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="G215" s="34" t="s">
+        <v>316</v>
+      </c>
+      <c r="H215" s="15" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A216" s="31"/>
+      <c r="B216" s="32"/>
+      <c r="C216" s="26"/>
+      <c r="D216" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E216" s="1">
+        <v>2</v>
+      </c>
+      <c r="F216" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="G215" s="26"/>
-      <c r="H215" s="15" t="s">
+      <c r="G216" s="34"/>
+      <c r="H216" s="15" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="216" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A216" s="32">
+    <row r="217" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A217" s="30">
         <v>85</v>
       </c>
-      <c r="B216" s="29" t="s">
+      <c r="B217" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="C216" s="27" t="s">
+      <c r="C217" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="D216" s="5" t="s">
+      <c r="D217" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="E216" s="1">
+      <c r="E217" s="1">
         <v>3</v>
-      </c>
-      <c r="F216" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="G216" s="26"/>
-      <c r="H216" s="15" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="217" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A217" s="33"/>
-      <c r="B217" s="29"/>
-      <c r="C217" s="27"/>
-      <c r="D217" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="E217" s="1">
-        <v>2</v>
       </c>
       <c r="F217" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="G217" s="26"/>
+      <c r="G217" s="34"/>
       <c r="H217" s="15" t="s">
-        <v>458</v>
+        <v>390</v>
       </c>
     </row>
     <row r="218" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A218" s="32">
-        <v>86</v>
-      </c>
-      <c r="B218" s="29" t="s">
-        <v>29</v>
-      </c>
-      <c r="C218" s="27" t="s">
-        <v>89</v>
-      </c>
+      <c r="A218" s="31"/>
+      <c r="B218" s="32"/>
+      <c r="C218" s="26"/>
       <c r="D218" s="5" t="s">
-        <v>152</v>
+        <v>101</v>
       </c>
       <c r="E218" s="1">
         <v>2</v>
       </c>
       <c r="F218" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="G218" s="26"/>
+        <v>226</v>
+      </c>
+      <c r="G218" s="34"/>
       <c r="H218" s="15" t="s">
-        <v>482</v>
+        <v>458</v>
       </c>
     </row>
     <row r="219" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A219" s="33"/>
-      <c r="B219" s="29"/>
-      <c r="C219" s="27"/>
+      <c r="A219" s="30">
+        <v>86</v>
+      </c>
+      <c r="B219" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="C219" s="26" t="s">
+        <v>89</v>
+      </c>
       <c r="D219" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E219" s="1">
         <v>2</v>
       </c>
       <c r="F219" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="G219" s="26"/>
+        <v>194</v>
+      </c>
+      <c r="G219" s="34"/>
       <c r="H219" s="15" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="220" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A220" s="32">
-        <v>87</v>
-      </c>
-      <c r="B220" s="29" t="s">
-        <v>29</v>
-      </c>
-      <c r="C220" s="30" t="s">
-        <v>89</v>
-      </c>
+      <c r="A220" s="31"/>
+      <c r="B220" s="32"/>
+      <c r="C220" s="26"/>
       <c r="D220" s="5" t="s">
-        <v>102</v>
+        <v>153</v>
       </c>
       <c r="E220" s="1">
         <v>2</v>
       </c>
       <c r="F220" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="G220" s="26"/>
+        <v>202</v>
+      </c>
+      <c r="G220" s="34"/>
       <c r="H220" s="15" t="s">
-        <v>391</v>
+        <v>483</v>
       </c>
     </row>
     <row r="221" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A221" s="33"/>
-      <c r="B221" s="29"/>
-      <c r="C221" s="30"/>
+      <c r="A221" s="30">
+        <v>87</v>
+      </c>
+      <c r="B221" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="C221" s="41" t="s">
+        <v>89</v>
+      </c>
       <c r="D221" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E221" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F221" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="G221" s="26"/>
+      <c r="G221" s="34" t="s">
+        <v>640</v>
+      </c>
       <c r="H221" s="15" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A222" s="31"/>
+      <c r="B222" s="32"/>
+      <c r="C222" s="41"/>
+      <c r="D222" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E222" s="1">
+        <v>1</v>
+      </c>
+      <c r="F222" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="G222" s="34"/>
+      <c r="H222" s="15" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="222" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A222" s="32">
+    <row r="223" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A223" s="30">
         <v>88</v>
       </c>
-      <c r="B222" s="29" t="s">
+      <c r="B223" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="C222" s="43" t="s">
+      <c r="C223" s="33" t="s">
         <v>89</v>
       </c>
-      <c r="D222" s="5" t="s">
+      <c r="D223" s="5" t="s">
         <v>144</v>
-      </c>
-      <c r="E222" s="1">
-        <v>3</v>
-      </c>
-      <c r="F222" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="G222" s="26"/>
-      <c r="H222" s="15" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="223" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A223" s="33"/>
-      <c r="B223" s="29"/>
-      <c r="C223" s="43"/>
-      <c r="D223" s="5" t="s">
-        <v>145</v>
       </c>
       <c r="E223" s="1">
         <v>3</v>
       </c>
       <c r="F223" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="G223" s="34"/>
+      <c r="H223" s="15" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A224" s="31"/>
+      <c r="B224" s="32"/>
+      <c r="C224" s="33"/>
+      <c r="D224" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="E224" s="1">
+        <v>3</v>
+      </c>
+      <c r="F224" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="G223" s="26"/>
-      <c r="H223" s="15" t="s">
+      <c r="G224" s="34"/>
+      <c r="H224" s="15" t="s">
         <v>460</v>
-      </c>
-    </row>
-    <row r="227" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A227" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="228" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A228" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="229" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A229" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="230" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A230" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="231" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A231" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="232" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A232" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
     </row>
     <row r="233" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A233" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="234" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A234" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="235" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A235" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A236" t="s">
         <v>296</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="377">
+  <mergeCells count="378">
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="G57:G58"/>
+    <mergeCell ref="G59:G60"/>
+    <mergeCell ref="C207:C208"/>
+    <mergeCell ref="B61:B62"/>
+    <mergeCell ref="C63:C64"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="G87:G88"/>
+    <mergeCell ref="C89:C90"/>
+    <mergeCell ref="G129:G130"/>
+    <mergeCell ref="C129:C130"/>
+    <mergeCell ref="G143:G144"/>
+    <mergeCell ref="B161:B162"/>
+    <mergeCell ref="C161:C162"/>
+    <mergeCell ref="B137:B138"/>
+    <mergeCell ref="G153:G154"/>
+    <mergeCell ref="G157:G158"/>
+    <mergeCell ref="C155:C156"/>
+    <mergeCell ref="C141:C142"/>
+    <mergeCell ref="G119:G120"/>
+    <mergeCell ref="G113:G114"/>
+    <mergeCell ref="A73:A74"/>
+    <mergeCell ref="B73:B74"/>
+    <mergeCell ref="C73:C74"/>
+    <mergeCell ref="A57:A58"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="C57:C58"/>
+    <mergeCell ref="A61:A62"/>
+    <mergeCell ref="C61:C62"/>
+    <mergeCell ref="A63:A64"/>
+    <mergeCell ref="B63:B64"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="B59:B60"/>
+    <mergeCell ref="C59:C60"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="A46:H46"/>
+    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="A40:H40"/>
+    <mergeCell ref="G49:G50"/>
+    <mergeCell ref="G51:G52"/>
+    <mergeCell ref="G53:G54"/>
+    <mergeCell ref="G55:G56"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="C51:C52"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="C53:C54"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="A137:A138"/>
+    <mergeCell ref="A123:A124"/>
+    <mergeCell ref="B123:B124"/>
+    <mergeCell ref="A117:A118"/>
+    <mergeCell ref="A133:A134"/>
+    <mergeCell ref="B133:B134"/>
+    <mergeCell ref="C133:C134"/>
+    <mergeCell ref="G213:G214"/>
+    <mergeCell ref="C117:C118"/>
+    <mergeCell ref="B117:B118"/>
+    <mergeCell ref="C123:C124"/>
+    <mergeCell ref="A151:A152"/>
+    <mergeCell ref="B151:B152"/>
+    <mergeCell ref="C151:C152"/>
+    <mergeCell ref="A145:A146"/>
+    <mergeCell ref="B145:B146"/>
+    <mergeCell ref="C145:C146"/>
+    <mergeCell ref="B149:B150"/>
+    <mergeCell ref="C149:C150"/>
+    <mergeCell ref="G149:G150"/>
+    <mergeCell ref="G159:G160"/>
+    <mergeCell ref="A165:A166"/>
+    <mergeCell ref="A161:A162"/>
+    <mergeCell ref="A187:A188"/>
+    <mergeCell ref="B187:B188"/>
+    <mergeCell ref="C171:C172"/>
+    <mergeCell ref="C157:C158"/>
+    <mergeCell ref="G155:G156"/>
+    <mergeCell ref="A155:A156"/>
+    <mergeCell ref="B155:B156"/>
+    <mergeCell ref="A173:A174"/>
+    <mergeCell ref="B173:B174"/>
+    <mergeCell ref="C173:C174"/>
+    <mergeCell ref="G173:G174"/>
+    <mergeCell ref="B157:B158"/>
+    <mergeCell ref="C185:C186"/>
+    <mergeCell ref="A157:A158"/>
+    <mergeCell ref="G185:G186"/>
+    <mergeCell ref="A181:A182"/>
+    <mergeCell ref="B181:B182"/>
+    <mergeCell ref="C167:C168"/>
+    <mergeCell ref="G165:G166"/>
+    <mergeCell ref="G199:G200"/>
+    <mergeCell ref="A197:A198"/>
+    <mergeCell ref="B197:B198"/>
+    <mergeCell ref="C197:C198"/>
+    <mergeCell ref="G193:G194"/>
+    <mergeCell ref="A169:A170"/>
+    <mergeCell ref="B169:B170"/>
+    <mergeCell ref="C169:C170"/>
+    <mergeCell ref="G167:G168"/>
+    <mergeCell ref="A171:A172"/>
+    <mergeCell ref="A185:A186"/>
+    <mergeCell ref="B185:B186"/>
+    <mergeCell ref="A179:A180"/>
+    <mergeCell ref="B179:B180"/>
+    <mergeCell ref="C187:C188"/>
+    <mergeCell ref="B183:B184"/>
+    <mergeCell ref="C183:C184"/>
+    <mergeCell ref="G183:G184"/>
+    <mergeCell ref="G191:G192"/>
+    <mergeCell ref="A189:A190"/>
+    <mergeCell ref="B189:B190"/>
+    <mergeCell ref="G181:G182"/>
+    <mergeCell ref="C189:C190"/>
+    <mergeCell ref="G187:G188"/>
+    <mergeCell ref="A183:A184"/>
+    <mergeCell ref="G147:G148"/>
+    <mergeCell ref="A149:A150"/>
+    <mergeCell ref="A159:A160"/>
+    <mergeCell ref="B159:B160"/>
+    <mergeCell ref="C159:C160"/>
+    <mergeCell ref="G127:G128"/>
+    <mergeCell ref="A153:A154"/>
+    <mergeCell ref="G161:G162"/>
+    <mergeCell ref="C179:C180"/>
+    <mergeCell ref="G177:G178"/>
+    <mergeCell ref="A175:A176"/>
+    <mergeCell ref="B131:B132"/>
+    <mergeCell ref="C131:C132"/>
+    <mergeCell ref="B153:B154"/>
+    <mergeCell ref="C153:C154"/>
+    <mergeCell ref="G151:G152"/>
+    <mergeCell ref="G171:G172"/>
+    <mergeCell ref="B175:B176"/>
+    <mergeCell ref="C175:C176"/>
+    <mergeCell ref="B171:B172"/>
+    <mergeCell ref="A167:A168"/>
+    <mergeCell ref="G169:G170"/>
+    <mergeCell ref="G175:G176"/>
+    <mergeCell ref="G141:G142"/>
+    <mergeCell ref="A141:A142"/>
+    <mergeCell ref="B141:B142"/>
+    <mergeCell ref="A147:A148"/>
+    <mergeCell ref="A125:A126"/>
+    <mergeCell ref="B125:B126"/>
+    <mergeCell ref="C125:C126"/>
+    <mergeCell ref="A135:A136"/>
+    <mergeCell ref="B135:B136"/>
+    <mergeCell ref="C135:C136"/>
+    <mergeCell ref="G139:G140"/>
+    <mergeCell ref="G125:G126"/>
+    <mergeCell ref="A127:A128"/>
+    <mergeCell ref="B127:B128"/>
+    <mergeCell ref="B147:B148"/>
+    <mergeCell ref="C147:C148"/>
+    <mergeCell ref="G145:G146"/>
+    <mergeCell ref="A143:A144"/>
+    <mergeCell ref="B143:B144"/>
+    <mergeCell ref="C143:C144"/>
+    <mergeCell ref="A139:A140"/>
+    <mergeCell ref="B139:B140"/>
+    <mergeCell ref="C139:C140"/>
+    <mergeCell ref="G135:G136"/>
+    <mergeCell ref="G75:G76"/>
+    <mergeCell ref="G97:G98"/>
+    <mergeCell ref="G83:G84"/>
+    <mergeCell ref="G91:G92"/>
+    <mergeCell ref="G81:G82"/>
+    <mergeCell ref="G89:G90"/>
+    <mergeCell ref="G99:G100"/>
+    <mergeCell ref="C137:C138"/>
+    <mergeCell ref="G137:G138"/>
+    <mergeCell ref="G115:G116"/>
+    <mergeCell ref="G107:G108"/>
+    <mergeCell ref="G109:G110"/>
+    <mergeCell ref="C109:C110"/>
+    <mergeCell ref="C101:C102"/>
+    <mergeCell ref="C75:C76"/>
+    <mergeCell ref="C113:C114"/>
+    <mergeCell ref="C111:C112"/>
+    <mergeCell ref="C115:C116"/>
+    <mergeCell ref="G121:G122"/>
+    <mergeCell ref="C121:C122"/>
+    <mergeCell ref="A131:A132"/>
+    <mergeCell ref="A101:A102"/>
+    <mergeCell ref="B101:B102"/>
+    <mergeCell ref="A107:A108"/>
+    <mergeCell ref="A95:A96"/>
+    <mergeCell ref="B95:B96"/>
+    <mergeCell ref="C95:C96"/>
+    <mergeCell ref="B107:B108"/>
+    <mergeCell ref="C107:C108"/>
+    <mergeCell ref="A103:A104"/>
+    <mergeCell ref="B97:B98"/>
+    <mergeCell ref="C97:C98"/>
+    <mergeCell ref="A113:A114"/>
+    <mergeCell ref="B113:B114"/>
+    <mergeCell ref="A111:A112"/>
+    <mergeCell ref="B111:B112"/>
+    <mergeCell ref="A115:A116"/>
+    <mergeCell ref="B115:B116"/>
+    <mergeCell ref="A121:A122"/>
+    <mergeCell ref="B121:B122"/>
+    <mergeCell ref="B81:B82"/>
+    <mergeCell ref="C81:C82"/>
+    <mergeCell ref="G131:G132"/>
+    <mergeCell ref="G105:G106"/>
+    <mergeCell ref="G95:G96"/>
+    <mergeCell ref="G79:G80"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="C93:C94"/>
+    <mergeCell ref="G93:G94"/>
+    <mergeCell ref="B109:B110"/>
+    <mergeCell ref="A97:A98"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="C99:C100"/>
+    <mergeCell ref="A93:A94"/>
+    <mergeCell ref="G65:G66"/>
+    <mergeCell ref="A67:A68"/>
+    <mergeCell ref="B67:B68"/>
+    <mergeCell ref="B83:B84"/>
+    <mergeCell ref="C83:C84"/>
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="B87:B88"/>
+    <mergeCell ref="C91:C92"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="G67:G68"/>
+    <mergeCell ref="A71:A72"/>
+    <mergeCell ref="C71:C72"/>
+    <mergeCell ref="G71:G72"/>
+    <mergeCell ref="B71:B72"/>
+    <mergeCell ref="C65:C66"/>
+    <mergeCell ref="G73:G74"/>
+    <mergeCell ref="A75:A76"/>
+    <mergeCell ref="B75:B76"/>
+    <mergeCell ref="A81:A82"/>
+    <mergeCell ref="B89:B90"/>
+    <mergeCell ref="C85:C86"/>
+    <mergeCell ref="A85:A86"/>
+    <mergeCell ref="B85:B86"/>
+    <mergeCell ref="C223:C224"/>
+    <mergeCell ref="G221:G222"/>
+    <mergeCell ref="G197:G198"/>
+    <mergeCell ref="A223:A224"/>
+    <mergeCell ref="G219:G220"/>
+    <mergeCell ref="A209:A210"/>
+    <mergeCell ref="B209:B210"/>
+    <mergeCell ref="C209:C210"/>
+    <mergeCell ref="G223:G224"/>
+    <mergeCell ref="B223:B224"/>
+    <mergeCell ref="A221:A222"/>
+    <mergeCell ref="B221:B222"/>
+    <mergeCell ref="C221:C222"/>
+    <mergeCell ref="G217:G218"/>
+    <mergeCell ref="A211:A212"/>
+    <mergeCell ref="B211:B212"/>
+    <mergeCell ref="C211:C212"/>
+    <mergeCell ref="B213:B214"/>
+    <mergeCell ref="C213:C214"/>
+    <mergeCell ref="B93:B94"/>
+    <mergeCell ref="A207:A208"/>
+    <mergeCell ref="A219:A220"/>
+    <mergeCell ref="B219:B220"/>
+    <mergeCell ref="C219:C220"/>
+    <mergeCell ref="C217:C218"/>
+    <mergeCell ref="B103:B104"/>
+    <mergeCell ref="C103:C104"/>
+    <mergeCell ref="G101:G102"/>
+    <mergeCell ref="A129:A130"/>
+    <mergeCell ref="B129:B130"/>
+    <mergeCell ref="A213:A214"/>
+    <mergeCell ref="G211:G212"/>
+    <mergeCell ref="G195:G196"/>
+    <mergeCell ref="C181:C182"/>
+    <mergeCell ref="G179:G180"/>
+    <mergeCell ref="A163:A164"/>
+    <mergeCell ref="B163:B164"/>
+    <mergeCell ref="C163:C164"/>
+    <mergeCell ref="G189:G190"/>
+    <mergeCell ref="A177:A178"/>
+    <mergeCell ref="B177:B178"/>
+    <mergeCell ref="G163:G164"/>
+    <mergeCell ref="C127:C128"/>
+    <mergeCell ref="A109:A110"/>
+    <mergeCell ref="G215:G216"/>
+    <mergeCell ref="B215:B216"/>
+    <mergeCell ref="B207:B208"/>
+    <mergeCell ref="A105:A106"/>
+    <mergeCell ref="A217:A218"/>
+    <mergeCell ref="B217:B218"/>
+    <mergeCell ref="C215:C216"/>
+    <mergeCell ref="G207:G208"/>
+    <mergeCell ref="A205:A206"/>
+    <mergeCell ref="B205:B206"/>
+    <mergeCell ref="C205:C206"/>
+    <mergeCell ref="G205:G206"/>
+    <mergeCell ref="A203:A204"/>
+    <mergeCell ref="B203:B204"/>
+    <mergeCell ref="C203:C204"/>
+    <mergeCell ref="G203:G204"/>
+    <mergeCell ref="G209:G210"/>
+    <mergeCell ref="A215:A216"/>
+    <mergeCell ref="G111:G112"/>
+    <mergeCell ref="G123:G124"/>
+    <mergeCell ref="B165:B166"/>
+    <mergeCell ref="C165:C166"/>
+    <mergeCell ref="B167:B168"/>
+    <mergeCell ref="C177:C178"/>
+    <mergeCell ref="G61:G62"/>
+    <mergeCell ref="C67:C68"/>
+    <mergeCell ref="G201:G202"/>
+    <mergeCell ref="A193:A194"/>
+    <mergeCell ref="B193:B194"/>
+    <mergeCell ref="C193:C194"/>
+    <mergeCell ref="A199:A200"/>
+    <mergeCell ref="B199:B200"/>
+    <mergeCell ref="C199:C200"/>
+    <mergeCell ref="A201:A202"/>
+    <mergeCell ref="B201:B202"/>
+    <mergeCell ref="C201:C202"/>
+    <mergeCell ref="A83:A84"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="G63:G64"/>
+    <mergeCell ref="B105:B106"/>
+    <mergeCell ref="C105:C106"/>
+    <mergeCell ref="G103:G104"/>
+    <mergeCell ref="A69:A70"/>
+    <mergeCell ref="B69:B70"/>
+    <mergeCell ref="C69:C70"/>
+    <mergeCell ref="G69:G70"/>
+    <mergeCell ref="A89:A90"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A195:A196"/>
+    <mergeCell ref="B195:B196"/>
+    <mergeCell ref="C195:C196"/>
+    <mergeCell ref="A191:A192"/>
+    <mergeCell ref="B191:B192"/>
+    <mergeCell ref="C191:C192"/>
+    <mergeCell ref="G85:G86"/>
+    <mergeCell ref="A119:A120"/>
+    <mergeCell ref="B119:B120"/>
+    <mergeCell ref="C119:C120"/>
+    <mergeCell ref="G117:G118"/>
+    <mergeCell ref="A79:A80"/>
+    <mergeCell ref="B79:B80"/>
+    <mergeCell ref="C79:C80"/>
+    <mergeCell ref="A77:A78"/>
+    <mergeCell ref="B77:B78"/>
+    <mergeCell ref="C77:C78"/>
+    <mergeCell ref="G77:G78"/>
     <mergeCell ref="C22:F22"/>
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="C19:F19"/>
@@ -7635,374 +8054,6 @@
     <mergeCell ref="C24:F24"/>
     <mergeCell ref="C25:F25"/>
     <mergeCell ref="C26:F26"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A194:A195"/>
-    <mergeCell ref="B194:B195"/>
-    <mergeCell ref="C194:C195"/>
-    <mergeCell ref="A190:A191"/>
-    <mergeCell ref="B190:B191"/>
-    <mergeCell ref="C190:C191"/>
-    <mergeCell ref="G84:G85"/>
-    <mergeCell ref="A118:A119"/>
-    <mergeCell ref="B118:B119"/>
-    <mergeCell ref="C118:C119"/>
-    <mergeCell ref="G116:G117"/>
-    <mergeCell ref="A78:A79"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="C76:C77"/>
-    <mergeCell ref="G76:G77"/>
-    <mergeCell ref="G60:G61"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="G200:G201"/>
-    <mergeCell ref="A192:A193"/>
-    <mergeCell ref="B192:B193"/>
-    <mergeCell ref="C192:C193"/>
-    <mergeCell ref="A198:A199"/>
-    <mergeCell ref="B198:B199"/>
-    <mergeCell ref="C198:C199"/>
-    <mergeCell ref="A200:A201"/>
-    <mergeCell ref="B200:B201"/>
-    <mergeCell ref="C200:C201"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="A90:A91"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="G62:G63"/>
-    <mergeCell ref="B104:B105"/>
-    <mergeCell ref="C104:C105"/>
-    <mergeCell ref="G102:G103"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="C68:C69"/>
-    <mergeCell ref="G68:G69"/>
-    <mergeCell ref="G214:G215"/>
-    <mergeCell ref="B214:B215"/>
-    <mergeCell ref="B206:B207"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="A216:A217"/>
-    <mergeCell ref="B216:B217"/>
-    <mergeCell ref="C214:C215"/>
-    <mergeCell ref="G206:G207"/>
-    <mergeCell ref="A204:A205"/>
-    <mergeCell ref="B204:B205"/>
-    <mergeCell ref="C204:C205"/>
-    <mergeCell ref="G204:G205"/>
-    <mergeCell ref="A202:A203"/>
-    <mergeCell ref="B202:B203"/>
-    <mergeCell ref="C202:C203"/>
-    <mergeCell ref="G202:G203"/>
-    <mergeCell ref="G208:G209"/>
-    <mergeCell ref="A214:A215"/>
-    <mergeCell ref="G110:G111"/>
-    <mergeCell ref="G122:G123"/>
-    <mergeCell ref="B164:B165"/>
-    <mergeCell ref="C164:C165"/>
-    <mergeCell ref="B166:B167"/>
-    <mergeCell ref="C176:C177"/>
-    <mergeCell ref="A206:A207"/>
-    <mergeCell ref="A218:A219"/>
-    <mergeCell ref="B218:B219"/>
-    <mergeCell ref="C218:C219"/>
-    <mergeCell ref="C216:C217"/>
-    <mergeCell ref="B102:B103"/>
-    <mergeCell ref="C102:C103"/>
-    <mergeCell ref="G100:G101"/>
-    <mergeCell ref="A128:A129"/>
-    <mergeCell ref="B128:B129"/>
-    <mergeCell ref="A212:A213"/>
-    <mergeCell ref="G210:G211"/>
-    <mergeCell ref="G194:G195"/>
-    <mergeCell ref="C180:C181"/>
-    <mergeCell ref="G178:G179"/>
-    <mergeCell ref="A162:A163"/>
-    <mergeCell ref="B162:B163"/>
-    <mergeCell ref="C162:C163"/>
-    <mergeCell ref="G188:G189"/>
-    <mergeCell ref="A176:A177"/>
-    <mergeCell ref="B176:B177"/>
-    <mergeCell ref="G162:G163"/>
-    <mergeCell ref="C126:C127"/>
-    <mergeCell ref="A88:A89"/>
-    <mergeCell ref="B88:B89"/>
-    <mergeCell ref="C84:C85"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="B84:B85"/>
-    <mergeCell ref="C222:C223"/>
-    <mergeCell ref="G220:G221"/>
-    <mergeCell ref="G196:G197"/>
-    <mergeCell ref="A222:A223"/>
-    <mergeCell ref="G218:G219"/>
-    <mergeCell ref="A208:A209"/>
-    <mergeCell ref="B208:B209"/>
-    <mergeCell ref="C208:C209"/>
-    <mergeCell ref="G222:G223"/>
-    <mergeCell ref="B222:B223"/>
-    <mergeCell ref="A220:A221"/>
-    <mergeCell ref="B220:B221"/>
-    <mergeCell ref="C220:C221"/>
-    <mergeCell ref="G216:G217"/>
-    <mergeCell ref="A210:A211"/>
-    <mergeCell ref="B210:B211"/>
-    <mergeCell ref="C210:C211"/>
-    <mergeCell ref="B212:B213"/>
-    <mergeCell ref="C212:C213"/>
-    <mergeCell ref="B92:B93"/>
-    <mergeCell ref="A96:A97"/>
-    <mergeCell ref="A98:A99"/>
-    <mergeCell ref="B98:B99"/>
-    <mergeCell ref="C98:C99"/>
-    <mergeCell ref="A92:A93"/>
-    <mergeCell ref="G64:G65"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="C82:C83"/>
-    <mergeCell ref="A86:A87"/>
-    <mergeCell ref="B86:B87"/>
-    <mergeCell ref="C90:C91"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="G66:G67"/>
-    <mergeCell ref="A70:A71"/>
-    <mergeCell ref="C70:C71"/>
-    <mergeCell ref="G70:G71"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="C64:C65"/>
-    <mergeCell ref="G72:G73"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="A80:A81"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="C80:C81"/>
-    <mergeCell ref="G130:G131"/>
-    <mergeCell ref="G104:G105"/>
-    <mergeCell ref="G94:G95"/>
-    <mergeCell ref="G78:G79"/>
-    <mergeCell ref="C86:C87"/>
-    <mergeCell ref="C92:C93"/>
-    <mergeCell ref="G92:G93"/>
-    <mergeCell ref="A108:A109"/>
-    <mergeCell ref="B108:B109"/>
-    <mergeCell ref="A130:A131"/>
-    <mergeCell ref="A100:A101"/>
-    <mergeCell ref="B100:B101"/>
-    <mergeCell ref="A106:A107"/>
-    <mergeCell ref="A94:A95"/>
-    <mergeCell ref="B94:B95"/>
-    <mergeCell ref="C94:C95"/>
-    <mergeCell ref="B106:B107"/>
-    <mergeCell ref="C106:C107"/>
-    <mergeCell ref="A102:A103"/>
-    <mergeCell ref="B96:B97"/>
-    <mergeCell ref="C96:C97"/>
-    <mergeCell ref="G74:G75"/>
-    <mergeCell ref="G96:G97"/>
-    <mergeCell ref="G82:G83"/>
-    <mergeCell ref="G90:G91"/>
-    <mergeCell ref="G80:G81"/>
-    <mergeCell ref="G88:G89"/>
-    <mergeCell ref="G98:G99"/>
-    <mergeCell ref="C136:C137"/>
-    <mergeCell ref="G136:G137"/>
-    <mergeCell ref="G114:G115"/>
-    <mergeCell ref="G106:G107"/>
-    <mergeCell ref="G108:G109"/>
-    <mergeCell ref="C108:C109"/>
-    <mergeCell ref="C100:C101"/>
-    <mergeCell ref="C74:C75"/>
-    <mergeCell ref="G140:G141"/>
-    <mergeCell ref="A140:A141"/>
-    <mergeCell ref="B140:B141"/>
-    <mergeCell ref="A146:A147"/>
-    <mergeCell ref="A124:A125"/>
-    <mergeCell ref="B124:B125"/>
-    <mergeCell ref="C124:C125"/>
-    <mergeCell ref="A134:A135"/>
-    <mergeCell ref="B134:B135"/>
-    <mergeCell ref="C134:C135"/>
-    <mergeCell ref="G138:G139"/>
-    <mergeCell ref="G124:G125"/>
-    <mergeCell ref="A182:A183"/>
-    <mergeCell ref="G146:G147"/>
-    <mergeCell ref="A148:A149"/>
-    <mergeCell ref="A158:A159"/>
-    <mergeCell ref="B158:B159"/>
-    <mergeCell ref="C158:C159"/>
-    <mergeCell ref="G126:G127"/>
-    <mergeCell ref="A152:A153"/>
-    <mergeCell ref="G160:G161"/>
-    <mergeCell ref="C178:C179"/>
-    <mergeCell ref="G176:G177"/>
-    <mergeCell ref="A174:A175"/>
-    <mergeCell ref="A112:A113"/>
-    <mergeCell ref="B112:B113"/>
-    <mergeCell ref="C112:C113"/>
-    <mergeCell ref="B130:B131"/>
-    <mergeCell ref="C130:C131"/>
-    <mergeCell ref="A110:A111"/>
-    <mergeCell ref="B110:B111"/>
-    <mergeCell ref="C110:C111"/>
-    <mergeCell ref="G198:G199"/>
-    <mergeCell ref="A196:A197"/>
-    <mergeCell ref="B196:B197"/>
-    <mergeCell ref="C196:C197"/>
-    <mergeCell ref="G192:G193"/>
-    <mergeCell ref="A168:A169"/>
-    <mergeCell ref="B168:B169"/>
-    <mergeCell ref="C168:C169"/>
-    <mergeCell ref="G166:G167"/>
-    <mergeCell ref="A170:A171"/>
-    <mergeCell ref="A184:A185"/>
-    <mergeCell ref="B184:B185"/>
-    <mergeCell ref="A178:A179"/>
-    <mergeCell ref="B178:B179"/>
-    <mergeCell ref="C186:C187"/>
-    <mergeCell ref="B182:B183"/>
-    <mergeCell ref="C182:C183"/>
-    <mergeCell ref="G182:G183"/>
-    <mergeCell ref="G190:G191"/>
-    <mergeCell ref="A188:A189"/>
-    <mergeCell ref="B188:B189"/>
-    <mergeCell ref="G180:G181"/>
-    <mergeCell ref="C188:C189"/>
-    <mergeCell ref="G186:G187"/>
-    <mergeCell ref="B152:B153"/>
-    <mergeCell ref="C152:C153"/>
-    <mergeCell ref="G150:G151"/>
-    <mergeCell ref="G170:G171"/>
-    <mergeCell ref="B174:B175"/>
-    <mergeCell ref="C174:C175"/>
-    <mergeCell ref="B170:B171"/>
-    <mergeCell ref="A166:A167"/>
-    <mergeCell ref="G168:G169"/>
-    <mergeCell ref="G174:G175"/>
-    <mergeCell ref="G158:G159"/>
-    <mergeCell ref="A164:A165"/>
-    <mergeCell ref="A160:A161"/>
-    <mergeCell ref="A186:A187"/>
-    <mergeCell ref="B186:B187"/>
-    <mergeCell ref="C170:C171"/>
-    <mergeCell ref="C156:C157"/>
-    <mergeCell ref="G154:G155"/>
-    <mergeCell ref="A154:A155"/>
-    <mergeCell ref="B154:B155"/>
-    <mergeCell ref="A172:A173"/>
-    <mergeCell ref="B172:B173"/>
-    <mergeCell ref="C172:C173"/>
-    <mergeCell ref="G172:G173"/>
-    <mergeCell ref="B156:B157"/>
-    <mergeCell ref="A126:A127"/>
-    <mergeCell ref="B126:B127"/>
-    <mergeCell ref="C184:C185"/>
-    <mergeCell ref="A156:A157"/>
-    <mergeCell ref="G184:G185"/>
-    <mergeCell ref="A180:A181"/>
-    <mergeCell ref="B180:B181"/>
-    <mergeCell ref="C166:C167"/>
-    <mergeCell ref="G164:G165"/>
-    <mergeCell ref="B146:B147"/>
-    <mergeCell ref="C146:C147"/>
-    <mergeCell ref="G144:G145"/>
-    <mergeCell ref="A142:A143"/>
-    <mergeCell ref="B142:B143"/>
-    <mergeCell ref="C142:C143"/>
-    <mergeCell ref="A150:A151"/>
-    <mergeCell ref="B150:B151"/>
-    <mergeCell ref="C150:C151"/>
-    <mergeCell ref="A144:A145"/>
-    <mergeCell ref="B144:B145"/>
-    <mergeCell ref="C144:C145"/>
-    <mergeCell ref="B148:B149"/>
-    <mergeCell ref="C148:C149"/>
-    <mergeCell ref="G148:G149"/>
-    <mergeCell ref="A114:A115"/>
-    <mergeCell ref="B114:B115"/>
-    <mergeCell ref="C114:C115"/>
-    <mergeCell ref="A138:A139"/>
-    <mergeCell ref="B138:B139"/>
-    <mergeCell ref="C138:C139"/>
-    <mergeCell ref="G134:G135"/>
-    <mergeCell ref="G120:G121"/>
-    <mergeCell ref="A120:A121"/>
-    <mergeCell ref="B120:B121"/>
-    <mergeCell ref="C120:C121"/>
-    <mergeCell ref="A136:A137"/>
-    <mergeCell ref="A122:A123"/>
-    <mergeCell ref="B122:B123"/>
-    <mergeCell ref="A116:A117"/>
-    <mergeCell ref="A132:A133"/>
-    <mergeCell ref="B132:B133"/>
-    <mergeCell ref="C132:C133"/>
-    <mergeCell ref="G212:G213"/>
-    <mergeCell ref="C116:C117"/>
-    <mergeCell ref="B116:B117"/>
-    <mergeCell ref="C122:C123"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="A45:H45"/>
-    <mergeCell ref="A46:H46"/>
-    <mergeCell ref="A39:H39"/>
-    <mergeCell ref="G48:G49"/>
-    <mergeCell ref="G50:G51"/>
-    <mergeCell ref="G52:G53"/>
-    <mergeCell ref="G54:G55"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="A62:A63"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="G56:G57"/>
-    <mergeCell ref="G58:G59"/>
-    <mergeCell ref="C206:C207"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C62:C63"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="G86:G87"/>
-    <mergeCell ref="C88:C89"/>
-    <mergeCell ref="G128:G129"/>
-    <mergeCell ref="C128:C129"/>
-    <mergeCell ref="G142:G143"/>
-    <mergeCell ref="B160:B161"/>
-    <mergeCell ref="C160:C161"/>
-    <mergeCell ref="B136:B137"/>
-    <mergeCell ref="G152:G153"/>
-    <mergeCell ref="G156:G157"/>
-    <mergeCell ref="C154:C155"/>
-    <mergeCell ref="C140:C141"/>
-    <mergeCell ref="G118:G119"/>
-    <mergeCell ref="G112:G113"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/main/resources/InesModResources/杀戮尖塔自制--伊内丝v0.2.xlsx
+++ b/src/main/resources/InesModResources/杀戮尖塔自制--伊内丝v0.2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\myMod\InesMod\InesMod\src\main\resources\InesModResources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFABF430-5FEC-4544-9A1E-264FDB002D1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05F84A5A-BBE3-438E-82E5-3A819889CAB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{7A3E14A4-2175-4856-859A-887D335814F1}"/>
   </bookViews>
@@ -7026,7 +7026,7 @@
       </c>
     </row>
     <row r="197" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A197" s="30">
+      <c r="A197" s="44">
         <v>75</v>
       </c>
       <c r="B197" s="36" t="s">
@@ -7052,7 +7052,7 @@
       </c>
     </row>
     <row r="198" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A198" s="31"/>
+      <c r="A198" s="45"/>
       <c r="B198" s="36"/>
       <c r="C198" s="26"/>
       <c r="D198" s="5" t="s">
@@ -7114,7 +7114,7 @@
       </c>
     </row>
     <row r="201" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A201" s="30">
+      <c r="A201" s="44">
         <v>77</v>
       </c>
       <c r="B201" s="36" t="s">
@@ -7140,7 +7140,7 @@
       </c>
     </row>
     <row r="202" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A202" s="31"/>
+      <c r="A202" s="45"/>
       <c r="B202" s="36"/>
       <c r="C202" s="26"/>
       <c r="D202" s="5" t="s">
@@ -7286,7 +7286,7 @@
       </c>
     </row>
     <row r="209" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A209" s="30">
+      <c r="A209" s="44">
         <v>81</v>
       </c>
       <c r="B209" s="36" t="s">
@@ -7312,7 +7312,7 @@
       </c>
     </row>
     <row r="210" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A210" s="31"/>
+      <c r="A210" s="45"/>
       <c r="B210" s="36"/>
       <c r="C210" s="26"/>
       <c r="D210" s="5" t="s">

--- a/src/main/resources/InesModResources/杀戮尖塔自制--伊内丝v0.2.xlsx
+++ b/src/main/resources/InesModResources/杀戮尖塔自制--伊内丝v0.2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\myMod\InesMod\InesMod\src\main\resources\InesModResources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05F84A5A-BBE3-438E-82E5-3A819889CAB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11E061CB-8AD1-4721-B8B9-104FB18BC9E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{7A3E14A4-2175-4856-859A-887D335814F1}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="647">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="660">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -643,18 +643,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>获得3-11点随机格挡。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>行踪不定+</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>获得4-16点随机格挡。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>心灵探查</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -803,14 +795,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>本次战斗后选择奖励牌时，可供选择的牌数增加1张。消耗。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>本次战斗后选择奖励牌时，可供选择的牌数增加1张。消耗。虚无。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>额外收获</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1007,9 +991,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>你的回合开始时，获得1层偷取。</t>
-  </si>
-  <si>
     <t>你的回合开始时，获得2层偷取。</t>
   </si>
   <si>
@@ -1192,14 +1173,6 @@
   </si>
   <si>
     <t>如果未处于隐匿，获得1层隐匿。否则获得2点能量。消耗。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>造成9点伤害。本回合内，在隐匿下打出攻击牌不消耗影哨。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>造成11点伤害。本回合内，在隐匿下打出攻击牌不消耗影哨。保留。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1953,15 +1926,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>攻击后消耗1层偷取，使所有命中目标失去1点临时力量，同时自身获得1点临时力量。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>对所有敌人造成11点伤害。消耗等同于敌人数量的偷取。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>对所有敌人造成15点伤害。消耗等同于敌人数量的偷取。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2098,18 +2063,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>只有在隐匿下才能打出。造成9点伤害2次。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>只有在隐匿下才能打出。造成12点伤害2次。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>此牌可消耗多层偷取。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>抽2张牌。获得2层偷取和1点能量。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2135,10 +2088,6 @@
   </si>
   <si>
     <t>必须有1点情报才能打出。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>造成8点伤害。获得1层隐匿。本回合你无法再打出攻击牌。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2394,23 +2343,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>造成8点伤害。消耗所有偷取，每层额外给予1层虚弱。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>造成14点伤害。消耗所有偷取，每层额外给予1层虚弱。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>每消耗1张影哨，对所有敌人造成3点伤害。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>拥有4层偷取时，偷取额外使目标获得1层易伤。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>拥有3层偷取时，偷取额外使目标获得1层易伤。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2447,6 +2380,134 @@
   </si>
   <si>
     <t>No Invisibility</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成7点伤害。本回合内，在隐匿下打出攻击牌改为丢弃影哨。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成9点伤害。本回合内，在隐匿下打出攻击牌改为丢弃影哨。保留。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你的回合开始时，获得1层偷取。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动打出。获得10点格挡。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动打出。获得14点格挡。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">攻击后消耗1层偷取，使所有命中目标失去1点临时力量，同时自身获得1点临时力量。
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>参考转经轮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本次战斗后额外掉落一次卡牌奖励。消耗。虚无。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本次战斗后额外掉落一次卡牌奖励。消耗。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>隐藏机制</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>真相
+（物品）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>远期设想：新地图</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主要为主线9-14章的boss，包括曼弗雷德、血魔大君、蒸汽骑士等</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>显示在右上角
+1=牌，2=稀有牌，3=遗物，5=结局遗物，自由行动但是限一次。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>从战斗中收集的所有真相，可在休息处解析为奖励，甚至从中触及高塔的秘密……</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>洞悉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Insight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>truth</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>直接consumeNum+1。
+（要求可以考虑改成+20%向上取整，或计入情报消耗。）
+弹一个弹窗：“提示：一次战斗中累计消耗10层偷取，即可获得1层洞悉。
+每有1层洞悉，攻击额外视为消耗1层偷取，战斗结束后获得1点真相。”
+出现真相这个power后，描述中显示进度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击额外生效1层偷取（不视作消耗），战斗结束后获得1点真相。
+消耗偷取x/10层：获得1层洞悉，并使所需层数+2。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>此牌可消耗多层偷取。上虚弱是卡牌的单独action</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对所有敌人造成8点伤害。消耗等同于敌人数量的偷取。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成9点伤害。获得1层隐匿。本回合你无法再打出攻击牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成6点伤害2次。消耗所有偷取，每层额外给予1层虚弱。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成8点伤害2次。消耗所有偷取，每层额外给予1层虚弱。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>只有在隐匿下才能打出。造成18点伤害。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>只有在隐匿下才能打出。造成22点伤害。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拥有4层偷取时，每消耗1层偷取给予1层易伤。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拥有3层偷取时，每消耗1层偷取给予1层易伤。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2648,7 +2709,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2718,6 +2779,9 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2728,6 +2792,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2739,31 +2830,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2772,7 +2842,19 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2781,23 +2863,8 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3120,7 +3187,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42CD751D-9911-4397-9269-1058B93A73AF}">
-  <dimension ref="A1:L236"/>
+  <dimension ref="A1:L253"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="3" width="9.1328125" customWidth="1"/>
@@ -3132,10 +3199,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="26" t="s">
-        <v>321</v>
-      </c>
-      <c r="B1" s="26"/>
+      <c r="A1" s="28" t="s">
+        <v>314</v>
+      </c>
+      <c r="B1" s="28"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -3143,10 +3210,10 @@
     </row>
     <row r="2" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="7" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="12"/>
@@ -3157,10 +3224,10 @@
     </row>
     <row r="3" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -3187,29 +3254,29 @@
       <c r="B6" s="2"/>
     </row>
     <row r="8" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="37" t="s">
         <v>108</v>
       </c>
-      <c r="B8" s="28"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="29"/>
+      <c r="B8" s="38"/>
+      <c r="C8" s="38"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="39"/>
     </row>
     <row r="9" spans="1:8" ht="25.7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C9" s="27" t="s">
-        <v>244</v>
-      </c>
-      <c r="D9" s="28"/>
-      <c r="E9" s="29"/>
+        <v>239</v>
+      </c>
+      <c r="C9" s="37" t="s">
+        <v>240</v>
+      </c>
+      <c r="D9" s="38"/>
+      <c r="E9" s="39"/>
       <c r="F9" s="8" t="s">
         <v>2</v>
       </c>
@@ -3217,7 +3284,7 @@
         <v>3</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
@@ -3227,134 +3294,134 @@
       <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="28" t="s">
-        <v>246</v>
-      </c>
-      <c r="D10" s="28"/>
-      <c r="E10" s="29"/>
+      <c r="C10" s="38" t="s">
+        <v>242</v>
+      </c>
+      <c r="D10" s="38"/>
+      <c r="E10" s="39"/>
       <c r="F10" s="9" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="G10" s="10"/>
       <c r="H10" s="17" t="s">
-        <v>539</v>
+        <v>530</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="C11" s="27" t="s">
-        <v>250</v>
-      </c>
-      <c r="D11" s="28"/>
-      <c r="E11" s="29"/>
+        <v>260</v>
+      </c>
+      <c r="C11" s="37" t="s">
+        <v>246</v>
+      </c>
+      <c r="D11" s="38"/>
+      <c r="E11" s="39"/>
       <c r="F11" s="9" t="s">
-        <v>551</v>
+        <v>542</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="H11" s="17" t="s">
-        <v>540</v>
+        <v>531</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C12" s="37" t="s">
+        <v>499</v>
+      </c>
+      <c r="D12" s="38"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="9" t="s">
         <v>253</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="C12" s="27" t="s">
-        <v>506</v>
-      </c>
-      <c r="D12" s="28"/>
-      <c r="E12" s="29"/>
-      <c r="F12" s="9" t="s">
-        <v>258</v>
       </c>
       <c r="G12" s="10"/>
       <c r="H12" s="17" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="C13" s="23" t="s">
-        <v>487</v>
-      </c>
-      <c r="D13" s="28"/>
-      <c r="E13" s="29"/>
+        <v>241</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>480</v>
+      </c>
+      <c r="D13" s="38"/>
+      <c r="E13" s="39"/>
       <c r="F13" s="9" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="G13" s="10"/>
       <c r="H13" s="17" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="C14" s="28" t="s">
-        <v>317</v>
-      </c>
-      <c r="D14" s="28"/>
-      <c r="E14" s="29"/>
+        <v>241</v>
+      </c>
+      <c r="C14" s="38" t="s">
+        <v>310</v>
+      </c>
+      <c r="D14" s="38"/>
+      <c r="E14" s="39"/>
       <c r="F14" s="9" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="G14" s="10"/>
       <c r="H14" s="17" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="16" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="17" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="26" t="s">
+      <c r="A18" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="B18" s="26"/>
-      <c r="C18" s="26"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="26"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="28"/>
     </row>
     <row r="19" spans="1:8" ht="25.7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>497</v>
-      </c>
-      <c r="C19" s="27" t="s">
+        <v>490</v>
+      </c>
+      <c r="C19" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="29"/>
+      <c r="D19" s="38"/>
+      <c r="E19" s="38"/>
+      <c r="F19" s="39"/>
       <c r="G19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
@@ -3362,192 +3429,192 @@
         <v>8</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="C20" s="23" t="s">
-        <v>525</v>
-      </c>
-      <c r="D20" s="24"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="25"/>
+        <v>489</v>
+      </c>
+      <c r="C20" s="24" t="s">
+        <v>635</v>
+      </c>
+      <c r="D20" s="25"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="26"/>
       <c r="G20" s="5" t="s">
-        <v>557</v>
+        <v>548</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
     </row>
     <row r="21" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="19" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="C21" s="23" t="s">
-        <v>559</v>
-      </c>
-      <c r="D21" s="24"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="25"/>
+        <v>489</v>
+      </c>
+      <c r="C21" s="24" t="s">
+        <v>550</v>
+      </c>
+      <c r="D21" s="25"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="26"/>
       <c r="G21" s="5" t="s">
-        <v>556</v>
+        <v>547</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
     </row>
     <row r="22" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="19" t="s">
-        <v>553</v>
+        <v>544</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="C22" s="23" t="s">
-        <v>560</v>
-      </c>
-      <c r="D22" s="24"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="25"/>
+        <v>491</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>551</v>
+      </c>
+      <c r="D22" s="25"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="26"/>
       <c r="G22" s="5" t="s">
-        <v>554</v>
+        <v>545</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>555</v>
+        <v>546</v>
       </c>
     </row>
     <row r="23" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="19" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="C23" s="23" t="s">
-        <v>582</v>
-      </c>
-      <c r="D23" s="24"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="25"/>
+        <v>489</v>
+      </c>
+      <c r="C23" s="24" t="s">
+        <v>569</v>
+      </c>
+      <c r="D23" s="25"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="26"/>
       <c r="G23" s="4" t="s">
-        <v>583</v>
+        <v>570</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="19" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="C24" s="23" t="s">
-        <v>501</v>
-      </c>
-      <c r="D24" s="24"/>
-      <c r="E24" s="24"/>
-      <c r="F24" s="25"/>
+        <v>491</v>
+      </c>
+      <c r="C24" s="24" t="s">
+        <v>494</v>
+      </c>
+      <c r="D24" s="25"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="26"/>
       <c r="G24" s="5" t="s">
-        <v>609</v>
+        <v>596</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="20" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="C25" s="23" t="s">
-        <v>502</v>
-      </c>
-      <c r="D25" s="24"/>
-      <c r="E25" s="24"/>
-      <c r="F25" s="25"/>
+        <v>491</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>495</v>
+      </c>
+      <c r="D25" s="25"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="26"/>
       <c r="G25" s="5" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="20" t="s">
-        <v>644</v>
+        <v>627</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="C26" s="23" t="s">
-        <v>645</v>
-      </c>
-      <c r="D26" s="24"/>
-      <c r="E26" s="24"/>
-      <c r="F26" s="25"/>
+        <v>491</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>628</v>
+      </c>
+      <c r="D26" s="25"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="26"/>
       <c r="G26" s="4"/>
       <c r="H26" s="16" t="s">
-        <v>646</v>
+        <v>629</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="1" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="C27" s="24" t="s">
         <v>498</v>
       </c>
-      <c r="C27" s="23" t="s">
-        <v>505</v>
-      </c>
-      <c r="D27" s="24"/>
-      <c r="E27" s="24"/>
-      <c r="F27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="26"/>
       <c r="G27" s="4" t="s">
-        <v>610</v>
+        <v>597</v>
       </c>
       <c r="H27" s="16" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="29" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="1:8" ht="21.7" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="31" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="26" t="s">
-        <v>541</v>
-      </c>
-      <c r="B31" s="26"/>
-      <c r="C31" s="26"/>
-      <c r="D31" s="26"/>
-      <c r="E31" s="26"/>
-      <c r="F31" s="26"/>
-      <c r="G31" s="26"/>
-      <c r="H31" s="26"/>
+      <c r="A31" s="28" t="s">
+        <v>532</v>
+      </c>
+      <c r="B31" s="28"/>
+      <c r="C31" s="28"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="28"/>
+      <c r="G31" s="28"/>
+      <c r="H31" s="28"/>
     </row>
     <row r="32" spans="1:8" ht="25.7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>497</v>
-      </c>
-      <c r="C32" s="27" t="s">
+        <v>490</v>
+      </c>
+      <c r="C32" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="29"/>
+      <c r="D32" s="38"/>
+      <c r="E32" s="38"/>
+      <c r="F32" s="39"/>
       <c r="G32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
@@ -3555,71 +3622,71 @@
         <v>8</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="C33" s="23" t="s">
-        <v>542</v>
-      </c>
-      <c r="D33" s="24"/>
-      <c r="E33" s="24"/>
-      <c r="F33" s="25"/>
+        <v>489</v>
+      </c>
+      <c r="C33" s="24" t="s">
+        <v>533</v>
+      </c>
+      <c r="D33" s="25"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="26"/>
       <c r="G33" s="5"/>
       <c r="H33" s="16" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
     </row>
     <row r="34" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="19" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="C34" s="23" t="s">
-        <v>552</v>
-      </c>
-      <c r="D34" s="24"/>
-      <c r="E34" s="24"/>
-      <c r="F34" s="25"/>
+        <v>489</v>
+      </c>
+      <c r="C34" s="24" t="s">
+        <v>543</v>
+      </c>
+      <c r="D34" s="25"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="26"/>
       <c r="G34" s="5"/>
       <c r="H34" s="16" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
     </row>
     <row r="35" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="19" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="C35" s="23" t="s">
-        <v>582</v>
-      </c>
-      <c r="D35" s="24"/>
-      <c r="E35" s="24"/>
-      <c r="F35" s="25"/>
+        <v>489</v>
+      </c>
+      <c r="C35" s="24" t="s">
+        <v>569</v>
+      </c>
+      <c r="D35" s="25"/>
+      <c r="E35" s="25"/>
+      <c r="F35" s="26"/>
       <c r="G35" s="5"/>
       <c r="H35" s="16" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
     </row>
     <row r="36" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="1" t="s">
-        <v>545</v>
+        <v>536</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="C36" s="23" t="s">
-        <v>546</v>
-      </c>
-      <c r="D36" s="24"/>
-      <c r="E36" s="24"/>
-      <c r="F36" s="25"/>
+        <v>489</v>
+      </c>
+      <c r="C36" s="24" t="s">
+        <v>537</v>
+      </c>
+      <c r="D36" s="25"/>
+      <c r="E36" s="25"/>
+      <c r="F36" s="26"/>
       <c r="G36" s="5"/>
       <c r="H36" s="16" t="s">
-        <v>547</v>
+        <v>538</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
@@ -3635,16 +3702,16 @@
       <c r="H39" s="11"/>
     </row>
     <row r="40" spans="1:8" s="3" customFormat="1" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="26" t="s">
-        <v>548</v>
-      </c>
-      <c r="B40" s="26"/>
-      <c r="C40" s="26"/>
-      <c r="D40" s="26"/>
-      <c r="E40" s="26"/>
-      <c r="F40" s="26"/>
-      <c r="G40" s="26"/>
-      <c r="H40" s="26"/>
+      <c r="A40" s="28" t="s">
+        <v>539</v>
+      </c>
+      <c r="B40" s="28"/>
+      <c r="C40" s="28"/>
+      <c r="D40" s="28"/>
+      <c r="E40" s="28"/>
+      <c r="F40" s="28"/>
+      <c r="G40" s="28"/>
+      <c r="H40" s="28"/>
     </row>
     <row r="41" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="1" t="s">
@@ -3669,7 +3736,7 @@
         <v>3</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
     </row>
     <row r="42" spans="1:8" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.4">
@@ -3680,54 +3747,57 @@
         <v>17</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="G42" s="4"/>
       <c r="H42" s="16" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
     </row>
     <row r="43" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="H43" s="2"/>
     </row>
     <row r="44" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F44" s="3" t="s">
+        <v>639</v>
+      </c>
       <c r="H44" s="2"/>
     </row>
     <row r="45" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="H45" s="2"/>
     </row>
     <row r="46" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="26" t="s">
+      <c r="A46" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="B46" s="26"/>
-      <c r="C46" s="26"/>
-      <c r="D46" s="26"/>
-      <c r="E46" s="26"/>
-      <c r="F46" s="26"/>
-      <c r="G46" s="26"/>
-      <c r="H46" s="26"/>
+      <c r="B46" s="28"/>
+      <c r="C46" s="28"/>
+      <c r="D46" s="28"/>
+      <c r="E46" s="28"/>
+      <c r="F46" s="28"/>
+      <c r="G46" s="28"/>
+      <c r="H46" s="28"/>
     </row>
     <row r="47" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="26" t="s">
-        <v>566</v>
-      </c>
-      <c r="B47" s="26"/>
-      <c r="C47" s="26"/>
-      <c r="D47" s="26"/>
-      <c r="E47" s="26"/>
-      <c r="F47" s="26"/>
-      <c r="G47" s="26"/>
-      <c r="H47" s="26"/>
+      <c r="A47" s="28" t="s">
+        <v>554</v>
+      </c>
+      <c r="B47" s="28"/>
+      <c r="C47" s="28"/>
+      <c r="D47" s="28"/>
+      <c r="E47" s="28"/>
+      <c r="F47" s="28"/>
+      <c r="G47" s="28"/>
+      <c r="H47" s="28"/>
     </row>
     <row r="48" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="1" t="s">
@@ -3752,17 +3822,17 @@
         <v>3</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="49">
-        <v>1</v>
-      </c>
-      <c r="B49" s="48" t="s">
+      <c r="A49" s="41">
+        <v>1</v>
+      </c>
+      <c r="B49" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="C49" s="26" t="s">
+      <c r="C49" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D49" s="6" t="s">
@@ -3774,15 +3844,15 @@
       <c r="F49" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G49" s="34"/>
+      <c r="G49" s="27"/>
       <c r="H49" s="15" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
     </row>
     <row r="50" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="49"/>
-      <c r="B50" s="48"/>
-      <c r="C50" s="26"/>
+      <c r="A50" s="41"/>
+      <c r="B50" s="40"/>
+      <c r="C50" s="28"/>
       <c r="D50" s="6" t="s">
         <v>18</v>
       </c>
@@ -3792,9 +3862,9 @@
       <c r="F50" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G50" s="34"/>
+      <c r="G50" s="27"/>
       <c r="H50" s="15" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
@@ -3802,13 +3872,13 @@
       <c r="L50" s="2"/>
     </row>
     <row r="51" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="44">
+      <c r="A51" s="35">
         <v>2</v>
       </c>
-      <c r="B51" s="48" t="s">
+      <c r="B51" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="C51" s="26" t="s">
+      <c r="C51" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D51" s="6" t="s">
@@ -3820,9 +3890,9 @@
       <c r="F51" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G51" s="34"/>
+      <c r="G51" s="27"/>
       <c r="H51" s="15" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
@@ -3830,9 +3900,9 @@
       <c r="L51" s="2"/>
     </row>
     <row r="52" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="45"/>
-      <c r="B52" s="48"/>
-      <c r="C52" s="26"/>
+      <c r="A52" s="36"/>
+      <c r="B52" s="40"/>
+      <c r="C52" s="28"/>
       <c r="D52" s="6" t="s">
         <v>19</v>
       </c>
@@ -3842,9 +3912,9 @@
       <c r="F52" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G52" s="34"/>
+      <c r="G52" s="27"/>
       <c r="H52" s="15" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
@@ -3852,13 +3922,13 @@
       <c r="L52" s="2"/>
     </row>
     <row r="53" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="44">
+      <c r="A53" s="35">
         <v>3</v>
       </c>
-      <c r="B53" s="48" t="s">
+      <c r="B53" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="C53" s="26" t="s">
+      <c r="C53" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D53" s="5" t="s">
@@ -3868,11 +3938,11 @@
         <v>1</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>538</v>
-      </c>
-      <c r="G53" s="34"/>
+        <v>529</v>
+      </c>
+      <c r="G53" s="27"/>
       <c r="H53" s="15" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
@@ -3880,9 +3950,9 @@
       <c r="L53" s="2"/>
     </row>
     <row r="54" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="45"/>
-      <c r="B54" s="48"/>
-      <c r="C54" s="26"/>
+      <c r="A54" s="36"/>
+      <c r="B54" s="40"/>
+      <c r="C54" s="28"/>
       <c r="D54" s="5" t="s">
         <v>20</v>
       </c>
@@ -3890,11 +3960,11 @@
         <v>1</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>564</v>
-      </c>
-      <c r="G54" s="34"/>
+        <v>552</v>
+      </c>
+      <c r="G54" s="27"/>
       <c r="H54" s="15" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
@@ -3902,13 +3972,13 @@
       <c r="L54" s="2"/>
     </row>
     <row r="55" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="44">
+      <c r="A55" s="35">
         <v>4</v>
       </c>
-      <c r="B55" s="48" t="s">
+      <c r="B55" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="C55" s="26" t="s">
+      <c r="C55" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D55" s="5" t="s">
@@ -3918,11 +3988,11 @@
         <v>1</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>508</v>
-      </c>
-      <c r="G55" s="34"/>
+        <v>501</v>
+      </c>
+      <c r="G55" s="27"/>
       <c r="H55" s="15" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
@@ -3930,9 +4000,9 @@
       <c r="L55" s="2"/>
     </row>
     <row r="56" spans="1:12" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="45"/>
-      <c r="B56" s="48"/>
-      <c r="C56" s="26"/>
+      <c r="A56" s="36"/>
+      <c r="B56" s="40"/>
+      <c r="C56" s="28"/>
       <c r="D56" s="5" t="s">
         <v>25</v>
       </c>
@@ -3940,11 +4010,11 @@
         <v>1</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>558</v>
-      </c>
-      <c r="G56" s="34"/>
+        <v>549</v>
+      </c>
+      <c r="G56" s="27"/>
       <c r="H56" s="15" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
@@ -3952,13 +4022,13 @@
       <c r="L56" s="2"/>
     </row>
     <row r="57" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="44">
+      <c r="A57" s="35">
         <v>5</v>
       </c>
-      <c r="B57" s="35" t="s">
+      <c r="B57" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="C57" s="26" t="s">
+      <c r="C57" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D57" s="5" t="s">
@@ -3968,13 +4038,13 @@
         <v>1</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>534</v>
-      </c>
-      <c r="G57" s="34" t="s">
-        <v>535</v>
+        <v>525</v>
+      </c>
+      <c r="G57" s="27" t="s">
+        <v>526</v>
       </c>
       <c r="H57" s="15" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
@@ -3982,9 +4052,9 @@
       <c r="L57" s="2"/>
     </row>
     <row r="58" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="45"/>
-      <c r="B58" s="35"/>
-      <c r="C58" s="26"/>
+      <c r="A58" s="36"/>
+      <c r="B58" s="29"/>
+      <c r="C58" s="28"/>
       <c r="D58" s="5" t="s">
         <v>26</v>
       </c>
@@ -3992,11 +4062,11 @@
         <v>1</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>585</v>
-      </c>
-      <c r="G58" s="34"/>
+        <v>572</v>
+      </c>
+      <c r="G58" s="27"/>
       <c r="H58" s="15" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
@@ -4004,13 +4074,13 @@
       <c r="L58" s="2"/>
     </row>
     <row r="59" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A59" s="44">
+      <c r="A59" s="35">
         <v>6</v>
       </c>
-      <c r="B59" s="35" t="s">
+      <c r="B59" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="C59" s="26" t="s">
+      <c r="C59" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D59" s="5" t="s">
@@ -4020,11 +4090,11 @@
         <v>0</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>628</v>
-      </c>
-      <c r="G59" s="34"/>
+        <v>615</v>
+      </c>
+      <c r="G59" s="27"/>
       <c r="H59" s="15" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
@@ -4032,9 +4102,9 @@
       <c r="L59" s="2"/>
     </row>
     <row r="60" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="45"/>
-      <c r="B60" s="35"/>
-      <c r="C60" s="26"/>
+      <c r="A60" s="36"/>
+      <c r="B60" s="29"/>
+      <c r="C60" s="28"/>
       <c r="D60" s="5" t="s">
         <v>28</v>
       </c>
@@ -4042,11 +4112,11 @@
         <v>0</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>627</v>
-      </c>
-      <c r="G60" s="34"/>
+        <v>614</v>
+      </c>
+      <c r="G60" s="27"/>
       <c r="H60" s="15" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
@@ -4054,13 +4124,13 @@
       <c r="L60" s="2"/>
     </row>
     <row r="61" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="44">
+      <c r="A61" s="35">
         <v>7</v>
       </c>
-      <c r="B61" s="35" t="s">
+      <c r="B61" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="C61" s="26" t="s">
+      <c r="C61" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D61" s="5" t="s">
@@ -4072,9 +4142,9 @@
       <c r="F61" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="G61" s="34"/>
+      <c r="G61" s="27"/>
       <c r="H61" s="15" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
@@ -4082,9 +4152,9 @@
       <c r="L61" s="2"/>
     </row>
     <row r="62" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="45"/>
-      <c r="B62" s="35"/>
-      <c r="C62" s="26"/>
+      <c r="A62" s="36"/>
+      <c r="B62" s="29"/>
+      <c r="C62" s="28"/>
       <c r="D62" s="5" t="s">
         <v>38</v>
       </c>
@@ -4094,9 +4164,9 @@
       <c r="F62" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="G62" s="34"/>
+      <c r="G62" s="27"/>
       <c r="H62" s="15" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="I62" s="2"/>
       <c r="J62" s="2"/>
@@ -4104,29 +4174,29 @@
       <c r="L62" s="2"/>
     </row>
     <row r="63" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="44">
+      <c r="A63" s="35">
         <v>8</v>
       </c>
-      <c r="B63" s="35" t="s">
+      <c r="B63" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="C63" s="26" t="s">
+      <c r="C63" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E63" s="1">
         <v>0</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>629</v>
-      </c>
-      <c r="G63" s="34" t="s">
-        <v>600</v>
+        <v>616</v>
+      </c>
+      <c r="G63" s="27" t="s">
+        <v>587</v>
       </c>
       <c r="H63" s="15" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
@@ -4134,21 +4204,21 @@
       <c r="L63" s="2"/>
     </row>
     <row r="64" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A64" s="45"/>
-      <c r="B64" s="35"/>
-      <c r="C64" s="26"/>
+      <c r="A64" s="36"/>
+      <c r="B64" s="29"/>
+      <c r="C64" s="28"/>
       <c r="D64" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E64" s="1">
         <v>0</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>630</v>
-      </c>
-      <c r="G64" s="34"/>
+        <v>617</v>
+      </c>
+      <c r="G64" s="27"/>
       <c r="H64" s="15" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="I64" s="2"/>
       <c r="J64" s="2"/>
@@ -4156,13 +4226,13 @@
       <c r="L64" s="2"/>
     </row>
     <row r="65" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A65" s="44">
+      <c r="A65" s="35">
         <v>9</v>
       </c>
-      <c r="B65" s="35" t="s">
+      <c r="B65" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="C65" s="26" t="s">
+      <c r="C65" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D65" s="5" t="s">
@@ -4172,19 +4242,19 @@
         <v>1</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>597</v>
-      </c>
-      <c r="G65" s="34" t="s">
-        <v>601</v>
+        <v>584</v>
+      </c>
+      <c r="G65" s="27" t="s">
+        <v>588</v>
       </c>
       <c r="H65" s="15" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="66" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A66" s="45"/>
-      <c r="B66" s="35"/>
-      <c r="C66" s="26"/>
+      <c r="A66" s="36"/>
+      <c r="B66" s="29"/>
+      <c r="C66" s="28"/>
       <c r="D66" s="5" t="s">
         <v>117</v>
       </c>
@@ -4192,21 +4262,21 @@
         <v>1</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>598</v>
-      </c>
-      <c r="G66" s="34"/>
+        <v>585</v>
+      </c>
+      <c r="G66" s="27"/>
       <c r="H66" s="15" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
     </row>
     <row r="67" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A67" s="44">
+      <c r="A67" s="35">
         <v>10</v>
       </c>
-      <c r="B67" s="35" t="s">
+      <c r="B67" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="C67" s="26" t="s">
+      <c r="C67" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D67" s="5" t="s">
@@ -4216,13 +4286,13 @@
         <v>1</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>577</v>
-      </c>
-      <c r="G67" s="34" t="s">
-        <v>602</v>
+        <v>564</v>
+      </c>
+      <c r="G67" s="27" t="s">
+        <v>589</v>
       </c>
       <c r="H67" s="15" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="I67" s="2"/>
       <c r="J67" s="2"/>
@@ -4230,9 +4300,9 @@
       <c r="L67" s="2"/>
     </row>
     <row r="68" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A68" s="45"/>
-      <c r="B68" s="35"/>
-      <c r="C68" s="26"/>
+      <c r="A68" s="36"/>
+      <c r="B68" s="29"/>
+      <c r="C68" s="28"/>
       <c r="D68" s="5" t="s">
         <v>161</v>
       </c>
@@ -4240,11 +4310,11 @@
         <v>1</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>576</v>
-      </c>
-      <c r="G68" s="34"/>
+        <v>563</v>
+      </c>
+      <c r="G68" s="27"/>
       <c r="H68" s="15" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="I68" s="2"/>
       <c r="J68" s="2"/>
@@ -4252,13 +4322,13 @@
       <c r="L68" s="2"/>
     </row>
     <row r="69" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A69" s="30">
+      <c r="A69" s="33">
         <v>11</v>
       </c>
-      <c r="B69" s="35" t="s">
+      <c r="B69" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="C69" s="26" t="s">
+      <c r="C69" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D69" s="5" t="s">
@@ -4268,13 +4338,13 @@
         <v>0</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>632</v>
-      </c>
-      <c r="G69" s="34" t="s">
-        <v>600</v>
+        <v>619</v>
+      </c>
+      <c r="G69" s="27" t="s">
+        <v>587</v>
       </c>
       <c r="H69" s="15" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="I69" s="2"/>
       <c r="J69" s="2"/>
@@ -4282,9 +4352,9 @@
       <c r="L69" s="2"/>
     </row>
     <row r="70" spans="1:12" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A70" s="31"/>
-      <c r="B70" s="35"/>
-      <c r="C70" s="26"/>
+      <c r="A70" s="34"/>
+      <c r="B70" s="29"/>
+      <c r="C70" s="28"/>
       <c r="D70" s="5" t="s">
         <v>159</v>
       </c>
@@ -4292,11 +4362,11 @@
         <v>0</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>633</v>
-      </c>
-      <c r="G70" s="34"/>
+        <v>620</v>
+      </c>
+      <c r="G70" s="27"/>
       <c r="H70" s="15" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="I70" s="2"/>
       <c r="J70" s="2"/>
@@ -4304,13 +4374,13 @@
       <c r="L70" s="2"/>
     </row>
     <row r="71" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A71" s="30">
+      <c r="A71" s="33">
         <v>12</v>
       </c>
-      <c r="B71" s="36" t="s">
+      <c r="B71" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="C71" s="26" t="s">
+      <c r="C71" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D71" s="5" t="s">
@@ -4320,13 +4390,13 @@
         <v>0</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>561</v>
-      </c>
-      <c r="G71" s="34" t="s">
-        <v>600</v>
+        <v>656</v>
+      </c>
+      <c r="G71" s="27" t="s">
+        <v>587</v>
       </c>
       <c r="H71" s="15" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="I71" s="2"/>
       <c r="J71" s="2"/>
@@ -4334,9 +4404,9 @@
       <c r="L71" s="2"/>
     </row>
     <row r="72" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A72" s="31"/>
-      <c r="B72" s="36"/>
-      <c r="C72" s="26"/>
+      <c r="A72" s="34"/>
+      <c r="B72" s="32"/>
+      <c r="C72" s="28"/>
       <c r="D72" s="5" t="s">
         <v>36</v>
       </c>
@@ -4344,11 +4414,11 @@
         <v>0</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>562</v>
-      </c>
-      <c r="G72" s="34"/>
+        <v>657</v>
+      </c>
+      <c r="G72" s="27"/>
       <c r="H72" s="15" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="I72" s="2"/>
       <c r="J72" s="2"/>
@@ -4356,13 +4426,13 @@
       <c r="L72" s="2"/>
     </row>
     <row r="73" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A73" s="30">
+      <c r="A73" s="33">
         <v>13</v>
       </c>
-      <c r="B73" s="36" t="s">
+      <c r="B73" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="C73" s="26" t="s">
+      <c r="C73" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D73" s="5" t="s">
@@ -4372,11 +4442,11 @@
         <v>0</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>574</v>
-      </c>
-      <c r="G73" s="34"/>
+        <v>561</v>
+      </c>
+      <c r="G73" s="27"/>
       <c r="H73" s="15" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="I73" s="2"/>
       <c r="J73" s="2"/>
@@ -4384,9 +4454,9 @@
       <c r="L73" s="2"/>
     </row>
     <row r="74" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A74" s="31"/>
-      <c r="B74" s="36"/>
-      <c r="C74" s="26"/>
+      <c r="A74" s="34"/>
+      <c r="B74" s="32"/>
+      <c r="C74" s="28"/>
       <c r="D74" s="5" t="s">
         <v>34</v>
       </c>
@@ -4394,11 +4464,11 @@
         <v>0</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>575</v>
-      </c>
-      <c r="G74" s="34"/>
+        <v>562</v>
+      </c>
+      <c r="G74" s="27"/>
       <c r="H74" s="15" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="I74" s="2"/>
       <c r="J74" s="2"/>
@@ -4406,13 +4476,13 @@
       <c r="L74" s="2"/>
     </row>
     <row r="75" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A75" s="44">
+      <c r="A75" s="35">
         <v>14</v>
       </c>
-      <c r="B75" s="36" t="s">
+      <c r="B75" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="C75" s="26" t="s">
+      <c r="C75" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D75" s="5" t="s">
@@ -4422,13 +4492,13 @@
         <v>1</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>509</v>
-      </c>
-      <c r="G75" s="34" t="s">
-        <v>600</v>
+        <v>502</v>
+      </c>
+      <c r="G75" s="27" t="s">
+        <v>587</v>
       </c>
       <c r="H75" s="15" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="I75" s="2"/>
       <c r="J75" s="2"/>
@@ -4436,9 +4506,9 @@
       <c r="L75" s="2"/>
     </row>
     <row r="76" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A76" s="45"/>
-      <c r="B76" s="36"/>
-      <c r="C76" s="26"/>
+      <c r="A76" s="36"/>
+      <c r="B76" s="32"/>
+      <c r="C76" s="28"/>
       <c r="D76" s="5" t="s">
         <v>128</v>
       </c>
@@ -4446,21 +4516,21 @@
         <v>1</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>510</v>
-      </c>
-      <c r="G76" s="34"/>
+        <v>503</v>
+      </c>
+      <c r="G76" s="27"/>
       <c r="H76" s="15" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
     </row>
     <row r="77" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A77" s="30">
+      <c r="A77" s="33">
         <v>15</v>
       </c>
-      <c r="B77" s="36" t="s">
+      <c r="B77" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="C77" s="26" t="s">
+      <c r="C77" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D77" s="5" t="s">
@@ -4470,19 +4540,19 @@
         <v>2</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>634</v>
-      </c>
-      <c r="G77" s="34" t="s">
-        <v>563</v>
+        <v>654</v>
+      </c>
+      <c r="G77" s="27" t="s">
+        <v>651</v>
       </c>
       <c r="H77" s="15" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
     </row>
     <row r="78" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A78" s="31"/>
-      <c r="B78" s="36"/>
-      <c r="C78" s="26"/>
+      <c r="A78" s="34"/>
+      <c r="B78" s="32"/>
+      <c r="C78" s="28"/>
       <c r="D78" s="5" t="s">
         <v>126</v>
       </c>
@@ -4490,21 +4560,21 @@
         <v>2</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>635</v>
-      </c>
-      <c r="G78" s="34"/>
+        <v>655</v>
+      </c>
+      <c r="G78" s="27"/>
       <c r="H78" s="15" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
     </row>
     <row r="79" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A79" s="30">
+      <c r="A79" s="33">
         <v>16</v>
       </c>
-      <c r="B79" s="36" t="s">
+      <c r="B79" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="C79" s="37" t="s">
+      <c r="C79" s="47" t="s">
         <v>6</v>
       </c>
       <c r="D79" s="5" t="s">
@@ -4514,19 +4584,19 @@
         <v>2</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>571</v>
-      </c>
-      <c r="G79" s="34" t="s">
-        <v>573</v>
+        <v>653</v>
+      </c>
+      <c r="G79" s="27" t="s">
+        <v>560</v>
       </c>
       <c r="H79" s="15" t="s">
-        <v>611</v>
+        <v>598</v>
       </c>
     </row>
     <row r="80" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A80" s="31"/>
-      <c r="B80" s="36"/>
-      <c r="C80" s="38"/>
+      <c r="A80" s="34"/>
+      <c r="B80" s="32"/>
+      <c r="C80" s="48"/>
       <c r="D80" s="5" t="s">
         <v>124</v>
       </c>
@@ -4534,21 +4604,21 @@
         <v>2</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>572</v>
-      </c>
-      <c r="G80" s="34"/>
+        <v>559</v>
+      </c>
+      <c r="G80" s="27"/>
       <c r="H80" s="15" t="s">
-        <v>612</v>
+        <v>599</v>
       </c>
     </row>
     <row r="81" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A81" s="30">
+      <c r="A81" s="33">
         <v>17</v>
       </c>
-      <c r="B81" s="36" t="s">
+      <c r="B81" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="C81" s="26" t="s">
+      <c r="C81" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D81" s="5" t="s">
@@ -4558,19 +4628,19 @@
         <v>1</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>526</v>
-      </c>
-      <c r="G81" s="34" t="s">
-        <v>230</v>
+        <v>652</v>
+      </c>
+      <c r="G81" s="27" t="s">
+        <v>226</v>
       </c>
       <c r="H81" s="15" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A82" s="31"/>
-      <c r="B82" s="36"/>
-      <c r="C82" s="26"/>
+      <c r="A82" s="34"/>
+      <c r="B82" s="32"/>
+      <c r="C82" s="28"/>
       <c r="D82" s="5" t="s">
         <v>40</v>
       </c>
@@ -4578,21 +4648,21 @@
         <v>1</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>527</v>
-      </c>
-      <c r="G82" s="34"/>
+        <v>518</v>
+      </c>
+      <c r="G82" s="27"/>
       <c r="H82" s="15" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
     </row>
     <row r="83" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A83" s="30">
+      <c r="A83" s="33">
         <v>18</v>
       </c>
-      <c r="B83" s="36" t="s">
+      <c r="B83" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="C83" s="33" t="s">
+      <c r="C83" s="44" t="s">
         <v>6</v>
       </c>
       <c r="D83" s="5" t="s">
@@ -4602,19 +4672,19 @@
         <v>43</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>511</v>
-      </c>
-      <c r="G83" s="34" t="s">
-        <v>524</v>
+        <v>504</v>
+      </c>
+      <c r="G83" s="27" t="s">
+        <v>517</v>
       </c>
       <c r="H83" s="15" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
     </row>
     <row r="84" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A84" s="31"/>
-      <c r="B84" s="36"/>
-      <c r="C84" s="33"/>
+      <c r="A84" s="34"/>
+      <c r="B84" s="32"/>
+      <c r="C84" s="44"/>
       <c r="D84" s="5" t="s">
         <v>42</v>
       </c>
@@ -4622,21 +4692,21 @@
         <v>43</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>512</v>
-      </c>
-      <c r="G84" s="34"/>
+        <v>505</v>
+      </c>
+      <c r="G84" s="27"/>
       <c r="H84" s="15" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
     </row>
     <row r="85" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A85" s="30">
+      <c r="A85" s="33">
         <v>19</v>
       </c>
-      <c r="B85" s="36" t="s">
+      <c r="B85" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="C85" s="26" t="s">
+      <c r="C85" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D85" s="5" t="s">
@@ -4646,17 +4716,17 @@
         <v>1</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="G85" s="34"/>
+        <v>630</v>
+      </c>
+      <c r="G85" s="27"/>
       <c r="H85" s="15" t="s">
-        <v>528</v>
+        <v>519</v>
       </c>
     </row>
     <row r="86" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A86" s="31"/>
-      <c r="B86" s="36"/>
-      <c r="C86" s="26"/>
+      <c r="A86" s="34"/>
+      <c r="B86" s="32"/>
+      <c r="C86" s="28"/>
       <c r="D86" s="5" t="s">
         <v>86</v>
       </c>
@@ -4664,65 +4734,65 @@
         <v>1</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="G86" s="34"/>
+        <v>631</v>
+      </c>
+      <c r="G86" s="27"/>
       <c r="H86" s="15" t="s">
-        <v>529</v>
+        <v>520</v>
       </c>
     </row>
     <row r="87" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A87" s="30">
+      <c r="A87" s="33">
         <v>20</v>
       </c>
-      <c r="B87" s="32" t="s">
+      <c r="B87" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="C87" s="26" t="s">
+      <c r="C87" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E87" s="1">
         <v>1</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="G87" s="34" t="s">
-        <v>287</v>
+        <v>283</v>
+      </c>
+      <c r="G87" s="27" t="s">
+        <v>282</v>
       </c>
       <c r="H87" s="15" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
     </row>
     <row r="88" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A88" s="31"/>
-      <c r="B88" s="32"/>
-      <c r="C88" s="26"/>
+      <c r="A88" s="34"/>
+      <c r="B88" s="30"/>
+      <c r="C88" s="28"/>
       <c r="D88" s="5" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="E88" s="1">
         <v>1</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="G88" s="34"/>
+        <v>284</v>
+      </c>
+      <c r="G88" s="27"/>
       <c r="H88" s="15" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
     </row>
     <row r="89" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A89" s="30">
+      <c r="A89" s="33">
         <v>21</v>
       </c>
-      <c r="B89" s="32" t="s">
+      <c r="B89" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="C89" s="26" t="s">
+      <c r="C89" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D89" s="5" t="s">
@@ -4732,19 +4802,19 @@
         <v>0</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>580</v>
-      </c>
-      <c r="G89" s="34" t="s">
-        <v>584</v>
+        <v>567</v>
+      </c>
+      <c r="G89" s="27" t="s">
+        <v>571</v>
       </c>
       <c r="H89" s="15" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
     </row>
     <row r="90" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A90" s="31"/>
-      <c r="B90" s="32"/>
-      <c r="C90" s="26"/>
+      <c r="A90" s="34"/>
+      <c r="B90" s="30"/>
+      <c r="C90" s="28"/>
       <c r="D90" s="5" t="s">
         <v>130</v>
       </c>
@@ -4752,65 +4822,65 @@
         <v>0</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>581</v>
-      </c>
-      <c r="G90" s="34"/>
+        <v>568</v>
+      </c>
+      <c r="G90" s="27"/>
       <c r="H90" s="15" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
     </row>
     <row r="91" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A91" s="30">
+      <c r="A91" s="35">
         <v>22</v>
       </c>
-      <c r="B91" s="32" t="s">
+      <c r="B91" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="C91" s="26" t="s">
+      <c r="C91" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E91" s="1">
         <v>2</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>536</v>
-      </c>
-      <c r="G91" s="34" t="s">
-        <v>530</v>
+        <v>527</v>
+      </c>
+      <c r="G91" s="27" t="s">
+        <v>521</v>
       </c>
       <c r="H91" s="15" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
     </row>
     <row r="92" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A92" s="31"/>
-      <c r="B92" s="32"/>
-      <c r="C92" s="26"/>
+      <c r="A92" s="36"/>
+      <c r="B92" s="30"/>
+      <c r="C92" s="28"/>
       <c r="D92" s="5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E92" s="1">
         <v>2</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>537</v>
-      </c>
-      <c r="G92" s="34"/>
+        <v>528</v>
+      </c>
+      <c r="G92" s="27"/>
       <c r="H92" s="15" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
     </row>
     <row r="93" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A93" s="30">
+      <c r="A93" s="33">
         <v>23</v>
       </c>
-      <c r="B93" s="32" t="s">
+      <c r="B93" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="C93" s="26" t="s">
+      <c r="C93" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D93" s="5" t="s">
@@ -4820,19 +4890,19 @@
         <v>2</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>543</v>
-      </c>
-      <c r="G93" s="34" t="s">
-        <v>304</v>
+        <v>534</v>
+      </c>
+      <c r="G93" s="27" t="s">
+        <v>297</v>
       </c>
       <c r="H93" s="15" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
     </row>
     <row r="94" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A94" s="31"/>
-      <c r="B94" s="32"/>
-      <c r="C94" s="26"/>
+      <c r="A94" s="34"/>
+      <c r="B94" s="30"/>
+      <c r="C94" s="28"/>
       <c r="D94" s="5" t="s">
         <v>31</v>
       </c>
@@ -4840,65 +4910,65 @@
         <v>2</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>544</v>
-      </c>
-      <c r="G94" s="34"/>
+        <v>535</v>
+      </c>
+      <c r="G94" s="27"/>
       <c r="H94" s="15" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
     </row>
     <row r="95" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A95" s="30">
+      <c r="A95" s="33">
         <v>24</v>
       </c>
-      <c r="B95" s="32" t="s">
+      <c r="B95" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="C95" s="26" t="s">
+      <c r="C95" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>578</v>
-      </c>
-      <c r="G95" s="34" t="s">
-        <v>211</v>
+        <v>565</v>
+      </c>
+      <c r="G95" s="27" t="s">
+        <v>207</v>
       </c>
       <c r="H95" s="15" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
     </row>
     <row r="96" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A96" s="31"/>
-      <c r="B96" s="32"/>
-      <c r="C96" s="26"/>
+      <c r="A96" s="34"/>
+      <c r="B96" s="30"/>
+      <c r="C96" s="28"/>
       <c r="D96" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>579</v>
-      </c>
-      <c r="G96" s="34"/>
+        <v>566</v>
+      </c>
+      <c r="G96" s="27"/>
       <c r="H96" s="15" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
     </row>
     <row r="97" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A97" s="30">
+      <c r="A97" s="33">
         <v>25</v>
       </c>
-      <c r="B97" s="35" t="s">
+      <c r="B97" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="C97" s="26" t="s">
+      <c r="C97" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D97" s="5" t="s">
@@ -4908,17 +4978,17 @@
         <v>0</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>568</v>
-      </c>
-      <c r="G97" s="34"/>
+        <v>556</v>
+      </c>
+      <c r="G97" s="27"/>
       <c r="H97" s="15" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
     </row>
     <row r="98" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A98" s="31"/>
-      <c r="B98" s="35"/>
-      <c r="C98" s="26"/>
+      <c r="A98" s="34"/>
+      <c r="B98" s="29"/>
+      <c r="C98" s="28"/>
       <c r="D98" s="5" t="s">
         <v>151</v>
       </c>
@@ -4926,21 +4996,21 @@
         <v>0</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>569</v>
-      </c>
-      <c r="G98" s="34"/>
+        <v>557</v>
+      </c>
+      <c r="G98" s="27"/>
       <c r="H98" s="15" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
     </row>
     <row r="99" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A99" s="30">
+      <c r="A99" s="33">
         <v>26</v>
       </c>
-      <c r="B99" s="35" t="s">
+      <c r="B99" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="C99" s="33" t="s">
+      <c r="C99" s="44" t="s">
         <v>14</v>
       </c>
       <c r="D99" s="5" t="s">
@@ -4950,39 +5020,39 @@
         <v>1</v>
       </c>
       <c r="F99" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="G99" s="27"/>
+      <c r="H99" s="15" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A100" s="34"/>
+      <c r="B100" s="29"/>
+      <c r="C100" s="44"/>
+      <c r="D100" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="G99" s="34"/>
-      <c r="H99" s="15" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A100" s="31"/>
-      <c r="B100" s="35"/>
-      <c r="C100" s="33"/>
-      <c r="D100" s="5" t="s">
-        <v>164</v>
-      </c>
       <c r="E100" s="1">
         <v>1</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="G100" s="34"/>
+        <v>634</v>
+      </c>
+      <c r="G100" s="27"/>
       <c r="H100" s="15" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
     </row>
     <row r="101" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A101" s="30">
+      <c r="A101" s="33">
         <v>27</v>
       </c>
-      <c r="B101" s="35" t="s">
+      <c r="B101" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="C101" s="26" t="s">
+      <c r="C101" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D101" s="5" t="s">
@@ -4992,17 +5062,17 @@
         <v>1</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="G101" s="34"/>
+        <v>274</v>
+      </c>
+      <c r="G101" s="27"/>
       <c r="H101" s="15" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
     </row>
     <row r="102" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A102" s="31"/>
-      <c r="B102" s="35"/>
-      <c r="C102" s="26"/>
+      <c r="A102" s="34"/>
+      <c r="B102" s="29"/>
+      <c r="C102" s="28"/>
       <c r="D102" s="5" t="s">
         <v>45</v>
       </c>
@@ -5010,21 +5080,21 @@
         <v>1</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="G102" s="34"/>
+        <v>275</v>
+      </c>
+      <c r="G102" s="27"/>
       <c r="H102" s="15" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
     </row>
     <row r="103" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A103" s="30">
+      <c r="A103" s="33">
         <v>28</v>
       </c>
-      <c r="B103" s="35" t="s">
+      <c r="B103" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="C103" s="26" t="s">
+      <c r="C103" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D103" s="5" t="s">
@@ -5034,17 +5104,17 @@
         <v>1</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>625</v>
-      </c>
-      <c r="G103" s="34"/>
+        <v>612</v>
+      </c>
+      <c r="G103" s="27"/>
       <c r="H103" s="15" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
     </row>
     <row r="104" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A104" s="31"/>
-      <c r="B104" s="35"/>
-      <c r="C104" s="26"/>
+      <c r="A104" s="34"/>
+      <c r="B104" s="29"/>
+      <c r="C104" s="28"/>
       <c r="D104" s="5" t="s">
         <v>70</v>
       </c>
@@ -5052,21 +5122,21 @@
         <v>1</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>626</v>
-      </c>
-      <c r="G104" s="34"/>
+        <v>613</v>
+      </c>
+      <c r="G104" s="27"/>
       <c r="H104" s="15" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
     </row>
     <row r="105" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A105" s="30">
+      <c r="A105" s="33">
         <v>29</v>
       </c>
-      <c r="B105" s="35" t="s">
+      <c r="B105" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="C105" s="26" t="s">
+      <c r="C105" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D105" s="5" t="s">
@@ -5076,19 +5146,19 @@
         <v>0</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="G105" s="34" t="s">
-        <v>565</v>
+        <v>294</v>
+      </c>
+      <c r="G105" s="27" t="s">
+        <v>553</v>
       </c>
       <c r="H105" s="15" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
     </row>
     <row r="106" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A106" s="31"/>
-      <c r="B106" s="35"/>
-      <c r="C106" s="26"/>
+      <c r="A106" s="34"/>
+      <c r="B106" s="29"/>
+      <c r="C106" s="28"/>
       <c r="D106" s="5" t="s">
         <v>157</v>
       </c>
@@ -5096,21 +5166,21 @@
         <v>0</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="G106" s="34"/>
+        <v>295</v>
+      </c>
+      <c r="G106" s="27"/>
       <c r="H106" s="15" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
     </row>
     <row r="107" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A107" s="30">
+      <c r="A107" s="33">
         <v>30</v>
       </c>
-      <c r="B107" s="35" t="s">
+      <c r="B107" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="C107" s="26" t="s">
+      <c r="C107" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D107" s="5" t="s">
@@ -5120,19 +5190,19 @@
         <v>1</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="G107" s="34" t="s">
-        <v>231</v>
+        <v>299</v>
+      </c>
+      <c r="G107" s="27" t="s">
+        <v>227</v>
       </c>
       <c r="H107" s="15" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
     </row>
     <row r="108" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A108" s="31"/>
-      <c r="B108" s="35"/>
-      <c r="C108" s="26"/>
+      <c r="A108" s="34"/>
+      <c r="B108" s="29"/>
+      <c r="C108" s="28"/>
       <c r="D108" s="5" t="s">
         <v>47</v>
       </c>
@@ -5140,85 +5210,85 @@
         <v>1</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="G108" s="34"/>
+        <v>300</v>
+      </c>
+      <c r="G108" s="27"/>
       <c r="H108" s="15" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
     </row>
     <row r="109" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A109" s="30">
+      <c r="A109" s="33">
         <v>31</v>
       </c>
-      <c r="B109" s="39" t="s">
+      <c r="B109" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="C109" s="37" t="s">
+      <c r="C109" s="47" t="s">
         <v>14</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E109" s="1">
         <v>1</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>586</v>
-      </c>
-      <c r="G109" s="46" t="s">
-        <v>281</v>
+        <v>573</v>
+      </c>
+      <c r="G109" s="45" t="s">
+        <v>276</v>
       </c>
       <c r="H109" s="15" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
     </row>
     <row r="110" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A110" s="31"/>
-      <c r="B110" s="40"/>
-      <c r="C110" s="38"/>
+      <c r="A110" s="34"/>
+      <c r="B110" s="43"/>
+      <c r="C110" s="48"/>
       <c r="D110" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E110" s="1">
         <v>1</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>587</v>
-      </c>
-      <c r="G110" s="47"/>
+        <v>574</v>
+      </c>
+      <c r="G110" s="46"/>
       <c r="H110" s="15" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
     </row>
     <row r="111" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A111" s="30">
+      <c r="A111" s="33">
         <v>32</v>
       </c>
-      <c r="B111" s="35" t="s">
+      <c r="B111" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="C111" s="33" t="s">
+      <c r="C111" s="44" t="s">
         <v>14</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="G111" s="34"/>
+        <v>217</v>
+      </c>
+      <c r="G111" s="27"/>
       <c r="H111" s="15" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
     </row>
     <row r="112" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A112" s="31"/>
-      <c r="B112" s="35"/>
-      <c r="C112" s="33"/>
+      <c r="A112" s="34"/>
+      <c r="B112" s="29"/>
+      <c r="C112" s="44"/>
       <c r="D112" s="5" t="s">
         <v>52</v>
       </c>
@@ -5226,21 +5296,21 @@
         <v>43</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="G112" s="34"/>
+        <v>216</v>
+      </c>
+      <c r="G112" s="27"/>
       <c r="H112" s="15" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
     </row>
     <row r="113" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A113" s="30">
+      <c r="A113" s="33">
         <v>33</v>
       </c>
-      <c r="B113" s="35" t="s">
+      <c r="B113" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="C113" s="26" t="s">
+      <c r="C113" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D113" s="5" t="s">
@@ -5250,17 +5320,17 @@
         <v>1</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>603</v>
-      </c>
-      <c r="G113" s="34"/>
+        <v>590</v>
+      </c>
+      <c r="G113" s="27"/>
       <c r="H113" s="15" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
     </row>
     <row r="114" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A114" s="31"/>
-      <c r="B114" s="35"/>
-      <c r="C114" s="26"/>
+      <c r="A114" s="34"/>
+      <c r="B114" s="29"/>
+      <c r="C114" s="28"/>
       <c r="D114" s="5" t="s">
         <v>136</v>
       </c>
@@ -5268,21 +5338,21 @@
         <v>1</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>604</v>
-      </c>
-      <c r="G114" s="34"/>
+        <v>591</v>
+      </c>
+      <c r="G114" s="27"/>
       <c r="H114" s="15" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
     </row>
     <row r="115" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A115" s="30">
+      <c r="A115" s="33">
         <v>34</v>
       </c>
-      <c r="B115" s="35" t="s">
+      <c r="B115" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="C115" s="26" t="s">
+      <c r="C115" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D115" s="5" t="s">
@@ -5292,19 +5362,19 @@
         <v>0</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="G115" s="34" t="s">
-        <v>231</v>
+        <v>205</v>
+      </c>
+      <c r="G115" s="27" t="s">
+        <v>227</v>
       </c>
       <c r="H115" s="15" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
     </row>
     <row r="116" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A116" s="31"/>
-      <c r="B116" s="35"/>
-      <c r="C116" s="26"/>
+      <c r="A116" s="34"/>
+      <c r="B116" s="29"/>
+      <c r="C116" s="28"/>
       <c r="D116" s="5" t="s">
         <v>78</v>
       </c>
@@ -5312,21 +5382,21 @@
         <v>0</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="G116" s="34"/>
+        <v>203</v>
+      </c>
+      <c r="G116" s="27"/>
       <c r="H116" s="15" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
     </row>
     <row r="117" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A117" s="30">
+      <c r="A117" s="33">
         <v>35</v>
       </c>
-      <c r="B117" s="35" t="s">
+      <c r="B117" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="C117" s="26" t="s">
+      <c r="C117" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D117" s="5" t="s">
@@ -5336,19 +5406,19 @@
         <v>0</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="G117" s="34" t="s">
-        <v>231</v>
+        <v>206</v>
+      </c>
+      <c r="G117" s="27" t="s">
+        <v>227</v>
       </c>
       <c r="H117" s="15" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
     </row>
     <row r="118" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A118" s="31"/>
-      <c r="B118" s="35"/>
-      <c r="C118" s="26"/>
+      <c r="A118" s="34"/>
+      <c r="B118" s="29"/>
+      <c r="C118" s="28"/>
       <c r="D118" s="5" t="s">
         <v>80</v>
       </c>
@@ -5356,21 +5426,21 @@
         <v>0</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="G118" s="34"/>
+        <v>204</v>
+      </c>
+      <c r="G118" s="27"/>
       <c r="H118" s="15" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
     </row>
     <row r="119" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A119" s="30">
+      <c r="A119" s="33">
         <v>36</v>
       </c>
-      <c r="B119" s="35" t="s">
+      <c r="B119" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="C119" s="26" t="s">
+      <c r="C119" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D119" s="5" t="s">
@@ -5380,19 +5450,19 @@
         <v>0</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>513</v>
-      </c>
-      <c r="G119" s="34" t="s">
-        <v>262</v>
+        <v>506</v>
+      </c>
+      <c r="G119" s="27" t="s">
+        <v>257</v>
       </c>
       <c r="H119" s="15" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
     </row>
     <row r="120" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A120" s="31"/>
-      <c r="B120" s="35"/>
-      <c r="C120" s="26"/>
+      <c r="A120" s="34"/>
+      <c r="B120" s="29"/>
+      <c r="C120" s="28"/>
       <c r="D120" s="5" t="s">
         <v>122</v>
       </c>
@@ -5400,63 +5470,63 @@
         <v>0</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>514</v>
-      </c>
-      <c r="G120" s="34"/>
+        <v>507</v>
+      </c>
+      <c r="G120" s="27"/>
       <c r="H120" s="15" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
     </row>
     <row r="121" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A121" s="30">
+      <c r="A121" s="33">
         <v>37</v>
       </c>
-      <c r="B121" s="39" t="s">
+      <c r="B121" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="C121" s="26" t="s">
+      <c r="C121" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E121" s="1">
         <v>2</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="G121" s="34"/>
+        <v>186</v>
+      </c>
+      <c r="G121" s="27"/>
       <c r="H121" s="15" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
     </row>
     <row r="122" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A122" s="31"/>
-      <c r="B122" s="40"/>
-      <c r="C122" s="26"/>
+      <c r="A122" s="34"/>
+      <c r="B122" s="43"/>
+      <c r="C122" s="28"/>
       <c r="D122" s="5" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E122" s="1">
         <v>1</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="G122" s="34"/>
+        <v>186</v>
+      </c>
+      <c r="G122" s="27"/>
       <c r="H122" s="15" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
     </row>
     <row r="123" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A123" s="30">
+      <c r="A123" s="33">
         <v>38</v>
       </c>
-      <c r="B123" s="39" t="s">
+      <c r="B123" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="C123" s="26" t="s">
+      <c r="C123" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D123" s="5" t="s">
@@ -5466,17 +5536,17 @@
         <v>1</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>520</v>
-      </c>
-      <c r="G123" s="34"/>
+        <v>513</v>
+      </c>
+      <c r="G123" s="27"/>
       <c r="H123" s="15" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
     </row>
     <row r="124" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A124" s="31"/>
-      <c r="B124" s="40"/>
-      <c r="C124" s="26"/>
+      <c r="A124" s="34"/>
+      <c r="B124" s="43"/>
+      <c r="C124" s="28"/>
       <c r="D124" s="5" t="s">
         <v>54</v>
       </c>
@@ -5484,21 +5554,21 @@
         <v>1</v>
       </c>
       <c r="F124" s="5" t="s">
-        <v>521</v>
-      </c>
-      <c r="G124" s="34"/>
+        <v>514</v>
+      </c>
+      <c r="G124" s="27"/>
       <c r="H124" s="15" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
     </row>
     <row r="125" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A125" s="30">
+      <c r="A125" s="33">
         <v>39</v>
       </c>
-      <c r="B125" s="39" t="s">
+      <c r="B125" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="C125" s="26" t="s">
+      <c r="C125" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D125" s="5" t="s">
@@ -5508,19 +5578,19 @@
         <v>0</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="G125" s="34" t="s">
-        <v>567</v>
+        <v>233</v>
+      </c>
+      <c r="G125" s="27" t="s">
+        <v>555</v>
       </c>
       <c r="H125" s="15" t="s">
-        <v>613</v>
+        <v>600</v>
       </c>
     </row>
     <row r="126" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A126" s="31"/>
-      <c r="B126" s="40"/>
-      <c r="C126" s="26"/>
+      <c r="A126" s="34"/>
+      <c r="B126" s="43"/>
+      <c r="C126" s="28"/>
       <c r="D126" s="5" t="s">
         <v>134</v>
       </c>
@@ -5528,21 +5598,21 @@
         <v>0</v>
       </c>
       <c r="F126" s="5" t="s">
-        <v>615</v>
-      </c>
-      <c r="G126" s="34"/>
+        <v>602</v>
+      </c>
+      <c r="G126" s="27"/>
       <c r="H126" s="15" t="s">
-        <v>614</v>
+        <v>601</v>
       </c>
     </row>
     <row r="127" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A127" s="30">
+      <c r="A127" s="33">
         <v>40</v>
       </c>
-      <c r="B127" s="39" t="s">
+      <c r="B127" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="C127" s="26" t="s">
+      <c r="C127" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D127" s="5" t="s">
@@ -5552,17 +5622,17 @@
         <v>1</v>
       </c>
       <c r="F127" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="G127" s="34"/>
+        <v>256</v>
+      </c>
+      <c r="G127" s="27"/>
       <c r="H127" s="15" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
     </row>
     <row r="128" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A128" s="31"/>
-      <c r="B128" s="40"/>
-      <c r="C128" s="26"/>
+      <c r="A128" s="34"/>
+      <c r="B128" s="43"/>
+      <c r="C128" s="28"/>
       <c r="D128" s="5" t="s">
         <v>82</v>
       </c>
@@ -5570,21 +5640,21 @@
         <v>1</v>
       </c>
       <c r="F128" s="5" t="s">
-        <v>531</v>
-      </c>
-      <c r="G128" s="34"/>
+        <v>522</v>
+      </c>
+      <c r="G128" s="27"/>
       <c r="H128" s="15" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
     </row>
     <row r="129" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A129" s="30">
+      <c r="A129" s="33">
         <v>41</v>
       </c>
-      <c r="B129" s="39" t="s">
+      <c r="B129" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="C129" s="41" t="s">
+      <c r="C129" s="31" t="s">
         <v>14</v>
       </c>
       <c r="D129" s="5" t="s">
@@ -5596,15 +5666,15 @@
       <c r="F129" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="G129" s="34"/>
+      <c r="G129" s="27"/>
       <c r="H129" s="15" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
     </row>
     <row r="130" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A130" s="31"/>
-      <c r="B130" s="40"/>
-      <c r="C130" s="41"/>
+      <c r="A130" s="34"/>
+      <c r="B130" s="43"/>
+      <c r="C130" s="31"/>
       <c r="D130" s="5" t="s">
         <v>65</v>
       </c>
@@ -5612,21 +5682,21 @@
         <v>1</v>
       </c>
       <c r="F130" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="G130" s="34"/>
+        <v>197</v>
+      </c>
+      <c r="G130" s="27"/>
       <c r="H130" s="15" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
     </row>
     <row r="131" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A131" s="30">
+      <c r="A131" s="33">
         <v>42</v>
       </c>
-      <c r="B131" s="36" t="s">
+      <c r="B131" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="C131" s="26" t="s">
+      <c r="C131" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D131" s="5" t="s">
@@ -5636,17 +5706,17 @@
         <v>0</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>619</v>
-      </c>
-      <c r="G131" s="34"/>
+        <v>606</v>
+      </c>
+      <c r="G131" s="27"/>
       <c r="H131" s="15" t="s">
-        <v>617</v>
+        <v>604</v>
       </c>
     </row>
     <row r="132" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A132" s="31"/>
-      <c r="B132" s="36"/>
-      <c r="C132" s="26"/>
+      <c r="A132" s="34"/>
+      <c r="B132" s="32"/>
+      <c r="C132" s="28"/>
       <c r="D132" s="5" t="s">
         <v>51</v>
       </c>
@@ -5654,21 +5724,21 @@
         <v>0</v>
       </c>
       <c r="F132" s="5" t="s">
-        <v>616</v>
-      </c>
-      <c r="G132" s="34"/>
+        <v>603</v>
+      </c>
+      <c r="G132" s="27"/>
       <c r="H132" s="15" t="s">
-        <v>618</v>
+        <v>605</v>
       </c>
     </row>
     <row r="133" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A133" s="30">
+      <c r="A133" s="33">
         <v>43</v>
       </c>
-      <c r="B133" s="36" t="s">
+      <c r="B133" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="C133" s="26" t="s">
+      <c r="C133" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D133" s="5" t="s">
@@ -5678,16 +5748,16 @@
         <v>1</v>
       </c>
       <c r="F133" s="5" t="s">
-        <v>631</v>
+        <v>618</v>
       </c>
       <c r="H133" s="15" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
     </row>
     <row r="134" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A134" s="31"/>
-      <c r="B134" s="36"/>
-      <c r="C134" s="26"/>
+      <c r="A134" s="34"/>
+      <c r="B134" s="32"/>
+      <c r="C134" s="28"/>
       <c r="D134" s="5" t="s">
         <v>140</v>
       </c>
@@ -5695,20 +5765,20 @@
         <v>0</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>631</v>
+        <v>618</v>
       </c>
       <c r="H134" s="15" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="135" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A135" s="30">
+      <c r="A135" s="33">
         <v>44</v>
       </c>
-      <c r="B135" s="36" t="s">
+      <c r="B135" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="C135" s="26" t="s">
+      <c r="C135" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D135" s="5" t="s">
@@ -5718,17 +5788,17 @@
         <v>1</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>515</v>
-      </c>
-      <c r="G135" s="34"/>
+        <v>508</v>
+      </c>
+      <c r="G135" s="27"/>
       <c r="H135" s="15" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
     </row>
     <row r="136" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A136" s="31"/>
-      <c r="B136" s="36"/>
-      <c r="C136" s="26"/>
+      <c r="A136" s="34"/>
+      <c r="B136" s="32"/>
+      <c r="C136" s="28"/>
       <c r="D136" s="5" t="s">
         <v>49</v>
       </c>
@@ -5736,67 +5806,67 @@
         <v>1</v>
       </c>
       <c r="F136" s="5" t="s">
-        <v>516</v>
-      </c>
-      <c r="G136" s="34"/>
+        <v>509</v>
+      </c>
+      <c r="G136" s="27"/>
       <c r="H136" s="15" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="137" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A137" s="30">
+      <c r="A137" s="33">
         <v>45</v>
       </c>
-      <c r="B137" s="36" t="s">
+      <c r="B137" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="C137" s="33" t="s">
+      <c r="C137" s="44" t="s">
         <v>14</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E137" s="1">
         <v>1</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="G137" s="34"/>
+        <v>221</v>
+      </c>
+      <c r="G137" s="27"/>
       <c r="H137" s="15" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
     </row>
     <row r="138" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A138" s="31"/>
-      <c r="B138" s="36"/>
-      <c r="C138" s="33"/>
+      <c r="A138" s="34"/>
+      <c r="B138" s="32"/>
+      <c r="C138" s="44"/>
       <c r="D138" s="5" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E138" s="1">
         <v>1</v>
       </c>
       <c r="F138" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="G138" s="34"/>
+        <v>220</v>
+      </c>
+      <c r="G138" s="27"/>
       <c r="H138" s="15" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
     </row>
     <row r="139" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A139" s="30">
+      <c r="A139" s="33">
         <v>46</v>
       </c>
-      <c r="B139" s="36" t="s">
+      <c r="B139" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="C139" s="26" t="s">
+      <c r="C139" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="E139" s="1">
         <v>0</v>
@@ -5804,19 +5874,19 @@
       <c r="F139" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="G139" s="34" t="s">
-        <v>223</v>
+      <c r="G139" s="27" t="s">
+        <v>219</v>
       </c>
       <c r="H139" s="15" t="s">
-        <v>594</v>
+        <v>581</v>
       </c>
     </row>
     <row r="140" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A140" s="31"/>
-      <c r="B140" s="36"/>
-      <c r="C140" s="26"/>
+      <c r="A140" s="34"/>
+      <c r="B140" s="32"/>
+      <c r="C140" s="28"/>
       <c r="D140" s="5" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="E140" s="1">
         <v>0</v>
@@ -5824,83 +5894,83 @@
       <c r="F140" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="G140" s="34"/>
+      <c r="G140" s="27"/>
       <c r="H140" s="15" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
     </row>
     <row r="141" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A141" s="30">
+      <c r="A141" s="33">
         <v>47</v>
       </c>
-      <c r="B141" s="36" t="s">
+      <c r="B141" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="C141" s="26" t="s">
+      <c r="C141" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E141" s="1">
         <v>1</v>
       </c>
       <c r="F141" s="5" t="s">
-        <v>517</v>
-      </c>
-      <c r="G141" s="34" t="s">
-        <v>600</v>
+        <v>510</v>
+      </c>
+      <c r="G141" s="27" t="s">
+        <v>587</v>
       </c>
       <c r="H141" s="15" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
     </row>
     <row r="142" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A142" s="31"/>
-      <c r="B142" s="36"/>
-      <c r="C142" s="26"/>
+      <c r="A142" s="34"/>
+      <c r="B142" s="32"/>
+      <c r="C142" s="28"/>
       <c r="D142" s="5" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E142" s="1">
         <v>1</v>
       </c>
       <c r="F142" s="5" t="s">
-        <v>518</v>
-      </c>
-      <c r="G142" s="34"/>
+        <v>511</v>
+      </c>
+      <c r="G142" s="27"/>
       <c r="H142" s="15" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
     </row>
     <row r="143" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A143" s="30">
+      <c r="A143" s="33">
         <v>48</v>
       </c>
-      <c r="B143" s="36" t="s">
+      <c r="B143" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="C143" s="26" t="s">
+      <c r="C143" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>588</v>
+        <v>575</v>
       </c>
       <c r="E143" s="1">
         <v>1</v>
       </c>
       <c r="F143" s="5" t="s">
-        <v>519</v>
-      </c>
-      <c r="G143" s="34"/>
+        <v>512</v>
+      </c>
+      <c r="G143" s="27"/>
       <c r="H143" s="15" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
     </row>
     <row r="144" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A144" s="31"/>
-      <c r="B144" s="36"/>
-      <c r="C144" s="26"/>
+      <c r="A144" s="34"/>
+      <c r="B144" s="32"/>
+      <c r="C144" s="28"/>
       <c r="D144" s="5" t="s">
         <v>55</v>
       </c>
@@ -5908,21 +5978,21 @@
         <v>0</v>
       </c>
       <c r="F144" s="5" t="s">
-        <v>519</v>
-      </c>
-      <c r="G144" s="34"/>
+        <v>512</v>
+      </c>
+      <c r="G144" s="27"/>
       <c r="H144" s="15" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
     </row>
     <row r="145" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A145" s="30">
+      <c r="A145" s="33">
         <v>49</v>
       </c>
-      <c r="B145" s="36" t="s">
+      <c r="B145" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="C145" s="33" t="s">
+      <c r="C145" s="44" t="s">
         <v>14</v>
       </c>
       <c r="D145" s="5" t="s">
@@ -5932,19 +6002,19 @@
         <v>1</v>
       </c>
       <c r="F145" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="G145" s="34" t="s">
-        <v>600</v>
+        <v>208</v>
+      </c>
+      <c r="G145" s="27" t="s">
+        <v>587</v>
       </c>
       <c r="H145" s="15" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
     </row>
     <row r="146" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A146" s="31"/>
-      <c r="B146" s="36"/>
-      <c r="C146" s="33"/>
+      <c r="A146" s="34"/>
+      <c r="B146" s="32"/>
+      <c r="C146" s="44"/>
       <c r="D146" s="5" t="s">
         <v>57</v>
       </c>
@@ -5952,21 +6022,21 @@
         <v>0</v>
       </c>
       <c r="F146" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="G146" s="34"/>
+        <v>208</v>
+      </c>
+      <c r="G146" s="27"/>
       <c r="H146" s="15" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
     </row>
     <row r="147" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A147" s="30">
+      <c r="A147" s="33">
         <v>50</v>
       </c>
-      <c r="B147" s="36" t="s">
+      <c r="B147" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="C147" s="41" t="s">
+      <c r="C147" s="31" t="s">
         <v>14</v>
       </c>
       <c r="D147" s="5" t="s">
@@ -5976,17 +6046,17 @@
         <v>1</v>
       </c>
       <c r="F147" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="G147" s="34"/>
+        <v>296</v>
+      </c>
+      <c r="G147" s="27"/>
       <c r="H147" s="15" t="s">
-        <v>549</v>
+        <v>540</v>
       </c>
     </row>
     <row r="148" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A148" s="31"/>
-      <c r="B148" s="36"/>
-      <c r="C148" s="41"/>
+      <c r="A148" s="34"/>
+      <c r="B148" s="32"/>
+      <c r="C148" s="31"/>
       <c r="D148" s="5" t="s">
         <v>59</v>
       </c>
@@ -5994,63 +6064,63 @@
         <v>0</v>
       </c>
       <c r="F148" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="G148" s="34"/>
+        <v>296</v>
+      </c>
+      <c r="G148" s="27"/>
       <c r="H148" s="15" t="s">
-        <v>550</v>
+        <v>541</v>
       </c>
     </row>
     <row r="149" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A149" s="30">
+      <c r="A149" s="33">
         <v>51</v>
       </c>
-      <c r="B149" s="36" t="s">
+      <c r="B149" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="C149" s="26" t="s">
+      <c r="C149" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D149" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="E149" s="1">
+        <v>1</v>
+      </c>
+      <c r="F149" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="E149" s="1">
-        <v>1</v>
-      </c>
-      <c r="F149" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="G149" s="34"/>
+      <c r="G149" s="27"/>
       <c r="H149" s="15" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
     </row>
     <row r="150" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A150" s="31"/>
-      <c r="B150" s="36"/>
-      <c r="C150" s="26"/>
+      <c r="A150" s="34"/>
+      <c r="B150" s="32"/>
+      <c r="C150" s="28"/>
       <c r="D150" s="5" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E150" s="1">
         <v>0</v>
       </c>
       <c r="F150" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="G150" s="34"/>
+        <v>189</v>
+      </c>
+      <c r="G150" s="27"/>
       <c r="H150" s="15" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
     </row>
     <row r="151" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A151" s="30">
+      <c r="A151" s="33">
         <v>52</v>
       </c>
-      <c r="B151" s="36" t="s">
+      <c r="B151" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="C151" s="26" t="s">
+      <c r="C151" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D151" s="5" t="s">
@@ -6062,37 +6132,37 @@
       <c r="F151" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="G151" s="34"/>
+      <c r="G151" s="27"/>
       <c r="H151" s="15" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
     </row>
     <row r="152" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A152" s="31"/>
-      <c r="B152" s="36"/>
-      <c r="C152" s="26"/>
+      <c r="A152" s="34"/>
+      <c r="B152" s="32"/>
+      <c r="C152" s="28"/>
       <c r="D152" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E152" s="1">
         <v>0</v>
       </c>
       <c r="F152" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="G152" s="34"/>
+        <v>261</v>
+      </c>
+      <c r="G152" s="27"/>
       <c r="H152" s="15" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
     </row>
     <row r="153" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A153" s="30">
+      <c r="A153" s="33">
         <v>53</v>
       </c>
-      <c r="B153" s="36" t="s">
+      <c r="B153" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="C153" s="26" t="s">
+      <c r="C153" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D153" s="5" t="s">
@@ -6102,19 +6172,19 @@
         <v>0</v>
       </c>
       <c r="F153" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="G153" s="34" t="s">
-        <v>273</v>
+        <v>272</v>
+      </c>
+      <c r="G153" s="27" t="s">
+        <v>268</v>
       </c>
       <c r="H153" s="15" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
     </row>
     <row r="154" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A154" s="31"/>
-      <c r="B154" s="36"/>
-      <c r="C154" s="26"/>
+      <c r="A154" s="34"/>
+      <c r="B154" s="32"/>
+      <c r="C154" s="28"/>
       <c r="D154" s="5" t="s">
         <v>63</v>
       </c>
@@ -6122,105 +6192,105 @@
         <v>0</v>
       </c>
       <c r="F154" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="G154" s="34"/>
+        <v>273</v>
+      </c>
+      <c r="G154" s="27"/>
       <c r="H154" s="15" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
     </row>
     <row r="155" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A155" s="30">
+      <c r="A155" s="33">
         <v>54</v>
       </c>
-      <c r="B155" s="36" t="s">
+      <c r="B155" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="C155" s="26" t="s">
+      <c r="C155" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D155" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="E155" s="1">
+        <v>1</v>
+      </c>
+      <c r="F155" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="G155" s="27"/>
+      <c r="H155" s="15" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A156" s="34"/>
+      <c r="B156" s="32"/>
+      <c r="C156" s="28"/>
+      <c r="D156" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="E156" s="1">
+        <v>1</v>
+      </c>
+      <c r="F156" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="G156" s="27"/>
+      <c r="H156" s="15" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A157" s="33">
+        <v>55</v>
+      </c>
+      <c r="B157" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="C157" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="D157" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="E155" s="1">
-        <v>1</v>
-      </c>
-      <c r="F155" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="G155" s="34"/>
-      <c r="H155" s="15" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="156" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A156" s="31"/>
-      <c r="B156" s="36"/>
-      <c r="C156" s="26"/>
-      <c r="D156" s="5" t="s">
+      <c r="E157" s="1">
+        <v>1</v>
+      </c>
+      <c r="F157" s="5" t="s">
+        <v>610</v>
+      </c>
+      <c r="G157" s="27"/>
+      <c r="H157" s="15" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A158" s="34"/>
+      <c r="B158" s="32"/>
+      <c r="C158" s="28"/>
+      <c r="D158" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="E156" s="1">
-        <v>1</v>
-      </c>
-      <c r="F156" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="G156" s="34"/>
-      <c r="H156" s="15" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="157" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A157" s="30">
-        <v>55</v>
-      </c>
-      <c r="B157" s="36" t="s">
+      <c r="E158" s="1">
+        <v>1</v>
+      </c>
+      <c r="F158" s="5" t="s">
+        <v>611</v>
+      </c>
+      <c r="G158" s="27"/>
+      <c r="H158" s="15" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A159" s="33">
+        <v>56</v>
+      </c>
+      <c r="B159" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="C157" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="D157" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="E157" s="1">
-        <v>1</v>
-      </c>
-      <c r="F157" s="5" t="s">
-        <v>623</v>
-      </c>
-      <c r="G157" s="34"/>
-      <c r="H157" s="15" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="158" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A158" s="31"/>
-      <c r="B158" s="36"/>
-      <c r="C158" s="26"/>
-      <c r="D158" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="E158" s="1">
-        <v>1</v>
-      </c>
-      <c r="F158" s="5" t="s">
-        <v>624</v>
-      </c>
-      <c r="G158" s="34"/>
-      <c r="H158" s="15" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="159" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A159" s="30">
-        <v>56</v>
-      </c>
-      <c r="B159" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="C159" s="26" t="s">
+      <c r="C159" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D159" s="5" t="s">
@@ -6230,19 +6300,19 @@
         <v>1</v>
       </c>
       <c r="F159" s="5" t="s">
-        <v>622</v>
-      </c>
-      <c r="G159" s="34" t="s">
-        <v>570</v>
+        <v>609</v>
+      </c>
+      <c r="G159" s="27" t="s">
+        <v>558</v>
       </c>
       <c r="H159" s="15" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
     </row>
     <row r="160" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A160" s="31"/>
-      <c r="B160" s="36"/>
-      <c r="C160" s="26"/>
+      <c r="A160" s="34"/>
+      <c r="B160" s="32"/>
+      <c r="C160" s="28"/>
       <c r="D160" s="5" t="s">
         <v>155</v>
       </c>
@@ -6250,107 +6320,107 @@
         <v>0</v>
       </c>
       <c r="F160" s="5" t="s">
-        <v>622</v>
-      </c>
-      <c r="G160" s="34"/>
+        <v>609</v>
+      </c>
+      <c r="G160" s="27"/>
       <c r="H160" s="15" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
     </row>
     <row r="161" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A161" s="30">
+      <c r="A161" s="33">
         <v>57</v>
       </c>
-      <c r="B161" s="36" t="s">
+      <c r="B161" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="C161" s="26" t="s">
+      <c r="C161" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E161" s="1">
         <v>0</v>
       </c>
       <c r="F161" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="G161" s="34" t="s">
-        <v>605</v>
+        <v>301</v>
+      </c>
+      <c r="G161" s="27" t="s">
+        <v>592</v>
       </c>
       <c r="H161" s="15" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
     </row>
     <row r="162" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A162" s="31"/>
-      <c r="B162" s="36"/>
-      <c r="C162" s="26"/>
+      <c r="A162" s="34"/>
+      <c r="B162" s="32"/>
+      <c r="C162" s="28"/>
       <c r="D162" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E162" s="1">
         <v>0</v>
       </c>
       <c r="F162" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="G162" s="34"/>
+        <v>302</v>
+      </c>
+      <c r="G162" s="27"/>
       <c r="H162" s="15" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
     </row>
     <row r="163" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A163" s="30">
+      <c r="A163" s="33">
         <v>58</v>
       </c>
-      <c r="B163" s="36" t="s">
+      <c r="B163" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="C163" s="33" t="s">
+      <c r="C163" s="44" t="s">
         <v>14</v>
       </c>
       <c r="D163" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E163" s="1">
         <v>0</v>
       </c>
       <c r="F163" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="G163" s="34"/>
+        <v>303</v>
+      </c>
+      <c r="G163" s="27"/>
       <c r="H163" s="15" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
     </row>
     <row r="164" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A164" s="31"/>
-      <c r="B164" s="36"/>
-      <c r="C164" s="33"/>
+      <c r="A164" s="34"/>
+      <c r="B164" s="32"/>
+      <c r="C164" s="44"/>
       <c r="D164" s="5" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E164" s="1">
         <v>0</v>
       </c>
       <c r="F164" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="G164" s="34"/>
+        <v>304</v>
+      </c>
+      <c r="G164" s="27"/>
       <c r="H164" s="15" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
     </row>
     <row r="165" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A165" s="30">
+      <c r="A165" s="33">
         <v>59</v>
       </c>
-      <c r="B165" s="36" t="s">
+      <c r="B165" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="C165" s="33" t="s">
+      <c r="C165" s="44" t="s">
         <v>14</v>
       </c>
       <c r="D165" s="5" t="s">
@@ -6360,19 +6430,19 @@
         <v>1</v>
       </c>
       <c r="F165" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="G165" s="34" t="s">
-        <v>201</v>
+        <v>270</v>
+      </c>
+      <c r="G165" s="27" t="s">
+        <v>199</v>
       </c>
       <c r="H165" s="15" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
     </row>
     <row r="166" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A166" s="31"/>
-      <c r="B166" s="36"/>
-      <c r="C166" s="33"/>
+      <c r="A166" s="34"/>
+      <c r="B166" s="32"/>
+      <c r="C166" s="44"/>
       <c r="D166" s="5" t="s">
         <v>147</v>
       </c>
@@ -6380,21 +6450,21 @@
         <v>0</v>
       </c>
       <c r="F166" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="G166" s="34"/>
+        <v>270</v>
+      </c>
+      <c r="G166" s="27"/>
       <c r="H166" s="15" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
     </row>
     <row r="167" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A167" s="30">
+      <c r="A167" s="33">
         <v>60</v>
       </c>
-      <c r="B167" s="36" t="s">
+      <c r="B167" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="C167" s="33" t="s">
+      <c r="C167" s="44" t="s">
         <v>14</v>
       </c>
       <c r="D167" s="5" t="s">
@@ -6404,17 +6474,17 @@
         <v>1</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="G167" s="34"/>
+        <v>266</v>
+      </c>
+      <c r="G167" s="27"/>
       <c r="H167" s="15" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
     </row>
     <row r="168" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A168" s="31"/>
-      <c r="B168" s="36"/>
-      <c r="C168" s="33"/>
+      <c r="A168" s="34"/>
+      <c r="B168" s="32"/>
+      <c r="C168" s="44"/>
       <c r="D168" s="5" t="s">
         <v>119</v>
       </c>
@@ -6422,21 +6492,21 @@
         <v>1</v>
       </c>
       <c r="F168" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="G168" s="34"/>
+        <v>267</v>
+      </c>
+      <c r="G168" s="27"/>
       <c r="H168" s="15" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
     </row>
     <row r="169" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A169" s="30">
+      <c r="A169" s="33">
         <v>61</v>
       </c>
-      <c r="B169" s="36" t="s">
+      <c r="B169" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="C169" s="26" t="s">
+      <c r="C169" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D169" s="5" t="s">
@@ -6446,17 +6516,17 @@
         <v>1</v>
       </c>
       <c r="F169" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="G169" s="34"/>
+        <v>265</v>
+      </c>
+      <c r="G169" s="27"/>
       <c r="H169" s="15" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
     </row>
     <row r="170" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A170" s="31"/>
-      <c r="B170" s="36"/>
-      <c r="C170" s="26"/>
+      <c r="A170" s="34"/>
+      <c r="B170" s="32"/>
+      <c r="C170" s="28"/>
       <c r="D170" s="5" t="s">
         <v>84</v>
       </c>
@@ -6464,105 +6534,107 @@
         <v>0</v>
       </c>
       <c r="F170" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="G170" s="34"/>
+        <v>265</v>
+      </c>
+      <c r="G170" s="27"/>
       <c r="H170" s="15" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
     </row>
     <row r="171" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A171" s="30">
+      <c r="A171" s="33">
         <v>62</v>
       </c>
-      <c r="B171" s="36" t="s">
+      <c r="B171" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="C171" s="41" t="s">
+      <c r="C171" s="31" t="s">
         <v>14</v>
       </c>
       <c r="D171" s="5" t="s">
-        <v>590</v>
+        <v>577</v>
       </c>
       <c r="E171" s="1">
         <v>1</v>
       </c>
       <c r="F171" s="5" t="s">
-        <v>592</v>
-      </c>
-      <c r="G171" s="34"/>
+        <v>579</v>
+      </c>
+      <c r="G171" s="27"/>
       <c r="H171" s="15" t="s">
-        <v>591</v>
+        <v>578</v>
       </c>
     </row>
     <row r="172" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A172" s="31"/>
-      <c r="B172" s="36"/>
-      <c r="C172" s="41"/>
+      <c r="A172" s="34"/>
+      <c r="B172" s="32"/>
+      <c r="C172" s="31"/>
       <c r="D172" s="5" t="s">
-        <v>589</v>
+        <v>576</v>
       </c>
       <c r="E172" s="1">
         <v>1</v>
       </c>
       <c r="F172" s="5" t="s">
-        <v>593</v>
-      </c>
-      <c r="G172" s="34"/>
+        <v>580</v>
+      </c>
+      <c r="G172" s="27"/>
       <c r="H172" s="15" t="s">
-        <v>591</v>
+        <v>578</v>
       </c>
     </row>
     <row r="173" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A173" s="30">
+      <c r="A173" s="33">
         <v>63</v>
       </c>
-      <c r="B173" s="36" t="s">
+      <c r="B173" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="C173" s="33" t="s">
+      <c r="C173" s="44" t="s">
         <v>14</v>
       </c>
       <c r="D173" s="5" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E173" s="1">
         <v>1</v>
       </c>
       <c r="F173" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="G173" s="34"/>
+        <v>637</v>
+      </c>
+      <c r="G173" s="27" t="s">
+        <v>636</v>
+      </c>
       <c r="H173" s="15" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
     </row>
     <row r="174" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A174" s="31"/>
-      <c r="B174" s="36"/>
-      <c r="C174" s="33"/>
+      <c r="A174" s="34"/>
+      <c r="B174" s="32"/>
+      <c r="C174" s="44"/>
       <c r="D174" s="5" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E174" s="1">
         <v>1</v>
       </c>
       <c r="F174" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="G174" s="34"/>
+        <v>638</v>
+      </c>
+      <c r="G174" s="27"/>
       <c r="H174" s="15" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
     </row>
     <row r="175" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A175" s="30">
+      <c r="A175" s="33">
         <v>64</v>
       </c>
-      <c r="B175" s="36" t="s">
+      <c r="B175" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="C175" s="26" t="s">
+      <c r="C175" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D175" s="5" t="s">
@@ -6572,19 +6644,19 @@
         <v>1</v>
       </c>
       <c r="F175" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="G175" s="34" t="s">
+        <v>523</v>
+      </c>
+      <c r="G175" s="27" t="s">
         <v>115</v>
       </c>
       <c r="H175" s="15" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
     </row>
     <row r="176" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A176" s="31"/>
-      <c r="B176" s="36"/>
-      <c r="C176" s="26"/>
+      <c r="A176" s="34"/>
+      <c r="B176" s="32"/>
+      <c r="C176" s="28"/>
       <c r="D176" s="5" t="s">
         <v>114</v>
       </c>
@@ -6592,21 +6664,21 @@
         <v>1</v>
       </c>
       <c r="F176" s="5" t="s">
-        <v>533</v>
-      </c>
-      <c r="G176" s="34"/>
+        <v>524</v>
+      </c>
+      <c r="G176" s="27"/>
       <c r="H176" s="15" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
     </row>
     <row r="177" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A177" s="30">
+      <c r="A177" s="33">
         <v>65</v>
       </c>
-      <c r="B177" s="32" t="s">
+      <c r="B177" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="C177" s="26" t="s">
+      <c r="C177" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D177" s="5" t="s">
@@ -6616,17 +6688,17 @@
         <v>1</v>
       </c>
       <c r="F177" s="5" t="s">
-        <v>620</v>
-      </c>
-      <c r="G177" s="34"/>
+        <v>607</v>
+      </c>
+      <c r="G177" s="27"/>
       <c r="H177" s="15" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
     </row>
     <row r="178" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A178" s="31"/>
-      <c r="B178" s="32"/>
-      <c r="C178" s="26"/>
+      <c r="A178" s="34"/>
+      <c r="B178" s="30"/>
+      <c r="C178" s="28"/>
       <c r="D178" s="5" t="s">
         <v>68</v>
       </c>
@@ -6634,21 +6706,21 @@
         <v>0</v>
       </c>
       <c r="F178" s="5" t="s">
-        <v>620</v>
-      </c>
-      <c r="G178" s="34"/>
+        <v>607</v>
+      </c>
+      <c r="G178" s="27"/>
       <c r="H178" s="15" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
     </row>
     <row r="179" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A179" s="30">
+      <c r="A179" s="33">
         <v>66</v>
       </c>
-      <c r="B179" s="32" t="s">
+      <c r="B179" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="C179" s="26" t="s">
+      <c r="C179" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D179" s="5" t="s">
@@ -6658,17 +6730,17 @@
         <v>1</v>
       </c>
       <c r="F179" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="G179" s="34"/>
+        <v>269</v>
+      </c>
+      <c r="G179" s="27"/>
       <c r="H179" s="15" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
     </row>
     <row r="180" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A180" s="31"/>
-      <c r="B180" s="32"/>
-      <c r="C180" s="26"/>
+      <c r="A180" s="34"/>
+      <c r="B180" s="30"/>
+      <c r="C180" s="28"/>
       <c r="D180" s="5" t="s">
         <v>61</v>
       </c>
@@ -6676,21 +6748,21 @@
         <v>1</v>
       </c>
       <c r="F180" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="G180" s="34"/>
+        <v>271</v>
+      </c>
+      <c r="G180" s="27"/>
       <c r="H180" s="15" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
     </row>
     <row r="181" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A181" s="30">
+      <c r="A181" s="33">
         <v>67</v>
       </c>
-      <c r="B181" s="32" t="s">
+      <c r="B181" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="C181" s="26" t="s">
+      <c r="C181" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D181" s="5" t="s">
@@ -6700,17 +6772,17 @@
         <v>3</v>
       </c>
       <c r="F181" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="G181" s="34"/>
+        <v>209</v>
+      </c>
+      <c r="G181" s="27"/>
       <c r="H181" s="15" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
     </row>
     <row r="182" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A182" s="31"/>
-      <c r="B182" s="32"/>
-      <c r="C182" s="26"/>
+      <c r="A182" s="34"/>
+      <c r="B182" s="30"/>
+      <c r="C182" s="28"/>
       <c r="D182" s="5" t="s">
         <v>72</v>
       </c>
@@ -6718,63 +6790,63 @@
         <v>3</v>
       </c>
       <c r="F182" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="G182" s="34"/>
+        <v>210</v>
+      </c>
+      <c r="G182" s="27"/>
       <c r="H182" s="15" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
     </row>
     <row r="183" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A183" s="30">
+      <c r="A183" s="33">
         <v>68</v>
       </c>
-      <c r="B183" s="32" t="s">
+      <c r="B183" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="C183" s="26" t="s">
+      <c r="C183" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D183" s="5" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E183" s="1">
         <v>3</v>
       </c>
       <c r="F183" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="G183" s="34"/>
+        <v>236</v>
+      </c>
+      <c r="G183" s="27"/>
       <c r="H183" s="15" t="s">
-        <v>595</v>
+        <v>582</v>
       </c>
     </row>
     <row r="184" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A184" s="31"/>
-      <c r="B184" s="32"/>
-      <c r="C184" s="26"/>
+      <c r="A184" s="34"/>
+      <c r="B184" s="30"/>
+      <c r="C184" s="28"/>
       <c r="D184" s="5" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E184" s="1">
         <v>2</v>
       </c>
       <c r="F184" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="G184" s="34"/>
+        <v>236</v>
+      </c>
+      <c r="G184" s="27"/>
       <c r="H184" s="15" t="s">
-        <v>596</v>
+        <v>583</v>
       </c>
     </row>
     <row r="185" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A185" s="30">
+      <c r="A185" s="33">
         <v>69</v>
       </c>
-      <c r="B185" s="32" t="s">
+      <c r="B185" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="C185" s="26" t="s">
+      <c r="C185" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D185" s="5" t="s">
@@ -6784,17 +6856,17 @@
         <v>3</v>
       </c>
       <c r="F185" s="5" t="s">
-        <v>621</v>
-      </c>
-      <c r="G185" s="34"/>
+        <v>608</v>
+      </c>
+      <c r="G185" s="27"/>
       <c r="H185" s="15" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
     </row>
     <row r="186" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A186" s="31"/>
-      <c r="B186" s="32"/>
-      <c r="C186" s="26"/>
+      <c r="A186" s="34"/>
+      <c r="B186" s="30"/>
+      <c r="C186" s="28"/>
       <c r="D186" s="5" t="s">
         <v>74</v>
       </c>
@@ -6802,63 +6874,63 @@
         <v>2</v>
       </c>
       <c r="F186" s="5" t="s">
-        <v>621</v>
-      </c>
-      <c r="G186" s="34"/>
+        <v>608</v>
+      </c>
+      <c r="G186" s="27"/>
       <c r="H186" s="15" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
     </row>
     <row r="187" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A187" s="30">
+      <c r="A187" s="33">
         <v>70</v>
       </c>
-      <c r="B187" s="32" t="s">
+      <c r="B187" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="C187" s="33" t="s">
+      <c r="C187" s="44" t="s">
         <v>14</v>
       </c>
       <c r="D187" s="5" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="E187" s="1">
         <v>0</v>
       </c>
       <c r="F187" s="5" t="s">
-        <v>476</v>
-      </c>
-      <c r="G187" s="34"/>
+        <v>469</v>
+      </c>
+      <c r="G187" s="27"/>
       <c r="H187" s="15" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
     </row>
     <row r="188" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A188" s="31"/>
-      <c r="B188" s="32"/>
-      <c r="C188" s="33"/>
+      <c r="A188" s="34"/>
+      <c r="B188" s="30"/>
+      <c r="C188" s="44"/>
       <c r="D188" s="5" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="E188" s="1">
         <v>0</v>
       </c>
       <c r="F188" s="5" t="s">
-        <v>477</v>
-      </c>
-      <c r="G188" s="34"/>
+        <v>470</v>
+      </c>
+      <c r="G188" s="27"/>
       <c r="H188" s="15" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
     </row>
     <row r="189" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A189" s="30">
+      <c r="A189" s="33">
         <v>71</v>
       </c>
-      <c r="B189" s="32" t="s">
+      <c r="B189" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="C189" s="33" t="s">
+      <c r="C189" s="44" t="s">
         <v>14</v>
       </c>
       <c r="D189" s="5" t="s">
@@ -6868,19 +6940,19 @@
         <v>0</v>
       </c>
       <c r="F189" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="G189" s="34" t="s">
-        <v>600</v>
+        <v>277</v>
+      </c>
+      <c r="G189" s="27" t="s">
+        <v>587</v>
       </c>
       <c r="H189" s="15" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
     </row>
     <row r="190" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A190" s="31"/>
-      <c r="B190" s="32"/>
-      <c r="C190" s="33"/>
+      <c r="A190" s="34"/>
+      <c r="B190" s="30"/>
+      <c r="C190" s="44"/>
       <c r="D190" s="5" t="s">
         <v>88</v>
       </c>
@@ -6888,63 +6960,63 @@
         <v>0</v>
       </c>
       <c r="F190" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="G190" s="34"/>
+        <v>278</v>
+      </c>
+      <c r="G190" s="27"/>
       <c r="H190" s="15" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
     </row>
     <row r="191" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A191" s="30">
+      <c r="A191" s="33">
         <v>72</v>
       </c>
-      <c r="B191" s="32" t="s">
+      <c r="B191" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="C191" s="33" t="s">
+      <c r="C191" s="44" t="s">
         <v>14</v>
       </c>
       <c r="D191" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E191" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F191" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="G191" s="34"/>
+        <v>230</v>
+      </c>
+      <c r="G191" s="27"/>
       <c r="H191" s="15" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
     </row>
     <row r="192" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A192" s="31"/>
-      <c r="B192" s="32"/>
-      <c r="C192" s="33"/>
+      <c r="A192" s="34"/>
+      <c r="B192" s="30"/>
+      <c r="C192" s="44"/>
       <c r="D192" s="5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E192" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F192" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="G192" s="34"/>
+        <v>231</v>
+      </c>
+      <c r="G192" s="27"/>
       <c r="H192" s="15" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
     </row>
     <row r="193" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A193" s="30">
+      <c r="A193" s="33">
         <v>73</v>
       </c>
-      <c r="B193" s="32" t="s">
+      <c r="B193" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="C193" s="26" t="s">
+      <c r="C193" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D193" s="5" t="s">
@@ -6954,19 +7026,19 @@
         <v>4</v>
       </c>
       <c r="F193" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="G193" s="34" t="s">
-        <v>222</v>
+        <v>305</v>
+      </c>
+      <c r="G193" s="27" t="s">
+        <v>218</v>
       </c>
       <c r="H193" s="15" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
     </row>
     <row r="194" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A194" s="31"/>
-      <c r="B194" s="32"/>
-      <c r="C194" s="26"/>
+      <c r="A194" s="34"/>
+      <c r="B194" s="30"/>
+      <c r="C194" s="28"/>
       <c r="D194" s="5" t="s">
         <v>132</v>
       </c>
@@ -6974,21 +7046,21 @@
         <v>4</v>
       </c>
       <c r="F194" s="5" t="s">
-        <v>313</v>
-      </c>
-      <c r="G194" s="34"/>
+        <v>306</v>
+      </c>
+      <c r="G194" s="27"/>
       <c r="H194" s="15" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
     </row>
     <row r="195" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A195" s="30">
+      <c r="A195" s="33">
         <v>74</v>
       </c>
-      <c r="B195" s="32" t="s">
+      <c r="B195" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="C195" s="26" t="s">
+      <c r="C195" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D195" s="5" t="s">
@@ -6998,19 +7070,19 @@
         <v>1</v>
       </c>
       <c r="F195" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="G195" s="34" t="s">
+        <v>263</v>
+      </c>
+      <c r="G195" s="27" t="s">
         <v>143</v>
       </c>
       <c r="H195" s="15" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
     </row>
     <row r="196" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A196" s="31"/>
-      <c r="B196" s="32"/>
-      <c r="C196" s="26"/>
+      <c r="A196" s="34"/>
+      <c r="B196" s="30"/>
+      <c r="C196" s="28"/>
       <c r="D196" s="5" t="s">
         <v>110</v>
       </c>
@@ -7018,21 +7090,21 @@
         <v>1</v>
       </c>
       <c r="F196" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="G196" s="34"/>
+        <v>264</v>
+      </c>
+      <c r="G196" s="27"/>
       <c r="H196" s="15" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
     </row>
     <row r="197" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A197" s="44">
+      <c r="A197" s="35">
         <v>75</v>
       </c>
-      <c r="B197" s="36" t="s">
+      <c r="B197" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="C197" s="26" t="s">
+      <c r="C197" s="28" t="s">
         <v>89</v>
       </c>
       <c r="D197" s="5" t="s">
@@ -7042,19 +7114,19 @@
         <v>2</v>
       </c>
       <c r="F197" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="G197" s="34" t="s">
-        <v>643</v>
+        <v>307</v>
+      </c>
+      <c r="G197" s="27" t="s">
+        <v>626</v>
       </c>
       <c r="H197" s="15" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
     </row>
     <row r="198" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A198" s="45"/>
-      <c r="B198" s="36"/>
-      <c r="C198" s="26"/>
+      <c r="A198" s="36"/>
+      <c r="B198" s="32"/>
+      <c r="C198" s="28"/>
       <c r="D198" s="5" t="s">
         <v>95</v>
       </c>
@@ -7062,21 +7134,21 @@
         <v>1</v>
       </c>
       <c r="F198" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="G198" s="34"/>
+        <v>307</v>
+      </c>
+      <c r="G198" s="27"/>
       <c r="H198" s="15" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
     </row>
     <row r="199" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A199" s="30">
+      <c r="A199" s="33">
         <v>76</v>
       </c>
-      <c r="B199" s="36" t="s">
+      <c r="B199" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="C199" s="26" t="s">
+      <c r="C199" s="28" t="s">
         <v>89</v>
       </c>
       <c r="D199" s="5" t="s">
@@ -7086,19 +7158,19 @@
         <v>1</v>
       </c>
       <c r="F199" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="G199" s="34" t="s">
-        <v>229</v>
+        <v>223</v>
+      </c>
+      <c r="G199" s="27" t="s">
+        <v>225</v>
       </c>
       <c r="H199" s="15" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
     </row>
     <row r="200" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A200" s="31"/>
-      <c r="B200" s="36"/>
-      <c r="C200" s="26"/>
+      <c r="A200" s="34"/>
+      <c r="B200" s="32"/>
+      <c r="C200" s="28"/>
       <c r="D200" s="5" t="s">
         <v>107</v>
       </c>
@@ -7106,21 +7178,21 @@
         <v>1</v>
       </c>
       <c r="F200" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="G200" s="34"/>
+        <v>224</v>
+      </c>
+      <c r="G200" s="27"/>
       <c r="H200" s="15" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
     </row>
     <row r="201" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A201" s="44">
+      <c r="A201" s="35">
         <v>77</v>
       </c>
-      <c r="B201" s="36" t="s">
+      <c r="B201" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="C201" s="26" t="s">
+      <c r="C201" s="28" t="s">
         <v>89</v>
       </c>
       <c r="D201" s="5" t="s">
@@ -7130,19 +7202,19 @@
         <v>2</v>
       </c>
       <c r="F201" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="G201" s="34" t="s">
-        <v>641</v>
+        <v>594</v>
+      </c>
+      <c r="G201" s="27" t="s">
+        <v>624</v>
       </c>
       <c r="H201" s="15" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
     </row>
     <row r="202" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A202" s="45"/>
-      <c r="B202" s="36"/>
-      <c r="C202" s="26"/>
+      <c r="A202" s="36"/>
+      <c r="B202" s="32"/>
+      <c r="C202" s="28"/>
       <c r="D202" s="5" t="s">
         <v>112</v>
       </c>
@@ -7150,21 +7222,21 @@
         <v>2</v>
       </c>
       <c r="F202" s="5" t="s">
-        <v>608</v>
-      </c>
-      <c r="G202" s="34"/>
+        <v>595</v>
+      </c>
+      <c r="G202" s="27"/>
       <c r="H202" s="15" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
     </row>
     <row r="203" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A203" s="30">
+      <c r="A203" s="33">
         <v>78</v>
       </c>
-      <c r="B203" s="36" t="s">
+      <c r="B203" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="C203" s="26" t="s">
+      <c r="C203" s="28" t="s">
         <v>89</v>
       </c>
       <c r="D203" s="5" t="s">
@@ -7174,17 +7246,17 @@
         <v>1</v>
       </c>
       <c r="F203" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="G203" s="34"/>
+        <v>632</v>
+      </c>
+      <c r="G203" s="27"/>
       <c r="H203" s="15" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
     </row>
     <row r="204" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A204" s="31"/>
-      <c r="B204" s="36"/>
-      <c r="C204" s="26"/>
+      <c r="A204" s="34"/>
+      <c r="B204" s="32"/>
+      <c r="C204" s="28"/>
       <c r="D204" s="5" t="s">
         <v>91</v>
       </c>
@@ -7192,21 +7264,21 @@
         <v>1</v>
       </c>
       <c r="F204" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="G204" s="34"/>
+        <v>250</v>
+      </c>
+      <c r="G204" s="27"/>
       <c r="H204" s="15" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
     </row>
     <row r="205" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A205" s="30">
+      <c r="A205" s="33">
         <v>79</v>
       </c>
-      <c r="B205" s="36" t="s">
+      <c r="B205" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="C205" s="26" t="s">
+      <c r="C205" s="28" t="s">
         <v>89</v>
       </c>
       <c r="D205" s="5" t="s">
@@ -7216,17 +7288,17 @@
         <v>1</v>
       </c>
       <c r="F205" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="G205" s="34"/>
+        <v>251</v>
+      </c>
+      <c r="G205" s="27"/>
       <c r="H205" s="15" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
     </row>
     <row r="206" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A206" s="31"/>
-      <c r="B206" s="36"/>
-      <c r="C206" s="26"/>
+      <c r="A206" s="34"/>
+      <c r="B206" s="32"/>
+      <c r="C206" s="28"/>
       <c r="D206" s="5" t="s">
         <v>93</v>
       </c>
@@ -7234,21 +7306,21 @@
         <v>0</v>
       </c>
       <c r="F206" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="G206" s="34"/>
+        <v>251</v>
+      </c>
+      <c r="G206" s="27"/>
       <c r="H206" s="15" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
     </row>
     <row r="207" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A207" s="30">
+      <c r="A207" s="33">
         <v>80</v>
       </c>
-      <c r="B207" s="36" t="s">
+      <c r="B207" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="C207" s="26" t="s">
+      <c r="C207" s="28" t="s">
         <v>89</v>
       </c>
       <c r="D207" s="5" t="s">
@@ -7258,19 +7330,19 @@
         <v>1</v>
       </c>
       <c r="F207" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="G207" s="34" t="s">
-        <v>249</v>
+        <v>237</v>
+      </c>
+      <c r="G207" s="27" t="s">
+        <v>245</v>
       </c>
       <c r="H207" s="15" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
     </row>
     <row r="208" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A208" s="31"/>
-      <c r="B208" s="36"/>
-      <c r="C208" s="26"/>
+      <c r="A208" s="34"/>
+      <c r="B208" s="32"/>
+      <c r="C208" s="28"/>
       <c r="D208" s="5" t="s">
         <v>105</v>
       </c>
@@ -7278,21 +7350,21 @@
         <v>1</v>
       </c>
       <c r="F208" s="5" t="s">
-        <v>636</v>
-      </c>
-      <c r="G208" s="34"/>
+        <v>621</v>
+      </c>
+      <c r="G208" s="27"/>
       <c r="H208" s="15" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
     </row>
     <row r="209" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A209" s="44">
+      <c r="A209" s="35">
         <v>81</v>
       </c>
-      <c r="B209" s="36" t="s">
+      <c r="B209" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="C209" s="26" t="s">
+      <c r="C209" s="28" t="s">
         <v>89</v>
       </c>
       <c r="D209" s="5" t="s">
@@ -7302,19 +7374,19 @@
         <v>1</v>
       </c>
       <c r="F209" s="5" t="s">
-        <v>637</v>
-      </c>
-      <c r="G209" s="34" t="s">
-        <v>639</v>
+        <v>658</v>
+      </c>
+      <c r="G209" s="27" t="s">
+        <v>622</v>
       </c>
       <c r="H209" s="15" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
     </row>
     <row r="210" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A210" s="45"/>
-      <c r="B210" s="36"/>
-      <c r="C210" s="26"/>
+      <c r="A210" s="36"/>
+      <c r="B210" s="32"/>
+      <c r="C210" s="28"/>
       <c r="D210" s="5" t="s">
         <v>99</v>
       </c>
@@ -7322,63 +7394,63 @@
         <v>1</v>
       </c>
       <c r="F210" s="5" t="s">
-        <v>638</v>
-      </c>
-      <c r="G210" s="34"/>
+        <v>659</v>
+      </c>
+      <c r="G210" s="27"/>
       <c r="H210" s="15" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
     </row>
     <row r="211" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A211" s="30">
+      <c r="A211" s="33">
         <v>82</v>
       </c>
-      <c r="B211" s="42" t="s">
+      <c r="B211" s="49" t="s">
         <v>29</v>
       </c>
-      <c r="C211" s="26" t="s">
+      <c r="C211" s="28" t="s">
         <v>89</v>
       </c>
       <c r="D211" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E211" s="1">
         <v>1</v>
       </c>
       <c r="F211" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="G211" s="34"/>
+        <v>279</v>
+      </c>
+      <c r="G211" s="27"/>
       <c r="H211" s="15" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
     </row>
     <row r="212" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A212" s="31"/>
-      <c r="B212" s="43"/>
-      <c r="C212" s="26"/>
+      <c r="A212" s="34"/>
+      <c r="B212" s="50"/>
+      <c r="C212" s="28"/>
       <c r="D212" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E212" s="1">
         <v>0</v>
       </c>
       <c r="F212" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="G212" s="34"/>
+        <v>279</v>
+      </c>
+      <c r="G212" s="27"/>
       <c r="H212" s="15" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
     </row>
     <row r="213" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A213" s="30">
+      <c r="A213" s="33">
         <v>83</v>
       </c>
-      <c r="B213" s="32" t="s">
+      <c r="B213" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="C213" s="26" t="s">
+      <c r="C213" s="28" t="s">
         <v>89</v>
       </c>
       <c r="D213" s="5" t="s">
@@ -7388,19 +7460,19 @@
         <v>2</v>
       </c>
       <c r="F213" s="5" t="s">
-        <v>599</v>
-      </c>
-      <c r="G213" s="34" t="s">
-        <v>642</v>
+        <v>586</v>
+      </c>
+      <c r="G213" s="27" t="s">
+        <v>625</v>
       </c>
       <c r="H213" s="15" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
     </row>
     <row r="214" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A214" s="31"/>
-      <c r="B214" s="32"/>
-      <c r="C214" s="26"/>
+      <c r="A214" s="34"/>
+      <c r="B214" s="30"/>
+      <c r="C214" s="28"/>
       <c r="D214" s="5" t="s">
         <v>138</v>
       </c>
@@ -7408,21 +7480,21 @@
         <v>1</v>
       </c>
       <c r="F214" s="5" t="s">
-        <v>606</v>
-      </c>
-      <c r="G214" s="34"/>
+        <v>593</v>
+      </c>
+      <c r="G214" s="27"/>
       <c r="H214" s="15" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
     </row>
     <row r="215" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A215" s="30">
+      <c r="A215" s="33">
         <v>84</v>
       </c>
-      <c r="B215" s="32" t="s">
+      <c r="B215" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="C215" s="26" t="s">
+      <c r="C215" s="28" t="s">
         <v>89</v>
       </c>
       <c r="D215" s="5" t="s">
@@ -7432,19 +7504,19 @@
         <v>2</v>
       </c>
       <c r="F215" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="G215" s="34" t="s">
-        <v>316</v>
+        <v>254</v>
+      </c>
+      <c r="G215" s="27" t="s">
+        <v>309</v>
       </c>
       <c r="H215" s="15" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
     </row>
     <row r="216" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A216" s="31"/>
-      <c r="B216" s="32"/>
-      <c r="C216" s="26"/>
+      <c r="A216" s="34"/>
+      <c r="B216" s="30"/>
+      <c r="C216" s="28"/>
       <c r="D216" s="5" t="s">
         <v>97</v>
       </c>
@@ -7452,21 +7524,21 @@
         <v>2</v>
       </c>
       <c r="F216" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="G216" s="34"/>
+        <v>255</v>
+      </c>
+      <c r="G216" s="27"/>
       <c r="H216" s="15" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
     </row>
     <row r="217" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A217" s="30">
+      <c r="A217" s="33">
         <v>85</v>
       </c>
-      <c r="B217" s="32" t="s">
+      <c r="B217" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="C217" s="26" t="s">
+      <c r="C217" s="28" t="s">
         <v>89</v>
       </c>
       <c r="D217" s="5" t="s">
@@ -7476,17 +7548,17 @@
         <v>3</v>
       </c>
       <c r="F217" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="G217" s="34"/>
+        <v>222</v>
+      </c>
+      <c r="G217" s="27"/>
       <c r="H217" s="15" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
     </row>
     <row r="218" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A218" s="31"/>
-      <c r="B218" s="32"/>
-      <c r="C218" s="26"/>
+      <c r="A218" s="34"/>
+      <c r="B218" s="30"/>
+      <c r="C218" s="28"/>
       <c r="D218" s="5" t="s">
         <v>101</v>
       </c>
@@ -7494,21 +7566,21 @@
         <v>2</v>
       </c>
       <c r="F218" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="G218" s="34"/>
+        <v>222</v>
+      </c>
+      <c r="G218" s="27"/>
       <c r="H218" s="15" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
     </row>
     <row r="219" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A219" s="30">
+      <c r="A219" s="33">
         <v>86</v>
       </c>
-      <c r="B219" s="32" t="s">
+      <c r="B219" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="C219" s="26" t="s">
+      <c r="C219" s="28" t="s">
         <v>89</v>
       </c>
       <c r="D219" s="5" t="s">
@@ -7518,17 +7590,17 @@
         <v>2</v>
       </c>
       <c r="F219" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="G219" s="34"/>
+        <v>192</v>
+      </c>
+      <c r="G219" s="27"/>
       <c r="H219" s="15" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
     </row>
     <row r="220" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A220" s="31"/>
-      <c r="B220" s="32"/>
-      <c r="C220" s="26"/>
+      <c r="A220" s="34"/>
+      <c r="B220" s="30"/>
+      <c r="C220" s="28"/>
       <c r="D220" s="5" t="s">
         <v>153</v>
       </c>
@@ -7536,21 +7608,21 @@
         <v>2</v>
       </c>
       <c r="F220" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="G220" s="34"/>
+        <v>200</v>
+      </c>
+      <c r="G220" s="27"/>
       <c r="H220" s="15" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
     </row>
     <row r="221" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A221" s="30">
+      <c r="A221" s="33">
         <v>87</v>
       </c>
-      <c r="B221" s="32" t="s">
+      <c r="B221" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="C221" s="41" t="s">
+      <c r="C221" s="31" t="s">
         <v>89</v>
       </c>
       <c r="D221" s="5" t="s">
@@ -7560,19 +7632,19 @@
         <v>2</v>
       </c>
       <c r="F221" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="G221" s="34" t="s">
-        <v>640</v>
+        <v>258</v>
+      </c>
+      <c r="G221" s="27" t="s">
+        <v>623</v>
       </c>
       <c r="H221" s="15" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
     </row>
     <row r="222" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A222" s="31"/>
-      <c r="B222" s="32"/>
-      <c r="C222" s="41"/>
+      <c r="A222" s="34"/>
+      <c r="B222" s="30"/>
+      <c r="C222" s="31"/>
       <c r="D222" s="5" t="s">
         <v>103</v>
       </c>
@@ -7580,21 +7652,21 @@
         <v>1</v>
       </c>
       <c r="F222" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="G222" s="34"/>
+        <v>258</v>
+      </c>
+      <c r="G222" s="27"/>
       <c r="H222" s="15" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
     </row>
     <row r="223" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A223" s="30">
+      <c r="A223" s="33">
         <v>88</v>
       </c>
-      <c r="B223" s="32" t="s">
+      <c r="B223" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="C223" s="33" t="s">
+      <c r="C223" s="44" t="s">
         <v>89</v>
       </c>
       <c r="D223" s="5" t="s">
@@ -7604,17 +7676,17 @@
         <v>3</v>
       </c>
       <c r="F223" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="G223" s="34"/>
+        <v>308</v>
+      </c>
+      <c r="G223" s="27"/>
       <c r="H223" s="15" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
     </row>
     <row r="224" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A224" s="31"/>
-      <c r="B224" s="32"/>
-      <c r="C224" s="33"/>
+      <c r="A224" s="34"/>
+      <c r="B224" s="30"/>
+      <c r="C224" s="44"/>
       <c r="D224" s="5" t="s">
         <v>145</v>
       </c>
@@ -7622,60 +7694,516 @@
         <v>3</v>
       </c>
       <c r="F224" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="G224" s="34"/>
+        <v>262</v>
+      </c>
+      <c r="G224" s="27"/>
       <c r="H224" s="15" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
     </row>
     <row r="228" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A228" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
     </row>
     <row r="229" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A229" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="230" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A230" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
     </row>
     <row r="231" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A231" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
     </row>
     <row r="232" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A232" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
     </row>
     <row r="233" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A233" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
     </row>
     <row r="234" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A234" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
     </row>
     <row r="235" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A235" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
     </row>
     <row r="236" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A236" t="s">
-        <v>296</v>
-      </c>
+        <v>291</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A244" s="28" t="s">
+        <v>640</v>
+      </c>
+      <c r="B244" s="28"/>
+      <c r="C244" s="28"/>
+      <c r="D244" s="28"/>
+      <c r="E244" s="28"/>
+      <c r="F244" s="28"/>
+      <c r="G244" s="28"/>
+      <c r="H244" s="28"/>
+    </row>
+    <row r="245" spans="1:8" ht="25.7" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A245" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B245" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="C245" s="37" t="s">
+        <v>2</v>
+      </c>
+      <c r="D245" s="38"/>
+      <c r="E245" s="38"/>
+      <c r="F245" s="39"/>
+      <c r="G245" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H245" s="1" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8" ht="100.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A246" s="18" t="s">
+        <v>646</v>
+      </c>
+      <c r="B246" s="23" t="s">
+        <v>489</v>
+      </c>
+      <c r="C246" s="24" t="s">
+        <v>650</v>
+      </c>
+      <c r="D246" s="25"/>
+      <c r="E246" s="25"/>
+      <c r="F246" s="26"/>
+      <c r="G246" s="4" t="s">
+        <v>649</v>
+      </c>
+      <c r="H246" s="16" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A247" s="51" t="s">
+        <v>641</v>
+      </c>
+      <c r="B247" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="C247" s="24" t="s">
+        <v>645</v>
+      </c>
+      <c r="D247" s="25"/>
+      <c r="E247" s="25"/>
+      <c r="F247" s="26"/>
+      <c r="G247" s="4" t="s">
+        <v>644</v>
+      </c>
+      <c r="H247" s="16" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A252" s="28" t="s">
+        <v>642</v>
+      </c>
+      <c r="B252" s="28"/>
+      <c r="C252" s="28"/>
+      <c r="D252" s="28"/>
+      <c r="E252" s="28"/>
+      <c r="F252" s="28"/>
+      <c r="G252" s="28"/>
+      <c r="H252" s="28"/>
+    </row>
+    <row r="253" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A253" s="28" t="s">
+        <v>643</v>
+      </c>
+      <c r="B253" s="28"/>
+      <c r="C253" s="28"/>
+      <c r="D253" s="28"/>
+      <c r="E253" s="28"/>
+      <c r="F253" s="28"/>
+      <c r="G253" s="28"/>
+      <c r="H253" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="378">
+  <mergeCells count="384">
+    <mergeCell ref="A244:H244"/>
+    <mergeCell ref="A252:H252"/>
+    <mergeCell ref="A253:H253"/>
+    <mergeCell ref="C245:F245"/>
+    <mergeCell ref="C246:F246"/>
+    <mergeCell ref="C247:F247"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A195:A196"/>
+    <mergeCell ref="B195:B196"/>
+    <mergeCell ref="C195:C196"/>
+    <mergeCell ref="A191:A192"/>
+    <mergeCell ref="B191:B192"/>
+    <mergeCell ref="C191:C192"/>
+    <mergeCell ref="G85:G86"/>
+    <mergeCell ref="A119:A120"/>
+    <mergeCell ref="B119:B120"/>
+    <mergeCell ref="C119:C120"/>
+    <mergeCell ref="G117:G118"/>
+    <mergeCell ref="A79:A80"/>
+    <mergeCell ref="B79:B80"/>
+    <mergeCell ref="C79:C80"/>
+    <mergeCell ref="A77:A78"/>
+    <mergeCell ref="B77:B78"/>
+    <mergeCell ref="C77:C78"/>
+    <mergeCell ref="G77:G78"/>
+    <mergeCell ref="G61:G62"/>
+    <mergeCell ref="C67:C68"/>
+    <mergeCell ref="G201:G202"/>
+    <mergeCell ref="A193:A194"/>
+    <mergeCell ref="B193:B194"/>
+    <mergeCell ref="C193:C194"/>
+    <mergeCell ref="A199:A200"/>
+    <mergeCell ref="B199:B200"/>
+    <mergeCell ref="C199:C200"/>
+    <mergeCell ref="A201:A202"/>
+    <mergeCell ref="B201:B202"/>
+    <mergeCell ref="C201:C202"/>
+    <mergeCell ref="A83:A84"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="G63:G64"/>
+    <mergeCell ref="B105:B106"/>
+    <mergeCell ref="C105:C106"/>
+    <mergeCell ref="G103:G104"/>
+    <mergeCell ref="A69:A70"/>
+    <mergeCell ref="B69:B70"/>
+    <mergeCell ref="C69:C70"/>
+    <mergeCell ref="G69:G70"/>
+    <mergeCell ref="A89:A90"/>
+    <mergeCell ref="G215:G216"/>
+    <mergeCell ref="B215:B216"/>
+    <mergeCell ref="B207:B208"/>
+    <mergeCell ref="A105:A106"/>
+    <mergeCell ref="A217:A218"/>
+    <mergeCell ref="B217:B218"/>
+    <mergeCell ref="C215:C216"/>
+    <mergeCell ref="G207:G208"/>
+    <mergeCell ref="A205:A206"/>
+    <mergeCell ref="B205:B206"/>
+    <mergeCell ref="C205:C206"/>
+    <mergeCell ref="G205:G206"/>
+    <mergeCell ref="A203:A204"/>
+    <mergeCell ref="B203:B204"/>
+    <mergeCell ref="C203:C204"/>
+    <mergeCell ref="G203:G204"/>
+    <mergeCell ref="G209:G210"/>
+    <mergeCell ref="A215:A216"/>
+    <mergeCell ref="G111:G112"/>
+    <mergeCell ref="G123:G124"/>
+    <mergeCell ref="B165:B166"/>
+    <mergeCell ref="C165:C166"/>
+    <mergeCell ref="B167:B168"/>
+    <mergeCell ref="C177:C178"/>
+    <mergeCell ref="A213:A214"/>
+    <mergeCell ref="G211:G212"/>
+    <mergeCell ref="G195:G196"/>
+    <mergeCell ref="C181:C182"/>
+    <mergeCell ref="G179:G180"/>
+    <mergeCell ref="A163:A164"/>
+    <mergeCell ref="B163:B164"/>
+    <mergeCell ref="C163:C164"/>
+    <mergeCell ref="G189:G190"/>
+    <mergeCell ref="A177:A178"/>
+    <mergeCell ref="B177:B178"/>
+    <mergeCell ref="G163:G164"/>
+    <mergeCell ref="C223:C224"/>
+    <mergeCell ref="G221:G222"/>
+    <mergeCell ref="G197:G198"/>
+    <mergeCell ref="A223:A224"/>
+    <mergeCell ref="G219:G220"/>
+    <mergeCell ref="A209:A210"/>
+    <mergeCell ref="B209:B210"/>
+    <mergeCell ref="C209:C210"/>
+    <mergeCell ref="G223:G224"/>
+    <mergeCell ref="B223:B224"/>
+    <mergeCell ref="A221:A222"/>
+    <mergeCell ref="B221:B222"/>
+    <mergeCell ref="C221:C222"/>
+    <mergeCell ref="G217:G218"/>
+    <mergeCell ref="A211:A212"/>
+    <mergeCell ref="B211:B212"/>
+    <mergeCell ref="C211:C212"/>
+    <mergeCell ref="B213:B214"/>
+    <mergeCell ref="C213:C214"/>
+    <mergeCell ref="A207:A208"/>
+    <mergeCell ref="A219:A220"/>
+    <mergeCell ref="B219:B220"/>
+    <mergeCell ref="C219:C220"/>
+    <mergeCell ref="C217:C218"/>
+    <mergeCell ref="G65:G66"/>
+    <mergeCell ref="A67:A68"/>
+    <mergeCell ref="B67:B68"/>
+    <mergeCell ref="B83:B84"/>
+    <mergeCell ref="C83:C84"/>
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="B87:B88"/>
+    <mergeCell ref="C91:C92"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="G67:G68"/>
+    <mergeCell ref="A71:A72"/>
+    <mergeCell ref="C71:C72"/>
+    <mergeCell ref="G71:G72"/>
+    <mergeCell ref="B71:B72"/>
+    <mergeCell ref="C65:C66"/>
+    <mergeCell ref="G73:G74"/>
+    <mergeCell ref="A75:A76"/>
+    <mergeCell ref="B75:B76"/>
+    <mergeCell ref="A81:A82"/>
+    <mergeCell ref="B89:B90"/>
+    <mergeCell ref="C85:C86"/>
+    <mergeCell ref="A85:A86"/>
+    <mergeCell ref="B85:B86"/>
+    <mergeCell ref="G79:G80"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="C93:C94"/>
+    <mergeCell ref="G93:G94"/>
+    <mergeCell ref="B109:B110"/>
+    <mergeCell ref="A97:A98"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="C99:C100"/>
+    <mergeCell ref="A93:A94"/>
+    <mergeCell ref="B93:B94"/>
+    <mergeCell ref="B103:B104"/>
+    <mergeCell ref="C103:C104"/>
+    <mergeCell ref="G101:G102"/>
+    <mergeCell ref="A109:A110"/>
+    <mergeCell ref="A113:A114"/>
+    <mergeCell ref="B113:B114"/>
+    <mergeCell ref="A111:A112"/>
+    <mergeCell ref="B111:B112"/>
+    <mergeCell ref="A115:A116"/>
+    <mergeCell ref="B115:B116"/>
+    <mergeCell ref="A121:A122"/>
+    <mergeCell ref="B121:B122"/>
+    <mergeCell ref="B81:B82"/>
+    <mergeCell ref="A101:A102"/>
+    <mergeCell ref="B101:B102"/>
+    <mergeCell ref="A107:A108"/>
+    <mergeCell ref="A95:A96"/>
+    <mergeCell ref="B95:B96"/>
+    <mergeCell ref="C95:C96"/>
+    <mergeCell ref="B107:B108"/>
+    <mergeCell ref="C107:C108"/>
+    <mergeCell ref="A103:A104"/>
+    <mergeCell ref="B97:B98"/>
+    <mergeCell ref="C97:C98"/>
+    <mergeCell ref="G75:G76"/>
+    <mergeCell ref="G97:G98"/>
+    <mergeCell ref="G83:G84"/>
+    <mergeCell ref="G91:G92"/>
+    <mergeCell ref="G81:G82"/>
+    <mergeCell ref="G89:G90"/>
+    <mergeCell ref="G99:G100"/>
+    <mergeCell ref="C137:C138"/>
+    <mergeCell ref="G137:G138"/>
+    <mergeCell ref="G115:G116"/>
+    <mergeCell ref="G107:G108"/>
+    <mergeCell ref="G109:G110"/>
+    <mergeCell ref="C109:C110"/>
+    <mergeCell ref="C101:C102"/>
+    <mergeCell ref="C75:C76"/>
+    <mergeCell ref="C113:C114"/>
+    <mergeCell ref="C111:C112"/>
+    <mergeCell ref="C115:C116"/>
+    <mergeCell ref="G121:G122"/>
+    <mergeCell ref="C121:C122"/>
+    <mergeCell ref="C81:C82"/>
+    <mergeCell ref="G131:G132"/>
+    <mergeCell ref="G105:G106"/>
+    <mergeCell ref="G95:G96"/>
+    <mergeCell ref="G139:G140"/>
+    <mergeCell ref="G125:G126"/>
+    <mergeCell ref="A127:A128"/>
+    <mergeCell ref="B127:B128"/>
+    <mergeCell ref="B147:B148"/>
+    <mergeCell ref="C147:C148"/>
+    <mergeCell ref="G145:G146"/>
+    <mergeCell ref="A143:A144"/>
+    <mergeCell ref="B143:B144"/>
+    <mergeCell ref="C143:C144"/>
+    <mergeCell ref="A139:A140"/>
+    <mergeCell ref="B139:B140"/>
+    <mergeCell ref="C139:C140"/>
+    <mergeCell ref="G135:G136"/>
+    <mergeCell ref="A131:A132"/>
+    <mergeCell ref="A129:A130"/>
+    <mergeCell ref="B129:B130"/>
+    <mergeCell ref="C127:C128"/>
+    <mergeCell ref="A141:A142"/>
+    <mergeCell ref="B141:B142"/>
+    <mergeCell ref="A147:A148"/>
+    <mergeCell ref="A125:A126"/>
+    <mergeCell ref="B125:B126"/>
+    <mergeCell ref="C125:C126"/>
+    <mergeCell ref="A135:A136"/>
+    <mergeCell ref="B135:B136"/>
+    <mergeCell ref="C135:C136"/>
+    <mergeCell ref="G147:G148"/>
+    <mergeCell ref="A149:A150"/>
+    <mergeCell ref="A159:A160"/>
+    <mergeCell ref="B159:B160"/>
+    <mergeCell ref="C159:C160"/>
+    <mergeCell ref="G127:G128"/>
+    <mergeCell ref="A153:A154"/>
+    <mergeCell ref="G161:G162"/>
+    <mergeCell ref="C179:C180"/>
+    <mergeCell ref="G177:G178"/>
+    <mergeCell ref="A175:A176"/>
+    <mergeCell ref="B131:B132"/>
+    <mergeCell ref="C131:C132"/>
+    <mergeCell ref="B153:B154"/>
+    <mergeCell ref="C153:C154"/>
+    <mergeCell ref="G151:G152"/>
+    <mergeCell ref="G171:G172"/>
+    <mergeCell ref="B175:B176"/>
+    <mergeCell ref="C175:C176"/>
+    <mergeCell ref="B171:B172"/>
+    <mergeCell ref="A167:A168"/>
+    <mergeCell ref="G169:G170"/>
+    <mergeCell ref="G175:G176"/>
+    <mergeCell ref="G141:G142"/>
+    <mergeCell ref="G199:G200"/>
+    <mergeCell ref="A197:A198"/>
+    <mergeCell ref="B197:B198"/>
+    <mergeCell ref="C197:C198"/>
+    <mergeCell ref="G193:G194"/>
+    <mergeCell ref="A169:A170"/>
+    <mergeCell ref="B169:B170"/>
+    <mergeCell ref="C169:C170"/>
+    <mergeCell ref="G167:G168"/>
+    <mergeCell ref="A171:A172"/>
+    <mergeCell ref="A185:A186"/>
+    <mergeCell ref="B185:B186"/>
+    <mergeCell ref="A179:A180"/>
+    <mergeCell ref="B179:B180"/>
+    <mergeCell ref="C187:C188"/>
+    <mergeCell ref="B183:B184"/>
+    <mergeCell ref="C183:C184"/>
+    <mergeCell ref="G183:G184"/>
+    <mergeCell ref="G191:G192"/>
+    <mergeCell ref="A189:A190"/>
+    <mergeCell ref="B189:B190"/>
+    <mergeCell ref="G181:G182"/>
+    <mergeCell ref="C189:C190"/>
+    <mergeCell ref="G187:G188"/>
+    <mergeCell ref="B187:B188"/>
+    <mergeCell ref="C171:C172"/>
+    <mergeCell ref="C157:C158"/>
+    <mergeCell ref="G155:G156"/>
+    <mergeCell ref="A155:A156"/>
+    <mergeCell ref="B155:B156"/>
+    <mergeCell ref="A173:A174"/>
+    <mergeCell ref="B173:B174"/>
+    <mergeCell ref="C173:C174"/>
+    <mergeCell ref="G173:G174"/>
+    <mergeCell ref="B157:B158"/>
+    <mergeCell ref="C185:C186"/>
+    <mergeCell ref="A157:A158"/>
+    <mergeCell ref="G185:G186"/>
+    <mergeCell ref="A181:A182"/>
+    <mergeCell ref="B181:B182"/>
+    <mergeCell ref="C167:C168"/>
+    <mergeCell ref="G165:G166"/>
+    <mergeCell ref="A183:A184"/>
+    <mergeCell ref="A137:A138"/>
+    <mergeCell ref="A123:A124"/>
+    <mergeCell ref="B123:B124"/>
+    <mergeCell ref="A117:A118"/>
+    <mergeCell ref="A133:A134"/>
+    <mergeCell ref="B133:B134"/>
+    <mergeCell ref="C133:C134"/>
+    <mergeCell ref="G213:G214"/>
+    <mergeCell ref="C117:C118"/>
+    <mergeCell ref="B117:B118"/>
+    <mergeCell ref="C123:C124"/>
+    <mergeCell ref="A151:A152"/>
+    <mergeCell ref="B151:B152"/>
+    <mergeCell ref="C151:C152"/>
+    <mergeCell ref="A145:A146"/>
+    <mergeCell ref="B145:B146"/>
+    <mergeCell ref="C145:C146"/>
+    <mergeCell ref="B149:B150"/>
+    <mergeCell ref="C149:C150"/>
+    <mergeCell ref="G149:G150"/>
+    <mergeCell ref="G159:G160"/>
+    <mergeCell ref="A165:A166"/>
+    <mergeCell ref="A161:A162"/>
+    <mergeCell ref="A187:A188"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="A46:H46"/>
+    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="A40:H40"/>
+    <mergeCell ref="G49:G50"/>
+    <mergeCell ref="G51:G52"/>
+    <mergeCell ref="G53:G54"/>
+    <mergeCell ref="G55:G56"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="C51:C52"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="C53:C54"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="A73:A74"/>
+    <mergeCell ref="B73:B74"/>
+    <mergeCell ref="C73:C74"/>
+    <mergeCell ref="A57:A58"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="C57:C58"/>
+    <mergeCell ref="A61:A62"/>
+    <mergeCell ref="C61:C62"/>
+    <mergeCell ref="A63:A64"/>
+    <mergeCell ref="B63:B64"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="B59:B60"/>
+    <mergeCell ref="C59:C60"/>
     <mergeCell ref="C27:F27"/>
     <mergeCell ref="C34:F34"/>
     <mergeCell ref="C35:F35"/>
@@ -7700,360 +8228,6 @@
     <mergeCell ref="C141:C142"/>
     <mergeCell ref="G119:G120"/>
     <mergeCell ref="G113:G114"/>
-    <mergeCell ref="A73:A74"/>
-    <mergeCell ref="B73:B74"/>
-    <mergeCell ref="C73:C74"/>
-    <mergeCell ref="A57:A58"/>
-    <mergeCell ref="B57:B58"/>
-    <mergeCell ref="C57:C58"/>
-    <mergeCell ref="A61:A62"/>
-    <mergeCell ref="C61:C62"/>
-    <mergeCell ref="A63:A64"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="A59:A60"/>
-    <mergeCell ref="B59:B60"/>
-    <mergeCell ref="C59:C60"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="A46:H46"/>
-    <mergeCell ref="A47:H47"/>
-    <mergeCell ref="A40:H40"/>
-    <mergeCell ref="G49:G50"/>
-    <mergeCell ref="G51:G52"/>
-    <mergeCell ref="G53:G54"/>
-    <mergeCell ref="G55:G56"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="C51:C52"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="C53:C54"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="A137:A138"/>
-    <mergeCell ref="A123:A124"/>
-    <mergeCell ref="B123:B124"/>
-    <mergeCell ref="A117:A118"/>
-    <mergeCell ref="A133:A134"/>
-    <mergeCell ref="B133:B134"/>
-    <mergeCell ref="C133:C134"/>
-    <mergeCell ref="G213:G214"/>
-    <mergeCell ref="C117:C118"/>
-    <mergeCell ref="B117:B118"/>
-    <mergeCell ref="C123:C124"/>
-    <mergeCell ref="A151:A152"/>
-    <mergeCell ref="B151:B152"/>
-    <mergeCell ref="C151:C152"/>
-    <mergeCell ref="A145:A146"/>
-    <mergeCell ref="B145:B146"/>
-    <mergeCell ref="C145:C146"/>
-    <mergeCell ref="B149:B150"/>
-    <mergeCell ref="C149:C150"/>
-    <mergeCell ref="G149:G150"/>
-    <mergeCell ref="G159:G160"/>
-    <mergeCell ref="A165:A166"/>
-    <mergeCell ref="A161:A162"/>
-    <mergeCell ref="A187:A188"/>
-    <mergeCell ref="B187:B188"/>
-    <mergeCell ref="C171:C172"/>
-    <mergeCell ref="C157:C158"/>
-    <mergeCell ref="G155:G156"/>
-    <mergeCell ref="A155:A156"/>
-    <mergeCell ref="B155:B156"/>
-    <mergeCell ref="A173:A174"/>
-    <mergeCell ref="B173:B174"/>
-    <mergeCell ref="C173:C174"/>
-    <mergeCell ref="G173:G174"/>
-    <mergeCell ref="B157:B158"/>
-    <mergeCell ref="C185:C186"/>
-    <mergeCell ref="A157:A158"/>
-    <mergeCell ref="G185:G186"/>
-    <mergeCell ref="A181:A182"/>
-    <mergeCell ref="B181:B182"/>
-    <mergeCell ref="C167:C168"/>
-    <mergeCell ref="G165:G166"/>
-    <mergeCell ref="G199:G200"/>
-    <mergeCell ref="A197:A198"/>
-    <mergeCell ref="B197:B198"/>
-    <mergeCell ref="C197:C198"/>
-    <mergeCell ref="G193:G194"/>
-    <mergeCell ref="A169:A170"/>
-    <mergeCell ref="B169:B170"/>
-    <mergeCell ref="C169:C170"/>
-    <mergeCell ref="G167:G168"/>
-    <mergeCell ref="A171:A172"/>
-    <mergeCell ref="A185:A186"/>
-    <mergeCell ref="B185:B186"/>
-    <mergeCell ref="A179:A180"/>
-    <mergeCell ref="B179:B180"/>
-    <mergeCell ref="C187:C188"/>
-    <mergeCell ref="B183:B184"/>
-    <mergeCell ref="C183:C184"/>
-    <mergeCell ref="G183:G184"/>
-    <mergeCell ref="G191:G192"/>
-    <mergeCell ref="A189:A190"/>
-    <mergeCell ref="B189:B190"/>
-    <mergeCell ref="G181:G182"/>
-    <mergeCell ref="C189:C190"/>
-    <mergeCell ref="G187:G188"/>
-    <mergeCell ref="A183:A184"/>
-    <mergeCell ref="G147:G148"/>
-    <mergeCell ref="A149:A150"/>
-    <mergeCell ref="A159:A160"/>
-    <mergeCell ref="B159:B160"/>
-    <mergeCell ref="C159:C160"/>
-    <mergeCell ref="G127:G128"/>
-    <mergeCell ref="A153:A154"/>
-    <mergeCell ref="G161:G162"/>
-    <mergeCell ref="C179:C180"/>
-    <mergeCell ref="G177:G178"/>
-    <mergeCell ref="A175:A176"/>
-    <mergeCell ref="B131:B132"/>
-    <mergeCell ref="C131:C132"/>
-    <mergeCell ref="B153:B154"/>
-    <mergeCell ref="C153:C154"/>
-    <mergeCell ref="G151:G152"/>
-    <mergeCell ref="G171:G172"/>
-    <mergeCell ref="B175:B176"/>
-    <mergeCell ref="C175:C176"/>
-    <mergeCell ref="B171:B172"/>
-    <mergeCell ref="A167:A168"/>
-    <mergeCell ref="G169:G170"/>
-    <mergeCell ref="G175:G176"/>
-    <mergeCell ref="G141:G142"/>
-    <mergeCell ref="A141:A142"/>
-    <mergeCell ref="B141:B142"/>
-    <mergeCell ref="A147:A148"/>
-    <mergeCell ref="A125:A126"/>
-    <mergeCell ref="B125:B126"/>
-    <mergeCell ref="C125:C126"/>
-    <mergeCell ref="A135:A136"/>
-    <mergeCell ref="B135:B136"/>
-    <mergeCell ref="C135:C136"/>
-    <mergeCell ref="G139:G140"/>
-    <mergeCell ref="G125:G126"/>
-    <mergeCell ref="A127:A128"/>
-    <mergeCell ref="B127:B128"/>
-    <mergeCell ref="B147:B148"/>
-    <mergeCell ref="C147:C148"/>
-    <mergeCell ref="G145:G146"/>
-    <mergeCell ref="A143:A144"/>
-    <mergeCell ref="B143:B144"/>
-    <mergeCell ref="C143:C144"/>
-    <mergeCell ref="A139:A140"/>
-    <mergeCell ref="B139:B140"/>
-    <mergeCell ref="C139:C140"/>
-    <mergeCell ref="G135:G136"/>
-    <mergeCell ref="G75:G76"/>
-    <mergeCell ref="G97:G98"/>
-    <mergeCell ref="G83:G84"/>
-    <mergeCell ref="G91:G92"/>
-    <mergeCell ref="G81:G82"/>
-    <mergeCell ref="G89:G90"/>
-    <mergeCell ref="G99:G100"/>
-    <mergeCell ref="C137:C138"/>
-    <mergeCell ref="G137:G138"/>
-    <mergeCell ref="G115:G116"/>
-    <mergeCell ref="G107:G108"/>
-    <mergeCell ref="G109:G110"/>
-    <mergeCell ref="C109:C110"/>
-    <mergeCell ref="C101:C102"/>
-    <mergeCell ref="C75:C76"/>
-    <mergeCell ref="C113:C114"/>
-    <mergeCell ref="C111:C112"/>
-    <mergeCell ref="C115:C116"/>
-    <mergeCell ref="G121:G122"/>
-    <mergeCell ref="C121:C122"/>
-    <mergeCell ref="A131:A132"/>
-    <mergeCell ref="A101:A102"/>
-    <mergeCell ref="B101:B102"/>
-    <mergeCell ref="A107:A108"/>
-    <mergeCell ref="A95:A96"/>
-    <mergeCell ref="B95:B96"/>
-    <mergeCell ref="C95:C96"/>
-    <mergeCell ref="B107:B108"/>
-    <mergeCell ref="C107:C108"/>
-    <mergeCell ref="A103:A104"/>
-    <mergeCell ref="B97:B98"/>
-    <mergeCell ref="C97:C98"/>
-    <mergeCell ref="A113:A114"/>
-    <mergeCell ref="B113:B114"/>
-    <mergeCell ref="A111:A112"/>
-    <mergeCell ref="B111:B112"/>
-    <mergeCell ref="A115:A116"/>
-    <mergeCell ref="B115:B116"/>
-    <mergeCell ref="A121:A122"/>
-    <mergeCell ref="B121:B122"/>
-    <mergeCell ref="B81:B82"/>
-    <mergeCell ref="C81:C82"/>
-    <mergeCell ref="G131:G132"/>
-    <mergeCell ref="G105:G106"/>
-    <mergeCell ref="G95:G96"/>
-    <mergeCell ref="G79:G80"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="C93:C94"/>
-    <mergeCell ref="G93:G94"/>
-    <mergeCell ref="B109:B110"/>
-    <mergeCell ref="A97:A98"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:B100"/>
-    <mergeCell ref="C99:C100"/>
-    <mergeCell ref="A93:A94"/>
-    <mergeCell ref="G65:G66"/>
-    <mergeCell ref="A67:A68"/>
-    <mergeCell ref="B67:B68"/>
-    <mergeCell ref="B83:B84"/>
-    <mergeCell ref="C83:C84"/>
-    <mergeCell ref="A87:A88"/>
-    <mergeCell ref="B87:B88"/>
-    <mergeCell ref="C91:C92"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="G67:G68"/>
-    <mergeCell ref="A71:A72"/>
-    <mergeCell ref="C71:C72"/>
-    <mergeCell ref="G71:G72"/>
-    <mergeCell ref="B71:B72"/>
-    <mergeCell ref="C65:C66"/>
-    <mergeCell ref="G73:G74"/>
-    <mergeCell ref="A75:A76"/>
-    <mergeCell ref="B75:B76"/>
-    <mergeCell ref="A81:A82"/>
-    <mergeCell ref="B89:B90"/>
-    <mergeCell ref="C85:C86"/>
-    <mergeCell ref="A85:A86"/>
-    <mergeCell ref="B85:B86"/>
-    <mergeCell ref="C223:C224"/>
-    <mergeCell ref="G221:G222"/>
-    <mergeCell ref="G197:G198"/>
-    <mergeCell ref="A223:A224"/>
-    <mergeCell ref="G219:G220"/>
-    <mergeCell ref="A209:A210"/>
-    <mergeCell ref="B209:B210"/>
-    <mergeCell ref="C209:C210"/>
-    <mergeCell ref="G223:G224"/>
-    <mergeCell ref="B223:B224"/>
-    <mergeCell ref="A221:A222"/>
-    <mergeCell ref="B221:B222"/>
-    <mergeCell ref="C221:C222"/>
-    <mergeCell ref="G217:G218"/>
-    <mergeCell ref="A211:A212"/>
-    <mergeCell ref="B211:B212"/>
-    <mergeCell ref="C211:C212"/>
-    <mergeCell ref="B213:B214"/>
-    <mergeCell ref="C213:C214"/>
-    <mergeCell ref="B93:B94"/>
-    <mergeCell ref="A207:A208"/>
-    <mergeCell ref="A219:A220"/>
-    <mergeCell ref="B219:B220"/>
-    <mergeCell ref="C219:C220"/>
-    <mergeCell ref="C217:C218"/>
-    <mergeCell ref="B103:B104"/>
-    <mergeCell ref="C103:C104"/>
-    <mergeCell ref="G101:G102"/>
-    <mergeCell ref="A129:A130"/>
-    <mergeCell ref="B129:B130"/>
-    <mergeCell ref="A213:A214"/>
-    <mergeCell ref="G211:G212"/>
-    <mergeCell ref="G195:G196"/>
-    <mergeCell ref="C181:C182"/>
-    <mergeCell ref="G179:G180"/>
-    <mergeCell ref="A163:A164"/>
-    <mergeCell ref="B163:B164"/>
-    <mergeCell ref="C163:C164"/>
-    <mergeCell ref="G189:G190"/>
-    <mergeCell ref="A177:A178"/>
-    <mergeCell ref="B177:B178"/>
-    <mergeCell ref="G163:G164"/>
-    <mergeCell ref="C127:C128"/>
-    <mergeCell ref="A109:A110"/>
-    <mergeCell ref="G215:G216"/>
-    <mergeCell ref="B215:B216"/>
-    <mergeCell ref="B207:B208"/>
-    <mergeCell ref="A105:A106"/>
-    <mergeCell ref="A217:A218"/>
-    <mergeCell ref="B217:B218"/>
-    <mergeCell ref="C215:C216"/>
-    <mergeCell ref="G207:G208"/>
-    <mergeCell ref="A205:A206"/>
-    <mergeCell ref="B205:B206"/>
-    <mergeCell ref="C205:C206"/>
-    <mergeCell ref="G205:G206"/>
-    <mergeCell ref="A203:A204"/>
-    <mergeCell ref="B203:B204"/>
-    <mergeCell ref="C203:C204"/>
-    <mergeCell ref="G203:G204"/>
-    <mergeCell ref="G209:G210"/>
-    <mergeCell ref="A215:A216"/>
-    <mergeCell ref="G111:G112"/>
-    <mergeCell ref="G123:G124"/>
-    <mergeCell ref="B165:B166"/>
-    <mergeCell ref="C165:C166"/>
-    <mergeCell ref="B167:B168"/>
-    <mergeCell ref="C177:C178"/>
-    <mergeCell ref="G61:G62"/>
-    <mergeCell ref="C67:C68"/>
-    <mergeCell ref="G201:G202"/>
-    <mergeCell ref="A193:A194"/>
-    <mergeCell ref="B193:B194"/>
-    <mergeCell ref="C193:C194"/>
-    <mergeCell ref="A199:A200"/>
-    <mergeCell ref="B199:B200"/>
-    <mergeCell ref="C199:C200"/>
-    <mergeCell ref="A201:A202"/>
-    <mergeCell ref="B201:B202"/>
-    <mergeCell ref="C201:C202"/>
-    <mergeCell ref="A83:A84"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="G63:G64"/>
-    <mergeCell ref="B105:B106"/>
-    <mergeCell ref="C105:C106"/>
-    <mergeCell ref="G103:G104"/>
-    <mergeCell ref="A69:A70"/>
-    <mergeCell ref="B69:B70"/>
-    <mergeCell ref="C69:C70"/>
-    <mergeCell ref="G69:G70"/>
-    <mergeCell ref="A89:A90"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="A31:H31"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A195:A196"/>
-    <mergeCell ref="B195:B196"/>
-    <mergeCell ref="C195:C196"/>
-    <mergeCell ref="A191:A192"/>
-    <mergeCell ref="B191:B192"/>
-    <mergeCell ref="C191:C192"/>
-    <mergeCell ref="G85:G86"/>
-    <mergeCell ref="A119:A120"/>
-    <mergeCell ref="B119:B120"/>
-    <mergeCell ref="C119:C120"/>
-    <mergeCell ref="G117:G118"/>
-    <mergeCell ref="A79:A80"/>
-    <mergeCell ref="B79:B80"/>
-    <mergeCell ref="C79:C80"/>
-    <mergeCell ref="A77:A78"/>
-    <mergeCell ref="B77:B78"/>
-    <mergeCell ref="C77:C78"/>
-    <mergeCell ref="G77:G78"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C26:F26"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/main/resources/InesModResources/杀戮尖塔自制--伊内丝v0.2.xlsx
+++ b/src/main/resources/InesModResources/杀戮尖塔自制--伊内丝v0.2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\myMod\InesMod\InesMod\src\main\resources\InesModResources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11E061CB-8AD1-4721-B8B9-104FB18BC9E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F851F601-FAF1-466F-B766-320FAE68BF67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{7A3E14A4-2175-4856-859A-887D335814F1}"/>
   </bookViews>
@@ -2462,52 +2462,52 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>攻击额外生效1层偷取（不视作消耗），战斗结束后获得1点真相。
+消耗偷取x/10层：获得1层洞悉，并使所需层数+2。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>此牌可消耗多层偷取。上虚弱是卡牌的单独action</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对所有敌人造成8点伤害。消耗等同于敌人数量的偷取。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成9点伤害。获得1层隐匿。本回合你无法再打出攻击牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成6点伤害2次。消耗所有偷取，每层额外给予1层虚弱。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成8点伤害2次。消耗所有偷取，每层额外给予1层虚弱。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拥有至少4层偷取时，每消耗1层偷取给予1层易伤。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拥有至少3层偷取时，每消耗1层偷取给予1层易伤。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>直接consumeNum+1。
 （要求可以考虑改成+20%向上取整，或计入情报消耗。）
 弹一个弹窗：“提示：一次战斗中累计消耗10层偷取，即可获得1层洞悉。
-每有1层洞悉，攻击额外视为消耗1层偷取，战斗结束后获得1点真相。”
+每有1层洞悉，攻击额外生效1层偷取（不视作消耗），战斗结束后获得1点真相。”
 出现真相这个power后，描述中显示进度</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>攻击额外生效1层偷取（不视作消耗），战斗结束后获得1点真相。
-消耗偷取x/10层：获得1层洞悉，并使所需层数+2。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>此牌可消耗多层偷取。上虚弱是卡牌的单独action</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>对所有敌人造成8点伤害。消耗等同于敌人数量的偷取。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>造成9点伤害。获得1层隐匿。本回合你无法再打出攻击牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>造成6点伤害2次。消耗所有偷取，每层额外给予1层虚弱。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>造成8点伤害2次。消耗所有偷取，每层额外给予1层虚弱。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>只有在隐匿下才能打出。造成18点伤害。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>只有在隐匿下才能打出。造成22点伤害。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>拥有4层偷取时，每消耗1层偷取给予1层易伤。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>拥有3层偷取时，每消耗1层偷取给予1层易伤。</t>
+    <t>造成16点伤害。若不处于隐匿：消耗。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成12点伤害。若不处于隐匿：消耗。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2782,43 +2782,10 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2830,10 +2797,55 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2842,29 +2854,17 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3199,10 +3199,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="25" t="s">
         <v>314</v>
       </c>
-      <c r="B1" s="28"/>
+      <c r="B1" s="25"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -3254,16 +3254,16 @@
       <c r="B6" s="2"/>
     </row>
     <row r="8" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="37" t="s">
+      <c r="A8" s="26" t="s">
         <v>108</v>
       </c>
-      <c r="B8" s="38"/>
-      <c r="C8" s="38"/>
-      <c r="D8" s="38"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="38"/>
-      <c r="H8" s="39"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="28"/>
     </row>
     <row r="9" spans="1:8" ht="25.7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
@@ -3272,11 +3272,11 @@
       <c r="B9" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="C9" s="37" t="s">
+      <c r="C9" s="26" t="s">
         <v>240</v>
       </c>
-      <c r="D9" s="38"/>
-      <c r="E9" s="39"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="28"/>
       <c r="F9" s="8" t="s">
         <v>2</v>
       </c>
@@ -3294,11 +3294,11 @@
       <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="38" t="s">
+      <c r="C10" s="27" t="s">
         <v>242</v>
       </c>
-      <c r="D10" s="38"/>
-      <c r="E10" s="39"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="28"/>
       <c r="F10" s="9" t="s">
         <v>259</v>
       </c>
@@ -3314,11 +3314,11 @@
       <c r="B11" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C11" s="37" t="s">
+      <c r="C11" s="26" t="s">
         <v>246</v>
       </c>
-      <c r="D11" s="38"/>
-      <c r="E11" s="39"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="28"/>
       <c r="F11" s="9" t="s">
         <v>542</v>
       </c>
@@ -3336,11 +3336,11 @@
       <c r="B12" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C12" s="37" t="s">
+      <c r="C12" s="26" t="s">
         <v>499</v>
       </c>
-      <c r="D12" s="38"/>
-      <c r="E12" s="39"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="28"/>
       <c r="F12" s="9" t="s">
         <v>253</v>
       </c>
@@ -3356,11 +3356,11 @@
       <c r="B13" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="C13" s="24" t="s">
+      <c r="C13" s="29" t="s">
         <v>480</v>
       </c>
-      <c r="D13" s="38"/>
-      <c r="E13" s="39"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="28"/>
       <c r="F13" s="9" t="s">
         <v>235</v>
       </c>
@@ -3376,11 +3376,11 @@
       <c r="B14" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="C14" s="38" t="s">
+      <c r="C14" s="27" t="s">
         <v>310</v>
       </c>
-      <c r="D14" s="38"/>
-      <c r="E14" s="39"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="28"/>
       <c r="F14" s="9" t="s">
         <v>252</v>
       </c>
@@ -3393,16 +3393,16 @@
     <row r="16" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="17" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="28" t="s">
+      <c r="A18" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="B18" s="28"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="28"/>
+      <c r="B18" s="25"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="25"/>
     </row>
     <row r="19" spans="1:8" ht="25.7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
@@ -3411,12 +3411,12 @@
       <c r="B19" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="C19" s="37" t="s">
+      <c r="C19" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="39"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="28"/>
       <c r="G19" s="1" t="s">
         <v>3</v>
       </c>
@@ -3431,12 +3431,12 @@
       <c r="B20" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="C20" s="24" t="s">
+      <c r="C20" s="29" t="s">
         <v>635</v>
       </c>
-      <c r="D20" s="25"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="26"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="31"/>
       <c r="G20" s="5" t="s">
         <v>548</v>
       </c>
@@ -3451,12 +3451,12 @@
       <c r="B21" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="C21" s="24" t="s">
+      <c r="C21" s="29" t="s">
         <v>550</v>
       </c>
-      <c r="D21" s="25"/>
-      <c r="E21" s="25"/>
-      <c r="F21" s="26"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="30"/>
+      <c r="F21" s="31"/>
       <c r="G21" s="5" t="s">
         <v>547</v>
       </c>
@@ -3471,12 +3471,12 @@
       <c r="B22" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="C22" s="24" t="s">
+      <c r="C22" s="29" t="s">
         <v>551</v>
       </c>
-      <c r="D22" s="25"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="26"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="31"/>
       <c r="G22" s="5" t="s">
         <v>545</v>
       </c>
@@ -3491,12 +3491,12 @@
       <c r="B23" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="C23" s="24" t="s">
+      <c r="C23" s="29" t="s">
         <v>569</v>
       </c>
-      <c r="D23" s="25"/>
-      <c r="E23" s="25"/>
-      <c r="F23" s="26"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="31"/>
       <c r="G23" s="4" t="s">
         <v>570</v>
       </c>
@@ -3511,12 +3511,12 @@
       <c r="B24" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="C24" s="24" t="s">
+      <c r="C24" s="29" t="s">
         <v>494</v>
       </c>
-      <c r="D24" s="25"/>
-      <c r="E24" s="25"/>
-      <c r="F24" s="26"/>
+      <c r="D24" s="30"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="31"/>
       <c r="G24" s="5" t="s">
         <v>596</v>
       </c>
@@ -3531,12 +3531,12 @@
       <c r="B25" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="C25" s="24" t="s">
+      <c r="C25" s="29" t="s">
         <v>495</v>
       </c>
-      <c r="D25" s="25"/>
-      <c r="E25" s="25"/>
-      <c r="F25" s="26"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="31"/>
       <c r="G25" s="5" t="s">
         <v>496</v>
       </c>
@@ -3551,12 +3551,12 @@
       <c r="B26" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="C26" s="24" t="s">
+      <c r="C26" s="29" t="s">
         <v>628</v>
       </c>
-      <c r="D26" s="25"/>
-      <c r="E26" s="25"/>
-      <c r="F26" s="26"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="31"/>
       <c r="G26" s="4"/>
       <c r="H26" s="16" t="s">
         <v>629</v>
@@ -3569,12 +3569,12 @@
       <c r="B27" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="C27" s="24" t="s">
+      <c r="C27" s="29" t="s">
         <v>498</v>
       </c>
-      <c r="D27" s="25"/>
-      <c r="E27" s="25"/>
-      <c r="F27" s="26"/>
+      <c r="D27" s="30"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="31"/>
       <c r="G27" s="4" t="s">
         <v>597</v>
       </c>
@@ -3586,16 +3586,16 @@
     <row r="29" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="1:8" ht="21.7" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="31" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="28" t="s">
+      <c r="A31" s="25" t="s">
         <v>532</v>
       </c>
-      <c r="B31" s="28"/>
-      <c r="C31" s="28"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="28"/>
-      <c r="H31" s="28"/>
+      <c r="B31" s="25"/>
+      <c r="C31" s="25"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="25"/>
+      <c r="G31" s="25"/>
+      <c r="H31" s="25"/>
     </row>
     <row r="32" spans="1:8" ht="25.7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="1" t="s">
@@ -3604,12 +3604,12 @@
       <c r="B32" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="C32" s="37" t="s">
+      <c r="C32" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="D32" s="38"/>
-      <c r="E32" s="38"/>
-      <c r="F32" s="39"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="28"/>
       <c r="G32" s="1" t="s">
         <v>3</v>
       </c>
@@ -3624,12 +3624,12 @@
       <c r="B33" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="C33" s="24" t="s">
+      <c r="C33" s="29" t="s">
         <v>533</v>
       </c>
-      <c r="D33" s="25"/>
-      <c r="E33" s="25"/>
-      <c r="F33" s="26"/>
+      <c r="D33" s="30"/>
+      <c r="E33" s="30"/>
+      <c r="F33" s="31"/>
       <c r="G33" s="5"/>
       <c r="H33" s="16" t="s">
         <v>478</v>
@@ -3642,12 +3642,12 @@
       <c r="B34" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="C34" s="24" t="s">
+      <c r="C34" s="29" t="s">
         <v>543</v>
       </c>
-      <c r="D34" s="25"/>
-      <c r="E34" s="25"/>
-      <c r="F34" s="26"/>
+      <c r="D34" s="30"/>
+      <c r="E34" s="30"/>
+      <c r="F34" s="31"/>
       <c r="G34" s="5"/>
       <c r="H34" s="16" t="s">
         <v>479</v>
@@ -3660,12 +3660,12 @@
       <c r="B35" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="C35" s="24" t="s">
+      <c r="C35" s="29" t="s">
         <v>569</v>
       </c>
-      <c r="D35" s="25"/>
-      <c r="E35" s="25"/>
-      <c r="F35" s="26"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="31"/>
       <c r="G35" s="5"/>
       <c r="H35" s="16" t="s">
         <v>477</v>
@@ -3678,12 +3678,12 @@
       <c r="B36" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="C36" s="24" t="s">
+      <c r="C36" s="29" t="s">
         <v>537</v>
       </c>
-      <c r="D36" s="25"/>
-      <c r="E36" s="25"/>
-      <c r="F36" s="26"/>
+      <c r="D36" s="30"/>
+      <c r="E36" s="30"/>
+      <c r="F36" s="31"/>
       <c r="G36" s="5"/>
       <c r="H36" s="16" t="s">
         <v>538</v>
@@ -3702,16 +3702,16 @@
       <c r="H39" s="11"/>
     </row>
     <row r="40" spans="1:8" s="3" customFormat="1" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="28" t="s">
+      <c r="A40" s="25" t="s">
         <v>539</v>
       </c>
-      <c r="B40" s="28"/>
-      <c r="C40" s="28"/>
-      <c r="D40" s="28"/>
-      <c r="E40" s="28"/>
-      <c r="F40" s="28"/>
-      <c r="G40" s="28"/>
-      <c r="H40" s="28"/>
+      <c r="B40" s="25"/>
+      <c r="C40" s="25"/>
+      <c r="D40" s="25"/>
+      <c r="E40" s="25"/>
+      <c r="F40" s="25"/>
+      <c r="G40" s="25"/>
+      <c r="H40" s="25"/>
     </row>
     <row r="41" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="1" t="s">
@@ -3776,28 +3776,28 @@
       <c r="H45" s="2"/>
     </row>
     <row r="46" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="28" t="s">
+      <c r="A46" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="B46" s="28"/>
-      <c r="C46" s="28"/>
-      <c r="D46" s="28"/>
-      <c r="E46" s="28"/>
-      <c r="F46" s="28"/>
-      <c r="G46" s="28"/>
-      <c r="H46" s="28"/>
+      <c r="B46" s="25"/>
+      <c r="C46" s="25"/>
+      <c r="D46" s="25"/>
+      <c r="E46" s="25"/>
+      <c r="F46" s="25"/>
+      <c r="G46" s="25"/>
+      <c r="H46" s="25"/>
     </row>
     <row r="47" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="28" t="s">
+      <c r="A47" s="25" t="s">
         <v>554</v>
       </c>
-      <c r="B47" s="28"/>
-      <c r="C47" s="28"/>
-      <c r="D47" s="28"/>
-      <c r="E47" s="28"/>
-      <c r="F47" s="28"/>
-      <c r="G47" s="28"/>
-      <c r="H47" s="28"/>
+      <c r="B47" s="25"/>
+      <c r="C47" s="25"/>
+      <c r="D47" s="25"/>
+      <c r="E47" s="25"/>
+      <c r="F47" s="25"/>
+      <c r="G47" s="25"/>
+      <c r="H47" s="25"/>
     </row>
     <row r="48" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="1" t="s">
@@ -3826,13 +3826,13 @@
       </c>
     </row>
     <row r="49" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="41">
-        <v>1</v>
-      </c>
-      <c r="B49" s="40" t="s">
+      <c r="A49" s="51">
+        <v>1</v>
+      </c>
+      <c r="B49" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="C49" s="28" t="s">
+      <c r="C49" s="25" t="s">
         <v>6</v>
       </c>
       <c r="D49" s="6" t="s">
@@ -3844,15 +3844,15 @@
       <c r="F49" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G49" s="27"/>
+      <c r="G49" s="36"/>
       <c r="H49" s="15" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="50" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="41"/>
-      <c r="B50" s="40"/>
-      <c r="C50" s="28"/>
+      <c r="A50" s="51"/>
+      <c r="B50" s="50"/>
+      <c r="C50" s="25"/>
       <c r="D50" s="6" t="s">
         <v>18</v>
       </c>
@@ -3862,7 +3862,7 @@
       <c r="F50" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G50" s="27"/>
+      <c r="G50" s="36"/>
       <c r="H50" s="15" t="s">
         <v>386</v>
       </c>
@@ -3872,13 +3872,13 @@
       <c r="L50" s="2"/>
     </row>
     <row r="51" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="35">
+      <c r="A51" s="41">
         <v>2</v>
       </c>
-      <c r="B51" s="40" t="s">
+      <c r="B51" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="C51" s="28" t="s">
+      <c r="C51" s="25" t="s">
         <v>14</v>
       </c>
       <c r="D51" s="6" t="s">
@@ -3890,7 +3890,7 @@
       <c r="F51" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G51" s="27"/>
+      <c r="G51" s="36"/>
       <c r="H51" s="15" t="s">
         <v>322</v>
       </c>
@@ -3900,9 +3900,9 @@
       <c r="L51" s="2"/>
     </row>
     <row r="52" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="36"/>
-      <c r="B52" s="40"/>
-      <c r="C52" s="28"/>
+      <c r="A52" s="42"/>
+      <c r="B52" s="50"/>
+      <c r="C52" s="25"/>
       <c r="D52" s="6" t="s">
         <v>19</v>
       </c>
@@ -3912,7 +3912,7 @@
       <c r="F52" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G52" s="27"/>
+      <c r="G52" s="36"/>
       <c r="H52" s="15" t="s">
         <v>387</v>
       </c>
@@ -3922,13 +3922,13 @@
       <c r="L52" s="2"/>
     </row>
     <row r="53" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="35">
+      <c r="A53" s="41">
         <v>3</v>
       </c>
-      <c r="B53" s="40" t="s">
+      <c r="B53" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="C53" s="28" t="s">
+      <c r="C53" s="25" t="s">
         <v>14</v>
       </c>
       <c r="D53" s="5" t="s">
@@ -3940,7 +3940,7 @@
       <c r="F53" s="5" t="s">
         <v>529</v>
       </c>
-      <c r="G53" s="27"/>
+      <c r="G53" s="36"/>
       <c r="H53" s="15" t="s">
         <v>488</v>
       </c>
@@ -3950,9 +3950,9 @@
       <c r="L53" s="2"/>
     </row>
     <row r="54" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="36"/>
-      <c r="B54" s="40"/>
-      <c r="C54" s="28"/>
+      <c r="A54" s="42"/>
+      <c r="B54" s="50"/>
+      <c r="C54" s="25"/>
       <c r="D54" s="5" t="s">
         <v>20</v>
       </c>
@@ -3962,7 +3962,7 @@
       <c r="F54" s="5" t="s">
         <v>552</v>
       </c>
-      <c r="G54" s="27"/>
+      <c r="G54" s="36"/>
       <c r="H54" s="15" t="s">
         <v>388</v>
       </c>
@@ -3972,13 +3972,13 @@
       <c r="L54" s="2"/>
     </row>
     <row r="55" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="35">
+      <c r="A55" s="41">
         <v>4</v>
       </c>
-      <c r="B55" s="40" t="s">
+      <c r="B55" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="C55" s="28" t="s">
+      <c r="C55" s="25" t="s">
         <v>6</v>
       </c>
       <c r="D55" s="5" t="s">
@@ -3990,7 +3990,7 @@
       <c r="F55" s="5" t="s">
         <v>501</v>
       </c>
-      <c r="G55" s="27"/>
+      <c r="G55" s="36"/>
       <c r="H55" s="15" t="s">
         <v>316</v>
       </c>
@@ -4000,9 +4000,9 @@
       <c r="L55" s="2"/>
     </row>
     <row r="56" spans="1:12" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="36"/>
-      <c r="B56" s="40"/>
-      <c r="C56" s="28"/>
+      <c r="A56" s="42"/>
+      <c r="B56" s="50"/>
+      <c r="C56" s="25"/>
       <c r="D56" s="5" t="s">
         <v>25</v>
       </c>
@@ -4012,7 +4012,7 @@
       <c r="F56" s="5" t="s">
         <v>549</v>
       </c>
-      <c r="G56" s="27"/>
+      <c r="G56" s="36"/>
       <c r="H56" s="15" t="s">
         <v>454</v>
       </c>
@@ -4022,13 +4022,13 @@
       <c r="L56" s="2"/>
     </row>
     <row r="57" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="35">
+      <c r="A57" s="41">
         <v>5</v>
       </c>
-      <c r="B57" s="29" t="s">
+      <c r="B57" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="C57" s="28" t="s">
+      <c r="C57" s="25" t="s">
         <v>6</v>
       </c>
       <c r="D57" s="5" t="s">
@@ -4040,7 +4040,7 @@
       <c r="F57" s="5" t="s">
         <v>525</v>
       </c>
-      <c r="G57" s="27" t="s">
+      <c r="G57" s="36" t="s">
         <v>526</v>
       </c>
       <c r="H57" s="15" t="s">
@@ -4052,9 +4052,9 @@
       <c r="L57" s="2"/>
     </row>
     <row r="58" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="36"/>
-      <c r="B58" s="29"/>
-      <c r="C58" s="28"/>
+      <c r="A58" s="42"/>
+      <c r="B58" s="37"/>
+      <c r="C58" s="25"/>
       <c r="D58" s="5" t="s">
         <v>26</v>
       </c>
@@ -4064,7 +4064,7 @@
       <c r="F58" s="5" t="s">
         <v>572</v>
       </c>
-      <c r="G58" s="27"/>
+      <c r="G58" s="36"/>
       <c r="H58" s="15" t="s">
         <v>389</v>
       </c>
@@ -4074,13 +4074,13 @@
       <c r="L58" s="2"/>
     </row>
     <row r="59" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A59" s="35">
+      <c r="A59" s="41">
         <v>6</v>
       </c>
-      <c r="B59" s="29" t="s">
+      <c r="B59" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="C59" s="28" t="s">
+      <c r="C59" s="25" t="s">
         <v>6</v>
       </c>
       <c r="D59" s="5" t="s">
@@ -4092,7 +4092,7 @@
       <c r="F59" s="5" t="s">
         <v>615</v>
       </c>
-      <c r="G59" s="27"/>
+      <c r="G59" s="36"/>
       <c r="H59" s="15" t="s">
         <v>324</v>
       </c>
@@ -4102,9 +4102,9 @@
       <c r="L59" s="2"/>
     </row>
     <row r="60" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="36"/>
-      <c r="B60" s="29"/>
-      <c r="C60" s="28"/>
+      <c r="A60" s="42"/>
+      <c r="B60" s="37"/>
+      <c r="C60" s="25"/>
       <c r="D60" s="5" t="s">
         <v>28</v>
       </c>
@@ -4114,7 +4114,7 @@
       <c r="F60" s="5" t="s">
         <v>614</v>
       </c>
-      <c r="G60" s="27"/>
+      <c r="G60" s="36"/>
       <c r="H60" s="15" t="s">
         <v>390</v>
       </c>
@@ -4124,13 +4124,13 @@
       <c r="L60" s="2"/>
     </row>
     <row r="61" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="35">
+      <c r="A61" s="41">
         <v>7</v>
       </c>
-      <c r="B61" s="29" t="s">
+      <c r="B61" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="C61" s="28" t="s">
+      <c r="C61" s="25" t="s">
         <v>6</v>
       </c>
       <c r="D61" s="5" t="s">
@@ -4142,7 +4142,7 @@
       <c r="F61" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="G61" s="27"/>
+      <c r="G61" s="36"/>
       <c r="H61" s="15" t="s">
         <v>325</v>
       </c>
@@ -4152,9 +4152,9 @@
       <c r="L61" s="2"/>
     </row>
     <row r="62" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="36"/>
-      <c r="B62" s="29"/>
-      <c r="C62" s="28"/>
+      <c r="A62" s="42"/>
+      <c r="B62" s="37"/>
+      <c r="C62" s="25"/>
       <c r="D62" s="5" t="s">
         <v>38</v>
       </c>
@@ -4164,7 +4164,7 @@
       <c r="F62" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="G62" s="27"/>
+      <c r="G62" s="36"/>
       <c r="H62" s="15" t="s">
         <v>391</v>
       </c>
@@ -4174,13 +4174,13 @@
       <c r="L62" s="2"/>
     </row>
     <row r="63" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="35">
+      <c r="A63" s="41">
         <v>8</v>
       </c>
-      <c r="B63" s="29" t="s">
+      <c r="B63" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="C63" s="28" t="s">
+      <c r="C63" s="25" t="s">
         <v>6</v>
       </c>
       <c r="D63" s="5" t="s">
@@ -4192,7 +4192,7 @@
       <c r="F63" s="5" t="s">
         <v>616</v>
       </c>
-      <c r="G63" s="27" t="s">
+      <c r="G63" s="36" t="s">
         <v>587</v>
       </c>
       <c r="H63" s="15" t="s">
@@ -4204,9 +4204,9 @@
       <c r="L63" s="2"/>
     </row>
     <row r="64" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A64" s="36"/>
-      <c r="B64" s="29"/>
-      <c r="C64" s="28"/>
+      <c r="A64" s="42"/>
+      <c r="B64" s="37"/>
+      <c r="C64" s="25"/>
       <c r="D64" s="5" t="s">
         <v>196</v>
       </c>
@@ -4216,7 +4216,7 @@
       <c r="F64" s="5" t="s">
         <v>617</v>
       </c>
-      <c r="G64" s="27"/>
+      <c r="G64" s="36"/>
       <c r="H64" s="15" t="s">
         <v>392</v>
       </c>
@@ -4226,13 +4226,13 @@
       <c r="L64" s="2"/>
     </row>
     <row r="65" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A65" s="35">
+      <c r="A65" s="41">
         <v>9</v>
       </c>
-      <c r="B65" s="29" t="s">
+      <c r="B65" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="C65" s="28" t="s">
+      <c r="C65" s="25" t="s">
         <v>6</v>
       </c>
       <c r="D65" s="5" t="s">
@@ -4244,7 +4244,7 @@
       <c r="F65" s="5" t="s">
         <v>584</v>
       </c>
-      <c r="G65" s="27" t="s">
+      <c r="G65" s="36" t="s">
         <v>588</v>
       </c>
       <c r="H65" s="15" t="s">
@@ -4252,9 +4252,9 @@
       </c>
     </row>
     <row r="66" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A66" s="36"/>
-      <c r="B66" s="29"/>
-      <c r="C66" s="28"/>
+      <c r="A66" s="42"/>
+      <c r="B66" s="37"/>
+      <c r="C66" s="25"/>
       <c r="D66" s="5" t="s">
         <v>117</v>
       </c>
@@ -4264,19 +4264,19 @@
       <c r="F66" s="5" t="s">
         <v>585</v>
       </c>
-      <c r="G66" s="27"/>
+      <c r="G66" s="36"/>
       <c r="H66" s="15" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="67" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A67" s="35">
+      <c r="A67" s="41">
         <v>10</v>
       </c>
-      <c r="B67" s="29" t="s">
+      <c r="B67" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="C67" s="28" t="s">
+      <c r="C67" s="25" t="s">
         <v>6</v>
       </c>
       <c r="D67" s="5" t="s">
@@ -4288,7 +4288,7 @@
       <c r="F67" s="5" t="s">
         <v>564</v>
       </c>
-      <c r="G67" s="27" t="s">
+      <c r="G67" s="36" t="s">
         <v>589</v>
       </c>
       <c r="H67" s="15" t="s">
@@ -4300,9 +4300,9 @@
       <c r="L67" s="2"/>
     </row>
     <row r="68" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A68" s="36"/>
-      <c r="B68" s="29"/>
-      <c r="C68" s="28"/>
+      <c r="A68" s="42"/>
+      <c r="B68" s="37"/>
+      <c r="C68" s="25"/>
       <c r="D68" s="5" t="s">
         <v>161</v>
       </c>
@@ -4312,7 +4312,7 @@
       <c r="F68" s="5" t="s">
         <v>563</v>
       </c>
-      <c r="G68" s="27"/>
+      <c r="G68" s="36"/>
       <c r="H68" s="15" t="s">
         <v>394</v>
       </c>
@@ -4322,13 +4322,13 @@
       <c r="L68" s="2"/>
     </row>
     <row r="69" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A69" s="33">
+      <c r="A69" s="41">
         <v>11</v>
       </c>
-      <c r="B69" s="29" t="s">
+      <c r="B69" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="C69" s="28" t="s">
+      <c r="C69" s="25" t="s">
         <v>6</v>
       </c>
       <c r="D69" s="5" t="s">
@@ -4340,7 +4340,7 @@
       <c r="F69" s="5" t="s">
         <v>619</v>
       </c>
-      <c r="G69" s="27" t="s">
+      <c r="G69" s="36" t="s">
         <v>587</v>
       </c>
       <c r="H69" s="15" t="s">
@@ -4352,9 +4352,9 @@
       <c r="L69" s="2"/>
     </row>
     <row r="70" spans="1:12" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A70" s="34"/>
-      <c r="B70" s="29"/>
-      <c r="C70" s="28"/>
+      <c r="A70" s="42"/>
+      <c r="B70" s="37"/>
+      <c r="C70" s="25"/>
       <c r="D70" s="5" t="s">
         <v>159</v>
       </c>
@@ -4364,7 +4364,7 @@
       <c r="F70" s="5" t="s">
         <v>620</v>
       </c>
-      <c r="G70" s="27"/>
+      <c r="G70" s="36"/>
       <c r="H70" s="15" t="s">
         <v>395</v>
       </c>
@@ -4374,13 +4374,13 @@
       <c r="L70" s="2"/>
     </row>
     <row r="71" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A71" s="33">
+      <c r="A71" s="32">
         <v>12</v>
       </c>
-      <c r="B71" s="32" t="s">
+      <c r="B71" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="C71" s="28" t="s">
+      <c r="C71" s="25" t="s">
         <v>6</v>
       </c>
       <c r="D71" s="5" t="s">
@@ -4390,9 +4390,9 @@
         <v>0</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>656</v>
-      </c>
-      <c r="G71" s="27" t="s">
+        <v>659</v>
+      </c>
+      <c r="G71" s="36" t="s">
         <v>587</v>
       </c>
       <c r="H71" s="15" t="s">
@@ -4404,9 +4404,9 @@
       <c r="L71" s="2"/>
     </row>
     <row r="72" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A72" s="34"/>
-      <c r="B72" s="32"/>
-      <c r="C72" s="28"/>
+      <c r="A72" s="33"/>
+      <c r="B72" s="38"/>
+      <c r="C72" s="25"/>
       <c r="D72" s="5" t="s">
         <v>36</v>
       </c>
@@ -4414,9 +4414,9 @@
         <v>0</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>657</v>
-      </c>
-      <c r="G72" s="27"/>
+        <v>658</v>
+      </c>
+      <c r="G72" s="36"/>
       <c r="H72" s="15" t="s">
         <v>396</v>
       </c>
@@ -4426,13 +4426,13 @@
       <c r="L72" s="2"/>
     </row>
     <row r="73" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A73" s="33">
+      <c r="A73" s="32">
         <v>13</v>
       </c>
-      <c r="B73" s="32" t="s">
+      <c r="B73" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="C73" s="28" t="s">
+      <c r="C73" s="25" t="s">
         <v>6</v>
       </c>
       <c r="D73" s="5" t="s">
@@ -4444,7 +4444,7 @@
       <c r="F73" s="5" t="s">
         <v>561</v>
       </c>
-      <c r="G73" s="27"/>
+      <c r="G73" s="36"/>
       <c r="H73" s="15" t="s">
         <v>331</v>
       </c>
@@ -4454,9 +4454,9 @@
       <c r="L73" s="2"/>
     </row>
     <row r="74" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A74" s="34"/>
-      <c r="B74" s="32"/>
-      <c r="C74" s="28"/>
+      <c r="A74" s="33"/>
+      <c r="B74" s="38"/>
+      <c r="C74" s="25"/>
       <c r="D74" s="5" t="s">
         <v>34</v>
       </c>
@@ -4466,7 +4466,7 @@
       <c r="F74" s="5" t="s">
         <v>562</v>
       </c>
-      <c r="G74" s="27"/>
+      <c r="G74" s="36"/>
       <c r="H74" s="15" t="s">
         <v>397</v>
       </c>
@@ -4476,13 +4476,13 @@
       <c r="L74" s="2"/>
     </row>
     <row r="75" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A75" s="35">
+      <c r="A75" s="41">
         <v>14</v>
       </c>
-      <c r="B75" s="32" t="s">
+      <c r="B75" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="C75" s="28" t="s">
+      <c r="C75" s="25" t="s">
         <v>6</v>
       </c>
       <c r="D75" s="5" t="s">
@@ -4494,7 +4494,7 @@
       <c r="F75" s="5" t="s">
         <v>502</v>
       </c>
-      <c r="G75" s="27" t="s">
+      <c r="G75" s="36" t="s">
         <v>587</v>
       </c>
       <c r="H75" s="15" t="s">
@@ -4506,9 +4506,9 @@
       <c r="L75" s="2"/>
     </row>
     <row r="76" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A76" s="36"/>
-      <c r="B76" s="32"/>
-      <c r="C76" s="28"/>
+      <c r="A76" s="42"/>
+      <c r="B76" s="38"/>
+      <c r="C76" s="25"/>
       <c r="D76" s="5" t="s">
         <v>128</v>
       </c>
@@ -4518,19 +4518,19 @@
       <c r="F76" s="5" t="s">
         <v>503</v>
       </c>
-      <c r="G76" s="27"/>
+      <c r="G76" s="36"/>
       <c r="H76" s="15" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="77" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A77" s="33">
+      <c r="A77" s="41">
         <v>15</v>
       </c>
-      <c r="B77" s="32" t="s">
+      <c r="B77" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="C77" s="28" t="s">
+      <c r="C77" s="25" t="s">
         <v>6</v>
       </c>
       <c r="D77" s="5" t="s">
@@ -4540,19 +4540,19 @@
         <v>2</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>654</v>
-      </c>
-      <c r="G77" s="27" t="s">
-        <v>651</v>
+        <v>653</v>
+      </c>
+      <c r="G77" s="36" t="s">
+        <v>650</v>
       </c>
       <c r="H77" s="15" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="78" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A78" s="34"/>
-      <c r="B78" s="32"/>
-      <c r="C78" s="28"/>
+      <c r="A78" s="42"/>
+      <c r="B78" s="38"/>
+      <c r="C78" s="25"/>
       <c r="D78" s="5" t="s">
         <v>126</v>
       </c>
@@ -4560,21 +4560,21 @@
         <v>2</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>655</v>
-      </c>
-      <c r="G78" s="27"/>
+        <v>654</v>
+      </c>
+      <c r="G78" s="36"/>
       <c r="H78" s="15" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="79" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A79" s="33">
+      <c r="A79" s="32">
         <v>16</v>
       </c>
-      <c r="B79" s="32" t="s">
+      <c r="B79" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="C79" s="47" t="s">
+      <c r="C79" s="39" t="s">
         <v>6</v>
       </c>
       <c r="D79" s="5" t="s">
@@ -4584,9 +4584,9 @@
         <v>2</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>653</v>
-      </c>
-      <c r="G79" s="27" t="s">
+        <v>652</v>
+      </c>
+      <c r="G79" s="36" t="s">
         <v>560</v>
       </c>
       <c r="H79" s="15" t="s">
@@ -4594,9 +4594,9 @@
       </c>
     </row>
     <row r="80" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A80" s="34"/>
-      <c r="B80" s="32"/>
-      <c r="C80" s="48"/>
+      <c r="A80" s="33"/>
+      <c r="B80" s="38"/>
+      <c r="C80" s="40"/>
       <c r="D80" s="5" t="s">
         <v>124</v>
       </c>
@@ -4606,19 +4606,19 @@
       <c r="F80" s="5" t="s">
         <v>559</v>
       </c>
-      <c r="G80" s="27"/>
+      <c r="G80" s="36"/>
       <c r="H80" s="15" t="s">
         <v>599</v>
       </c>
     </row>
     <row r="81" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A81" s="33">
+      <c r="A81" s="32">
         <v>17</v>
       </c>
-      <c r="B81" s="32" t="s">
+      <c r="B81" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="C81" s="28" t="s">
+      <c r="C81" s="25" t="s">
         <v>6</v>
       </c>
       <c r="D81" s="5" t="s">
@@ -4628,9 +4628,9 @@
         <v>1</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>652</v>
-      </c>
-      <c r="G81" s="27" t="s">
+        <v>651</v>
+      </c>
+      <c r="G81" s="36" t="s">
         <v>226</v>
       </c>
       <c r="H81" s="15" t="s">
@@ -4638,9 +4638,9 @@
       </c>
     </row>
     <row r="82" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A82" s="34"/>
-      <c r="B82" s="32"/>
-      <c r="C82" s="28"/>
+      <c r="A82" s="33"/>
+      <c r="B82" s="38"/>
+      <c r="C82" s="25"/>
       <c r="D82" s="5" t="s">
         <v>40</v>
       </c>
@@ -4650,19 +4650,19 @@
       <c r="F82" s="5" t="s">
         <v>518</v>
       </c>
-      <c r="G82" s="27"/>
+      <c r="G82" s="36"/>
       <c r="H82" s="15" t="s">
         <v>400</v>
       </c>
     </row>
     <row r="83" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A83" s="33">
+      <c r="A83" s="32">
         <v>18</v>
       </c>
-      <c r="B83" s="32" t="s">
+      <c r="B83" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="C83" s="44" t="s">
+      <c r="C83" s="35" t="s">
         <v>6</v>
       </c>
       <c r="D83" s="5" t="s">
@@ -4674,7 +4674,7 @@
       <c r="F83" s="5" t="s">
         <v>504</v>
       </c>
-      <c r="G83" s="27" t="s">
+      <c r="G83" s="36" t="s">
         <v>517</v>
       </c>
       <c r="H83" s="15" t="s">
@@ -4682,9 +4682,9 @@
       </c>
     </row>
     <row r="84" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A84" s="34"/>
-      <c r="B84" s="32"/>
-      <c r="C84" s="44"/>
+      <c r="A84" s="33"/>
+      <c r="B84" s="38"/>
+      <c r="C84" s="35"/>
       <c r="D84" s="5" t="s">
         <v>42</v>
       </c>
@@ -4694,19 +4694,19 @@
       <c r="F84" s="5" t="s">
         <v>505</v>
       </c>
-      <c r="G84" s="27"/>
+      <c r="G84" s="36"/>
       <c r="H84" s="15" t="s">
         <v>401</v>
       </c>
     </row>
     <row r="85" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A85" s="33">
+      <c r="A85" s="32">
         <v>19</v>
       </c>
-      <c r="B85" s="32" t="s">
+      <c r="B85" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="C85" s="28" t="s">
+      <c r="C85" s="25" t="s">
         <v>6</v>
       </c>
       <c r="D85" s="5" t="s">
@@ -4718,15 +4718,15 @@
       <c r="F85" s="5" t="s">
         <v>630</v>
       </c>
-      <c r="G85" s="27"/>
+      <c r="G85" s="36"/>
       <c r="H85" s="15" t="s">
         <v>519</v>
       </c>
     </row>
     <row r="86" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A86" s="34"/>
-      <c r="B86" s="32"/>
-      <c r="C86" s="28"/>
+      <c r="A86" s="33"/>
+      <c r="B86" s="38"/>
+      <c r="C86" s="25"/>
       <c r="D86" s="5" t="s">
         <v>86</v>
       </c>
@@ -4736,19 +4736,19 @@
       <c r="F86" s="5" t="s">
         <v>631</v>
       </c>
-      <c r="G86" s="27"/>
+      <c r="G86" s="36"/>
       <c r="H86" s="15" t="s">
         <v>520</v>
       </c>
     </row>
     <row r="87" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A87" s="33">
+      <c r="A87" s="32">
         <v>20</v>
       </c>
-      <c r="B87" s="30" t="s">
+      <c r="B87" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="C87" s="28" t="s">
+      <c r="C87" s="25" t="s">
         <v>6</v>
       </c>
       <c r="D87" s="5" t="s">
@@ -4760,7 +4760,7 @@
       <c r="F87" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="G87" s="27" t="s">
+      <c r="G87" s="36" t="s">
         <v>282</v>
       </c>
       <c r="H87" s="15" t="s">
@@ -4768,9 +4768,9 @@
       </c>
     </row>
     <row r="88" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A88" s="34"/>
-      <c r="B88" s="30"/>
-      <c r="C88" s="28"/>
+      <c r="A88" s="33"/>
+      <c r="B88" s="34"/>
+      <c r="C88" s="25"/>
       <c r="D88" s="5" t="s">
         <v>281</v>
       </c>
@@ -4780,19 +4780,19 @@
       <c r="F88" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="G88" s="27"/>
+      <c r="G88" s="36"/>
       <c r="H88" s="15" t="s">
         <v>402</v>
       </c>
     </row>
     <row r="89" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A89" s="33">
+      <c r="A89" s="32">
         <v>21</v>
       </c>
-      <c r="B89" s="30" t="s">
+      <c r="B89" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="C89" s="28" t="s">
+      <c r="C89" s="25" t="s">
         <v>6</v>
       </c>
       <c r="D89" s="5" t="s">
@@ -4804,7 +4804,7 @@
       <c r="F89" s="5" t="s">
         <v>567</v>
       </c>
-      <c r="G89" s="27" t="s">
+      <c r="G89" s="36" t="s">
         <v>571</v>
       </c>
       <c r="H89" s="15" t="s">
@@ -4812,9 +4812,9 @@
       </c>
     </row>
     <row r="90" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A90" s="34"/>
-      <c r="B90" s="30"/>
-      <c r="C90" s="28"/>
+      <c r="A90" s="33"/>
+      <c r="B90" s="34"/>
+      <c r="C90" s="25"/>
       <c r="D90" s="5" t="s">
         <v>130</v>
       </c>
@@ -4824,19 +4824,19 @@
       <c r="F90" s="5" t="s">
         <v>568</v>
       </c>
-      <c r="G90" s="27"/>
+      <c r="G90" s="36"/>
       <c r="H90" s="15" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="91" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A91" s="35">
+      <c r="A91" s="41">
         <v>22</v>
       </c>
-      <c r="B91" s="30" t="s">
+      <c r="B91" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="C91" s="28" t="s">
+      <c r="C91" s="25" t="s">
         <v>6</v>
       </c>
       <c r="D91" s="5" t="s">
@@ -4848,7 +4848,7 @@
       <c r="F91" s="5" t="s">
         <v>527</v>
       </c>
-      <c r="G91" s="27" t="s">
+      <c r="G91" s="36" t="s">
         <v>521</v>
       </c>
       <c r="H91" s="15" t="s">
@@ -4856,9 +4856,9 @@
       </c>
     </row>
     <row r="92" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A92" s="36"/>
-      <c r="B92" s="30"/>
-      <c r="C92" s="28"/>
+      <c r="A92" s="42"/>
+      <c r="B92" s="34"/>
+      <c r="C92" s="25"/>
       <c r="D92" s="5" t="s">
         <v>181</v>
       </c>
@@ -4868,19 +4868,19 @@
       <c r="F92" s="5" t="s">
         <v>528</v>
       </c>
-      <c r="G92" s="27"/>
+      <c r="G92" s="36"/>
       <c r="H92" s="15" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="93" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A93" s="33">
+      <c r="A93" s="32">
         <v>23</v>
       </c>
-      <c r="B93" s="30" t="s">
+      <c r="B93" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="C93" s="28" t="s">
+      <c r="C93" s="25" t="s">
         <v>6</v>
       </c>
       <c r="D93" s="5" t="s">
@@ -4892,7 +4892,7 @@
       <c r="F93" s="5" t="s">
         <v>534</v>
       </c>
-      <c r="G93" s="27" t="s">
+      <c r="G93" s="36" t="s">
         <v>297</v>
       </c>
       <c r="H93" s="15" t="s">
@@ -4900,9 +4900,9 @@
       </c>
     </row>
     <row r="94" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A94" s="34"/>
-      <c r="B94" s="30"/>
-      <c r="C94" s="28"/>
+      <c r="A94" s="33"/>
+      <c r="B94" s="34"/>
+      <c r="C94" s="25"/>
       <c r="D94" s="5" t="s">
         <v>31</v>
       </c>
@@ -4912,19 +4912,19 @@
       <c r="F94" s="5" t="s">
         <v>535</v>
       </c>
-      <c r="G94" s="27"/>
+      <c r="G94" s="36"/>
       <c r="H94" s="15" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="95" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A95" s="33">
+      <c r="A95" s="32">
         <v>24</v>
       </c>
-      <c r="B95" s="30" t="s">
+      <c r="B95" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="C95" s="28" t="s">
+      <c r="C95" s="25" t="s">
         <v>6</v>
       </c>
       <c r="D95" s="5" t="s">
@@ -4936,7 +4936,7 @@
       <c r="F95" s="5" t="s">
         <v>565</v>
       </c>
-      <c r="G95" s="27" t="s">
+      <c r="G95" s="36" t="s">
         <v>207</v>
       </c>
       <c r="H95" s="15" t="s">
@@ -4944,9 +4944,9 @@
       </c>
     </row>
     <row r="96" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A96" s="34"/>
-      <c r="B96" s="30"/>
-      <c r="C96" s="28"/>
+      <c r="A96" s="33"/>
+      <c r="B96" s="34"/>
+      <c r="C96" s="25"/>
       <c r="D96" s="5" t="s">
         <v>171</v>
       </c>
@@ -4956,19 +4956,19 @@
       <c r="F96" s="5" t="s">
         <v>566</v>
       </c>
-      <c r="G96" s="27"/>
+      <c r="G96" s="36"/>
       <c r="H96" s="15" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="97" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A97" s="33">
+      <c r="A97" s="32">
         <v>25</v>
       </c>
-      <c r="B97" s="29" t="s">
+      <c r="B97" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="C97" s="28" t="s">
+      <c r="C97" s="25" t="s">
         <v>14</v>
       </c>
       <c r="D97" s="5" t="s">
@@ -4980,15 +4980,15 @@
       <c r="F97" s="5" t="s">
         <v>556</v>
       </c>
-      <c r="G97" s="27"/>
+      <c r="G97" s="36"/>
       <c r="H97" s="15" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="98" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A98" s="34"/>
-      <c r="B98" s="29"/>
-      <c r="C98" s="28"/>
+      <c r="A98" s="33"/>
+      <c r="B98" s="37"/>
+      <c r="C98" s="25"/>
       <c r="D98" s="5" t="s">
         <v>151</v>
       </c>
@@ -4998,19 +4998,19 @@
       <c r="F98" s="5" t="s">
         <v>557</v>
       </c>
-      <c r="G98" s="27"/>
+      <c r="G98" s="36"/>
       <c r="H98" s="15" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="99" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A99" s="33">
+      <c r="A99" s="32">
         <v>26</v>
       </c>
-      <c r="B99" s="29" t="s">
+      <c r="B99" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="C99" s="44" t="s">
+      <c r="C99" s="35" t="s">
         <v>14</v>
       </c>
       <c r="D99" s="5" t="s">
@@ -5022,15 +5022,15 @@
       <c r="F99" s="5" t="s">
         <v>633</v>
       </c>
-      <c r="G99" s="27"/>
+      <c r="G99" s="36"/>
       <c r="H99" s="15" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="100" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A100" s="34"/>
-      <c r="B100" s="29"/>
-      <c r="C100" s="44"/>
+      <c r="A100" s="33"/>
+      <c r="B100" s="37"/>
+      <c r="C100" s="35"/>
       <c r="D100" s="5" t="s">
         <v>163</v>
       </c>
@@ -5040,19 +5040,19 @@
       <c r="F100" s="5" t="s">
         <v>634</v>
       </c>
-      <c r="G100" s="27"/>
+      <c r="G100" s="36"/>
       <c r="H100" s="15" t="s">
         <v>408</v>
       </c>
     </row>
     <row r="101" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A101" s="33">
+      <c r="A101" s="32">
         <v>27</v>
       </c>
-      <c r="B101" s="29" t="s">
+      <c r="B101" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="C101" s="28" t="s">
+      <c r="C101" s="25" t="s">
         <v>14</v>
       </c>
       <c r="D101" s="5" t="s">
@@ -5064,15 +5064,15 @@
       <c r="F101" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="G101" s="27"/>
+      <c r="G101" s="36"/>
       <c r="H101" s="15" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="102" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A102" s="34"/>
-      <c r="B102" s="29"/>
-      <c r="C102" s="28"/>
+      <c r="A102" s="33"/>
+      <c r="B102" s="37"/>
+      <c r="C102" s="25"/>
       <c r="D102" s="5" t="s">
         <v>45</v>
       </c>
@@ -5082,19 +5082,19 @@
       <c r="F102" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="G102" s="27"/>
+      <c r="G102" s="36"/>
       <c r="H102" s="15" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="103" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A103" s="33">
+      <c r="A103" s="32">
         <v>28</v>
       </c>
-      <c r="B103" s="29" t="s">
+      <c r="B103" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="C103" s="28" t="s">
+      <c r="C103" s="25" t="s">
         <v>14</v>
       </c>
       <c r="D103" s="5" t="s">
@@ -5106,15 +5106,15 @@
       <c r="F103" s="5" t="s">
         <v>612</v>
       </c>
-      <c r="G103" s="27"/>
+      <c r="G103" s="36"/>
       <c r="H103" s="15" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="104" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A104" s="34"/>
-      <c r="B104" s="29"/>
-      <c r="C104" s="28"/>
+      <c r="A104" s="33"/>
+      <c r="B104" s="37"/>
+      <c r="C104" s="25"/>
       <c r="D104" s="5" t="s">
         <v>70</v>
       </c>
@@ -5124,19 +5124,19 @@
       <c r="F104" s="5" t="s">
         <v>613</v>
       </c>
-      <c r="G104" s="27"/>
+      <c r="G104" s="36"/>
       <c r="H104" s="15" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="105" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A105" s="33">
+      <c r="A105" s="32">
         <v>29</v>
       </c>
-      <c r="B105" s="29" t="s">
+      <c r="B105" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="C105" s="28" t="s">
+      <c r="C105" s="25" t="s">
         <v>14</v>
       </c>
       <c r="D105" s="5" t="s">
@@ -5148,7 +5148,7 @@
       <c r="F105" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="G105" s="27" t="s">
+      <c r="G105" s="36" t="s">
         <v>553</v>
       </c>
       <c r="H105" s="15" t="s">
@@ -5156,9 +5156,9 @@
       </c>
     </row>
     <row r="106" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A106" s="34"/>
-      <c r="B106" s="29"/>
-      <c r="C106" s="28"/>
+      <c r="A106" s="33"/>
+      <c r="B106" s="37"/>
+      <c r="C106" s="25"/>
       <c r="D106" s="5" t="s">
         <v>157</v>
       </c>
@@ -5168,19 +5168,19 @@
       <c r="F106" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="G106" s="27"/>
+      <c r="G106" s="36"/>
       <c r="H106" s="15" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="107" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A107" s="33">
+      <c r="A107" s="32">
         <v>30</v>
       </c>
-      <c r="B107" s="29" t="s">
+      <c r="B107" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="C107" s="28" t="s">
+      <c r="C107" s="25" t="s">
         <v>14</v>
       </c>
       <c r="D107" s="5" t="s">
@@ -5192,7 +5192,7 @@
       <c r="F107" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="G107" s="27" t="s">
+      <c r="G107" s="36" t="s">
         <v>227</v>
       </c>
       <c r="H107" s="15" t="s">
@@ -5200,9 +5200,9 @@
       </c>
     </row>
     <row r="108" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A108" s="34"/>
-      <c r="B108" s="29"/>
-      <c r="C108" s="28"/>
+      <c r="A108" s="33"/>
+      <c r="B108" s="37"/>
+      <c r="C108" s="25"/>
       <c r="D108" s="5" t="s">
         <v>47</v>
       </c>
@@ -5212,19 +5212,19 @@
       <c r="F108" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="G108" s="27"/>
+      <c r="G108" s="36"/>
       <c r="H108" s="15" t="s">
         <v>412</v>
       </c>
     </row>
     <row r="109" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A109" s="33">
+      <c r="A109" s="32">
         <v>31</v>
       </c>
-      <c r="B109" s="42" t="s">
+      <c r="B109" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="C109" s="47" t="s">
+      <c r="C109" s="39" t="s">
         <v>14</v>
       </c>
       <c r="D109" s="5" t="s">
@@ -5236,7 +5236,7 @@
       <c r="F109" s="5" t="s">
         <v>573</v>
       </c>
-      <c r="G109" s="45" t="s">
+      <c r="G109" s="48" t="s">
         <v>276</v>
       </c>
       <c r="H109" s="15" t="s">
@@ -5244,9 +5244,9 @@
       </c>
     </row>
     <row r="110" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A110" s="34"/>
-      <c r="B110" s="43"/>
-      <c r="C110" s="48"/>
+      <c r="A110" s="33"/>
+      <c r="B110" s="47"/>
+      <c r="C110" s="40"/>
       <c r="D110" s="5" t="s">
         <v>194</v>
       </c>
@@ -5256,19 +5256,19 @@
       <c r="F110" s="5" t="s">
         <v>574</v>
       </c>
-      <c r="G110" s="46"/>
+      <c r="G110" s="49"/>
       <c r="H110" s="15" t="s">
         <v>413</v>
       </c>
     </row>
     <row r="111" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A111" s="33">
+      <c r="A111" s="32">
         <v>32</v>
       </c>
-      <c r="B111" s="29" t="s">
+      <c r="B111" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="C111" s="44" t="s">
+      <c r="C111" s="35" t="s">
         <v>14</v>
       </c>
       <c r="D111" s="5" t="s">
@@ -5280,15 +5280,15 @@
       <c r="F111" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="G111" s="27"/>
+      <c r="G111" s="36"/>
       <c r="H111" s="15" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="112" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A112" s="34"/>
-      <c r="B112" s="29"/>
-      <c r="C112" s="44"/>
+      <c r="A112" s="33"/>
+      <c r="B112" s="37"/>
+      <c r="C112" s="35"/>
       <c r="D112" s="5" t="s">
         <v>52</v>
       </c>
@@ -5298,19 +5298,19 @@
       <c r="F112" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="G112" s="27"/>
+      <c r="G112" s="36"/>
       <c r="H112" s="15" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="113" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A113" s="33">
+      <c r="A113" s="32">
         <v>33</v>
       </c>
-      <c r="B113" s="29" t="s">
+      <c r="B113" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="C113" s="28" t="s">
+      <c r="C113" s="25" t="s">
         <v>14</v>
       </c>
       <c r="D113" s="5" t="s">
@@ -5322,15 +5322,15 @@
       <c r="F113" s="5" t="s">
         <v>590</v>
       </c>
-      <c r="G113" s="27"/>
+      <c r="G113" s="36"/>
       <c r="H113" s="15" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="114" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A114" s="34"/>
-      <c r="B114" s="29"/>
-      <c r="C114" s="28"/>
+      <c r="A114" s="33"/>
+      <c r="B114" s="37"/>
+      <c r="C114" s="25"/>
       <c r="D114" s="5" t="s">
         <v>136</v>
       </c>
@@ -5340,19 +5340,19 @@
       <c r="F114" s="5" t="s">
         <v>591</v>
       </c>
-      <c r="G114" s="27"/>
+      <c r="G114" s="36"/>
       <c r="H114" s="15" t="s">
         <v>415</v>
       </c>
     </row>
     <row r="115" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A115" s="33">
+      <c r="A115" s="32">
         <v>34</v>
       </c>
-      <c r="B115" s="29" t="s">
+      <c r="B115" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="C115" s="28" t="s">
+      <c r="C115" s="25" t="s">
         <v>14</v>
       </c>
       <c r="D115" s="5" t="s">
@@ -5364,7 +5364,7 @@
       <c r="F115" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="G115" s="27" t="s">
+      <c r="G115" s="36" t="s">
         <v>227</v>
       </c>
       <c r="H115" s="15" t="s">
@@ -5372,9 +5372,9 @@
       </c>
     </row>
     <row r="116" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A116" s="34"/>
-      <c r="B116" s="29"/>
-      <c r="C116" s="28"/>
+      <c r="A116" s="33"/>
+      <c r="B116" s="37"/>
+      <c r="C116" s="25"/>
       <c r="D116" s="5" t="s">
         <v>78</v>
       </c>
@@ -5384,19 +5384,19 @@
       <c r="F116" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="G116" s="27"/>
+      <c r="G116" s="36"/>
       <c r="H116" s="15" t="s">
         <v>462</v>
       </c>
     </row>
     <row r="117" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A117" s="33">
+      <c r="A117" s="32">
         <v>35</v>
       </c>
-      <c r="B117" s="29" t="s">
+      <c r="B117" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="C117" s="28" t="s">
+      <c r="C117" s="25" t="s">
         <v>14</v>
       </c>
       <c r="D117" s="5" t="s">
@@ -5408,7 +5408,7 @@
       <c r="F117" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="G117" s="27" t="s">
+      <c r="G117" s="36" t="s">
         <v>227</v>
       </c>
       <c r="H117" s="15" t="s">
@@ -5416,9 +5416,9 @@
       </c>
     </row>
     <row r="118" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A118" s="34"/>
-      <c r="B118" s="29"/>
-      <c r="C118" s="28"/>
+      <c r="A118" s="33"/>
+      <c r="B118" s="37"/>
+      <c r="C118" s="25"/>
       <c r="D118" s="5" t="s">
         <v>80</v>
       </c>
@@ -5428,19 +5428,19 @@
       <c r="F118" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="G118" s="27"/>
+      <c r="G118" s="36"/>
       <c r="H118" s="15" t="s">
         <v>416</v>
       </c>
     </row>
     <row r="119" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A119" s="33">
+      <c r="A119" s="32">
         <v>36</v>
       </c>
-      <c r="B119" s="29" t="s">
+      <c r="B119" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="C119" s="28" t="s">
+      <c r="C119" s="25" t="s">
         <v>14</v>
       </c>
       <c r="D119" s="5" t="s">
@@ -5452,7 +5452,7 @@
       <c r="F119" s="5" t="s">
         <v>506</v>
       </c>
-      <c r="G119" s="27" t="s">
+      <c r="G119" s="36" t="s">
         <v>257</v>
       </c>
       <c r="H119" s="15" t="s">
@@ -5460,9 +5460,9 @@
       </c>
     </row>
     <row r="120" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A120" s="34"/>
-      <c r="B120" s="29"/>
-      <c r="C120" s="28"/>
+      <c r="A120" s="33"/>
+      <c r="B120" s="37"/>
+      <c r="C120" s="25"/>
       <c r="D120" s="5" t="s">
         <v>122</v>
       </c>
@@ -5472,19 +5472,19 @@
       <c r="F120" s="5" t="s">
         <v>507</v>
       </c>
-      <c r="G120" s="27"/>
+      <c r="G120" s="36"/>
       <c r="H120" s="15" t="s">
         <v>417</v>
       </c>
     </row>
     <row r="121" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A121" s="33">
+      <c r="A121" s="32">
         <v>37</v>
       </c>
-      <c r="B121" s="42" t="s">
+      <c r="B121" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="C121" s="28" t="s">
+      <c r="C121" s="25" t="s">
         <v>14</v>
       </c>
       <c r="D121" s="5" t="s">
@@ -5496,15 +5496,15 @@
       <c r="F121" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="G121" s="27"/>
+      <c r="G121" s="36"/>
       <c r="H121" s="15" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="122" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A122" s="34"/>
-      <c r="B122" s="43"/>
-      <c r="C122" s="28"/>
+      <c r="A122" s="33"/>
+      <c r="B122" s="47"/>
+      <c r="C122" s="25"/>
       <c r="D122" s="5" t="s">
         <v>185</v>
       </c>
@@ -5514,19 +5514,19 @@
       <c r="F122" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="G122" s="27"/>
+      <c r="G122" s="36"/>
       <c r="H122" s="15" t="s">
         <v>418</v>
       </c>
     </row>
     <row r="123" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A123" s="33">
+      <c r="A123" s="32">
         <v>38</v>
       </c>
-      <c r="B123" s="42" t="s">
+      <c r="B123" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="C123" s="28" t="s">
+      <c r="C123" s="25" t="s">
         <v>14</v>
       </c>
       <c r="D123" s="5" t="s">
@@ -5538,15 +5538,15 @@
       <c r="F123" s="5" t="s">
         <v>513</v>
       </c>
-      <c r="G123" s="27"/>
+      <c r="G123" s="36"/>
       <c r="H123" s="15" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="124" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A124" s="34"/>
-      <c r="B124" s="43"/>
-      <c r="C124" s="28"/>
+      <c r="A124" s="33"/>
+      <c r="B124" s="47"/>
+      <c r="C124" s="25"/>
       <c r="D124" s="5" t="s">
         <v>54</v>
       </c>
@@ -5556,19 +5556,19 @@
       <c r="F124" s="5" t="s">
         <v>514</v>
       </c>
-      <c r="G124" s="27"/>
+      <c r="G124" s="36"/>
       <c r="H124" s="15" t="s">
         <v>423</v>
       </c>
     </row>
     <row r="125" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A125" s="33">
+      <c r="A125" s="32">
         <v>39</v>
       </c>
-      <c r="B125" s="42" t="s">
+      <c r="B125" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="C125" s="28" t="s">
+      <c r="C125" s="25" t="s">
         <v>14</v>
       </c>
       <c r="D125" s="5" t="s">
@@ -5580,7 +5580,7 @@
       <c r="F125" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="G125" s="27" t="s">
+      <c r="G125" s="36" t="s">
         <v>555</v>
       </c>
       <c r="H125" s="15" t="s">
@@ -5588,9 +5588,9 @@
       </c>
     </row>
     <row r="126" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A126" s="34"/>
-      <c r="B126" s="43"/>
-      <c r="C126" s="28"/>
+      <c r="A126" s="33"/>
+      <c r="B126" s="47"/>
+      <c r="C126" s="25"/>
       <c r="D126" s="5" t="s">
         <v>134</v>
       </c>
@@ -5600,19 +5600,19 @@
       <c r="F126" s="5" t="s">
         <v>602</v>
       </c>
-      <c r="G126" s="27"/>
+      <c r="G126" s="36"/>
       <c r="H126" s="15" t="s">
         <v>601</v>
       </c>
     </row>
     <row r="127" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A127" s="33">
+      <c r="A127" s="32">
         <v>40</v>
       </c>
-      <c r="B127" s="42" t="s">
+      <c r="B127" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="C127" s="28" t="s">
+      <c r="C127" s="25" t="s">
         <v>14</v>
       </c>
       <c r="D127" s="5" t="s">
@@ -5624,15 +5624,15 @@
       <c r="F127" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="G127" s="27"/>
+      <c r="G127" s="36"/>
       <c r="H127" s="15" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="128" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A128" s="34"/>
-      <c r="B128" s="43"/>
-      <c r="C128" s="28"/>
+      <c r="A128" s="33"/>
+      <c r="B128" s="47"/>
+      <c r="C128" s="25"/>
       <c r="D128" s="5" t="s">
         <v>82</v>
       </c>
@@ -5642,19 +5642,19 @@
       <c r="F128" s="5" t="s">
         <v>522</v>
       </c>
-      <c r="G128" s="27"/>
+      <c r="G128" s="36"/>
       <c r="H128" s="15" t="s">
         <v>429</v>
       </c>
     </row>
     <row r="129" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A129" s="33">
+      <c r="A129" s="32">
         <v>41</v>
       </c>
-      <c r="B129" s="42" t="s">
+      <c r="B129" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="C129" s="31" t="s">
+      <c r="C129" s="43" t="s">
         <v>14</v>
       </c>
       <c r="D129" s="5" t="s">
@@ -5666,15 +5666,15 @@
       <c r="F129" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="G129" s="27"/>
+      <c r="G129" s="36"/>
       <c r="H129" s="15" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="130" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A130" s="34"/>
-      <c r="B130" s="43"/>
-      <c r="C130" s="31"/>
+      <c r="A130" s="33"/>
+      <c r="B130" s="47"/>
+      <c r="C130" s="43"/>
       <c r="D130" s="5" t="s">
         <v>65</v>
       </c>
@@ -5684,19 +5684,19 @@
       <c r="F130" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="G130" s="27"/>
+      <c r="G130" s="36"/>
       <c r="H130" s="15" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="131" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A131" s="33">
+      <c r="A131" s="32">
         <v>42</v>
       </c>
-      <c r="B131" s="32" t="s">
+      <c r="B131" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="C131" s="28" t="s">
+      <c r="C131" s="25" t="s">
         <v>14</v>
       </c>
       <c r="D131" s="5" t="s">
@@ -5708,15 +5708,15 @@
       <c r="F131" s="5" t="s">
         <v>606</v>
       </c>
-      <c r="G131" s="27"/>
+      <c r="G131" s="36"/>
       <c r="H131" s="15" t="s">
         <v>604</v>
       </c>
     </row>
     <row r="132" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A132" s="34"/>
-      <c r="B132" s="32"/>
-      <c r="C132" s="28"/>
+      <c r="A132" s="33"/>
+      <c r="B132" s="38"/>
+      <c r="C132" s="25"/>
       <c r="D132" s="5" t="s">
         <v>51</v>
       </c>
@@ -5726,19 +5726,19 @@
       <c r="F132" s="5" t="s">
         <v>603</v>
       </c>
-      <c r="G132" s="27"/>
+      <c r="G132" s="36"/>
       <c r="H132" s="15" t="s">
         <v>605</v>
       </c>
     </row>
     <row r="133" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A133" s="33">
+      <c r="A133" s="32">
         <v>43</v>
       </c>
-      <c r="B133" s="32" t="s">
+      <c r="B133" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="C133" s="28" t="s">
+      <c r="C133" s="25" t="s">
         <v>14</v>
       </c>
       <c r="D133" s="5" t="s">
@@ -5755,9 +5755,9 @@
       </c>
     </row>
     <row r="134" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A134" s="34"/>
-      <c r="B134" s="32"/>
-      <c r="C134" s="28"/>
+      <c r="A134" s="33"/>
+      <c r="B134" s="38"/>
+      <c r="C134" s="25"/>
       <c r="D134" s="5" t="s">
         <v>140</v>
       </c>
@@ -5772,13 +5772,13 @@
       </c>
     </row>
     <row r="135" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A135" s="33">
+      <c r="A135" s="32">
         <v>44</v>
       </c>
-      <c r="B135" s="32" t="s">
+      <c r="B135" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="C135" s="28" t="s">
+      <c r="C135" s="25" t="s">
         <v>14</v>
       </c>
       <c r="D135" s="5" t="s">
@@ -5790,15 +5790,15 @@
       <c r="F135" s="5" t="s">
         <v>508</v>
       </c>
-      <c r="G135" s="27"/>
+      <c r="G135" s="36"/>
       <c r="H135" s="15" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="136" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A136" s="34"/>
-      <c r="B136" s="32"/>
-      <c r="C136" s="28"/>
+      <c r="A136" s="33"/>
+      <c r="B136" s="38"/>
+      <c r="C136" s="25"/>
       <c r="D136" s="5" t="s">
         <v>49</v>
       </c>
@@ -5808,19 +5808,19 @@
       <c r="F136" s="5" t="s">
         <v>509</v>
       </c>
-      <c r="G136" s="27"/>
+      <c r="G136" s="36"/>
       <c r="H136" s="15" t="s">
         <v>420</v>
       </c>
     </row>
     <row r="137" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A137" s="33">
+      <c r="A137" s="32">
         <v>45</v>
       </c>
-      <c r="B137" s="32" t="s">
+      <c r="B137" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="C137" s="44" t="s">
+      <c r="C137" s="35" t="s">
         <v>14</v>
       </c>
       <c r="D137" s="5" t="s">
@@ -5832,15 +5832,15 @@
       <c r="F137" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="G137" s="27"/>
+      <c r="G137" s="36"/>
       <c r="H137" s="15" t="s">
         <v>484</v>
       </c>
     </row>
     <row r="138" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A138" s="34"/>
-      <c r="B138" s="32"/>
-      <c r="C138" s="44"/>
+      <c r="A138" s="33"/>
+      <c r="B138" s="38"/>
+      <c r="C138" s="35"/>
       <c r="D138" s="5" t="s">
         <v>183</v>
       </c>
@@ -5850,19 +5850,19 @@
       <c r="F138" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="G138" s="27"/>
+      <c r="G138" s="36"/>
       <c r="H138" s="15" t="s">
         <v>485</v>
       </c>
     </row>
     <row r="139" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A139" s="33">
+      <c r="A139" s="32">
         <v>46</v>
       </c>
-      <c r="B139" s="32" t="s">
+      <c r="B139" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="C139" s="28" t="s">
+      <c r="C139" s="25" t="s">
         <v>14</v>
       </c>
       <c r="D139" s="5" t="s">
@@ -5874,7 +5874,7 @@
       <c r="F139" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="G139" s="27" t="s">
+      <c r="G139" s="36" t="s">
         <v>219</v>
       </c>
       <c r="H139" s="15" t="s">
@@ -5882,9 +5882,9 @@
       </c>
     </row>
     <row r="140" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A140" s="34"/>
-      <c r="B140" s="32"/>
-      <c r="C140" s="28"/>
+      <c r="A140" s="33"/>
+      <c r="B140" s="38"/>
+      <c r="C140" s="25"/>
       <c r="D140" s="5" t="s">
         <v>244</v>
       </c>
@@ -5894,19 +5894,19 @@
       <c r="F140" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="G140" s="27"/>
+      <c r="G140" s="36"/>
       <c r="H140" s="15" t="s">
         <v>421</v>
       </c>
     </row>
     <row r="141" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A141" s="33">
+      <c r="A141" s="32">
         <v>47</v>
       </c>
-      <c r="B141" s="32" t="s">
+      <c r="B141" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="C141" s="28" t="s">
+      <c r="C141" s="25" t="s">
         <v>14</v>
       </c>
       <c r="D141" s="5" t="s">
@@ -5918,7 +5918,7 @@
       <c r="F141" s="5" t="s">
         <v>510</v>
       </c>
-      <c r="G141" s="27" t="s">
+      <c r="G141" s="36" t="s">
         <v>587</v>
       </c>
       <c r="H141" s="15" t="s">
@@ -5926,9 +5926,9 @@
       </c>
     </row>
     <row r="142" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A142" s="34"/>
-      <c r="B142" s="32"/>
-      <c r="C142" s="28"/>
+      <c r="A142" s="33"/>
+      <c r="B142" s="38"/>
+      <c r="C142" s="25"/>
       <c r="D142" s="5" t="s">
         <v>170</v>
       </c>
@@ -5938,19 +5938,19 @@
       <c r="F142" s="5" t="s">
         <v>511</v>
       </c>
-      <c r="G142" s="27"/>
+      <c r="G142" s="36"/>
       <c r="H142" s="15" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="143" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A143" s="33">
+      <c r="A143" s="32">
         <v>48</v>
       </c>
-      <c r="B143" s="32" t="s">
+      <c r="B143" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="C143" s="28" t="s">
+      <c r="C143" s="25" t="s">
         <v>14</v>
       </c>
       <c r="D143" s="5" t="s">
@@ -5962,15 +5962,15 @@
       <c r="F143" s="5" t="s">
         <v>512</v>
       </c>
-      <c r="G143" s="27"/>
+      <c r="G143" s="36"/>
       <c r="H143" s="15" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="144" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A144" s="34"/>
-      <c r="B144" s="32"/>
-      <c r="C144" s="28"/>
+      <c r="A144" s="33"/>
+      <c r="B144" s="38"/>
+      <c r="C144" s="25"/>
       <c r="D144" s="5" t="s">
         <v>55</v>
       </c>
@@ -5980,19 +5980,19 @@
       <c r="F144" s="5" t="s">
         <v>512</v>
       </c>
-      <c r="G144" s="27"/>
+      <c r="G144" s="36"/>
       <c r="H144" s="15" t="s">
         <v>424</v>
       </c>
     </row>
     <row r="145" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A145" s="33">
+      <c r="A145" s="32">
         <v>49</v>
       </c>
-      <c r="B145" s="32" t="s">
+      <c r="B145" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="C145" s="44" t="s">
+      <c r="C145" s="35" t="s">
         <v>14</v>
       </c>
       <c r="D145" s="5" t="s">
@@ -6004,7 +6004,7 @@
       <c r="F145" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="G145" s="27" t="s">
+      <c r="G145" s="36" t="s">
         <v>587</v>
       </c>
       <c r="H145" s="15" t="s">
@@ -6012,9 +6012,9 @@
       </c>
     </row>
     <row r="146" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A146" s="34"/>
-      <c r="B146" s="32"/>
-      <c r="C146" s="44"/>
+      <c r="A146" s="33"/>
+      <c r="B146" s="38"/>
+      <c r="C146" s="35"/>
       <c r="D146" s="5" t="s">
         <v>57</v>
       </c>
@@ -6024,19 +6024,19 @@
       <c r="F146" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="G146" s="27"/>
+      <c r="G146" s="36"/>
       <c r="H146" s="15" t="s">
         <v>458</v>
       </c>
     </row>
     <row r="147" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A147" s="33">
+      <c r="A147" s="32">
         <v>50</v>
       </c>
-      <c r="B147" s="32" t="s">
+      <c r="B147" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="C147" s="31" t="s">
+      <c r="C147" s="43" t="s">
         <v>14</v>
       </c>
       <c r="D147" s="5" t="s">
@@ -6048,15 +6048,15 @@
       <c r="F147" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="G147" s="27"/>
+      <c r="G147" s="36"/>
       <c r="H147" s="15" t="s">
         <v>540</v>
       </c>
     </row>
     <row r="148" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A148" s="34"/>
-      <c r="B148" s="32"/>
-      <c r="C148" s="31"/>
+      <c r="A148" s="33"/>
+      <c r="B148" s="38"/>
+      <c r="C148" s="43"/>
       <c r="D148" s="5" t="s">
         <v>59</v>
       </c>
@@ -6066,19 +6066,19 @@
       <c r="F148" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="G148" s="27"/>
+      <c r="G148" s="36"/>
       <c r="H148" s="15" t="s">
         <v>541</v>
       </c>
     </row>
     <row r="149" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A149" s="33">
+      <c r="A149" s="32">
         <v>51</v>
       </c>
-      <c r="B149" s="32" t="s">
+      <c r="B149" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="C149" s="28" t="s">
+      <c r="C149" s="25" t="s">
         <v>14</v>
       </c>
       <c r="D149" s="5" t="s">
@@ -6090,15 +6090,15 @@
       <c r="F149" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="G149" s="27"/>
+      <c r="G149" s="36"/>
       <c r="H149" s="15" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="150" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A150" s="34"/>
-      <c r="B150" s="32"/>
-      <c r="C150" s="28"/>
+      <c r="A150" s="33"/>
+      <c r="B150" s="38"/>
+      <c r="C150" s="25"/>
       <c r="D150" s="5" t="s">
         <v>188</v>
       </c>
@@ -6108,19 +6108,19 @@
       <c r="F150" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="G150" s="27"/>
+      <c r="G150" s="36"/>
       <c r="H150" s="15" t="s">
         <v>425</v>
       </c>
     </row>
     <row r="151" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A151" s="33">
+      <c r="A151" s="32">
         <v>52</v>
       </c>
-      <c r="B151" s="32" t="s">
+      <c r="B151" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="C151" s="28" t="s">
+      <c r="C151" s="25" t="s">
         <v>14</v>
       </c>
       <c r="D151" s="5" t="s">
@@ -6132,15 +6132,15 @@
       <c r="F151" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="G151" s="27"/>
+      <c r="G151" s="36"/>
       <c r="H151" s="15" t="s">
         <v>459</v>
       </c>
     </row>
     <row r="152" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A152" s="34"/>
-      <c r="B152" s="32"/>
-      <c r="C152" s="28"/>
+      <c r="A152" s="33"/>
+      <c r="B152" s="38"/>
+      <c r="C152" s="25"/>
       <c r="D152" s="5" t="s">
         <v>198</v>
       </c>
@@ -6150,19 +6150,19 @@
       <c r="F152" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="G152" s="27"/>
+      <c r="G152" s="36"/>
       <c r="H152" s="15" t="s">
         <v>460</v>
       </c>
     </row>
     <row r="153" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A153" s="33">
+      <c r="A153" s="32">
         <v>53</v>
       </c>
-      <c r="B153" s="32" t="s">
+      <c r="B153" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="C153" s="28" t="s">
+      <c r="C153" s="25" t="s">
         <v>14</v>
       </c>
       <c r="D153" s="5" t="s">
@@ -6174,7 +6174,7 @@
       <c r="F153" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="G153" s="27" t="s">
+      <c r="G153" s="36" t="s">
         <v>268</v>
       </c>
       <c r="H153" s="15" t="s">
@@ -6182,9 +6182,9 @@
       </c>
     </row>
     <row r="154" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A154" s="34"/>
-      <c r="B154" s="32"/>
-      <c r="C154" s="28"/>
+      <c r="A154" s="33"/>
+      <c r="B154" s="38"/>
+      <c r="C154" s="25"/>
       <c r="D154" s="5" t="s">
         <v>63</v>
       </c>
@@ -6194,19 +6194,19 @@
       <c r="F154" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="G154" s="27"/>
+      <c r="G154" s="36"/>
       <c r="H154" s="15" t="s">
         <v>487</v>
       </c>
     </row>
     <row r="155" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A155" s="33">
+      <c r="A155" s="32">
         <v>54</v>
       </c>
-      <c r="B155" s="32" t="s">
+      <c r="B155" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="C155" s="28" t="s">
+      <c r="C155" s="25" t="s">
         <v>14</v>
       </c>
       <c r="D155" s="5" t="s">
@@ -6218,15 +6218,15 @@
       <c r="F155" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="G155" s="27"/>
+      <c r="G155" s="36"/>
       <c r="H155" s="15" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="156" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A156" s="34"/>
-      <c r="B156" s="32"/>
-      <c r="C156" s="28"/>
+      <c r="A156" s="33"/>
+      <c r="B156" s="38"/>
+      <c r="C156" s="25"/>
       <c r="D156" s="5" t="s">
         <v>165</v>
       </c>
@@ -6236,19 +6236,19 @@
       <c r="F156" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="G156" s="27"/>
+      <c r="G156" s="36"/>
       <c r="H156" s="15" t="s">
         <v>427</v>
       </c>
     </row>
     <row r="157" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A157" s="33">
+      <c r="A157" s="32">
         <v>55</v>
       </c>
-      <c r="B157" s="32" t="s">
+      <c r="B157" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="C157" s="28" t="s">
+      <c r="C157" s="25" t="s">
         <v>14</v>
       </c>
       <c r="D157" s="5" t="s">
@@ -6260,15 +6260,15 @@
       <c r="F157" s="5" t="s">
         <v>610</v>
       </c>
-      <c r="G157" s="27"/>
+      <c r="G157" s="36"/>
       <c r="H157" s="15" t="s">
         <v>361</v>
       </c>
     </row>
     <row r="158" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A158" s="34"/>
-      <c r="B158" s="32"/>
-      <c r="C158" s="28"/>
+      <c r="A158" s="33"/>
+      <c r="B158" s="38"/>
+      <c r="C158" s="25"/>
       <c r="D158" s="5" t="s">
         <v>167</v>
       </c>
@@ -6278,19 +6278,19 @@
       <c r="F158" s="5" t="s">
         <v>611</v>
       </c>
-      <c r="G158" s="27"/>
+      <c r="G158" s="36"/>
       <c r="H158" s="15" t="s">
         <v>428</v>
       </c>
     </row>
     <row r="159" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A159" s="33">
+      <c r="A159" s="32">
         <v>56</v>
       </c>
-      <c r="B159" s="32" t="s">
+      <c r="B159" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="C159" s="28" t="s">
+      <c r="C159" s="25" t="s">
         <v>14</v>
       </c>
       <c r="D159" s="5" t="s">
@@ -6302,7 +6302,7 @@
       <c r="F159" s="5" t="s">
         <v>609</v>
       </c>
-      <c r="G159" s="27" t="s">
+      <c r="G159" s="36" t="s">
         <v>558</v>
       </c>
       <c r="H159" s="15" t="s">
@@ -6310,9 +6310,9 @@
       </c>
     </row>
     <row r="160" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A160" s="34"/>
-      <c r="B160" s="32"/>
-      <c r="C160" s="28"/>
+      <c r="A160" s="33"/>
+      <c r="B160" s="38"/>
+      <c r="C160" s="25"/>
       <c r="D160" s="5" t="s">
         <v>155</v>
       </c>
@@ -6322,19 +6322,19 @@
       <c r="F160" s="5" t="s">
         <v>609</v>
       </c>
-      <c r="G160" s="27"/>
+      <c r="G160" s="36"/>
       <c r="H160" s="15" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="161" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A161" s="33">
+      <c r="A161" s="32">
         <v>57</v>
       </c>
-      <c r="B161" s="32" t="s">
+      <c r="B161" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="C161" s="28" t="s">
+      <c r="C161" s="25" t="s">
         <v>14</v>
       </c>
       <c r="D161" s="5" t="s">
@@ -6346,7 +6346,7 @@
       <c r="F161" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="G161" s="27" t="s">
+      <c r="G161" s="36" t="s">
         <v>592</v>
       </c>
       <c r="H161" s="15" t="s">
@@ -6354,9 +6354,9 @@
       </c>
     </row>
     <row r="162" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A162" s="34"/>
-      <c r="B162" s="32"/>
-      <c r="C162" s="28"/>
+      <c r="A162" s="33"/>
+      <c r="B162" s="38"/>
+      <c r="C162" s="25"/>
       <c r="D162" s="5" t="s">
         <v>175</v>
       </c>
@@ -6366,19 +6366,19 @@
       <c r="F162" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="G162" s="27"/>
+      <c r="G162" s="36"/>
       <c r="H162" s="15" t="s">
         <v>431</v>
       </c>
     </row>
     <row r="163" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A163" s="33">
+      <c r="A163" s="32">
         <v>58</v>
       </c>
-      <c r="B163" s="32" t="s">
+      <c r="B163" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="C163" s="44" t="s">
+      <c r="C163" s="35" t="s">
         <v>14</v>
       </c>
       <c r="D163" s="5" t="s">
@@ -6390,15 +6390,15 @@
       <c r="F163" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="G163" s="27"/>
+      <c r="G163" s="36"/>
       <c r="H163" s="15" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="164" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A164" s="34"/>
-      <c r="B164" s="32"/>
-      <c r="C164" s="44"/>
+      <c r="A164" s="33"/>
+      <c r="B164" s="38"/>
+      <c r="C164" s="35"/>
       <c r="D164" s="5" t="s">
         <v>177</v>
       </c>
@@ -6408,19 +6408,19 @@
       <c r="F164" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="G164" s="27"/>
+      <c r="G164" s="36"/>
       <c r="H164" s="15" t="s">
         <v>432</v>
       </c>
     </row>
     <row r="165" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A165" s="33">
+      <c r="A165" s="32">
         <v>59</v>
       </c>
-      <c r="B165" s="32" t="s">
+      <c r="B165" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="C165" s="44" t="s">
+      <c r="C165" s="35" t="s">
         <v>14</v>
       </c>
       <c r="D165" s="5" t="s">
@@ -6432,7 +6432,7 @@
       <c r="F165" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="G165" s="27" t="s">
+      <c r="G165" s="36" t="s">
         <v>199</v>
       </c>
       <c r="H165" s="15" t="s">
@@ -6440,9 +6440,9 @@
       </c>
     </row>
     <row r="166" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A166" s="34"/>
-      <c r="B166" s="32"/>
-      <c r="C166" s="44"/>
+      <c r="A166" s="33"/>
+      <c r="B166" s="38"/>
+      <c r="C166" s="35"/>
       <c r="D166" s="5" t="s">
         <v>147</v>
       </c>
@@ -6452,19 +6452,19 @@
       <c r="F166" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="G166" s="27"/>
+      <c r="G166" s="36"/>
       <c r="H166" s="15" t="s">
         <v>433</v>
       </c>
     </row>
     <row r="167" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A167" s="33">
+      <c r="A167" s="32">
         <v>60</v>
       </c>
-      <c r="B167" s="32" t="s">
+      <c r="B167" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="C167" s="44" t="s">
+      <c r="C167" s="35" t="s">
         <v>14</v>
       </c>
       <c r="D167" s="5" t="s">
@@ -6476,15 +6476,15 @@
       <c r="F167" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="G167" s="27"/>
+      <c r="G167" s="36"/>
       <c r="H167" s="15" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="168" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A168" s="34"/>
-      <c r="B168" s="32"/>
-      <c r="C168" s="44"/>
+      <c r="A168" s="33"/>
+      <c r="B168" s="38"/>
+      <c r="C168" s="35"/>
       <c r="D168" s="5" t="s">
         <v>119</v>
       </c>
@@ -6494,19 +6494,19 @@
       <c r="F168" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="G168" s="27"/>
+      <c r="G168" s="36"/>
       <c r="H168" s="15" t="s">
         <v>434</v>
       </c>
     </row>
     <row r="169" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A169" s="33">
+      <c r="A169" s="32">
         <v>61</v>
       </c>
-      <c r="B169" s="32" t="s">
+      <c r="B169" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="C169" s="28" t="s">
+      <c r="C169" s="25" t="s">
         <v>14</v>
       </c>
       <c r="D169" s="5" t="s">
@@ -6518,15 +6518,15 @@
       <c r="F169" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="G169" s="27"/>
+      <c r="G169" s="36"/>
       <c r="H169" s="15" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="170" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A170" s="34"/>
-      <c r="B170" s="32"/>
-      <c r="C170" s="28"/>
+      <c r="A170" s="33"/>
+      <c r="B170" s="38"/>
+      <c r="C170" s="25"/>
       <c r="D170" s="5" t="s">
         <v>84</v>
       </c>
@@ -6536,19 +6536,19 @@
       <c r="F170" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="G170" s="27"/>
+      <c r="G170" s="36"/>
       <c r="H170" s="15" t="s">
         <v>455</v>
       </c>
     </row>
     <row r="171" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A171" s="33">
+      <c r="A171" s="32">
         <v>62</v>
       </c>
-      <c r="B171" s="32" t="s">
+      <c r="B171" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="C171" s="31" t="s">
+      <c r="C171" s="43" t="s">
         <v>14</v>
       </c>
       <c r="D171" s="5" t="s">
@@ -6560,15 +6560,15 @@
       <c r="F171" s="5" t="s">
         <v>579</v>
       </c>
-      <c r="G171" s="27"/>
+      <c r="G171" s="36"/>
       <c r="H171" s="15" t="s">
         <v>578</v>
       </c>
     </row>
     <row r="172" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A172" s="34"/>
-      <c r="B172" s="32"/>
-      <c r="C172" s="31"/>
+      <c r="A172" s="33"/>
+      <c r="B172" s="38"/>
+      <c r="C172" s="43"/>
       <c r="D172" s="5" t="s">
         <v>576</v>
       </c>
@@ -6578,19 +6578,19 @@
       <c r="F172" s="5" t="s">
         <v>580</v>
       </c>
-      <c r="G172" s="27"/>
+      <c r="G172" s="36"/>
       <c r="H172" s="15" t="s">
         <v>578</v>
       </c>
     </row>
     <row r="173" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A173" s="33">
+      <c r="A173" s="32">
         <v>63</v>
       </c>
-      <c r="B173" s="32" t="s">
+      <c r="B173" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="C173" s="44" t="s">
+      <c r="C173" s="35" t="s">
         <v>14</v>
       </c>
       <c r="D173" s="5" t="s">
@@ -6602,7 +6602,7 @@
       <c r="F173" s="5" t="s">
         <v>637</v>
       </c>
-      <c r="G173" s="27" t="s">
+      <c r="G173" s="36" t="s">
         <v>636</v>
       </c>
       <c r="H173" s="15" t="s">
@@ -6610,9 +6610,9 @@
       </c>
     </row>
     <row r="174" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A174" s="34"/>
-      <c r="B174" s="32"/>
-      <c r="C174" s="44"/>
+      <c r="A174" s="33"/>
+      <c r="B174" s="38"/>
+      <c r="C174" s="35"/>
       <c r="D174" s="5" t="s">
         <v>202</v>
       </c>
@@ -6622,19 +6622,19 @@
       <c r="F174" s="5" t="s">
         <v>638</v>
       </c>
-      <c r="G174" s="27"/>
+      <c r="G174" s="36"/>
       <c r="H174" s="15" t="s">
         <v>435</v>
       </c>
     </row>
     <row r="175" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A175" s="33">
+      <c r="A175" s="32">
         <v>64</v>
       </c>
-      <c r="B175" s="32" t="s">
+      <c r="B175" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="C175" s="28" t="s">
+      <c r="C175" s="25" t="s">
         <v>14</v>
       </c>
       <c r="D175" s="5" t="s">
@@ -6646,7 +6646,7 @@
       <c r="F175" s="5" t="s">
         <v>523</v>
       </c>
-      <c r="G175" s="27" t="s">
+      <c r="G175" s="36" t="s">
         <v>115</v>
       </c>
       <c r="H175" s="15" t="s">
@@ -6654,9 +6654,9 @@
       </c>
     </row>
     <row r="176" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A176" s="34"/>
-      <c r="B176" s="32"/>
-      <c r="C176" s="28"/>
+      <c r="A176" s="33"/>
+      <c r="B176" s="38"/>
+      <c r="C176" s="25"/>
       <c r="D176" s="5" t="s">
         <v>114</v>
       </c>
@@ -6666,19 +6666,19 @@
       <c r="F176" s="5" t="s">
         <v>524</v>
       </c>
-      <c r="G176" s="27"/>
+      <c r="G176" s="36"/>
       <c r="H176" s="15" t="s">
         <v>436</v>
       </c>
     </row>
     <row r="177" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A177" s="33">
+      <c r="A177" s="32">
         <v>65</v>
       </c>
-      <c r="B177" s="30" t="s">
+      <c r="B177" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="C177" s="28" t="s">
+      <c r="C177" s="25" t="s">
         <v>14</v>
       </c>
       <c r="D177" s="5" t="s">
@@ -6690,15 +6690,15 @@
       <c r="F177" s="5" t="s">
         <v>607</v>
       </c>
-      <c r="G177" s="27"/>
+      <c r="G177" s="36"/>
       <c r="H177" s="15" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="178" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A178" s="34"/>
-      <c r="B178" s="30"/>
-      <c r="C178" s="28"/>
+      <c r="A178" s="33"/>
+      <c r="B178" s="34"/>
+      <c r="C178" s="25"/>
       <c r="D178" s="5" t="s">
         <v>68</v>
       </c>
@@ -6708,19 +6708,19 @@
       <c r="F178" s="5" t="s">
         <v>607</v>
       </c>
-      <c r="G178" s="27"/>
+      <c r="G178" s="36"/>
       <c r="H178" s="15" t="s">
         <v>437</v>
       </c>
     </row>
     <row r="179" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A179" s="33">
+      <c r="A179" s="32">
         <v>66</v>
       </c>
-      <c r="B179" s="30" t="s">
+      <c r="B179" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="C179" s="28" t="s">
+      <c r="C179" s="25" t="s">
         <v>14</v>
       </c>
       <c r="D179" s="5" t="s">
@@ -6732,15 +6732,15 @@
       <c r="F179" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="G179" s="27"/>
+      <c r="G179" s="36"/>
       <c r="H179" s="15" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="180" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A180" s="34"/>
-      <c r="B180" s="30"/>
-      <c r="C180" s="28"/>
+      <c r="A180" s="33"/>
+      <c r="B180" s="34"/>
+      <c r="C180" s="25"/>
       <c r="D180" s="5" t="s">
         <v>61</v>
       </c>
@@ -6750,19 +6750,19 @@
       <c r="F180" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="G180" s="27"/>
+      <c r="G180" s="36"/>
       <c r="H180" s="15" t="s">
         <v>438</v>
       </c>
     </row>
     <row r="181" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A181" s="33">
+      <c r="A181" s="32">
         <v>67</v>
       </c>
-      <c r="B181" s="30" t="s">
+      <c r="B181" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="C181" s="28" t="s">
+      <c r="C181" s="25" t="s">
         <v>14</v>
       </c>
       <c r="D181" s="5" t="s">
@@ -6774,15 +6774,15 @@
       <c r="F181" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="G181" s="27"/>
+      <c r="G181" s="36"/>
       <c r="H181" s="15" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="182" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A182" s="34"/>
-      <c r="B182" s="30"/>
-      <c r="C182" s="28"/>
+      <c r="A182" s="33"/>
+      <c r="B182" s="34"/>
+      <c r="C182" s="25"/>
       <c r="D182" s="5" t="s">
         <v>72</v>
       </c>
@@ -6792,19 +6792,19 @@
       <c r="F182" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="G182" s="27"/>
+      <c r="G182" s="36"/>
       <c r="H182" s="15" t="s">
         <v>439</v>
       </c>
     </row>
     <row r="183" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A183" s="33">
+      <c r="A183" s="32">
         <v>68</v>
       </c>
-      <c r="B183" s="30" t="s">
+      <c r="B183" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="C183" s="28" t="s">
+      <c r="C183" s="25" t="s">
         <v>14</v>
       </c>
       <c r="D183" s="5" t="s">
@@ -6816,15 +6816,15 @@
       <c r="F183" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="G183" s="27"/>
+      <c r="G183" s="36"/>
       <c r="H183" s="15" t="s">
         <v>582</v>
       </c>
     </row>
     <row r="184" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A184" s="34"/>
-      <c r="B184" s="30"/>
-      <c r="C184" s="28"/>
+      <c r="A184" s="33"/>
+      <c r="B184" s="34"/>
+      <c r="C184" s="25"/>
       <c r="D184" s="5" t="s">
         <v>229</v>
       </c>
@@ -6834,19 +6834,19 @@
       <c r="F184" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="G184" s="27"/>
+      <c r="G184" s="36"/>
       <c r="H184" s="15" t="s">
         <v>583</v>
       </c>
     </row>
     <row r="185" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A185" s="33">
+      <c r="A185" s="32">
         <v>69</v>
       </c>
-      <c r="B185" s="30" t="s">
+      <c r="B185" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="C185" s="28" t="s">
+      <c r="C185" s="25" t="s">
         <v>14</v>
       </c>
       <c r="D185" s="5" t="s">
@@ -6858,15 +6858,15 @@
       <c r="F185" s="5" t="s">
         <v>608</v>
       </c>
-      <c r="G185" s="27"/>
+      <c r="G185" s="36"/>
       <c r="H185" s="15" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="186" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A186" s="34"/>
-      <c r="B186" s="30"/>
-      <c r="C186" s="28"/>
+      <c r="A186" s="33"/>
+      <c r="B186" s="34"/>
+      <c r="C186" s="25"/>
       <c r="D186" s="5" t="s">
         <v>74</v>
       </c>
@@ -6876,19 +6876,19 @@
       <c r="F186" s="5" t="s">
         <v>608</v>
       </c>
-      <c r="G186" s="27"/>
+      <c r="G186" s="36"/>
       <c r="H186" s="15" t="s">
         <v>464</v>
       </c>
     </row>
     <row r="187" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A187" s="33">
+      <c r="A187" s="32">
         <v>70</v>
       </c>
-      <c r="B187" s="30" t="s">
+      <c r="B187" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="C187" s="44" t="s">
+      <c r="C187" s="35" t="s">
         <v>14</v>
       </c>
       <c r="D187" s="5" t="s">
@@ -6900,15 +6900,15 @@
       <c r="F187" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="G187" s="27"/>
+      <c r="G187" s="36"/>
       <c r="H187" s="15" t="s">
         <v>473</v>
       </c>
     </row>
     <row r="188" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A188" s="34"/>
-      <c r="B188" s="30"/>
-      <c r="C188" s="44"/>
+      <c r="A188" s="33"/>
+      <c r="B188" s="34"/>
+      <c r="C188" s="35"/>
       <c r="D188" s="5" t="s">
         <v>471</v>
       </c>
@@ -6918,19 +6918,19 @@
       <c r="F188" s="5" t="s">
         <v>470</v>
       </c>
-      <c r="G188" s="27"/>
+      <c r="G188" s="36"/>
       <c r="H188" s="15" t="s">
         <v>474</v>
       </c>
     </row>
     <row r="189" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A189" s="33">
+      <c r="A189" s="32">
         <v>71</v>
       </c>
-      <c r="B189" s="30" t="s">
+      <c r="B189" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="C189" s="44" t="s">
+      <c r="C189" s="35" t="s">
         <v>14</v>
       </c>
       <c r="D189" s="5" t="s">
@@ -6942,7 +6942,7 @@
       <c r="F189" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="G189" s="27" t="s">
+      <c r="G189" s="36" t="s">
         <v>587</v>
       </c>
       <c r="H189" s="15" t="s">
@@ -6950,9 +6950,9 @@
       </c>
     </row>
     <row r="190" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A190" s="34"/>
-      <c r="B190" s="30"/>
-      <c r="C190" s="44"/>
+      <c r="A190" s="33"/>
+      <c r="B190" s="34"/>
+      <c r="C190" s="35"/>
       <c r="D190" s="5" t="s">
         <v>88</v>
       </c>
@@ -6962,19 +6962,19 @@
       <c r="F190" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="G190" s="27"/>
+      <c r="G190" s="36"/>
       <c r="H190" s="15" t="s">
         <v>440</v>
       </c>
     </row>
     <row r="191" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A191" s="33">
+      <c r="A191" s="32">
         <v>72</v>
       </c>
-      <c r="B191" s="30" t="s">
+      <c r="B191" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="C191" s="44" t="s">
+      <c r="C191" s="35" t="s">
         <v>14</v>
       </c>
       <c r="D191" s="5" t="s">
@@ -6986,15 +6986,15 @@
       <c r="F191" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="G191" s="27"/>
+      <c r="G191" s="36"/>
       <c r="H191" s="15" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="192" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A192" s="34"/>
-      <c r="B192" s="30"/>
-      <c r="C192" s="44"/>
+      <c r="A192" s="33"/>
+      <c r="B192" s="34"/>
+      <c r="C192" s="35"/>
       <c r="D192" s="5" t="s">
         <v>191</v>
       </c>
@@ -7004,19 +7004,19 @@
       <c r="F192" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="G192" s="27"/>
+      <c r="G192" s="36"/>
       <c r="H192" s="15" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="193" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A193" s="33">
+      <c r="A193" s="32">
         <v>73</v>
       </c>
-      <c r="B193" s="30" t="s">
+      <c r="B193" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="C193" s="28" t="s">
+      <c r="C193" s="25" t="s">
         <v>14</v>
       </c>
       <c r="D193" s="5" t="s">
@@ -7028,7 +7028,7 @@
       <c r="F193" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="G193" s="27" t="s">
+      <c r="G193" s="36" t="s">
         <v>218</v>
       </c>
       <c r="H193" s="15" t="s">
@@ -7036,9 +7036,9 @@
       </c>
     </row>
     <row r="194" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A194" s="34"/>
-      <c r="B194" s="30"/>
-      <c r="C194" s="28"/>
+      <c r="A194" s="33"/>
+      <c r="B194" s="34"/>
+      <c r="C194" s="25"/>
       <c r="D194" s="5" t="s">
         <v>132</v>
       </c>
@@ -7048,19 +7048,19 @@
       <c r="F194" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="G194" s="27"/>
+      <c r="G194" s="36"/>
       <c r="H194" s="15" t="s">
         <v>442</v>
       </c>
     </row>
     <row r="195" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A195" s="33">
+      <c r="A195" s="32">
         <v>74</v>
       </c>
-      <c r="B195" s="30" t="s">
+      <c r="B195" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="C195" s="28" t="s">
+      <c r="C195" s="25" t="s">
         <v>14</v>
       </c>
       <c r="D195" s="5" t="s">
@@ -7072,7 +7072,7 @@
       <c r="F195" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="G195" s="27" t="s">
+      <c r="G195" s="36" t="s">
         <v>143</v>
       </c>
       <c r="H195" s="15" t="s">
@@ -7080,9 +7080,9 @@
       </c>
     </row>
     <row r="196" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A196" s="34"/>
-      <c r="B196" s="30"/>
-      <c r="C196" s="28"/>
+      <c r="A196" s="33"/>
+      <c r="B196" s="34"/>
+      <c r="C196" s="25"/>
       <c r="D196" s="5" t="s">
         <v>110</v>
       </c>
@@ -7092,19 +7092,19 @@
       <c r="F196" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="G196" s="27"/>
+      <c r="G196" s="36"/>
       <c r="H196" s="15" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="197" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A197" s="35">
+      <c r="A197" s="41">
         <v>75</v>
       </c>
-      <c r="B197" s="32" t="s">
+      <c r="B197" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="C197" s="28" t="s">
+      <c r="C197" s="25" t="s">
         <v>89</v>
       </c>
       <c r="D197" s="5" t="s">
@@ -7116,7 +7116,7 @@
       <c r="F197" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="G197" s="27" t="s">
+      <c r="G197" s="36" t="s">
         <v>626</v>
       </c>
       <c r="H197" s="15" t="s">
@@ -7124,9 +7124,9 @@
       </c>
     </row>
     <row r="198" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A198" s="36"/>
-      <c r="B198" s="32"/>
-      <c r="C198" s="28"/>
+      <c r="A198" s="42"/>
+      <c r="B198" s="38"/>
+      <c r="C198" s="25"/>
       <c r="D198" s="5" t="s">
         <v>95</v>
       </c>
@@ -7136,19 +7136,19 @@
       <c r="F198" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="G198" s="27"/>
+      <c r="G198" s="36"/>
       <c r="H198" s="15" t="s">
         <v>466</v>
       </c>
     </row>
     <row r="199" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A199" s="33">
+      <c r="A199" s="32">
         <v>76</v>
       </c>
-      <c r="B199" s="32" t="s">
+      <c r="B199" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="C199" s="28" t="s">
+      <c r="C199" s="25" t="s">
         <v>89</v>
       </c>
       <c r="D199" s="5" t="s">
@@ -7160,7 +7160,7 @@
       <c r="F199" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="G199" s="27" t="s">
+      <c r="G199" s="36" t="s">
         <v>225</v>
       </c>
       <c r="H199" s="15" t="s">
@@ -7168,9 +7168,9 @@
       </c>
     </row>
     <row r="200" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A200" s="34"/>
-      <c r="B200" s="32"/>
-      <c r="C200" s="28"/>
+      <c r="A200" s="33"/>
+      <c r="B200" s="38"/>
+      <c r="C200" s="25"/>
       <c r="D200" s="5" t="s">
         <v>107</v>
       </c>
@@ -7180,19 +7180,19 @@
       <c r="F200" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="G200" s="27"/>
+      <c r="G200" s="36"/>
       <c r="H200" s="15" t="s">
         <v>468</v>
       </c>
     </row>
     <row r="201" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A201" s="35">
+      <c r="A201" s="41">
         <v>77</v>
       </c>
-      <c r="B201" s="32" t="s">
+      <c r="B201" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="C201" s="28" t="s">
+      <c r="C201" s="25" t="s">
         <v>89</v>
       </c>
       <c r="D201" s="5" t="s">
@@ -7204,7 +7204,7 @@
       <c r="F201" s="5" t="s">
         <v>594</v>
       </c>
-      <c r="G201" s="27" t="s">
+      <c r="G201" s="36" t="s">
         <v>624</v>
       </c>
       <c r="H201" s="15" t="s">
@@ -7212,9 +7212,9 @@
       </c>
     </row>
     <row r="202" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A202" s="36"/>
-      <c r="B202" s="32"/>
-      <c r="C202" s="28"/>
+      <c r="A202" s="42"/>
+      <c r="B202" s="38"/>
+      <c r="C202" s="25"/>
       <c r="D202" s="5" t="s">
         <v>112</v>
       </c>
@@ -7224,19 +7224,19 @@
       <c r="F202" s="5" t="s">
         <v>595</v>
       </c>
-      <c r="G202" s="27"/>
+      <c r="G202" s="36"/>
       <c r="H202" s="15" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="203" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A203" s="33">
+      <c r="A203" s="32">
         <v>78</v>
       </c>
-      <c r="B203" s="32" t="s">
+      <c r="B203" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="C203" s="28" t="s">
+      <c r="C203" s="25" t="s">
         <v>89</v>
       </c>
       <c r="D203" s="5" t="s">
@@ -7248,15 +7248,15 @@
       <c r="F203" s="5" t="s">
         <v>632</v>
       </c>
-      <c r="G203" s="27"/>
+      <c r="G203" s="36"/>
       <c r="H203" s="15" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="204" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A204" s="34"/>
-      <c r="B204" s="32"/>
-      <c r="C204" s="28"/>
+      <c r="A204" s="33"/>
+      <c r="B204" s="38"/>
+      <c r="C204" s="25"/>
       <c r="D204" s="5" t="s">
         <v>91</v>
       </c>
@@ -7266,19 +7266,19 @@
       <c r="F204" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="G204" s="27"/>
+      <c r="G204" s="36"/>
       <c r="H204" s="15" t="s">
         <v>456</v>
       </c>
     </row>
     <row r="205" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A205" s="33">
+      <c r="A205" s="32">
         <v>79</v>
       </c>
-      <c r="B205" s="32" t="s">
+      <c r="B205" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="C205" s="28" t="s">
+      <c r="C205" s="25" t="s">
         <v>89</v>
       </c>
       <c r="D205" s="5" t="s">
@@ -7290,15 +7290,15 @@
       <c r="F205" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="G205" s="27"/>
+      <c r="G205" s="36"/>
       <c r="H205" s="15" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="206" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A206" s="34"/>
-      <c r="B206" s="32"/>
-      <c r="C206" s="28"/>
+      <c r="A206" s="33"/>
+      <c r="B206" s="38"/>
+      <c r="C206" s="25"/>
       <c r="D206" s="5" t="s">
         <v>93</v>
       </c>
@@ -7308,19 +7308,19 @@
       <c r="F206" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="G206" s="27"/>
+      <c r="G206" s="36"/>
       <c r="H206" s="15" t="s">
         <v>445</v>
       </c>
     </row>
     <row r="207" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A207" s="33">
+      <c r="A207" s="32">
         <v>80</v>
       </c>
-      <c r="B207" s="32" t="s">
+      <c r="B207" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="C207" s="28" t="s">
+      <c r="C207" s="25" t="s">
         <v>89</v>
       </c>
       <c r="D207" s="5" t="s">
@@ -7332,7 +7332,7 @@
       <c r="F207" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="G207" s="27" t="s">
+      <c r="G207" s="36" t="s">
         <v>245</v>
       </c>
       <c r="H207" s="15" t="s">
@@ -7340,9 +7340,9 @@
       </c>
     </row>
     <row r="208" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A208" s="34"/>
-      <c r="B208" s="32"/>
-      <c r="C208" s="28"/>
+      <c r="A208" s="33"/>
+      <c r="B208" s="38"/>
+      <c r="C208" s="25"/>
       <c r="D208" s="5" t="s">
         <v>105</v>
       </c>
@@ -7352,19 +7352,19 @@
       <c r="F208" s="5" t="s">
         <v>621</v>
       </c>
-      <c r="G208" s="27"/>
+      <c r="G208" s="36"/>
       <c r="H208" s="15" t="s">
         <v>446</v>
       </c>
     </row>
     <row r="209" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A209" s="35">
+      <c r="A209" s="41">
         <v>81</v>
       </c>
-      <c r="B209" s="32" t="s">
+      <c r="B209" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="C209" s="28" t="s">
+      <c r="C209" s="25" t="s">
         <v>89</v>
       </c>
       <c r="D209" s="5" t="s">
@@ -7374,9 +7374,9 @@
         <v>1</v>
       </c>
       <c r="F209" s="5" t="s">
-        <v>658</v>
-      </c>
-      <c r="G209" s="27" t="s">
+        <v>655</v>
+      </c>
+      <c r="G209" s="36" t="s">
         <v>622</v>
       </c>
       <c r="H209" s="15" t="s">
@@ -7384,9 +7384,9 @@
       </c>
     </row>
     <row r="210" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A210" s="36"/>
-      <c r="B210" s="32"/>
-      <c r="C210" s="28"/>
+      <c r="A210" s="42"/>
+      <c r="B210" s="38"/>
+      <c r="C210" s="25"/>
       <c r="D210" s="5" t="s">
         <v>99</v>
       </c>
@@ -7394,21 +7394,21 @@
         <v>1</v>
       </c>
       <c r="F210" s="5" t="s">
-        <v>659</v>
-      </c>
-      <c r="G210" s="27"/>
+        <v>656</v>
+      </c>
+      <c r="G210" s="36"/>
       <c r="H210" s="15" t="s">
         <v>450</v>
       </c>
     </row>
     <row r="211" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A211" s="33">
+      <c r="A211" s="32">
         <v>82</v>
       </c>
-      <c r="B211" s="49" t="s">
+      <c r="B211" s="44" t="s">
         <v>29</v>
       </c>
-      <c r="C211" s="28" t="s">
+      <c r="C211" s="25" t="s">
         <v>89</v>
       </c>
       <c r="D211" s="5" t="s">
@@ -7420,15 +7420,15 @@
       <c r="F211" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="G211" s="27"/>
+      <c r="G211" s="36"/>
       <c r="H211" s="15" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="212" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A212" s="34"/>
-      <c r="B212" s="50"/>
-      <c r="C212" s="28"/>
+      <c r="A212" s="33"/>
+      <c r="B212" s="45"/>
+      <c r="C212" s="25"/>
       <c r="D212" s="5" t="s">
         <v>179</v>
       </c>
@@ -7438,19 +7438,19 @@
       <c r="F212" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="G212" s="27"/>
+      <c r="G212" s="36"/>
       <c r="H212" s="15" t="s">
         <v>447</v>
       </c>
     </row>
     <row r="213" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A213" s="33">
+      <c r="A213" s="32">
         <v>83</v>
       </c>
-      <c r="B213" s="30" t="s">
+      <c r="B213" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="C213" s="28" t="s">
+      <c r="C213" s="25" t="s">
         <v>89</v>
       </c>
       <c r="D213" s="5" t="s">
@@ -7462,7 +7462,7 @@
       <c r="F213" s="5" t="s">
         <v>586</v>
       </c>
-      <c r="G213" s="27" t="s">
+      <c r="G213" s="36" t="s">
         <v>625</v>
       </c>
       <c r="H213" s="15" t="s">
@@ -7470,9 +7470,9 @@
       </c>
     </row>
     <row r="214" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A214" s="34"/>
-      <c r="B214" s="30"/>
-      <c r="C214" s="28"/>
+      <c r="A214" s="33"/>
+      <c r="B214" s="34"/>
+      <c r="C214" s="25"/>
       <c r="D214" s="5" t="s">
         <v>138</v>
       </c>
@@ -7482,19 +7482,19 @@
       <c r="F214" s="5" t="s">
         <v>593</v>
       </c>
-      <c r="G214" s="27"/>
+      <c r="G214" s="36"/>
       <c r="H214" s="15" t="s">
         <v>448</v>
       </c>
     </row>
     <row r="215" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A215" s="33">
+      <c r="A215" s="32">
         <v>84</v>
       </c>
-      <c r="B215" s="30" t="s">
+      <c r="B215" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="C215" s="28" t="s">
+      <c r="C215" s="25" t="s">
         <v>89</v>
       </c>
       <c r="D215" s="5" t="s">
@@ -7506,7 +7506,7 @@
       <c r="F215" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="G215" s="27" t="s">
+      <c r="G215" s="36" t="s">
         <v>309</v>
       </c>
       <c r="H215" s="15" t="s">
@@ -7514,9 +7514,9 @@
       </c>
     </row>
     <row r="216" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A216" s="34"/>
-      <c r="B216" s="30"/>
-      <c r="C216" s="28"/>
+      <c r="A216" s="33"/>
+      <c r="B216" s="34"/>
+      <c r="C216" s="25"/>
       <c r="D216" s="5" t="s">
         <v>97</v>
       </c>
@@ -7526,19 +7526,19 @@
       <c r="F216" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="G216" s="27"/>
+      <c r="G216" s="36"/>
       <c r="H216" s="15" t="s">
         <v>449</v>
       </c>
     </row>
     <row r="217" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A217" s="33">
+      <c r="A217" s="32">
         <v>85</v>
       </c>
-      <c r="B217" s="30" t="s">
+      <c r="B217" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="C217" s="28" t="s">
+      <c r="C217" s="25" t="s">
         <v>89</v>
       </c>
       <c r="D217" s="5" t="s">
@@ -7550,15 +7550,15 @@
       <c r="F217" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="G217" s="27"/>
+      <c r="G217" s="36"/>
       <c r="H217" s="15" t="s">
         <v>383</v>
       </c>
     </row>
     <row r="218" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A218" s="34"/>
-      <c r="B218" s="30"/>
-      <c r="C218" s="28"/>
+      <c r="A218" s="33"/>
+      <c r="B218" s="34"/>
+      <c r="C218" s="25"/>
       <c r="D218" s="5" t="s">
         <v>101</v>
       </c>
@@ -7568,19 +7568,19 @@
       <c r="F218" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="G218" s="27"/>
+      <c r="G218" s="36"/>
       <c r="H218" s="15" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="219" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A219" s="33">
+      <c r="A219" s="32">
         <v>86</v>
       </c>
-      <c r="B219" s="30" t="s">
+      <c r="B219" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="C219" s="28" t="s">
+      <c r="C219" s="25" t="s">
         <v>89</v>
       </c>
       <c r="D219" s="5" t="s">
@@ -7592,15 +7592,15 @@
       <c r="F219" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="G219" s="27"/>
+      <c r="G219" s="36"/>
       <c r="H219" s="15" t="s">
         <v>475</v>
       </c>
     </row>
     <row r="220" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A220" s="34"/>
-      <c r="B220" s="30"/>
-      <c r="C220" s="28"/>
+      <c r="A220" s="33"/>
+      <c r="B220" s="34"/>
+      <c r="C220" s="25"/>
       <c r="D220" s="5" t="s">
         <v>153</v>
       </c>
@@ -7610,19 +7610,19 @@
       <c r="F220" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="G220" s="27"/>
+      <c r="G220" s="36"/>
       <c r="H220" s="15" t="s">
         <v>476</v>
       </c>
     </row>
     <row r="221" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A221" s="33">
+      <c r="A221" s="32">
         <v>87</v>
       </c>
-      <c r="B221" s="30" t="s">
+      <c r="B221" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="C221" s="31" t="s">
+      <c r="C221" s="43" t="s">
         <v>89</v>
       </c>
       <c r="D221" s="5" t="s">
@@ -7634,7 +7634,7 @@
       <c r="F221" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="G221" s="27" t="s">
+      <c r="G221" s="36" t="s">
         <v>623</v>
       </c>
       <c r="H221" s="15" t="s">
@@ -7642,9 +7642,9 @@
       </c>
     </row>
     <row r="222" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A222" s="34"/>
-      <c r="B222" s="30"/>
-      <c r="C222" s="31"/>
+      <c r="A222" s="33"/>
+      <c r="B222" s="34"/>
+      <c r="C222" s="43"/>
       <c r="D222" s="5" t="s">
         <v>103</v>
       </c>
@@ -7654,19 +7654,19 @@
       <c r="F222" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="G222" s="27"/>
+      <c r="G222" s="36"/>
       <c r="H222" s="15" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="223" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A223" s="33">
+      <c r="A223" s="32">
         <v>88</v>
       </c>
-      <c r="B223" s="30" t="s">
+      <c r="B223" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="C223" s="44" t="s">
+      <c r="C223" s="35" t="s">
         <v>89</v>
       </c>
       <c r="D223" s="5" t="s">
@@ -7678,15 +7678,15 @@
       <c r="F223" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="G223" s="27"/>
+      <c r="G223" s="36"/>
       <c r="H223" s="15" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="224" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A224" s="34"/>
-      <c r="B224" s="30"/>
-      <c r="C224" s="44"/>
+      <c r="A224" s="33"/>
+      <c r="B224" s="34"/>
+      <c r="C224" s="35"/>
       <c r="D224" s="5" t="s">
         <v>145</v>
       </c>
@@ -7696,7 +7696,7 @@
       <c r="F224" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="G224" s="27"/>
+      <c r="G224" s="36"/>
       <c r="H224" s="15" t="s">
         <v>453</v>
       </c>
@@ -7747,16 +7747,16 @@
       </c>
     </row>
     <row r="244" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A244" s="28" t="s">
+      <c r="A244" s="25" t="s">
         <v>640</v>
       </c>
-      <c r="B244" s="28"/>
-      <c r="C244" s="28"/>
-      <c r="D244" s="28"/>
-      <c r="E244" s="28"/>
-      <c r="F244" s="28"/>
-      <c r="G244" s="28"/>
-      <c r="H244" s="28"/>
+      <c r="B244" s="25"/>
+      <c r="C244" s="25"/>
+      <c r="D244" s="25"/>
+      <c r="E244" s="25"/>
+      <c r="F244" s="25"/>
+      <c r="G244" s="25"/>
+      <c r="H244" s="25"/>
     </row>
     <row r="245" spans="1:8" ht="25.7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A245" s="1" t="s">
@@ -7765,12 +7765,12 @@
       <c r="B245" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="C245" s="37" t="s">
+      <c r="C245" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="D245" s="38"/>
-      <c r="E245" s="38"/>
-      <c r="F245" s="39"/>
+      <c r="D245" s="27"/>
+      <c r="E245" s="27"/>
+      <c r="F245" s="28"/>
       <c r="G245" s="1" t="s">
         <v>3</v>
       </c>
@@ -7785,32 +7785,32 @@
       <c r="B246" s="23" t="s">
         <v>489</v>
       </c>
-      <c r="C246" s="24" t="s">
-        <v>650</v>
-      </c>
-      <c r="D246" s="25"/>
-      <c r="E246" s="25"/>
-      <c r="F246" s="26"/>
+      <c r="C246" s="29" t="s">
+        <v>649</v>
+      </c>
+      <c r="D246" s="30"/>
+      <c r="E246" s="30"/>
+      <c r="F246" s="31"/>
       <c r="G246" s="4" t="s">
-        <v>649</v>
+        <v>657</v>
       </c>
       <c r="H246" s="16" t="s">
         <v>647</v>
       </c>
     </row>
     <row r="247" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A247" s="51" t="s">
+      <c r="A247" s="24" t="s">
         <v>641</v>
       </c>
       <c r="B247" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="C247" s="24" t="s">
+      <c r="C247" s="29" t="s">
         <v>645</v>
       </c>
-      <c r="D247" s="25"/>
-      <c r="E247" s="25"/>
-      <c r="F247" s="26"/>
+      <c r="D247" s="30"/>
+      <c r="E247" s="30"/>
+      <c r="F247" s="31"/>
       <c r="G247" s="4" t="s">
         <v>644</v>
       </c>
@@ -7819,46 +7819,367 @@
       </c>
     </row>
     <row r="252" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A252" s="28" t="s">
+      <c r="A252" s="25" t="s">
         <v>642</v>
       </c>
-      <c r="B252" s="28"/>
-      <c r="C252" s="28"/>
-      <c r="D252" s="28"/>
-      <c r="E252" s="28"/>
-      <c r="F252" s="28"/>
-      <c r="G252" s="28"/>
-      <c r="H252" s="28"/>
+      <c r="B252" s="25"/>
+      <c r="C252" s="25"/>
+      <c r="D252" s="25"/>
+      <c r="E252" s="25"/>
+      <c r="F252" s="25"/>
+      <c r="G252" s="25"/>
+      <c r="H252" s="25"/>
     </row>
     <row r="253" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A253" s="28" t="s">
+      <c r="A253" s="25" t="s">
         <v>643</v>
       </c>
-      <c r="B253" s="28"/>
-      <c r="C253" s="28"/>
-      <c r="D253" s="28"/>
-      <c r="E253" s="28"/>
-      <c r="F253" s="28"/>
-      <c r="G253" s="28"/>
-      <c r="H253" s="28"/>
+      <c r="B253" s="25"/>
+      <c r="C253" s="25"/>
+      <c r="D253" s="25"/>
+      <c r="E253" s="25"/>
+      <c r="F253" s="25"/>
+      <c r="G253" s="25"/>
+      <c r="H253" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="384">
-    <mergeCell ref="A244:H244"/>
-    <mergeCell ref="A252:H252"/>
-    <mergeCell ref="A253:H253"/>
-    <mergeCell ref="C245:F245"/>
-    <mergeCell ref="C246:F246"/>
-    <mergeCell ref="C247:F247"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="G57:G58"/>
+    <mergeCell ref="G59:G60"/>
+    <mergeCell ref="C207:C208"/>
+    <mergeCell ref="B61:B62"/>
+    <mergeCell ref="C63:C64"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="G87:G88"/>
+    <mergeCell ref="C89:C90"/>
+    <mergeCell ref="G129:G130"/>
+    <mergeCell ref="C129:C130"/>
+    <mergeCell ref="G143:G144"/>
+    <mergeCell ref="B161:B162"/>
+    <mergeCell ref="C161:C162"/>
+    <mergeCell ref="B137:B138"/>
+    <mergeCell ref="G153:G154"/>
+    <mergeCell ref="G157:G158"/>
+    <mergeCell ref="C155:C156"/>
+    <mergeCell ref="C141:C142"/>
+    <mergeCell ref="G119:G120"/>
+    <mergeCell ref="G113:G114"/>
+    <mergeCell ref="A57:A58"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="C57:C58"/>
+    <mergeCell ref="A61:A62"/>
+    <mergeCell ref="C61:C62"/>
+    <mergeCell ref="A63:A64"/>
+    <mergeCell ref="B63:B64"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="B59:B60"/>
+    <mergeCell ref="C59:C60"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="A46:H46"/>
+    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="A40:H40"/>
+    <mergeCell ref="G49:G50"/>
+    <mergeCell ref="G51:G52"/>
+    <mergeCell ref="G53:G54"/>
+    <mergeCell ref="G55:G56"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="C51:C52"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="C53:C54"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="A123:A124"/>
+    <mergeCell ref="B123:B124"/>
+    <mergeCell ref="A117:A118"/>
+    <mergeCell ref="A133:A134"/>
+    <mergeCell ref="B133:B134"/>
+    <mergeCell ref="C133:C134"/>
+    <mergeCell ref="G213:G214"/>
+    <mergeCell ref="C117:C118"/>
+    <mergeCell ref="B117:B118"/>
+    <mergeCell ref="C123:C124"/>
+    <mergeCell ref="A151:A152"/>
+    <mergeCell ref="B151:B152"/>
+    <mergeCell ref="C151:C152"/>
+    <mergeCell ref="A145:A146"/>
+    <mergeCell ref="B145:B146"/>
+    <mergeCell ref="C145:C146"/>
+    <mergeCell ref="B149:B150"/>
+    <mergeCell ref="C149:C150"/>
+    <mergeCell ref="G149:G150"/>
+    <mergeCell ref="G159:G160"/>
+    <mergeCell ref="A165:A166"/>
+    <mergeCell ref="A161:A162"/>
+    <mergeCell ref="A187:A188"/>
+    <mergeCell ref="A189:A190"/>
+    <mergeCell ref="B189:B190"/>
+    <mergeCell ref="G181:G182"/>
+    <mergeCell ref="C189:C190"/>
+    <mergeCell ref="G187:G188"/>
+    <mergeCell ref="B187:B188"/>
+    <mergeCell ref="C171:C172"/>
+    <mergeCell ref="C157:C158"/>
+    <mergeCell ref="G155:G156"/>
+    <mergeCell ref="A155:A156"/>
+    <mergeCell ref="B155:B156"/>
+    <mergeCell ref="A173:A174"/>
+    <mergeCell ref="B173:B174"/>
+    <mergeCell ref="C173:C174"/>
+    <mergeCell ref="G173:G174"/>
+    <mergeCell ref="B157:B158"/>
+    <mergeCell ref="C185:C186"/>
+    <mergeCell ref="A157:A158"/>
+    <mergeCell ref="G185:G186"/>
+    <mergeCell ref="A181:A182"/>
+    <mergeCell ref="B181:B182"/>
+    <mergeCell ref="C167:C168"/>
+    <mergeCell ref="G165:G166"/>
+    <mergeCell ref="A183:A184"/>
+    <mergeCell ref="G161:G162"/>
+    <mergeCell ref="C179:C180"/>
+    <mergeCell ref="G177:G178"/>
+    <mergeCell ref="A175:A176"/>
+    <mergeCell ref="B131:B132"/>
+    <mergeCell ref="C131:C132"/>
+    <mergeCell ref="B153:B154"/>
+    <mergeCell ref="C153:C154"/>
+    <mergeCell ref="G151:G152"/>
+    <mergeCell ref="G171:G172"/>
+    <mergeCell ref="B175:B176"/>
+    <mergeCell ref="C175:C176"/>
+    <mergeCell ref="B171:B172"/>
+    <mergeCell ref="A167:A168"/>
+    <mergeCell ref="G169:G170"/>
+    <mergeCell ref="G175:G176"/>
+    <mergeCell ref="G141:G142"/>
+    <mergeCell ref="A169:A170"/>
+    <mergeCell ref="B169:B170"/>
+    <mergeCell ref="C169:C170"/>
+    <mergeCell ref="G167:G168"/>
+    <mergeCell ref="A171:A172"/>
+    <mergeCell ref="A179:A180"/>
+    <mergeCell ref="B179:B180"/>
+    <mergeCell ref="A135:A136"/>
+    <mergeCell ref="B135:B136"/>
+    <mergeCell ref="C135:C136"/>
+    <mergeCell ref="G147:G148"/>
+    <mergeCell ref="A149:A150"/>
+    <mergeCell ref="A159:A160"/>
+    <mergeCell ref="B159:B160"/>
+    <mergeCell ref="C159:C160"/>
+    <mergeCell ref="G127:G128"/>
+    <mergeCell ref="A153:A154"/>
+    <mergeCell ref="A137:A138"/>
+    <mergeCell ref="G139:G140"/>
+    <mergeCell ref="G125:G126"/>
+    <mergeCell ref="A127:A128"/>
+    <mergeCell ref="B127:B128"/>
+    <mergeCell ref="B147:B148"/>
+    <mergeCell ref="C147:C148"/>
+    <mergeCell ref="G145:G146"/>
+    <mergeCell ref="A143:A144"/>
+    <mergeCell ref="B143:B144"/>
+    <mergeCell ref="C143:C144"/>
+    <mergeCell ref="A139:A140"/>
+    <mergeCell ref="B139:B140"/>
+    <mergeCell ref="C139:C140"/>
+    <mergeCell ref="G135:G136"/>
+    <mergeCell ref="A131:A132"/>
+    <mergeCell ref="A129:A130"/>
+    <mergeCell ref="B129:B130"/>
+    <mergeCell ref="C127:C128"/>
+    <mergeCell ref="A141:A142"/>
+    <mergeCell ref="B141:B142"/>
+    <mergeCell ref="A147:A148"/>
+    <mergeCell ref="A125:A126"/>
+    <mergeCell ref="B125:B126"/>
+    <mergeCell ref="C125:C126"/>
+    <mergeCell ref="G97:G98"/>
+    <mergeCell ref="G83:G84"/>
+    <mergeCell ref="G91:G92"/>
+    <mergeCell ref="G81:G82"/>
+    <mergeCell ref="G89:G90"/>
+    <mergeCell ref="G99:G100"/>
+    <mergeCell ref="C137:C138"/>
+    <mergeCell ref="G137:G138"/>
+    <mergeCell ref="G115:G116"/>
+    <mergeCell ref="G107:G108"/>
+    <mergeCell ref="G109:G110"/>
+    <mergeCell ref="C109:C110"/>
+    <mergeCell ref="C101:C102"/>
+    <mergeCell ref="C113:C114"/>
+    <mergeCell ref="C111:C112"/>
+    <mergeCell ref="C115:C116"/>
+    <mergeCell ref="G121:G122"/>
+    <mergeCell ref="C121:C122"/>
+    <mergeCell ref="C81:C82"/>
+    <mergeCell ref="G131:G132"/>
+    <mergeCell ref="G105:G106"/>
+    <mergeCell ref="G95:G96"/>
+    <mergeCell ref="G101:G102"/>
+    <mergeCell ref="A109:A110"/>
+    <mergeCell ref="A113:A114"/>
+    <mergeCell ref="B113:B114"/>
+    <mergeCell ref="A111:A112"/>
+    <mergeCell ref="B111:B112"/>
+    <mergeCell ref="A115:A116"/>
+    <mergeCell ref="B115:B116"/>
+    <mergeCell ref="A121:A122"/>
+    <mergeCell ref="B121:B122"/>
+    <mergeCell ref="A101:A102"/>
+    <mergeCell ref="B101:B102"/>
+    <mergeCell ref="A107:A108"/>
+    <mergeCell ref="B107:B108"/>
+    <mergeCell ref="C107:C108"/>
+    <mergeCell ref="A103:A104"/>
+    <mergeCell ref="B109:B110"/>
+    <mergeCell ref="A97:A98"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="C99:C100"/>
+    <mergeCell ref="A93:A94"/>
+    <mergeCell ref="B93:B94"/>
+    <mergeCell ref="B103:B104"/>
+    <mergeCell ref="C103:C104"/>
+    <mergeCell ref="A95:A96"/>
+    <mergeCell ref="B95:B96"/>
+    <mergeCell ref="C95:C96"/>
+    <mergeCell ref="B97:B98"/>
+    <mergeCell ref="C97:C98"/>
+    <mergeCell ref="A81:A82"/>
+    <mergeCell ref="B89:B90"/>
+    <mergeCell ref="C85:C86"/>
+    <mergeCell ref="A85:A86"/>
+    <mergeCell ref="B85:B86"/>
+    <mergeCell ref="G79:G80"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="C93:C94"/>
+    <mergeCell ref="G93:G94"/>
+    <mergeCell ref="B81:B82"/>
+    <mergeCell ref="G67:G68"/>
+    <mergeCell ref="A71:A72"/>
+    <mergeCell ref="C71:C72"/>
+    <mergeCell ref="G71:G72"/>
+    <mergeCell ref="B71:B72"/>
+    <mergeCell ref="C65:C66"/>
+    <mergeCell ref="G73:G74"/>
+    <mergeCell ref="A75:A76"/>
+    <mergeCell ref="B75:B76"/>
+    <mergeCell ref="G75:G76"/>
+    <mergeCell ref="C75:C76"/>
+    <mergeCell ref="A73:A74"/>
+    <mergeCell ref="B73:B74"/>
+    <mergeCell ref="C73:C74"/>
+    <mergeCell ref="C223:C224"/>
+    <mergeCell ref="G221:G222"/>
+    <mergeCell ref="G197:G198"/>
+    <mergeCell ref="A223:A224"/>
+    <mergeCell ref="G219:G220"/>
+    <mergeCell ref="A209:A210"/>
+    <mergeCell ref="B209:B210"/>
+    <mergeCell ref="C209:C210"/>
+    <mergeCell ref="G223:G224"/>
+    <mergeCell ref="B223:B224"/>
+    <mergeCell ref="A221:A222"/>
+    <mergeCell ref="B221:B222"/>
+    <mergeCell ref="C221:C222"/>
+    <mergeCell ref="G217:G218"/>
+    <mergeCell ref="A211:A212"/>
+    <mergeCell ref="B211:B212"/>
+    <mergeCell ref="C211:C212"/>
+    <mergeCell ref="B213:B214"/>
+    <mergeCell ref="C213:C214"/>
+    <mergeCell ref="A207:A208"/>
+    <mergeCell ref="A219:A220"/>
+    <mergeCell ref="B219:B220"/>
+    <mergeCell ref="C219:C220"/>
+    <mergeCell ref="C217:C218"/>
+    <mergeCell ref="A213:A214"/>
+    <mergeCell ref="G211:G212"/>
+    <mergeCell ref="G195:G196"/>
+    <mergeCell ref="C181:C182"/>
+    <mergeCell ref="G179:G180"/>
+    <mergeCell ref="A163:A164"/>
+    <mergeCell ref="B163:B164"/>
+    <mergeCell ref="C163:C164"/>
+    <mergeCell ref="G189:G190"/>
+    <mergeCell ref="A177:A178"/>
+    <mergeCell ref="B177:B178"/>
+    <mergeCell ref="G163:G164"/>
+    <mergeCell ref="G199:G200"/>
+    <mergeCell ref="A197:A198"/>
+    <mergeCell ref="B197:B198"/>
+    <mergeCell ref="C197:C198"/>
+    <mergeCell ref="G193:G194"/>
+    <mergeCell ref="A185:A186"/>
+    <mergeCell ref="B185:B186"/>
+    <mergeCell ref="C187:C188"/>
+    <mergeCell ref="B183:B184"/>
+    <mergeCell ref="C183:C184"/>
+    <mergeCell ref="G183:G184"/>
+    <mergeCell ref="G191:G192"/>
+    <mergeCell ref="G215:G216"/>
+    <mergeCell ref="B215:B216"/>
+    <mergeCell ref="B207:B208"/>
+    <mergeCell ref="A105:A106"/>
+    <mergeCell ref="A217:A218"/>
+    <mergeCell ref="B217:B218"/>
+    <mergeCell ref="C215:C216"/>
+    <mergeCell ref="G207:G208"/>
+    <mergeCell ref="A205:A206"/>
+    <mergeCell ref="B205:B206"/>
+    <mergeCell ref="C205:C206"/>
+    <mergeCell ref="G205:G206"/>
+    <mergeCell ref="A203:A204"/>
+    <mergeCell ref="B203:B204"/>
+    <mergeCell ref="C203:C204"/>
+    <mergeCell ref="G203:G204"/>
+    <mergeCell ref="G209:G210"/>
+    <mergeCell ref="A215:A216"/>
+    <mergeCell ref="G111:G112"/>
+    <mergeCell ref="G123:G124"/>
+    <mergeCell ref="B165:B166"/>
+    <mergeCell ref="C165:C166"/>
+    <mergeCell ref="B167:B168"/>
+    <mergeCell ref="C177:C178"/>
+    <mergeCell ref="A201:A202"/>
+    <mergeCell ref="B201:B202"/>
+    <mergeCell ref="C201:C202"/>
+    <mergeCell ref="A83:A84"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="G63:G64"/>
+    <mergeCell ref="B105:B106"/>
+    <mergeCell ref="C105:C106"/>
+    <mergeCell ref="G103:G104"/>
+    <mergeCell ref="A69:A70"/>
+    <mergeCell ref="B69:B70"/>
+    <mergeCell ref="C69:C70"/>
+    <mergeCell ref="G69:G70"/>
+    <mergeCell ref="A89:A90"/>
+    <mergeCell ref="G65:G66"/>
+    <mergeCell ref="A67:A68"/>
+    <mergeCell ref="B67:B68"/>
+    <mergeCell ref="B83:B84"/>
+    <mergeCell ref="C83:C84"/>
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="B87:B88"/>
+    <mergeCell ref="C91:C92"/>
+    <mergeCell ref="A65:A66"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C9:E9"/>
     <mergeCell ref="C10:E10"/>
@@ -7883,6 +8204,21 @@
     <mergeCell ref="B77:B78"/>
     <mergeCell ref="C77:C78"/>
     <mergeCell ref="G77:G78"/>
+    <mergeCell ref="A244:H244"/>
+    <mergeCell ref="A252:H252"/>
+    <mergeCell ref="A253:H253"/>
+    <mergeCell ref="C245:F245"/>
+    <mergeCell ref="C246:F246"/>
+    <mergeCell ref="C247:F247"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C26:F26"/>
     <mergeCell ref="G61:G62"/>
     <mergeCell ref="C67:C68"/>
     <mergeCell ref="G201:G202"/>
@@ -7892,342 +8228,6 @@
     <mergeCell ref="A199:A200"/>
     <mergeCell ref="B199:B200"/>
     <mergeCell ref="C199:C200"/>
-    <mergeCell ref="A201:A202"/>
-    <mergeCell ref="B201:B202"/>
-    <mergeCell ref="C201:C202"/>
-    <mergeCell ref="A83:A84"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="G63:G64"/>
-    <mergeCell ref="B105:B106"/>
-    <mergeCell ref="C105:C106"/>
-    <mergeCell ref="G103:G104"/>
-    <mergeCell ref="A69:A70"/>
-    <mergeCell ref="B69:B70"/>
-    <mergeCell ref="C69:C70"/>
-    <mergeCell ref="G69:G70"/>
-    <mergeCell ref="A89:A90"/>
-    <mergeCell ref="G215:G216"/>
-    <mergeCell ref="B215:B216"/>
-    <mergeCell ref="B207:B208"/>
-    <mergeCell ref="A105:A106"/>
-    <mergeCell ref="A217:A218"/>
-    <mergeCell ref="B217:B218"/>
-    <mergeCell ref="C215:C216"/>
-    <mergeCell ref="G207:G208"/>
-    <mergeCell ref="A205:A206"/>
-    <mergeCell ref="B205:B206"/>
-    <mergeCell ref="C205:C206"/>
-    <mergeCell ref="G205:G206"/>
-    <mergeCell ref="A203:A204"/>
-    <mergeCell ref="B203:B204"/>
-    <mergeCell ref="C203:C204"/>
-    <mergeCell ref="G203:G204"/>
-    <mergeCell ref="G209:G210"/>
-    <mergeCell ref="A215:A216"/>
-    <mergeCell ref="G111:G112"/>
-    <mergeCell ref="G123:G124"/>
-    <mergeCell ref="B165:B166"/>
-    <mergeCell ref="C165:C166"/>
-    <mergeCell ref="B167:B168"/>
-    <mergeCell ref="C177:C178"/>
-    <mergeCell ref="A213:A214"/>
-    <mergeCell ref="G211:G212"/>
-    <mergeCell ref="G195:G196"/>
-    <mergeCell ref="C181:C182"/>
-    <mergeCell ref="G179:G180"/>
-    <mergeCell ref="A163:A164"/>
-    <mergeCell ref="B163:B164"/>
-    <mergeCell ref="C163:C164"/>
-    <mergeCell ref="G189:G190"/>
-    <mergeCell ref="A177:A178"/>
-    <mergeCell ref="B177:B178"/>
-    <mergeCell ref="G163:G164"/>
-    <mergeCell ref="C223:C224"/>
-    <mergeCell ref="G221:G222"/>
-    <mergeCell ref="G197:G198"/>
-    <mergeCell ref="A223:A224"/>
-    <mergeCell ref="G219:G220"/>
-    <mergeCell ref="A209:A210"/>
-    <mergeCell ref="B209:B210"/>
-    <mergeCell ref="C209:C210"/>
-    <mergeCell ref="G223:G224"/>
-    <mergeCell ref="B223:B224"/>
-    <mergeCell ref="A221:A222"/>
-    <mergeCell ref="B221:B222"/>
-    <mergeCell ref="C221:C222"/>
-    <mergeCell ref="G217:G218"/>
-    <mergeCell ref="A211:A212"/>
-    <mergeCell ref="B211:B212"/>
-    <mergeCell ref="C211:C212"/>
-    <mergeCell ref="B213:B214"/>
-    <mergeCell ref="C213:C214"/>
-    <mergeCell ref="A207:A208"/>
-    <mergeCell ref="A219:A220"/>
-    <mergeCell ref="B219:B220"/>
-    <mergeCell ref="C219:C220"/>
-    <mergeCell ref="C217:C218"/>
-    <mergeCell ref="G65:G66"/>
-    <mergeCell ref="A67:A68"/>
-    <mergeCell ref="B67:B68"/>
-    <mergeCell ref="B83:B84"/>
-    <mergeCell ref="C83:C84"/>
-    <mergeCell ref="A87:A88"/>
-    <mergeCell ref="B87:B88"/>
-    <mergeCell ref="C91:C92"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="G67:G68"/>
-    <mergeCell ref="A71:A72"/>
-    <mergeCell ref="C71:C72"/>
-    <mergeCell ref="G71:G72"/>
-    <mergeCell ref="B71:B72"/>
-    <mergeCell ref="C65:C66"/>
-    <mergeCell ref="G73:G74"/>
-    <mergeCell ref="A75:A76"/>
-    <mergeCell ref="B75:B76"/>
-    <mergeCell ref="A81:A82"/>
-    <mergeCell ref="B89:B90"/>
-    <mergeCell ref="C85:C86"/>
-    <mergeCell ref="A85:A86"/>
-    <mergeCell ref="B85:B86"/>
-    <mergeCell ref="G79:G80"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="C93:C94"/>
-    <mergeCell ref="G93:G94"/>
-    <mergeCell ref="B109:B110"/>
-    <mergeCell ref="A97:A98"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:B100"/>
-    <mergeCell ref="C99:C100"/>
-    <mergeCell ref="A93:A94"/>
-    <mergeCell ref="B93:B94"/>
-    <mergeCell ref="B103:B104"/>
-    <mergeCell ref="C103:C104"/>
-    <mergeCell ref="G101:G102"/>
-    <mergeCell ref="A109:A110"/>
-    <mergeCell ref="A113:A114"/>
-    <mergeCell ref="B113:B114"/>
-    <mergeCell ref="A111:A112"/>
-    <mergeCell ref="B111:B112"/>
-    <mergeCell ref="A115:A116"/>
-    <mergeCell ref="B115:B116"/>
-    <mergeCell ref="A121:A122"/>
-    <mergeCell ref="B121:B122"/>
-    <mergeCell ref="B81:B82"/>
-    <mergeCell ref="A101:A102"/>
-    <mergeCell ref="B101:B102"/>
-    <mergeCell ref="A107:A108"/>
-    <mergeCell ref="A95:A96"/>
-    <mergeCell ref="B95:B96"/>
-    <mergeCell ref="C95:C96"/>
-    <mergeCell ref="B107:B108"/>
-    <mergeCell ref="C107:C108"/>
-    <mergeCell ref="A103:A104"/>
-    <mergeCell ref="B97:B98"/>
-    <mergeCell ref="C97:C98"/>
-    <mergeCell ref="G75:G76"/>
-    <mergeCell ref="G97:G98"/>
-    <mergeCell ref="G83:G84"/>
-    <mergeCell ref="G91:G92"/>
-    <mergeCell ref="G81:G82"/>
-    <mergeCell ref="G89:G90"/>
-    <mergeCell ref="G99:G100"/>
-    <mergeCell ref="C137:C138"/>
-    <mergeCell ref="G137:G138"/>
-    <mergeCell ref="G115:G116"/>
-    <mergeCell ref="G107:G108"/>
-    <mergeCell ref="G109:G110"/>
-    <mergeCell ref="C109:C110"/>
-    <mergeCell ref="C101:C102"/>
-    <mergeCell ref="C75:C76"/>
-    <mergeCell ref="C113:C114"/>
-    <mergeCell ref="C111:C112"/>
-    <mergeCell ref="C115:C116"/>
-    <mergeCell ref="G121:G122"/>
-    <mergeCell ref="C121:C122"/>
-    <mergeCell ref="C81:C82"/>
-    <mergeCell ref="G131:G132"/>
-    <mergeCell ref="G105:G106"/>
-    <mergeCell ref="G95:G96"/>
-    <mergeCell ref="G139:G140"/>
-    <mergeCell ref="G125:G126"/>
-    <mergeCell ref="A127:A128"/>
-    <mergeCell ref="B127:B128"/>
-    <mergeCell ref="B147:B148"/>
-    <mergeCell ref="C147:C148"/>
-    <mergeCell ref="G145:G146"/>
-    <mergeCell ref="A143:A144"/>
-    <mergeCell ref="B143:B144"/>
-    <mergeCell ref="C143:C144"/>
-    <mergeCell ref="A139:A140"/>
-    <mergeCell ref="B139:B140"/>
-    <mergeCell ref="C139:C140"/>
-    <mergeCell ref="G135:G136"/>
-    <mergeCell ref="A131:A132"/>
-    <mergeCell ref="A129:A130"/>
-    <mergeCell ref="B129:B130"/>
-    <mergeCell ref="C127:C128"/>
-    <mergeCell ref="A141:A142"/>
-    <mergeCell ref="B141:B142"/>
-    <mergeCell ref="A147:A148"/>
-    <mergeCell ref="A125:A126"/>
-    <mergeCell ref="B125:B126"/>
-    <mergeCell ref="C125:C126"/>
-    <mergeCell ref="A135:A136"/>
-    <mergeCell ref="B135:B136"/>
-    <mergeCell ref="C135:C136"/>
-    <mergeCell ref="G147:G148"/>
-    <mergeCell ref="A149:A150"/>
-    <mergeCell ref="A159:A160"/>
-    <mergeCell ref="B159:B160"/>
-    <mergeCell ref="C159:C160"/>
-    <mergeCell ref="G127:G128"/>
-    <mergeCell ref="A153:A154"/>
-    <mergeCell ref="G161:G162"/>
-    <mergeCell ref="C179:C180"/>
-    <mergeCell ref="G177:G178"/>
-    <mergeCell ref="A175:A176"/>
-    <mergeCell ref="B131:B132"/>
-    <mergeCell ref="C131:C132"/>
-    <mergeCell ref="B153:B154"/>
-    <mergeCell ref="C153:C154"/>
-    <mergeCell ref="G151:G152"/>
-    <mergeCell ref="G171:G172"/>
-    <mergeCell ref="B175:B176"/>
-    <mergeCell ref="C175:C176"/>
-    <mergeCell ref="B171:B172"/>
-    <mergeCell ref="A167:A168"/>
-    <mergeCell ref="G169:G170"/>
-    <mergeCell ref="G175:G176"/>
-    <mergeCell ref="G141:G142"/>
-    <mergeCell ref="G199:G200"/>
-    <mergeCell ref="A197:A198"/>
-    <mergeCell ref="B197:B198"/>
-    <mergeCell ref="C197:C198"/>
-    <mergeCell ref="G193:G194"/>
-    <mergeCell ref="A169:A170"/>
-    <mergeCell ref="B169:B170"/>
-    <mergeCell ref="C169:C170"/>
-    <mergeCell ref="G167:G168"/>
-    <mergeCell ref="A171:A172"/>
-    <mergeCell ref="A185:A186"/>
-    <mergeCell ref="B185:B186"/>
-    <mergeCell ref="A179:A180"/>
-    <mergeCell ref="B179:B180"/>
-    <mergeCell ref="C187:C188"/>
-    <mergeCell ref="B183:B184"/>
-    <mergeCell ref="C183:C184"/>
-    <mergeCell ref="G183:G184"/>
-    <mergeCell ref="G191:G192"/>
-    <mergeCell ref="A189:A190"/>
-    <mergeCell ref="B189:B190"/>
-    <mergeCell ref="G181:G182"/>
-    <mergeCell ref="C189:C190"/>
-    <mergeCell ref="G187:G188"/>
-    <mergeCell ref="B187:B188"/>
-    <mergeCell ref="C171:C172"/>
-    <mergeCell ref="C157:C158"/>
-    <mergeCell ref="G155:G156"/>
-    <mergeCell ref="A155:A156"/>
-    <mergeCell ref="B155:B156"/>
-    <mergeCell ref="A173:A174"/>
-    <mergeCell ref="B173:B174"/>
-    <mergeCell ref="C173:C174"/>
-    <mergeCell ref="G173:G174"/>
-    <mergeCell ref="B157:B158"/>
-    <mergeCell ref="C185:C186"/>
-    <mergeCell ref="A157:A158"/>
-    <mergeCell ref="G185:G186"/>
-    <mergeCell ref="A181:A182"/>
-    <mergeCell ref="B181:B182"/>
-    <mergeCell ref="C167:C168"/>
-    <mergeCell ref="G165:G166"/>
-    <mergeCell ref="A183:A184"/>
-    <mergeCell ref="A137:A138"/>
-    <mergeCell ref="A123:A124"/>
-    <mergeCell ref="B123:B124"/>
-    <mergeCell ref="A117:A118"/>
-    <mergeCell ref="A133:A134"/>
-    <mergeCell ref="B133:B134"/>
-    <mergeCell ref="C133:C134"/>
-    <mergeCell ref="G213:G214"/>
-    <mergeCell ref="C117:C118"/>
-    <mergeCell ref="B117:B118"/>
-    <mergeCell ref="C123:C124"/>
-    <mergeCell ref="A151:A152"/>
-    <mergeCell ref="B151:B152"/>
-    <mergeCell ref="C151:C152"/>
-    <mergeCell ref="A145:A146"/>
-    <mergeCell ref="B145:B146"/>
-    <mergeCell ref="C145:C146"/>
-    <mergeCell ref="B149:B150"/>
-    <mergeCell ref="C149:C150"/>
-    <mergeCell ref="G149:G150"/>
-    <mergeCell ref="G159:G160"/>
-    <mergeCell ref="A165:A166"/>
-    <mergeCell ref="A161:A162"/>
-    <mergeCell ref="A187:A188"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="A46:H46"/>
-    <mergeCell ref="A47:H47"/>
-    <mergeCell ref="A40:H40"/>
-    <mergeCell ref="G49:G50"/>
-    <mergeCell ref="G51:G52"/>
-    <mergeCell ref="G53:G54"/>
-    <mergeCell ref="G55:G56"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="C51:C52"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="C53:C54"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="A73:A74"/>
-    <mergeCell ref="B73:B74"/>
-    <mergeCell ref="C73:C74"/>
-    <mergeCell ref="A57:A58"/>
-    <mergeCell ref="B57:B58"/>
-    <mergeCell ref="C57:C58"/>
-    <mergeCell ref="A61:A62"/>
-    <mergeCell ref="C61:C62"/>
-    <mergeCell ref="A63:A64"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="A59:A60"/>
-    <mergeCell ref="B59:B60"/>
-    <mergeCell ref="C59:C60"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="G57:G58"/>
-    <mergeCell ref="G59:G60"/>
-    <mergeCell ref="C207:C208"/>
-    <mergeCell ref="B61:B62"/>
-    <mergeCell ref="C63:C64"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="G87:G88"/>
-    <mergeCell ref="C89:C90"/>
-    <mergeCell ref="G129:G130"/>
-    <mergeCell ref="C129:C130"/>
-    <mergeCell ref="G143:G144"/>
-    <mergeCell ref="B161:B162"/>
-    <mergeCell ref="C161:C162"/>
-    <mergeCell ref="B137:B138"/>
-    <mergeCell ref="G153:G154"/>
-    <mergeCell ref="G157:G158"/>
-    <mergeCell ref="C155:C156"/>
-    <mergeCell ref="C141:C142"/>
-    <mergeCell ref="G119:G120"/>
-    <mergeCell ref="G113:G114"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/main/resources/InesModResources/杀戮尖塔自制--伊内丝v0.2.xlsx
+++ b/src/main/resources/InesModResources/杀戮尖塔自制--伊内丝v0.2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\myMod\InesMod\InesMod\src\main\resources\InesModResources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F851F601-FAF1-466F-B766-320FAE68BF67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E866DDC-F838-46C3-80AE-C1F319540ADE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{7A3E14A4-2175-4856-859A-887D335814F1}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="660">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="916" uniqueCount="664">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -275,13 +275,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>连战</t>
-  </si>
-  <si>
-    <t>连战+</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>武器储备</t>
   </si>
   <si>
@@ -811,14 +804,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>下一次手牌数不超过0时，抽2张牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>下一次手牌数不超过0时，获得1点能量。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>注意是消耗手牌</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -983,10 +968,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>替换初始遗物</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>虚实绊线</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1049,10 +1030,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>消耗手牌中所有技能牌，将相应数量的影哨加入手牌。消耗。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>本回合内，每次抽牌后需选择等量牌丢弃。抽2张牌。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1061,10 +1038,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>可以1张都不保留，即全扔</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>下一次出牌时，将其一张耗能为0的复制品加入抽牌堆。消耗。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1184,14 +1157,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>下一次攻击如果消耗了偷取，获得3点情报。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>下一次攻击如果消耗了偷取，获得4点情报。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>本回合内每丢弃1张牌，下回合开始时就获得1点情报。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1418,9 +1383,6 @@
     <t>Endless Night</t>
   </si>
   <si>
-    <t>Consecutive Battles</t>
-  </si>
-  <si>
     <t>Photographic Memory</t>
   </si>
   <si>
@@ -1617,9 +1579,6 @@
   </si>
   <si>
     <t>Endless Night+</t>
-  </si>
-  <si>
-    <t>Consecutive Battles+</t>
   </si>
   <si>
     <t>Photographic Memory+</t>
@@ -1990,22 +1949,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>自动打出，对所有敌人造成14点伤害2次。若无法自动打出则消耗。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自动打出，对所有敌人造成18点伤害2次。若无法自动打出则消耗。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>自动打出</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>此牌加入手牌后会立即消耗能量打出。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Auto Play</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2022,10 +1969,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>战斗开始时，获得1层偷取。你的回合开始时，获得1层偷取。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>从卡牌中获得的格挡提升25%，但打出攻击牌后会消耗影哨。回合开始时，失去1层隐匿并获得1层虚影。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2051,11 +1994,6 @@
   </si>
   <si>
     <t>造成8点伤害。向手牌中加入1张影哨。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>从卡牌中获得的格挡提升25%，但打出攻击牌后会消耗1张影哨。回合结束时，失去1层隐匿并获得1层虚影。
-虚影可抵挡一次攻击伤害或在回合开始时转为1点能量。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2149,14 +2087,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>下一次攻击如果消耗了偷取，额外给予2层易伤。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>下一次攻击如果消耗了偷取，额外给予3层易伤</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>遁入影中</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2287,10 +2217,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>本回合每次打出攻击牌，手牌中随机1张攻击牌在本场战斗中耗能-1。消耗。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>当前所有手牌在本回合的耗能-1。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2332,14 +2258,6 @@
   </si>
   <si>
     <t>下一张打出的攻击牌造成2倍伤害，随后失去所有格挡并结束你的回合。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>如果本回合你尚未出牌，造成10点伤害，抽1张牌。消耗。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>如果本回合你尚未出牌，造成10点伤害，抽2张牌。消耗。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2503,11 +2421,113 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>造成16点伤害。若不处于隐匿：消耗。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>造成12点伤害。若不处于隐匿：消耗。</t>
+    <t>造成11点伤害。若不处于隐匿，消耗。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成14点伤害。若不处于隐匿，消耗。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果本回合尚未出牌，造成10点伤害，抽1张牌。消耗。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果本回合尚未出牌，造成10点伤害，抽2张牌。消耗。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>下一次手牌数不超过1时，抽3张牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>下一次手牌数不超过1时，获得2点能量。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以1张都不保留，即全扔
+如果实现不了本回合保留，就改成“获得保留”</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>潜伏。攻击如果消耗了偷取，获得2点情报。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>潜伏。攻击如果消耗了偷取，获得3点情报。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>潜伏。攻击如果消耗了偷取，给予1点易伤。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>潜伏。攻击如果消耗了偷取，给予2点易伤。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>潜伏</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>此牌在手牌时，生效其效果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lurk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>潜伏。每次打出攻击牌，手牌中随机攻击牌在本场战斗中耗能-1。虚无。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一个接一个</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>One by one</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>One by one+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一个接一个+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>潜伏。每次打出攻击牌，手牌中随机攻击牌在本场战斗中耗能-1。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>潜伏。打出手牌时将其消耗，将1张影哨加入手牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>潜伏。打出手牌时将其消耗，将2张影哨加入手牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>从卡牌中获得的格挡提升50%，但打出攻击牌后会消耗1张影哨。回合结束时，失去1层隐匿并获得1层虚影。
+虚影可抵挡一次攻击伤害或在回合开始时转为1点能量。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>替换无锋绣针。战斗开始时，获得1层偷取。你的回合开始时，获得1层偷取。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动打出。对所有敌人造成14点伤害2次。若无法自动打出则消耗。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>此牌加入手牌后，立即尝试消耗能量打出。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动打出。对所有敌人造成12点伤害2次。若无法自动打出则消耗。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2785,7 +2805,37 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2797,55 +2847,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2854,16 +2865,25 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3187,7 +3207,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42CD751D-9911-4397-9269-1058B93A73AF}">
-  <dimension ref="A1:L253"/>
+  <dimension ref="A1:L254"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="3" width="9.1328125" customWidth="1"/>
@@ -3199,10 +3219,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="25" t="s">
-        <v>314</v>
-      </c>
-      <c r="B1" s="25"/>
+      <c r="A1" s="29" t="s">
+        <v>305</v>
+      </c>
+      <c r="B1" s="29"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -3210,10 +3230,10 @@
     </row>
     <row r="2" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="7" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="12"/>
@@ -3224,10 +3244,10 @@
     </row>
     <row r="3" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -3254,29 +3274,29 @@
       <c r="B6" s="2"/>
     </row>
     <row r="8" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="26" t="s">
-        <v>108</v>
-      </c>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="28"/>
+      <c r="A8" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="B8" s="37"/>
+      <c r="C8" s="37"/>
+      <c r="D8" s="37"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="38"/>
     </row>
     <row r="9" spans="1:8" ht="25.7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="C9" s="26" t="s">
-        <v>240</v>
-      </c>
-      <c r="D9" s="27"/>
-      <c r="E9" s="28"/>
+        <v>235</v>
+      </c>
+      <c r="C9" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="D9" s="37"/>
+      <c r="E9" s="38"/>
       <c r="F9" s="8" t="s">
         <v>2</v>
       </c>
@@ -3284,144 +3304,142 @@
         <v>3</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="19" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="27" t="s">
-        <v>242</v>
-      </c>
-      <c r="D10" s="27"/>
-      <c r="E10" s="28"/>
+      <c r="C10" s="37" t="s">
+        <v>238</v>
+      </c>
+      <c r="D10" s="37"/>
+      <c r="E10" s="38"/>
       <c r="F10" s="9" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="G10" s="10"/>
       <c r="H10" s="17" t="s">
-        <v>530</v>
+        <v>519</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="C11" s="26" t="s">
-        <v>246</v>
-      </c>
-      <c r="D11" s="27"/>
-      <c r="E11" s="28"/>
+        <v>255</v>
+      </c>
+      <c r="C11" s="36" t="s">
+        <v>242</v>
+      </c>
+      <c r="D11" s="37"/>
+      <c r="E11" s="38"/>
       <c r="F11" s="9" t="s">
-        <v>542</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>248</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="G11" s="10"/>
       <c r="H11" s="17" t="s">
-        <v>531</v>
+        <v>520</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="C12" s="26" t="s">
-        <v>499</v>
-      </c>
-      <c r="D12" s="27"/>
-      <c r="E12" s="28"/>
+        <v>255</v>
+      </c>
+      <c r="C12" s="36" t="s">
+        <v>488</v>
+      </c>
+      <c r="D12" s="37"/>
+      <c r="E12" s="38"/>
       <c r="F12" s="9" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="G12" s="10"/>
       <c r="H12" s="17" t="s">
-        <v>481</v>
+        <v>470</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="C13" s="29" t="s">
-        <v>480</v>
-      </c>
-      <c r="D13" s="27"/>
-      <c r="E13" s="28"/>
+        <v>237</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>469</v>
+      </c>
+      <c r="D13" s="37"/>
+      <c r="E13" s="38"/>
       <c r="F13" s="9" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="G13" s="10"/>
       <c r="H13" s="17" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="C14" s="27" t="s">
-        <v>310</v>
-      </c>
-      <c r="D14" s="27"/>
-      <c r="E14" s="28"/>
+        <v>237</v>
+      </c>
+      <c r="C14" s="37" t="s">
+        <v>301</v>
+      </c>
+      <c r="D14" s="37"/>
+      <c r="E14" s="38"/>
       <c r="F14" s="9" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="G14" s="10"/>
       <c r="H14" s="17" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="16" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="17" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="B18" s="25"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="25"/>
-      <c r="H18" s="25"/>
+      <c r="A18" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="B18" s="29"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="29"/>
+      <c r="G18" s="29"/>
+      <c r="H18" s="29"/>
     </row>
     <row r="19" spans="1:8" ht="25.7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>490</v>
-      </c>
-      <c r="C19" s="26" t="s">
+        <v>479</v>
+      </c>
+      <c r="C19" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="D19" s="27"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="28"/>
+      <c r="D19" s="37"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="38"/>
       <c r="G19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
@@ -3429,192 +3447,192 @@
         <v>8</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="C20" s="29" t="s">
-        <v>635</v>
-      </c>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="31"/>
+        <v>478</v>
+      </c>
+      <c r="C20" s="25" t="s">
+        <v>614</v>
+      </c>
+      <c r="D20" s="26"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="27"/>
       <c r="G20" s="5" t="s">
-        <v>548</v>
+        <v>533</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>478</v>
+        <v>467</v>
       </c>
     </row>
     <row r="21" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="19" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="C21" s="29" t="s">
-        <v>550</v>
-      </c>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="31"/>
+        <v>478</v>
+      </c>
+      <c r="C21" s="25" t="s">
+        <v>659</v>
+      </c>
+      <c r="D21" s="26"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="27"/>
       <c r="G21" s="5" t="s">
-        <v>547</v>
+        <v>532</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>479</v>
+        <v>468</v>
       </c>
     </row>
     <row r="22" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="19" t="s">
-        <v>544</v>
+        <v>529</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>491</v>
-      </c>
-      <c r="C22" s="29" t="s">
-        <v>551</v>
-      </c>
-      <c r="D22" s="30"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="31"/>
+        <v>480</v>
+      </c>
+      <c r="C22" s="25" t="s">
+        <v>535</v>
+      </c>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="27"/>
       <c r="G22" s="5" t="s">
-        <v>545</v>
+        <v>530</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>546</v>
+        <v>531</v>
       </c>
     </row>
     <row r="23" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="19" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="C23" s="29" t="s">
-        <v>569</v>
-      </c>
-      <c r="D23" s="30"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="31"/>
+        <v>478</v>
+      </c>
+      <c r="C23" s="25" t="s">
+        <v>553</v>
+      </c>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="27"/>
       <c r="G23" s="4" t="s">
-        <v>570</v>
+        <v>554</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>477</v>
+        <v>466</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="19" t="s">
-        <v>492</v>
+        <v>481</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>491</v>
-      </c>
-      <c r="C24" s="29" t="s">
-        <v>494</v>
-      </c>
-      <c r="D24" s="30"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="31"/>
+        <v>480</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>483</v>
+      </c>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="27"/>
       <c r="G24" s="5" t="s">
-        <v>596</v>
+        <v>578</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>516</v>
+        <v>505</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="20" t="s">
-        <v>493</v>
+        <v>482</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>491</v>
-      </c>
-      <c r="C25" s="29" t="s">
-        <v>495</v>
-      </c>
-      <c r="D25" s="30"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="31"/>
+        <v>480</v>
+      </c>
+      <c r="C25" s="25" t="s">
+        <v>484</v>
+      </c>
+      <c r="D25" s="26"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="27"/>
       <c r="G25" s="5" t="s">
-        <v>496</v>
+        <v>485</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>515</v>
+        <v>504</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="20" t="s">
-        <v>627</v>
+        <v>606</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>491</v>
-      </c>
-      <c r="C26" s="29" t="s">
-        <v>628</v>
-      </c>
-      <c r="D26" s="30"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="31"/>
+        <v>480</v>
+      </c>
+      <c r="C26" s="25" t="s">
+        <v>607</v>
+      </c>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="27"/>
       <c r="G26" s="4"/>
       <c r="H26" s="16" t="s">
-        <v>629</v>
+        <v>608</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="1" t="s">
-        <v>497</v>
+        <v>486</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>491</v>
-      </c>
-      <c r="C27" s="29" t="s">
-        <v>498</v>
-      </c>
-      <c r="D27" s="30"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="31"/>
+        <v>480</v>
+      </c>
+      <c r="C27" s="25" t="s">
+        <v>487</v>
+      </c>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="27"/>
       <c r="G27" s="4" t="s">
-        <v>597</v>
+        <v>579</v>
       </c>
       <c r="H27" s="16" t="s">
-        <v>500</v>
+        <v>489</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="29" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="1:8" ht="21.7" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="31" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="25" t="s">
-        <v>532</v>
-      </c>
-      <c r="B31" s="25"/>
-      <c r="C31" s="25"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="25"/>
-      <c r="F31" s="25"/>
-      <c r="G31" s="25"/>
-      <c r="H31" s="25"/>
+      <c r="A31" s="29" t="s">
+        <v>521</v>
+      </c>
+      <c r="B31" s="29"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="29"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="29"/>
+      <c r="H31" s="29"/>
     </row>
     <row r="32" spans="1:8" ht="25.7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>490</v>
-      </c>
-      <c r="C32" s="26" t="s">
+        <v>479</v>
+      </c>
+      <c r="C32" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="D32" s="27"/>
-      <c r="E32" s="27"/>
-      <c r="F32" s="28"/>
+      <c r="D32" s="37"/>
+      <c r="E32" s="37"/>
+      <c r="F32" s="38"/>
       <c r="G32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
@@ -3622,277 +3640,267 @@
         <v>8</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="C33" s="29" t="s">
-        <v>533</v>
-      </c>
-      <c r="D33" s="30"/>
-      <c r="E33" s="30"/>
-      <c r="F33" s="31"/>
+        <v>478</v>
+      </c>
+      <c r="C33" s="25" t="s">
+        <v>522</v>
+      </c>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="27"/>
       <c r="G33" s="5"/>
       <c r="H33" s="16" t="s">
-        <v>478</v>
+        <v>467</v>
       </c>
     </row>
     <row r="34" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="19" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="C34" s="29" t="s">
-        <v>543</v>
-      </c>
-      <c r="D34" s="30"/>
-      <c r="E34" s="30"/>
-      <c r="F34" s="31"/>
+        <v>478</v>
+      </c>
+      <c r="C34" s="25" t="s">
+        <v>528</v>
+      </c>
+      <c r="D34" s="26"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="27"/>
       <c r="G34" s="5"/>
       <c r="H34" s="16" t="s">
-        <v>479</v>
+        <v>468</v>
       </c>
     </row>
     <row r="35" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="19" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="C35" s="29" t="s">
-        <v>569</v>
-      </c>
-      <c r="D35" s="30"/>
-      <c r="E35" s="30"/>
-      <c r="F35" s="31"/>
+        <v>478</v>
+      </c>
+      <c r="C35" s="25" t="s">
+        <v>553</v>
+      </c>
+      <c r="D35" s="26"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="27"/>
       <c r="G35" s="5"/>
       <c r="H35" s="16" t="s">
-        <v>477</v>
+        <v>466</v>
       </c>
     </row>
     <row r="36" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="1" t="s">
-        <v>536</v>
+      <c r="A36" s="19" t="s">
+        <v>648</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="C36" s="29" t="s">
-        <v>537</v>
-      </c>
-      <c r="D36" s="30"/>
-      <c r="E36" s="30"/>
-      <c r="F36" s="31"/>
+        <v>478</v>
+      </c>
+      <c r="C36" s="25" t="s">
+        <v>649</v>
+      </c>
+      <c r="D36" s="26"/>
+      <c r="E36" s="26"/>
+      <c r="F36" s="27"/>
       <c r="G36" s="5"/>
       <c r="H36" s="16" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="C37" s="25" t="s">
+        <v>662</v>
+      </c>
+      <c r="D37" s="26"/>
+      <c r="E37" s="26"/>
+      <c r="F37" s="27"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="16" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="39" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="40" spans="1:8" s="3" customFormat="1" ht="23.35" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A40"/>
+      <c r="B40"/>
+      <c r="C40"/>
+      <c r="D40"/>
+      <c r="E40"/>
+      <c r="F40"/>
+      <c r="G40"/>
+      <c r="H40" s="11"/>
+    </row>
+    <row r="41" spans="1:8" s="3" customFormat="1" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A41" s="29" t="s">
+        <v>525</v>
+      </c>
+      <c r="B41" s="29"/>
+      <c r="C41" s="29"/>
+      <c r="D41" s="29"/>
+      <c r="E41" s="29"/>
+      <c r="F41" s="29"/>
+      <c r="G41" s="29"/>
+      <c r="H41" s="29"/>
+    </row>
+    <row r="42" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="22">
+        <v>1</v>
+      </c>
+      <c r="B43" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="G43" s="4"/>
+      <c r="H43" s="16" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="H44" s="2"/>
+    </row>
+    <row r="45" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F45" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="H45" s="2"/>
+    </row>
+    <row r="46" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="H46" s="2"/>
+    </row>
+    <row r="47" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A47" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="B47" s="29"/>
+      <c r="C47" s="29"/>
+      <c r="D47" s="29"/>
+      <c r="E47" s="29"/>
+      <c r="F47" s="29"/>
+      <c r="G47" s="29"/>
+      <c r="H47" s="29"/>
+    </row>
+    <row r="48" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="29" t="s">
         <v>538</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="38" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="39" spans="1:8" s="3" customFormat="1" ht="23.35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A39"/>
-      <c r="B39"/>
-      <c r="C39"/>
-      <c r="D39"/>
-      <c r="E39"/>
-      <c r="F39"/>
-      <c r="G39"/>
-      <c r="H39" s="11"/>
-    </row>
-    <row r="40" spans="1:8" s="3" customFormat="1" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="25" t="s">
-        <v>539</v>
-      </c>
-      <c r="B40" s="25"/>
-      <c r="C40" s="25"/>
-      <c r="D40" s="25"/>
-      <c r="E40" s="25"/>
-      <c r="F40" s="25"/>
-      <c r="G40" s="25"/>
-      <c r="H40" s="25"/>
-    </row>
-    <row r="41" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="1" t="s">
+      <c r="B48" s="29"/>
+      <c r="C48" s="29"/>
+      <c r="D48" s="29"/>
+      <c r="E48" s="29"/>
+      <c r="F48" s="29"/>
+      <c r="G48" s="29"/>
+      <c r="H48" s="29"/>
+    </row>
+    <row r="49" spans="1:12" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A49" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B49" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C41" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D41" s="1" t="s">
+      <c r="C49" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="E49" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F41" s="1" t="s">
+      <c r="F49" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G41" s="1" t="s">
+      <c r="G49" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H41" s="1" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="22">
-        <v>1</v>
-      </c>
-      <c r="B42" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="F42" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="G42" s="4"/>
-      <c r="H42" s="16" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="H43" s="2"/>
-    </row>
-    <row r="44" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="F44" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="H44" s="2"/>
-    </row>
-    <row r="45" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="H45" s="2"/>
-    </row>
-    <row r="46" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="B46" s="25"/>
-      <c r="C46" s="25"/>
-      <c r="D46" s="25"/>
-      <c r="E46" s="25"/>
-      <c r="F46" s="25"/>
-      <c r="G46" s="25"/>
-      <c r="H46" s="25"/>
-    </row>
-    <row r="47" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="25" t="s">
-        <v>554</v>
-      </c>
-      <c r="B47" s="25"/>
-      <c r="C47" s="25"/>
-      <c r="D47" s="25"/>
-      <c r="E47" s="25"/>
-      <c r="F47" s="25"/>
-      <c r="G47" s="25"/>
-      <c r="H47" s="25"/>
-    </row>
-    <row r="48" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H48" s="1" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="51">
-        <v>1</v>
-      </c>
-      <c r="B49" s="50" t="s">
+      <c r="H49" s="1" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A50" s="40">
+        <v>1</v>
+      </c>
+      <c r="B50" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="C49" s="25" t="s">
+      <c r="C50" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="D49" s="6" t="s">
+      <c r="D50" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E49" s="1">
-        <v>1</v>
-      </c>
-      <c r="F49" s="5" t="s">
+      <c r="E50" s="1">
+        <v>1</v>
+      </c>
+      <c r="F50" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G49" s="36"/>
-      <c r="H49" s="15" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="51"/>
-      <c r="B50" s="50"/>
-      <c r="C50" s="25"/>
-      <c r="D50" s="6" t="s">
+      <c r="G50" s="28"/>
+      <c r="H50" s="15" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A51" s="40"/>
+      <c r="B51" s="39"/>
+      <c r="C51" s="29"/>
+      <c r="D51" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E50" s="1">
-        <v>1</v>
-      </c>
-      <c r="F50" s="5" t="s">
+      <c r="E51" s="1">
+        <v>1</v>
+      </c>
+      <c r="F51" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G50" s="36"/>
-      <c r="H50" s="15" t="s">
-        <v>386</v>
-      </c>
-      <c r="I50" s="2"/>
-      <c r="J50" s="2"/>
-      <c r="K50" s="2"/>
-      <c r="L50" s="2"/>
-    </row>
-    <row r="51" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="41">
-        <v>2</v>
-      </c>
-      <c r="B51" s="50" t="s">
-        <v>5</v>
-      </c>
-      <c r="C51" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="D51" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E51" s="1">
-        <v>1</v>
-      </c>
-      <c r="F51" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G51" s="36"/>
+      <c r="G51" s="28"/>
       <c r="H51" s="15" t="s">
-        <v>322</v>
+        <v>376</v>
       </c>
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
@@ -3900,21 +3908,27 @@
       <c r="L51" s="2"/>
     </row>
     <row r="52" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="42"/>
-      <c r="B52" s="50"/>
-      <c r="C52" s="25"/>
+      <c r="A52" s="34">
+        <v>2</v>
+      </c>
+      <c r="B52" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="C52" s="29" t="s">
+        <v>14</v>
+      </c>
       <c r="D52" s="6" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E52" s="1">
         <v>1</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G52" s="36"/>
+        <v>23</v>
+      </c>
+      <c r="G52" s="28"/>
       <c r="H52" s="15" t="s">
-        <v>387</v>
+        <v>313</v>
       </c>
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
@@ -3922,27 +3936,21 @@
       <c r="L52" s="2"/>
     </row>
     <row r="53" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="41">
-        <v>3</v>
-      </c>
-      <c r="B53" s="50" t="s">
-        <v>5</v>
-      </c>
-      <c r="C53" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>13</v>
+      <c r="A53" s="35"/>
+      <c r="B53" s="39"/>
+      <c r="C53" s="29"/>
+      <c r="D53" s="6" t="s">
+        <v>19</v>
       </c>
       <c r="E53" s="1">
         <v>1</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>529</v>
-      </c>
-      <c r="G53" s="36"/>
+        <v>24</v>
+      </c>
+      <c r="G53" s="28"/>
       <c r="H53" s="15" t="s">
-        <v>488</v>
+        <v>377</v>
       </c>
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
@@ -3950,21 +3958,27 @@
       <c r="L53" s="2"/>
     </row>
     <row r="54" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="42"/>
-      <c r="B54" s="50"/>
-      <c r="C54" s="25"/>
+      <c r="A54" s="34">
+        <v>3</v>
+      </c>
+      <c r="B54" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="C54" s="29" t="s">
+        <v>14</v>
+      </c>
       <c r="D54" s="5" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E54" s="1">
         <v>1</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>552</v>
-      </c>
-      <c r="G54" s="36"/>
+        <v>518</v>
+      </c>
+      <c r="G54" s="28"/>
       <c r="H54" s="15" t="s">
-        <v>388</v>
+        <v>477</v>
       </c>
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
@@ -3972,79 +3986,71 @@
       <c r="L54" s="2"/>
     </row>
     <row r="55" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="41">
-        <v>4</v>
-      </c>
-      <c r="B55" s="50" t="s">
-        <v>5</v>
-      </c>
-      <c r="C55" s="25" t="s">
-        <v>6</v>
-      </c>
+      <c r="A55" s="35"/>
+      <c r="B55" s="39"/>
+      <c r="C55" s="29"/>
       <c r="D55" s="5" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E55" s="1">
         <v>1</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>501</v>
-      </c>
-      <c r="G55" s="36"/>
+        <v>536</v>
+      </c>
+      <c r="G55" s="28"/>
       <c r="H55" s="15" t="s">
-        <v>316</v>
+        <v>378</v>
       </c>
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
       <c r="K55" s="2"/>
       <c r="L55" s="2"/>
     </row>
-    <row r="56" spans="1:12" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="42"/>
-      <c r="B56" s="50"/>
-      <c r="C56" s="25"/>
+    <row r="56" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A56" s="34">
+        <v>4</v>
+      </c>
+      <c r="B56" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="C56" s="29" t="s">
+        <v>6</v>
+      </c>
       <c r="D56" s="5" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E56" s="1">
         <v>1</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>549</v>
-      </c>
-      <c r="G56" s="36"/>
+        <v>490</v>
+      </c>
+      <c r="G56" s="28"/>
       <c r="H56" s="15" t="s">
-        <v>454</v>
+        <v>307</v>
       </c>
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
       <c r="K56" s="2"/>
       <c r="L56" s="2"/>
     </row>
-    <row r="57" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="41">
-        <v>5</v>
-      </c>
-      <c r="B57" s="37" t="s">
-        <v>17</v>
-      </c>
-      <c r="C57" s="25" t="s">
-        <v>6</v>
-      </c>
+    <row r="57" spans="1:12" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A57" s="35"/>
+      <c r="B57" s="39"/>
+      <c r="C57" s="29"/>
       <c r="D57" s="5" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E57" s="1">
         <v>1</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>525</v>
-      </c>
-      <c r="G57" s="36" t="s">
-        <v>526</v>
-      </c>
+        <v>534</v>
+      </c>
+      <c r="G57" s="28"/>
       <c r="H57" s="15" t="s">
-        <v>323</v>
+        <v>443</v>
       </c>
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
@@ -4052,21 +4058,29 @@
       <c r="L57" s="2"/>
     </row>
     <row r="58" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="42"/>
-      <c r="B58" s="37"/>
-      <c r="C58" s="25"/>
+      <c r="A58" s="34">
+        <v>5</v>
+      </c>
+      <c r="B58" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="C58" s="29" t="s">
+        <v>6</v>
+      </c>
       <c r="D58" s="5" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="E58" s="1">
         <v>1</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>572</v>
-      </c>
-      <c r="G58" s="36"/>
+        <v>514</v>
+      </c>
+      <c r="G58" s="28" t="s">
+        <v>515</v>
+      </c>
       <c r="H58" s="15" t="s">
-        <v>389</v>
+        <v>314</v>
       </c>
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
@@ -4074,27 +4088,21 @@
       <c r="L58" s="2"/>
     </row>
     <row r="59" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A59" s="41">
-        <v>6</v>
-      </c>
-      <c r="B59" s="37" t="s">
-        <v>17</v>
-      </c>
-      <c r="C59" s="25" t="s">
-        <v>6</v>
-      </c>
+      <c r="A59" s="35"/>
+      <c r="B59" s="30"/>
+      <c r="C59" s="29"/>
       <c r="D59" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E59" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>615</v>
-      </c>
-      <c r="G59" s="36"/>
+        <v>556</v>
+      </c>
+      <c r="G59" s="28"/>
       <c r="H59" s="15" t="s">
-        <v>324</v>
+        <v>379</v>
       </c>
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
@@ -4102,21 +4110,27 @@
       <c r="L59" s="2"/>
     </row>
     <row r="60" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="42"/>
-      <c r="B60" s="37"/>
-      <c r="C60" s="25"/>
+      <c r="A60" s="34">
+        <v>6</v>
+      </c>
+      <c r="B60" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="C60" s="29" t="s">
+        <v>6</v>
+      </c>
       <c r="D60" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E60" s="1">
         <v>0</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>614</v>
-      </c>
-      <c r="G60" s="36"/>
+        <v>596</v>
+      </c>
+      <c r="G60" s="28"/>
       <c r="H60" s="15" t="s">
-        <v>390</v>
+        <v>315</v>
       </c>
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
@@ -4124,27 +4138,21 @@
       <c r="L60" s="2"/>
     </row>
     <row r="61" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="41">
-        <v>7</v>
-      </c>
-      <c r="B61" s="37" t="s">
-        <v>17</v>
-      </c>
-      <c r="C61" s="25" t="s">
-        <v>6</v>
-      </c>
+      <c r="A61" s="35"/>
+      <c r="B61" s="30"/>
+      <c r="C61" s="29"/>
       <c r="D61" s="5" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="E61" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="G61" s="36"/>
+        <v>595</v>
+      </c>
+      <c r="G61" s="28"/>
       <c r="H61" s="15" t="s">
-        <v>325</v>
+        <v>380</v>
       </c>
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
@@ -4152,21 +4160,27 @@
       <c r="L61" s="2"/>
     </row>
     <row r="62" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="42"/>
-      <c r="B62" s="37"/>
-      <c r="C62" s="25"/>
+      <c r="A62" s="34">
+        <v>7</v>
+      </c>
+      <c r="B62" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="C62" s="29" t="s">
+        <v>6</v>
+      </c>
       <c r="D62" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E62" s="1">
         <v>1</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="G62" s="36"/>
+        <v>146</v>
+      </c>
+      <c r="G62" s="28"/>
       <c r="H62" s="15" t="s">
-        <v>391</v>
+        <v>316</v>
       </c>
       <c r="I62" s="2"/>
       <c r="J62" s="2"/>
@@ -4174,29 +4188,21 @@
       <c r="L62" s="2"/>
     </row>
     <row r="63" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="41">
-        <v>8</v>
-      </c>
-      <c r="B63" s="37" t="s">
-        <v>17</v>
-      </c>
-      <c r="C63" s="25" t="s">
-        <v>6</v>
-      </c>
+      <c r="A63" s="35"/>
+      <c r="B63" s="30"/>
+      <c r="C63" s="29"/>
       <c r="D63" s="5" t="s">
-        <v>195</v>
+        <v>38</v>
       </c>
       <c r="E63" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>616</v>
-      </c>
-      <c r="G63" s="36" t="s">
-        <v>587</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="G63" s="28"/>
       <c r="H63" s="15" t="s">
-        <v>326</v>
+        <v>381</v>
       </c>
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
@@ -4204,21 +4210,29 @@
       <c r="L63" s="2"/>
     </row>
     <row r="64" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A64" s="42"/>
-      <c r="B64" s="37"/>
-      <c r="C64" s="25"/>
+      <c r="A64" s="34">
+        <v>8</v>
+      </c>
+      <c r="B64" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="C64" s="29" t="s">
+        <v>6</v>
+      </c>
       <c r="D64" s="5" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E64" s="1">
         <v>0</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>617</v>
-      </c>
-      <c r="G64" s="36"/>
+        <v>597</v>
+      </c>
+      <c r="G64" s="28" t="s">
+        <v>569</v>
+      </c>
       <c r="H64" s="15" t="s">
-        <v>392</v>
+        <v>317</v>
       </c>
       <c r="I64" s="2"/>
       <c r="J64" s="2"/>
@@ -4226,95 +4240,95 @@
       <c r="L64" s="2"/>
     </row>
     <row r="65" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A65" s="41">
+      <c r="A65" s="35"/>
+      <c r="B65" s="30"/>
+      <c r="C65" s="29"/>
+      <c r="D65" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="E65" s="1">
+        <v>0</v>
+      </c>
+      <c r="F65" s="5" t="s">
+        <v>598</v>
+      </c>
+      <c r="G65" s="28"/>
+      <c r="H65" s="15" t="s">
+        <v>382</v>
+      </c>
+      <c r="I65" s="2"/>
+      <c r="J65" s="2"/>
+      <c r="K65" s="2"/>
+      <c r="L65" s="2"/>
+    </row>
+    <row r="66" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A66" s="34">
         <v>9</v>
       </c>
-      <c r="B65" s="37" t="s">
+      <c r="B66" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C65" s="25" t="s">
+      <c r="C66" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="D65" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="E65" s="1">
-        <v>1</v>
-      </c>
-      <c r="F65" s="5" t="s">
-        <v>584</v>
-      </c>
-      <c r="G65" s="36" t="s">
-        <v>588</v>
-      </c>
-      <c r="H65" s="15" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A66" s="42"/>
-      <c r="B66" s="37"/>
-      <c r="C66" s="25"/>
       <c r="D66" s="5" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E66" s="1">
         <v>1</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>585</v>
-      </c>
-      <c r="G66" s="36"/>
+        <v>566</v>
+      </c>
+      <c r="G66" s="28" t="s">
+        <v>570</v>
+      </c>
       <c r="H66" s="15" t="s">
-        <v>393</v>
+        <v>318</v>
       </c>
     </row>
     <row r="67" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A67" s="41">
+      <c r="A67" s="35"/>
+      <c r="B67" s="30"/>
+      <c r="C67" s="29"/>
+      <c r="D67" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="E67" s="1">
+        <v>1</v>
+      </c>
+      <c r="F67" s="5" t="s">
+        <v>567</v>
+      </c>
+      <c r="G67" s="28"/>
+      <c r="H67" s="15" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A68" s="34">
         <v>10</v>
       </c>
-      <c r="B67" s="37" t="s">
+      <c r="B68" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C67" s="25" t="s">
+      <c r="C68" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="D67" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="E67" s="1">
-        <v>1</v>
-      </c>
-      <c r="F67" s="5" t="s">
-        <v>564</v>
-      </c>
-      <c r="G67" s="36" t="s">
-        <v>589</v>
-      </c>
-      <c r="H67" s="15" t="s">
-        <v>328</v>
-      </c>
-      <c r="I67" s="2"/>
-      <c r="J67" s="2"/>
-      <c r="K67" s="2"/>
-      <c r="L67" s="2"/>
-    </row>
-    <row r="68" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A68" s="42"/>
-      <c r="B68" s="37"/>
-      <c r="C68" s="25"/>
       <c r="D68" s="5" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E68" s="1">
         <v>1</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>563</v>
-      </c>
-      <c r="G68" s="36"/>
+        <v>548</v>
+      </c>
+      <c r="G68" s="28" t="s">
+        <v>571</v>
+      </c>
       <c r="H68" s="15" t="s">
-        <v>394</v>
+        <v>319</v>
       </c>
       <c r="I68" s="2"/>
       <c r="J68" s="2"/>
@@ -4322,81 +4336,73 @@
       <c r="L68" s="2"/>
     </row>
     <row r="69" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A69" s="41">
-        <v>11</v>
-      </c>
-      <c r="B69" s="37" t="s">
-        <v>17</v>
-      </c>
-      <c r="C69" s="25" t="s">
-        <v>6</v>
-      </c>
+      <c r="A69" s="35"/>
+      <c r="B69" s="30"/>
+      <c r="C69" s="29"/>
       <c r="D69" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E69" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>619</v>
-      </c>
-      <c r="G69" s="36" t="s">
-        <v>587</v>
-      </c>
+        <v>547</v>
+      </c>
+      <c r="G69" s="28"/>
       <c r="H69" s="15" t="s">
-        <v>329</v>
+        <v>384</v>
       </c>
       <c r="I69" s="2"/>
       <c r="J69" s="2"/>
       <c r="K69" s="2"/>
       <c r="L69" s="2"/>
     </row>
-    <row r="70" spans="1:12" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A70" s="42"/>
-      <c r="B70" s="37"/>
-      <c r="C70" s="25"/>
+    <row r="70" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A70" s="34">
+        <v>11</v>
+      </c>
+      <c r="B70" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="C70" s="29" t="s">
+        <v>6</v>
+      </c>
       <c r="D70" s="5" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E70" s="1">
         <v>0</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>620</v>
-      </c>
-      <c r="G70" s="36"/>
+        <v>639</v>
+      </c>
+      <c r="G70" s="28" t="s">
+        <v>569</v>
+      </c>
       <c r="H70" s="15" t="s">
-        <v>395</v>
+        <v>320</v>
       </c>
       <c r="I70" s="2"/>
       <c r="J70" s="2"/>
       <c r="K70" s="2"/>
       <c r="L70" s="2"/>
     </row>
-    <row r="71" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A71" s="32">
-        <v>12</v>
-      </c>
-      <c r="B71" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="C71" s="25" t="s">
-        <v>6</v>
-      </c>
+    <row r="71" spans="1:12" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A71" s="35"/>
+      <c r="B71" s="30"/>
+      <c r="C71" s="29"/>
       <c r="D71" s="5" t="s">
-        <v>35</v>
+        <v>157</v>
       </c>
       <c r="E71" s="1">
         <v>0</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>659</v>
-      </c>
-      <c r="G71" s="36" t="s">
-        <v>587</v>
-      </c>
+        <v>640</v>
+      </c>
+      <c r="G71" s="28"/>
       <c r="H71" s="15" t="s">
-        <v>330</v>
+        <v>385</v>
       </c>
       <c r="I71" s="2"/>
       <c r="J71" s="2"/>
@@ -4404,21 +4410,29 @@
       <c r="L71" s="2"/>
     </row>
     <row r="72" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A72" s="33"/>
-      <c r="B72" s="38"/>
-      <c r="C72" s="25"/>
+      <c r="A72" s="34">
+        <v>12</v>
+      </c>
+      <c r="B72" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="C72" s="29" t="s">
+        <v>6</v>
+      </c>
       <c r="D72" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E72" s="1">
         <v>0</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>658</v>
-      </c>
-      <c r="G72" s="36"/>
+        <v>637</v>
+      </c>
+      <c r="G72" s="28" t="s">
+        <v>569</v>
+      </c>
       <c r="H72" s="15" t="s">
-        <v>396</v>
+        <v>321</v>
       </c>
       <c r="I72" s="2"/>
       <c r="J72" s="2"/>
@@ -4426,27 +4440,21 @@
       <c r="L72" s="2"/>
     </row>
     <row r="73" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A73" s="32">
-        <v>13</v>
-      </c>
-      <c r="B73" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="C73" s="25" t="s">
-        <v>6</v>
-      </c>
+      <c r="A73" s="35"/>
+      <c r="B73" s="33"/>
+      <c r="C73" s="29"/>
       <c r="D73" s="5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E73" s="1">
         <v>0</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>561</v>
-      </c>
-      <c r="G73" s="36"/>
+        <v>638</v>
+      </c>
+      <c r="G73" s="28"/>
       <c r="H73" s="15" t="s">
-        <v>331</v>
+        <v>386</v>
       </c>
       <c r="I73" s="2"/>
       <c r="J73" s="2"/>
@@ -4454,21 +4462,27 @@
       <c r="L73" s="2"/>
     </row>
     <row r="74" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A74" s="33"/>
-      <c r="B74" s="38"/>
-      <c r="C74" s="25"/>
+      <c r="A74" s="41">
+        <v>13</v>
+      </c>
+      <c r="B74" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="C74" s="29" t="s">
+        <v>6</v>
+      </c>
       <c r="D74" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E74" s="1">
         <v>0</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>562</v>
-      </c>
-      <c r="G74" s="36"/>
+        <v>545</v>
+      </c>
+      <c r="G74" s="28"/>
       <c r="H74" s="15" t="s">
-        <v>397</v>
+        <v>322</v>
       </c>
       <c r="I74" s="2"/>
       <c r="J74" s="2"/>
@@ -4476,29 +4490,21 @@
       <c r="L74" s="2"/>
     </row>
     <row r="75" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A75" s="41">
-        <v>14</v>
-      </c>
-      <c r="B75" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="C75" s="25" t="s">
-        <v>6</v>
-      </c>
+      <c r="A75" s="42"/>
+      <c r="B75" s="33"/>
+      <c r="C75" s="29"/>
       <c r="D75" s="5" t="s">
-        <v>127</v>
+        <v>34</v>
       </c>
       <c r="E75" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>502</v>
-      </c>
-      <c r="G75" s="36" t="s">
-        <v>587</v>
-      </c>
+        <v>546</v>
+      </c>
+      <c r="G75" s="28"/>
       <c r="H75" s="15" t="s">
-        <v>332</v>
+        <v>387</v>
       </c>
       <c r="I75" s="2"/>
       <c r="J75" s="2"/>
@@ -4506,3710 +4512,3381 @@
       <c r="L75" s="2"/>
     </row>
     <row r="76" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A76" s="42"/>
-      <c r="B76" s="38"/>
-      <c r="C76" s="25"/>
+      <c r="A76" s="34">
+        <v>14</v>
+      </c>
+      <c r="B76" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="C76" s="29" t="s">
+        <v>6</v>
+      </c>
       <c r="D76" s="5" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E76" s="1">
         <v>1</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>503</v>
-      </c>
-      <c r="G76" s="36"/>
+        <v>491</v>
+      </c>
+      <c r="G76" s="28" t="s">
+        <v>569</v>
+      </c>
       <c r="H76" s="15" t="s">
-        <v>398</v>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="I76" s="2"/>
+      <c r="J76" s="2"/>
+      <c r="K76" s="2"/>
+      <c r="L76" s="2"/>
     </row>
     <row r="77" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A77" s="41">
+      <c r="A77" s="35"/>
+      <c r="B77" s="33"/>
+      <c r="C77" s="29"/>
+      <c r="D77" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="E77" s="1">
+        <v>1</v>
+      </c>
+      <c r="F77" s="5" t="s">
+        <v>492</v>
+      </c>
+      <c r="G77" s="28"/>
+      <c r="H77" s="15" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A78" s="34">
         <v>15</v>
       </c>
-      <c r="B77" s="38" t="s">
+      <c r="B78" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C77" s="25" t="s">
+      <c r="C78" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="D77" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="E77" s="1">
-        <v>2</v>
-      </c>
-      <c r="F77" s="5" t="s">
-        <v>653</v>
-      </c>
-      <c r="G77" s="36" t="s">
-        <v>650</v>
-      </c>
-      <c r="H77" s="15" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A78" s="42"/>
-      <c r="B78" s="38"/>
-      <c r="C78" s="25"/>
       <c r="D78" s="5" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E78" s="1">
         <v>2</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>654</v>
-      </c>
-      <c r="G78" s="36"/>
+        <v>632</v>
+      </c>
+      <c r="G78" s="28" t="s">
+        <v>629</v>
+      </c>
       <c r="H78" s="15" t="s">
-        <v>399</v>
+        <v>324</v>
       </c>
     </row>
     <row r="79" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A79" s="32">
-        <v>16</v>
-      </c>
-      <c r="B79" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="C79" s="39" t="s">
-        <v>6</v>
-      </c>
+      <c r="A79" s="35"/>
+      <c r="B79" s="33"/>
+      <c r="C79" s="29"/>
       <c r="D79" s="5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E79" s="1">
         <v>2</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>652</v>
-      </c>
-      <c r="G79" s="36" t="s">
-        <v>560</v>
-      </c>
+        <v>633</v>
+      </c>
+      <c r="G79" s="28"/>
       <c r="H79" s="15" t="s">
-        <v>598</v>
+        <v>389</v>
       </c>
     </row>
     <row r="80" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A80" s="33"/>
-      <c r="B80" s="38"/>
-      <c r="C80" s="40"/>
+      <c r="A80" s="41">
+        <v>16</v>
+      </c>
+      <c r="B80" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="C80" s="50" t="s">
+        <v>6</v>
+      </c>
       <c r="D80" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E80" s="1">
         <v>2</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>559</v>
-      </c>
-      <c r="G80" s="36"/>
+        <v>631</v>
+      </c>
+      <c r="G80" s="28" t="s">
+        <v>544</v>
+      </c>
       <c r="H80" s="15" t="s">
-        <v>599</v>
+        <v>580</v>
       </c>
     </row>
     <row r="81" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A81" s="32">
+      <c r="A81" s="42"/>
+      <c r="B81" s="33"/>
+      <c r="C81" s="51"/>
+      <c r="D81" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="E81" s="1">
+        <v>2</v>
+      </c>
+      <c r="F81" s="5" t="s">
+        <v>543</v>
+      </c>
+      <c r="G81" s="28"/>
+      <c r="H81" s="15" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A82" s="41">
         <v>17</v>
       </c>
-      <c r="B81" s="38" t="s">
+      <c r="B82" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C81" s="25" t="s">
+      <c r="C82" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="D81" s="5" t="s">
+      <c r="D82" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E81" s="1">
-        <v>1</v>
-      </c>
-      <c r="F81" s="5" t="s">
-        <v>651</v>
-      </c>
-      <c r="G81" s="36" t="s">
-        <v>226</v>
-      </c>
-      <c r="H81" s="15" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A82" s="33"/>
-      <c r="B82" s="38"/>
-      <c r="C82" s="25"/>
-      <c r="D82" s="5" t="s">
+      <c r="E82" s="1">
+        <v>1</v>
+      </c>
+      <c r="F82" s="5" t="s">
+        <v>630</v>
+      </c>
+      <c r="G82" s="28" t="s">
+        <v>222</v>
+      </c>
+      <c r="H82" s="15" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A83" s="42"/>
+      <c r="B83" s="33"/>
+      <c r="C83" s="29"/>
+      <c r="D83" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E82" s="1">
-        <v>1</v>
-      </c>
-      <c r="F82" s="5" t="s">
-        <v>518</v>
-      </c>
-      <c r="G82" s="36"/>
-      <c r="H82" s="15" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A83" s="32">
+      <c r="E83" s="1">
+        <v>1</v>
+      </c>
+      <c r="F83" s="5" t="s">
+        <v>507</v>
+      </c>
+      <c r="G83" s="28"/>
+      <c r="H83" s="15" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A84" s="41">
         <v>18</v>
       </c>
-      <c r="B83" s="38" t="s">
+      <c r="B84" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C83" s="35" t="s">
+      <c r="C84" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="D83" s="5" t="s">
+      <c r="D84" s="5" t="s">
         <v>41</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F83" s="5" t="s">
-        <v>504</v>
-      </c>
-      <c r="G83" s="36" t="s">
-        <v>517</v>
-      </c>
-      <c r="H83" s="15" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A84" s="33"/>
-      <c r="B84" s="38"/>
-      <c r="C84" s="35"/>
-      <c r="D84" s="5" t="s">
-        <v>42</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>505</v>
-      </c>
-      <c r="G84" s="36"/>
+        <v>493</v>
+      </c>
+      <c r="G84" s="28" t="s">
+        <v>506</v>
+      </c>
       <c r="H84" s="15" t="s">
-        <v>401</v>
+        <v>326</v>
       </c>
     </row>
     <row r="85" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A85" s="32">
+      <c r="A85" s="42"/>
+      <c r="B85" s="33"/>
+      <c r="C85" s="45"/>
+      <c r="D85" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F85" s="5" t="s">
+        <v>494</v>
+      </c>
+      <c r="G85" s="28"/>
+      <c r="H85" s="15" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A86" s="41">
         <v>19</v>
       </c>
-      <c r="B85" s="38" t="s">
+      <c r="B86" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C85" s="25" t="s">
+      <c r="C86" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="D85" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="E85" s="1">
-        <v>1</v>
-      </c>
-      <c r="F85" s="5" t="s">
-        <v>630</v>
-      </c>
-      <c r="G85" s="36"/>
-      <c r="H85" s="15" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A86" s="33"/>
-      <c r="B86" s="38"/>
-      <c r="C86" s="25"/>
       <c r="D86" s="5" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E86" s="1">
         <v>1</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>631</v>
-      </c>
-      <c r="G86" s="36"/>
+        <v>609</v>
+      </c>
+      <c r="G86" s="28"/>
       <c r="H86" s="15" t="s">
-        <v>520</v>
+        <v>508</v>
       </c>
     </row>
     <row r="87" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A87" s="32">
+      <c r="A87" s="42"/>
+      <c r="B87" s="33"/>
+      <c r="C87" s="29"/>
+      <c r="D87" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E87" s="1">
+        <v>1</v>
+      </c>
+      <c r="F87" s="5" t="s">
+        <v>610</v>
+      </c>
+      <c r="G87" s="28"/>
+      <c r="H87" s="15" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A88" s="41">
         <v>20</v>
       </c>
-      <c r="B87" s="34" t="s">
+      <c r="B88" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C87" s="25" t="s">
+      <c r="C88" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="D87" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="E87" s="1">
-        <v>1</v>
-      </c>
-      <c r="F87" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="G87" s="36" t="s">
-        <v>282</v>
-      </c>
-      <c r="H87" s="15" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A88" s="33"/>
-      <c r="B88" s="34"/>
-      <c r="C88" s="25"/>
       <c r="D88" s="5" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="E88" s="1">
         <v>1</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="G88" s="36"/>
+        <v>276</v>
+      </c>
+      <c r="G88" s="28" t="s">
+        <v>275</v>
+      </c>
       <c r="H88" s="15" t="s">
-        <v>402</v>
+        <v>327</v>
       </c>
     </row>
     <row r="89" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A89" s="32">
+      <c r="A89" s="42"/>
+      <c r="B89" s="31"/>
+      <c r="C89" s="29"/>
+      <c r="D89" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="E89" s="1">
+        <v>1</v>
+      </c>
+      <c r="F89" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="G89" s="28"/>
+      <c r="H89" s="15" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A90" s="41">
         <v>21</v>
       </c>
-      <c r="B89" s="34" t="s">
+      <c r="B90" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C89" s="25" t="s">
+      <c r="C90" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="D89" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="E89" s="1">
-        <v>0</v>
-      </c>
-      <c r="F89" s="5" t="s">
-        <v>567</v>
-      </c>
-      <c r="G89" s="36" t="s">
-        <v>571</v>
-      </c>
-      <c r="H89" s="15" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A90" s="33"/>
-      <c r="B90" s="34"/>
-      <c r="C90" s="25"/>
       <c r="D90" s="5" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E90" s="1">
         <v>0</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>568</v>
-      </c>
-      <c r="G90" s="36"/>
+        <v>551</v>
+      </c>
+      <c r="G90" s="28" t="s">
+        <v>555</v>
+      </c>
       <c r="H90" s="15" t="s">
-        <v>403</v>
+        <v>328</v>
       </c>
     </row>
     <row r="91" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A91" s="41">
+      <c r="A91" s="42"/>
+      <c r="B91" s="31"/>
+      <c r="C91" s="29"/>
+      <c r="D91" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="E91" s="1">
+        <v>0</v>
+      </c>
+      <c r="F91" s="5" t="s">
+        <v>552</v>
+      </c>
+      <c r="G91" s="28"/>
+      <c r="H91" s="15" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A92" s="34">
         <v>22</v>
       </c>
-      <c r="B91" s="34" t="s">
+      <c r="B92" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C91" s="25" t="s">
+      <c r="C92" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="D91" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="E91" s="1">
-        <v>2</v>
-      </c>
-      <c r="F91" s="5" t="s">
-        <v>527</v>
-      </c>
-      <c r="G91" s="36" t="s">
-        <v>521</v>
-      </c>
-      <c r="H91" s="15" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A92" s="42"/>
-      <c r="B92" s="34"/>
-      <c r="C92" s="25"/>
       <c r="D92" s="5" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E92" s="1">
         <v>2</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>528</v>
-      </c>
-      <c r="G92" s="36"/>
+        <v>516</v>
+      </c>
+      <c r="G92" s="28" t="s">
+        <v>510</v>
+      </c>
       <c r="H92" s="15" t="s">
-        <v>404</v>
+        <v>329</v>
       </c>
     </row>
     <row r="93" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A93" s="32">
-        <v>23</v>
-      </c>
-      <c r="B93" s="34" t="s">
-        <v>29</v>
-      </c>
-      <c r="C93" s="25" t="s">
-        <v>6</v>
-      </c>
+      <c r="A93" s="35"/>
+      <c r="B93" s="31"/>
+      <c r="C93" s="29"/>
       <c r="D93" s="5" t="s">
-        <v>30</v>
+        <v>179</v>
       </c>
       <c r="E93" s="1">
         <v>2</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>534</v>
-      </c>
-      <c r="G93" s="36" t="s">
-        <v>297</v>
-      </c>
+        <v>517</v>
+      </c>
+      <c r="G93" s="28"/>
       <c r="H93" s="15" t="s">
-        <v>339</v>
+        <v>394</v>
       </c>
     </row>
     <row r="94" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A94" s="33"/>
-      <c r="B94" s="34"/>
-      <c r="C94" s="25"/>
+      <c r="A94" s="41">
+        <v>23</v>
+      </c>
+      <c r="B94" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="C94" s="29" t="s">
+        <v>6</v>
+      </c>
       <c r="D94" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E94" s="1">
         <v>2</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>535</v>
-      </c>
-      <c r="G94" s="36"/>
+        <v>663</v>
+      </c>
+      <c r="G94" s="28" t="s">
+        <v>290</v>
+      </c>
       <c r="H94" s="15" t="s">
-        <v>405</v>
+        <v>330</v>
       </c>
     </row>
     <row r="95" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A95" s="32">
+      <c r="A95" s="42"/>
+      <c r="B95" s="31"/>
+      <c r="C95" s="29"/>
+      <c r="D95" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E95" s="1">
+        <v>2</v>
+      </c>
+      <c r="F95" s="5" t="s">
+        <v>661</v>
+      </c>
+      <c r="G95" s="28"/>
+      <c r="H95" s="15" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A96" s="41">
         <v>24</v>
       </c>
-      <c r="B95" s="34" t="s">
+      <c r="B96" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C95" s="25" t="s">
+      <c r="C96" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="D95" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F95" s="5" t="s">
-        <v>565</v>
-      </c>
-      <c r="G95" s="36" t="s">
-        <v>207</v>
-      </c>
-      <c r="H95" s="15" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A96" s="33"/>
-      <c r="B96" s="34"/>
-      <c r="C96" s="25"/>
       <c r="D96" s="5" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>566</v>
-      </c>
-      <c r="G96" s="36"/>
+        <v>549</v>
+      </c>
+      <c r="G96" s="28" t="s">
+        <v>203</v>
+      </c>
       <c r="H96" s="15" t="s">
-        <v>406</v>
+        <v>331</v>
       </c>
     </row>
     <row r="97" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A97" s="32">
+      <c r="A97" s="42"/>
+      <c r="B97" s="31"/>
+      <c r="C97" s="29"/>
+      <c r="D97" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F97" s="5" t="s">
+        <v>550</v>
+      </c>
+      <c r="G97" s="28"/>
+      <c r="H97" s="15" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A98" s="34">
         <v>25</v>
       </c>
-      <c r="B97" s="37" t="s">
+      <c r="B98" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C97" s="25" t="s">
+      <c r="C98" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="D97" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="E97" s="1">
-        <v>0</v>
-      </c>
-      <c r="F97" s="5" t="s">
-        <v>556</v>
-      </c>
-      <c r="G97" s="36"/>
-      <c r="H97" s="15" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A98" s="33"/>
-      <c r="B98" s="37"/>
-      <c r="C98" s="25"/>
       <c r="D98" s="5" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E98" s="1">
         <v>0</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>557</v>
-      </c>
-      <c r="G98" s="36"/>
+        <v>540</v>
+      </c>
+      <c r="G98" s="28"/>
       <c r="H98" s="15" t="s">
-        <v>407</v>
+        <v>332</v>
       </c>
     </row>
     <row r="99" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A99" s="32">
+      <c r="A99" s="35"/>
+      <c r="B99" s="30"/>
+      <c r="C99" s="29"/>
+      <c r="D99" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="E99" s="1">
+        <v>0</v>
+      </c>
+      <c r="F99" s="5" t="s">
+        <v>541</v>
+      </c>
+      <c r="G99" s="28"/>
+      <c r="H99" s="15" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A100" s="41">
         <v>26</v>
       </c>
-      <c r="B99" s="37" t="s">
+      <c r="B100" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C99" s="35" t="s">
+      <c r="C100" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="D99" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="E99" s="1">
-        <v>1</v>
-      </c>
-      <c r="F99" s="5" t="s">
-        <v>633</v>
-      </c>
-      <c r="G99" s="36"/>
-      <c r="H99" s="15" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A100" s="33"/>
-      <c r="B100" s="37"/>
-      <c r="C100" s="35"/>
       <c r="D100" s="5" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E100" s="1">
         <v>1</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>634</v>
-      </c>
-      <c r="G100" s="36"/>
+        <v>612</v>
+      </c>
+      <c r="G100" s="28"/>
       <c r="H100" s="15" t="s">
-        <v>408</v>
+        <v>333</v>
       </c>
     </row>
     <row r="101" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A101" s="32">
+      <c r="A101" s="42"/>
+      <c r="B101" s="30"/>
+      <c r="C101" s="45"/>
+      <c r="D101" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="E101" s="1">
+        <v>1</v>
+      </c>
+      <c r="F101" s="5" t="s">
+        <v>613</v>
+      </c>
+      <c r="G101" s="28"/>
+      <c r="H101" s="15" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A102" s="41">
         <v>27</v>
       </c>
-      <c r="B101" s="37" t="s">
+      <c r="B102" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C101" s="25" t="s">
+      <c r="C102" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="D101" s="5" t="s">
+      <c r="D102" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E101" s="1">
-        <v>1</v>
-      </c>
-      <c r="F101" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="G101" s="36"/>
-      <c r="H101" s="15" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A102" s="33"/>
-      <c r="B102" s="37"/>
-      <c r="C102" s="25"/>
-      <c r="D102" s="5" t="s">
+      <c r="E102" s="1">
+        <v>1</v>
+      </c>
+      <c r="F102" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="G102" s="28"/>
+      <c r="H102" s="15" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A103" s="42"/>
+      <c r="B103" s="30"/>
+      <c r="C103" s="29"/>
+      <c r="D103" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E102" s="1">
-        <v>1</v>
-      </c>
-      <c r="F102" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="G102" s="36"/>
-      <c r="H102" s="15" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A103" s="32">
+      <c r="E103" s="1">
+        <v>1</v>
+      </c>
+      <c r="F103" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="G103" s="28"/>
+      <c r="H103" s="15" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A104" s="41">
         <v>28</v>
       </c>
-      <c r="B103" s="37" t="s">
+      <c r="B104" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C103" s="25" t="s">
+      <c r="C104" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="D103" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E103" s="1">
-        <v>1</v>
-      </c>
-      <c r="F103" s="5" t="s">
-        <v>612</v>
-      </c>
-      <c r="G103" s="36"/>
-      <c r="H103" s="15" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A104" s="33"/>
-      <c r="B104" s="37"/>
-      <c r="C104" s="25"/>
       <c r="D104" s="5" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E104" s="1">
         <v>1</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>613</v>
-      </c>
-      <c r="G104" s="36"/>
+        <v>593</v>
+      </c>
+      <c r="G104" s="28"/>
       <c r="H104" s="15" t="s">
-        <v>410</v>
+        <v>335</v>
       </c>
     </row>
     <row r="105" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A105" s="32">
+      <c r="A105" s="42"/>
+      <c r="B105" s="30"/>
+      <c r="C105" s="29"/>
+      <c r="D105" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E105" s="1">
+        <v>1</v>
+      </c>
+      <c r="F105" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="G105" s="28"/>
+      <c r="H105" s="15" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A106" s="41">
         <v>29</v>
       </c>
-      <c r="B105" s="37" t="s">
+      <c r="B106" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C105" s="25" t="s">
+      <c r="C106" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="D105" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="E105" s="1">
-        <v>0</v>
-      </c>
-      <c r="F105" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="G105" s="36" t="s">
-        <v>553</v>
-      </c>
-      <c r="H105" s="15" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A106" s="33"/>
-      <c r="B106" s="37"/>
-      <c r="C106" s="25"/>
       <c r="D106" s="5" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E106" s="1">
         <v>0</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="G106" s="36"/>
+        <v>287</v>
+      </c>
+      <c r="G106" s="28" t="s">
+        <v>537</v>
+      </c>
       <c r="H106" s="15" t="s">
-        <v>411</v>
+        <v>336</v>
       </c>
     </row>
     <row r="107" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A107" s="32">
+      <c r="A107" s="42"/>
+      <c r="B107" s="30"/>
+      <c r="C107" s="29"/>
+      <c r="D107" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="E107" s="1">
+        <v>0</v>
+      </c>
+      <c r="F107" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="G107" s="28"/>
+      <c r="H107" s="15" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A108" s="34">
         <v>30</v>
       </c>
-      <c r="B107" s="37" t="s">
+      <c r="B108" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C107" s="25" t="s">
+      <c r="C108" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="D107" s="5" t="s">
+      <c r="D108" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E107" s="1">
-        <v>1</v>
-      </c>
-      <c r="F107" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="G107" s="36" t="s">
-        <v>227</v>
-      </c>
-      <c r="H107" s="15" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A108" s="33"/>
-      <c r="B108" s="37"/>
-      <c r="C108" s="25"/>
-      <c r="D108" s="5" t="s">
+      <c r="E108" s="1">
+        <v>1</v>
+      </c>
+      <c r="F108" s="5" t="s">
+        <v>644</v>
+      </c>
+      <c r="G108" s="28" t="s">
+        <v>223</v>
+      </c>
+      <c r="H108" s="15" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A109" s="35"/>
+      <c r="B109" s="30"/>
+      <c r="C109" s="29"/>
+      <c r="D109" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E108" s="1">
-        <v>1</v>
-      </c>
-      <c r="F108" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="G108" s="36"/>
-      <c r="H108" s="15" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A109" s="32">
+      <c r="E109" s="1">
+        <v>1</v>
+      </c>
+      <c r="F109" s="5" t="s">
+        <v>645</v>
+      </c>
+      <c r="G109" s="28"/>
+      <c r="H109" s="15" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A110" s="34">
         <v>31</v>
       </c>
-      <c r="B109" s="46" t="s">
+      <c r="B110" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="C109" s="39" t="s">
+      <c r="C110" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="D109" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="E109" s="1">
-        <v>1</v>
-      </c>
-      <c r="F109" s="5" t="s">
-        <v>573</v>
-      </c>
-      <c r="G109" s="48" t="s">
-        <v>276</v>
-      </c>
-      <c r="H109" s="15" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A110" s="33"/>
-      <c r="B110" s="47"/>
-      <c r="C110" s="40"/>
       <c r="D110" s="5" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E110" s="1">
         <v>1</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>574</v>
-      </c>
-      <c r="G110" s="49"/>
+        <v>646</v>
+      </c>
+      <c r="G110" s="46" t="s">
+        <v>269</v>
+      </c>
       <c r="H110" s="15" t="s">
-        <v>413</v>
+        <v>338</v>
       </c>
     </row>
     <row r="111" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A111" s="32">
+      <c r="A111" s="35"/>
+      <c r="B111" s="44"/>
+      <c r="C111" s="32"/>
+      <c r="D111" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="E111" s="1">
+        <v>1</v>
+      </c>
+      <c r="F111" s="5" t="s">
+        <v>647</v>
+      </c>
+      <c r="G111" s="47"/>
+      <c r="H111" s="15" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A112" s="41">
         <v>32</v>
       </c>
-      <c r="B111" s="37" t="s">
+      <c r="B112" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C111" s="35" t="s">
+      <c r="C112" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="D111" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="E111" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F111" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="G111" s="36"/>
-      <c r="H111" s="15" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A112" s="33"/>
-      <c r="B112" s="37"/>
-      <c r="C112" s="35"/>
       <c r="D112" s="5" t="s">
-        <v>52</v>
+        <v>228</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="G112" s="36"/>
+        <v>213</v>
+      </c>
+      <c r="G112" s="28"/>
       <c r="H112" s="15" t="s">
-        <v>414</v>
+        <v>339</v>
       </c>
     </row>
     <row r="113" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A113" s="32">
+      <c r="A113" s="42"/>
+      <c r="B113" s="30"/>
+      <c r="C113" s="45"/>
+      <c r="D113" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F113" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="G113" s="28"/>
+      <c r="H113" s="15" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A114" s="34">
         <v>33</v>
       </c>
-      <c r="B113" s="37" t="s">
+      <c r="B114" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C113" s="25" t="s">
+      <c r="C114" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="D113" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="E113" s="1">
-        <v>1</v>
-      </c>
-      <c r="F113" s="5" t="s">
-        <v>590</v>
-      </c>
-      <c r="G113" s="36"/>
-      <c r="H113" s="15" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A114" s="33"/>
-      <c r="B114" s="37"/>
-      <c r="C114" s="25"/>
       <c r="D114" s="5" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E114" s="1">
         <v>1</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>591</v>
-      </c>
-      <c r="G114" s="36"/>
+        <v>572</v>
+      </c>
+      <c r="G114" s="28"/>
       <c r="H114" s="15" t="s">
-        <v>415</v>
+        <v>340</v>
       </c>
     </row>
     <row r="115" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A115" s="32">
+      <c r="A115" s="35"/>
+      <c r="B115" s="30"/>
+      <c r="C115" s="29"/>
+      <c r="D115" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="E115" s="1">
+        <v>1</v>
+      </c>
+      <c r="F115" s="5" t="s">
+        <v>573</v>
+      </c>
+      <c r="G115" s="28"/>
+      <c r="H115" s="15" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A116" s="41">
         <v>34</v>
       </c>
-      <c r="B115" s="37" t="s">
+      <c r="B116" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C115" s="25" t="s">
+      <c r="C116" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="D115" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="E115" s="1">
-        <v>0</v>
-      </c>
-      <c r="F115" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="G115" s="36" t="s">
-        <v>227</v>
-      </c>
-      <c r="H115" s="15" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A116" s="33"/>
-      <c r="B116" s="37"/>
-      <c r="C116" s="25"/>
       <c r="D116" s="5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E116" s="1">
         <v>0</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="G116" s="36"/>
+        <v>201</v>
+      </c>
+      <c r="G116" s="28" t="s">
+        <v>223</v>
+      </c>
       <c r="H116" s="15" t="s">
-        <v>462</v>
+        <v>450</v>
       </c>
     </row>
     <row r="117" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A117" s="32">
-        <v>35</v>
-      </c>
-      <c r="B117" s="37" t="s">
-        <v>17</v>
-      </c>
-      <c r="C117" s="25" t="s">
-        <v>14</v>
-      </c>
+      <c r="A117" s="42"/>
+      <c r="B117" s="30"/>
+      <c r="C117" s="29"/>
       <c r="D117" s="5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E117" s="1">
         <v>0</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="G117" s="36" t="s">
-        <v>227</v>
-      </c>
+        <v>641</v>
+      </c>
+      <c r="G117" s="28"/>
       <c r="H117" s="15" t="s">
-        <v>350</v>
+        <v>451</v>
       </c>
     </row>
     <row r="118" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A118" s="33"/>
-      <c r="B118" s="37"/>
-      <c r="C118" s="25"/>
+      <c r="A118" s="41">
+        <v>35</v>
+      </c>
+      <c r="B118" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="C118" s="29" t="s">
+        <v>14</v>
+      </c>
       <c r="D118" s="5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E118" s="1">
         <v>0</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="G118" s="36"/>
+        <v>202</v>
+      </c>
+      <c r="G118" s="28" t="s">
+        <v>223</v>
+      </c>
       <c r="H118" s="15" t="s">
-        <v>416</v>
+        <v>341</v>
       </c>
     </row>
     <row r="119" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A119" s="32">
-        <v>36</v>
-      </c>
-      <c r="B119" s="37" t="s">
-        <v>17</v>
-      </c>
-      <c r="C119" s="25" t="s">
-        <v>14</v>
-      </c>
+      <c r="A119" s="42"/>
+      <c r="B119" s="30"/>
+      <c r="C119" s="29"/>
       <c r="D119" s="5" t="s">
-        <v>121</v>
+        <v>78</v>
       </c>
       <c r="E119" s="1">
         <v>0</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>506</v>
-      </c>
-      <c r="G119" s="36" t="s">
-        <v>257</v>
-      </c>
+        <v>642</v>
+      </c>
+      <c r="G119" s="28"/>
       <c r="H119" s="15" t="s">
-        <v>351</v>
+        <v>406</v>
       </c>
     </row>
     <row r="120" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A120" s="33"/>
-      <c r="B120" s="37"/>
-      <c r="C120" s="25"/>
+      <c r="A120" s="41">
+        <v>36</v>
+      </c>
+      <c r="B120" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="C120" s="29" t="s">
+        <v>14</v>
+      </c>
       <c r="D120" s="5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E120" s="1">
         <v>0</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>507</v>
-      </c>
-      <c r="G120" s="36"/>
+        <v>495</v>
+      </c>
+      <c r="G120" s="28" t="s">
+        <v>252</v>
+      </c>
       <c r="H120" s="15" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A121" s="32">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A121" s="42"/>
+      <c r="B121" s="30"/>
+      <c r="C121" s="29"/>
+      <c r="D121" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="E121" s="1">
+        <v>0</v>
+      </c>
+      <c r="F121" s="5" t="s">
+        <v>496</v>
+      </c>
+      <c r="G121" s="28"/>
+      <c r="H121" s="15" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A122" s="41">
         <v>37</v>
       </c>
-      <c r="B121" s="46" t="s">
+      <c r="B122" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="C121" s="25" t="s">
+      <c r="C122" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="D121" s="5" t="s">
+      <c r="D122" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="E122" s="1">
+        <v>2</v>
+      </c>
+      <c r="F122" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="E121" s="1">
-        <v>2</v>
-      </c>
-      <c r="F121" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="G121" s="36"/>
-      <c r="H121" s="15" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A122" s="33"/>
-      <c r="B122" s="47"/>
-      <c r="C122" s="25"/>
-      <c r="D122" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="E122" s="1">
-        <v>1</v>
-      </c>
-      <c r="F122" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="G122" s="36"/>
+      <c r="G122" s="28"/>
       <c r="H122" s="15" t="s">
-        <v>418</v>
+        <v>343</v>
       </c>
     </row>
     <row r="123" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A123" s="32">
+      <c r="A123" s="42"/>
+      <c r="B123" s="44"/>
+      <c r="C123" s="29"/>
+      <c r="D123" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="E123" s="1">
+        <v>1</v>
+      </c>
+      <c r="F123" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="G123" s="28"/>
+      <c r="H123" s="15" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A124" s="41">
         <v>38</v>
       </c>
-      <c r="B123" s="46" t="s">
+      <c r="B124" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="C123" s="25" t="s">
+      <c r="C124" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="D123" s="5" t="s">
+      <c r="D124" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E123" s="1">
-        <v>1</v>
-      </c>
-      <c r="F123" s="5" t="s">
-        <v>513</v>
-      </c>
-      <c r="G123" s="36"/>
-      <c r="H123" s="15" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A124" s="33"/>
-      <c r="B124" s="47"/>
-      <c r="C124" s="25"/>
-      <c r="D124" s="5" t="s">
+      <c r="E124" s="1">
+        <v>1</v>
+      </c>
+      <c r="F124" s="5" t="s">
+        <v>502</v>
+      </c>
+      <c r="G124" s="28"/>
+      <c r="H124" s="15" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A125" s="42"/>
+      <c r="B125" s="44"/>
+      <c r="C125" s="29"/>
+      <c r="D125" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E124" s="1">
-        <v>1</v>
-      </c>
-      <c r="F124" s="5" t="s">
-        <v>514</v>
-      </c>
-      <c r="G124" s="36"/>
-      <c r="H124" s="15" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A125" s="32">
+      <c r="E125" s="1">
+        <v>1</v>
+      </c>
+      <c r="F125" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="G125" s="28"/>
+      <c r="H125" s="15" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A126" s="41">
         <v>39</v>
       </c>
-      <c r="B125" s="46" t="s">
+      <c r="B126" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="C125" s="25" t="s">
+      <c r="C126" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="D125" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="E125" s="1">
-        <v>0</v>
-      </c>
-      <c r="F125" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="G125" s="36" t="s">
-        <v>555</v>
-      </c>
-      <c r="H125" s="15" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A126" s="33"/>
-      <c r="B126" s="47"/>
-      <c r="C126" s="25"/>
       <c r="D126" s="5" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E126" s="1">
         <v>0</v>
       </c>
       <c r="F126" s="5" t="s">
-        <v>602</v>
-      </c>
-      <c r="G126" s="36"/>
+        <v>229</v>
+      </c>
+      <c r="G126" s="28" t="s">
+        <v>539</v>
+      </c>
       <c r="H126" s="15" t="s">
-        <v>601</v>
+        <v>582</v>
       </c>
     </row>
     <row r="127" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A127" s="32">
+      <c r="A127" s="42"/>
+      <c r="B127" s="44"/>
+      <c r="C127" s="29"/>
+      <c r="D127" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="E127" s="1">
+        <v>0</v>
+      </c>
+      <c r="F127" s="5" t="s">
+        <v>584</v>
+      </c>
+      <c r="G127" s="28"/>
+      <c r="H127" s="15" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A128" s="41">
         <v>40</v>
       </c>
-      <c r="B127" s="46" t="s">
+      <c r="B128" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="C127" s="25" t="s">
+      <c r="C128" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="D127" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="E127" s="1">
-        <v>1</v>
-      </c>
-      <c r="F127" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="G127" s="36"/>
-      <c r="H127" s="15" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A128" s="33"/>
-      <c r="B128" s="47"/>
-      <c r="C128" s="25"/>
       <c r="D128" s="5" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E128" s="1">
         <v>1</v>
       </c>
       <c r="F128" s="5" t="s">
-        <v>522</v>
-      </c>
-      <c r="G128" s="36"/>
+        <v>251</v>
+      </c>
+      <c r="G128" s="28"/>
       <c r="H128" s="15" t="s">
-        <v>429</v>
+        <v>353</v>
       </c>
     </row>
     <row r="129" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A129" s="32">
+      <c r="A129" s="42"/>
+      <c r="B129" s="44"/>
+      <c r="C129" s="29"/>
+      <c r="D129" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="E129" s="1">
+        <v>1</v>
+      </c>
+      <c r="F129" s="5" t="s">
+        <v>511</v>
+      </c>
+      <c r="G129" s="28"/>
+      <c r="H129" s="15" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A130" s="41">
         <v>41</v>
       </c>
-      <c r="B129" s="46" t="s">
+      <c r="B130" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="C129" s="43" t="s">
+      <c r="C130" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="D129" s="5" t="s">
+      <c r="D130" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E129" s="1">
-        <v>1</v>
-      </c>
-      <c r="F129" s="5" t="s">
+      <c r="E130" s="1">
+        <v>1</v>
+      </c>
+      <c r="F130" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="G129" s="36"/>
-      <c r="H129" s="15" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A130" s="33"/>
-      <c r="B130" s="47"/>
-      <c r="C130" s="43"/>
-      <c r="D130" s="5" t="s">
+      <c r="G130" s="28"/>
+      <c r="H130" s="15" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A131" s="42"/>
+      <c r="B131" s="44"/>
+      <c r="C131" s="32"/>
+      <c r="D131" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="E130" s="1">
-        <v>1</v>
-      </c>
-      <c r="F130" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="G130" s="36"/>
-      <c r="H130" s="15" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="131" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A131" s="32">
+      <c r="E131" s="1">
+        <v>1</v>
+      </c>
+      <c r="F131" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="G131" s="28"/>
+      <c r="H131" s="15" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A132" s="41">
         <v>42</v>
       </c>
-      <c r="B131" s="38" t="s">
+      <c r="B132" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C131" s="25" t="s">
+      <c r="C132" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="D131" s="5" t="s">
+      <c r="D132" s="5" t="s">
         <v>50</v>
-      </c>
-      <c r="E131" s="1">
-        <v>0</v>
-      </c>
-      <c r="F131" s="5" t="s">
-        <v>606</v>
-      </c>
-      <c r="G131" s="36"/>
-      <c r="H131" s="15" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="132" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A132" s="33"/>
-      <c r="B132" s="38"/>
-      <c r="C132" s="25"/>
-      <c r="D132" s="5" t="s">
-        <v>51</v>
       </c>
       <c r="E132" s="1">
         <v>0</v>
       </c>
       <c r="F132" s="5" t="s">
-        <v>603</v>
-      </c>
-      <c r="G132" s="36"/>
+        <v>588</v>
+      </c>
+      <c r="G132" s="28"/>
       <c r="H132" s="15" t="s">
-        <v>605</v>
+        <v>586</v>
       </c>
     </row>
     <row r="133" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A133" s="32">
+      <c r="A133" s="42"/>
+      <c r="B133" s="33"/>
+      <c r="C133" s="29"/>
+      <c r="D133" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E133" s="1">
+        <v>0</v>
+      </c>
+      <c r="F133" s="5" t="s">
+        <v>585</v>
+      </c>
+      <c r="G133" s="28"/>
+      <c r="H133" s="15" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A134" s="41">
         <v>43</v>
       </c>
-      <c r="B133" s="38" t="s">
+      <c r="B134" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C133" s="25" t="s">
+      <c r="C134" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="D133" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="E133" s="1">
-        <v>1</v>
-      </c>
-      <c r="F133" s="5" t="s">
-        <v>618</v>
-      </c>
-      <c r="H133" s="15" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="134" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A134" s="33"/>
-      <c r="B134" s="38"/>
-      <c r="C134" s="25"/>
       <c r="D134" s="5" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E134" s="1">
+        <v>1</v>
+      </c>
+      <c r="F134" s="5" t="s">
+        <v>599</v>
+      </c>
+      <c r="H134" s="15" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A135" s="42"/>
+      <c r="B135" s="33"/>
+      <c r="C135" s="29"/>
+      <c r="D135" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="E135" s="1">
         <v>0</v>
       </c>
-      <c r="F134" s="5" t="s">
-        <v>618</v>
-      </c>
-      <c r="H134" s="15" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="135" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A135" s="32">
+      <c r="F135" s="5" t="s">
+        <v>599</v>
+      </c>
+      <c r="H135" s="15" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A136" s="41">
         <v>44</v>
       </c>
-      <c r="B135" s="38" t="s">
+      <c r="B136" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C135" s="25" t="s">
+      <c r="C136" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="D135" s="5" t="s">
+      <c r="D136" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E135" s="1">
-        <v>1</v>
-      </c>
-      <c r="F135" s="5" t="s">
-        <v>508</v>
-      </c>
-      <c r="G135" s="36"/>
-      <c r="H135" s="15" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="136" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A136" s="33"/>
-      <c r="B136" s="38"/>
-      <c r="C136" s="25"/>
-      <c r="D136" s="5" t="s">
+      <c r="E136" s="1">
+        <v>1</v>
+      </c>
+      <c r="F136" s="5" t="s">
+        <v>497</v>
+      </c>
+      <c r="G136" s="28"/>
+      <c r="H136" s="15" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A137" s="42"/>
+      <c r="B137" s="33"/>
+      <c r="C137" s="29"/>
+      <c r="D137" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="E136" s="1">
-        <v>1</v>
-      </c>
-      <c r="F136" s="5" t="s">
-        <v>509</v>
-      </c>
-      <c r="G136" s="36"/>
-      <c r="H136" s="15" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A137" s="32">
+      <c r="E137" s="1">
+        <v>1</v>
+      </c>
+      <c r="F137" s="5" t="s">
+        <v>498</v>
+      </c>
+      <c r="G137" s="28"/>
+      <c r="H137" s="15" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A138" s="41">
         <v>45</v>
       </c>
-      <c r="B137" s="38" t="s">
+      <c r="B138" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C137" s="35" t="s">
+      <c r="C138" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="D137" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="E137" s="1">
-        <v>1</v>
-      </c>
-      <c r="F137" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="G137" s="36"/>
-      <c r="H137" s="15" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="138" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A138" s="33"/>
-      <c r="B138" s="38"/>
-      <c r="C138" s="35"/>
       <c r="D138" s="5" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E138" s="1">
         <v>1</v>
       </c>
       <c r="F138" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="G138" s="36"/>
+        <v>217</v>
+      </c>
+      <c r="G138" s="28"/>
       <c r="H138" s="15" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
     </row>
     <row r="139" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A139" s="32">
+      <c r="A139" s="42"/>
+      <c r="B139" s="33"/>
+      <c r="C139" s="45"/>
+      <c r="D139" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="E139" s="1">
+        <v>1</v>
+      </c>
+      <c r="F139" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="G139" s="28"/>
+      <c r="H139" s="15" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A140" s="41">
         <v>46</v>
       </c>
-      <c r="B139" s="38" t="s">
+      <c r="B140" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C139" s="25" t="s">
+      <c r="C140" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="D139" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="E139" s="1">
-        <v>0</v>
-      </c>
-      <c r="F139" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="G139" s="36" t="s">
-        <v>219</v>
-      </c>
-      <c r="H139" s="15" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="140" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A140" s="33"/>
-      <c r="B140" s="38"/>
-      <c r="C140" s="25"/>
       <c r="D140" s="5" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="E140" s="1">
         <v>0</v>
       </c>
       <c r="F140" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="G140" s="36"/>
+        <v>139</v>
+      </c>
+      <c r="G140" s="28" t="s">
+        <v>215</v>
+      </c>
       <c r="H140" s="15" t="s">
-        <v>421</v>
+        <v>563</v>
       </c>
     </row>
     <row r="141" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A141" s="32">
+      <c r="A141" s="42"/>
+      <c r="B141" s="33"/>
+      <c r="C141" s="29"/>
+      <c r="D141" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="E141" s="1">
+        <v>0</v>
+      </c>
+      <c r="F141" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="G141" s="28"/>
+      <c r="H141" s="15" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A142" s="41">
         <v>47</v>
       </c>
-      <c r="B141" s="38" t="s">
+      <c r="B142" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C141" s="25" t="s">
+      <c r="C142" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="D141" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="E141" s="1">
-        <v>1</v>
-      </c>
-      <c r="F141" s="5" t="s">
-        <v>510</v>
-      </c>
-      <c r="G141" s="36" t="s">
-        <v>587</v>
-      </c>
-      <c r="H141" s="15" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="142" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A142" s="33"/>
-      <c r="B142" s="38"/>
-      <c r="C142" s="25"/>
       <c r="D142" s="5" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E142" s="1">
         <v>1</v>
       </c>
       <c r="F142" s="5" t="s">
-        <v>511</v>
-      </c>
-      <c r="G142" s="36"/>
+        <v>499</v>
+      </c>
+      <c r="G142" s="28" t="s">
+        <v>569</v>
+      </c>
       <c r="H142" s="15" t="s">
-        <v>422</v>
+        <v>346</v>
       </c>
     </row>
     <row r="143" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A143" s="32">
+      <c r="A143" s="42"/>
+      <c r="B143" s="33"/>
+      <c r="C143" s="29"/>
+      <c r="D143" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="E143" s="1">
+        <v>1</v>
+      </c>
+      <c r="F143" s="5" t="s">
+        <v>500</v>
+      </c>
+      <c r="G143" s="28"/>
+      <c r="H143" s="15" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A144" s="41">
         <v>48</v>
       </c>
-      <c r="B143" s="38" t="s">
+      <c r="B144" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C143" s="25" t="s">
+      <c r="C144" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="D143" s="5" t="s">
-        <v>575</v>
-      </c>
-      <c r="E143" s="1">
-        <v>1</v>
-      </c>
-      <c r="F143" s="5" t="s">
-        <v>512</v>
-      </c>
-      <c r="G143" s="36"/>
-      <c r="H143" s="15" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="144" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A144" s="33"/>
-      <c r="B144" s="38"/>
-      <c r="C144" s="25"/>
       <c r="D144" s="5" t="s">
+        <v>557</v>
+      </c>
+      <c r="E144" s="1">
+        <v>1</v>
+      </c>
+      <c r="F144" s="5" t="s">
+        <v>501</v>
+      </c>
+      <c r="G144" s="28"/>
+      <c r="H144" s="15" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A145" s="42"/>
+      <c r="B145" s="33"/>
+      <c r="C145" s="29"/>
+      <c r="D145" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="E144" s="1">
+      <c r="E145" s="1">
         <v>0</v>
       </c>
-      <c r="F144" s="5" t="s">
-        <v>512</v>
-      </c>
-      <c r="G144" s="36"/>
-      <c r="H144" s="15" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A145" s="32">
+      <c r="F145" s="5" t="s">
+        <v>501</v>
+      </c>
+      <c r="G145" s="28"/>
+      <c r="H145" s="15" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A146" s="41">
         <v>49</v>
       </c>
-      <c r="B145" s="38" t="s">
+      <c r="B146" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C145" s="35" t="s">
+      <c r="C146" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="D145" s="5" t="s">
+      <c r="D146" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="E145" s="1">
-        <v>1</v>
-      </c>
-      <c r="F145" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="G145" s="36" t="s">
-        <v>587</v>
-      </c>
-      <c r="H145" s="15" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="146" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A146" s="33"/>
-      <c r="B146" s="38"/>
-      <c r="C146" s="35"/>
-      <c r="D146" s="5" t="s">
+      <c r="E146" s="1">
+        <v>1</v>
+      </c>
+      <c r="F146" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="G146" s="28" t="s">
+        <v>569</v>
+      </c>
+      <c r="H146" s="15" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A147" s="42"/>
+      <c r="B147" s="33"/>
+      <c r="C147" s="45"/>
+      <c r="D147" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E146" s="1">
+      <c r="E147" s="1">
         <v>0</v>
       </c>
-      <c r="F146" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="G146" s="36"/>
-      <c r="H146" s="15" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="147" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A147" s="32">
+      <c r="F147" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="G147" s="28"/>
+      <c r="H147" s="15" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A148" s="34">
         <v>50</v>
       </c>
-      <c r="B147" s="38" t="s">
+      <c r="B148" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C147" s="43" t="s">
+      <c r="C148" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="D147" s="5" t="s">
+      <c r="D148" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="E147" s="1">
-        <v>1</v>
-      </c>
-      <c r="F147" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="G147" s="36"/>
-      <c r="H147" s="15" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="148" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A148" s="33"/>
-      <c r="B148" s="38"/>
-      <c r="C148" s="43"/>
-      <c r="D148" s="5" t="s">
+      <c r="E148" s="1">
+        <v>1</v>
+      </c>
+      <c r="F148" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="G148" s="28"/>
+      <c r="H148" s="15" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A149" s="35"/>
+      <c r="B149" s="33"/>
+      <c r="C149" s="32"/>
+      <c r="D149" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E148" s="1">
+      <c r="E149" s="1">
         <v>0</v>
       </c>
-      <c r="F148" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="G148" s="36"/>
-      <c r="H148" s="15" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="149" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A149" s="32">
+      <c r="F149" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="G149" s="28"/>
+      <c r="H149" s="15" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A150" s="34">
         <v>51</v>
       </c>
-      <c r="B149" s="38" t="s">
+      <c r="B150" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C149" s="25" t="s">
+      <c r="C150" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="D149" s="5" t="s">
+      <c r="D150" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="E150" s="1">
+        <v>1</v>
+      </c>
+      <c r="F150" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="E149" s="1">
-        <v>1</v>
-      </c>
-      <c r="F149" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="G149" s="36"/>
-      <c r="H149" s="15" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="150" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A150" s="33"/>
-      <c r="B150" s="38"/>
-      <c r="C150" s="25"/>
-      <c r="D150" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="E150" s="1">
-        <v>0</v>
-      </c>
-      <c r="F150" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="G150" s="36"/>
+      <c r="G150" s="28"/>
       <c r="H150" s="15" t="s">
-        <v>425</v>
+        <v>349</v>
       </c>
     </row>
     <row r="151" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A151" s="32">
-        <v>52</v>
-      </c>
-      <c r="B151" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="C151" s="25" t="s">
-        <v>14</v>
-      </c>
+      <c r="A151" s="35"/>
+      <c r="B151" s="33"/>
+      <c r="C151" s="29"/>
       <c r="D151" s="5" t="s">
-        <v>75</v>
+        <v>186</v>
       </c>
       <c r="E151" s="1">
         <v>0</v>
       </c>
       <c r="F151" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="G151" s="36"/>
+        <v>187</v>
+      </c>
+      <c r="G151" s="28"/>
       <c r="H151" s="15" t="s">
-        <v>459</v>
+        <v>415</v>
       </c>
     </row>
     <row r="152" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A152" s="33"/>
-      <c r="B152" s="38"/>
-      <c r="C152" s="25"/>
+      <c r="A152" s="41">
+        <v>52</v>
+      </c>
+      <c r="B152" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="C152" s="29" t="s">
+        <v>14</v>
+      </c>
       <c r="D152" s="5" t="s">
-        <v>198</v>
+        <v>73</v>
       </c>
       <c r="E152" s="1">
         <v>0</v>
       </c>
       <c r="F152" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="G152" s="36"/>
+        <v>74</v>
+      </c>
+      <c r="G152" s="28"/>
       <c r="H152" s="15" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
     </row>
     <row r="153" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A153" s="32">
-        <v>53</v>
-      </c>
-      <c r="B153" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="C153" s="25" t="s">
-        <v>14</v>
-      </c>
+      <c r="A153" s="42"/>
+      <c r="B153" s="33"/>
+      <c r="C153" s="29"/>
       <c r="D153" s="5" t="s">
-        <v>62</v>
+        <v>196</v>
       </c>
       <c r="E153" s="1">
         <v>0</v>
       </c>
       <c r="F153" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="G153" s="36" t="s">
-        <v>268</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="G153" s="28"/>
       <c r="H153" s="15" t="s">
-        <v>486</v>
+        <v>449</v>
       </c>
     </row>
     <row r="154" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A154" s="33"/>
-      <c r="B154" s="38"/>
-      <c r="C154" s="25"/>
+      <c r="A154" s="41">
+        <v>53</v>
+      </c>
+      <c r="B154" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="C154" s="29" t="s">
+        <v>14</v>
+      </c>
       <c r="D154" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E154" s="1">
         <v>0</v>
       </c>
       <c r="F154" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="G154" s="36"/>
+        <v>265</v>
+      </c>
+      <c r="G154" s="28" t="s">
+        <v>643</v>
+      </c>
       <c r="H154" s="15" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
     </row>
     <row r="155" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A155" s="32">
+      <c r="A155" s="42"/>
+      <c r="B155" s="33"/>
+      <c r="C155" s="29"/>
+      <c r="D155" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E155" s="1">
+        <v>0</v>
+      </c>
+      <c r="F155" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="G155" s="28"/>
+      <c r="H155" s="15" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A156" s="41">
         <v>54</v>
       </c>
-      <c r="B155" s="38" t="s">
+      <c r="B156" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C155" s="25" t="s">
+      <c r="C156" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="D155" s="5" t="s">
+      <c r="D156" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="E156" s="1">
+        <v>1</v>
+      </c>
+      <c r="F156" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="G156" s="28"/>
+      <c r="H156" s="15" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A157" s="42"/>
+      <c r="B157" s="33"/>
+      <c r="C157" s="29"/>
+      <c r="D157" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="E157" s="1">
+        <v>1</v>
+      </c>
+      <c r="F157" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="G157" s="28"/>
+      <c r="H157" s="15" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A158" s="41">
+        <v>55</v>
+      </c>
+      <c r="B158" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="C158" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="D158" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="E155" s="1">
-        <v>1</v>
-      </c>
-      <c r="F155" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="G155" s="36"/>
-      <c r="H155" s="15" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="156" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A156" s="33"/>
-      <c r="B156" s="38"/>
-      <c r="C156" s="25"/>
-      <c r="D156" s="5" t="s">
+      <c r="E158" s="1">
+        <v>1</v>
+      </c>
+      <c r="F158" s="5" t="s">
+        <v>591</v>
+      </c>
+      <c r="G158" s="28"/>
+      <c r="H158" s="15" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A159" s="42"/>
+      <c r="B159" s="33"/>
+      <c r="C159" s="29"/>
+      <c r="D159" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="E156" s="1">
-        <v>1</v>
-      </c>
-      <c r="F156" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="G156" s="36"/>
-      <c r="H156" s="15" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="157" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A157" s="32">
-        <v>55</v>
-      </c>
-      <c r="B157" s="38" t="s">
+      <c r="E159" s="1">
+        <v>1</v>
+      </c>
+      <c r="F159" s="5" t="s">
+        <v>592</v>
+      </c>
+      <c r="G159" s="28"/>
+      <c r="H159" s="15" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A160" s="41">
+        <v>56</v>
+      </c>
+      <c r="B160" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C157" s="25" t="s">
+      <c r="C160" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="D157" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="E157" s="1">
-        <v>1</v>
-      </c>
-      <c r="F157" s="5" t="s">
-        <v>610</v>
-      </c>
-      <c r="G157" s="36"/>
-      <c r="H157" s="15" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="158" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A158" s="33"/>
-      <c r="B158" s="38"/>
-      <c r="C158" s="25"/>
-      <c r="D158" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="E158" s="1">
-        <v>1</v>
-      </c>
-      <c r="F158" s="5" t="s">
-        <v>611</v>
-      </c>
-      <c r="G158" s="36"/>
-      <c r="H158" s="15" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="159" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A159" s="32">
-        <v>56</v>
-      </c>
-      <c r="B159" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="C159" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="D159" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="E159" s="1">
-        <v>1</v>
-      </c>
-      <c r="F159" s="5" t="s">
-        <v>609</v>
-      </c>
-      <c r="G159" s="36" t="s">
-        <v>558</v>
-      </c>
-      <c r="H159" s="15" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="160" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A160" s="33"/>
-      <c r="B160" s="38"/>
-      <c r="C160" s="25"/>
       <c r="D160" s="5" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E160" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F160" s="5" t="s">
-        <v>609</v>
-      </c>
-      <c r="G160" s="36"/>
+        <v>590</v>
+      </c>
+      <c r="G160" s="28" t="s">
+        <v>542</v>
+      </c>
       <c r="H160" s="15" t="s">
-        <v>430</v>
+        <v>354</v>
       </c>
     </row>
     <row r="161" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A161" s="32">
-        <v>57</v>
-      </c>
-      <c r="B161" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="C161" s="25" t="s">
-        <v>14</v>
-      </c>
+      <c r="A161" s="42"/>
+      <c r="B161" s="33"/>
+      <c r="C161" s="29"/>
       <c r="D161" s="5" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="E161" s="1">
         <v>0</v>
       </c>
       <c r="F161" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="G161" s="36" t="s">
-        <v>592</v>
-      </c>
+        <v>590</v>
+      </c>
+      <c r="G161" s="28"/>
       <c r="H161" s="15" t="s">
-        <v>364</v>
+        <v>420</v>
       </c>
     </row>
     <row r="162" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A162" s="33"/>
-      <c r="B162" s="38"/>
-      <c r="C162" s="25"/>
+      <c r="A162" s="41">
+        <v>57</v>
+      </c>
+      <c r="B162" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="C162" s="29" t="s">
+        <v>14</v>
+      </c>
       <c r="D162" s="5" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E162" s="1">
         <v>0</v>
       </c>
       <c r="F162" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="G162" s="36"/>
+        <v>292</v>
+      </c>
+      <c r="G162" s="28" t="s">
+        <v>574</v>
+      </c>
       <c r="H162" s="15" t="s">
-        <v>431</v>
+        <v>355</v>
       </c>
     </row>
     <row r="163" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A163" s="32">
-        <v>58</v>
-      </c>
-      <c r="B163" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="C163" s="35" t="s">
-        <v>14</v>
-      </c>
+      <c r="A163" s="42"/>
+      <c r="B163" s="33"/>
+      <c r="C163" s="29"/>
       <c r="D163" s="5" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E163" s="1">
         <v>0</v>
       </c>
       <c r="F163" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="G163" s="36"/>
+        <v>293</v>
+      </c>
+      <c r="G163" s="28"/>
       <c r="H163" s="15" t="s">
-        <v>365</v>
+        <v>421</v>
       </c>
     </row>
     <row r="164" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A164" s="33"/>
-      <c r="B164" s="38"/>
-      <c r="C164" s="35"/>
+      <c r="A164" s="41">
+        <v>58</v>
+      </c>
+      <c r="B164" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="C164" s="45" t="s">
+        <v>14</v>
+      </c>
       <c r="D164" s="5" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E164" s="1">
         <v>0</v>
       </c>
       <c r="F164" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="G164" s="36"/>
+        <v>294</v>
+      </c>
+      <c r="G164" s="28"/>
       <c r="H164" s="15" t="s">
-        <v>432</v>
+        <v>356</v>
       </c>
     </row>
     <row r="165" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A165" s="32">
+      <c r="A165" s="42"/>
+      <c r="B165" s="33"/>
+      <c r="C165" s="45"/>
+      <c r="D165" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="E165" s="1">
+        <v>0</v>
+      </c>
+      <c r="F165" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="G165" s="28"/>
+      <c r="H165" s="15" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A166" s="41">
         <v>59</v>
       </c>
-      <c r="B165" s="38" t="s">
+      <c r="B166" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C165" s="35" t="s">
+      <c r="C166" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="D165" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="E165" s="1">
-        <v>1</v>
-      </c>
-      <c r="F165" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="G165" s="36" t="s">
+      <c r="D166" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="E166" s="1">
+        <v>1</v>
+      </c>
+      <c r="F166" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="G166" s="28" t="s">
+        <v>197</v>
+      </c>
+      <c r="H166" s="15" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A167" s="42"/>
+      <c r="B167" s="33"/>
+      <c r="C167" s="45"/>
+      <c r="D167" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="E167" s="1">
+        <v>0</v>
+      </c>
+      <c r="F167" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="G167" s="28"/>
+      <c r="H167" s="15" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A168" s="41">
+        <v>60</v>
+      </c>
+      <c r="B168" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="C168" s="45" t="s">
+        <v>14</v>
+      </c>
+      <c r="D168" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="E168" s="1">
+        <v>1</v>
+      </c>
+      <c r="F168" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="G168" s="28"/>
+      <c r="H168" s="15" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A169" s="42"/>
+      <c r="B169" s="33"/>
+      <c r="C169" s="45"/>
+      <c r="D169" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="E169" s="1">
+        <v>1</v>
+      </c>
+      <c r="F169" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="G169" s="28"/>
+      <c r="H169" s="15" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A170" s="41">
+        <v>61</v>
+      </c>
+      <c r="B170" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="C170" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="D170" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E170" s="1">
+        <v>2</v>
+      </c>
+      <c r="F170" s="5" t="s">
+        <v>657</v>
+      </c>
+      <c r="G170" s="28"/>
+      <c r="H170" s="15" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A171" s="42"/>
+      <c r="B171" s="33"/>
+      <c r="C171" s="29"/>
+      <c r="D171" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E171" s="1">
+        <v>2</v>
+      </c>
+      <c r="F171" s="5" t="s">
+        <v>658</v>
+      </c>
+      <c r="G171" s="28"/>
+      <c r="H171" s="15" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A172" s="41">
+        <v>62</v>
+      </c>
+      <c r="B172" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="C172" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="D172" s="5" t="s">
+        <v>559</v>
+      </c>
+      <c r="E172" s="1">
+        <v>1</v>
+      </c>
+      <c r="F172" s="5" t="s">
+        <v>561</v>
+      </c>
+      <c r="G172" s="28"/>
+      <c r="H172" s="15" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A173" s="42"/>
+      <c r="B173" s="33"/>
+      <c r="C173" s="32"/>
+      <c r="D173" s="5" t="s">
+        <v>558</v>
+      </c>
+      <c r="E173" s="1">
+        <v>1</v>
+      </c>
+      <c r="F173" s="5" t="s">
+        <v>562</v>
+      </c>
+      <c r="G173" s="28"/>
+      <c r="H173" s="15" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A174" s="41">
+        <v>63</v>
+      </c>
+      <c r="B174" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="C174" s="45" t="s">
+        <v>14</v>
+      </c>
+      <c r="D174" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="H165" s="15" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="166" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A166" s="33"/>
-      <c r="B166" s="38"/>
-      <c r="C166" s="35"/>
-      <c r="D166" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="E166" s="1">
-        <v>0</v>
-      </c>
-      <c r="F166" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="G166" s="36"/>
-      <c r="H166" s="15" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="167" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A167" s="32">
+      <c r="E174" s="1">
+        <v>1</v>
+      </c>
+      <c r="F174" s="5" t="s">
+        <v>616</v>
+      </c>
+      <c r="G174" s="28" t="s">
+        <v>615</v>
+      </c>
+      <c r="H174" s="15" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A175" s="42"/>
+      <c r="B175" s="33"/>
+      <c r="C175" s="45"/>
+      <c r="D175" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="E175" s="1">
+        <v>1</v>
+      </c>
+      <c r="F175" s="5" t="s">
+        <v>617</v>
+      </c>
+      <c r="G175" s="28"/>
+      <c r="H175" s="15" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A176" s="41">
+        <v>64</v>
+      </c>
+      <c r="B176" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="C176" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="D176" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="E176" s="1">
+        <v>1</v>
+      </c>
+      <c r="F176" s="5" t="s">
+        <v>512</v>
+      </c>
+      <c r="G176" s="28" t="s">
+        <v>113</v>
+      </c>
+      <c r="H176" s="15" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A177" s="42"/>
+      <c r="B177" s="33"/>
+      <c r="C177" s="29"/>
+      <c r="D177" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="E177" s="1">
+        <v>1</v>
+      </c>
+      <c r="F177" s="5" t="s">
+        <v>513</v>
+      </c>
+      <c r="G177" s="28"/>
+      <c r="H177" s="15" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A178" s="41">
+        <v>65</v>
+      </c>
+      <c r="B178" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="C178" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="D178" s="5" t="s">
+        <v>652</v>
+      </c>
+      <c r="E178" s="1">
+        <v>1</v>
+      </c>
+      <c r="F178" s="5" t="s">
+        <v>651</v>
+      </c>
+      <c r="G178" s="28"/>
+      <c r="H178" s="15" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A179" s="42"/>
+      <c r="B179" s="31"/>
+      <c r="C179" s="29"/>
+      <c r="D179" s="5" t="s">
+        <v>655</v>
+      </c>
+      <c r="E179" s="1">
+        <v>1</v>
+      </c>
+      <c r="F179" s="5" t="s">
+        <v>656</v>
+      </c>
+      <c r="G179" s="28"/>
+      <c r="H179" s="15" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A180" s="41">
+        <v>66</v>
+      </c>
+      <c r="B180" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="C180" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="D180" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B167" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="C167" s="35" t="s">
+      <c r="E180" s="1">
+        <v>1</v>
+      </c>
+      <c r="F180" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="G180" s="28"/>
+      <c r="H180" s="15" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A181" s="42"/>
+      <c r="B181" s="31"/>
+      <c r="C181" s="29"/>
+      <c r="D181" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E181" s="1">
+        <v>1</v>
+      </c>
+      <c r="F181" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="G181" s="28"/>
+      <c r="H181" s="15" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A182" s="41">
+        <v>67</v>
+      </c>
+      <c r="B182" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="C182" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="D167" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="E167" s="1">
-        <v>1</v>
-      </c>
-      <c r="F167" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="G167" s="36"/>
-      <c r="H167" s="15" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="168" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A168" s="33"/>
-      <c r="B168" s="38"/>
-      <c r="C168" s="35"/>
-      <c r="D168" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="E168" s="1">
-        <v>1</v>
-      </c>
-      <c r="F168" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="G168" s="36"/>
-      <c r="H168" s="15" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="169" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A169" s="32">
-        <v>61</v>
-      </c>
-      <c r="B169" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="C169" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="D169" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="E169" s="1">
-        <v>1</v>
-      </c>
-      <c r="F169" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="G169" s="36"/>
-      <c r="H169" s="15" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="170" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A170" s="33"/>
-      <c r="B170" s="38"/>
-      <c r="C170" s="25"/>
-      <c r="D170" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="E170" s="1">
-        <v>0</v>
-      </c>
-      <c r="F170" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="G170" s="36"/>
-      <c r="H170" s="15" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="171" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A171" s="32">
-        <v>62</v>
-      </c>
-      <c r="B171" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="C171" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="D171" s="5" t="s">
-        <v>577</v>
-      </c>
-      <c r="E171" s="1">
-        <v>1</v>
-      </c>
-      <c r="F171" s="5" t="s">
-        <v>579</v>
-      </c>
-      <c r="G171" s="36"/>
-      <c r="H171" s="15" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="172" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A172" s="33"/>
-      <c r="B172" s="38"/>
-      <c r="C172" s="43"/>
-      <c r="D172" s="5" t="s">
-        <v>576</v>
-      </c>
-      <c r="E172" s="1">
-        <v>1</v>
-      </c>
-      <c r="F172" s="5" t="s">
-        <v>580</v>
-      </c>
-      <c r="G172" s="36"/>
-      <c r="H172" s="15" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="173" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A173" s="32">
-        <v>63</v>
-      </c>
-      <c r="B173" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="C173" s="35" t="s">
-        <v>14</v>
-      </c>
-      <c r="D173" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="E173" s="1">
-        <v>1</v>
-      </c>
-      <c r="F173" s="5" t="s">
-        <v>637</v>
-      </c>
-      <c r="G173" s="36" t="s">
-        <v>636</v>
-      </c>
-      <c r="H173" s="15" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="174" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A174" s="33"/>
-      <c r="B174" s="38"/>
-      <c r="C174" s="35"/>
-      <c r="D174" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="E174" s="1">
-        <v>1</v>
-      </c>
-      <c r="F174" s="5" t="s">
-        <v>638</v>
-      </c>
-      <c r="G174" s="36"/>
-      <c r="H174" s="15" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="175" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A175" s="32">
-        <v>64</v>
-      </c>
-      <c r="B175" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="C175" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="D175" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="E175" s="1">
-        <v>1</v>
-      </c>
-      <c r="F175" s="5" t="s">
-        <v>523</v>
-      </c>
-      <c r="G175" s="36" t="s">
-        <v>115</v>
-      </c>
-      <c r="H175" s="15" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="176" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A176" s="33"/>
-      <c r="B176" s="38"/>
-      <c r="C176" s="25"/>
-      <c r="D176" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="E176" s="1">
-        <v>1</v>
-      </c>
-      <c r="F176" s="5" t="s">
-        <v>524</v>
-      </c>
-      <c r="G176" s="36"/>
-      <c r="H176" s="15" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="177" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A177" s="32">
-        <v>65</v>
-      </c>
-      <c r="B177" s="34" t="s">
-        <v>29</v>
-      </c>
-      <c r="C177" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="D177" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="E177" s="1">
-        <v>1</v>
-      </c>
-      <c r="F177" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="G177" s="36"/>
-      <c r="H177" s="15" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="178" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A178" s="33"/>
-      <c r="B178" s="34"/>
-      <c r="C178" s="25"/>
-      <c r="D178" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="E178" s="1">
-        <v>0</v>
-      </c>
-      <c r="F178" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="G178" s="36"/>
-      <c r="H178" s="15" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="179" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A179" s="32">
-        <v>66</v>
-      </c>
-      <c r="B179" s="34" t="s">
-        <v>29</v>
-      </c>
-      <c r="C179" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="D179" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E179" s="1">
-        <v>1</v>
-      </c>
-      <c r="F179" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="G179" s="36"/>
-      <c r="H179" s="15" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="180" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A180" s="33"/>
-      <c r="B180" s="34"/>
-      <c r="C180" s="25"/>
-      <c r="D180" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E180" s="1">
-        <v>1</v>
-      </c>
-      <c r="F180" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="G180" s="36"/>
-      <c r="H180" s="15" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="181" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A181" s="32">
-        <v>67</v>
-      </c>
-      <c r="B181" s="34" t="s">
-        <v>29</v>
-      </c>
-      <c r="C181" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="D181" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="E181" s="1">
-        <v>3</v>
-      </c>
-      <c r="F181" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="G181" s="36"/>
-      <c r="H181" s="15" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="182" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A182" s="33"/>
-      <c r="B182" s="34"/>
-      <c r="C182" s="25"/>
       <c r="D182" s="5" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E182" s="1">
         <v>3</v>
       </c>
       <c r="F182" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="G182" s="36"/>
+        <v>205</v>
+      </c>
+      <c r="G182" s="28"/>
       <c r="H182" s="15" t="s">
-        <v>439</v>
+        <v>362</v>
       </c>
     </row>
     <row r="183" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A183" s="32">
-        <v>68</v>
-      </c>
-      <c r="B183" s="34" t="s">
-        <v>29</v>
-      </c>
-      <c r="C183" s="25" t="s">
-        <v>14</v>
-      </c>
+      <c r="A183" s="42"/>
+      <c r="B183" s="31"/>
+      <c r="C183" s="29"/>
       <c r="D183" s="5" t="s">
-        <v>228</v>
+        <v>70</v>
       </c>
       <c r="E183" s="1">
         <v>3</v>
       </c>
-      <c r="F183" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="G183" s="36"/>
+      <c r="F183" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="G183" s="28"/>
       <c r="H183" s="15" t="s">
-        <v>582</v>
+        <v>428</v>
       </c>
     </row>
     <row r="184" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A184" s="33"/>
-      <c r="B184" s="34"/>
-      <c r="C184" s="25"/>
+      <c r="A184" s="41">
+        <v>68</v>
+      </c>
+      <c r="B184" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="C184" s="29" t="s">
+        <v>14</v>
+      </c>
       <c r="D184" s="5" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="E184" s="1">
+        <v>3</v>
+      </c>
+      <c r="F184" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="G184" s="28"/>
+      <c r="H184" s="15" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A185" s="42"/>
+      <c r="B185" s="31"/>
+      <c r="C185" s="29"/>
+      <c r="D185" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="E185" s="1">
         <v>2</v>
       </c>
-      <c r="F184" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="G184" s="36"/>
-      <c r="H184" s="15" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="185" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A185" s="32">
+      <c r="F185" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="G185" s="28"/>
+      <c r="H185" s="15" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A186" s="41">
         <v>69</v>
       </c>
-      <c r="B185" s="34" t="s">
+      <c r="B186" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C185" s="25" t="s">
+      <c r="C186" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="D185" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="E185" s="1">
+      <c r="D186" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E186" s="1">
         <v>3</v>
       </c>
-      <c r="F185" s="5" t="s">
-        <v>608</v>
-      </c>
-      <c r="G185" s="36"/>
-      <c r="H185" s="15" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="186" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A186" s="33"/>
-      <c r="B186" s="34"/>
-      <c r="C186" s="25"/>
-      <c r="D186" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E186" s="1">
+      <c r="F186" s="5" t="s">
+        <v>589</v>
+      </c>
+      <c r="G186" s="28"/>
+      <c r="H186" s="15" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A187" s="42"/>
+      <c r="B187" s="31"/>
+      <c r="C187" s="29"/>
+      <c r="D187" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="E187" s="1">
         <v>2</v>
       </c>
-      <c r="F186" s="5" t="s">
-        <v>608</v>
-      </c>
-      <c r="G186" s="36"/>
-      <c r="H186" s="15" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="187" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A187" s="32">
+      <c r="F187" s="5" t="s">
+        <v>589</v>
+      </c>
+      <c r="G187" s="28"/>
+      <c r="H187" s="15" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A188" s="41">
         <v>70</v>
       </c>
-      <c r="B187" s="34" t="s">
+      <c r="B188" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C187" s="35" t="s">
+      <c r="C188" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="D187" s="5" t="s">
-        <v>472</v>
-      </c>
-      <c r="E187" s="1">
-        <v>0</v>
-      </c>
-      <c r="F187" s="5" t="s">
-        <v>469</v>
-      </c>
-      <c r="G187" s="36"/>
-      <c r="H187" s="15" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="188" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A188" s="33"/>
-      <c r="B188" s="34"/>
-      <c r="C188" s="35"/>
       <c r="D188" s="5" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="E188" s="1">
         <v>0</v>
       </c>
       <c r="F188" s="5" t="s">
-        <v>470</v>
-      </c>
-      <c r="G188" s="36"/>
+        <v>458</v>
+      </c>
+      <c r="G188" s="28"/>
       <c r="H188" s="15" t="s">
-        <v>474</v>
+        <v>462</v>
       </c>
     </row>
     <row r="189" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A189" s="32">
-        <v>71</v>
-      </c>
-      <c r="B189" s="34" t="s">
-        <v>29</v>
-      </c>
-      <c r="C189" s="35" t="s">
-        <v>14</v>
-      </c>
+      <c r="A189" s="42"/>
+      <c r="B189" s="31"/>
+      <c r="C189" s="45"/>
       <c r="D189" s="5" t="s">
-        <v>87</v>
+        <v>460</v>
       </c>
       <c r="E189" s="1">
         <v>0</v>
       </c>
       <c r="F189" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="G189" s="36" t="s">
-        <v>587</v>
-      </c>
+        <v>459</v>
+      </c>
+      <c r="G189" s="28"/>
       <c r="H189" s="15" t="s">
-        <v>373</v>
+        <v>463</v>
       </c>
     </row>
     <row r="190" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A190" s="33"/>
-      <c r="B190" s="34"/>
-      <c r="C190" s="35"/>
+      <c r="A190" s="41">
+        <v>71</v>
+      </c>
+      <c r="B190" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="C190" s="45" t="s">
+        <v>14</v>
+      </c>
       <c r="D190" s="5" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E190" s="1">
         <v>0</v>
       </c>
       <c r="F190" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="G190" s="36"/>
+        <v>270</v>
+      </c>
+      <c r="G190" s="28" t="s">
+        <v>569</v>
+      </c>
       <c r="H190" s="15" t="s">
-        <v>440</v>
+        <v>363</v>
       </c>
     </row>
     <row r="191" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A191" s="32">
+      <c r="A191" s="42"/>
+      <c r="B191" s="31"/>
+      <c r="C191" s="45"/>
+      <c r="D191" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E191" s="1">
+        <v>0</v>
+      </c>
+      <c r="F191" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="G191" s="28"/>
+      <c r="H191" s="15" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A192" s="41">
         <v>72</v>
       </c>
-      <c r="B191" s="34" t="s">
+      <c r="B192" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C191" s="35" t="s">
+      <c r="C192" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="D191" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="E191" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F191" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="G191" s="36"/>
-      <c r="H191" s="15" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="192" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A192" s="33"/>
-      <c r="B192" s="34"/>
-      <c r="C192" s="35"/>
       <c r="D192" s="5" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E192" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F192" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="G192" s="36"/>
+        <v>226</v>
+      </c>
+      <c r="G192" s="28"/>
       <c r="H192" s="15" t="s">
-        <v>441</v>
+        <v>364</v>
       </c>
     </row>
     <row r="193" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A193" s="32">
+      <c r="A193" s="42"/>
+      <c r="B193" s="31"/>
+      <c r="C193" s="45"/>
+      <c r="D193" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="E193" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F193" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="G193" s="28"/>
+      <c r="H193" s="15" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A194" s="41">
         <v>73</v>
       </c>
-      <c r="B193" s="34" t="s">
+      <c r="B194" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C193" s="25" t="s">
+      <c r="C194" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="D193" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="E193" s="1">
-        <v>4</v>
-      </c>
-      <c r="F193" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="G193" s="36" t="s">
-        <v>218</v>
-      </c>
-      <c r="H193" s="15" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="194" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A194" s="33"/>
-      <c r="B194" s="34"/>
-      <c r="C194" s="25"/>
       <c r="D194" s="5" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E194" s="1">
         <v>4</v>
       </c>
       <c r="F194" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="G194" s="36"/>
+        <v>296</v>
+      </c>
+      <c r="G194" s="28" t="s">
+        <v>214</v>
+      </c>
       <c r="H194" s="15" t="s">
-        <v>442</v>
+        <v>365</v>
       </c>
     </row>
     <row r="195" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A195" s="32">
+      <c r="A195" s="42"/>
+      <c r="B195" s="31"/>
+      <c r="C195" s="29"/>
+      <c r="D195" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="E195" s="1">
+        <v>4</v>
+      </c>
+      <c r="F195" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="G195" s="28"/>
+      <c r="H195" s="15" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A196" s="41">
         <v>74</v>
       </c>
-      <c r="B195" s="34" t="s">
+      <c r="B196" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C195" s="25" t="s">
+      <c r="C196" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="D195" s="5" t="s">
+      <c r="D196" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E196" s="1">
+        <v>1</v>
+      </c>
+      <c r="F196" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="G196" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="H196" s="15" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A197" s="42"/>
+      <c r="B197" s="31"/>
+      <c r="C197" s="29"/>
+      <c r="D197" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E197" s="1">
+        <v>1</v>
+      </c>
+      <c r="F197" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="G197" s="28"/>
+      <c r="H197" s="15" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A198" s="34">
+        <v>75</v>
+      </c>
+      <c r="B198" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="C198" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="D198" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E198" s="1">
+        <v>2</v>
+      </c>
+      <c r="F198" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="G198" s="28" t="s">
+        <v>605</v>
+      </c>
+      <c r="H198" s="15" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A199" s="35"/>
+      <c r="B199" s="33"/>
+      <c r="C199" s="29"/>
+      <c r="D199" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E199" s="1">
+        <v>1</v>
+      </c>
+      <c r="F199" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="G199" s="28"/>
+      <c r="H199" s="15" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A200" s="41">
+        <v>76</v>
+      </c>
+      <c r="B200" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="C200" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="D200" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E200" s="1">
+        <v>1</v>
+      </c>
+      <c r="F200" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="G200" s="28" t="s">
+        <v>221</v>
+      </c>
+      <c r="H200" s="15" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A201" s="42"/>
+      <c r="B201" s="33"/>
+      <c r="C201" s="29"/>
+      <c r="D201" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="E201" s="1">
+        <v>1</v>
+      </c>
+      <c r="F201" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="G201" s="28"/>
+      <c r="H201" s="15" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A202" s="34">
+        <v>77</v>
+      </c>
+      <c r="B202" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="C202" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="D202" s="5" t="s">
         <v>109</v>
-      </c>
-      <c r="E195" s="1">
-        <v>1</v>
-      </c>
-      <c r="F195" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="G195" s="36" t="s">
-        <v>143</v>
-      </c>
-      <c r="H195" s="15" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="196" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A196" s="33"/>
-      <c r="B196" s="34"/>
-      <c r="C196" s="25"/>
-      <c r="D196" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="E196" s="1">
-        <v>1</v>
-      </c>
-      <c r="F196" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="G196" s="36"/>
-      <c r="H196" s="15" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="197" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A197" s="41">
-        <v>75</v>
-      </c>
-      <c r="B197" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="C197" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D197" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="E197" s="1">
-        <v>2</v>
-      </c>
-      <c r="F197" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="G197" s="36" t="s">
-        <v>626</v>
-      </c>
-      <c r="H197" s="15" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="198" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A198" s="42"/>
-      <c r="B198" s="38"/>
-      <c r="C198" s="25"/>
-      <c r="D198" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="E198" s="1">
-        <v>1</v>
-      </c>
-      <c r="F198" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="G198" s="36"/>
-      <c r="H198" s="15" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="199" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A199" s="32">
-        <v>76</v>
-      </c>
-      <c r="B199" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="C199" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D199" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="E199" s="1">
-        <v>1</v>
-      </c>
-      <c r="F199" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="G199" s="36" t="s">
-        <v>225</v>
-      </c>
-      <c r="H199" s="15" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="200" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A200" s="33"/>
-      <c r="B200" s="38"/>
-      <c r="C200" s="25"/>
-      <c r="D200" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="E200" s="1">
-        <v>1</v>
-      </c>
-      <c r="F200" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="G200" s="36"/>
-      <c r="H200" s="15" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="201" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A201" s="41">
-        <v>77</v>
-      </c>
-      <c r="B201" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="C201" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D201" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="E201" s="1">
-        <v>2</v>
-      </c>
-      <c r="F201" s="5" t="s">
-        <v>594</v>
-      </c>
-      <c r="G201" s="36" t="s">
-        <v>624</v>
-      </c>
-      <c r="H201" s="15" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="202" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A202" s="42"/>
-      <c r="B202" s="38"/>
-      <c r="C202" s="25"/>
-      <c r="D202" s="5" t="s">
-        <v>112</v>
       </c>
       <c r="E202" s="1">
         <v>2</v>
       </c>
       <c r="F202" s="5" t="s">
-        <v>595</v>
-      </c>
-      <c r="G202" s="36"/>
+        <v>576</v>
+      </c>
+      <c r="G202" s="28" t="s">
+        <v>603</v>
+      </c>
       <c r="H202" s="15" t="s">
-        <v>444</v>
+        <v>367</v>
       </c>
     </row>
     <row r="203" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A203" s="32">
+      <c r="A203" s="35"/>
+      <c r="B203" s="33"/>
+      <c r="C203" s="29"/>
+      <c r="D203" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E203" s="1">
+        <v>2</v>
+      </c>
+      <c r="F203" s="5" t="s">
+        <v>577</v>
+      </c>
+      <c r="G203" s="28"/>
+      <c r="H203" s="15" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A204" s="41">
         <v>78</v>
       </c>
-      <c r="B203" s="38" t="s">
+      <c r="B204" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C203" s="25" t="s">
+      <c r="C204" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="D204" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E204" s="1">
+        <v>1</v>
+      </c>
+      <c r="F204" s="5" t="s">
+        <v>611</v>
+      </c>
+      <c r="G204" s="28"/>
+      <c r="H204" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A205" s="42"/>
+      <c r="B205" s="33"/>
+      <c r="C205" s="29"/>
+      <c r="D205" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="D203" s="5" t="s">
+      <c r="E205" s="1">
+        <v>1</v>
+      </c>
+      <c r="F205" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="G205" s="28"/>
+      <c r="H205" s="15" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A206" s="41">
+        <v>79</v>
+      </c>
+      <c r="B206" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="C206" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="D206" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="E203" s="1">
-        <v>1</v>
-      </c>
-      <c r="F203" s="5" t="s">
-        <v>632</v>
-      </c>
-      <c r="G203" s="36"/>
-      <c r="H203" s="15" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="204" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A204" s="33"/>
-      <c r="B204" s="38"/>
-      <c r="C204" s="25"/>
-      <c r="D204" s="5" t="s">
+      <c r="E206" s="1">
+        <v>1</v>
+      </c>
+      <c r="F206" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="G206" s="28"/>
+      <c r="H206" s="15" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A207" s="42"/>
+      <c r="B207" s="33"/>
+      <c r="C207" s="29"/>
+      <c r="D207" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="E204" s="1">
-        <v>1</v>
-      </c>
-      <c r="F204" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="G204" s="36"/>
-      <c r="H204" s="15" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="205" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A205" s="32">
-        <v>79</v>
-      </c>
-      <c r="B205" s="38" t="s">
+      <c r="E207" s="1">
+        <v>0</v>
+      </c>
+      <c r="F207" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="G207" s="28"/>
+      <c r="H207" s="15" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A208" s="41">
+        <v>80</v>
+      </c>
+      <c r="B208" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C205" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D205" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="E205" s="1">
-        <v>1</v>
-      </c>
-      <c r="F205" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="G205" s="36"/>
-      <c r="H205" s="15" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="206" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A206" s="33"/>
-      <c r="B206" s="38"/>
-      <c r="C206" s="25"/>
-      <c r="D206" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="E206" s="1">
+      <c r="C208" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="D208" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="E208" s="1">
+        <v>1</v>
+      </c>
+      <c r="F208" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="G208" s="28" t="s">
+        <v>241</v>
+      </c>
+      <c r="H208" s="15" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A209" s="42"/>
+      <c r="B209" s="33"/>
+      <c r="C209" s="29"/>
+      <c r="D209" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E209" s="1">
+        <v>1</v>
+      </c>
+      <c r="F209" s="5" t="s">
+        <v>600</v>
+      </c>
+      <c r="G209" s="28"/>
+      <c r="H209" s="15" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A210" s="34">
+        <v>81</v>
+      </c>
+      <c r="B210" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="C210" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="D210" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E210" s="1">
+        <v>1</v>
+      </c>
+      <c r="F210" s="5" t="s">
+        <v>634</v>
+      </c>
+      <c r="G210" s="28" t="s">
+        <v>601</v>
+      </c>
+      <c r="H210" s="15" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A211" s="35"/>
+      <c r="B211" s="33"/>
+      <c r="C211" s="29"/>
+      <c r="D211" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E211" s="1">
+        <v>1</v>
+      </c>
+      <c r="F211" s="5" t="s">
+        <v>635</v>
+      </c>
+      <c r="G211" s="28"/>
+      <c r="H211" s="15" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A212" s="41">
+        <v>82</v>
+      </c>
+      <c r="B212" s="48" t="s">
+        <v>29</v>
+      </c>
+      <c r="C212" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="D212" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="E212" s="1">
+        <v>1</v>
+      </c>
+      <c r="F212" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="G212" s="28"/>
+      <c r="H212" s="15" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A213" s="42"/>
+      <c r="B213" s="49"/>
+      <c r="C213" s="29"/>
+      <c r="D213" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="E213" s="1">
         <v>0</v>
       </c>
-      <c r="F206" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="G206" s="36"/>
-      <c r="H206" s="15" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="207" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A207" s="32">
-        <v>80</v>
-      </c>
-      <c r="B207" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="C207" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D207" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="E207" s="1">
-        <v>1</v>
-      </c>
-      <c r="F207" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="G207" s="36" t="s">
-        <v>245</v>
-      </c>
-      <c r="H207" s="15" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="208" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A208" s="33"/>
-      <c r="B208" s="38"/>
-      <c r="C208" s="25"/>
-      <c r="D208" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="E208" s="1">
-        <v>1</v>
-      </c>
-      <c r="F208" s="5" t="s">
-        <v>621</v>
-      </c>
-      <c r="G208" s="36"/>
-      <c r="H208" s="15" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="209" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A209" s="41">
-        <v>81</v>
-      </c>
-      <c r="B209" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="C209" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D209" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="E209" s="1">
-        <v>1</v>
-      </c>
-      <c r="F209" s="5" t="s">
-        <v>655</v>
-      </c>
-      <c r="G209" s="36" t="s">
-        <v>622</v>
-      </c>
-      <c r="H209" s="15" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="210" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A210" s="42"/>
-      <c r="B210" s="38"/>
-      <c r="C210" s="25"/>
-      <c r="D210" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="E210" s="1">
-        <v>1</v>
-      </c>
-      <c r="F210" s="5" t="s">
-        <v>656</v>
-      </c>
-      <c r="G210" s="36"/>
-      <c r="H210" s="15" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="211" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A211" s="32">
-        <v>82</v>
-      </c>
-      <c r="B211" s="44" t="s">
+      <c r="F213" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="G213" s="28"/>
+      <c r="H213" s="15" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A214" s="41">
+        <v>83</v>
+      </c>
+      <c r="B214" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C211" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D211" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="E211" s="1">
-        <v>1</v>
-      </c>
-      <c r="F211" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="G211" s="36"/>
-      <c r="H211" s="15" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="212" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A212" s="33"/>
-      <c r="B212" s="45"/>
-      <c r="C212" s="25"/>
-      <c r="D212" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="E212" s="1">
-        <v>0</v>
-      </c>
-      <c r="F212" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="G212" s="36"/>
-      <c r="H212" s="15" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="213" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A213" s="32">
-        <v>83</v>
-      </c>
-      <c r="B213" s="34" t="s">
+      <c r="C214" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="D214" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="E214" s="1">
+        <v>2</v>
+      </c>
+      <c r="F214" s="5" t="s">
+        <v>568</v>
+      </c>
+      <c r="G214" s="28" t="s">
+        <v>604</v>
+      </c>
+      <c r="H214" s="15" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A215" s="42"/>
+      <c r="B215" s="31"/>
+      <c r="C215" s="29"/>
+      <c r="D215" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E215" s="1">
+        <v>1</v>
+      </c>
+      <c r="F215" s="5" t="s">
+        <v>575</v>
+      </c>
+      <c r="G215" s="28"/>
+      <c r="H215" s="15" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A216" s="41">
+        <v>84</v>
+      </c>
+      <c r="B216" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C213" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D213" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="E213" s="1">
-        <v>2</v>
-      </c>
-      <c r="F213" s="5" t="s">
-        <v>586</v>
-      </c>
-      <c r="G213" s="36" t="s">
-        <v>625</v>
-      </c>
-      <c r="H213" s="15" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="214" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A214" s="33"/>
-      <c r="B214" s="34"/>
-      <c r="C214" s="25"/>
-      <c r="D214" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="E214" s="1">
-        <v>1</v>
-      </c>
-      <c r="F214" s="5" t="s">
-        <v>593</v>
-      </c>
-      <c r="G214" s="36"/>
-      <c r="H214" s="15" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="215" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A215" s="32">
-        <v>84</v>
-      </c>
-      <c r="B215" s="34" t="s">
-        <v>29</v>
-      </c>
-      <c r="C215" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D215" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="E215" s="1">
-        <v>2</v>
-      </c>
-      <c r="F215" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="G215" s="36" t="s">
-        <v>309</v>
-      </c>
-      <c r="H215" s="15" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="216" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A216" s="33"/>
-      <c r="B216" s="34"/>
-      <c r="C216" s="25"/>
+      <c r="C216" s="29" t="s">
+        <v>87</v>
+      </c>
       <c r="D216" s="5" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E216" s="1">
         <v>2</v>
       </c>
       <c r="F216" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="G216" s="36"/>
+        <v>249</v>
+      </c>
+      <c r="G216" s="28" t="s">
+        <v>300</v>
+      </c>
       <c r="H216" s="15" t="s">
-        <v>449</v>
+        <v>371</v>
       </c>
     </row>
     <row r="217" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A217" s="32">
+      <c r="A217" s="42"/>
+      <c r="B217" s="31"/>
+      <c r="C217" s="29"/>
+      <c r="D217" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E217" s="1">
+        <v>2</v>
+      </c>
+      <c r="F217" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="G217" s="28"/>
+      <c r="H217" s="15" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A218" s="41">
         <v>85</v>
       </c>
-      <c r="B217" s="34" t="s">
+      <c r="B218" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C217" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D217" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="E217" s="1">
+      <c r="C218" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="D218" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E218" s="1">
         <v>3</v>
       </c>
-      <c r="F217" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="G217" s="36"/>
-      <c r="H217" s="15" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="218" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A218" s="33"/>
-      <c r="B218" s="34"/>
-      <c r="C218" s="25"/>
-      <c r="D218" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="E218" s="1">
-        <v>2</v>
-      </c>
       <c r="F218" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="G218" s="36"/>
+        <v>218</v>
+      </c>
+      <c r="G218" s="28"/>
       <c r="H218" s="15" t="s">
-        <v>451</v>
+        <v>373</v>
       </c>
     </row>
     <row r="219" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A219" s="32">
-        <v>86</v>
-      </c>
-      <c r="B219" s="34" t="s">
-        <v>29</v>
-      </c>
-      <c r="C219" s="25" t="s">
-        <v>89</v>
-      </c>
+      <c r="A219" s="42"/>
+      <c r="B219" s="31"/>
+      <c r="C219" s="29"/>
       <c r="D219" s="5" t="s">
-        <v>152</v>
+        <v>99</v>
       </c>
       <c r="E219" s="1">
         <v>2</v>
       </c>
       <c r="F219" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="G219" s="36"/>
+        <v>218</v>
+      </c>
+      <c r="G219" s="28"/>
       <c r="H219" s="15" t="s">
-        <v>475</v>
+        <v>440</v>
       </c>
     </row>
     <row r="220" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A220" s="33"/>
-      <c r="B220" s="34"/>
-      <c r="C220" s="25"/>
+      <c r="A220" s="41">
+        <v>86</v>
+      </c>
+      <c r="B220" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="C220" s="29" t="s">
+        <v>87</v>
+      </c>
       <c r="D220" s="5" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E220" s="1">
         <v>2</v>
       </c>
       <c r="F220" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="G220" s="36"/>
+        <v>190</v>
+      </c>
+      <c r="G220" s="28"/>
       <c r="H220" s="15" t="s">
-        <v>476</v>
+        <v>464</v>
       </c>
     </row>
     <row r="221" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A221" s="32">
-        <v>87</v>
-      </c>
-      <c r="B221" s="34" t="s">
-        <v>29</v>
-      </c>
-      <c r="C221" s="43" t="s">
-        <v>89</v>
-      </c>
+      <c r="A221" s="42"/>
+      <c r="B221" s="31"/>
+      <c r="C221" s="29"/>
       <c r="D221" s="5" t="s">
-        <v>102</v>
+        <v>151</v>
       </c>
       <c r="E221" s="1">
         <v>2</v>
       </c>
       <c r="F221" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="G221" s="36" t="s">
-        <v>623</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="G221" s="28"/>
       <c r="H221" s="15" t="s">
-        <v>384</v>
+        <v>465</v>
       </c>
     </row>
     <row r="222" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A222" s="33"/>
-      <c r="B222" s="34"/>
-      <c r="C222" s="43"/>
+      <c r="A222" s="41">
+        <v>87</v>
+      </c>
+      <c r="B222" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="C222" s="32" t="s">
+        <v>87</v>
+      </c>
       <c r="D222" s="5" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E222" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F222" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="G222" s="36"/>
+        <v>253</v>
+      </c>
+      <c r="G222" s="28" t="s">
+        <v>602</v>
+      </c>
       <c r="H222" s="15" t="s">
-        <v>452</v>
+        <v>374</v>
       </c>
     </row>
     <row r="223" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A223" s="32">
+      <c r="A223" s="42"/>
+      <c r="B223" s="31"/>
+      <c r="C223" s="32"/>
+      <c r="D223" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="E223" s="1">
+        <v>1</v>
+      </c>
+      <c r="F223" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="G223" s="28"/>
+      <c r="H223" s="15" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A224" s="41">
         <v>88</v>
       </c>
-      <c r="B223" s="34" t="s">
+      <c r="B224" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C223" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="D223" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="E223" s="1">
-        <v>3</v>
-      </c>
-      <c r="F223" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="G223" s="36"/>
-      <c r="H223" s="15" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="224" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A224" s="33"/>
-      <c r="B224" s="34"/>
-      <c r="C224" s="35"/>
+      <c r="C224" s="45" t="s">
+        <v>87</v>
+      </c>
       <c r="D224" s="5" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E224" s="1">
         <v>3</v>
       </c>
       <c r="F224" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="G224" s="36"/>
+        <v>299</v>
+      </c>
+      <c r="G224" s="28"/>
       <c r="H224" s="15" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="228" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A228" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A225" s="42"/>
+      <c r="B225" s="31"/>
+      <c r="C225" s="45"/>
+      <c r="D225" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="E225" s="1">
+        <v>3</v>
+      </c>
+      <c r="F225" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="G225" s="28"/>
+      <c r="H225" s="15" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A229" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A230" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A231" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A232" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A233" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A234" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A235" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A236" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="229" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A229" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="230" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A230" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="231" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A231" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="232" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A232" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="233" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A233" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="234" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A234" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="235" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A235" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="236" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A236" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="244" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A244" s="25" t="s">
-        <v>640</v>
-      </c>
-      <c r="B244" s="25"/>
-      <c r="C244" s="25"/>
-      <c r="D244" s="25"/>
-      <c r="E244" s="25"/>
-      <c r="F244" s="25"/>
-      <c r="G244" s="25"/>
-      <c r="H244" s="25"/>
-    </row>
-    <row r="245" spans="1:8" ht="25.7" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A245" s="1" t="s">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A237" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A245" s="29" t="s">
+        <v>619</v>
+      </c>
+      <c r="B245" s="29"/>
+      <c r="C245" s="29"/>
+      <c r="D245" s="29"/>
+      <c r="E245" s="29"/>
+      <c r="F245" s="29"/>
+      <c r="G245" s="29"/>
+      <c r="H245" s="29"/>
+    </row>
+    <row r="246" spans="1:8" ht="25.7" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A246" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B245" s="1" t="s">
-        <v>490</v>
-      </c>
-      <c r="C245" s="26" t="s">
+      <c r="B246" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="C246" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="D245" s="27"/>
-      <c r="E245" s="27"/>
-      <c r="F245" s="28"/>
-      <c r="G245" s="1" t="s">
+      <c r="D246" s="37"/>
+      <c r="E246" s="37"/>
+      <c r="F246" s="38"/>
+      <c r="G246" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H245" s="1" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="246" spans="1:8" ht="100.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A246" s="18" t="s">
-        <v>646</v>
-      </c>
-      <c r="B246" s="23" t="s">
-        <v>489</v>
-      </c>
-      <c r="C246" s="29" t="s">
-        <v>649</v>
-      </c>
-      <c r="D246" s="30"/>
-      <c r="E246" s="30"/>
-      <c r="F246" s="31"/>
-      <c r="G246" s="4" t="s">
-        <v>657</v>
-      </c>
-      <c r="H246" s="16" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="247" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A247" s="24" t="s">
-        <v>641</v>
-      </c>
-      <c r="B247" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="C247" s="29" t="s">
-        <v>645</v>
-      </c>
-      <c r="D247" s="30"/>
-      <c r="E247" s="30"/>
-      <c r="F247" s="31"/>
+      <c r="H246" s="1" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8" ht="100.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A247" s="18" t="s">
+        <v>625</v>
+      </c>
+      <c r="B247" s="23" t="s">
+        <v>478</v>
+      </c>
+      <c r="C247" s="25" t="s">
+        <v>628</v>
+      </c>
+      <c r="D247" s="26"/>
+      <c r="E247" s="26"/>
+      <c r="F247" s="27"/>
       <c r="G247" s="4" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="H247" s="16" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="252" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A252" s="25" t="s">
-        <v>642</v>
-      </c>
-      <c r="B252" s="25"/>
-      <c r="C252" s="25"/>
-      <c r="D252" s="25"/>
-      <c r="E252" s="25"/>
-      <c r="F252" s="25"/>
-      <c r="G252" s="25"/>
-      <c r="H252" s="25"/>
+        <v>626</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A248" s="24" t="s">
+        <v>620</v>
+      </c>
+      <c r="B248" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="C248" s="25" t="s">
+        <v>624</v>
+      </c>
+      <c r="D248" s="26"/>
+      <c r="E248" s="26"/>
+      <c r="F248" s="27"/>
+      <c r="G248" s="4" t="s">
+        <v>623</v>
+      </c>
+      <c r="H248" s="16" t="s">
+        <v>627</v>
+      </c>
     </row>
     <row r="253" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A253" s="25" t="s">
-        <v>643</v>
-      </c>
-      <c r="B253" s="25"/>
-      <c r="C253" s="25"/>
-      <c r="D253" s="25"/>
-      <c r="E253" s="25"/>
-      <c r="F253" s="25"/>
-      <c r="G253" s="25"/>
-      <c r="H253" s="25"/>
+      <c r="A253" s="29" t="s">
+        <v>621</v>
+      </c>
+      <c r="B253" s="29"/>
+      <c r="C253" s="29"/>
+      <c r="D253" s="29"/>
+      <c r="E253" s="29"/>
+      <c r="F253" s="29"/>
+      <c r="G253" s="29"/>
+      <c r="H253" s="29"/>
+    </row>
+    <row r="254" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A254" s="29" t="s">
+        <v>622</v>
+      </c>
+      <c r="B254" s="29"/>
+      <c r="C254" s="29"/>
+      <c r="D254" s="29"/>
+      <c r="E254" s="29"/>
+      <c r="F254" s="29"/>
+      <c r="G254" s="29"/>
+      <c r="H254" s="29"/>
     </row>
   </sheetData>
-  <mergeCells count="384">
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C35:F35"/>
+  <mergeCells count="385">
     <mergeCell ref="C36:F36"/>
-    <mergeCell ref="G57:G58"/>
-    <mergeCell ref="G59:G60"/>
-    <mergeCell ref="C207:C208"/>
-    <mergeCell ref="B61:B62"/>
-    <mergeCell ref="C63:C64"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="G87:G88"/>
-    <mergeCell ref="C89:C90"/>
-    <mergeCell ref="G129:G130"/>
-    <mergeCell ref="C129:C130"/>
-    <mergeCell ref="G143:G144"/>
-    <mergeCell ref="B161:B162"/>
-    <mergeCell ref="C161:C162"/>
-    <mergeCell ref="B137:B138"/>
-    <mergeCell ref="G153:G154"/>
-    <mergeCell ref="G157:G158"/>
-    <mergeCell ref="C155:C156"/>
-    <mergeCell ref="C141:C142"/>
-    <mergeCell ref="G119:G120"/>
-    <mergeCell ref="G113:G114"/>
-    <mergeCell ref="A57:A58"/>
-    <mergeCell ref="B57:B58"/>
-    <mergeCell ref="C57:C58"/>
-    <mergeCell ref="A61:A62"/>
-    <mergeCell ref="C61:C62"/>
-    <mergeCell ref="A63:A64"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="A59:A60"/>
-    <mergeCell ref="B59:B60"/>
-    <mergeCell ref="C59:C60"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="A46:H46"/>
-    <mergeCell ref="A47:H47"/>
-    <mergeCell ref="A40:H40"/>
-    <mergeCell ref="G49:G50"/>
-    <mergeCell ref="G51:G52"/>
-    <mergeCell ref="G53:G54"/>
-    <mergeCell ref="G55:G56"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="C51:C52"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="C53:C54"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="A123:A124"/>
-    <mergeCell ref="B123:B124"/>
-    <mergeCell ref="A117:A118"/>
-    <mergeCell ref="A133:A134"/>
-    <mergeCell ref="B133:B134"/>
-    <mergeCell ref="C133:C134"/>
-    <mergeCell ref="G213:G214"/>
-    <mergeCell ref="C117:C118"/>
-    <mergeCell ref="B117:B118"/>
-    <mergeCell ref="C123:C124"/>
-    <mergeCell ref="A151:A152"/>
-    <mergeCell ref="B151:B152"/>
-    <mergeCell ref="C151:C152"/>
-    <mergeCell ref="A145:A146"/>
-    <mergeCell ref="B145:B146"/>
-    <mergeCell ref="C145:C146"/>
-    <mergeCell ref="B149:B150"/>
-    <mergeCell ref="C149:C150"/>
-    <mergeCell ref="G149:G150"/>
-    <mergeCell ref="G159:G160"/>
-    <mergeCell ref="A165:A166"/>
-    <mergeCell ref="A161:A162"/>
-    <mergeCell ref="A187:A188"/>
-    <mergeCell ref="A189:A190"/>
-    <mergeCell ref="B189:B190"/>
-    <mergeCell ref="G181:G182"/>
-    <mergeCell ref="C189:C190"/>
-    <mergeCell ref="G187:G188"/>
-    <mergeCell ref="B187:B188"/>
-    <mergeCell ref="C171:C172"/>
-    <mergeCell ref="C157:C158"/>
-    <mergeCell ref="G155:G156"/>
-    <mergeCell ref="A155:A156"/>
-    <mergeCell ref="B155:B156"/>
-    <mergeCell ref="A173:A174"/>
-    <mergeCell ref="B173:B174"/>
-    <mergeCell ref="C173:C174"/>
-    <mergeCell ref="G173:G174"/>
-    <mergeCell ref="B157:B158"/>
-    <mergeCell ref="C185:C186"/>
-    <mergeCell ref="A157:A158"/>
-    <mergeCell ref="G185:G186"/>
-    <mergeCell ref="A181:A182"/>
-    <mergeCell ref="B181:B182"/>
-    <mergeCell ref="C167:C168"/>
-    <mergeCell ref="G165:G166"/>
-    <mergeCell ref="A183:A184"/>
-    <mergeCell ref="G161:G162"/>
-    <mergeCell ref="C179:C180"/>
-    <mergeCell ref="G177:G178"/>
-    <mergeCell ref="A175:A176"/>
-    <mergeCell ref="B131:B132"/>
-    <mergeCell ref="C131:C132"/>
-    <mergeCell ref="B153:B154"/>
-    <mergeCell ref="C153:C154"/>
-    <mergeCell ref="G151:G152"/>
-    <mergeCell ref="G171:G172"/>
-    <mergeCell ref="B175:B176"/>
-    <mergeCell ref="C175:C176"/>
-    <mergeCell ref="B171:B172"/>
-    <mergeCell ref="A167:A168"/>
-    <mergeCell ref="G169:G170"/>
-    <mergeCell ref="G175:G176"/>
-    <mergeCell ref="G141:G142"/>
-    <mergeCell ref="A169:A170"/>
-    <mergeCell ref="B169:B170"/>
-    <mergeCell ref="C169:C170"/>
-    <mergeCell ref="G167:G168"/>
-    <mergeCell ref="A171:A172"/>
-    <mergeCell ref="A179:A180"/>
-    <mergeCell ref="B179:B180"/>
-    <mergeCell ref="A135:A136"/>
-    <mergeCell ref="B135:B136"/>
-    <mergeCell ref="C135:C136"/>
-    <mergeCell ref="G147:G148"/>
-    <mergeCell ref="A149:A150"/>
-    <mergeCell ref="A159:A160"/>
-    <mergeCell ref="B159:B160"/>
-    <mergeCell ref="C159:C160"/>
-    <mergeCell ref="G127:G128"/>
-    <mergeCell ref="A153:A154"/>
-    <mergeCell ref="A137:A138"/>
-    <mergeCell ref="G139:G140"/>
-    <mergeCell ref="G125:G126"/>
-    <mergeCell ref="A127:A128"/>
-    <mergeCell ref="B127:B128"/>
-    <mergeCell ref="B147:B148"/>
-    <mergeCell ref="C147:C148"/>
-    <mergeCell ref="G145:G146"/>
-    <mergeCell ref="A143:A144"/>
-    <mergeCell ref="B143:B144"/>
-    <mergeCell ref="C143:C144"/>
-    <mergeCell ref="A139:A140"/>
-    <mergeCell ref="B139:B140"/>
-    <mergeCell ref="C139:C140"/>
-    <mergeCell ref="G135:G136"/>
-    <mergeCell ref="A131:A132"/>
-    <mergeCell ref="A129:A130"/>
-    <mergeCell ref="B129:B130"/>
-    <mergeCell ref="C127:C128"/>
-    <mergeCell ref="A141:A142"/>
-    <mergeCell ref="B141:B142"/>
-    <mergeCell ref="A147:A148"/>
-    <mergeCell ref="A125:A126"/>
-    <mergeCell ref="B125:B126"/>
-    <mergeCell ref="C125:C126"/>
-    <mergeCell ref="G97:G98"/>
-    <mergeCell ref="G83:G84"/>
-    <mergeCell ref="G91:G92"/>
-    <mergeCell ref="G81:G82"/>
-    <mergeCell ref="G89:G90"/>
-    <mergeCell ref="G99:G100"/>
-    <mergeCell ref="C137:C138"/>
-    <mergeCell ref="G137:G138"/>
-    <mergeCell ref="G115:G116"/>
-    <mergeCell ref="G107:G108"/>
-    <mergeCell ref="G109:G110"/>
-    <mergeCell ref="C109:C110"/>
-    <mergeCell ref="C101:C102"/>
-    <mergeCell ref="C113:C114"/>
-    <mergeCell ref="C111:C112"/>
-    <mergeCell ref="C115:C116"/>
-    <mergeCell ref="G121:G122"/>
-    <mergeCell ref="C121:C122"/>
-    <mergeCell ref="C81:C82"/>
-    <mergeCell ref="G131:G132"/>
-    <mergeCell ref="G105:G106"/>
-    <mergeCell ref="G95:G96"/>
-    <mergeCell ref="G101:G102"/>
-    <mergeCell ref="A109:A110"/>
-    <mergeCell ref="A113:A114"/>
-    <mergeCell ref="B113:B114"/>
-    <mergeCell ref="A111:A112"/>
-    <mergeCell ref="B111:B112"/>
-    <mergeCell ref="A115:A116"/>
-    <mergeCell ref="B115:B116"/>
-    <mergeCell ref="A121:A122"/>
-    <mergeCell ref="B121:B122"/>
-    <mergeCell ref="A101:A102"/>
-    <mergeCell ref="B101:B102"/>
-    <mergeCell ref="A107:A108"/>
-    <mergeCell ref="B107:B108"/>
-    <mergeCell ref="C107:C108"/>
-    <mergeCell ref="A103:A104"/>
-    <mergeCell ref="B109:B110"/>
-    <mergeCell ref="A97:A98"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:B100"/>
-    <mergeCell ref="C99:C100"/>
-    <mergeCell ref="A93:A94"/>
-    <mergeCell ref="B93:B94"/>
-    <mergeCell ref="B103:B104"/>
-    <mergeCell ref="C103:C104"/>
-    <mergeCell ref="A95:A96"/>
-    <mergeCell ref="B95:B96"/>
-    <mergeCell ref="C95:C96"/>
-    <mergeCell ref="B97:B98"/>
-    <mergeCell ref="C97:C98"/>
-    <mergeCell ref="A81:A82"/>
-    <mergeCell ref="B89:B90"/>
-    <mergeCell ref="C85:C86"/>
-    <mergeCell ref="A85:A86"/>
-    <mergeCell ref="B85:B86"/>
-    <mergeCell ref="G79:G80"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="C93:C94"/>
-    <mergeCell ref="G93:G94"/>
-    <mergeCell ref="B81:B82"/>
-    <mergeCell ref="G67:G68"/>
-    <mergeCell ref="A71:A72"/>
-    <mergeCell ref="C71:C72"/>
-    <mergeCell ref="G71:G72"/>
-    <mergeCell ref="B71:B72"/>
-    <mergeCell ref="C65:C66"/>
-    <mergeCell ref="G73:G74"/>
-    <mergeCell ref="A75:A76"/>
-    <mergeCell ref="B75:B76"/>
-    <mergeCell ref="G75:G76"/>
-    <mergeCell ref="C75:C76"/>
-    <mergeCell ref="A73:A74"/>
-    <mergeCell ref="B73:B74"/>
-    <mergeCell ref="C73:C74"/>
-    <mergeCell ref="C223:C224"/>
-    <mergeCell ref="G221:G222"/>
-    <mergeCell ref="G197:G198"/>
-    <mergeCell ref="A223:A224"/>
-    <mergeCell ref="G219:G220"/>
-    <mergeCell ref="A209:A210"/>
-    <mergeCell ref="B209:B210"/>
-    <mergeCell ref="C209:C210"/>
-    <mergeCell ref="G223:G224"/>
-    <mergeCell ref="B223:B224"/>
-    <mergeCell ref="A221:A222"/>
-    <mergeCell ref="B221:B222"/>
-    <mergeCell ref="C221:C222"/>
-    <mergeCell ref="G217:G218"/>
-    <mergeCell ref="A211:A212"/>
-    <mergeCell ref="B211:B212"/>
-    <mergeCell ref="C211:C212"/>
-    <mergeCell ref="B213:B214"/>
-    <mergeCell ref="C213:C214"/>
-    <mergeCell ref="A207:A208"/>
-    <mergeCell ref="A219:A220"/>
-    <mergeCell ref="B219:B220"/>
-    <mergeCell ref="C219:C220"/>
-    <mergeCell ref="C217:C218"/>
-    <mergeCell ref="A213:A214"/>
-    <mergeCell ref="G211:G212"/>
-    <mergeCell ref="G195:G196"/>
-    <mergeCell ref="C181:C182"/>
-    <mergeCell ref="G179:G180"/>
-    <mergeCell ref="A163:A164"/>
-    <mergeCell ref="B163:B164"/>
-    <mergeCell ref="C163:C164"/>
-    <mergeCell ref="G189:G190"/>
-    <mergeCell ref="A177:A178"/>
-    <mergeCell ref="B177:B178"/>
-    <mergeCell ref="G163:G164"/>
-    <mergeCell ref="G199:G200"/>
-    <mergeCell ref="A197:A198"/>
-    <mergeCell ref="B197:B198"/>
-    <mergeCell ref="C197:C198"/>
-    <mergeCell ref="G193:G194"/>
-    <mergeCell ref="A185:A186"/>
-    <mergeCell ref="B185:B186"/>
-    <mergeCell ref="C187:C188"/>
-    <mergeCell ref="B183:B184"/>
-    <mergeCell ref="C183:C184"/>
-    <mergeCell ref="G183:G184"/>
-    <mergeCell ref="G191:G192"/>
-    <mergeCell ref="G215:G216"/>
-    <mergeCell ref="B215:B216"/>
-    <mergeCell ref="B207:B208"/>
-    <mergeCell ref="A105:A106"/>
-    <mergeCell ref="A217:A218"/>
-    <mergeCell ref="B217:B218"/>
-    <mergeCell ref="C215:C216"/>
-    <mergeCell ref="G207:G208"/>
-    <mergeCell ref="A205:A206"/>
-    <mergeCell ref="B205:B206"/>
-    <mergeCell ref="C205:C206"/>
-    <mergeCell ref="G205:G206"/>
-    <mergeCell ref="A203:A204"/>
-    <mergeCell ref="B203:B204"/>
-    <mergeCell ref="C203:C204"/>
-    <mergeCell ref="G203:G204"/>
-    <mergeCell ref="G209:G210"/>
-    <mergeCell ref="A215:A216"/>
-    <mergeCell ref="G111:G112"/>
-    <mergeCell ref="G123:G124"/>
-    <mergeCell ref="B165:B166"/>
-    <mergeCell ref="C165:C166"/>
-    <mergeCell ref="B167:B168"/>
-    <mergeCell ref="C177:C178"/>
-    <mergeCell ref="A201:A202"/>
-    <mergeCell ref="B201:B202"/>
-    <mergeCell ref="C201:C202"/>
-    <mergeCell ref="A83:A84"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="G63:G64"/>
-    <mergeCell ref="B105:B106"/>
-    <mergeCell ref="C105:C106"/>
-    <mergeCell ref="G103:G104"/>
-    <mergeCell ref="A69:A70"/>
-    <mergeCell ref="B69:B70"/>
-    <mergeCell ref="C69:C70"/>
-    <mergeCell ref="G69:G70"/>
-    <mergeCell ref="A89:A90"/>
-    <mergeCell ref="G65:G66"/>
-    <mergeCell ref="A67:A68"/>
-    <mergeCell ref="B67:B68"/>
-    <mergeCell ref="B83:B84"/>
-    <mergeCell ref="C83:C84"/>
-    <mergeCell ref="A87:A88"/>
-    <mergeCell ref="B87:B88"/>
-    <mergeCell ref="C91:C92"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="A31:H31"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A195:A196"/>
-    <mergeCell ref="B195:B196"/>
-    <mergeCell ref="C195:C196"/>
-    <mergeCell ref="A191:A192"/>
-    <mergeCell ref="B191:B192"/>
-    <mergeCell ref="C191:C192"/>
-    <mergeCell ref="G85:G86"/>
-    <mergeCell ref="A119:A120"/>
-    <mergeCell ref="B119:B120"/>
-    <mergeCell ref="C119:C120"/>
-    <mergeCell ref="G117:G118"/>
-    <mergeCell ref="A79:A80"/>
-    <mergeCell ref="B79:B80"/>
-    <mergeCell ref="C79:C80"/>
-    <mergeCell ref="A77:A78"/>
-    <mergeCell ref="B77:B78"/>
-    <mergeCell ref="C77:C78"/>
-    <mergeCell ref="G77:G78"/>
-    <mergeCell ref="A244:H244"/>
-    <mergeCell ref="A252:H252"/>
+    <mergeCell ref="A245:H245"/>
     <mergeCell ref="A253:H253"/>
-    <mergeCell ref="C245:F245"/>
+    <mergeCell ref="A254:H254"/>
     <mergeCell ref="C246:F246"/>
     <mergeCell ref="C247:F247"/>
+    <mergeCell ref="C248:F248"/>
     <mergeCell ref="C22:F22"/>
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="C19:F19"/>
@@ -8219,15 +7896,375 @@
     <mergeCell ref="C24:F24"/>
     <mergeCell ref="C25:F25"/>
     <mergeCell ref="C26:F26"/>
-    <mergeCell ref="G61:G62"/>
-    <mergeCell ref="C67:C68"/>
-    <mergeCell ref="G201:G202"/>
-    <mergeCell ref="A193:A194"/>
-    <mergeCell ref="B193:B194"/>
-    <mergeCell ref="C193:C194"/>
-    <mergeCell ref="A199:A200"/>
-    <mergeCell ref="B199:B200"/>
-    <mergeCell ref="C199:C200"/>
+    <mergeCell ref="G62:G63"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="G202:G203"/>
+    <mergeCell ref="A194:A195"/>
+    <mergeCell ref="B194:B195"/>
+    <mergeCell ref="C194:C195"/>
+    <mergeCell ref="A200:A201"/>
+    <mergeCell ref="B200:B201"/>
+    <mergeCell ref="C200:C201"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A196:A197"/>
+    <mergeCell ref="B196:B197"/>
+    <mergeCell ref="C196:C197"/>
+    <mergeCell ref="A192:A193"/>
+    <mergeCell ref="B192:B193"/>
+    <mergeCell ref="C192:C193"/>
+    <mergeCell ref="G86:G87"/>
+    <mergeCell ref="A120:A121"/>
+    <mergeCell ref="B120:B121"/>
+    <mergeCell ref="C120:C121"/>
+    <mergeCell ref="G118:G119"/>
+    <mergeCell ref="A80:A81"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="C80:C81"/>
+    <mergeCell ref="A78:A79"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="G78:G79"/>
+    <mergeCell ref="A202:A203"/>
+    <mergeCell ref="B202:B203"/>
+    <mergeCell ref="C202:C203"/>
+    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="G64:G65"/>
+    <mergeCell ref="B106:B107"/>
+    <mergeCell ref="C106:C107"/>
+    <mergeCell ref="G104:G105"/>
+    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="G70:G71"/>
+    <mergeCell ref="A90:A91"/>
+    <mergeCell ref="G66:G67"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="B84:B85"/>
+    <mergeCell ref="C84:C85"/>
+    <mergeCell ref="A88:A89"/>
+    <mergeCell ref="B88:B89"/>
+    <mergeCell ref="C92:C93"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="G216:G217"/>
+    <mergeCell ref="B216:B217"/>
+    <mergeCell ref="B208:B209"/>
+    <mergeCell ref="A106:A107"/>
+    <mergeCell ref="A218:A219"/>
+    <mergeCell ref="B218:B219"/>
+    <mergeCell ref="C216:C217"/>
+    <mergeCell ref="G208:G209"/>
+    <mergeCell ref="A206:A207"/>
+    <mergeCell ref="B206:B207"/>
+    <mergeCell ref="C206:C207"/>
+    <mergeCell ref="G206:G207"/>
+    <mergeCell ref="A204:A205"/>
+    <mergeCell ref="B204:B205"/>
+    <mergeCell ref="C204:C205"/>
+    <mergeCell ref="G204:G205"/>
+    <mergeCell ref="G210:G211"/>
+    <mergeCell ref="A216:A217"/>
+    <mergeCell ref="G112:G113"/>
+    <mergeCell ref="G124:G125"/>
+    <mergeCell ref="B166:B167"/>
+    <mergeCell ref="C166:C167"/>
+    <mergeCell ref="B168:B169"/>
+    <mergeCell ref="C178:C179"/>
+    <mergeCell ref="A214:A215"/>
+    <mergeCell ref="G212:G213"/>
+    <mergeCell ref="G196:G197"/>
+    <mergeCell ref="C182:C183"/>
+    <mergeCell ref="G180:G181"/>
+    <mergeCell ref="A164:A165"/>
+    <mergeCell ref="B164:B165"/>
+    <mergeCell ref="C164:C165"/>
+    <mergeCell ref="G190:G191"/>
+    <mergeCell ref="A178:A179"/>
+    <mergeCell ref="B178:B179"/>
+    <mergeCell ref="G164:G165"/>
+    <mergeCell ref="G200:G201"/>
+    <mergeCell ref="A198:A199"/>
+    <mergeCell ref="B198:B199"/>
+    <mergeCell ref="C198:C199"/>
+    <mergeCell ref="G194:G195"/>
+    <mergeCell ref="A186:A187"/>
+    <mergeCell ref="B186:B187"/>
+    <mergeCell ref="C188:C189"/>
+    <mergeCell ref="B184:B185"/>
+    <mergeCell ref="C184:C185"/>
+    <mergeCell ref="G184:G185"/>
+    <mergeCell ref="G192:G193"/>
+    <mergeCell ref="C224:C225"/>
+    <mergeCell ref="G222:G223"/>
+    <mergeCell ref="G198:G199"/>
+    <mergeCell ref="A224:A225"/>
+    <mergeCell ref="G220:G221"/>
+    <mergeCell ref="A210:A211"/>
+    <mergeCell ref="B210:B211"/>
+    <mergeCell ref="C210:C211"/>
+    <mergeCell ref="G224:G225"/>
+    <mergeCell ref="B224:B225"/>
+    <mergeCell ref="A222:A223"/>
+    <mergeCell ref="B222:B223"/>
+    <mergeCell ref="C222:C223"/>
+    <mergeCell ref="G218:G219"/>
+    <mergeCell ref="A212:A213"/>
+    <mergeCell ref="B212:B213"/>
+    <mergeCell ref="C212:C213"/>
+    <mergeCell ref="B214:B215"/>
+    <mergeCell ref="C214:C215"/>
+    <mergeCell ref="A208:A209"/>
+    <mergeCell ref="A220:A221"/>
+    <mergeCell ref="B220:B221"/>
+    <mergeCell ref="C220:C221"/>
+    <mergeCell ref="C218:C219"/>
+    <mergeCell ref="G68:G69"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="G72:G73"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="G74:G75"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="G76:G77"/>
+    <mergeCell ref="C76:C77"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="C86:C87"/>
+    <mergeCell ref="A86:A87"/>
+    <mergeCell ref="B86:B87"/>
+    <mergeCell ref="G80:G81"/>
+    <mergeCell ref="C88:C89"/>
+    <mergeCell ref="C94:C95"/>
+    <mergeCell ref="G94:G95"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="A94:A95"/>
+    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="B104:B105"/>
+    <mergeCell ref="C104:C105"/>
+    <mergeCell ref="A96:A97"/>
+    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="C96:C97"/>
+    <mergeCell ref="B98:B99"/>
+    <mergeCell ref="C98:C99"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="B102:B103"/>
+    <mergeCell ref="A108:A109"/>
+    <mergeCell ref="B108:B109"/>
+    <mergeCell ref="C108:C109"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="B110:B111"/>
+    <mergeCell ref="A98:A99"/>
+    <mergeCell ref="A100:A101"/>
+    <mergeCell ref="B100:B101"/>
+    <mergeCell ref="C100:C101"/>
+    <mergeCell ref="A110:A111"/>
+    <mergeCell ref="A114:A115"/>
+    <mergeCell ref="B114:B115"/>
+    <mergeCell ref="A112:A113"/>
+    <mergeCell ref="B112:B113"/>
+    <mergeCell ref="A116:A117"/>
+    <mergeCell ref="B116:B117"/>
+    <mergeCell ref="A122:A123"/>
+    <mergeCell ref="B122:B123"/>
+    <mergeCell ref="G98:G99"/>
+    <mergeCell ref="G84:G85"/>
+    <mergeCell ref="G92:G93"/>
+    <mergeCell ref="G82:G83"/>
+    <mergeCell ref="G90:G91"/>
+    <mergeCell ref="G100:G101"/>
+    <mergeCell ref="C138:C139"/>
+    <mergeCell ref="G138:G139"/>
+    <mergeCell ref="G116:G117"/>
+    <mergeCell ref="G108:G109"/>
+    <mergeCell ref="G110:G111"/>
+    <mergeCell ref="C110:C111"/>
+    <mergeCell ref="C102:C103"/>
+    <mergeCell ref="C114:C115"/>
+    <mergeCell ref="C112:C113"/>
+    <mergeCell ref="C116:C117"/>
+    <mergeCell ref="G122:G123"/>
+    <mergeCell ref="C122:C123"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="G132:G133"/>
+    <mergeCell ref="G106:G107"/>
+    <mergeCell ref="G96:G97"/>
+    <mergeCell ref="G102:G103"/>
+    <mergeCell ref="G126:G127"/>
+    <mergeCell ref="A128:A129"/>
+    <mergeCell ref="B128:B129"/>
+    <mergeCell ref="B148:B149"/>
+    <mergeCell ref="C148:C149"/>
+    <mergeCell ref="G146:G147"/>
+    <mergeCell ref="A144:A145"/>
+    <mergeCell ref="B144:B145"/>
+    <mergeCell ref="C144:C145"/>
+    <mergeCell ref="A140:A141"/>
+    <mergeCell ref="B140:B141"/>
+    <mergeCell ref="C140:C141"/>
+    <mergeCell ref="G136:G137"/>
+    <mergeCell ref="A132:A133"/>
+    <mergeCell ref="A130:A131"/>
+    <mergeCell ref="B130:B131"/>
+    <mergeCell ref="C128:C129"/>
+    <mergeCell ref="A142:A143"/>
+    <mergeCell ref="B142:B143"/>
+    <mergeCell ref="A148:A149"/>
+    <mergeCell ref="A126:A127"/>
+    <mergeCell ref="B126:B127"/>
+    <mergeCell ref="C126:C127"/>
+    <mergeCell ref="B136:B137"/>
+    <mergeCell ref="C136:C137"/>
+    <mergeCell ref="G148:G149"/>
+    <mergeCell ref="A150:A151"/>
+    <mergeCell ref="A160:A161"/>
+    <mergeCell ref="B160:B161"/>
+    <mergeCell ref="C160:C161"/>
+    <mergeCell ref="G128:G129"/>
+    <mergeCell ref="A154:A155"/>
+    <mergeCell ref="A138:A139"/>
+    <mergeCell ref="G140:G141"/>
+    <mergeCell ref="C180:C181"/>
+    <mergeCell ref="G178:G179"/>
+    <mergeCell ref="A176:A177"/>
+    <mergeCell ref="B132:B133"/>
+    <mergeCell ref="C132:C133"/>
+    <mergeCell ref="B154:B155"/>
+    <mergeCell ref="C154:C155"/>
+    <mergeCell ref="G152:G153"/>
+    <mergeCell ref="G172:G173"/>
+    <mergeCell ref="B176:B177"/>
+    <mergeCell ref="C176:C177"/>
+    <mergeCell ref="B172:B173"/>
+    <mergeCell ref="A168:A169"/>
+    <mergeCell ref="G170:G171"/>
+    <mergeCell ref="G176:G177"/>
+    <mergeCell ref="G142:G143"/>
+    <mergeCell ref="A170:A171"/>
+    <mergeCell ref="B170:B171"/>
+    <mergeCell ref="C170:C171"/>
+    <mergeCell ref="G168:G169"/>
+    <mergeCell ref="A172:A173"/>
+    <mergeCell ref="A180:A181"/>
+    <mergeCell ref="B180:B181"/>
+    <mergeCell ref="A136:A137"/>
+    <mergeCell ref="B190:B191"/>
+    <mergeCell ref="G182:G183"/>
+    <mergeCell ref="C190:C191"/>
+    <mergeCell ref="G188:G189"/>
+    <mergeCell ref="B188:B189"/>
+    <mergeCell ref="C172:C173"/>
+    <mergeCell ref="C158:C159"/>
+    <mergeCell ref="G156:G157"/>
+    <mergeCell ref="A156:A157"/>
+    <mergeCell ref="B156:B157"/>
+    <mergeCell ref="A174:A175"/>
+    <mergeCell ref="B174:B175"/>
+    <mergeCell ref="C174:C175"/>
+    <mergeCell ref="G174:G175"/>
+    <mergeCell ref="B158:B159"/>
+    <mergeCell ref="C186:C187"/>
+    <mergeCell ref="A158:A159"/>
+    <mergeCell ref="G186:G187"/>
+    <mergeCell ref="A182:A183"/>
+    <mergeCell ref="B182:B183"/>
+    <mergeCell ref="C168:C169"/>
+    <mergeCell ref="G166:G167"/>
+    <mergeCell ref="A184:A185"/>
+    <mergeCell ref="G162:G163"/>
+    <mergeCell ref="A124:A125"/>
+    <mergeCell ref="B124:B125"/>
+    <mergeCell ref="A118:A119"/>
+    <mergeCell ref="A134:A135"/>
+    <mergeCell ref="B134:B135"/>
+    <mergeCell ref="C134:C135"/>
+    <mergeCell ref="G214:G215"/>
+    <mergeCell ref="C118:C119"/>
+    <mergeCell ref="B118:B119"/>
+    <mergeCell ref="C124:C125"/>
+    <mergeCell ref="A152:A153"/>
+    <mergeCell ref="B152:B153"/>
+    <mergeCell ref="C152:C153"/>
+    <mergeCell ref="A146:A147"/>
+    <mergeCell ref="B146:B147"/>
+    <mergeCell ref="C146:C147"/>
+    <mergeCell ref="B150:B151"/>
+    <mergeCell ref="C150:C151"/>
+    <mergeCell ref="G150:G151"/>
+    <mergeCell ref="G160:G161"/>
+    <mergeCell ref="A166:A167"/>
+    <mergeCell ref="A162:A163"/>
+    <mergeCell ref="A188:A189"/>
+    <mergeCell ref="A190:A191"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="A48:H48"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="G50:G51"/>
+    <mergeCell ref="G52:G53"/>
+    <mergeCell ref="G54:G55"/>
+    <mergeCell ref="G56:G57"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="C62:C63"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="G60:G61"/>
+    <mergeCell ref="C208:C209"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="B92:B93"/>
+    <mergeCell ref="G88:G89"/>
+    <mergeCell ref="C90:C91"/>
+    <mergeCell ref="G130:G131"/>
+    <mergeCell ref="C130:C131"/>
+    <mergeCell ref="G144:G145"/>
+    <mergeCell ref="B162:B163"/>
+    <mergeCell ref="C162:C163"/>
+    <mergeCell ref="B138:B139"/>
+    <mergeCell ref="G154:G155"/>
+    <mergeCell ref="G158:G159"/>
+    <mergeCell ref="C156:C157"/>
+    <mergeCell ref="C142:C143"/>
+    <mergeCell ref="G120:G121"/>
+    <mergeCell ref="G114:G115"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/main/resources/InesModResources/杀戮尖塔自制--伊内丝v0.2.xlsx
+++ b/src/main/resources/InesModResources/杀戮尖塔自制--伊内丝v0.2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\myMod\InesMod\InesMod\src\main\resources\InesModResources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E866DDC-F838-46C3-80AE-C1F319540ADE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FF22376-0CC0-4490-B0E9-962DAF953238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{7A3E14A4-2175-4856-859A-887D335814F1}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="916" uniqueCount="664">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="916" uniqueCount="665">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -540,14 +540,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>埋伏</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>埋伏+</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>回复3点生命值。此牌每被抽到一次，其效果+3。消耗。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1323,18 +1315,12 @@
     <t>Disguise</t>
   </si>
   <si>
-    <t>Ad Hoc Strategy</t>
-  </si>
-  <si>
     <t>Old Intel</t>
   </si>
   <si>
     <t>Immediate Effect</t>
   </si>
   <si>
-    <t>Ambush</t>
-  </si>
-  <si>
     <t>Intel Network</t>
   </si>
   <si>
@@ -1525,9 +1511,6 @@
   </si>
   <si>
     <t>Immediate Effect+</t>
-  </si>
-  <si>
-    <t>Ambush+</t>
   </si>
   <si>
     <t>Intel Network+</t>
@@ -2257,10 +2240,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>下一张打出的攻击牌造成2倍伤害，随后失去所有格挡并结束你的回合。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>每消耗1张影哨，对所有敌人造成3点伤害。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2310,14 +2289,6 @@
   </si>
   <si>
     <t>你的回合开始时，获得1层偷取。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自动打出。获得10点格挡。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自动打出。获得14点格挡。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2458,14 +2429,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>潜伏。攻击如果消耗了偷取，给予1点易伤。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>潜伏。攻击如果消耗了偷取，给予2点易伤。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>潜伏</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2483,14 +2446,6 @@
   </si>
   <si>
     <t>一个接一个</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>One by one</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>One by one+</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2528,6 +2483,58 @@
   </si>
   <si>
     <t>自动打出。对所有敌人造成12点伤害2次。若无法自动打出则消耗。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>One by One</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>One by One+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>致命契机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>致命契机+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>潜伏。下一张打出的攻击牌造成2倍伤害，随后失去所有格挡并结束你的回合。虚无。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Deadly Opportunity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Deadly Opportunity+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>潜伏。下一张打出的攻击牌造成2倍伤害，随后失去一半格挡并结束你的回合。虚无。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动打出。获得9点格挡。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动打出。获得12点格挡。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>潜伏。攻击如果消耗了偷取，给予1层易伤。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>潜伏。攻击如果消耗了偷取，给予2层易伤。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ad Hoc Strategy</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2815,27 +2822,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2847,16 +2833,46 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2865,25 +2881,16 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3219,10 +3226,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="29" t="s">
-        <v>305</v>
-      </c>
-      <c r="B1" s="29"/>
+      <c r="A1" s="28" t="s">
+        <v>303</v>
+      </c>
+      <c r="B1" s="28"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -3230,10 +3237,10 @@
     </row>
     <row r="2" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="7" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="12"/>
@@ -3244,10 +3251,10 @@
     </row>
     <row r="3" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -3274,29 +3281,29 @@
       <c r="B6" s="2"/>
     </row>
     <row r="8" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="36" t="s">
+      <c r="A8" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="B8" s="37"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="38"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="31"/>
     </row>
     <row r="9" spans="1:8" ht="25.7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="C9" s="36" t="s">
-        <v>236</v>
-      </c>
-      <c r="D9" s="37"/>
-      <c r="E9" s="38"/>
+        <v>233</v>
+      </c>
+      <c r="C9" s="29" t="s">
+        <v>234</v>
+      </c>
+      <c r="D9" s="30"/>
+      <c r="E9" s="31"/>
       <c r="F9" s="8" t="s">
         <v>2</v>
       </c>
@@ -3304,7 +3311,7 @@
         <v>3</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
@@ -3314,132 +3321,132 @@
       <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="37" t="s">
-        <v>238</v>
-      </c>
-      <c r="D10" s="37"/>
-      <c r="E10" s="38"/>
+      <c r="C10" s="30" t="s">
+        <v>236</v>
+      </c>
+      <c r="D10" s="30"/>
+      <c r="E10" s="31"/>
       <c r="F10" s="9" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="G10" s="10"/>
       <c r="H10" s="17" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="C11" s="36" t="s">
-        <v>242</v>
-      </c>
-      <c r="D11" s="37"/>
-      <c r="E11" s="38"/>
+        <v>253</v>
+      </c>
+      <c r="C11" s="29" t="s">
+        <v>240</v>
+      </c>
+      <c r="D11" s="30"/>
+      <c r="E11" s="31"/>
       <c r="F11" s="9" t="s">
-        <v>660</v>
+        <v>648</v>
       </c>
       <c r="G11" s="10"/>
       <c r="H11" s="17" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="C12" s="36" t="s">
-        <v>488</v>
-      </c>
-      <c r="D12" s="37"/>
-      <c r="E12" s="38"/>
+        <v>253</v>
+      </c>
+      <c r="C12" s="29" t="s">
+        <v>483</v>
+      </c>
+      <c r="D12" s="30"/>
+      <c r="E12" s="31"/>
       <c r="F12" s="9" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="G12" s="10"/>
       <c r="H12" s="17" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>469</v>
-      </c>
-      <c r="D13" s="37"/>
-      <c r="E13" s="38"/>
+        <v>464</v>
+      </c>
+      <c r="D13" s="30"/>
+      <c r="E13" s="31"/>
       <c r="F13" s="9" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G13" s="10"/>
       <c r="H13" s="17" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="C14" s="37" t="s">
-        <v>301</v>
-      </c>
-      <c r="D14" s="37"/>
-      <c r="E14" s="38"/>
+        <v>235</v>
+      </c>
+      <c r="C14" s="30" t="s">
+        <v>299</v>
+      </c>
+      <c r="D14" s="30"/>
+      <c r="E14" s="31"/>
       <c r="F14" s="9" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G14" s="10"/>
       <c r="H14" s="17" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="16" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="17" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="29" t="s">
+      <c r="A18" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="B18" s="29"/>
-      <c r="C18" s="29"/>
-      <c r="D18" s="29"/>
-      <c r="E18" s="29"/>
-      <c r="F18" s="29"/>
-      <c r="G18" s="29"/>
-      <c r="H18" s="29"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="28"/>
     </row>
     <row r="19" spans="1:8" ht="25.7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>479</v>
-      </c>
-      <c r="C19" s="36" t="s">
+        <v>474</v>
+      </c>
+      <c r="C19" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="D19" s="37"/>
-      <c r="E19" s="37"/>
-      <c r="F19" s="38"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="31"/>
       <c r="G19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
@@ -3447,192 +3454,192 @@
         <v>8</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="C20" s="25" t="s">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="D20" s="26"/>
       <c r="E20" s="26"/>
       <c r="F20" s="27"/>
       <c r="G20" s="5" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
     </row>
     <row r="21" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="19" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="C21" s="25" t="s">
-        <v>659</v>
+        <v>647</v>
       </c>
       <c r="D21" s="26"/>
       <c r="E21" s="26"/>
       <c r="F21" s="27"/>
       <c r="G21" s="5" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
     </row>
     <row r="22" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="19" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="C22" s="25" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="D22" s="26"/>
       <c r="E22" s="26"/>
       <c r="F22" s="27"/>
       <c r="G22" s="5" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
     </row>
     <row r="23" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="19" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="C23" s="25" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="D23" s="26"/>
       <c r="E23" s="26"/>
       <c r="F23" s="27"/>
       <c r="G23" s="4" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="19" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="C24" s="25" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="D24" s="26"/>
       <c r="E24" s="26"/>
       <c r="F24" s="27"/>
       <c r="G24" s="5" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="20" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="C25" s="25" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="D25" s="26"/>
       <c r="E25" s="26"/>
       <c r="F25" s="27"/>
       <c r="G25" s="5" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="20" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="C26" s="25" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="D26" s="26"/>
       <c r="E26" s="26"/>
       <c r="F26" s="27"/>
       <c r="G26" s="4"/>
       <c r="H26" s="16" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="1" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="C27" s="25" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="D27" s="26"/>
       <c r="E27" s="26"/>
       <c r="F27" s="27"/>
       <c r="G27" s="4" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="H27" s="16" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="29" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="1:8" ht="21.7" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="31" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="29" t="s">
-        <v>521</v>
-      </c>
-      <c r="B31" s="29"/>
-      <c r="C31" s="29"/>
-      <c r="D31" s="29"/>
-      <c r="E31" s="29"/>
-      <c r="F31" s="29"/>
-      <c r="G31" s="29"/>
-      <c r="H31" s="29"/>
+      <c r="A31" s="28" t="s">
+        <v>516</v>
+      </c>
+      <c r="B31" s="28"/>
+      <c r="C31" s="28"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="28"/>
+      <c r="G31" s="28"/>
+      <c r="H31" s="28"/>
     </row>
     <row r="32" spans="1:8" ht="25.7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>479</v>
-      </c>
-      <c r="C32" s="36" t="s">
+        <v>474</v>
+      </c>
+      <c r="C32" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="D32" s="37"/>
-      <c r="E32" s="37"/>
-      <c r="F32" s="38"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="31"/>
       <c r="G32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
@@ -3640,89 +3647,89 @@
         <v>8</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="C33" s="25" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="D33" s="26"/>
       <c r="E33" s="26"/>
       <c r="F33" s="27"/>
       <c r="G33" s="5"/>
       <c r="H33" s="16" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
     </row>
     <row r="34" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="19" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="C34" s="25" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="D34" s="26"/>
       <c r="E34" s="26"/>
       <c r="F34" s="27"/>
       <c r="G34" s="5"/>
       <c r="H34" s="16" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
     </row>
     <row r="35" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="19" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="D35" s="26"/>
       <c r="E35" s="26"/>
       <c r="F35" s="27"/>
       <c r="G35" s="5"/>
       <c r="H35" s="16" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
     </row>
     <row r="36" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="19" t="s">
-        <v>648</v>
+        <v>638</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="C36" s="25" t="s">
-        <v>649</v>
+        <v>639</v>
       </c>
       <c r="D36" s="26"/>
       <c r="E36" s="26"/>
       <c r="F36" s="27"/>
       <c r="G36" s="5"/>
       <c r="H36" s="16" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="19" t="s">
+        <v>518</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="C37" s="25" t="s">
         <v>650</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="1" t="s">
-        <v>523</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>478</v>
-      </c>
-      <c r="C37" s="25" t="s">
-        <v>662</v>
       </c>
       <c r="D37" s="26"/>
       <c r="E37" s="26"/>
       <c r="F37" s="27"/>
       <c r="G37" s="5"/>
       <c r="H37" s="16" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
@@ -3738,16 +3745,16 @@
       <c r="H40" s="11"/>
     </row>
     <row r="41" spans="1:8" s="3" customFormat="1" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="29" t="s">
-        <v>525</v>
-      </c>
-      <c r="B41" s="29"/>
-      <c r="C41" s="29"/>
-      <c r="D41" s="29"/>
-      <c r="E41" s="29"/>
-      <c r="F41" s="29"/>
-      <c r="G41" s="29"/>
-      <c r="H41" s="29"/>
+      <c r="A41" s="28" t="s">
+        <v>520</v>
+      </c>
+      <c r="B41" s="28"/>
+      <c r="C41" s="28"/>
+      <c r="D41" s="28"/>
+      <c r="E41" s="28"/>
+      <c r="F41" s="28"/>
+      <c r="G41" s="28"/>
+      <c r="H41" s="28"/>
     </row>
     <row r="42" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="1" t="s">
@@ -3772,7 +3779,7 @@
         <v>3</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="43" spans="1:8" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.4">
@@ -3783,20 +3790,20 @@
         <v>17</v>
       </c>
       <c r="C43" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="E43" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="D43" s="6" t="s">
+      <c r="F43" s="5" t="s">
         <v>208</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="F43" s="5" t="s">
-        <v>210</v>
       </c>
       <c r="G43" s="4"/>
       <c r="H43" s="16" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -3804,7 +3811,7 @@
     </row>
     <row r="45" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="F45" s="3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="H45" s="2"/>
     </row>
@@ -3812,28 +3819,28 @@
       <c r="H46" s="2"/>
     </row>
     <row r="47" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="29" t="s">
+      <c r="A47" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="B47" s="29"/>
-      <c r="C47" s="29"/>
-      <c r="D47" s="29"/>
-      <c r="E47" s="29"/>
-      <c r="F47" s="29"/>
-      <c r="G47" s="29"/>
-      <c r="H47" s="29"/>
+      <c r="B47" s="28"/>
+      <c r="C47" s="28"/>
+      <c r="D47" s="28"/>
+      <c r="E47" s="28"/>
+      <c r="F47" s="28"/>
+      <c r="G47" s="28"/>
+      <c r="H47" s="28"/>
     </row>
     <row r="48" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="29" t="s">
-        <v>538</v>
-      </c>
-      <c r="B48" s="29"/>
-      <c r="C48" s="29"/>
-      <c r="D48" s="29"/>
-      <c r="E48" s="29"/>
-      <c r="F48" s="29"/>
-      <c r="G48" s="29"/>
-      <c r="H48" s="29"/>
+      <c r="A48" s="28" t="s">
+        <v>533</v>
+      </c>
+      <c r="B48" s="28"/>
+      <c r="C48" s="28"/>
+      <c r="D48" s="28"/>
+      <c r="E48" s="28"/>
+      <c r="F48" s="28"/>
+      <c r="G48" s="28"/>
+      <c r="H48" s="28"/>
     </row>
     <row r="49" spans="1:12" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="1" t="s">
@@ -3858,17 +3865,17 @@
         <v>3</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="50" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="40">
-        <v>1</v>
-      </c>
-      <c r="B50" s="39" t="s">
+      <c r="A50" s="51">
+        <v>1</v>
+      </c>
+      <c r="B50" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="C50" s="29" t="s">
+      <c r="C50" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D50" s="6" t="s">
@@ -3880,15 +3887,15 @@
       <c r="F50" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G50" s="28"/>
+      <c r="G50" s="32"/>
       <c r="H50" s="15" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="51" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="40"/>
-      <c r="B51" s="39"/>
-      <c r="C51" s="29"/>
+      <c r="A51" s="51"/>
+      <c r="B51" s="50"/>
+      <c r="C51" s="28"/>
       <c r="D51" s="6" t="s">
         <v>18</v>
       </c>
@@ -3898,9 +3905,9 @@
       <c r="F51" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G51" s="28"/>
+      <c r="G51" s="32"/>
       <c r="H51" s="15" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
@@ -3908,13 +3915,13 @@
       <c r="L51" s="2"/>
     </row>
     <row r="52" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="34">
+      <c r="A52" s="41">
         <v>2</v>
       </c>
-      <c r="B52" s="39" t="s">
+      <c r="B52" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="29" t="s">
+      <c r="C52" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D52" s="6" t="s">
@@ -3926,9 +3933,9 @@
       <c r="F52" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G52" s="28"/>
+      <c r="G52" s="32"/>
       <c r="H52" s="15" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
@@ -3936,9 +3943,9 @@
       <c r="L52" s="2"/>
     </row>
     <row r="53" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="35"/>
-      <c r="B53" s="39"/>
-      <c r="C53" s="29"/>
+      <c r="A53" s="42"/>
+      <c r="B53" s="50"/>
+      <c r="C53" s="28"/>
       <c r="D53" s="6" t="s">
         <v>19</v>
       </c>
@@ -3948,9 +3955,9 @@
       <c r="F53" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G53" s="28"/>
+      <c r="G53" s="32"/>
       <c r="H53" s="15" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
@@ -3958,13 +3965,13 @@
       <c r="L53" s="2"/>
     </row>
     <row r="54" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="34">
+      <c r="A54" s="41">
         <v>3</v>
       </c>
-      <c r="B54" s="39" t="s">
+      <c r="B54" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="29" t="s">
+      <c r="C54" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D54" s="5" t="s">
@@ -3974,11 +3981,11 @@
         <v>1</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>518</v>
-      </c>
-      <c r="G54" s="28"/>
+        <v>513</v>
+      </c>
+      <c r="G54" s="32"/>
       <c r="H54" s="15" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
@@ -3986,9 +3993,9 @@
       <c r="L54" s="2"/>
     </row>
     <row r="55" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="35"/>
-      <c r="B55" s="39"/>
-      <c r="C55" s="29"/>
+      <c r="A55" s="42"/>
+      <c r="B55" s="50"/>
+      <c r="C55" s="28"/>
       <c r="D55" s="5" t="s">
         <v>20</v>
       </c>
@@ -3996,11 +4003,11 @@
         <v>1</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>536</v>
-      </c>
-      <c r="G55" s="28"/>
+        <v>531</v>
+      </c>
+      <c r="G55" s="32"/>
       <c r="H55" s="15" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
@@ -4008,13 +4015,13 @@
       <c r="L55" s="2"/>
     </row>
     <row r="56" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="34">
+      <c r="A56" s="41">
         <v>4</v>
       </c>
-      <c r="B56" s="39" t="s">
+      <c r="B56" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="C56" s="29" t="s">
+      <c r="C56" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D56" s="5" t="s">
@@ -4024,11 +4031,11 @@
         <v>1</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>490</v>
-      </c>
-      <c r="G56" s="28"/>
+        <v>485</v>
+      </c>
+      <c r="G56" s="32"/>
       <c r="H56" s="15" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
@@ -4036,9 +4043,9 @@
       <c r="L56" s="2"/>
     </row>
     <row r="57" spans="1:12" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="35"/>
-      <c r="B57" s="39"/>
-      <c r="C57" s="29"/>
+      <c r="A57" s="42"/>
+      <c r="B57" s="50"/>
+      <c r="C57" s="28"/>
       <c r="D57" s="5" t="s">
         <v>25</v>
       </c>
@@ -4046,11 +4053,11 @@
         <v>1</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>534</v>
-      </c>
-      <c r="G57" s="28"/>
+        <v>529</v>
+      </c>
+      <c r="G57" s="32"/>
       <c r="H57" s="15" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
@@ -4058,13 +4065,13 @@
       <c r="L57" s="2"/>
     </row>
     <row r="58" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="34">
+      <c r="A58" s="41">
         <v>5</v>
       </c>
-      <c r="B58" s="30" t="s">
+      <c r="B58" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="C58" s="29" t="s">
+      <c r="C58" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D58" s="5" t="s">
@@ -4074,13 +4081,13 @@
         <v>1</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>514</v>
-      </c>
-      <c r="G58" s="28" t="s">
-        <v>515</v>
+        <v>509</v>
+      </c>
+      <c r="G58" s="32" t="s">
+        <v>510</v>
       </c>
       <c r="H58" s="15" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
@@ -4088,9 +4095,9 @@
       <c r="L58" s="2"/>
     </row>
     <row r="59" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A59" s="35"/>
-      <c r="B59" s="30"/>
-      <c r="C59" s="29"/>
+      <c r="A59" s="42"/>
+      <c r="B59" s="38"/>
+      <c r="C59" s="28"/>
       <c r="D59" s="5" t="s">
         <v>26</v>
       </c>
@@ -4098,11 +4105,11 @@
         <v>1</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>556</v>
-      </c>
-      <c r="G59" s="28"/>
+        <v>551</v>
+      </c>
+      <c r="G59" s="32"/>
       <c r="H59" s="15" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
@@ -4110,13 +4117,13 @@
       <c r="L59" s="2"/>
     </row>
     <row r="60" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="34">
+      <c r="A60" s="41">
         <v>6</v>
       </c>
-      <c r="B60" s="30" t="s">
+      <c r="B60" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="C60" s="29" t="s">
+      <c r="C60" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D60" s="5" t="s">
@@ -4126,11 +4133,11 @@
         <v>0</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>596</v>
-      </c>
-      <c r="G60" s="28"/>
+        <v>591</v>
+      </c>
+      <c r="G60" s="32"/>
       <c r="H60" s="15" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
@@ -4138,9 +4145,9 @@
       <c r="L60" s="2"/>
     </row>
     <row r="61" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="35"/>
-      <c r="B61" s="30"/>
-      <c r="C61" s="29"/>
+      <c r="A61" s="42"/>
+      <c r="B61" s="38"/>
+      <c r="C61" s="28"/>
       <c r="D61" s="5" t="s">
         <v>28</v>
       </c>
@@ -4148,11 +4155,11 @@
         <v>0</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>595</v>
-      </c>
-      <c r="G61" s="28"/>
+        <v>590</v>
+      </c>
+      <c r="G61" s="32"/>
       <c r="H61" s="15" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
@@ -4160,13 +4167,13 @@
       <c r="L61" s="2"/>
     </row>
     <row r="62" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="34">
+      <c r="A62" s="41">
         <v>7</v>
       </c>
-      <c r="B62" s="30" t="s">
+      <c r="B62" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="C62" s="29" t="s">
+      <c r="C62" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D62" s="5" t="s">
@@ -4176,11 +4183,11 @@
         <v>1</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="G62" s="28"/>
+        <v>144</v>
+      </c>
+      <c r="G62" s="32"/>
       <c r="H62" s="15" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="I62" s="2"/>
       <c r="J62" s="2"/>
@@ -4188,9 +4195,9 @@
       <c r="L62" s="2"/>
     </row>
     <row r="63" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="35"/>
-      <c r="B63" s="30"/>
-      <c r="C63" s="29"/>
+      <c r="A63" s="42"/>
+      <c r="B63" s="38"/>
+      <c r="C63" s="28"/>
       <c r="D63" s="5" t="s">
         <v>38</v>
       </c>
@@ -4198,11 +4205,11 @@
         <v>1</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="G63" s="28"/>
+        <v>145</v>
+      </c>
+      <c r="G63" s="32"/>
       <c r="H63" s="15" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
@@ -4210,29 +4217,29 @@
       <c r="L63" s="2"/>
     </row>
     <row r="64" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A64" s="34">
+      <c r="A64" s="41">
         <v>8</v>
       </c>
-      <c r="B64" s="30" t="s">
+      <c r="B64" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="C64" s="29" t="s">
+      <c r="C64" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E64" s="1">
         <v>0</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>597</v>
-      </c>
-      <c r="G64" s="28" t="s">
-        <v>569</v>
+        <v>592</v>
+      </c>
+      <c r="G64" s="32" t="s">
+        <v>564</v>
       </c>
       <c r="H64" s="15" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I64" s="2"/>
       <c r="J64" s="2"/>
@@ -4240,21 +4247,21 @@
       <c r="L64" s="2"/>
     </row>
     <row r="65" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A65" s="35"/>
-      <c r="B65" s="30"/>
-      <c r="C65" s="29"/>
+      <c r="A65" s="42"/>
+      <c r="B65" s="38"/>
+      <c r="C65" s="28"/>
       <c r="D65" s="5" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E65" s="1">
         <v>0</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>598</v>
-      </c>
-      <c r="G65" s="28"/>
+        <v>593</v>
+      </c>
+      <c r="G65" s="32"/>
       <c r="H65" s="15" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="I65" s="2"/>
       <c r="J65" s="2"/>
@@ -4262,13 +4269,13 @@
       <c r="L65" s="2"/>
     </row>
     <row r="66" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A66" s="34">
+      <c r="A66" s="41">
         <v>9</v>
       </c>
-      <c r="B66" s="30" t="s">
+      <c r="B66" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="C66" s="29" t="s">
+      <c r="C66" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D66" s="5" t="s">
@@ -4278,19 +4285,19 @@
         <v>1</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>566</v>
-      </c>
-      <c r="G66" s="28" t="s">
-        <v>570</v>
+        <v>561</v>
+      </c>
+      <c r="G66" s="32" t="s">
+        <v>565</v>
       </c>
       <c r="H66" s="15" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="67" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A67" s="35"/>
-      <c r="B67" s="30"/>
-      <c r="C67" s="29"/>
+      <c r="A67" s="42"/>
+      <c r="B67" s="38"/>
+      <c r="C67" s="28"/>
       <c r="D67" s="5" t="s">
         <v>115</v>
       </c>
@@ -4298,37 +4305,37 @@
         <v>1</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>567</v>
-      </c>
-      <c r="G67" s="28"/>
+        <v>562</v>
+      </c>
+      <c r="G67" s="32"/>
       <c r="H67" s="15" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
     </row>
     <row r="68" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A68" s="34">
+      <c r="A68" s="41">
         <v>10</v>
       </c>
-      <c r="B68" s="30" t="s">
+      <c r="B68" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="C68" s="29" t="s">
+      <c r="C68" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E68" s="1">
         <v>1</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>548</v>
-      </c>
-      <c r="G68" s="28" t="s">
-        <v>571</v>
+        <v>543</v>
+      </c>
+      <c r="G68" s="32" t="s">
+        <v>566</v>
       </c>
       <c r="H68" s="15" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="I68" s="2"/>
       <c r="J68" s="2"/>
@@ -4336,21 +4343,21 @@
       <c r="L68" s="2"/>
     </row>
     <row r="69" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A69" s="35"/>
-      <c r="B69" s="30"/>
-      <c r="C69" s="29"/>
+      <c r="A69" s="42"/>
+      <c r="B69" s="38"/>
+      <c r="C69" s="28"/>
       <c r="D69" s="5" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E69" s="1">
         <v>1</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>547</v>
-      </c>
-      <c r="G69" s="28"/>
+        <v>542</v>
+      </c>
+      <c r="G69" s="32"/>
       <c r="H69" s="15" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="I69" s="2"/>
       <c r="J69" s="2"/>
@@ -4358,29 +4365,29 @@
       <c r="L69" s="2"/>
     </row>
     <row r="70" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A70" s="34">
+      <c r="A70" s="41">
         <v>11</v>
       </c>
-      <c r="B70" s="30" t="s">
+      <c r="B70" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="C70" s="29" t="s">
+      <c r="C70" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E70" s="1">
         <v>0</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>639</v>
-      </c>
-      <c r="G70" s="28" t="s">
-        <v>569</v>
+        <v>631</v>
+      </c>
+      <c r="G70" s="32" t="s">
+        <v>564</v>
       </c>
       <c r="H70" s="15" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="I70" s="2"/>
       <c r="J70" s="2"/>
@@ -4388,21 +4395,21 @@
       <c r="L70" s="2"/>
     </row>
     <row r="71" spans="1:12" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A71" s="35"/>
-      <c r="B71" s="30"/>
-      <c r="C71" s="29"/>
+      <c r="A71" s="42"/>
+      <c r="B71" s="38"/>
+      <c r="C71" s="28"/>
       <c r="D71" s="5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E71" s="1">
         <v>0</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>640</v>
-      </c>
-      <c r="G71" s="28"/>
+        <v>632</v>
+      </c>
+      <c r="G71" s="32"/>
       <c r="H71" s="15" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="I71" s="2"/>
       <c r="J71" s="2"/>
@@ -4410,13 +4417,13 @@
       <c r="L71" s="2"/>
     </row>
     <row r="72" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A72" s="34">
+      <c r="A72" s="41">
         <v>12</v>
       </c>
-      <c r="B72" s="33" t="s">
+      <c r="B72" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C72" s="29" t="s">
+      <c r="C72" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D72" s="5" t="s">
@@ -4426,13 +4433,13 @@
         <v>0</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>637</v>
-      </c>
-      <c r="G72" s="28" t="s">
-        <v>569</v>
+        <v>629</v>
+      </c>
+      <c r="G72" s="32" t="s">
+        <v>564</v>
       </c>
       <c r="H72" s="15" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="I72" s="2"/>
       <c r="J72" s="2"/>
@@ -4440,9 +4447,9 @@
       <c r="L72" s="2"/>
     </row>
     <row r="73" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A73" s="35"/>
-      <c r="B73" s="33"/>
-      <c r="C73" s="29"/>
+      <c r="A73" s="42"/>
+      <c r="B73" s="36"/>
+      <c r="C73" s="28"/>
       <c r="D73" s="5" t="s">
         <v>36</v>
       </c>
@@ -4450,11 +4457,11 @@
         <v>0</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>638</v>
-      </c>
-      <c r="G73" s="28"/>
+        <v>630</v>
+      </c>
+      <c r="G73" s="32"/>
       <c r="H73" s="15" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="I73" s="2"/>
       <c r="J73" s="2"/>
@@ -4462,13 +4469,13 @@
       <c r="L73" s="2"/>
     </row>
     <row r="74" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A74" s="41">
+      <c r="A74" s="33">
         <v>13</v>
       </c>
-      <c r="B74" s="33" t="s">
+      <c r="B74" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C74" s="29" t="s">
+      <c r="C74" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D74" s="5" t="s">
@@ -4478,11 +4485,11 @@
         <v>0</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>545</v>
-      </c>
-      <c r="G74" s="28"/>
+        <v>540</v>
+      </c>
+      <c r="G74" s="32"/>
       <c r="H74" s="15" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="I74" s="2"/>
       <c r="J74" s="2"/>
@@ -4490,9 +4497,9 @@
       <c r="L74" s="2"/>
     </row>
     <row r="75" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A75" s="42"/>
-      <c r="B75" s="33"/>
-      <c r="C75" s="29"/>
+      <c r="A75" s="34"/>
+      <c r="B75" s="36"/>
+      <c r="C75" s="28"/>
       <c r="D75" s="5" t="s">
         <v>34</v>
       </c>
@@ -4500,11 +4507,11 @@
         <v>0</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>546</v>
-      </c>
-      <c r="G75" s="28"/>
+        <v>541</v>
+      </c>
+      <c r="G75" s="32"/>
       <c r="H75" s="15" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="I75" s="2"/>
       <c r="J75" s="2"/>
@@ -4512,13 +4519,13 @@
       <c r="L75" s="2"/>
     </row>
     <row r="76" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A76" s="34">
+      <c r="A76" s="41">
         <v>14</v>
       </c>
-      <c r="B76" s="33" t="s">
+      <c r="B76" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C76" s="29" t="s">
+      <c r="C76" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D76" s="5" t="s">
@@ -4528,13 +4535,13 @@
         <v>1</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>491</v>
-      </c>
-      <c r="G76" s="28" t="s">
-        <v>569</v>
+        <v>486</v>
+      </c>
+      <c r="G76" s="32" t="s">
+        <v>564</v>
       </c>
       <c r="H76" s="15" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="I76" s="2"/>
       <c r="J76" s="2"/>
@@ -4542,9 +4549,9 @@
       <c r="L76" s="2"/>
     </row>
     <row r="77" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A77" s="35"/>
-      <c r="B77" s="33"/>
-      <c r="C77" s="29"/>
+      <c r="A77" s="42"/>
+      <c r="B77" s="36"/>
+      <c r="C77" s="28"/>
       <c r="D77" s="5" t="s">
         <v>126</v>
       </c>
@@ -4552,21 +4559,21 @@
         <v>1</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>492</v>
-      </c>
-      <c r="G77" s="28"/>
+        <v>487</v>
+      </c>
+      <c r="G77" s="32"/>
       <c r="H77" s="15" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
     </row>
     <row r="78" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A78" s="34">
+      <c r="A78" s="41">
         <v>15</v>
       </c>
-      <c r="B78" s="33" t="s">
+      <c r="B78" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C78" s="29" t="s">
+      <c r="C78" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D78" s="5" t="s">
@@ -4576,19 +4583,19 @@
         <v>2</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>632</v>
-      </c>
-      <c r="G78" s="28" t="s">
-        <v>629</v>
+        <v>624</v>
+      </c>
+      <c r="G78" s="32" t="s">
+        <v>621</v>
       </c>
       <c r="H78" s="15" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="79" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A79" s="35"/>
-      <c r="B79" s="33"/>
-      <c r="C79" s="29"/>
+      <c r="A79" s="42"/>
+      <c r="B79" s="36"/>
+      <c r="C79" s="28"/>
       <c r="D79" s="5" t="s">
         <v>124</v>
       </c>
@@ -4596,21 +4603,21 @@
         <v>2</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>633</v>
-      </c>
-      <c r="G79" s="28"/>
+        <v>625</v>
+      </c>
+      <c r="G79" s="32"/>
       <c r="H79" s="15" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
     </row>
     <row r="80" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A80" s="41">
+      <c r="A80" s="33">
         <v>16</v>
       </c>
-      <c r="B80" s="33" t="s">
+      <c r="B80" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C80" s="50" t="s">
+      <c r="C80" s="39" t="s">
         <v>6</v>
       </c>
       <c r="D80" s="5" t="s">
@@ -4620,19 +4627,19 @@
         <v>2</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>631</v>
-      </c>
-      <c r="G80" s="28" t="s">
-        <v>544</v>
+        <v>623</v>
+      </c>
+      <c r="G80" s="32" t="s">
+        <v>539</v>
       </c>
       <c r="H80" s="15" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
     </row>
     <row r="81" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A81" s="42"/>
-      <c r="B81" s="33"/>
-      <c r="C81" s="51"/>
+      <c r="A81" s="34"/>
+      <c r="B81" s="36"/>
+      <c r="C81" s="40"/>
       <c r="D81" s="5" t="s">
         <v>122</v>
       </c>
@@ -4640,21 +4647,21 @@
         <v>2</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>543</v>
-      </c>
-      <c r="G81" s="28"/>
+        <v>538</v>
+      </c>
+      <c r="G81" s="32"/>
       <c r="H81" s="15" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A82" s="41">
+      <c r="A82" s="33">
         <v>17</v>
       </c>
-      <c r="B82" s="33" t="s">
+      <c r="B82" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C82" s="29" t="s">
+      <c r="C82" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D82" s="5" t="s">
@@ -4664,19 +4671,19 @@
         <v>1</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>630</v>
-      </c>
-      <c r="G82" s="28" t="s">
-        <v>222</v>
+        <v>622</v>
+      </c>
+      <c r="G82" s="32" t="s">
+        <v>220</v>
       </c>
       <c r="H82" s="15" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="83" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A83" s="42"/>
-      <c r="B83" s="33"/>
-      <c r="C83" s="29"/>
+      <c r="A83" s="34"/>
+      <c r="B83" s="36"/>
+      <c r="C83" s="28"/>
       <c r="D83" s="5" t="s">
         <v>40</v>
       </c>
@@ -4684,21 +4691,21 @@
         <v>1</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>507</v>
-      </c>
-      <c r="G83" s="28"/>
+        <v>502</v>
+      </c>
+      <c r="G83" s="32"/>
       <c r="H83" s="15" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
     </row>
     <row r="84" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A84" s="41">
+      <c r="A84" s="33">
         <v>18</v>
       </c>
-      <c r="B84" s="33" t="s">
+      <c r="B84" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C84" s="45" t="s">
+      <c r="C84" s="37" t="s">
         <v>6</v>
       </c>
       <c r="D84" s="5" t="s">
@@ -4708,19 +4715,19 @@
         <v>43</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>493</v>
-      </c>
-      <c r="G84" s="28" t="s">
-        <v>506</v>
+        <v>488</v>
+      </c>
+      <c r="G84" s="32" t="s">
+        <v>501</v>
       </c>
       <c r="H84" s="15" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="85" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A85" s="42"/>
-      <c r="B85" s="33"/>
-      <c r="C85" s="45"/>
+      <c r="A85" s="34"/>
+      <c r="B85" s="36"/>
+      <c r="C85" s="37"/>
       <c r="D85" s="5" t="s">
         <v>42</v>
       </c>
@@ -4728,21 +4735,21 @@
         <v>43</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>494</v>
-      </c>
-      <c r="G85" s="28"/>
+        <v>489</v>
+      </c>
+      <c r="G85" s="32"/>
       <c r="H85" s="15" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
     </row>
     <row r="86" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A86" s="41">
+      <c r="A86" s="33">
         <v>19</v>
       </c>
-      <c r="B86" s="33" t="s">
+      <c r="B86" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C86" s="29" t="s">
+      <c r="C86" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D86" s="5" t="s">
@@ -4752,17 +4759,17 @@
         <v>1</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>609</v>
-      </c>
-      <c r="G86" s="28"/>
+        <v>603</v>
+      </c>
+      <c r="G86" s="32"/>
       <c r="H86" s="15" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
     </row>
     <row r="87" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A87" s="42"/>
-      <c r="B87" s="33"/>
-      <c r="C87" s="29"/>
+      <c r="A87" s="34"/>
+      <c r="B87" s="36"/>
+      <c r="C87" s="28"/>
       <c r="D87" s="5" t="s">
         <v>84</v>
       </c>
@@ -4770,65 +4777,65 @@
         <v>1</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>610</v>
-      </c>
-      <c r="G87" s="28"/>
+        <v>604</v>
+      </c>
+      <c r="G87" s="32"/>
       <c r="H87" s="15" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
     </row>
     <row r="88" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A88" s="41">
+      <c r="A88" s="33">
         <v>20</v>
       </c>
-      <c r="B88" s="31" t="s">
+      <c r="B88" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C88" s="29" t="s">
+      <c r="C88" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D88" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="E88" s="1">
+        <v>1</v>
+      </c>
+      <c r="F88" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="G88" s="32" t="s">
         <v>273</v>
       </c>
-      <c r="E88" s="1">
-        <v>1</v>
-      </c>
-      <c r="F88" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="G88" s="28" t="s">
+      <c r="H88" s="15" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A89" s="34"/>
+      <c r="B89" s="35"/>
+      <c r="C89" s="28"/>
+      <c r="D89" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="E89" s="1">
+        <v>1</v>
+      </c>
+      <c r="F89" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="H88" s="15" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A89" s="42"/>
-      <c r="B89" s="31"/>
-      <c r="C89" s="29"/>
-      <c r="D89" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="E89" s="1">
-        <v>1</v>
-      </c>
-      <c r="F89" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="G89" s="28"/>
+      <c r="G89" s="32"/>
       <c r="H89" s="15" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
     </row>
     <row r="90" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A90" s="41">
+      <c r="A90" s="33">
         <v>21</v>
       </c>
-      <c r="B90" s="31" t="s">
+      <c r="B90" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C90" s="29" t="s">
+      <c r="C90" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D90" s="5" t="s">
@@ -4838,19 +4845,19 @@
         <v>0</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>551</v>
-      </c>
-      <c r="G90" s="28" t="s">
-        <v>555</v>
+        <v>546</v>
+      </c>
+      <c r="G90" s="32" t="s">
+        <v>550</v>
       </c>
       <c r="H90" s="15" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="91" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A91" s="42"/>
-      <c r="B91" s="31"/>
-      <c r="C91" s="29"/>
+      <c r="A91" s="34"/>
+      <c r="B91" s="35"/>
+      <c r="C91" s="28"/>
       <c r="D91" s="5" t="s">
         <v>128</v>
       </c>
@@ -4858,65 +4865,65 @@
         <v>0</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>552</v>
-      </c>
-      <c r="G91" s="28"/>
+        <v>547</v>
+      </c>
+      <c r="G91" s="32"/>
       <c r="H91" s="15" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
     </row>
     <row r="92" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A92" s="34">
+      <c r="A92" s="41">
         <v>22</v>
       </c>
-      <c r="B92" s="31" t="s">
+      <c r="B92" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C92" s="29" t="s">
+      <c r="C92" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E92" s="1">
         <v>2</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>516</v>
-      </c>
-      <c r="G92" s="28" t="s">
-        <v>510</v>
+        <v>511</v>
+      </c>
+      <c r="G92" s="32" t="s">
+        <v>505</v>
       </c>
       <c r="H92" s="15" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="93" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A93" s="35"/>
-      <c r="B93" s="31"/>
-      <c r="C93" s="29"/>
+      <c r="A93" s="42"/>
+      <c r="B93" s="35"/>
+      <c r="C93" s="28"/>
       <c r="D93" s="5" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E93" s="1">
         <v>2</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>517</v>
-      </c>
-      <c r="G93" s="28"/>
+        <v>512</v>
+      </c>
+      <c r="G93" s="32"/>
       <c r="H93" s="15" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
     </row>
     <row r="94" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="41">
         <v>23</v>
       </c>
-      <c r="B94" s="31" t="s">
+      <c r="B94" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C94" s="29" t="s">
+      <c r="C94" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D94" s="5" t="s">
@@ -4926,19 +4933,19 @@
         <v>2</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>663</v>
-      </c>
-      <c r="G94" s="28" t="s">
-        <v>290</v>
+        <v>651</v>
+      </c>
+      <c r="G94" s="32" t="s">
+        <v>288</v>
       </c>
       <c r="H94" s="15" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="95" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="42"/>
-      <c r="B95" s="31"/>
-      <c r="C95" s="29"/>
+      <c r="B95" s="35"/>
+      <c r="C95" s="28"/>
       <c r="D95" s="5" t="s">
         <v>31</v>
       </c>
@@ -4946,149 +4953,149 @@
         <v>2</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>661</v>
-      </c>
-      <c r="G95" s="28"/>
+        <v>649</v>
+      </c>
+      <c r="G95" s="32"/>
       <c r="H95" s="15" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
     </row>
     <row r="96" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A96" s="41">
+      <c r="A96" s="33">
         <v>24</v>
       </c>
-      <c r="B96" s="31" t="s">
+      <c r="B96" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C96" s="29" t="s">
+      <c r="C96" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>549</v>
-      </c>
-      <c r="G96" s="28" t="s">
-        <v>203</v>
+        <v>544</v>
+      </c>
+      <c r="G96" s="32" t="s">
+        <v>201</v>
       </c>
       <c r="H96" s="15" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="97" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A97" s="42"/>
-      <c r="B97" s="31"/>
-      <c r="C97" s="29"/>
+      <c r="A97" s="34"/>
+      <c r="B97" s="35"/>
+      <c r="C97" s="28"/>
       <c r="D97" s="5" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>550</v>
-      </c>
-      <c r="G97" s="28"/>
+        <v>545</v>
+      </c>
+      <c r="G97" s="32"/>
       <c r="H97" s="15" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="98" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A98" s="34">
+      <c r="A98" s="41">
         <v>25</v>
       </c>
-      <c r="B98" s="30" t="s">
+      <c r="B98" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="C98" s="29" t="s">
+      <c r="C98" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E98" s="1">
         <v>0</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>540</v>
-      </c>
-      <c r="G98" s="28"/>
+        <v>535</v>
+      </c>
+      <c r="G98" s="32"/>
       <c r="H98" s="15" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="99" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A99" s="35"/>
-      <c r="B99" s="30"/>
-      <c r="C99" s="29"/>
+      <c r="A99" s="42"/>
+      <c r="B99" s="38"/>
+      <c r="C99" s="28"/>
       <c r="D99" s="5" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E99" s="1">
         <v>0</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>541</v>
-      </c>
-      <c r="G99" s="28"/>
+        <v>536</v>
+      </c>
+      <c r="G99" s="32"/>
       <c r="H99" s="15" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
     </row>
     <row r="100" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A100" s="41">
+      <c r="A100" s="33">
         <v>26</v>
       </c>
-      <c r="B100" s="30" t="s">
+      <c r="B100" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="C100" s="45" t="s">
+      <c r="C100" s="37" t="s">
         <v>14</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E100" s="1">
         <v>1</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>612</v>
-      </c>
-      <c r="G100" s="28"/>
+        <v>660</v>
+      </c>
+      <c r="G100" s="32"/>
       <c r="H100" s="15" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="101" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A101" s="42"/>
-      <c r="B101" s="30"/>
-      <c r="C101" s="45"/>
+      <c r="A101" s="34"/>
+      <c r="B101" s="38"/>
+      <c r="C101" s="37"/>
       <c r="D101" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E101" s="1">
         <v>1</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>613</v>
-      </c>
-      <c r="G101" s="28"/>
+        <v>661</v>
+      </c>
+      <c r="G101" s="32"/>
       <c r="H101" s="15" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
     </row>
     <row r="102" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A102" s="41">
+      <c r="A102" s="33">
         <v>27</v>
       </c>
-      <c r="B102" s="30" t="s">
+      <c r="B102" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="C102" s="29" t="s">
+      <c r="C102" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D102" s="5" t="s">
@@ -5098,17 +5105,17 @@
         <v>1</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="G102" s="28"/>
+        <v>265</v>
+      </c>
+      <c r="G102" s="32"/>
       <c r="H102" s="15" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="103" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A103" s="42"/>
-      <c r="B103" s="30"/>
-      <c r="C103" s="29"/>
+      <c r="A103" s="34"/>
+      <c r="B103" s="38"/>
+      <c r="C103" s="28"/>
       <c r="D103" s="5" t="s">
         <v>45</v>
       </c>
@@ -5116,21 +5123,21 @@
         <v>1</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="G103" s="28"/>
+        <v>266</v>
+      </c>
+      <c r="G103" s="32"/>
       <c r="H103" s="15" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
     </row>
     <row r="104" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A104" s="41">
+      <c r="A104" s="33">
         <v>28</v>
       </c>
-      <c r="B104" s="30" t="s">
+      <c r="B104" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="C104" s="29" t="s">
+      <c r="C104" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D104" s="5" t="s">
@@ -5140,17 +5147,17 @@
         <v>1</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>593</v>
-      </c>
-      <c r="G104" s="28"/>
+        <v>588</v>
+      </c>
+      <c r="G104" s="32"/>
       <c r="H104" s="15" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="105" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A105" s="42"/>
-      <c r="B105" s="30"/>
-      <c r="C105" s="29"/>
+      <c r="A105" s="34"/>
+      <c r="B105" s="38"/>
+      <c r="C105" s="28"/>
       <c r="D105" s="5" t="s">
         <v>68</v>
       </c>
@@ -5158,65 +5165,65 @@
         <v>1</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>594</v>
-      </c>
-      <c r="G105" s="28"/>
+        <v>589</v>
+      </c>
+      <c r="G105" s="32"/>
       <c r="H105" s="15" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
     </row>
     <row r="106" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A106" s="41">
+      <c r="A106" s="33">
         <v>29</v>
       </c>
-      <c r="B106" s="30" t="s">
+      <c r="B106" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="C106" s="29" t="s">
+      <c r="C106" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E106" s="1">
         <v>0</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="G106" s="28" t="s">
-        <v>537</v>
+        <v>285</v>
+      </c>
+      <c r="G106" s="32" t="s">
+        <v>532</v>
       </c>
       <c r="H106" s="15" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="107" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A107" s="42"/>
-      <c r="B107" s="30"/>
-      <c r="C107" s="29"/>
+      <c r="A107" s="34"/>
+      <c r="B107" s="38"/>
+      <c r="C107" s="28"/>
       <c r="D107" s="5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E107" s="1">
         <v>0</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="G107" s="28"/>
+        <v>286</v>
+      </c>
+      <c r="G107" s="32"/>
       <c r="H107" s="15" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
     </row>
     <row r="108" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A108" s="34">
+      <c r="A108" s="41">
         <v>30</v>
       </c>
-      <c r="B108" s="30" t="s">
+      <c r="B108" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="C108" s="29" t="s">
+      <c r="C108" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D108" s="5" t="s">
@@ -5226,19 +5233,19 @@
         <v>1</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>644</v>
-      </c>
-      <c r="G108" s="28" t="s">
-        <v>223</v>
+        <v>636</v>
+      </c>
+      <c r="G108" s="32" t="s">
+        <v>221</v>
       </c>
       <c r="H108" s="15" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="109" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A109" s="35"/>
-      <c r="B109" s="30"/>
-      <c r="C109" s="29"/>
+      <c r="A109" s="42"/>
+      <c r="B109" s="38"/>
+      <c r="C109" s="28"/>
       <c r="D109" s="5" t="s">
         <v>47</v>
       </c>
@@ -5246,85 +5253,85 @@
         <v>1</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>645</v>
-      </c>
-      <c r="G109" s="28"/>
+        <v>637</v>
+      </c>
+      <c r="G109" s="32"/>
       <c r="H109" s="15" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
     </row>
     <row r="110" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A110" s="34">
+      <c r="A110" s="41">
         <v>31</v>
       </c>
-      <c r="B110" s="43" t="s">
+      <c r="B110" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="C110" s="32" t="s">
+      <c r="C110" s="43" t="s">
         <v>14</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E110" s="1">
         <v>1</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>646</v>
-      </c>
-      <c r="G110" s="46" t="s">
-        <v>269</v>
+        <v>662</v>
+      </c>
+      <c r="G110" s="48" t="s">
+        <v>267</v>
       </c>
       <c r="H110" s="15" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="111" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A111" s="35"/>
-      <c r="B111" s="44"/>
-      <c r="C111" s="32"/>
+      <c r="A111" s="42"/>
+      <c r="B111" s="47"/>
+      <c r="C111" s="43"/>
       <c r="D111" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E111" s="1">
         <v>1</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>647</v>
-      </c>
-      <c r="G111" s="47"/>
+        <v>663</v>
+      </c>
+      <c r="G111" s="49"/>
       <c r="H111" s="15" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
     </row>
     <row r="112" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A112" s="41">
+      <c r="A112" s="33">
         <v>32</v>
       </c>
-      <c r="B112" s="30" t="s">
+      <c r="B112" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="C112" s="45" t="s">
+      <c r="C112" s="37" t="s">
         <v>14</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="G112" s="28"/>
+        <v>211</v>
+      </c>
+      <c r="G112" s="32"/>
       <c r="H112" s="15" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="113" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A113" s="42"/>
-      <c r="B113" s="30"/>
-      <c r="C113" s="45"/>
+      <c r="A113" s="34"/>
+      <c r="B113" s="38"/>
+      <c r="C113" s="37"/>
       <c r="D113" s="5" t="s">
         <v>52</v>
       </c>
@@ -5332,21 +5339,21 @@
         <v>43</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="G113" s="28"/>
+        <v>210</v>
+      </c>
+      <c r="G113" s="32"/>
       <c r="H113" s="15" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
     </row>
     <row r="114" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A114" s="34">
+      <c r="A114" s="41">
         <v>33</v>
       </c>
-      <c r="B114" s="30" t="s">
+      <c r="B114" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="C114" s="29" t="s">
+      <c r="C114" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D114" s="5" t="s">
@@ -5356,17 +5363,17 @@
         <v>1</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>572</v>
-      </c>
-      <c r="G114" s="28"/>
+        <v>567</v>
+      </c>
+      <c r="G114" s="32"/>
       <c r="H114" s="15" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="115" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A115" s="35"/>
-      <c r="B115" s="30"/>
-      <c r="C115" s="29"/>
+      <c r="A115" s="42"/>
+      <c r="B115" s="38"/>
+      <c r="C115" s="28"/>
       <c r="D115" s="5" t="s">
         <v>134</v>
       </c>
@@ -5374,21 +5381,21 @@
         <v>1</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>573</v>
-      </c>
-      <c r="G115" s="28"/>
+        <v>568</v>
+      </c>
+      <c r="G115" s="32"/>
       <c r="H115" s="15" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
     </row>
     <row r="116" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="41">
         <v>34</v>
       </c>
-      <c r="B116" s="30" t="s">
+      <c r="B116" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="C116" s="29" t="s">
+      <c r="C116" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D116" s="5" t="s">
@@ -5398,19 +5405,19 @@
         <v>0</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="G116" s="28" t="s">
-        <v>223</v>
+        <v>200</v>
+      </c>
+      <c r="G116" s="32" t="s">
+        <v>221</v>
       </c>
       <c r="H116" s="15" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
     </row>
     <row r="117" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="42"/>
-      <c r="B117" s="30"/>
-      <c r="C117" s="29"/>
+      <c r="B117" s="38"/>
+      <c r="C117" s="28"/>
       <c r="D117" s="5" t="s">
         <v>76</v>
       </c>
@@ -5418,21 +5425,21 @@
         <v>0</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>641</v>
-      </c>
-      <c r="G117" s="28"/>
+        <v>634</v>
+      </c>
+      <c r="G117" s="32"/>
       <c r="H117" s="15" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
     </row>
     <row r="118" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="41">
         <v>35</v>
       </c>
-      <c r="B118" s="30" t="s">
+      <c r="B118" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="C118" s="29" t="s">
+      <c r="C118" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D118" s="5" t="s">
@@ -5442,19 +5449,19 @@
         <v>0</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="G118" s="28" t="s">
-        <v>223</v>
+        <v>199</v>
+      </c>
+      <c r="G118" s="32" t="s">
+        <v>221</v>
       </c>
       <c r="H118" s="15" t="s">
-        <v>341</v>
+        <v>664</v>
       </c>
     </row>
     <row r="119" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="42"/>
-      <c r="B119" s="30"/>
-      <c r="C119" s="29"/>
+      <c r="B119" s="38"/>
+      <c r="C119" s="28"/>
       <c r="D119" s="5" t="s">
         <v>78</v>
       </c>
@@ -5462,21 +5469,21 @@
         <v>0</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>642</v>
-      </c>
-      <c r="G119" s="28"/>
+        <v>633</v>
+      </c>
+      <c r="G119" s="32"/>
       <c r="H119" s="15" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
     </row>
     <row r="120" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A120" s="41">
+      <c r="A120" s="33">
         <v>36</v>
       </c>
-      <c r="B120" s="30" t="s">
+      <c r="B120" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="C120" s="29" t="s">
+      <c r="C120" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D120" s="5" t="s">
@@ -5486,19 +5493,19 @@
         <v>0</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>495</v>
-      </c>
-      <c r="G120" s="28" t="s">
-        <v>252</v>
+        <v>490</v>
+      </c>
+      <c r="G120" s="32" t="s">
+        <v>250</v>
       </c>
       <c r="H120" s="15" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
     <row r="121" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A121" s="42"/>
-      <c r="B121" s="30"/>
-      <c r="C121" s="29"/>
+      <c r="A121" s="34"/>
+      <c r="B121" s="38"/>
+      <c r="C121" s="28"/>
       <c r="D121" s="5" t="s">
         <v>120</v>
       </c>
@@ -5506,63 +5513,63 @@
         <v>0</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>496</v>
-      </c>
-      <c r="G121" s="28"/>
+        <v>491</v>
+      </c>
+      <c r="G121" s="32"/>
       <c r="H121" s="15" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
     </row>
     <row r="122" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A122" s="41">
+      <c r="A122" s="33">
         <v>37</v>
       </c>
-      <c r="B122" s="43" t="s">
+      <c r="B122" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="C122" s="29" t="s">
+      <c r="C122" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E122" s="1">
         <v>2</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="G122" s="28"/>
+        <v>182</v>
+      </c>
+      <c r="G122" s="32"/>
       <c r="H122" s="15" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
     </row>
     <row r="123" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A123" s="42"/>
-      <c r="B123" s="44"/>
-      <c r="C123" s="29"/>
+      <c r="A123" s="34"/>
+      <c r="B123" s="47"/>
+      <c r="C123" s="28"/>
       <c r="D123" s="5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E123" s="1">
         <v>1</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="G123" s="28"/>
+        <v>182</v>
+      </c>
+      <c r="G123" s="32"/>
       <c r="H123" s="15" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
     </row>
     <row r="124" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A124" s="41">
+      <c r="A124" s="33">
         <v>38</v>
       </c>
-      <c r="B124" s="43" t="s">
+      <c r="B124" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="C124" s="29" t="s">
+      <c r="C124" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D124" s="5" t="s">
@@ -5572,17 +5579,17 @@
         <v>1</v>
       </c>
       <c r="F124" s="5" t="s">
-        <v>502</v>
-      </c>
-      <c r="G124" s="28"/>
+        <v>497</v>
+      </c>
+      <c r="G124" s="32"/>
       <c r="H124" s="15" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
     </row>
     <row r="125" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A125" s="42"/>
-      <c r="B125" s="44"/>
-      <c r="C125" s="29"/>
+      <c r="A125" s="34"/>
+      <c r="B125" s="47"/>
+      <c r="C125" s="28"/>
       <c r="D125" s="5" t="s">
         <v>54</v>
       </c>
@@ -5590,21 +5597,21 @@
         <v>1</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>503</v>
-      </c>
-      <c r="G125" s="28"/>
+        <v>498</v>
+      </c>
+      <c r="G125" s="32"/>
       <c r="H125" s="15" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
     </row>
     <row r="126" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A126" s="41">
+      <c r="A126" s="33">
         <v>39</v>
       </c>
-      <c r="B126" s="43" t="s">
+      <c r="B126" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="C126" s="29" t="s">
+      <c r="C126" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D126" s="5" t="s">
@@ -5614,19 +5621,19 @@
         <v>0</v>
       </c>
       <c r="F126" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="G126" s="28" t="s">
-        <v>539</v>
+        <v>227</v>
+      </c>
+      <c r="G126" s="32" t="s">
+        <v>534</v>
       </c>
       <c r="H126" s="15" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
     </row>
     <row r="127" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A127" s="42"/>
-      <c r="B127" s="44"/>
-      <c r="C127" s="29"/>
+      <c r="A127" s="34"/>
+      <c r="B127" s="47"/>
+      <c r="C127" s="28"/>
       <c r="D127" s="5" t="s">
         <v>132</v>
       </c>
@@ -5634,21 +5641,21 @@
         <v>0</v>
       </c>
       <c r="F127" s="5" t="s">
-        <v>584</v>
-      </c>
-      <c r="G127" s="28"/>
+        <v>579</v>
+      </c>
+      <c r="G127" s="32"/>
       <c r="H127" s="15" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
     </row>
     <row r="128" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A128" s="41">
+      <c r="A128" s="33">
         <v>40</v>
       </c>
-      <c r="B128" s="43" t="s">
+      <c r="B128" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="C128" s="29" t="s">
+      <c r="C128" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D128" s="5" t="s">
@@ -5658,17 +5665,17 @@
         <v>1</v>
       </c>
       <c r="F128" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="G128" s="28"/>
+        <v>249</v>
+      </c>
+      <c r="G128" s="32"/>
       <c r="H128" s="15" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
     </row>
     <row r="129" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A129" s="42"/>
-      <c r="B129" s="44"/>
-      <c r="C129" s="29"/>
+      <c r="A129" s="34"/>
+      <c r="B129" s="47"/>
+      <c r="C129" s="28"/>
       <c r="D129" s="5" t="s">
         <v>80</v>
       </c>
@@ -5676,21 +5683,21 @@
         <v>1</v>
       </c>
       <c r="F129" s="5" t="s">
-        <v>511</v>
-      </c>
-      <c r="G129" s="28"/>
+        <v>506</v>
+      </c>
+      <c r="G129" s="32"/>
       <c r="H129" s="15" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
     </row>
     <row r="130" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A130" s="41">
+      <c r="A130" s="33">
         <v>41</v>
       </c>
-      <c r="B130" s="43" t="s">
+      <c r="B130" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="C130" s="32" t="s">
+      <c r="C130" s="43" t="s">
         <v>14</v>
       </c>
       <c r="D130" s="5" t="s">
@@ -5702,15 +5709,15 @@
       <c r="F130" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="G130" s="28"/>
+      <c r="G130" s="32"/>
       <c r="H130" s="15" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="131" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A131" s="42"/>
-      <c r="B131" s="44"/>
-      <c r="C131" s="32"/>
+      <c r="A131" s="34"/>
+      <c r="B131" s="47"/>
+      <c r="C131" s="43"/>
       <c r="D131" s="5" t="s">
         <v>65</v>
       </c>
@@ -5718,21 +5725,21 @@
         <v>1</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="G131" s="28"/>
+        <v>193</v>
+      </c>
+      <c r="G131" s="32"/>
       <c r="H131" s="15" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="132" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A132" s="41">
+      <c r="A132" s="33">
         <v>42</v>
       </c>
-      <c r="B132" s="33" t="s">
+      <c r="B132" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C132" s="29" t="s">
+      <c r="C132" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D132" s="5" t="s">
@@ -5742,17 +5749,17 @@
         <v>0</v>
       </c>
       <c r="F132" s="5" t="s">
-        <v>588</v>
-      </c>
-      <c r="G132" s="28"/>
+        <v>583</v>
+      </c>
+      <c r="G132" s="32"/>
       <c r="H132" s="15" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
     </row>
     <row r="133" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A133" s="42"/>
-      <c r="B133" s="33"/>
-      <c r="C133" s="29"/>
+      <c r="A133" s="34"/>
+      <c r="B133" s="36"/>
+      <c r="C133" s="28"/>
       <c r="D133" s="5" t="s">
         <v>51</v>
       </c>
@@ -5760,61 +5767,63 @@
         <v>0</v>
       </c>
       <c r="F133" s="5" t="s">
-        <v>585</v>
-      </c>
-      <c r="G133" s="28"/>
+        <v>580</v>
+      </c>
+      <c r="G133" s="32"/>
       <c r="H133" s="15" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
     </row>
     <row r="134" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A134" s="41">
+      <c r="A134" s="33">
         <v>43</v>
       </c>
-      <c r="B134" s="33" t="s">
+      <c r="B134" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C134" s="29" t="s">
+      <c r="C134" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>137</v>
+        <v>654</v>
       </c>
       <c r="E134" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>599</v>
-      </c>
+        <v>656</v>
+      </c>
+      <c r="G134" s="32"/>
       <c r="H134" s="15" t="s">
-        <v>344</v>
+        <v>657</v>
       </c>
     </row>
     <row r="135" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A135" s="42"/>
-      <c r="B135" s="33"/>
-      <c r="C135" s="29"/>
+      <c r="A135" s="34"/>
+      <c r="B135" s="36"/>
+      <c r="C135" s="28"/>
       <c r="D135" s="5" t="s">
-        <v>138</v>
+        <v>655</v>
       </c>
       <c r="E135" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>599</v>
-      </c>
+        <v>659</v>
+      </c>
+      <c r="G135" s="32"/>
       <c r="H135" s="15" t="s">
-        <v>409</v>
+        <v>658</v>
       </c>
     </row>
     <row r="136" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A136" s="41">
+      <c r="A136" s="33">
         <v>44</v>
       </c>
-      <c r="B136" s="33" t="s">
+      <c r="B136" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C136" s="29" t="s">
+      <c r="C136" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D136" s="5" t="s">
@@ -5824,17 +5833,17 @@
         <v>1</v>
       </c>
       <c r="F136" s="5" t="s">
-        <v>497</v>
-      </c>
-      <c r="G136" s="28"/>
+        <v>492</v>
+      </c>
+      <c r="G136" s="32"/>
       <c r="H136" s="15" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="137" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A137" s="42"/>
-      <c r="B137" s="33"/>
-      <c r="C137" s="29"/>
+      <c r="A137" s="34"/>
+      <c r="B137" s="36"/>
+      <c r="C137" s="28"/>
       <c r="D137" s="5" t="s">
         <v>49</v>
       </c>
@@ -5842,171 +5851,171 @@
         <v>1</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>498</v>
-      </c>
-      <c r="G137" s="28"/>
+        <v>493</v>
+      </c>
+      <c r="G137" s="32"/>
       <c r="H137" s="15" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
     </row>
     <row r="138" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A138" s="41">
+      <c r="A138" s="33">
         <v>45</v>
       </c>
-      <c r="B138" s="33" t="s">
+      <c r="B138" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C138" s="45" t="s">
+      <c r="C138" s="37" t="s">
         <v>14</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E138" s="1">
         <v>1</v>
       </c>
       <c r="F138" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="G138" s="28"/>
+        <v>215</v>
+      </c>
+      <c r="G138" s="32"/>
       <c r="H138" s="15" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
     </row>
     <row r="139" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A139" s="42"/>
-      <c r="B139" s="33"/>
-      <c r="C139" s="45"/>
+      <c r="A139" s="34"/>
+      <c r="B139" s="36"/>
+      <c r="C139" s="37"/>
       <c r="D139" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E139" s="1">
         <v>1</v>
       </c>
       <c r="F139" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="G139" s="28"/>
+        <v>214</v>
+      </c>
+      <c r="G139" s="32"/>
       <c r="H139" s="15" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
     </row>
     <row r="140" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A140" s="41">
+      <c r="A140" s="33">
         <v>46</v>
       </c>
-      <c r="B140" s="33" t="s">
+      <c r="B140" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C140" s="29" t="s">
+      <c r="C140" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E140" s="1">
         <v>0</v>
       </c>
       <c r="F140" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="G140" s="28" t="s">
-        <v>215</v>
+        <v>137</v>
+      </c>
+      <c r="G140" s="32" t="s">
+        <v>213</v>
       </c>
       <c r="H140" s="15" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
     </row>
     <row r="141" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A141" s="42"/>
-      <c r="B141" s="33"/>
-      <c r="C141" s="29"/>
+      <c r="A141" s="34"/>
+      <c r="B141" s="36"/>
+      <c r="C141" s="28"/>
       <c r="D141" s="5" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E141" s="1">
         <v>0</v>
       </c>
       <c r="F141" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="G141" s="28"/>
+        <v>138</v>
+      </c>
+      <c r="G141" s="32"/>
       <c r="H141" s="15" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
     </row>
     <row r="142" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A142" s="41">
+      <c r="A142" s="33">
         <v>47</v>
       </c>
-      <c r="B142" s="33" t="s">
+      <c r="B142" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C142" s="29" t="s">
+      <c r="C142" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E142" s="1">
         <v>1</v>
       </c>
       <c r="F142" s="5" t="s">
-        <v>499</v>
-      </c>
-      <c r="G142" s="28" t="s">
-        <v>569</v>
+        <v>494</v>
+      </c>
+      <c r="G142" s="32" t="s">
+        <v>564</v>
       </c>
       <c r="H142" s="15" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="143" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A143" s="42"/>
-      <c r="B143" s="33"/>
-      <c r="C143" s="29"/>
+      <c r="A143" s="34"/>
+      <c r="B143" s="36"/>
+      <c r="C143" s="28"/>
       <c r="D143" s="5" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E143" s="1">
         <v>1</v>
       </c>
       <c r="F143" s="5" t="s">
-        <v>500</v>
-      </c>
-      <c r="G143" s="28"/>
+        <v>495</v>
+      </c>
+      <c r="G143" s="32"/>
       <c r="H143" s="15" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
     </row>
     <row r="144" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A144" s="41">
+      <c r="A144" s="33">
         <v>48</v>
       </c>
-      <c r="B144" s="33" t="s">
+      <c r="B144" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C144" s="29" t="s">
+      <c r="C144" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D144" s="5" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="E144" s="1">
         <v>1</v>
       </c>
       <c r="F144" s="5" t="s">
-        <v>501</v>
-      </c>
-      <c r="G144" s="28"/>
+        <v>496</v>
+      </c>
+      <c r="G144" s="32"/>
       <c r="H144" s="15" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
     <row r="145" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A145" s="42"/>
-      <c r="B145" s="33"/>
-      <c r="C145" s="29"/>
+      <c r="A145" s="34"/>
+      <c r="B145" s="36"/>
+      <c r="C145" s="28"/>
       <c r="D145" s="5" t="s">
         <v>55</v>
       </c>
@@ -6014,21 +6023,21 @@
         <v>0</v>
       </c>
       <c r="F145" s="5" t="s">
-        <v>501</v>
-      </c>
-      <c r="G145" s="28"/>
+        <v>496</v>
+      </c>
+      <c r="G145" s="32"/>
       <c r="H145" s="15" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
     </row>
     <row r="146" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A146" s="41">
+      <c r="A146" s="33">
         <v>49</v>
       </c>
-      <c r="B146" s="33" t="s">
+      <c r="B146" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C146" s="45" t="s">
+      <c r="C146" s="37" t="s">
         <v>14</v>
       </c>
       <c r="D146" s="5" t="s">
@@ -6038,19 +6047,19 @@
         <v>1</v>
       </c>
       <c r="F146" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="G146" s="28" t="s">
-        <v>569</v>
+        <v>202</v>
+      </c>
+      <c r="G146" s="32" t="s">
+        <v>564</v>
       </c>
       <c r="H146" s="15" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
     </row>
     <row r="147" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A147" s="42"/>
-      <c r="B147" s="33"/>
-      <c r="C147" s="45"/>
+      <c r="A147" s="34"/>
+      <c r="B147" s="36"/>
+      <c r="C147" s="37"/>
       <c r="D147" s="5" t="s">
         <v>57</v>
       </c>
@@ -6058,21 +6067,21 @@
         <v>0</v>
       </c>
       <c r="F147" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="G147" s="28"/>
+        <v>202</v>
+      </c>
+      <c r="G147" s="32"/>
       <c r="H147" s="15" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
     </row>
     <row r="148" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A148" s="34">
+      <c r="A148" s="41">
         <v>50</v>
       </c>
-      <c r="B148" s="33" t="s">
+      <c r="B148" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C148" s="32" t="s">
+      <c r="C148" s="43" t="s">
         <v>14</v>
       </c>
       <c r="D148" s="5" t="s">
@@ -6082,17 +6091,17 @@
         <v>1</v>
       </c>
       <c r="F148" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="G148" s="28"/>
+        <v>287</v>
+      </c>
+      <c r="G148" s="32"/>
       <c r="H148" s="15" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
     </row>
     <row r="149" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A149" s="35"/>
-      <c r="B149" s="33"/>
-      <c r="C149" s="32"/>
+      <c r="A149" s="42"/>
+      <c r="B149" s="36"/>
+      <c r="C149" s="43"/>
       <c r="D149" s="5" t="s">
         <v>59</v>
       </c>
@@ -6100,63 +6109,63 @@
         <v>0</v>
       </c>
       <c r="F149" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="G149" s="28"/>
+        <v>287</v>
+      </c>
+      <c r="G149" s="32"/>
       <c r="H149" s="15" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
     </row>
     <row r="150" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A150" s="34">
+      <c r="A150" s="41">
         <v>51</v>
       </c>
-      <c r="B150" s="33" t="s">
+      <c r="B150" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C150" s="29" t="s">
+      <c r="C150" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D150" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="E150" s="1">
+        <v>1</v>
+      </c>
+      <c r="F150" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="E150" s="1">
-        <v>1</v>
-      </c>
-      <c r="F150" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="G150" s="28"/>
+      <c r="G150" s="32"/>
       <c r="H150" s="15" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
     </row>
     <row r="151" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A151" s="35"/>
-      <c r="B151" s="33"/>
-      <c r="C151" s="29"/>
+      <c r="A151" s="42"/>
+      <c r="B151" s="36"/>
+      <c r="C151" s="28"/>
       <c r="D151" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E151" s="1">
         <v>0</v>
       </c>
       <c r="F151" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="G151" s="28"/>
+        <v>185</v>
+      </c>
+      <c r="G151" s="32"/>
       <c r="H151" s="15" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
     </row>
     <row r="152" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A152" s="41">
+      <c r="A152" s="33">
         <v>52</v>
       </c>
-      <c r="B152" s="33" t="s">
+      <c r="B152" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C152" s="29" t="s">
+      <c r="C152" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D152" s="5" t="s">
@@ -6168,37 +6177,37 @@
       <c r="F152" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="G152" s="28"/>
+      <c r="G152" s="32"/>
       <c r="H152" s="15" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
     </row>
     <row r="153" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A153" s="42"/>
-      <c r="B153" s="33"/>
-      <c r="C153" s="29"/>
+      <c r="A153" s="34"/>
+      <c r="B153" s="36"/>
+      <c r="C153" s="28"/>
       <c r="D153" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E153" s="1">
         <v>0</v>
       </c>
       <c r="F153" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="G153" s="28"/>
+        <v>254</v>
+      </c>
+      <c r="G153" s="32"/>
       <c r="H153" s="15" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
     </row>
     <row r="154" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A154" s="41">
+      <c r="A154" s="33">
         <v>53</v>
       </c>
-      <c r="B154" s="33" t="s">
+      <c r="B154" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C154" s="29" t="s">
+      <c r="C154" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D154" s="5" t="s">
@@ -6208,19 +6217,19 @@
         <v>0</v>
       </c>
       <c r="F154" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="G154" s="28" t="s">
-        <v>643</v>
+        <v>263</v>
+      </c>
+      <c r="G154" s="32" t="s">
+        <v>635</v>
       </c>
       <c r="H154" s="15" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
     </row>
     <row r="155" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A155" s="42"/>
-      <c r="B155" s="33"/>
-      <c r="C155" s="29"/>
+      <c r="A155" s="34"/>
+      <c r="B155" s="36"/>
+      <c r="C155" s="28"/>
       <c r="D155" s="5" t="s">
         <v>63</v>
       </c>
@@ -6228,279 +6237,279 @@
         <v>0</v>
       </c>
       <c r="F155" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="G155" s="28"/>
+        <v>264</v>
+      </c>
+      <c r="G155" s="32"/>
       <c r="H155" s="15" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
     </row>
     <row r="156" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A156" s="41">
+      <c r="A156" s="33">
         <v>54</v>
       </c>
-      <c r="B156" s="33" t="s">
+      <c r="B156" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C156" s="29" t="s">
+      <c r="C156" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D156" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="E156" s="1">
+        <v>1</v>
+      </c>
+      <c r="F156" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="G156" s="32"/>
+      <c r="H156" s="15" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A157" s="34"/>
+      <c r="B157" s="36"/>
+      <c r="C157" s="28"/>
+      <c r="D157" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="E157" s="1">
+        <v>1</v>
+      </c>
+      <c r="F157" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="G157" s="32"/>
+      <c r="H157" s="15" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A158" s="33">
+        <v>55</v>
+      </c>
+      <c r="B158" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="C158" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="D158" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="E156" s="1">
-        <v>1</v>
-      </c>
-      <c r="F156" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="G156" s="28"/>
-      <c r="H156" s="15" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="157" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A157" s="42"/>
-      <c r="B157" s="33"/>
-      <c r="C157" s="29"/>
-      <c r="D157" s="5" t="s">
+      <c r="E158" s="1">
+        <v>1</v>
+      </c>
+      <c r="F158" s="5" t="s">
+        <v>586</v>
+      </c>
+      <c r="G158" s="32"/>
+      <c r="H158" s="15" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A159" s="34"/>
+      <c r="B159" s="36"/>
+      <c r="C159" s="28"/>
+      <c r="D159" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="E157" s="1">
-        <v>1</v>
-      </c>
-      <c r="F157" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="G157" s="28"/>
-      <c r="H157" s="15" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="158" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A158" s="41">
-        <v>55</v>
-      </c>
-      <c r="B158" s="33" t="s">
+      <c r="E159" s="1">
+        <v>1</v>
+      </c>
+      <c r="F159" s="5" t="s">
+        <v>587</v>
+      </c>
+      <c r="G159" s="32"/>
+      <c r="H159" s="15" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A160" s="33">
+        <v>56</v>
+      </c>
+      <c r="B160" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C158" s="29" t="s">
+      <c r="C160" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="D158" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="E158" s="1">
-        <v>1</v>
-      </c>
-      <c r="F158" s="5" t="s">
-        <v>591</v>
-      </c>
-      <c r="G158" s="28"/>
-      <c r="H158" s="15" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="159" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A159" s="42"/>
-      <c r="B159" s="33"/>
-      <c r="C159" s="29"/>
-      <c r="D159" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="E159" s="1">
-        <v>1</v>
-      </c>
-      <c r="F159" s="5" t="s">
-        <v>592</v>
-      </c>
-      <c r="G159" s="28"/>
-      <c r="H159" s="15" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="160" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A160" s="41">
-        <v>56</v>
-      </c>
-      <c r="B160" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="C160" s="29" t="s">
-        <v>14</v>
-      </c>
       <c r="D160" s="5" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E160" s="1">
         <v>1</v>
       </c>
       <c r="F160" s="5" t="s">
-        <v>590</v>
-      </c>
-      <c r="G160" s="28" t="s">
-        <v>542</v>
+        <v>585</v>
+      </c>
+      <c r="G160" s="32" t="s">
+        <v>537</v>
       </c>
       <c r="H160" s="15" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
     </row>
     <row r="161" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A161" s="42"/>
-      <c r="B161" s="33"/>
-      <c r="C161" s="29"/>
+      <c r="A161" s="34"/>
+      <c r="B161" s="36"/>
+      <c r="C161" s="28"/>
       <c r="D161" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E161" s="1">
         <v>0</v>
       </c>
       <c r="F161" s="5" t="s">
-        <v>590</v>
-      </c>
-      <c r="G161" s="28"/>
+        <v>585</v>
+      </c>
+      <c r="G161" s="32"/>
       <c r="H161" s="15" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
     </row>
     <row r="162" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A162" s="41">
+      <c r="A162" s="33">
         <v>57</v>
       </c>
-      <c r="B162" s="33" t="s">
+      <c r="B162" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C162" s="29" t="s">
+      <c r="C162" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D162" s="5" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E162" s="1">
         <v>0</v>
       </c>
       <c r="F162" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="G162" s="28" t="s">
-        <v>574</v>
+        <v>290</v>
+      </c>
+      <c r="G162" s="32" t="s">
+        <v>569</v>
       </c>
       <c r="H162" s="15" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
     </row>
     <row r="163" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A163" s="42"/>
-      <c r="B163" s="33"/>
-      <c r="C163" s="29"/>
+      <c r="A163" s="34"/>
+      <c r="B163" s="36"/>
+      <c r="C163" s="28"/>
       <c r="D163" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E163" s="1">
         <v>0</v>
       </c>
       <c r="F163" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="G163" s="28"/>
+        <v>291</v>
+      </c>
+      <c r="G163" s="32"/>
       <c r="H163" s="15" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
     </row>
     <row r="164" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A164" s="41">
+      <c r="A164" s="33">
         <v>58</v>
       </c>
-      <c r="B164" s="33" t="s">
+      <c r="B164" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C164" s="45" t="s">
+      <c r="C164" s="37" t="s">
         <v>14</v>
       </c>
       <c r="D164" s="5" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E164" s="1">
         <v>0</v>
       </c>
       <c r="F164" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="G164" s="28"/>
+        <v>292</v>
+      </c>
+      <c r="G164" s="32"/>
       <c r="H164" s="15" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="165" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A165" s="42"/>
-      <c r="B165" s="33"/>
-      <c r="C165" s="45"/>
+      <c r="A165" s="34"/>
+      <c r="B165" s="36"/>
+      <c r="C165" s="37"/>
       <c r="D165" s="5" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E165" s="1">
         <v>0</v>
       </c>
       <c r="F165" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="G165" s="28"/>
+        <v>293</v>
+      </c>
+      <c r="G165" s="32"/>
       <c r="H165" s="15" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
     </row>
     <row r="166" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A166" s="41">
+      <c r="A166" s="33">
         <v>59</v>
       </c>
-      <c r="B166" s="33" t="s">
+      <c r="B166" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C166" s="45" t="s">
+      <c r="C166" s="37" t="s">
         <v>14</v>
       </c>
       <c r="D166" s="5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E166" s="1">
         <v>1</v>
       </c>
       <c r="F166" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="G166" s="28" t="s">
-        <v>197</v>
+        <v>261</v>
+      </c>
+      <c r="G166" s="32" t="s">
+        <v>195</v>
       </c>
       <c r="H166" s="15" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
     </row>
     <row r="167" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A167" s="42"/>
-      <c r="B167" s="33"/>
-      <c r="C167" s="45"/>
+      <c r="A167" s="34"/>
+      <c r="B167" s="36"/>
+      <c r="C167" s="37"/>
       <c r="D167" s="5" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E167" s="1">
         <v>0</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="G167" s="28"/>
+        <v>261</v>
+      </c>
+      <c r="G167" s="32"/>
       <c r="H167" s="15" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
     </row>
     <row r="168" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A168" s="41">
+      <c r="A168" s="33">
         <v>60</v>
       </c>
-      <c r="B168" s="33" t="s">
+      <c r="B168" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C168" s="45" t="s">
+      <c r="C168" s="37" t="s">
         <v>14</v>
       </c>
       <c r="D168" s="5" t="s">
@@ -6510,17 +6519,17 @@
         <v>1</v>
       </c>
       <c r="F168" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="G168" s="28"/>
+        <v>258</v>
+      </c>
+      <c r="G168" s="32"/>
       <c r="H168" s="15" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="169" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A169" s="42"/>
-      <c r="B169" s="33"/>
-      <c r="C169" s="45"/>
+      <c r="A169" s="34"/>
+      <c r="B169" s="36"/>
+      <c r="C169" s="37"/>
       <c r="D169" s="5" t="s">
         <v>117</v>
       </c>
@@ -6528,21 +6537,21 @@
         <v>1</v>
       </c>
       <c r="F169" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="G169" s="28"/>
+        <v>259</v>
+      </c>
+      <c r="G169" s="32"/>
       <c r="H169" s="15" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
     </row>
     <row r="170" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A170" s="41">
+      <c r="A170" s="33">
         <v>61</v>
       </c>
-      <c r="B170" s="33" t="s">
+      <c r="B170" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C170" s="29" t="s">
+      <c r="C170" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D170" s="5" t="s">
@@ -6552,17 +6561,17 @@
         <v>2</v>
       </c>
       <c r="F170" s="5" t="s">
-        <v>657</v>
-      </c>
-      <c r="G170" s="28"/>
+        <v>645</v>
+      </c>
+      <c r="G170" s="32"/>
       <c r="H170" s="15" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="171" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A171" s="42"/>
-      <c r="B171" s="33"/>
-      <c r="C171" s="29"/>
+      <c r="A171" s="34"/>
+      <c r="B171" s="36"/>
+      <c r="C171" s="28"/>
       <c r="D171" s="5" t="s">
         <v>82</v>
       </c>
@@ -6570,107 +6579,107 @@
         <v>2</v>
       </c>
       <c r="F171" s="5" t="s">
-        <v>658</v>
-      </c>
-      <c r="G171" s="28"/>
+        <v>646</v>
+      </c>
+      <c r="G171" s="32"/>
       <c r="H171" s="15" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
     </row>
     <row r="172" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A172" s="41">
+      <c r="A172" s="33">
         <v>62</v>
       </c>
-      <c r="B172" s="33" t="s">
+      <c r="B172" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C172" s="32" t="s">
+      <c r="C172" s="43" t="s">
         <v>14</v>
       </c>
       <c r="D172" s="5" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="E172" s="1">
         <v>1</v>
       </c>
       <c r="F172" s="5" t="s">
-        <v>561</v>
-      </c>
-      <c r="G172" s="28"/>
+        <v>556</v>
+      </c>
+      <c r="G172" s="32"/>
       <c r="H172" s="15" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
     </row>
     <row r="173" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A173" s="42"/>
-      <c r="B173" s="33"/>
-      <c r="C173" s="32"/>
+      <c r="A173" s="34"/>
+      <c r="B173" s="36"/>
+      <c r="C173" s="43"/>
       <c r="D173" s="5" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="E173" s="1">
         <v>1</v>
       </c>
       <c r="F173" s="5" t="s">
-        <v>562</v>
-      </c>
-      <c r="G173" s="28"/>
+        <v>557</v>
+      </c>
+      <c r="G173" s="32"/>
       <c r="H173" s="15" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
     </row>
     <row r="174" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A174" s="41">
+      <c r="A174" s="33">
         <v>63</v>
       </c>
-      <c r="B174" s="33" t="s">
+      <c r="B174" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C174" s="45" t="s">
+      <c r="C174" s="37" t="s">
         <v>14</v>
       </c>
       <c r="D174" s="5" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E174" s="1">
         <v>1</v>
       </c>
       <c r="F174" s="5" t="s">
-        <v>616</v>
-      </c>
-      <c r="G174" s="28" t="s">
-        <v>615</v>
+        <v>608</v>
+      </c>
+      <c r="G174" s="32" t="s">
+        <v>607</v>
       </c>
       <c r="H174" s="15" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
     </row>
     <row r="175" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A175" s="42"/>
-      <c r="B175" s="33"/>
-      <c r="C175" s="45"/>
+      <c r="A175" s="34"/>
+      <c r="B175" s="36"/>
+      <c r="C175" s="37"/>
       <c r="D175" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E175" s="1">
         <v>1</v>
       </c>
       <c r="F175" s="5" t="s">
-        <v>617</v>
-      </c>
-      <c r="G175" s="28"/>
+        <v>609</v>
+      </c>
+      <c r="G175" s="32"/>
       <c r="H175" s="15" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
     </row>
     <row r="176" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A176" s="41">
+      <c r="A176" s="33">
         <v>64</v>
       </c>
-      <c r="B176" s="33" t="s">
+      <c r="B176" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C176" s="29" t="s">
+      <c r="C176" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D176" s="5" t="s">
@@ -6680,19 +6689,19 @@
         <v>1</v>
       </c>
       <c r="F176" s="5" t="s">
-        <v>512</v>
-      </c>
-      <c r="G176" s="28" t="s">
+        <v>507</v>
+      </c>
+      <c r="G176" s="32" t="s">
         <v>113</v>
       </c>
       <c r="H176" s="15" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
     </row>
     <row r="177" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A177" s="42"/>
-      <c r="B177" s="33"/>
-      <c r="C177" s="29"/>
+      <c r="A177" s="34"/>
+      <c r="B177" s="36"/>
+      <c r="C177" s="28"/>
       <c r="D177" s="5" t="s">
         <v>112</v>
       </c>
@@ -6700,63 +6709,63 @@
         <v>1</v>
       </c>
       <c r="F177" s="5" t="s">
-        <v>513</v>
-      </c>
-      <c r="G177" s="28"/>
+        <v>508</v>
+      </c>
+      <c r="G177" s="32"/>
       <c r="H177" s="15" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
     </row>
     <row r="178" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A178" s="41">
+      <c r="A178" s="33">
         <v>65</v>
       </c>
-      <c r="B178" s="31" t="s">
+      <c r="B178" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C178" s="29" t="s">
+      <c r="C178" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D178" s="5" t="s">
+        <v>642</v>
+      </c>
+      <c r="E178" s="1">
+        <v>1</v>
+      </c>
+      <c r="F178" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="G178" s="32"/>
+      <c r="H178" s="15" t="s">
         <v>652</v>
       </c>
-      <c r="E178" s="1">
-        <v>1</v>
-      </c>
-      <c r="F178" s="5" t="s">
-        <v>651</v>
-      </c>
-      <c r="G178" s="28"/>
-      <c r="H178" s="15" t="s">
+    </row>
+    <row r="179" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A179" s="34"/>
+      <c r="B179" s="35"/>
+      <c r="C179" s="28"/>
+      <c r="D179" s="5" t="s">
+        <v>643</v>
+      </c>
+      <c r="E179" s="1">
+        <v>1</v>
+      </c>
+      <c r="F179" s="5" t="s">
+        <v>644</v>
+      </c>
+      <c r="G179" s="32"/>
+      <c r="H179" s="15" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="179" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A179" s="42"/>
-      <c r="B179" s="31"/>
-      <c r="C179" s="29"/>
-      <c r="D179" s="5" t="s">
-        <v>655</v>
-      </c>
-      <c r="E179" s="1">
-        <v>1</v>
-      </c>
-      <c r="F179" s="5" t="s">
-        <v>656</v>
-      </c>
-      <c r="G179" s="28"/>
-      <c r="H179" s="15" t="s">
-        <v>654</v>
-      </c>
-    </row>
     <row r="180" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A180" s="41">
+      <c r="A180" s="33">
         <v>66</v>
       </c>
-      <c r="B180" s="31" t="s">
+      <c r="B180" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C180" s="29" t="s">
+      <c r="C180" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D180" s="5" t="s">
@@ -6766,17 +6775,17 @@
         <v>1</v>
       </c>
       <c r="F180" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="G180" s="28"/>
+        <v>260</v>
+      </c>
+      <c r="G180" s="32"/>
       <c r="H180" s="15" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
     </row>
     <row r="181" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A181" s="42"/>
-      <c r="B181" s="31"/>
-      <c r="C181" s="29"/>
+      <c r="A181" s="34"/>
+      <c r="B181" s="35"/>
+      <c r="C181" s="28"/>
       <c r="D181" s="5" t="s">
         <v>61</v>
       </c>
@@ -6784,21 +6793,21 @@
         <v>1</v>
       </c>
       <c r="F181" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="G181" s="28"/>
+        <v>262</v>
+      </c>
+      <c r="G181" s="32"/>
       <c r="H181" s="15" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
     </row>
     <row r="182" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A182" s="41">
+      <c r="A182" s="33">
         <v>67</v>
       </c>
-      <c r="B182" s="31" t="s">
+      <c r="B182" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C182" s="29" t="s">
+      <c r="C182" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D182" s="5" t="s">
@@ -6808,17 +6817,17 @@
         <v>3</v>
       </c>
       <c r="F182" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="G182" s="28"/>
+        <v>203</v>
+      </c>
+      <c r="G182" s="32"/>
       <c r="H182" s="15" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
     </row>
     <row r="183" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A183" s="42"/>
-      <c r="B183" s="31"/>
-      <c r="C183" s="29"/>
+      <c r="A183" s="34"/>
+      <c r="B183" s="35"/>
+      <c r="C183" s="28"/>
       <c r="D183" s="5" t="s">
         <v>70</v>
       </c>
@@ -6826,63 +6835,63 @@
         <v>3</v>
       </c>
       <c r="F183" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="G183" s="28"/>
+        <v>204</v>
+      </c>
+      <c r="G183" s="32"/>
       <c r="H183" s="15" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
     </row>
     <row r="184" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A184" s="41">
+      <c r="A184" s="33">
         <v>68</v>
       </c>
-      <c r="B184" s="31" t="s">
+      <c r="B184" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C184" s="29" t="s">
+      <c r="C184" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D184" s="5" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E184" s="1">
         <v>3</v>
       </c>
       <c r="F184" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="G184" s="28"/>
+        <v>230</v>
+      </c>
+      <c r="G184" s="32"/>
       <c r="H184" s="15" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
     </row>
     <row r="185" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A185" s="42"/>
-      <c r="B185" s="31"/>
-      <c r="C185" s="29"/>
+      <c r="A185" s="34"/>
+      <c r="B185" s="35"/>
+      <c r="C185" s="28"/>
       <c r="D185" s="5" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E185" s="1">
         <v>2</v>
       </c>
       <c r="F185" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="G185" s="28"/>
+        <v>230</v>
+      </c>
+      <c r="G185" s="32"/>
       <c r="H185" s="15" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
     </row>
     <row r="186" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A186" s="41">
+      <c r="A186" s="33">
         <v>69</v>
       </c>
-      <c r="B186" s="31" t="s">
+      <c r="B186" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C186" s="29" t="s">
+      <c r="C186" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D186" s="5" t="s">
@@ -6892,17 +6901,17 @@
         <v>3</v>
       </c>
       <c r="F186" s="5" t="s">
-        <v>589</v>
-      </c>
-      <c r="G186" s="28"/>
+        <v>584</v>
+      </c>
+      <c r="G186" s="32"/>
       <c r="H186" s="15" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
     </row>
     <row r="187" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A187" s="42"/>
-      <c r="B187" s="31"/>
-      <c r="C187" s="29"/>
+      <c r="A187" s="34"/>
+      <c r="B187" s="35"/>
+      <c r="C187" s="28"/>
       <c r="D187" s="5" t="s">
         <v>72</v>
       </c>
@@ -6910,63 +6919,63 @@
         <v>2</v>
       </c>
       <c r="F187" s="5" t="s">
-        <v>589</v>
-      </c>
-      <c r="G187" s="28"/>
+        <v>584</v>
+      </c>
+      <c r="G187" s="32"/>
       <c r="H187" s="15" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
     </row>
     <row r="188" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A188" s="41">
+      <c r="A188" s="33">
         <v>70</v>
       </c>
-      <c r="B188" s="31" t="s">
+      <c r="B188" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C188" s="45" t="s">
+      <c r="C188" s="37" t="s">
         <v>14</v>
       </c>
       <c r="D188" s="5" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="E188" s="1">
         <v>0</v>
       </c>
       <c r="F188" s="5" t="s">
-        <v>458</v>
-      </c>
-      <c r="G188" s="28"/>
+        <v>453</v>
+      </c>
+      <c r="G188" s="32"/>
       <c r="H188" s="15" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
     </row>
     <row r="189" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A189" s="42"/>
-      <c r="B189" s="31"/>
-      <c r="C189" s="45"/>
+      <c r="A189" s="34"/>
+      <c r="B189" s="35"/>
+      <c r="C189" s="37"/>
       <c r="D189" s="5" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="E189" s="1">
         <v>0</v>
       </c>
       <c r="F189" s="5" t="s">
-        <v>459</v>
-      </c>
-      <c r="G189" s="28"/>
+        <v>454</v>
+      </c>
+      <c r="G189" s="32"/>
       <c r="H189" s="15" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
     </row>
     <row r="190" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A190" s="41">
+      <c r="A190" s="33">
         <v>71</v>
       </c>
-      <c r="B190" s="31" t="s">
+      <c r="B190" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C190" s="45" t="s">
+      <c r="C190" s="37" t="s">
         <v>14</v>
       </c>
       <c r="D190" s="5" t="s">
@@ -6976,19 +6985,19 @@
         <v>0</v>
       </c>
       <c r="F190" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="G190" s="28" t="s">
-        <v>569</v>
+        <v>268</v>
+      </c>
+      <c r="G190" s="32" t="s">
+        <v>564</v>
       </c>
       <c r="H190" s="15" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
     </row>
     <row r="191" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A191" s="42"/>
-      <c r="B191" s="31"/>
-      <c r="C191" s="45"/>
+      <c r="A191" s="34"/>
+      <c r="B191" s="35"/>
+      <c r="C191" s="37"/>
       <c r="D191" s="5" t="s">
         <v>86</v>
       </c>
@@ -6996,63 +7005,63 @@
         <v>0</v>
       </c>
       <c r="F191" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="G191" s="28"/>
+        <v>269</v>
+      </c>
+      <c r="G191" s="32"/>
       <c r="H191" s="15" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
     </row>
     <row r="192" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A192" s="41">
+      <c r="A192" s="33">
         <v>72</v>
       </c>
-      <c r="B192" s="31" t="s">
+      <c r="B192" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C192" s="45" t="s">
+      <c r="C192" s="37" t="s">
         <v>14</v>
       </c>
       <c r="D192" s="5" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E192" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F192" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="G192" s="28"/>
+        <v>224</v>
+      </c>
+      <c r="G192" s="32"/>
       <c r="H192" s="15" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="193" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A193" s="42"/>
-      <c r="B193" s="31"/>
-      <c r="C193" s="45"/>
+      <c r="A193" s="34"/>
+      <c r="B193" s="35"/>
+      <c r="C193" s="37"/>
       <c r="D193" s="5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E193" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F193" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="G193" s="28"/>
+        <v>225</v>
+      </c>
+      <c r="G193" s="32"/>
       <c r="H193" s="15" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
     </row>
     <row r="194" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A194" s="41">
+      <c r="A194" s="33">
         <v>73</v>
       </c>
-      <c r="B194" s="31" t="s">
+      <c r="B194" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C194" s="29" t="s">
+      <c r="C194" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D194" s="5" t="s">
@@ -7062,19 +7071,19 @@
         <v>4</v>
       </c>
       <c r="F194" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="G194" s="28" t="s">
-        <v>214</v>
+        <v>294</v>
+      </c>
+      <c r="G194" s="32" t="s">
+        <v>212</v>
       </c>
       <c r="H194" s="15" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
     </row>
     <row r="195" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A195" s="42"/>
-      <c r="B195" s="31"/>
-      <c r="C195" s="29"/>
+      <c r="A195" s="34"/>
+      <c r="B195" s="35"/>
+      <c r="C195" s="28"/>
       <c r="D195" s="5" t="s">
         <v>130</v>
       </c>
@@ -7082,21 +7091,21 @@
         <v>4</v>
       </c>
       <c r="F195" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="G195" s="28"/>
+        <v>295</v>
+      </c>
+      <c r="G195" s="32"/>
       <c r="H195" s="15" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
     </row>
     <row r="196" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A196" s="41">
+      <c r="A196" s="33">
         <v>74</v>
       </c>
-      <c r="B196" s="31" t="s">
+      <c r="B196" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C196" s="29" t="s">
+      <c r="C196" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D196" s="5" t="s">
@@ -7106,19 +7115,19 @@
         <v>1</v>
       </c>
       <c r="F196" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="G196" s="28" t="s">
-        <v>141</v>
+        <v>256</v>
+      </c>
+      <c r="G196" s="32" t="s">
+        <v>139</v>
       </c>
       <c r="H196" s="15" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
     </row>
     <row r="197" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A197" s="42"/>
-      <c r="B197" s="31"/>
-      <c r="C197" s="29"/>
+      <c r="A197" s="34"/>
+      <c r="B197" s="35"/>
+      <c r="C197" s="28"/>
       <c r="D197" s="5" t="s">
         <v>108</v>
       </c>
@@ -7126,21 +7135,21 @@
         <v>1</v>
       </c>
       <c r="F197" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="G197" s="28"/>
+        <v>257</v>
+      </c>
+      <c r="G197" s="32"/>
       <c r="H197" s="15" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
     </row>
     <row r="198" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A198" s="34">
+      <c r="A198" s="41">
         <v>75</v>
       </c>
-      <c r="B198" s="33" t="s">
+      <c r="B198" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C198" s="29" t="s">
+      <c r="C198" s="28" t="s">
         <v>87</v>
       </c>
       <c r="D198" s="5" t="s">
@@ -7150,19 +7159,19 @@
         <v>2</v>
       </c>
       <c r="F198" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="G198" s="28" t="s">
-        <v>605</v>
+        <v>296</v>
+      </c>
+      <c r="G198" s="32" t="s">
+        <v>599</v>
       </c>
       <c r="H198" s="15" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
     </row>
     <row r="199" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A199" s="35"/>
-      <c r="B199" s="33"/>
-      <c r="C199" s="29"/>
+      <c r="A199" s="42"/>
+      <c r="B199" s="36"/>
+      <c r="C199" s="28"/>
       <c r="D199" s="5" t="s">
         <v>93</v>
       </c>
@@ -7170,21 +7179,21 @@
         <v>1</v>
       </c>
       <c r="F199" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="G199" s="28"/>
+        <v>296</v>
+      </c>
+      <c r="G199" s="32"/>
       <c r="H199" s="15" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
     </row>
     <row r="200" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A200" s="41">
+      <c r="A200" s="33">
         <v>76</v>
       </c>
-      <c r="B200" s="33" t="s">
+      <c r="B200" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C200" s="29" t="s">
+      <c r="C200" s="28" t="s">
         <v>87</v>
       </c>
       <c r="D200" s="5" t="s">
@@ -7194,19 +7203,19 @@
         <v>1</v>
       </c>
       <c r="F200" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="G200" s="32" t="s">
         <v>219</v>
       </c>
-      <c r="G200" s="28" t="s">
-        <v>221</v>
-      </c>
       <c r="H200" s="15" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
     </row>
     <row r="201" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A201" s="42"/>
-      <c r="B201" s="33"/>
-      <c r="C201" s="29"/>
+      <c r="A201" s="34"/>
+      <c r="B201" s="36"/>
+      <c r="C201" s="28"/>
       <c r="D201" s="5" t="s">
         <v>105</v>
       </c>
@@ -7214,21 +7223,21 @@
         <v>1</v>
       </c>
       <c r="F201" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="G201" s="28"/>
+        <v>218</v>
+      </c>
+      <c r="G201" s="32"/>
       <c r="H201" s="15" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
     </row>
     <row r="202" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A202" s="34">
+      <c r="A202" s="41">
         <v>77</v>
       </c>
-      <c r="B202" s="33" t="s">
+      <c r="B202" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C202" s="29" t="s">
+      <c r="C202" s="28" t="s">
         <v>87</v>
       </c>
       <c r="D202" s="5" t="s">
@@ -7238,19 +7247,19 @@
         <v>2</v>
       </c>
       <c r="F202" s="5" t="s">
-        <v>576</v>
-      </c>
-      <c r="G202" s="28" t="s">
-        <v>603</v>
+        <v>571</v>
+      </c>
+      <c r="G202" s="32" t="s">
+        <v>597</v>
       </c>
       <c r="H202" s="15" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
     </row>
     <row r="203" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A203" s="35"/>
-      <c r="B203" s="33"/>
-      <c r="C203" s="29"/>
+      <c r="A203" s="42"/>
+      <c r="B203" s="36"/>
+      <c r="C203" s="28"/>
       <c r="D203" s="5" t="s">
         <v>110</v>
       </c>
@@ -7258,21 +7267,21 @@
         <v>2</v>
       </c>
       <c r="F203" s="5" t="s">
-        <v>577</v>
-      </c>
-      <c r="G203" s="28"/>
+        <v>572</v>
+      </c>
+      <c r="G203" s="32"/>
       <c r="H203" s="15" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
     </row>
     <row r="204" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A204" s="41">
+      <c r="A204" s="33">
         <v>78</v>
       </c>
-      <c r="B204" s="33" t="s">
+      <c r="B204" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C204" s="29" t="s">
+      <c r="C204" s="28" t="s">
         <v>87</v>
       </c>
       <c r="D204" s="5" t="s">
@@ -7282,17 +7291,17 @@
         <v>1</v>
       </c>
       <c r="F204" s="5" t="s">
-        <v>611</v>
-      </c>
-      <c r="G204" s="28"/>
+        <v>605</v>
+      </c>
+      <c r="G204" s="32"/>
       <c r="H204" s="15" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="205" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A205" s="42"/>
-      <c r="B205" s="33"/>
-      <c r="C205" s="29"/>
+      <c r="A205" s="34"/>
+      <c r="B205" s="36"/>
+      <c r="C205" s="28"/>
       <c r="D205" s="5" t="s">
         <v>89</v>
       </c>
@@ -7300,21 +7309,21 @@
         <v>1</v>
       </c>
       <c r="F205" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="G205" s="28"/>
+        <v>243</v>
+      </c>
+      <c r="G205" s="32"/>
       <c r="H205" s="15" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
     </row>
     <row r="206" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A206" s="41">
+      <c r="A206" s="33">
         <v>79</v>
       </c>
-      <c r="B206" s="33" t="s">
+      <c r="B206" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C206" s="29" t="s">
+      <c r="C206" s="28" t="s">
         <v>87</v>
       </c>
       <c r="D206" s="5" t="s">
@@ -7324,17 +7333,17 @@
         <v>1</v>
       </c>
       <c r="F206" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="G206" s="28"/>
+        <v>244</v>
+      </c>
+      <c r="G206" s="32"/>
       <c r="H206" s="15" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="207" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A207" s="42"/>
-      <c r="B207" s="33"/>
-      <c r="C207" s="29"/>
+      <c r="A207" s="34"/>
+      <c r="B207" s="36"/>
+      <c r="C207" s="28"/>
       <c r="D207" s="5" t="s">
         <v>91</v>
       </c>
@@ -7342,21 +7351,21 @@
         <v>0</v>
       </c>
       <c r="F207" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="G207" s="28"/>
+        <v>244</v>
+      </c>
+      <c r="G207" s="32"/>
       <c r="H207" s="15" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="208" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A208" s="41">
+      <c r="A208" s="33">
         <v>80</v>
       </c>
-      <c r="B208" s="33" t="s">
+      <c r="B208" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C208" s="29" t="s">
+      <c r="C208" s="28" t="s">
         <v>87</v>
       </c>
       <c r="D208" s="5" t="s">
@@ -7366,19 +7375,19 @@
         <v>1</v>
       </c>
       <c r="F208" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="G208" s="28" t="s">
-        <v>241</v>
+        <v>231</v>
+      </c>
+      <c r="G208" s="32" t="s">
+        <v>239</v>
       </c>
       <c r="H208" s="15" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="209" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A209" s="42"/>
-      <c r="B209" s="33"/>
-      <c r="C209" s="29"/>
+      <c r="A209" s="34"/>
+      <c r="B209" s="36"/>
+      <c r="C209" s="28"/>
       <c r="D209" s="5" t="s">
         <v>103</v>
       </c>
@@ -7386,21 +7395,21 @@
         <v>1</v>
       </c>
       <c r="F209" s="5" t="s">
-        <v>600</v>
-      </c>
-      <c r="G209" s="28"/>
+        <v>594</v>
+      </c>
+      <c r="G209" s="32"/>
       <c r="H209" s="15" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
     </row>
     <row r="210" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A210" s="34">
+      <c r="A210" s="41">
         <v>81</v>
       </c>
-      <c r="B210" s="33" t="s">
+      <c r="B210" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C210" s="29" t="s">
+      <c r="C210" s="28" t="s">
         <v>87</v>
       </c>
       <c r="D210" s="5" t="s">
@@ -7410,19 +7419,19 @@
         <v>1</v>
       </c>
       <c r="F210" s="5" t="s">
-        <v>634</v>
-      </c>
-      <c r="G210" s="28" t="s">
-        <v>601</v>
+        <v>626</v>
+      </c>
+      <c r="G210" s="32" t="s">
+        <v>595</v>
       </c>
       <c r="H210" s="15" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
     </row>
     <row r="211" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A211" s="35"/>
-      <c r="B211" s="33"/>
-      <c r="C211" s="29"/>
+      <c r="A211" s="42"/>
+      <c r="B211" s="36"/>
+      <c r="C211" s="28"/>
       <c r="D211" s="5" t="s">
         <v>97</v>
       </c>
@@ -7430,63 +7439,63 @@
         <v>1</v>
       </c>
       <c r="F211" s="5" t="s">
-        <v>635</v>
-      </c>
-      <c r="G211" s="28"/>
+        <v>627</v>
+      </c>
+      <c r="G211" s="32"/>
       <c r="H211" s="15" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
     </row>
     <row r="212" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A212" s="41">
+      <c r="A212" s="33">
         <v>82</v>
       </c>
-      <c r="B212" s="48" t="s">
+      <c r="B212" s="44" t="s">
         <v>29</v>
       </c>
-      <c r="C212" s="29" t="s">
+      <c r="C212" s="28" t="s">
         <v>87</v>
       </c>
       <c r="D212" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E212" s="1">
         <v>1</v>
       </c>
       <c r="F212" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="G212" s="28"/>
+        <v>270</v>
+      </c>
+      <c r="G212" s="32"/>
       <c r="H212" s="15" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
     </row>
     <row r="213" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A213" s="42"/>
-      <c r="B213" s="49"/>
-      <c r="C213" s="29"/>
+      <c r="A213" s="34"/>
+      <c r="B213" s="45"/>
+      <c r="C213" s="28"/>
       <c r="D213" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E213" s="1">
         <v>0</v>
       </c>
       <c r="F213" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="G213" s="28"/>
+        <v>270</v>
+      </c>
+      <c r="G213" s="32"/>
       <c r="H213" s="15" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
     </row>
     <row r="214" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A214" s="41">
+      <c r="A214" s="33">
         <v>83</v>
       </c>
-      <c r="B214" s="31" t="s">
+      <c r="B214" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C214" s="29" t="s">
+      <c r="C214" s="28" t="s">
         <v>87</v>
       </c>
       <c r="D214" s="5" t="s">
@@ -7496,19 +7505,19 @@
         <v>2</v>
       </c>
       <c r="F214" s="5" t="s">
-        <v>568</v>
-      </c>
-      <c r="G214" s="28" t="s">
-        <v>604</v>
+        <v>563</v>
+      </c>
+      <c r="G214" s="32" t="s">
+        <v>598</v>
       </c>
       <c r="H214" s="15" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
     </row>
     <row r="215" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A215" s="42"/>
-      <c r="B215" s="31"/>
-      <c r="C215" s="29"/>
+      <c r="A215" s="34"/>
+      <c r="B215" s="35"/>
+      <c r="C215" s="28"/>
       <c r="D215" s="5" t="s">
         <v>136</v>
       </c>
@@ -7516,21 +7525,21 @@
         <v>1</v>
       </c>
       <c r="F215" s="5" t="s">
-        <v>575</v>
-      </c>
-      <c r="G215" s="28"/>
+        <v>570</v>
+      </c>
+      <c r="G215" s="32"/>
       <c r="H215" s="15" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
     </row>
     <row r="216" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A216" s="41">
+      <c r="A216" s="33">
         <v>84</v>
       </c>
-      <c r="B216" s="31" t="s">
+      <c r="B216" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C216" s="29" t="s">
+      <c r="C216" s="28" t="s">
         <v>87</v>
       </c>
       <c r="D216" s="5" t="s">
@@ -7540,19 +7549,19 @@
         <v>2</v>
       </c>
       <c r="F216" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="G216" s="28" t="s">
-        <v>300</v>
+        <v>247</v>
+      </c>
+      <c r="G216" s="32" t="s">
+        <v>298</v>
       </c>
       <c r="H216" s="15" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
     </row>
     <row r="217" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A217" s="42"/>
-      <c r="B217" s="31"/>
-      <c r="C217" s="29"/>
+      <c r="A217" s="34"/>
+      <c r="B217" s="35"/>
+      <c r="C217" s="28"/>
       <c r="D217" s="5" t="s">
         <v>95</v>
       </c>
@@ -7560,21 +7569,21 @@
         <v>2</v>
       </c>
       <c r="F217" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="G217" s="28"/>
+        <v>248</v>
+      </c>
+      <c r="G217" s="32"/>
       <c r="H217" s="15" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
     </row>
     <row r="218" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A218" s="41">
+      <c r="A218" s="33">
         <v>85</v>
       </c>
-      <c r="B218" s="31" t="s">
+      <c r="B218" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C218" s="29" t="s">
+      <c r="C218" s="28" t="s">
         <v>87</v>
       </c>
       <c r="D218" s="5" t="s">
@@ -7584,17 +7593,17 @@
         <v>3</v>
       </c>
       <c r="F218" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="G218" s="28"/>
+        <v>216</v>
+      </c>
+      <c r="G218" s="32"/>
       <c r="H218" s="15" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
     </row>
     <row r="219" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A219" s="42"/>
-      <c r="B219" s="31"/>
-      <c r="C219" s="29"/>
+      <c r="A219" s="34"/>
+      <c r="B219" s="35"/>
+      <c r="C219" s="28"/>
       <c r="D219" s="5" t="s">
         <v>99</v>
       </c>
@@ -7602,63 +7611,63 @@
         <v>2</v>
       </c>
       <c r="F219" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="G219" s="28"/>
+        <v>216</v>
+      </c>
+      <c r="G219" s="32"/>
       <c r="H219" s="15" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
     </row>
     <row r="220" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A220" s="41">
+      <c r="A220" s="33">
         <v>86</v>
       </c>
-      <c r="B220" s="31" t="s">
+      <c r="B220" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C220" s="29" t="s">
+      <c r="C220" s="28" t="s">
         <v>87</v>
       </c>
       <c r="D220" s="5" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E220" s="1">
         <v>2</v>
       </c>
       <c r="F220" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="G220" s="28"/>
+        <v>188</v>
+      </c>
+      <c r="G220" s="32"/>
       <c r="H220" s="15" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
     </row>
     <row r="221" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A221" s="42"/>
-      <c r="B221" s="31"/>
-      <c r="C221" s="29"/>
+      <c r="A221" s="34"/>
+      <c r="B221" s="35"/>
+      <c r="C221" s="28"/>
       <c r="D221" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E221" s="1">
         <v>2</v>
       </c>
       <c r="F221" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="G221" s="28"/>
+        <v>196</v>
+      </c>
+      <c r="G221" s="32"/>
       <c r="H221" s="15" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
     </row>
     <row r="222" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A222" s="41">
+      <c r="A222" s="33">
         <v>87</v>
       </c>
-      <c r="B222" s="31" t="s">
+      <c r="B222" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C222" s="32" t="s">
+      <c r="C222" s="43" t="s">
         <v>87</v>
       </c>
       <c r="D222" s="5" t="s">
@@ -7668,19 +7677,19 @@
         <v>2</v>
       </c>
       <c r="F222" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="G222" s="28" t="s">
-        <v>602</v>
+        <v>251</v>
+      </c>
+      <c r="G222" s="32" t="s">
+        <v>596</v>
       </c>
       <c r="H222" s="15" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
     </row>
     <row r="223" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A223" s="42"/>
-      <c r="B223" s="31"/>
-      <c r="C223" s="32"/>
+      <c r="A223" s="34"/>
+      <c r="B223" s="35"/>
+      <c r="C223" s="43"/>
       <c r="D223" s="5" t="s">
         <v>101</v>
       </c>
@@ -7688,198 +7697,560 @@
         <v>1</v>
       </c>
       <c r="F223" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="G223" s="28"/>
+        <v>251</v>
+      </c>
+      <c r="G223" s="32"/>
       <c r="H223" s="15" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
     </row>
     <row r="224" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A224" s="41">
+      <c r="A224" s="33">
         <v>88</v>
       </c>
-      <c r="B224" s="31" t="s">
+      <c r="B224" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C224" s="45" t="s">
+      <c r="C224" s="37" t="s">
         <v>87</v>
       </c>
       <c r="D224" s="5" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E224" s="1">
         <v>3</v>
       </c>
       <c r="F224" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="G224" s="28"/>
+        <v>297</v>
+      </c>
+      <c r="G224" s="32"/>
       <c r="H224" s="15" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="225" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A225" s="42"/>
-      <c r="B225" s="31"/>
-      <c r="C225" s="45"/>
+      <c r="A225" s="34"/>
+      <c r="B225" s="35"/>
+      <c r="C225" s="37"/>
       <c r="D225" s="5" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E225" s="1">
         <v>3</v>
       </c>
       <c r="F225" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="G225" s="28"/>
+        <v>255</v>
+      </c>
+      <c r="G225" s="32"/>
       <c r="H225" s="15" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A229" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A230" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A231" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A232" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A233" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A234" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A235" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A236" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A237" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="245" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A245" s="29" t="s">
-        <v>619</v>
-      </c>
-      <c r="B245" s="29"/>
-      <c r="C245" s="29"/>
-      <c r="D245" s="29"/>
-      <c r="E245" s="29"/>
-      <c r="F245" s="29"/>
-      <c r="G245" s="29"/>
-      <c r="H245" s="29"/>
+      <c r="A245" s="28" t="s">
+        <v>611</v>
+      </c>
+      <c r="B245" s="28"/>
+      <c r="C245" s="28"/>
+      <c r="D245" s="28"/>
+      <c r="E245" s="28"/>
+      <c r="F245" s="28"/>
+      <c r="G245" s="28"/>
+      <c r="H245" s="28"/>
     </row>
     <row r="246" spans="1:8" ht="25.7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A246" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>479</v>
-      </c>
-      <c r="C246" s="36" t="s">
+        <v>474</v>
+      </c>
+      <c r="C246" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="D246" s="37"/>
-      <c r="E246" s="37"/>
-      <c r="F246" s="38"/>
+      <c r="D246" s="30"/>
+      <c r="E246" s="30"/>
+      <c r="F246" s="31"/>
       <c r="G246" s="1" t="s">
         <v>3</v>
       </c>
       <c r="H246" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="247" spans="1:8" ht="100.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A247" s="18" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="B247" s="23" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="C247" s="25" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="D247" s="26"/>
       <c r="E247" s="26"/>
       <c r="F247" s="27"/>
       <c r="G247" s="4" t="s">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="H247" s="16" t="s">
-        <v>626</v>
+        <v>618</v>
       </c>
     </row>
     <row r="248" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A248" s="24" t="s">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="C248" s="25" t="s">
-        <v>624</v>
+        <v>616</v>
       </c>
       <c r="D248" s="26"/>
       <c r="E248" s="26"/>
       <c r="F248" s="27"/>
       <c r="G248" s="4" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="H248" s="16" t="s">
-        <v>627</v>
+        <v>619</v>
       </c>
     </row>
     <row r="253" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A253" s="29" t="s">
-        <v>621</v>
-      </c>
-      <c r="B253" s="29"/>
-      <c r="C253" s="29"/>
-      <c r="D253" s="29"/>
-      <c r="E253" s="29"/>
-      <c r="F253" s="29"/>
-      <c r="G253" s="29"/>
-      <c r="H253" s="29"/>
+      <c r="A253" s="28" t="s">
+        <v>613</v>
+      </c>
+      <c r="B253" s="28"/>
+      <c r="C253" s="28"/>
+      <c r="D253" s="28"/>
+      <c r="E253" s="28"/>
+      <c r="F253" s="28"/>
+      <c r="G253" s="28"/>
+      <c r="H253" s="28"/>
     </row>
     <row r="254" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A254" s="29" t="s">
-        <v>622</v>
-      </c>
-      <c r="B254" s="29"/>
-      <c r="C254" s="29"/>
-      <c r="D254" s="29"/>
-      <c r="E254" s="29"/>
-      <c r="F254" s="29"/>
-      <c r="G254" s="29"/>
-      <c r="H254" s="29"/>
+      <c r="A254" s="28" t="s">
+        <v>614</v>
+      </c>
+      <c r="B254" s="28"/>
+      <c r="C254" s="28"/>
+      <c r="D254" s="28"/>
+      <c r="E254" s="28"/>
+      <c r="F254" s="28"/>
+      <c r="G254" s="28"/>
+      <c r="H254" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="385">
+  <mergeCells count="386">
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="G60:G61"/>
+    <mergeCell ref="C208:C209"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="B92:B93"/>
+    <mergeCell ref="G88:G89"/>
+    <mergeCell ref="C90:C91"/>
+    <mergeCell ref="G130:G131"/>
+    <mergeCell ref="C130:C131"/>
+    <mergeCell ref="G144:G145"/>
+    <mergeCell ref="B162:B163"/>
+    <mergeCell ref="C162:C163"/>
+    <mergeCell ref="B138:B139"/>
+    <mergeCell ref="G154:G155"/>
+    <mergeCell ref="G158:G159"/>
+    <mergeCell ref="C156:C157"/>
+    <mergeCell ref="C142:C143"/>
+    <mergeCell ref="G120:G121"/>
+    <mergeCell ref="G114:G115"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="C62:C63"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="A48:H48"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="G50:G51"/>
+    <mergeCell ref="G52:G53"/>
+    <mergeCell ref="G54:G55"/>
+    <mergeCell ref="G56:G57"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="A124:A125"/>
+    <mergeCell ref="B124:B125"/>
+    <mergeCell ref="A118:A119"/>
+    <mergeCell ref="A134:A135"/>
+    <mergeCell ref="B134:B135"/>
+    <mergeCell ref="C134:C135"/>
+    <mergeCell ref="G214:G215"/>
+    <mergeCell ref="C118:C119"/>
+    <mergeCell ref="B118:B119"/>
+    <mergeCell ref="C124:C125"/>
+    <mergeCell ref="A152:A153"/>
+    <mergeCell ref="B152:B153"/>
+    <mergeCell ref="C152:C153"/>
+    <mergeCell ref="A146:A147"/>
+    <mergeCell ref="B146:B147"/>
+    <mergeCell ref="C146:C147"/>
+    <mergeCell ref="B150:B151"/>
+    <mergeCell ref="C150:C151"/>
+    <mergeCell ref="G150:G151"/>
+    <mergeCell ref="G160:G161"/>
+    <mergeCell ref="A166:A167"/>
+    <mergeCell ref="A162:A163"/>
+    <mergeCell ref="A188:A189"/>
+    <mergeCell ref="A190:A191"/>
+    <mergeCell ref="B190:B191"/>
+    <mergeCell ref="G182:G183"/>
+    <mergeCell ref="C190:C191"/>
+    <mergeCell ref="G188:G189"/>
+    <mergeCell ref="B188:B189"/>
+    <mergeCell ref="C172:C173"/>
+    <mergeCell ref="C158:C159"/>
+    <mergeCell ref="G156:G157"/>
+    <mergeCell ref="A156:A157"/>
+    <mergeCell ref="B156:B157"/>
+    <mergeCell ref="A174:A175"/>
+    <mergeCell ref="B174:B175"/>
+    <mergeCell ref="C174:C175"/>
+    <mergeCell ref="G174:G175"/>
+    <mergeCell ref="B158:B159"/>
+    <mergeCell ref="C186:C187"/>
+    <mergeCell ref="A158:A159"/>
+    <mergeCell ref="G186:G187"/>
+    <mergeCell ref="A182:A183"/>
+    <mergeCell ref="B182:B183"/>
+    <mergeCell ref="C168:C169"/>
+    <mergeCell ref="G166:G167"/>
+    <mergeCell ref="A184:A185"/>
+    <mergeCell ref="G162:G163"/>
+    <mergeCell ref="C180:C181"/>
+    <mergeCell ref="G178:G179"/>
+    <mergeCell ref="A176:A177"/>
+    <mergeCell ref="B132:B133"/>
+    <mergeCell ref="C132:C133"/>
+    <mergeCell ref="B154:B155"/>
+    <mergeCell ref="C154:C155"/>
+    <mergeCell ref="G152:G153"/>
+    <mergeCell ref="G172:G173"/>
+    <mergeCell ref="B176:B177"/>
+    <mergeCell ref="C176:C177"/>
+    <mergeCell ref="B172:B173"/>
+    <mergeCell ref="A168:A169"/>
+    <mergeCell ref="G170:G171"/>
+    <mergeCell ref="G176:G177"/>
+    <mergeCell ref="G142:G143"/>
+    <mergeCell ref="A170:A171"/>
+    <mergeCell ref="B170:B171"/>
+    <mergeCell ref="C170:C171"/>
+    <mergeCell ref="G168:G169"/>
+    <mergeCell ref="A172:A173"/>
+    <mergeCell ref="A180:A181"/>
+    <mergeCell ref="B180:B181"/>
+    <mergeCell ref="A136:A137"/>
+    <mergeCell ref="A126:A127"/>
+    <mergeCell ref="B126:B127"/>
+    <mergeCell ref="C126:C127"/>
+    <mergeCell ref="B136:B137"/>
+    <mergeCell ref="C136:C137"/>
+    <mergeCell ref="G148:G149"/>
+    <mergeCell ref="A150:A151"/>
+    <mergeCell ref="A160:A161"/>
+    <mergeCell ref="B160:B161"/>
+    <mergeCell ref="C160:C161"/>
+    <mergeCell ref="G128:G129"/>
+    <mergeCell ref="A154:A155"/>
+    <mergeCell ref="A138:A139"/>
+    <mergeCell ref="G140:G141"/>
+    <mergeCell ref="G134:G135"/>
+    <mergeCell ref="A128:A129"/>
+    <mergeCell ref="B128:B129"/>
+    <mergeCell ref="B148:B149"/>
+    <mergeCell ref="C148:C149"/>
+    <mergeCell ref="G146:G147"/>
+    <mergeCell ref="A144:A145"/>
+    <mergeCell ref="B144:B145"/>
+    <mergeCell ref="C144:C145"/>
+    <mergeCell ref="A140:A141"/>
+    <mergeCell ref="B140:B141"/>
+    <mergeCell ref="C140:C141"/>
+    <mergeCell ref="G136:G137"/>
+    <mergeCell ref="A132:A133"/>
+    <mergeCell ref="A130:A131"/>
+    <mergeCell ref="B130:B131"/>
+    <mergeCell ref="C128:C129"/>
+    <mergeCell ref="A142:A143"/>
+    <mergeCell ref="B142:B143"/>
+    <mergeCell ref="A148:A149"/>
+    <mergeCell ref="G84:G85"/>
+    <mergeCell ref="G92:G93"/>
+    <mergeCell ref="G82:G83"/>
+    <mergeCell ref="G90:G91"/>
+    <mergeCell ref="G100:G101"/>
+    <mergeCell ref="C138:C139"/>
+    <mergeCell ref="G138:G139"/>
+    <mergeCell ref="G116:G117"/>
+    <mergeCell ref="G108:G109"/>
+    <mergeCell ref="G110:G111"/>
+    <mergeCell ref="C110:C111"/>
+    <mergeCell ref="C102:C103"/>
+    <mergeCell ref="C114:C115"/>
+    <mergeCell ref="C112:C113"/>
+    <mergeCell ref="C116:C117"/>
+    <mergeCell ref="G122:G123"/>
+    <mergeCell ref="C122:C123"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="G132:G133"/>
+    <mergeCell ref="G106:G107"/>
+    <mergeCell ref="G96:G97"/>
+    <mergeCell ref="G102:G103"/>
+    <mergeCell ref="G126:G127"/>
+    <mergeCell ref="A114:A115"/>
+    <mergeCell ref="B114:B115"/>
+    <mergeCell ref="A112:A113"/>
+    <mergeCell ref="B112:B113"/>
+    <mergeCell ref="A116:A117"/>
+    <mergeCell ref="B116:B117"/>
+    <mergeCell ref="A122:A123"/>
+    <mergeCell ref="B122:B123"/>
+    <mergeCell ref="G98:G99"/>
+    <mergeCell ref="A108:A109"/>
+    <mergeCell ref="B108:B109"/>
+    <mergeCell ref="C108:C109"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="B110:B111"/>
+    <mergeCell ref="A98:A99"/>
+    <mergeCell ref="A100:A101"/>
+    <mergeCell ref="B100:B101"/>
+    <mergeCell ref="C100:C101"/>
+    <mergeCell ref="A110:A111"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="A94:A95"/>
+    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="B104:B105"/>
+    <mergeCell ref="C104:C105"/>
+    <mergeCell ref="A96:A97"/>
+    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="C96:C97"/>
+    <mergeCell ref="B98:B99"/>
+    <mergeCell ref="C98:C99"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="B102:B103"/>
+    <mergeCell ref="C218:C219"/>
+    <mergeCell ref="G68:G69"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="G72:G73"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="G74:G75"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="G76:G77"/>
+    <mergeCell ref="C76:C77"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="C86:C87"/>
+    <mergeCell ref="A86:A87"/>
+    <mergeCell ref="B86:B87"/>
+    <mergeCell ref="G80:G81"/>
+    <mergeCell ref="C88:C89"/>
+    <mergeCell ref="C94:C95"/>
+    <mergeCell ref="G94:G95"/>
+    <mergeCell ref="G192:G193"/>
+    <mergeCell ref="C224:C225"/>
+    <mergeCell ref="G222:G223"/>
+    <mergeCell ref="G198:G199"/>
+    <mergeCell ref="A224:A225"/>
+    <mergeCell ref="G220:G221"/>
+    <mergeCell ref="A210:A211"/>
+    <mergeCell ref="B210:B211"/>
+    <mergeCell ref="C210:C211"/>
+    <mergeCell ref="G224:G225"/>
+    <mergeCell ref="B224:B225"/>
+    <mergeCell ref="A222:A223"/>
+    <mergeCell ref="B222:B223"/>
+    <mergeCell ref="C222:C223"/>
+    <mergeCell ref="G218:G219"/>
+    <mergeCell ref="A212:A213"/>
+    <mergeCell ref="B212:B213"/>
+    <mergeCell ref="C212:C213"/>
+    <mergeCell ref="B214:B215"/>
+    <mergeCell ref="C214:C215"/>
+    <mergeCell ref="A208:A209"/>
+    <mergeCell ref="A220:A221"/>
+    <mergeCell ref="B220:B221"/>
+    <mergeCell ref="C220:C221"/>
+    <mergeCell ref="C178:C179"/>
+    <mergeCell ref="A214:A215"/>
+    <mergeCell ref="G212:G213"/>
+    <mergeCell ref="G196:G197"/>
+    <mergeCell ref="C182:C183"/>
+    <mergeCell ref="G180:G181"/>
+    <mergeCell ref="A164:A165"/>
+    <mergeCell ref="B164:B165"/>
+    <mergeCell ref="C164:C165"/>
+    <mergeCell ref="G190:G191"/>
+    <mergeCell ref="A178:A179"/>
+    <mergeCell ref="B178:B179"/>
+    <mergeCell ref="G164:G165"/>
+    <mergeCell ref="G200:G201"/>
+    <mergeCell ref="A198:A199"/>
+    <mergeCell ref="B198:B199"/>
+    <mergeCell ref="C198:C199"/>
+    <mergeCell ref="G194:G195"/>
+    <mergeCell ref="A186:A187"/>
+    <mergeCell ref="B186:B187"/>
+    <mergeCell ref="C188:C189"/>
+    <mergeCell ref="B184:B185"/>
+    <mergeCell ref="C184:C185"/>
+    <mergeCell ref="G184:G185"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="G216:G217"/>
+    <mergeCell ref="B216:B217"/>
+    <mergeCell ref="B208:B209"/>
+    <mergeCell ref="A106:A107"/>
+    <mergeCell ref="A218:A219"/>
+    <mergeCell ref="B218:B219"/>
+    <mergeCell ref="C216:C217"/>
+    <mergeCell ref="G208:G209"/>
+    <mergeCell ref="A206:A207"/>
+    <mergeCell ref="B206:B207"/>
+    <mergeCell ref="C206:C207"/>
+    <mergeCell ref="G206:G207"/>
+    <mergeCell ref="A204:A205"/>
+    <mergeCell ref="B204:B205"/>
+    <mergeCell ref="C204:C205"/>
+    <mergeCell ref="G204:G205"/>
+    <mergeCell ref="G210:G211"/>
+    <mergeCell ref="A216:A217"/>
+    <mergeCell ref="G112:G113"/>
+    <mergeCell ref="G124:G125"/>
+    <mergeCell ref="B166:B167"/>
+    <mergeCell ref="C166:C167"/>
+    <mergeCell ref="B168:B169"/>
+    <mergeCell ref="G78:G79"/>
+    <mergeCell ref="A202:A203"/>
+    <mergeCell ref="B202:B203"/>
+    <mergeCell ref="C202:C203"/>
+    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="G64:G65"/>
+    <mergeCell ref="B106:B107"/>
+    <mergeCell ref="C106:C107"/>
+    <mergeCell ref="G104:G105"/>
+    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="G70:G71"/>
+    <mergeCell ref="A90:A91"/>
+    <mergeCell ref="G66:G67"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="B84:B85"/>
+    <mergeCell ref="C84:C85"/>
+    <mergeCell ref="A88:A89"/>
+    <mergeCell ref="B88:B89"/>
+    <mergeCell ref="C92:C93"/>
+    <mergeCell ref="C200:C201"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A196:A197"/>
+    <mergeCell ref="B196:B197"/>
+    <mergeCell ref="C196:C197"/>
+    <mergeCell ref="A192:A193"/>
+    <mergeCell ref="B192:B193"/>
+    <mergeCell ref="C192:C193"/>
+    <mergeCell ref="G86:G87"/>
+    <mergeCell ref="A120:A121"/>
+    <mergeCell ref="B120:B121"/>
+    <mergeCell ref="C120:C121"/>
+    <mergeCell ref="G118:G119"/>
+    <mergeCell ref="A80:A81"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="C80:C81"/>
+    <mergeCell ref="A78:A79"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
     <mergeCell ref="C36:F36"/>
     <mergeCell ref="A245:H245"/>
     <mergeCell ref="A253:H253"/>
@@ -7904,367 +8275,6 @@
     <mergeCell ref="C194:C195"/>
     <mergeCell ref="A200:A201"/>
     <mergeCell ref="B200:B201"/>
-    <mergeCell ref="C200:C201"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="A31:H31"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A196:A197"/>
-    <mergeCell ref="B196:B197"/>
-    <mergeCell ref="C196:C197"/>
-    <mergeCell ref="A192:A193"/>
-    <mergeCell ref="B192:B193"/>
-    <mergeCell ref="C192:C193"/>
-    <mergeCell ref="G86:G87"/>
-    <mergeCell ref="A120:A121"/>
-    <mergeCell ref="B120:B121"/>
-    <mergeCell ref="C120:C121"/>
-    <mergeCell ref="G118:G119"/>
-    <mergeCell ref="A80:A81"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="C80:C81"/>
-    <mergeCell ref="A78:A79"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="G78:G79"/>
-    <mergeCell ref="A202:A203"/>
-    <mergeCell ref="B202:B203"/>
-    <mergeCell ref="C202:C203"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="A92:A93"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="G64:G65"/>
-    <mergeCell ref="B106:B107"/>
-    <mergeCell ref="C106:C107"/>
-    <mergeCell ref="G104:G105"/>
-    <mergeCell ref="A70:A71"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="C70:C71"/>
-    <mergeCell ref="G70:G71"/>
-    <mergeCell ref="A90:A91"/>
-    <mergeCell ref="G66:G67"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="B84:B85"/>
-    <mergeCell ref="C84:C85"/>
-    <mergeCell ref="A88:A89"/>
-    <mergeCell ref="B88:B89"/>
-    <mergeCell ref="C92:C93"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="G216:G217"/>
-    <mergeCell ref="B216:B217"/>
-    <mergeCell ref="B208:B209"/>
-    <mergeCell ref="A106:A107"/>
-    <mergeCell ref="A218:A219"/>
-    <mergeCell ref="B218:B219"/>
-    <mergeCell ref="C216:C217"/>
-    <mergeCell ref="G208:G209"/>
-    <mergeCell ref="A206:A207"/>
-    <mergeCell ref="B206:B207"/>
-    <mergeCell ref="C206:C207"/>
-    <mergeCell ref="G206:G207"/>
-    <mergeCell ref="A204:A205"/>
-    <mergeCell ref="B204:B205"/>
-    <mergeCell ref="C204:C205"/>
-    <mergeCell ref="G204:G205"/>
-    <mergeCell ref="G210:G211"/>
-    <mergeCell ref="A216:A217"/>
-    <mergeCell ref="G112:G113"/>
-    <mergeCell ref="G124:G125"/>
-    <mergeCell ref="B166:B167"/>
-    <mergeCell ref="C166:C167"/>
-    <mergeCell ref="B168:B169"/>
-    <mergeCell ref="C178:C179"/>
-    <mergeCell ref="A214:A215"/>
-    <mergeCell ref="G212:G213"/>
-    <mergeCell ref="G196:G197"/>
-    <mergeCell ref="C182:C183"/>
-    <mergeCell ref="G180:G181"/>
-    <mergeCell ref="A164:A165"/>
-    <mergeCell ref="B164:B165"/>
-    <mergeCell ref="C164:C165"/>
-    <mergeCell ref="G190:G191"/>
-    <mergeCell ref="A178:A179"/>
-    <mergeCell ref="B178:B179"/>
-    <mergeCell ref="G164:G165"/>
-    <mergeCell ref="G200:G201"/>
-    <mergeCell ref="A198:A199"/>
-    <mergeCell ref="B198:B199"/>
-    <mergeCell ref="C198:C199"/>
-    <mergeCell ref="G194:G195"/>
-    <mergeCell ref="A186:A187"/>
-    <mergeCell ref="B186:B187"/>
-    <mergeCell ref="C188:C189"/>
-    <mergeCell ref="B184:B185"/>
-    <mergeCell ref="C184:C185"/>
-    <mergeCell ref="G184:G185"/>
-    <mergeCell ref="G192:G193"/>
-    <mergeCell ref="C224:C225"/>
-    <mergeCell ref="G222:G223"/>
-    <mergeCell ref="G198:G199"/>
-    <mergeCell ref="A224:A225"/>
-    <mergeCell ref="G220:G221"/>
-    <mergeCell ref="A210:A211"/>
-    <mergeCell ref="B210:B211"/>
-    <mergeCell ref="C210:C211"/>
-    <mergeCell ref="G224:G225"/>
-    <mergeCell ref="B224:B225"/>
-    <mergeCell ref="A222:A223"/>
-    <mergeCell ref="B222:B223"/>
-    <mergeCell ref="C222:C223"/>
-    <mergeCell ref="G218:G219"/>
-    <mergeCell ref="A212:A213"/>
-    <mergeCell ref="B212:B213"/>
-    <mergeCell ref="C212:C213"/>
-    <mergeCell ref="B214:B215"/>
-    <mergeCell ref="C214:C215"/>
-    <mergeCell ref="A208:A209"/>
-    <mergeCell ref="A220:A221"/>
-    <mergeCell ref="B220:B221"/>
-    <mergeCell ref="C220:C221"/>
-    <mergeCell ref="C218:C219"/>
-    <mergeCell ref="G68:G69"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="G72:G73"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="G74:G75"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="G76:G77"/>
-    <mergeCell ref="C76:C77"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="C74:C75"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="C86:C87"/>
-    <mergeCell ref="A86:A87"/>
-    <mergeCell ref="B86:B87"/>
-    <mergeCell ref="G80:G81"/>
-    <mergeCell ref="C88:C89"/>
-    <mergeCell ref="C94:C95"/>
-    <mergeCell ref="G94:G95"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="A94:A95"/>
-    <mergeCell ref="B94:B95"/>
-    <mergeCell ref="B104:B105"/>
-    <mergeCell ref="C104:C105"/>
-    <mergeCell ref="A96:A97"/>
-    <mergeCell ref="B96:B97"/>
-    <mergeCell ref="C96:C97"/>
-    <mergeCell ref="B98:B99"/>
-    <mergeCell ref="C98:C99"/>
-    <mergeCell ref="A102:A103"/>
-    <mergeCell ref="B102:B103"/>
-    <mergeCell ref="A108:A109"/>
-    <mergeCell ref="B108:B109"/>
-    <mergeCell ref="C108:C109"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="B110:B111"/>
-    <mergeCell ref="A98:A99"/>
-    <mergeCell ref="A100:A101"/>
-    <mergeCell ref="B100:B101"/>
-    <mergeCell ref="C100:C101"/>
-    <mergeCell ref="A110:A111"/>
-    <mergeCell ref="A114:A115"/>
-    <mergeCell ref="B114:B115"/>
-    <mergeCell ref="A112:A113"/>
-    <mergeCell ref="B112:B113"/>
-    <mergeCell ref="A116:A117"/>
-    <mergeCell ref="B116:B117"/>
-    <mergeCell ref="A122:A123"/>
-    <mergeCell ref="B122:B123"/>
-    <mergeCell ref="G98:G99"/>
-    <mergeCell ref="G84:G85"/>
-    <mergeCell ref="G92:G93"/>
-    <mergeCell ref="G82:G83"/>
-    <mergeCell ref="G90:G91"/>
-    <mergeCell ref="G100:G101"/>
-    <mergeCell ref="C138:C139"/>
-    <mergeCell ref="G138:G139"/>
-    <mergeCell ref="G116:G117"/>
-    <mergeCell ref="G108:G109"/>
-    <mergeCell ref="G110:G111"/>
-    <mergeCell ref="C110:C111"/>
-    <mergeCell ref="C102:C103"/>
-    <mergeCell ref="C114:C115"/>
-    <mergeCell ref="C112:C113"/>
-    <mergeCell ref="C116:C117"/>
-    <mergeCell ref="G122:G123"/>
-    <mergeCell ref="C122:C123"/>
-    <mergeCell ref="C82:C83"/>
-    <mergeCell ref="G132:G133"/>
-    <mergeCell ref="G106:G107"/>
-    <mergeCell ref="G96:G97"/>
-    <mergeCell ref="G102:G103"/>
-    <mergeCell ref="G126:G127"/>
-    <mergeCell ref="A128:A129"/>
-    <mergeCell ref="B128:B129"/>
-    <mergeCell ref="B148:B149"/>
-    <mergeCell ref="C148:C149"/>
-    <mergeCell ref="G146:G147"/>
-    <mergeCell ref="A144:A145"/>
-    <mergeCell ref="B144:B145"/>
-    <mergeCell ref="C144:C145"/>
-    <mergeCell ref="A140:A141"/>
-    <mergeCell ref="B140:B141"/>
-    <mergeCell ref="C140:C141"/>
-    <mergeCell ref="G136:G137"/>
-    <mergeCell ref="A132:A133"/>
-    <mergeCell ref="A130:A131"/>
-    <mergeCell ref="B130:B131"/>
-    <mergeCell ref="C128:C129"/>
-    <mergeCell ref="A142:A143"/>
-    <mergeCell ref="B142:B143"/>
-    <mergeCell ref="A148:A149"/>
-    <mergeCell ref="A126:A127"/>
-    <mergeCell ref="B126:B127"/>
-    <mergeCell ref="C126:C127"/>
-    <mergeCell ref="B136:B137"/>
-    <mergeCell ref="C136:C137"/>
-    <mergeCell ref="G148:G149"/>
-    <mergeCell ref="A150:A151"/>
-    <mergeCell ref="A160:A161"/>
-    <mergeCell ref="B160:B161"/>
-    <mergeCell ref="C160:C161"/>
-    <mergeCell ref="G128:G129"/>
-    <mergeCell ref="A154:A155"/>
-    <mergeCell ref="A138:A139"/>
-    <mergeCell ref="G140:G141"/>
-    <mergeCell ref="C180:C181"/>
-    <mergeCell ref="G178:G179"/>
-    <mergeCell ref="A176:A177"/>
-    <mergeCell ref="B132:B133"/>
-    <mergeCell ref="C132:C133"/>
-    <mergeCell ref="B154:B155"/>
-    <mergeCell ref="C154:C155"/>
-    <mergeCell ref="G152:G153"/>
-    <mergeCell ref="G172:G173"/>
-    <mergeCell ref="B176:B177"/>
-    <mergeCell ref="C176:C177"/>
-    <mergeCell ref="B172:B173"/>
-    <mergeCell ref="A168:A169"/>
-    <mergeCell ref="G170:G171"/>
-    <mergeCell ref="G176:G177"/>
-    <mergeCell ref="G142:G143"/>
-    <mergeCell ref="A170:A171"/>
-    <mergeCell ref="B170:B171"/>
-    <mergeCell ref="C170:C171"/>
-    <mergeCell ref="G168:G169"/>
-    <mergeCell ref="A172:A173"/>
-    <mergeCell ref="A180:A181"/>
-    <mergeCell ref="B180:B181"/>
-    <mergeCell ref="A136:A137"/>
-    <mergeCell ref="B190:B191"/>
-    <mergeCell ref="G182:G183"/>
-    <mergeCell ref="C190:C191"/>
-    <mergeCell ref="G188:G189"/>
-    <mergeCell ref="B188:B189"/>
-    <mergeCell ref="C172:C173"/>
-    <mergeCell ref="C158:C159"/>
-    <mergeCell ref="G156:G157"/>
-    <mergeCell ref="A156:A157"/>
-    <mergeCell ref="B156:B157"/>
-    <mergeCell ref="A174:A175"/>
-    <mergeCell ref="B174:B175"/>
-    <mergeCell ref="C174:C175"/>
-    <mergeCell ref="G174:G175"/>
-    <mergeCell ref="B158:B159"/>
-    <mergeCell ref="C186:C187"/>
-    <mergeCell ref="A158:A159"/>
-    <mergeCell ref="G186:G187"/>
-    <mergeCell ref="A182:A183"/>
-    <mergeCell ref="B182:B183"/>
-    <mergeCell ref="C168:C169"/>
-    <mergeCell ref="G166:G167"/>
-    <mergeCell ref="A184:A185"/>
-    <mergeCell ref="G162:G163"/>
-    <mergeCell ref="A124:A125"/>
-    <mergeCell ref="B124:B125"/>
-    <mergeCell ref="A118:A119"/>
-    <mergeCell ref="A134:A135"/>
-    <mergeCell ref="B134:B135"/>
-    <mergeCell ref="C134:C135"/>
-    <mergeCell ref="G214:G215"/>
-    <mergeCell ref="C118:C119"/>
-    <mergeCell ref="B118:B119"/>
-    <mergeCell ref="C124:C125"/>
-    <mergeCell ref="A152:A153"/>
-    <mergeCell ref="B152:B153"/>
-    <mergeCell ref="C152:C153"/>
-    <mergeCell ref="A146:A147"/>
-    <mergeCell ref="B146:B147"/>
-    <mergeCell ref="C146:C147"/>
-    <mergeCell ref="B150:B151"/>
-    <mergeCell ref="C150:C151"/>
-    <mergeCell ref="G150:G151"/>
-    <mergeCell ref="G160:G161"/>
-    <mergeCell ref="A166:A167"/>
-    <mergeCell ref="A162:A163"/>
-    <mergeCell ref="A188:A189"/>
-    <mergeCell ref="A190:A191"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="A47:H47"/>
-    <mergeCell ref="A48:H48"/>
-    <mergeCell ref="A41:H41"/>
-    <mergeCell ref="G50:G51"/>
-    <mergeCell ref="G52:G53"/>
-    <mergeCell ref="G54:G55"/>
-    <mergeCell ref="G56:G57"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="A62:A63"/>
-    <mergeCell ref="C62:C63"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="G58:G59"/>
-    <mergeCell ref="G60:G61"/>
-    <mergeCell ref="C208:C209"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="C64:C65"/>
-    <mergeCell ref="B92:B93"/>
-    <mergeCell ref="G88:G89"/>
-    <mergeCell ref="C90:C91"/>
-    <mergeCell ref="G130:G131"/>
-    <mergeCell ref="C130:C131"/>
-    <mergeCell ref="G144:G145"/>
-    <mergeCell ref="B162:B163"/>
-    <mergeCell ref="C162:C163"/>
-    <mergeCell ref="B138:B139"/>
-    <mergeCell ref="G154:G155"/>
-    <mergeCell ref="G158:G159"/>
-    <mergeCell ref="C156:C157"/>
-    <mergeCell ref="C142:C143"/>
-    <mergeCell ref="G120:G121"/>
-    <mergeCell ref="G114:G115"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/main/resources/InesModResources/杀戮尖塔自制--伊内丝v0.2.xlsx
+++ b/src/main/resources/InesModResources/杀戮尖塔自制--伊内丝v0.2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\myMod\InesMod\InesMod\src\main\resources\InesModResources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FF22376-0CC0-4490-B0E9-962DAF953238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FE56407-E3FE-424F-BAE5-A9809505EA2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{7A3E14A4-2175-4856-859A-887D335814F1}"/>
   </bookViews>
@@ -271,10 +271,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>选择手牌中1张攻击牌，使其在本回合中耗能变为0。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>武器储备</t>
   </si>
   <si>
@@ -764,10 +760,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>选择手牌中2张攻击牌，使其在本回合中耗能变为0。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>先手为强</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -872,10 +864,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>此牌可消耗多层偷取。层数不足则全部消耗。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>实际为获得1层同名buff（效果可叠加，可跨回合），达到条件时触发。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1050,14 +1038,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>选择任意张牌加入抽牌堆，丢弃其它所有手牌。消耗。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>选择任意张牌加入抽牌堆，丢弃其它所有手牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>实际为获得1层同名buff（效果可叠加，可跨回合）。对群攻击则对群挂。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1258,9 +1238,6 @@
     <t>Throat Lock</t>
   </si>
   <si>
-    <t>Shadow Breaker</t>
-  </si>
-  <si>
     <t>Track Under Night</t>
   </si>
   <si>
@@ -1445,9 +1422,6 @@
   </si>
   <si>
     <t>Throat Lock+</t>
-  </si>
-  <si>
-    <t>Shadow Breaker+</t>
   </si>
   <si>
     <t>Track Under Night+</t>
@@ -1952,10 +1926,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>从卡牌中获得的格挡提升25%，但打出攻击牌后会消耗影哨。回合开始时，失去1层隐匿并获得1层虚影。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>虚影</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2009,10 +1979,6 @@
   </si>
   <si>
     <t>必须有1点情报才能打出。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>造成12点伤害。获得1层隐匿。本回合你无法再打出攻击牌。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2164,14 +2130,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">Veiled in sight </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Veiled in sight +</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Layered Shadows</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2197,10 +2155,6 @@
   </si>
   <si>
     <t>将手牌中所有影哨移入抽牌堆，然后抽相应数量的牌。消耗。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>当前所有手牌在本回合的耗能-1。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2361,10 +2315,6 @@
   </si>
   <si>
     <t>对所有敌人造成8点伤害。消耗等同于敌人数量的偷取。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>造成9点伤害。获得1层隐匿。本回合你无法再打出攻击牌。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2535,6 +2485,58 @@
   </si>
   <si>
     <t>Ad Hoc Strategy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得4点格挡。选择任意张牌加入抽牌堆，丢弃其它所有手牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得7点格挡。选择任意张牌加入抽牌堆，丢弃其它所有手牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>此牌可消耗多层偷取。层数不足则全部消耗。研究药瓶动画</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Break the Shadow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Break the Shadow+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Veiled in Sight </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Veiled in Sight +</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对所有敌人造成9点伤害。获得1层隐匿。本回合你无法再打出攻击牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对所有敌人造成12点伤害。获得1层隐匿。本回合你无法再打出攻击牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>从卡牌中获得的格挡提升50%，但打出攻击牌后会消耗影哨。回合结束时，失去1层隐匿并获得1层虚影。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当前所有手牌在本回合的耗能-2。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动打出。你打出的下2张攻击牌耗能变为0。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动打出。你打出的下3张攻击牌耗能变为0。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3227,7 +3229,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="28" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="B1" s="28"/>
       <c r="D1" s="2"/>
@@ -3237,10 +3239,10 @@
     </row>
     <row r="2" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="7" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="12"/>
@@ -3251,10 +3253,10 @@
     </row>
     <row r="3" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -3282,7 +3284,7 @@
     </row>
     <row r="8" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="29" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B8" s="30"/>
       <c r="C8" s="30"/>
@@ -3297,10 +3299,10 @@
         <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="D9" s="30"/>
       <c r="E9" s="31"/>
@@ -3311,107 +3313,107 @@
         <v>3</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="19" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="30" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="D10" s="30"/>
       <c r="E10" s="31"/>
       <c r="F10" s="9" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="G10" s="10"/>
       <c r="H10" s="17" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C11" s="29" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D11" s="30"/>
       <c r="E11" s="31"/>
       <c r="F11" s="9" t="s">
-        <v>648</v>
+        <v>635</v>
       </c>
       <c r="G11" s="10"/>
       <c r="H11" s="17" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="D12" s="30"/>
       <c r="E12" s="31"/>
       <c r="F12" s="9" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="G12" s="10"/>
       <c r="H12" s="17" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="D13" s="30"/>
       <c r="E13" s="31"/>
       <c r="F13" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="G13" s="10"/>
       <c r="H13" s="17" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>235</v>
-      </c>
       <c r="C14" s="30" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="D14" s="30"/>
       <c r="E14" s="31"/>
       <c r="F14" s="9" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="G14" s="10"/>
       <c r="H14" s="17" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
@@ -3419,7 +3421,7 @@
     <row r="17" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="28" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B18" s="28"/>
       <c r="C18" s="28"/>
@@ -3434,7 +3436,7 @@
         <v>9</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="C19" s="29" t="s">
         <v>2</v>
@@ -3446,7 +3448,7 @@
         <v>3</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
@@ -3454,157 +3456,157 @@
         <v>8</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="C20" s="25" t="s">
-        <v>606</v>
+        <v>594</v>
       </c>
       <c r="D20" s="26"/>
       <c r="E20" s="26"/>
       <c r="F20" s="27"/>
       <c r="G20" s="5" t="s">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
     </row>
     <row r="21" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="19" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="C21" s="25" t="s">
-        <v>647</v>
+        <v>634</v>
       </c>
       <c r="D21" s="26"/>
       <c r="E21" s="26"/>
       <c r="F21" s="27"/>
       <c r="G21" s="5" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
     </row>
     <row r="22" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="19" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="C22" s="25" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="D22" s="26"/>
       <c r="E22" s="26"/>
       <c r="F22" s="27"/>
       <c r="G22" s="5" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
     </row>
     <row r="23" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="19" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="C23" s="25" t="s">
-        <v>548</v>
+        <v>539</v>
       </c>
       <c r="D23" s="26"/>
       <c r="E23" s="26"/>
       <c r="F23" s="27"/>
       <c r="G23" s="4" t="s">
-        <v>549</v>
+        <v>540</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="19" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="C24" s="25" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="D24" s="26"/>
       <c r="E24" s="26"/>
       <c r="F24" s="27"/>
       <c r="G24" s="5" t="s">
-        <v>573</v>
+        <v>564</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="20" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="C25" s="25" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="D25" s="26"/>
       <c r="E25" s="26"/>
       <c r="F25" s="27"/>
       <c r="G25" s="5" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="20" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="C26" s="25" t="s">
-        <v>601</v>
+        <v>589</v>
       </c>
       <c r="D26" s="26"/>
       <c r="E26" s="26"/>
       <c r="F26" s="27"/>
       <c r="G26" s="4"/>
       <c r="H26" s="16" t="s">
-        <v>602</v>
+        <v>590</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="1" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="C27" s="25" t="s">
         <v>475</v>
-      </c>
-      <c r="C27" s="25" t="s">
-        <v>482</v>
       </c>
       <c r="D27" s="26"/>
       <c r="E27" s="26"/>
       <c r="F27" s="27"/>
       <c r="G27" s="4" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="H27" s="16" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
@@ -3612,7 +3614,7 @@
     <row r="30" spans="1:8" ht="21.7" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="31" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="28" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="B31" s="28"/>
       <c r="C31" s="28"/>
@@ -3627,7 +3629,7 @@
         <v>9</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="C32" s="29" t="s">
         <v>2</v>
@@ -3639,7 +3641,7 @@
         <v>3</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
@@ -3647,89 +3649,89 @@
         <v>8</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="C33" s="25" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="D33" s="26"/>
       <c r="E33" s="26"/>
       <c r="F33" s="27"/>
       <c r="G33" s="5"/>
       <c r="H33" s="16" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
     </row>
     <row r="34" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="19" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="C34" s="25" t="s">
-        <v>523</v>
+        <v>661</v>
       </c>
       <c r="D34" s="26"/>
       <c r="E34" s="26"/>
       <c r="F34" s="27"/>
       <c r="G34" s="5"/>
       <c r="H34" s="16" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
     </row>
     <row r="35" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="19" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>548</v>
+        <v>539</v>
       </c>
       <c r="D35" s="26"/>
       <c r="E35" s="26"/>
       <c r="F35" s="27"/>
       <c r="G35" s="5"/>
       <c r="H35" s="16" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
     </row>
     <row r="36" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="19" t="s">
-        <v>638</v>
+        <v>625</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="C36" s="25" t="s">
-        <v>639</v>
+        <v>626</v>
       </c>
       <c r="D36" s="26"/>
       <c r="E36" s="26"/>
       <c r="F36" s="27"/>
       <c r="G36" s="5"/>
       <c r="H36" s="16" t="s">
-        <v>640</v>
+        <v>627</v>
       </c>
     </row>
     <row r="37" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="19" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="C37" s="25" t="s">
-        <v>650</v>
+        <v>637</v>
       </c>
       <c r="D37" s="26"/>
       <c r="E37" s="26"/>
       <c r="F37" s="27"/>
       <c r="G37" s="5"/>
       <c r="H37" s="16" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
@@ -3746,7 +3748,7 @@
     </row>
     <row r="41" spans="1:8" s="3" customFormat="1" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="28" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="B41" s="28"/>
       <c r="C41" s="28"/>
@@ -3779,7 +3781,7 @@
         <v>3</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
     </row>
     <row r="43" spans="1:8" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.4">
@@ -3790,20 +3792,20 @@
         <v>17</v>
       </c>
       <c r="C43" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="E43" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="D43" s="6" t="s">
+      <c r="F43" s="5" t="s">
         <v>206</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="F43" s="5" t="s">
-        <v>208</v>
       </c>
       <c r="G43" s="4"/>
       <c r="H43" s="16" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
     </row>
     <row r="44" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -3811,7 +3813,7 @@
     </row>
     <row r="45" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="F45" s="3" t="s">
-        <v>610</v>
+        <v>598</v>
       </c>
       <c r="H45" s="2"/>
     </row>
@@ -3832,7 +3834,7 @@
     </row>
     <row r="48" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="28" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="B48" s="28"/>
       <c r="C48" s="28"/>
@@ -3865,7 +3867,7 @@
         <v>3</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
     </row>
     <row r="50" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -3889,7 +3891,7 @@
       </c>
       <c r="G50" s="32"/>
       <c r="H50" s="15" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
     </row>
     <row r="51" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -3907,7 +3909,7 @@
       </c>
       <c r="G51" s="32"/>
       <c r="H51" s="15" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
@@ -3935,7 +3937,7 @@
       </c>
       <c r="G52" s="32"/>
       <c r="H52" s="15" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
@@ -3957,7 +3959,7 @@
       </c>
       <c r="G53" s="32"/>
       <c r="H53" s="15" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
@@ -3981,11 +3983,11 @@
         <v>1</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="G54" s="32"/>
       <c r="H54" s="15" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
@@ -4003,11 +4005,11 @@
         <v>1</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="G55" s="32"/>
       <c r="H55" s="15" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
@@ -4031,11 +4033,11 @@
         <v>1</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="G56" s="32"/>
       <c r="H56" s="15" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
@@ -4053,11 +4055,11 @@
         <v>1</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="G57" s="32"/>
       <c r="H57" s="15" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
@@ -4081,13 +4083,13 @@
         <v>1</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="G58" s="32" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="H58" s="15" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
@@ -4105,11 +4107,11 @@
         <v>1</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>551</v>
+        <v>542</v>
       </c>
       <c r="G59" s="32"/>
       <c r="H59" s="15" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
@@ -4133,11 +4135,11 @@
         <v>0</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>591</v>
+        <v>579</v>
       </c>
       <c r="G60" s="32"/>
       <c r="H60" s="15" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
@@ -4155,11 +4157,11 @@
         <v>0</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>590</v>
+        <v>578</v>
       </c>
       <c r="G61" s="32"/>
       <c r="H61" s="15" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
@@ -4183,11 +4185,11 @@
         <v>1</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G62" s="32"/>
       <c r="H62" s="15" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="I62" s="2"/>
       <c r="J62" s="2"/>
@@ -4205,11 +4207,11 @@
         <v>1</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G63" s="32"/>
       <c r="H63" s="15" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
@@ -4227,19 +4229,19 @@
         <v>6</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E64" s="1">
         <v>0</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>592</v>
+        <v>580</v>
       </c>
       <c r="G64" s="32" t="s">
-        <v>564</v>
+        <v>555</v>
       </c>
       <c r="H64" s="15" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="I64" s="2"/>
       <c r="J64" s="2"/>
@@ -4251,17 +4253,17 @@
       <c r="B65" s="38"/>
       <c r="C65" s="28"/>
       <c r="D65" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E65" s="1">
         <v>0</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>593</v>
+        <v>581</v>
       </c>
       <c r="G65" s="32"/>
       <c r="H65" s="15" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="I65" s="2"/>
       <c r="J65" s="2"/>
@@ -4279,19 +4281,19 @@
         <v>6</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E66" s="1">
         <v>1</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>561</v>
+        <v>552</v>
       </c>
       <c r="G66" s="32" t="s">
-        <v>565</v>
+        <v>556</v>
       </c>
       <c r="H66" s="15" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
     </row>
     <row r="67" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4299,17 +4301,17 @@
       <c r="B67" s="38"/>
       <c r="C67" s="28"/>
       <c r="D67" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E67" s="1">
         <v>1</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>562</v>
+        <v>553</v>
       </c>
       <c r="G67" s="32"/>
       <c r="H67" s="15" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
     </row>
     <row r="68" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4323,19 +4325,19 @@
         <v>6</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E68" s="1">
         <v>1</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>543</v>
+        <v>534</v>
       </c>
       <c r="G68" s="32" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
       <c r="H68" s="15" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="I68" s="2"/>
       <c r="J68" s="2"/>
@@ -4347,17 +4349,17 @@
       <c r="B69" s="38"/>
       <c r="C69" s="28"/>
       <c r="D69" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E69" s="1">
         <v>1</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>542</v>
+        <v>533</v>
       </c>
       <c r="G69" s="32"/>
       <c r="H69" s="15" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="I69" s="2"/>
       <c r="J69" s="2"/>
@@ -4375,19 +4377,19 @@
         <v>6</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E70" s="1">
         <v>0</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>631</v>
+        <v>618</v>
       </c>
       <c r="G70" s="32" t="s">
-        <v>564</v>
+        <v>555</v>
       </c>
       <c r="H70" s="15" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="I70" s="2"/>
       <c r="J70" s="2"/>
@@ -4399,17 +4401,17 @@
       <c r="B71" s="38"/>
       <c r="C71" s="28"/>
       <c r="D71" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E71" s="1">
         <v>0</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>632</v>
+        <v>619</v>
       </c>
       <c r="G71" s="32"/>
       <c r="H71" s="15" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="I71" s="2"/>
       <c r="J71" s="2"/>
@@ -4433,13 +4435,13 @@
         <v>0</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>629</v>
+        <v>616</v>
       </c>
       <c r="G72" s="32" t="s">
-        <v>564</v>
+        <v>555</v>
       </c>
       <c r="H72" s="15" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="I72" s="2"/>
       <c r="J72" s="2"/>
@@ -4457,11 +4459,11 @@
         <v>0</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>630</v>
+        <v>617</v>
       </c>
       <c r="G73" s="32"/>
       <c r="H73" s="15" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="I73" s="2"/>
       <c r="J73" s="2"/>
@@ -4469,7 +4471,7 @@
       <c r="L73" s="2"/>
     </row>
     <row r="74" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A74" s="33">
+      <c r="A74" s="41">
         <v>13</v>
       </c>
       <c r="B74" s="36" t="s">
@@ -4485,11 +4487,11 @@
         <v>0</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>540</v>
+        <v>531</v>
       </c>
       <c r="G74" s="32"/>
       <c r="H74" s="15" t="s">
-        <v>320</v>
+        <v>655</v>
       </c>
       <c r="I74" s="2"/>
       <c r="J74" s="2"/>
@@ -4497,7 +4499,7 @@
       <c r="L74" s="2"/>
     </row>
     <row r="75" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A75" s="34"/>
+      <c r="A75" s="42"/>
       <c r="B75" s="36"/>
       <c r="C75" s="28"/>
       <c r="D75" s="5" t="s">
@@ -4507,11 +4509,11 @@
         <v>0</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>541</v>
+        <v>532</v>
       </c>
       <c r="G75" s="32"/>
       <c r="H75" s="15" t="s">
-        <v>383</v>
+        <v>656</v>
       </c>
       <c r="I75" s="2"/>
       <c r="J75" s="2"/>
@@ -4529,19 +4531,19 @@
         <v>6</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E76" s="1">
         <v>1</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="G76" s="32" t="s">
-        <v>564</v>
+        <v>555</v>
       </c>
       <c r="H76" s="15" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="I76" s="2"/>
       <c r="J76" s="2"/>
@@ -4553,17 +4555,17 @@
       <c r="B77" s="36"/>
       <c r="C77" s="28"/>
       <c r="D77" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E77" s="1">
         <v>1</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="G77" s="32"/>
       <c r="H77" s="15" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
     </row>
     <row r="78" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4577,19 +4579,19 @@
         <v>6</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E78" s="1">
         <v>2</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>624</v>
+        <v>611</v>
       </c>
       <c r="G78" s="32" t="s">
-        <v>621</v>
+        <v>609</v>
       </c>
       <c r="H78" s="15" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
     </row>
     <row r="79" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4597,21 +4599,21 @@
       <c r="B79" s="36"/>
       <c r="C79" s="28"/>
       <c r="D79" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E79" s="1">
         <v>2</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>625</v>
+        <v>612</v>
       </c>
       <c r="G79" s="32"/>
       <c r="H79" s="15" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
     </row>
     <row r="80" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A80" s="33">
+      <c r="A80" s="41">
         <v>16</v>
       </c>
       <c r="B80" s="36" t="s">
@@ -4621,41 +4623,41 @@
         <v>6</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E80" s="1">
         <v>2</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>623</v>
+        <v>659</v>
       </c>
       <c r="G80" s="32" t="s">
-        <v>539</v>
+        <v>530</v>
       </c>
       <c r="H80" s="15" t="s">
-        <v>575</v>
+        <v>657</v>
       </c>
     </row>
     <row r="81" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A81" s="34"/>
+      <c r="A81" s="42"/>
       <c r="B81" s="36"/>
       <c r="C81" s="40"/>
       <c r="D81" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E81" s="1">
         <v>2</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>538</v>
+        <v>660</v>
       </c>
       <c r="G81" s="32"/>
       <c r="H81" s="15" t="s">
-        <v>576</v>
+        <v>658</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A82" s="33">
+      <c r="A82" s="41">
         <v>17</v>
       </c>
       <c r="B82" s="36" t="s">
@@ -4671,17 +4673,17 @@
         <v>1</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>622</v>
+        <v>610</v>
       </c>
       <c r="G82" s="32" t="s">
-        <v>220</v>
+        <v>654</v>
       </c>
       <c r="H82" s="15" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
     </row>
     <row r="83" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A83" s="34"/>
+      <c r="A83" s="42"/>
       <c r="B83" s="36"/>
       <c r="C83" s="28"/>
       <c r="D83" s="5" t="s">
@@ -4691,11 +4693,11 @@
         <v>1</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="G83" s="32"/>
       <c r="H83" s="15" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
     </row>
     <row r="84" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4715,13 +4717,13 @@
         <v>43</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="G84" s="32" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="H84" s="15" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
     </row>
     <row r="85" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4735,11 +4737,11 @@
         <v>43</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="G85" s="32"/>
       <c r="H85" s="15" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
     </row>
     <row r="86" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4753,17 +4755,17 @@
         <v>6</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E86" s="1">
         <v>1</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>603</v>
+        <v>591</v>
       </c>
       <c r="G86" s="32"/>
       <c r="H86" s="15" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
     </row>
     <row r="87" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4771,17 +4773,17 @@
       <c r="B87" s="36"/>
       <c r="C87" s="28"/>
       <c r="D87" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E87" s="1">
         <v>1</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="G87" s="32"/>
       <c r="H87" s="15" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
     </row>
     <row r="88" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4795,19 +4797,19 @@
         <v>6</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="E88" s="1">
         <v>1</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="G88" s="32" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="H88" s="15" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="89" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4815,17 +4817,17 @@
       <c r="B89" s="35"/>
       <c r="C89" s="28"/>
       <c r="D89" s="5" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="E89" s="1">
         <v>1</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="G89" s="32"/>
       <c r="H89" s="15" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
     </row>
     <row r="90" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4839,19 +4841,19 @@
         <v>6</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E90" s="1">
         <v>0</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>546</v>
+        <v>537</v>
       </c>
       <c r="G90" s="32" t="s">
-        <v>550</v>
+        <v>541</v>
       </c>
       <c r="H90" s="15" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
     <row r="91" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4859,17 +4861,17 @@
       <c r="B91" s="35"/>
       <c r="C91" s="28"/>
       <c r="D91" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E91" s="1">
         <v>0</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>547</v>
+        <v>538</v>
       </c>
       <c r="G91" s="32"/>
       <c r="H91" s="15" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
     </row>
     <row r="92" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4883,19 +4885,19 @@
         <v>6</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E92" s="1">
         <v>2</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="G92" s="32" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="H92" s="15" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
     </row>
     <row r="93" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4903,17 +4905,17 @@
       <c r="B93" s="35"/>
       <c r="C93" s="28"/>
       <c r="D93" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E93" s="1">
         <v>2</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="G93" s="32"/>
       <c r="H93" s="15" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
     </row>
     <row r="94" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4933,13 +4935,13 @@
         <v>2</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>651</v>
+        <v>638</v>
       </c>
       <c r="G94" s="32" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="H94" s="15" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
     </row>
     <row r="95" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4953,11 +4955,11 @@
         <v>2</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>649</v>
+        <v>636</v>
       </c>
       <c r="G95" s="32"/>
       <c r="H95" s="15" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
     </row>
     <row r="96" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4971,19 +4973,19 @@
         <v>6</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="G96" s="32" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="H96" s="15" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
     </row>
     <row r="97" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4991,17 +4993,17 @@
       <c r="B97" s="35"/>
       <c r="C97" s="28"/>
       <c r="D97" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>545</v>
+        <v>536</v>
       </c>
       <c r="G97" s="32"/>
       <c r="H97" s="15" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
     </row>
     <row r="98" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5015,17 +5017,17 @@
         <v>14</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E98" s="1">
         <v>0</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="G98" s="32"/>
       <c r="H98" s="15" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
     </row>
     <row r="99" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5033,17 +5035,17 @@
       <c r="B99" s="38"/>
       <c r="C99" s="28"/>
       <c r="D99" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E99" s="1">
         <v>0</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="G99" s="32"/>
       <c r="H99" s="15" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
     </row>
     <row r="100" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5057,17 +5059,17 @@
         <v>14</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E100" s="1">
         <v>1</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>660</v>
+        <v>647</v>
       </c>
       <c r="G100" s="32"/>
       <c r="H100" s="15" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
     </row>
     <row r="101" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5075,17 +5077,17 @@
       <c r="B101" s="38"/>
       <c r="C101" s="37"/>
       <c r="D101" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E101" s="1">
         <v>1</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>661</v>
+        <v>648</v>
       </c>
       <c r="G101" s="32"/>
       <c r="H101" s="15" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
     </row>
     <row r="102" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5105,11 +5107,11 @@
         <v>1</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>265</v>
+        <v>652</v>
       </c>
       <c r="G102" s="32"/>
       <c r="H102" s="15" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
     </row>
     <row r="103" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5123,11 +5125,11 @@
         <v>1</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>266</v>
+        <v>653</v>
       </c>
       <c r="G103" s="32"/>
       <c r="H103" s="15" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
     </row>
     <row r="104" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5141,17 +5143,17 @@
         <v>14</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E104" s="1">
         <v>1</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>588</v>
+        <v>576</v>
       </c>
       <c r="G104" s="32"/>
       <c r="H104" s="15" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
     </row>
     <row r="105" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5159,17 +5161,17 @@
       <c r="B105" s="38"/>
       <c r="C105" s="28"/>
       <c r="D105" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E105" s="1">
         <v>1</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>589</v>
+        <v>577</v>
       </c>
       <c r="G105" s="32"/>
       <c r="H105" s="15" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
     </row>
     <row r="106" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5183,19 +5185,19 @@
         <v>14</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E106" s="1">
         <v>0</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="G106" s="32" t="s">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="H106" s="15" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="107" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5203,17 +5205,17 @@
       <c r="B107" s="38"/>
       <c r="C107" s="28"/>
       <c r="D107" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E107" s="1">
         <v>0</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="G107" s="32"/>
       <c r="H107" s="15" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
     </row>
     <row r="108" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5233,13 +5235,13 @@
         <v>1</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>636</v>
+        <v>623</v>
       </c>
       <c r="G108" s="32" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="H108" s="15" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
     </row>
     <row r="109" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5253,11 +5255,11 @@
         <v>1</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>637</v>
+        <v>624</v>
       </c>
       <c r="G109" s="32"/>
       <c r="H109" s="15" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
     </row>
     <row r="110" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5271,19 +5273,19 @@
         <v>14</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E110" s="1">
         <v>1</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>662</v>
+        <v>649</v>
       </c>
       <c r="G110" s="48" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="H110" s="15" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
     </row>
     <row r="111" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5291,17 +5293,17 @@
       <c r="B111" s="47"/>
       <c r="C111" s="43"/>
       <c r="D111" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E111" s="1">
         <v>1</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>663</v>
+        <v>650</v>
       </c>
       <c r="G111" s="49"/>
       <c r="H111" s="15" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
     </row>
     <row r="112" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5315,17 +5317,17 @@
         <v>14</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G112" s="32"/>
       <c r="H112" s="15" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
     </row>
     <row r="113" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5339,11 +5341,11 @@
         <v>43</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G113" s="32"/>
       <c r="H113" s="15" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
     </row>
     <row r="114" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5357,17 +5359,17 @@
         <v>14</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E114" s="1">
         <v>1</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>567</v>
+        <v>558</v>
       </c>
       <c r="G114" s="32"/>
       <c r="H114" s="15" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
     </row>
     <row r="115" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5375,17 +5377,17 @@
       <c r="B115" s="38"/>
       <c r="C115" s="28"/>
       <c r="D115" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E115" s="1">
         <v>1</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>568</v>
+        <v>559</v>
       </c>
       <c r="G115" s="32"/>
       <c r="H115" s="15" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
     </row>
     <row r="116" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5399,19 +5401,19 @@
         <v>14</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E116" s="1">
         <v>0</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G116" s="32" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="H116" s="15" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
     </row>
     <row r="117" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5419,17 +5421,17 @@
       <c r="B117" s="38"/>
       <c r="C117" s="28"/>
       <c r="D117" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E117" s="1">
         <v>0</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>634</v>
+        <v>621</v>
       </c>
       <c r="G117" s="32"/>
       <c r="H117" s="15" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
     </row>
     <row r="118" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5443,19 +5445,19 @@
         <v>14</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E118" s="1">
         <v>0</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="G118" s="32" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="H118" s="15" t="s">
-        <v>664</v>
+        <v>651</v>
       </c>
     </row>
     <row r="119" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5463,17 +5465,17 @@
       <c r="B119" s="38"/>
       <c r="C119" s="28"/>
       <c r="D119" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E119" s="1">
         <v>0</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>633</v>
+        <v>620</v>
       </c>
       <c r="G119" s="32"/>
       <c r="H119" s="15" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
     </row>
     <row r="120" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5487,19 +5489,19 @@
         <v>14</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E120" s="1">
         <v>0</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="G120" s="32" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="H120" s="15" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
     </row>
     <row r="121" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5507,17 +5509,17 @@
       <c r="B121" s="38"/>
       <c r="C121" s="28"/>
       <c r="D121" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E121" s="1">
         <v>0</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
       <c r="G121" s="32"/>
       <c r="H121" s="15" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
     </row>
     <row r="122" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
@@ -5531,17 +5533,17 @@
         <v>14</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E122" s="1">
         <v>2</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G122" s="32"/>
       <c r="H122" s="15" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
     </row>
     <row r="123" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5549,17 +5551,17 @@
       <c r="B123" s="47"/>
       <c r="C123" s="28"/>
       <c r="D123" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="E123" s="1">
+        <v>1</v>
+      </c>
+      <c r="F123" s="5" t="s">
         <v>181</v>
-      </c>
-      <c r="E123" s="1">
-        <v>1</v>
-      </c>
-      <c r="F123" s="5" t="s">
-        <v>182</v>
       </c>
       <c r="G123" s="32"/>
       <c r="H123" s="15" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
     </row>
     <row r="124" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5579,11 +5581,11 @@
         <v>1</v>
       </c>
       <c r="F124" s="5" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="G124" s="32"/>
       <c r="H124" s="15" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
     </row>
     <row r="125" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5597,11 +5599,11 @@
         <v>1</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="G125" s="32"/>
       <c r="H125" s="15" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
     </row>
     <row r="126" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5615,19 +5617,19 @@
         <v>14</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E126" s="1">
         <v>0</v>
       </c>
       <c r="F126" s="5" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G126" s="32" t="s">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="H126" s="15" t="s">
-        <v>577</v>
+        <v>566</v>
       </c>
     </row>
     <row r="127" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5635,17 +5637,17 @@
       <c r="B127" s="47"/>
       <c r="C127" s="28"/>
       <c r="D127" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E127" s="1">
         <v>0</v>
       </c>
       <c r="F127" s="5" t="s">
-        <v>579</v>
+        <v>568</v>
       </c>
       <c r="G127" s="32"/>
       <c r="H127" s="15" t="s">
-        <v>578</v>
+        <v>567</v>
       </c>
     </row>
     <row r="128" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5659,17 +5661,17 @@
         <v>14</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E128" s="1">
         <v>1</v>
       </c>
       <c r="F128" s="5" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="G128" s="32"/>
       <c r="H128" s="15" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
     </row>
     <row r="129" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5677,17 +5679,17 @@
       <c r="B129" s="47"/>
       <c r="C129" s="28"/>
       <c r="D129" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E129" s="1">
         <v>1</v>
       </c>
       <c r="F129" s="5" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="G129" s="32"/>
       <c r="H129" s="15" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
     </row>
     <row r="130" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5707,11 +5709,11 @@
         <v>1</v>
       </c>
       <c r="F130" s="5" t="s">
-        <v>66</v>
+        <v>663</v>
       </c>
       <c r="G130" s="32"/>
       <c r="H130" s="15" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="131" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5725,11 +5727,11 @@
         <v>1</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>193</v>
+        <v>664</v>
       </c>
       <c r="G131" s="32"/>
       <c r="H131" s="15" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
     </row>
     <row r="132" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5749,11 +5751,11 @@
         <v>0</v>
       </c>
       <c r="F132" s="5" t="s">
-        <v>583</v>
+        <v>572</v>
       </c>
       <c r="G132" s="32"/>
       <c r="H132" s="15" t="s">
-        <v>581</v>
+        <v>570</v>
       </c>
     </row>
     <row r="133" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5767,11 +5769,11 @@
         <v>0</v>
       </c>
       <c r="F133" s="5" t="s">
-        <v>580</v>
+        <v>569</v>
       </c>
       <c r="G133" s="32"/>
       <c r="H133" s="15" t="s">
-        <v>582</v>
+        <v>571</v>
       </c>
     </row>
     <row r="134" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5785,17 +5787,17 @@
         <v>14</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>654</v>
+        <v>641</v>
       </c>
       <c r="E134" s="1">
         <v>2</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>656</v>
+        <v>643</v>
       </c>
       <c r="G134" s="32"/>
       <c r="H134" s="15" t="s">
-        <v>657</v>
+        <v>644</v>
       </c>
     </row>
     <row r="135" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5803,17 +5805,17 @@
       <c r="B135" s="36"/>
       <c r="C135" s="28"/>
       <c r="D135" s="5" t="s">
-        <v>655</v>
+        <v>642</v>
       </c>
       <c r="E135" s="1">
         <v>2</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>659</v>
+        <v>646</v>
       </c>
       <c r="G135" s="32"/>
       <c r="H135" s="15" t="s">
-        <v>658</v>
+        <v>645</v>
       </c>
     </row>
     <row r="136" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5833,11 +5835,11 @@
         <v>1</v>
       </c>
       <c r="F136" s="5" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="G136" s="32"/>
       <c r="H136" s="15" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
     </row>
     <row r="137" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5851,11 +5853,11 @@
         <v>1</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="G137" s="32"/>
       <c r="H137" s="15" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
     </row>
     <row r="138" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5869,17 +5871,17 @@
         <v>14</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E138" s="1">
         <v>1</v>
       </c>
       <c r="F138" s="5" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="G138" s="32"/>
       <c r="H138" s="15" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
     </row>
     <row r="139" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5887,17 +5889,17 @@
       <c r="B139" s="36"/>
       <c r="C139" s="37"/>
       <c r="D139" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E139" s="1">
         <v>1</v>
       </c>
       <c r="F139" s="5" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G139" s="32"/>
       <c r="H139" s="15" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
     </row>
     <row r="140" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5911,19 +5913,19 @@
         <v>14</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E140" s="1">
         <v>0</v>
       </c>
       <c r="F140" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G140" s="32" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="H140" s="15" t="s">
-        <v>558</v>
+        <v>549</v>
       </c>
     </row>
     <row r="141" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5931,17 +5933,17 @@
       <c r="B141" s="36"/>
       <c r="C141" s="28"/>
       <c r="D141" s="5" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E141" s="1">
         <v>0</v>
       </c>
       <c r="F141" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G141" s="32"/>
       <c r="H141" s="15" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
     </row>
     <row r="142" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5955,19 +5957,19 @@
         <v>14</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E142" s="1">
         <v>1</v>
       </c>
       <c r="F142" s="5" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="G142" s="32" t="s">
-        <v>564</v>
+        <v>555</v>
       </c>
       <c r="H142" s="15" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
     </row>
     <row r="143" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5975,17 +5977,17 @@
       <c r="B143" s="36"/>
       <c r="C143" s="28"/>
       <c r="D143" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E143" s="1">
         <v>1</v>
       </c>
       <c r="F143" s="5" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="G143" s="32"/>
       <c r="H143" s="15" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
     </row>
     <row r="144" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5999,17 +6001,17 @@
         <v>14</v>
       </c>
       <c r="D144" s="5" t="s">
-        <v>552</v>
+        <v>543</v>
       </c>
       <c r="E144" s="1">
         <v>1</v>
       </c>
       <c r="F144" s="5" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="G144" s="32"/>
       <c r="H144" s="15" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
     </row>
     <row r="145" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6023,11 +6025,11 @@
         <v>0</v>
       </c>
       <c r="F145" s="5" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="G145" s="32"/>
       <c r="H145" s="15" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
     </row>
     <row r="146" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6047,13 +6049,13 @@
         <v>1</v>
       </c>
       <c r="F146" s="5" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="G146" s="32" t="s">
-        <v>564</v>
+        <v>555</v>
       </c>
       <c r="H146" s="15" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
     </row>
     <row r="147" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6067,11 +6069,11 @@
         <v>0</v>
       </c>
       <c r="F147" s="5" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="G147" s="32"/>
       <c r="H147" s="15" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
     </row>
     <row r="148" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6091,11 +6093,11 @@
         <v>1</v>
       </c>
       <c r="F148" s="5" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="G148" s="32"/>
       <c r="H148" s="15" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
     </row>
     <row r="149" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6109,11 +6111,11 @@
         <v>0</v>
       </c>
       <c r="F149" s="5" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="G149" s="32"/>
       <c r="H149" s="15" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="150" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6127,17 +6129,17 @@
         <v>14</v>
       </c>
       <c r="D150" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E150" s="1">
         <v>1</v>
       </c>
       <c r="F150" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G150" s="32"/>
       <c r="H150" s="15" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="151" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6145,17 +6147,17 @@
       <c r="B151" s="36"/>
       <c r="C151" s="28"/>
       <c r="D151" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E151" s="1">
         <v>0</v>
       </c>
       <c r="F151" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G151" s="32"/>
       <c r="H151" s="15" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
     </row>
     <row r="152" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6169,17 +6171,17 @@
         <v>14</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E152" s="1">
         <v>0</v>
       </c>
       <c r="F152" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G152" s="32"/>
       <c r="H152" s="15" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
     </row>
     <row r="153" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6187,17 +6189,17 @@
       <c r="B153" s="36"/>
       <c r="C153" s="28"/>
       <c r="D153" s="5" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E153" s="1">
         <v>0</v>
       </c>
       <c r="F153" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="G153" s="32"/>
       <c r="H153" s="15" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
     </row>
     <row r="154" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6217,13 +6219,13 @@
         <v>0</v>
       </c>
       <c r="F154" s="5" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="G154" s="32" t="s">
-        <v>635</v>
+        <v>622</v>
       </c>
       <c r="H154" s="15" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
     </row>
     <row r="155" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6237,11 +6239,11 @@
         <v>0</v>
       </c>
       <c r="F155" s="5" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="G155" s="32"/>
       <c r="H155" s="15" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
     </row>
     <row r="156" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6255,17 +6257,17 @@
         <v>14</v>
       </c>
       <c r="D156" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E156" s="1">
         <v>1</v>
       </c>
       <c r="F156" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G156" s="32"/>
       <c r="H156" s="15" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="157" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6273,17 +6275,17 @@
       <c r="B157" s="36"/>
       <c r="C157" s="28"/>
       <c r="D157" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E157" s="1">
         <v>1</v>
       </c>
       <c r="F157" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G157" s="32"/>
       <c r="H157" s="15" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
     </row>
     <row r="158" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6297,17 +6299,17 @@
         <v>14</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E158" s="1">
         <v>1</v>
       </c>
       <c r="F158" s="5" t="s">
-        <v>586</v>
+        <v>574</v>
       </c>
       <c r="G158" s="32"/>
       <c r="H158" s="15" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
     </row>
     <row r="159" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
@@ -6315,17 +6317,17 @@
       <c r="B159" s="36"/>
       <c r="C159" s="28"/>
       <c r="D159" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E159" s="1">
         <v>1</v>
       </c>
       <c r="F159" s="5" t="s">
-        <v>587</v>
+        <v>575</v>
       </c>
       <c r="G159" s="32"/>
       <c r="H159" s="15" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
     </row>
     <row r="160" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6339,19 +6341,19 @@
         <v>14</v>
       </c>
       <c r="D160" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E160" s="1">
         <v>1</v>
       </c>
       <c r="F160" s="5" t="s">
-        <v>585</v>
+        <v>573</v>
       </c>
       <c r="G160" s="32" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="H160" s="15" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
     </row>
     <row r="161" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6359,17 +6361,17 @@
       <c r="B161" s="36"/>
       <c r="C161" s="28"/>
       <c r="D161" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E161" s="1">
         <v>0</v>
       </c>
       <c r="F161" s="5" t="s">
-        <v>585</v>
+        <v>573</v>
       </c>
       <c r="G161" s="32"/>
       <c r="H161" s="15" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
     </row>
     <row r="162" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6383,19 +6385,19 @@
         <v>14</v>
       </c>
       <c r="D162" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E162" s="1">
         <v>0</v>
       </c>
       <c r="F162" s="5" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="G162" s="32" t="s">
-        <v>569</v>
+        <v>560</v>
       </c>
       <c r="H162" s="15" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
     </row>
     <row r="163" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6403,17 +6405,17 @@
       <c r="B163" s="36"/>
       <c r="C163" s="28"/>
       <c r="D163" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E163" s="1">
         <v>0</v>
       </c>
       <c r="F163" s="5" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="G163" s="32"/>
       <c r="H163" s="15" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
     </row>
     <row r="164" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6427,17 +6429,17 @@
         <v>14</v>
       </c>
       <c r="D164" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E164" s="1">
         <v>0</v>
       </c>
       <c r="F164" s="5" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="G164" s="32"/>
       <c r="H164" s="15" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
     </row>
     <row r="165" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6445,17 +6447,17 @@
       <c r="B165" s="36"/>
       <c r="C165" s="37"/>
       <c r="D165" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E165" s="1">
         <v>0</v>
       </c>
       <c r="F165" s="5" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="G165" s="32"/>
       <c r="H165" s="15" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
     </row>
     <row r="166" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6469,19 +6471,19 @@
         <v>14</v>
       </c>
       <c r="D166" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E166" s="1">
         <v>1</v>
       </c>
       <c r="F166" s="5" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="G166" s="32" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H166" s="15" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
     </row>
     <row r="167" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6489,17 +6491,17 @@
       <c r="B167" s="36"/>
       <c r="C167" s="37"/>
       <c r="D167" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E167" s="1">
         <v>0</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="G167" s="32"/>
       <c r="H167" s="15" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
     </row>
     <row r="168" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6513,17 +6515,17 @@
         <v>14</v>
       </c>
       <c r="D168" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E168" s="1">
         <v>1</v>
       </c>
       <c r="F168" s="5" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="G168" s="32"/>
       <c r="H168" s="15" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
     </row>
     <row r="169" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6531,17 +6533,17 @@
       <c r="B169" s="36"/>
       <c r="C169" s="37"/>
       <c r="D169" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E169" s="1">
         <v>1</v>
       </c>
       <c r="F169" s="5" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="G169" s="32"/>
       <c r="H169" s="15" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
     </row>
     <row r="170" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6555,17 +6557,17 @@
         <v>14</v>
       </c>
       <c r="D170" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E170" s="1">
         <v>2</v>
       </c>
       <c r="F170" s="5" t="s">
-        <v>645</v>
+        <v>632</v>
       </c>
       <c r="G170" s="32"/>
       <c r="H170" s="15" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
     </row>
     <row r="171" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6573,17 +6575,17 @@
       <c r="B171" s="36"/>
       <c r="C171" s="28"/>
       <c r="D171" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E171" s="1">
         <v>2</v>
       </c>
       <c r="F171" s="5" t="s">
-        <v>646</v>
+        <v>633</v>
       </c>
       <c r="G171" s="32"/>
       <c r="H171" s="15" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
     </row>
     <row r="172" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6597,17 +6599,17 @@
         <v>14</v>
       </c>
       <c r="D172" s="5" t="s">
-        <v>554</v>
+        <v>545</v>
       </c>
       <c r="E172" s="1">
         <v>1</v>
       </c>
       <c r="F172" s="5" t="s">
-        <v>556</v>
+        <v>547</v>
       </c>
       <c r="G172" s="32"/>
       <c r="H172" s="15" t="s">
-        <v>555</v>
+        <v>546</v>
       </c>
     </row>
     <row r="173" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6615,17 +6617,17 @@
       <c r="B173" s="36"/>
       <c r="C173" s="43"/>
       <c r="D173" s="5" t="s">
-        <v>553</v>
+        <v>544</v>
       </c>
       <c r="E173" s="1">
         <v>1</v>
       </c>
       <c r="F173" s="5" t="s">
-        <v>557</v>
+        <v>548</v>
       </c>
       <c r="G173" s="32"/>
       <c r="H173" s="15" t="s">
-        <v>555</v>
+        <v>546</v>
       </c>
     </row>
     <row r="174" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6639,19 +6641,19 @@
         <v>14</v>
       </c>
       <c r="D174" s="5" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E174" s="1">
         <v>1</v>
       </c>
       <c r="F174" s="5" t="s">
-        <v>608</v>
+        <v>596</v>
       </c>
       <c r="G174" s="32" t="s">
-        <v>607</v>
+        <v>595</v>
       </c>
       <c r="H174" s="15" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
     </row>
     <row r="175" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6659,17 +6661,17 @@
       <c r="B175" s="36"/>
       <c r="C175" s="37"/>
       <c r="D175" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E175" s="1">
         <v>1</v>
       </c>
       <c r="F175" s="5" t="s">
-        <v>609</v>
+        <v>597</v>
       </c>
       <c r="G175" s="32"/>
       <c r="H175" s="15" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
     </row>
     <row r="176" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6683,19 +6685,19 @@
         <v>14</v>
       </c>
       <c r="D176" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E176" s="1">
         <v>1</v>
       </c>
       <c r="F176" s="5" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="G176" s="32" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H176" s="15" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
     </row>
     <row r="177" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6703,17 +6705,17 @@
       <c r="B177" s="36"/>
       <c r="C177" s="28"/>
       <c r="D177" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E177" s="1">
         <v>1</v>
       </c>
       <c r="F177" s="5" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="G177" s="32"/>
       <c r="H177" s="15" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
     </row>
     <row r="178" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6727,17 +6729,17 @@
         <v>14</v>
       </c>
       <c r="D178" s="5" t="s">
-        <v>642</v>
+        <v>629</v>
       </c>
       <c r="E178" s="1">
         <v>1</v>
       </c>
       <c r="F178" s="5" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
       <c r="G178" s="32"/>
       <c r="H178" s="15" t="s">
-        <v>652</v>
+        <v>639</v>
       </c>
     </row>
     <row r="179" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6745,17 +6747,17 @@
       <c r="B179" s="35"/>
       <c r="C179" s="28"/>
       <c r="D179" s="5" t="s">
-        <v>643</v>
+        <v>630</v>
       </c>
       <c r="E179" s="1">
         <v>1</v>
       </c>
       <c r="F179" s="5" t="s">
-        <v>644</v>
+        <v>631</v>
       </c>
       <c r="G179" s="32"/>
       <c r="H179" s="15" t="s">
-        <v>653</v>
+        <v>640</v>
       </c>
     </row>
     <row r="180" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6775,11 +6777,11 @@
         <v>1</v>
       </c>
       <c r="F180" s="5" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="G180" s="32"/>
       <c r="H180" s="15" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
     </row>
     <row r="181" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6793,11 +6795,11 @@
         <v>1</v>
       </c>
       <c r="F181" s="5" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G181" s="32"/>
       <c r="H181" s="15" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
     </row>
     <row r="182" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6811,17 +6813,17 @@
         <v>14</v>
       </c>
       <c r="D182" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E182" s="1">
         <v>3</v>
       </c>
       <c r="F182" s="5" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G182" s="32"/>
       <c r="H182" s="15" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
     </row>
     <row r="183" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6829,17 +6831,17 @@
       <c r="B183" s="35"/>
       <c r="C183" s="28"/>
       <c r="D183" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E183" s="1">
         <v>3</v>
       </c>
       <c r="F183" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G183" s="32"/>
       <c r="H183" s="15" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
     </row>
     <row r="184" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6853,17 +6855,17 @@
         <v>14</v>
       </c>
       <c r="D184" s="5" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E184" s="1">
         <v>3</v>
       </c>
       <c r="F184" s="4" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G184" s="32"/>
       <c r="H184" s="15" t="s">
-        <v>559</v>
+        <v>550</v>
       </c>
     </row>
     <row r="185" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6871,17 +6873,17 @@
       <c r="B185" s="35"/>
       <c r="C185" s="28"/>
       <c r="D185" s="5" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E185" s="1">
         <v>2</v>
       </c>
       <c r="F185" s="4" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G185" s="32"/>
       <c r="H185" s="15" t="s">
-        <v>560</v>
+        <v>551</v>
       </c>
     </row>
     <row r="186" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6895,17 +6897,17 @@
         <v>14</v>
       </c>
       <c r="D186" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E186" s="1">
         <v>3</v>
       </c>
       <c r="F186" s="5" t="s">
-        <v>584</v>
+        <v>662</v>
       </c>
       <c r="G186" s="32"/>
       <c r="H186" s="15" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
     </row>
     <row r="187" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6913,17 +6915,17 @@
       <c r="B187" s="35"/>
       <c r="C187" s="28"/>
       <c r="D187" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E187" s="1">
         <v>2</v>
       </c>
       <c r="F187" s="5" t="s">
-        <v>584</v>
+        <v>662</v>
       </c>
       <c r="G187" s="32"/>
       <c r="H187" s="15" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
     </row>
     <row r="188" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6937,17 +6939,17 @@
         <v>14</v>
       </c>
       <c r="D188" s="5" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="E188" s="1">
         <v>0</v>
       </c>
       <c r="F188" s="5" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="G188" s="32"/>
       <c r="H188" s="15" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
     </row>
     <row r="189" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6955,17 +6957,17 @@
       <c r="B189" s="35"/>
       <c r="C189" s="37"/>
       <c r="D189" s="5" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="E189" s="1">
         <v>0</v>
       </c>
       <c r="F189" s="5" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="G189" s="32"/>
       <c r="H189" s="15" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
     </row>
     <row r="190" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6979,19 +6981,19 @@
         <v>14</v>
       </c>
       <c r="D190" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E190" s="1">
         <v>0</v>
       </c>
       <c r="F190" s="5" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="G190" s="32" t="s">
-        <v>564</v>
+        <v>555</v>
       </c>
       <c r="H190" s="15" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
     </row>
     <row r="191" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6999,17 +7001,17 @@
       <c r="B191" s="35"/>
       <c r="C191" s="37"/>
       <c r="D191" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E191" s="1">
         <v>0</v>
       </c>
       <c r="F191" s="5" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="G191" s="32"/>
       <c r="H191" s="15" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
     </row>
     <row r="192" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7023,17 +7025,17 @@
         <v>14</v>
       </c>
       <c r="D192" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E192" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F192" s="5" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="G192" s="32"/>
       <c r="H192" s="15" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
     </row>
     <row r="193" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7041,17 +7043,17 @@
       <c r="B193" s="35"/>
       <c r="C193" s="37"/>
       <c r="D193" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E193" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F193" s="5" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="G193" s="32"/>
       <c r="H193" s="15" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
     </row>
     <row r="194" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7065,19 +7067,19 @@
         <v>14</v>
       </c>
       <c r="D194" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E194" s="1">
         <v>4</v>
       </c>
       <c r="F194" s="5" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="G194" s="32" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H194" s="15" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
     </row>
     <row r="195" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7085,17 +7087,17 @@
       <c r="B195" s="35"/>
       <c r="C195" s="28"/>
       <c r="D195" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E195" s="1">
         <v>4</v>
       </c>
       <c r="F195" s="5" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="G195" s="32"/>
       <c r="H195" s="15" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="196" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7109,19 +7111,19 @@
         <v>14</v>
       </c>
       <c r="D196" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E196" s="1">
         <v>1</v>
       </c>
       <c r="F196" s="5" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="G196" s="32" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H196" s="15" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
     </row>
     <row r="197" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7129,17 +7131,17 @@
       <c r="B197" s="35"/>
       <c r="C197" s="28"/>
       <c r="D197" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E197" s="1">
         <v>1</v>
       </c>
       <c r="F197" s="5" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="G197" s="32"/>
       <c r="H197" s="15" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="198" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7150,22 +7152,22 @@
         <v>32</v>
       </c>
       <c r="C198" s="28" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D198" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E198" s="1">
         <v>2</v>
       </c>
       <c r="F198" s="5" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="G198" s="32" t="s">
-        <v>599</v>
+        <v>587</v>
       </c>
       <c r="H198" s="15" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
     </row>
     <row r="199" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7173,17 +7175,17 @@
       <c r="B199" s="36"/>
       <c r="C199" s="28"/>
       <c r="D199" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E199" s="1">
         <v>1</v>
       </c>
       <c r="F199" s="5" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="G199" s="32"/>
       <c r="H199" s="15" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
     </row>
     <row r="200" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7194,22 +7196,22 @@
         <v>32</v>
       </c>
       <c r="C200" s="28" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D200" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E200" s="1">
         <v>1</v>
       </c>
       <c r="F200" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="G200" s="32" t="s">
         <v>217</v>
       </c>
-      <c r="G200" s="32" t="s">
-        <v>219</v>
-      </c>
       <c r="H200" s="15" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
     </row>
     <row r="201" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7217,17 +7219,17 @@
       <c r="B201" s="36"/>
       <c r="C201" s="28"/>
       <c r="D201" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E201" s="1">
         <v>1</v>
       </c>
       <c r="F201" s="5" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G201" s="32"/>
       <c r="H201" s="15" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
     </row>
     <row r="202" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7238,22 +7240,22 @@
         <v>32</v>
       </c>
       <c r="C202" s="28" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D202" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E202" s="1">
         <v>2</v>
       </c>
       <c r="F202" s="5" t="s">
-        <v>571</v>
+        <v>562</v>
       </c>
       <c r="G202" s="32" t="s">
-        <v>597</v>
+        <v>585</v>
       </c>
       <c r="H202" s="15" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
     </row>
     <row r="203" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7261,17 +7263,17 @@
       <c r="B203" s="36"/>
       <c r="C203" s="28"/>
       <c r="D203" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E203" s="1">
         <v>2</v>
       </c>
       <c r="F203" s="5" t="s">
-        <v>572</v>
+        <v>563</v>
       </c>
       <c r="G203" s="32"/>
       <c r="H203" s="15" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
     </row>
     <row r="204" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7282,20 +7284,20 @@
         <v>32</v>
       </c>
       <c r="C204" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="D204" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="D204" s="5" t="s">
-        <v>88</v>
-      </c>
       <c r="E204" s="1">
         <v>1</v>
       </c>
       <c r="F204" s="5" t="s">
-        <v>605</v>
+        <v>593</v>
       </c>
       <c r="G204" s="32"/>
       <c r="H204" s="15" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
     </row>
     <row r="205" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7303,17 +7305,17 @@
       <c r="B205" s="36"/>
       <c r="C205" s="28"/>
       <c r="D205" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E205" s="1">
         <v>1</v>
       </c>
       <c r="F205" s="5" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="G205" s="32"/>
       <c r="H205" s="15" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
     </row>
     <row r="206" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7324,20 +7326,20 @@
         <v>32</v>
       </c>
       <c r="C206" s="28" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D206" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E206" s="1">
         <v>1</v>
       </c>
       <c r="F206" s="5" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="G206" s="32"/>
       <c r="H206" s="15" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
     </row>
     <row r="207" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7345,17 +7347,17 @@
       <c r="B207" s="36"/>
       <c r="C207" s="28"/>
       <c r="D207" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E207" s="1">
         <v>0</v>
       </c>
       <c r="F207" s="5" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="G207" s="32"/>
       <c r="H207" s="15" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
     </row>
     <row r="208" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7366,22 +7368,22 @@
         <v>32</v>
       </c>
       <c r="C208" s="28" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D208" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E208" s="1">
         <v>1</v>
       </c>
       <c r="F208" s="5" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="G208" s="32" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H208" s="15" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
     </row>
     <row r="209" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7389,17 +7391,17 @@
       <c r="B209" s="36"/>
       <c r="C209" s="28"/>
       <c r="D209" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E209" s="1">
         <v>1</v>
       </c>
       <c r="F209" s="5" t="s">
-        <v>594</v>
+        <v>582</v>
       </c>
       <c r="G209" s="32"/>
       <c r="H209" s="15" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
     </row>
     <row r="210" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
@@ -7410,22 +7412,22 @@
         <v>32</v>
       </c>
       <c r="C210" s="28" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D210" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E210" s="1">
         <v>1</v>
       </c>
       <c r="F210" s="5" t="s">
-        <v>626</v>
+        <v>613</v>
       </c>
       <c r="G210" s="32" t="s">
-        <v>595</v>
+        <v>583</v>
       </c>
       <c r="H210" s="15" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
     </row>
     <row r="211" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
@@ -7433,17 +7435,17 @@
       <c r="B211" s="36"/>
       <c r="C211" s="28"/>
       <c r="D211" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E211" s="1">
         <v>1</v>
       </c>
       <c r="F211" s="5" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="G211" s="32"/>
       <c r="H211" s="15" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
     </row>
     <row r="212" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7454,20 +7456,20 @@
         <v>29</v>
       </c>
       <c r="C212" s="28" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D212" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E212" s="1">
         <v>1</v>
       </c>
       <c r="F212" s="5" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="G212" s="32"/>
       <c r="H212" s="15" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
     </row>
     <row r="213" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7475,17 +7477,17 @@
       <c r="B213" s="45"/>
       <c r="C213" s="28"/>
       <c r="D213" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E213" s="1">
         <v>0</v>
       </c>
       <c r="F213" s="5" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="G213" s="32"/>
       <c r="H213" s="15" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
     </row>
     <row r="214" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7496,22 +7498,22 @@
         <v>29</v>
       </c>
       <c r="C214" s="28" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D214" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E214" s="1">
         <v>2</v>
       </c>
       <c r="F214" s="5" t="s">
-        <v>563</v>
+        <v>554</v>
       </c>
       <c r="G214" s="32" t="s">
-        <v>598</v>
+        <v>586</v>
       </c>
       <c r="H214" s="15" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
     </row>
     <row r="215" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
@@ -7519,17 +7521,17 @@
       <c r="B215" s="35"/>
       <c r="C215" s="28"/>
       <c r="D215" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E215" s="1">
         <v>1</v>
       </c>
       <c r="F215" s="5" t="s">
-        <v>570</v>
+        <v>561</v>
       </c>
       <c r="G215" s="32"/>
       <c r="H215" s="15" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
     </row>
     <row r="216" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
@@ -7540,22 +7542,22 @@
         <v>29</v>
       </c>
       <c r="C216" s="28" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D216" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E216" s="1">
         <v>2</v>
       </c>
       <c r="F216" s="5" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="G216" s="32" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="H216" s="15" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
     </row>
     <row r="217" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
@@ -7563,17 +7565,17 @@
       <c r="B217" s="35"/>
       <c r="C217" s="28"/>
       <c r="D217" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E217" s="1">
         <v>2</v>
       </c>
       <c r="F217" s="5" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="G217" s="32"/>
       <c r="H217" s="15" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
     </row>
     <row r="218" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
@@ -7584,20 +7586,20 @@
         <v>29</v>
       </c>
       <c r="C218" s="28" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D218" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E218" s="1">
         <v>3</v>
       </c>
       <c r="F218" s="5" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="G218" s="32"/>
       <c r="H218" s="15" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
     </row>
     <row r="219" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
@@ -7605,17 +7607,17 @@
       <c r="B219" s="35"/>
       <c r="C219" s="28"/>
       <c r="D219" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E219" s="1">
         <v>2</v>
       </c>
       <c r="F219" s="5" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="G219" s="32"/>
       <c r="H219" s="15" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
     </row>
     <row r="220" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
@@ -7626,20 +7628,20 @@
         <v>29</v>
       </c>
       <c r="C220" s="28" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D220" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E220" s="1">
         <v>2</v>
       </c>
       <c r="F220" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G220" s="32"/>
       <c r="H220" s="15" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
     </row>
     <row r="221" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
@@ -7647,17 +7649,17 @@
       <c r="B221" s="35"/>
       <c r="C221" s="28"/>
       <c r="D221" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E221" s="1">
         <v>2</v>
       </c>
       <c r="F221" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G221" s="32"/>
       <c r="H221" s="15" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
     </row>
     <row r="222" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
@@ -7668,22 +7670,22 @@
         <v>29</v>
       </c>
       <c r="C222" s="43" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D222" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E222" s="1">
         <v>2</v>
       </c>
       <c r="F222" s="5" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="G222" s="32" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
       <c r="H222" s="15" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
     </row>
     <row r="223" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
@@ -7691,17 +7693,17 @@
       <c r="B223" s="35"/>
       <c r="C223" s="43"/>
       <c r="D223" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E223" s="1">
         <v>1</v>
       </c>
       <c r="F223" s="5" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="G223" s="32"/>
       <c r="H223" s="15" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
     </row>
     <row r="224" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
@@ -7712,20 +7714,20 @@
         <v>29</v>
       </c>
       <c r="C224" s="37" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D224" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E224" s="1">
         <v>3</v>
       </c>
       <c r="F224" s="5" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="G224" s="32"/>
       <c r="H224" s="15" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
     </row>
     <row r="225" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
@@ -7733,67 +7735,67 @@
       <c r="B225" s="35"/>
       <c r="C225" s="37"/>
       <c r="D225" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E225" s="1">
         <v>3</v>
       </c>
       <c r="F225" s="5" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="G225" s="32"/>
       <c r="H225" s="15" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A229" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A230" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A231" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A232" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A233" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A234" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A235" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A236" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A237" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
     </row>
     <row r="245" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A245" s="28" t="s">
-        <v>611</v>
+        <v>599</v>
       </c>
       <c r="B245" s="28"/>
       <c r="C245" s="28"/>
@@ -7808,7 +7810,7 @@
         <v>9</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="C246" s="29" t="s">
         <v>2</v>
@@ -7820,52 +7822,52 @@
         <v>3</v>
       </c>
       <c r="H246" s="1" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
     </row>
     <row r="247" spans="1:8" ht="100.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A247" s="18" t="s">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="B247" s="23" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="C247" s="25" t="s">
-        <v>620</v>
+        <v>608</v>
       </c>
       <c r="D247" s="26"/>
       <c r="E247" s="26"/>
       <c r="F247" s="27"/>
       <c r="G247" s="4" t="s">
-        <v>628</v>
+        <v>615</v>
       </c>
       <c r="H247" s="16" t="s">
-        <v>618</v>
+        <v>606</v>
       </c>
     </row>
     <row r="248" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A248" s="24" t="s">
-        <v>612</v>
+        <v>600</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="C248" s="25" t="s">
-        <v>616</v>
+        <v>604</v>
       </c>
       <c r="D248" s="26"/>
       <c r="E248" s="26"/>
       <c r="F248" s="27"/>
       <c r="G248" s="4" t="s">
-        <v>615</v>
+        <v>603</v>
       </c>
       <c r="H248" s="16" t="s">
-        <v>619</v>
+        <v>607</v>
       </c>
     </row>
     <row r="253" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A253" s="28" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
       <c r="B253" s="28"/>
       <c r="C253" s="28"/>
@@ -7877,7 +7879,7 @@
     </row>
     <row r="254" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A254" s="28" t="s">
-        <v>614</v>
+        <v>602</v>
       </c>
       <c r="B254" s="28"/>
       <c r="C254" s="28"/>

--- a/src/main/resources/InesModResources/杀戮尖塔自制--伊内丝v0.2.xlsx
+++ b/src/main/resources/InesModResources/杀戮尖塔自制--伊内丝v0.2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\myMod\InesMod\InesMod\src\main\resources\InesModResources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FE56407-E3FE-424F-BAE5-A9809505EA2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA580072-45D6-4BD1-B98F-7912A089B7BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{7A3E14A4-2175-4856-859A-887D335814F1}"/>
   </bookViews>
@@ -880,10 +880,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>获得X+1层隐匿。消耗。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>联合哨戒</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -986,10 +982,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>战斗开始时，获得3层偷取。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>BOSS</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1010,19 +1002,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>本回合内，每次抽牌后需选择等量牌丢弃。抽2张牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>本回合内，每次抽牌后需选择等量牌丢弃。抽3张牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>下一次出牌时，将其一张耗能为0的复制品加入抽牌堆。消耗。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>下一次丢弃牌时，将其一张复制品加入到抽牌区的顶部。消耗。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1793,14 +1773,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>抽3张牌。丢弃1张牌。此牌每进入弃牌堆1次，抽牌数-1。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>抽3张牌。丢弃1张牌。此牌每被打出1次，抽牌数-1。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>获得2点情报。然后抽1张牌。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1970,14 +1942,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>获得等同于敌人数量的偷取。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>获得等同于敌人数量+1的偷取。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>必须有1点情报才能打出。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2231,14 +2195,6 @@
   </si>
   <si>
     <t>No Invisibility</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>造成7点伤害。本回合内，在隐匿下打出攻击牌改为丢弃影哨。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>造成9点伤害。本回合内，在隐匿下打出攻击牌改为丢弃影哨。保留。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2420,10 +2376,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>替换无锋绣针。战斗开始时，获得1层偷取。你的回合开始时，获得1层偷取。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>自动打出。对所有敌人造成14点伤害2次。若无法自动打出则消耗。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2468,14 +2420,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>自动打出。获得9点格挡。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自动打出。获得12点格挡。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>潜伏。攻击如果消耗了偷取，给予1层易伤。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2488,14 +2432,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>获得4点格挡。选择任意张牌加入抽牌堆，丢弃其它所有手牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>获得7点格挡。选择任意张牌加入抽牌堆，丢弃其它所有手牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>此牌可消耗多层偷取。层数不足则全部消耗。研究药瓶动画</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2537,6 +2473,70 @@
   </si>
   <si>
     <t>自动打出。你打出的下3张攻击牌耗能变为0。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成10点伤害。本回合内，在隐匿下打出攻击牌改为丢弃影哨。保留。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成9点伤害。本回合内，在隐匿下打出攻击牌改为丢弃影哨。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>替换无锋绣针。你的回合开始时，获得2层偷取。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斗开始时，获得4层偷取。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动打出。获得10点格挡。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动打出。获得14点格挡。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得X层隐匿。消耗。虚无。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>下一次丢弃牌时，将其立即打出一次。消耗。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本回合内，每抽1张牌可选择1张手牌丢弃。抽2张牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本回合内，每抽1张牌可选择1张手牌丢弃。抽3张牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得6点格挡。选择任意张手牌加入抽牌堆，丢弃其它所有手牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得8点格挡。选择任意张手牌加入抽牌堆，丢弃其它所有手牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得等同于敌人数量的偷取。抽1张牌。在弃牌堆放入一张此牌的复制品。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得等同于敌人数量+1的偷取。抽1张牌。在弃牌堆放入一张此牌的复制品。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>抽3张牌。丢弃1张牌。此牌每进入弃牌堆一次，抽牌数-1。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>抽3张牌。丢弃1张牌。此牌每被打出一次，抽牌数-1。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3229,7 +3229,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="28" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="B1" s="28"/>
       <c r="D1" s="2"/>
@@ -3239,10 +3239,10 @@
     </row>
     <row r="2" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="7" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="12"/>
@@ -3253,10 +3253,10 @@
     </row>
     <row r="3" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -3299,10 +3299,10 @@
         <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C9" s="29" t="s">
         <v>230</v>
-      </c>
-      <c r="C9" s="29" t="s">
-        <v>231</v>
       </c>
       <c r="D9" s="30"/>
       <c r="E9" s="31"/>
@@ -3313,7 +3313,7 @@
         <v>3</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
@@ -3324,96 +3324,96 @@
         <v>5</v>
       </c>
       <c r="C10" s="30" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D10" s="30"/>
       <c r="E10" s="31"/>
       <c r="F10" s="9" t="s">
-        <v>249</v>
+        <v>652</v>
       </c>
       <c r="G10" s="10"/>
       <c r="H10" s="17" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C11" s="29" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D11" s="30"/>
       <c r="E11" s="31"/>
       <c r="F11" s="9" t="s">
-        <v>635</v>
+        <v>651</v>
       </c>
       <c r="G11" s="10"/>
       <c r="H11" s="17" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="D12" s="30"/>
       <c r="E12" s="31"/>
       <c r="F12" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G12" s="10"/>
       <c r="H12" s="17" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="D13" s="30"/>
       <c r="E13" s="31"/>
       <c r="F13" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G13" s="10"/>
       <c r="H13" s="17" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C14" s="30" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="D14" s="30"/>
       <c r="E14" s="31"/>
       <c r="F14" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G14" s="10"/>
       <c r="H14" s="17" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
@@ -3436,7 +3436,7 @@
         <v>9</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="C19" s="29" t="s">
         <v>2</v>
@@ -3448,7 +3448,7 @@
         <v>3</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
@@ -3456,19 +3456,19 @@
         <v>8</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="C20" s="25" t="s">
-        <v>594</v>
+        <v>583</v>
       </c>
       <c r="D20" s="26"/>
       <c r="E20" s="26"/>
       <c r="F20" s="27"/>
       <c r="G20" s="5" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
     </row>
     <row r="21" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
@@ -3476,137 +3476,137 @@
         <v>207</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="C21" s="25" t="s">
-        <v>634</v>
+        <v>623</v>
       </c>
       <c r="D21" s="26"/>
       <c r="E21" s="26"/>
       <c r="F21" s="27"/>
       <c r="G21" s="5" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
     </row>
     <row r="22" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="19" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="C22" s="25" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="D22" s="26"/>
       <c r="E22" s="26"/>
       <c r="F22" s="27"/>
       <c r="G22" s="5" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
     </row>
     <row r="23" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="19" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="C23" s="25" t="s">
-        <v>539</v>
+        <v>530</v>
       </c>
       <c r="D23" s="26"/>
       <c r="E23" s="26"/>
       <c r="F23" s="27"/>
       <c r="G23" s="4" t="s">
-        <v>540</v>
+        <v>531</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="19" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="C24" s="25" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="D24" s="26"/>
       <c r="E24" s="26"/>
       <c r="F24" s="27"/>
       <c r="G24" s="5" t="s">
-        <v>564</v>
+        <v>555</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="20" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="C25" s="25" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="D25" s="26"/>
       <c r="E25" s="26"/>
       <c r="F25" s="27"/>
       <c r="G25" s="5" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="20" t="s">
-        <v>588</v>
+        <v>579</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="C26" s="25" t="s">
-        <v>589</v>
+        <v>580</v>
       </c>
       <c r="D26" s="26"/>
       <c r="E26" s="26"/>
       <c r="F26" s="27"/>
       <c r="G26" s="4"/>
       <c r="H26" s="16" t="s">
-        <v>590</v>
+        <v>581</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="1" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="C27" s="25" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="D27" s="26"/>
       <c r="E27" s="26"/>
       <c r="F27" s="27"/>
       <c r="G27" s="4" t="s">
-        <v>565</v>
+        <v>556</v>
       </c>
       <c r="H27" s="16" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
@@ -3614,7 +3614,7 @@
     <row r="30" spans="1:8" ht="21.7" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="31" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="28" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="B31" s="28"/>
       <c r="C31" s="28"/>
@@ -3629,7 +3629,7 @@
         <v>9</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="C32" s="29" t="s">
         <v>2</v>
@@ -3641,7 +3641,7 @@
         <v>3</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
@@ -3649,17 +3649,17 @@
         <v>8</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="C33" s="25" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="D33" s="26"/>
       <c r="E33" s="26"/>
       <c r="F33" s="27"/>
       <c r="G33" s="5"/>
       <c r="H33" s="16" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
     </row>
     <row r="34" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
@@ -3667,71 +3667,71 @@
         <v>207</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="C34" s="25" t="s">
-        <v>661</v>
+        <v>645</v>
       </c>
       <c r="D34" s="26"/>
       <c r="E34" s="26"/>
       <c r="F34" s="27"/>
       <c r="G34" s="5"/>
       <c r="H34" s="16" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
     </row>
     <row r="35" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="19" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>539</v>
+        <v>530</v>
       </c>
       <c r="D35" s="26"/>
       <c r="E35" s="26"/>
       <c r="F35" s="27"/>
       <c r="G35" s="5"/>
       <c r="H35" s="16" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
     </row>
     <row r="36" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="19" t="s">
-        <v>625</v>
+        <v>614</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="C36" s="25" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="D36" s="26"/>
       <c r="E36" s="26"/>
       <c r="F36" s="27"/>
       <c r="G36" s="5"/>
       <c r="H36" s="16" t="s">
-        <v>627</v>
+        <v>616</v>
       </c>
     </row>
     <row r="37" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="19" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="C37" s="25" t="s">
-        <v>637</v>
+        <v>625</v>
       </c>
       <c r="D37" s="26"/>
       <c r="E37" s="26"/>
       <c r="F37" s="27"/>
       <c r="G37" s="5"/>
       <c r="H37" s="16" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
@@ -3748,7 +3748,7 @@
     </row>
     <row r="41" spans="1:8" s="3" customFormat="1" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="28" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="B41" s="28"/>
       <c r="C41" s="28"/>
@@ -3781,7 +3781,7 @@
         <v>3</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
     </row>
     <row r="43" spans="1:8" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.4">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="G43" s="4"/>
       <c r="H43" s="16" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
     </row>
     <row r="44" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -3813,7 +3813,7 @@
     </row>
     <row r="45" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="F45" s="3" t="s">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="H45" s="2"/>
     </row>
@@ -3834,7 +3834,7 @@
     </row>
     <row r="48" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="28" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="B48" s="28"/>
       <c r="C48" s="28"/>
@@ -3867,7 +3867,7 @@
         <v>3</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
     </row>
     <row r="50" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G50" s="32"/>
       <c r="H50" s="15" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
     </row>
     <row r="51" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="G51" s="32"/>
       <c r="H51" s="15" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
@@ -3937,7 +3937,7 @@
       </c>
       <c r="G52" s="32"/>
       <c r="H52" s="15" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
@@ -3959,7 +3959,7 @@
       </c>
       <c r="G53" s="32"/>
       <c r="H53" s="15" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
@@ -3983,11 +3983,11 @@
         <v>1</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="G54" s="32"/>
       <c r="H54" s="15" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
@@ -4005,11 +4005,11 @@
         <v>1</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="G55" s="32"/>
       <c r="H55" s="15" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
@@ -4033,11 +4033,11 @@
         <v>1</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="G56" s="32"/>
       <c r="H56" s="15" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
@@ -4055,11 +4055,11 @@
         <v>1</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="G57" s="32"/>
       <c r="H57" s="15" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
@@ -4083,13 +4083,13 @@
         <v>1</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="G58" s="32" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="H58" s="15" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
@@ -4107,11 +4107,11 @@
         <v>1</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>542</v>
+        <v>533</v>
       </c>
       <c r="G59" s="32"/>
       <c r="H59" s="15" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
@@ -4135,11 +4135,11 @@
         <v>0</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="G60" s="32"/>
       <c r="H60" s="15" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
@@ -4157,11 +4157,11 @@
         <v>0</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
       <c r="G61" s="32"/>
       <c r="H61" s="15" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
@@ -4189,7 +4189,7 @@
       </c>
       <c r="G62" s="32"/>
       <c r="H62" s="15" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="I62" s="2"/>
       <c r="J62" s="2"/>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="G63" s="32"/>
       <c r="H63" s="15" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
@@ -4235,13 +4235,13 @@
         <v>0</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>580</v>
+        <v>571</v>
       </c>
       <c r="G64" s="32" t="s">
-        <v>555</v>
+        <v>546</v>
       </c>
       <c r="H64" s="15" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="I64" s="2"/>
       <c r="J64" s="2"/>
@@ -4259,11 +4259,11 @@
         <v>0</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>581</v>
+        <v>572</v>
       </c>
       <c r="G65" s="32"/>
       <c r="H65" s="15" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="I65" s="2"/>
       <c r="J65" s="2"/>
@@ -4287,13 +4287,13 @@
         <v>1</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>552</v>
+        <v>543</v>
       </c>
       <c r="G66" s="32" t="s">
-        <v>556</v>
+        <v>547</v>
       </c>
       <c r="H66" s="15" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
     </row>
     <row r="67" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4307,11 +4307,11 @@
         <v>1</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>553</v>
+        <v>544</v>
       </c>
       <c r="G67" s="32"/>
       <c r="H67" s="15" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
     </row>
     <row r="68" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4331,13 +4331,13 @@
         <v>1</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>534</v>
+        <v>525</v>
       </c>
       <c r="G68" s="32" t="s">
-        <v>557</v>
+        <v>548</v>
       </c>
       <c r="H68" s="15" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="I68" s="2"/>
       <c r="J68" s="2"/>
@@ -4355,11 +4355,11 @@
         <v>1</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>533</v>
+        <v>524</v>
       </c>
       <c r="G69" s="32"/>
       <c r="H69" s="15" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="I69" s="2"/>
       <c r="J69" s="2"/>
@@ -4383,13 +4383,13 @@
         <v>0</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="G70" s="32" t="s">
-        <v>555</v>
+        <v>546</v>
       </c>
       <c r="H70" s="15" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="I70" s="2"/>
       <c r="J70" s="2"/>
@@ -4407,11 +4407,11 @@
         <v>0</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>619</v>
+        <v>608</v>
       </c>
       <c r="G71" s="32"/>
       <c r="H71" s="15" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="I71" s="2"/>
       <c r="J71" s="2"/>
@@ -4435,13 +4435,13 @@
         <v>0</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>616</v>
+        <v>605</v>
       </c>
       <c r="G72" s="32" t="s">
-        <v>555</v>
+        <v>546</v>
       </c>
       <c r="H72" s="15" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="I72" s="2"/>
       <c r="J72" s="2"/>
@@ -4459,11 +4459,11 @@
         <v>0</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>617</v>
+        <v>606</v>
       </c>
       <c r="G73" s="32"/>
       <c r="H73" s="15" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="I73" s="2"/>
       <c r="J73" s="2"/>
@@ -4487,11 +4487,11 @@
         <v>0</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>531</v>
+        <v>522</v>
       </c>
       <c r="G74" s="32"/>
       <c r="H74" s="15" t="s">
-        <v>655</v>
+        <v>639</v>
       </c>
       <c r="I74" s="2"/>
       <c r="J74" s="2"/>
@@ -4509,11 +4509,11 @@
         <v>0</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>532</v>
+        <v>523</v>
       </c>
       <c r="G75" s="32"/>
       <c r="H75" s="15" t="s">
-        <v>656</v>
+        <v>640</v>
       </c>
       <c r="I75" s="2"/>
       <c r="J75" s="2"/>
@@ -4537,13 +4537,13 @@
         <v>1</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="G76" s="32" t="s">
-        <v>555</v>
+        <v>546</v>
       </c>
       <c r="H76" s="15" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="I76" s="2"/>
       <c r="J76" s="2"/>
@@ -4561,11 +4561,11 @@
         <v>1</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="G77" s="32"/>
       <c r="H77" s="15" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
     </row>
     <row r="78" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4585,13 +4585,13 @@
         <v>2</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>611</v>
+        <v>600</v>
       </c>
       <c r="G78" s="32" t="s">
-        <v>609</v>
+        <v>598</v>
       </c>
       <c r="H78" s="15" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
     </row>
     <row r="79" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4605,11 +4605,11 @@
         <v>2</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>612</v>
+        <v>601</v>
       </c>
       <c r="G79" s="32"/>
       <c r="H79" s="15" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
     </row>
     <row r="80" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4629,13 +4629,13 @@
         <v>2</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>659</v>
+        <v>643</v>
       </c>
       <c r="G80" s="32" t="s">
-        <v>530</v>
+        <v>521</v>
       </c>
       <c r="H80" s="15" t="s">
-        <v>657</v>
+        <v>641</v>
       </c>
     </row>
     <row r="81" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4649,11 +4649,11 @@
         <v>2</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>660</v>
+        <v>644</v>
       </c>
       <c r="G81" s="32"/>
       <c r="H81" s="15" t="s">
-        <v>658</v>
+        <v>642</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4673,13 +4673,13 @@
         <v>1</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>610</v>
+        <v>599</v>
       </c>
       <c r="G82" s="32" t="s">
-        <v>654</v>
+        <v>638</v>
       </c>
       <c r="H82" s="15" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
     </row>
     <row r="83" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4693,11 +4693,11 @@
         <v>1</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="G83" s="32"/>
       <c r="H83" s="15" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
     </row>
     <row r="84" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4717,13 +4717,13 @@
         <v>43</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="G84" s="32" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="H84" s="15" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
     </row>
     <row r="85" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4737,15 +4737,15 @@
         <v>43</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="G85" s="32"/>
       <c r="H85" s="15" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
     </row>
     <row r="86" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A86" s="33">
+      <c r="A86" s="41">
         <v>19</v>
       </c>
       <c r="B86" s="36" t="s">
@@ -4761,15 +4761,15 @@
         <v>1</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>591</v>
+        <v>650</v>
       </c>
       <c r="G86" s="32"/>
       <c r="H86" s="15" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
     </row>
     <row r="87" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A87" s="34"/>
+      <c r="A87" s="42"/>
       <c r="B87" s="36"/>
       <c r="C87" s="28"/>
       <c r="D87" s="5" t="s">
@@ -4779,11 +4779,11 @@
         <v>1</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>592</v>
+        <v>649</v>
       </c>
       <c r="G87" s="32"/>
       <c r="H87" s="15" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
     </row>
     <row r="88" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4797,19 +4797,19 @@
         <v>6</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="E88" s="1">
         <v>1</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="G88" s="32" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="H88" s="15" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
     </row>
     <row r="89" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4817,17 +4817,17 @@
       <c r="B89" s="35"/>
       <c r="C89" s="28"/>
       <c r="D89" s="5" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="E89" s="1">
         <v>1</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="G89" s="32"/>
       <c r="H89" s="15" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
     </row>
     <row r="90" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4847,13 +4847,13 @@
         <v>0</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>537</v>
+        <v>528</v>
       </c>
       <c r="G90" s="32" t="s">
-        <v>541</v>
+        <v>532</v>
       </c>
       <c r="H90" s="15" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
     </row>
     <row r="91" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4867,11 +4867,11 @@
         <v>0</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>538</v>
+        <v>529</v>
       </c>
       <c r="G91" s="32"/>
       <c r="H91" s="15" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
     </row>
     <row r="92" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4891,13 +4891,13 @@
         <v>2</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="G92" s="32" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="H92" s="15" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
     </row>
     <row r="93" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4911,11 +4911,11 @@
         <v>2</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="G93" s="32"/>
       <c r="H93" s="15" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
     </row>
     <row r="94" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4935,13 +4935,13 @@
         <v>2</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>638</v>
+        <v>626</v>
       </c>
       <c r="G94" s="32" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="H94" s="15" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
     </row>
     <row r="95" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4955,11 +4955,11 @@
         <v>2</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>636</v>
+        <v>624</v>
       </c>
       <c r="G95" s="32"/>
       <c r="H95" s="15" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="96" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4979,13 +4979,13 @@
         <v>43</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="G96" s="32" t="s">
         <v>199</v>
       </c>
       <c r="H96" s="15" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
     </row>
     <row r="97" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4999,11 +4999,11 @@
         <v>43</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>536</v>
+        <v>527</v>
       </c>
       <c r="G97" s="32"/>
       <c r="H97" s="15" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
     </row>
     <row r="98" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5023,11 +5023,11 @@
         <v>0</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>527</v>
+        <v>661</v>
       </c>
       <c r="G98" s="32"/>
       <c r="H98" s="15" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="99" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5041,11 +5041,11 @@
         <v>0</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>528</v>
+        <v>662</v>
       </c>
       <c r="G99" s="32"/>
       <c r="H99" s="15" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
     </row>
     <row r="100" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5065,11 +5065,11 @@
         <v>1</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="G100" s="32"/>
       <c r="H100" s="15" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
     </row>
     <row r="101" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5083,15 +5083,15 @@
         <v>1</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="G101" s="32"/>
       <c r="H101" s="15" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
     </row>
     <row r="102" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A102" s="33">
+      <c r="A102" s="41">
         <v>27</v>
       </c>
       <c r="B102" s="38" t="s">
@@ -5107,15 +5107,15 @@
         <v>1</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>652</v>
+        <v>659</v>
       </c>
       <c r="G102" s="32"/>
       <c r="H102" s="15" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
     </row>
     <row r="103" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A103" s="34"/>
+      <c r="A103" s="42"/>
       <c r="B103" s="38"/>
       <c r="C103" s="28"/>
       <c r="D103" s="5" t="s">
@@ -5125,15 +5125,15 @@
         <v>1</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>653</v>
+        <v>660</v>
       </c>
       <c r="G103" s="32"/>
       <c r="H103" s="15" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
     </row>
     <row r="104" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A104" s="33">
+      <c r="A104" s="41">
         <v>28</v>
       </c>
       <c r="B104" s="38" t="s">
@@ -5149,15 +5149,15 @@
         <v>1</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>576</v>
+        <v>567</v>
       </c>
       <c r="G104" s="32"/>
       <c r="H104" s="15" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
     </row>
     <row r="105" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A105" s="34"/>
+      <c r="A105" s="42"/>
       <c r="B105" s="38"/>
       <c r="C105" s="28"/>
       <c r="D105" s="5" t="s">
@@ -5167,11 +5167,11 @@
         <v>1</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>577</v>
+        <v>568</v>
       </c>
       <c r="G105" s="32"/>
       <c r="H105" s="15" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
     </row>
     <row r="106" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5191,13 +5191,13 @@
         <v>0</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="G106" s="32" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="H106" s="15" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
     </row>
     <row r="107" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5211,11 +5211,11 @@
         <v>0</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="G107" s="32"/>
       <c r="H107" s="15" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
     </row>
     <row r="108" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5235,13 +5235,13 @@
         <v>1</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>623</v>
+        <v>612</v>
       </c>
       <c r="G108" s="32" t="s">
         <v>218</v>
       </c>
       <c r="H108" s="15" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
     </row>
     <row r="109" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5255,11 +5255,11 @@
         <v>1</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>624</v>
+        <v>613</v>
       </c>
       <c r="G109" s="32"/>
       <c r="H109" s="15" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
     </row>
     <row r="110" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5279,13 +5279,13 @@
         <v>1</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>649</v>
+        <v>635</v>
       </c>
       <c r="G110" s="48" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="H110" s="15" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
     </row>
     <row r="111" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5299,11 +5299,11 @@
         <v>1</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>650</v>
+        <v>636</v>
       </c>
       <c r="G111" s="49"/>
       <c r="H111" s="15" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
     </row>
     <row r="112" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5317,7 +5317,7 @@
         <v>14</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>43</v>
@@ -5327,7 +5327,7 @@
       </c>
       <c r="G112" s="32"/>
       <c r="H112" s="15" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
     </row>
     <row r="113" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="G113" s="32"/>
       <c r="H113" s="15" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
     </row>
     <row r="114" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5365,11 +5365,11 @@
         <v>1</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>558</v>
+        <v>549</v>
       </c>
       <c r="G114" s="32"/>
       <c r="H114" s="15" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
     </row>
     <row r="115" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5383,11 +5383,11 @@
         <v>1</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>559</v>
+        <v>550</v>
       </c>
       <c r="G115" s="32"/>
       <c r="H115" s="15" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
     </row>
     <row r="116" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5413,7 +5413,7 @@
         <v>218</v>
       </c>
       <c r="H116" s="15" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
     </row>
     <row r="117" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5427,11 +5427,11 @@
         <v>0</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="G117" s="32"/>
       <c r="H117" s="15" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
     </row>
     <row r="118" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5457,7 +5457,7 @@
         <v>218</v>
       </c>
       <c r="H118" s="15" t="s">
-        <v>651</v>
+        <v>637</v>
       </c>
     </row>
     <row r="119" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5471,15 +5471,15 @@
         <v>0</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="G119" s="32"/>
       <c r="H119" s="15" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
     </row>
     <row r="120" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A120" s="33">
+      <c r="A120" s="41">
         <v>36</v>
       </c>
       <c r="B120" s="38" t="s">
@@ -5495,17 +5495,17 @@
         <v>0</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>483</v>
+        <v>663</v>
       </c>
       <c r="G120" s="32" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H120" s="15" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
     </row>
     <row r="121" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A121" s="34"/>
+      <c r="A121" s="42"/>
       <c r="B121" s="38"/>
       <c r="C121" s="28"/>
       <c r="D121" s="5" t="s">
@@ -5515,15 +5515,15 @@
         <v>0</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>484</v>
+        <v>664</v>
       </c>
       <c r="G121" s="32"/>
       <c r="H121" s="15" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
     </row>
     <row r="122" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A122" s="33">
+      <c r="A122" s="41">
         <v>37</v>
       </c>
       <c r="B122" s="46" t="s">
@@ -5543,11 +5543,11 @@
       </c>
       <c r="G122" s="32"/>
       <c r="H122" s="15" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
     </row>
     <row r="123" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A123" s="34"/>
+      <c r="A123" s="42"/>
       <c r="B123" s="47"/>
       <c r="C123" s="28"/>
       <c r="D123" s="5" t="s">
@@ -5561,11 +5561,11 @@
       </c>
       <c r="G123" s="32"/>
       <c r="H123" s="15" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
     </row>
     <row r="124" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A124" s="33">
+      <c r="A124" s="41">
         <v>38</v>
       </c>
       <c r="B124" s="46" t="s">
@@ -5581,15 +5581,15 @@
         <v>1</v>
       </c>
       <c r="F124" s="5" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="G124" s="32"/>
       <c r="H124" s="15" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
     </row>
     <row r="125" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A125" s="34"/>
+      <c r="A125" s="42"/>
       <c r="B125" s="47"/>
       <c r="C125" s="28"/>
       <c r="D125" s="5" t="s">
@@ -5599,15 +5599,15 @@
         <v>1</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
       <c r="G125" s="32"/>
       <c r="H125" s="15" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
     </row>
     <row r="126" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A126" s="33">
+      <c r="A126" s="41">
         <v>39</v>
       </c>
       <c r="B126" s="46" t="s">
@@ -5623,17 +5623,17 @@
         <v>0</v>
       </c>
       <c r="F126" s="5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G126" s="32" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="H126" s="15" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
     </row>
     <row r="127" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A127" s="34"/>
+      <c r="A127" s="42"/>
       <c r="B127" s="47"/>
       <c r="C127" s="28"/>
       <c r="D127" s="5" t="s">
@@ -5643,11 +5643,11 @@
         <v>0</v>
       </c>
       <c r="F127" s="5" t="s">
-        <v>568</v>
+        <v>559</v>
       </c>
       <c r="G127" s="32"/>
       <c r="H127" s="15" t="s">
-        <v>567</v>
+        <v>558</v>
       </c>
     </row>
     <row r="128" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5667,11 +5667,11 @@
         <v>1</v>
       </c>
       <c r="F128" s="5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G128" s="32"/>
       <c r="H128" s="15" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
     </row>
     <row r="129" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5685,15 +5685,15 @@
         <v>1</v>
       </c>
       <c r="F129" s="5" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="G129" s="32"/>
       <c r="H129" s="15" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
     </row>
     <row r="130" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A130" s="33">
+      <c r="A130" s="41">
         <v>41</v>
       </c>
       <c r="B130" s="46" t="s">
@@ -5709,15 +5709,15 @@
         <v>1</v>
       </c>
       <c r="F130" s="5" t="s">
-        <v>663</v>
+        <v>647</v>
       </c>
       <c r="G130" s="32"/>
       <c r="H130" s="15" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
     </row>
     <row r="131" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A131" s="34"/>
+      <c r="A131" s="42"/>
       <c r="B131" s="47"/>
       <c r="C131" s="43"/>
       <c r="D131" s="5" t="s">
@@ -5727,11 +5727,11 @@
         <v>1</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>664</v>
+        <v>648</v>
       </c>
       <c r="G131" s="32"/>
       <c r="H131" s="15" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
     </row>
     <row r="132" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5751,11 +5751,11 @@
         <v>0</v>
       </c>
       <c r="F132" s="5" t="s">
-        <v>572</v>
+        <v>563</v>
       </c>
       <c r="G132" s="32"/>
       <c r="H132" s="15" t="s">
-        <v>570</v>
+        <v>561</v>
       </c>
     </row>
     <row r="133" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5769,11 +5769,11 @@
         <v>0</v>
       </c>
       <c r="F133" s="5" t="s">
-        <v>569</v>
+        <v>560</v>
       </c>
       <c r="G133" s="32"/>
       <c r="H133" s="15" t="s">
-        <v>571</v>
+        <v>562</v>
       </c>
     </row>
     <row r="134" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5787,17 +5787,17 @@
         <v>14</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>641</v>
+        <v>629</v>
       </c>
       <c r="E134" s="1">
         <v>2</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>643</v>
+        <v>631</v>
       </c>
       <c r="G134" s="32"/>
       <c r="H134" s="15" t="s">
-        <v>644</v>
+        <v>632</v>
       </c>
     </row>
     <row r="135" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5805,17 +5805,17 @@
       <c r="B135" s="36"/>
       <c r="C135" s="28"/>
       <c r="D135" s="5" t="s">
-        <v>642</v>
+        <v>630</v>
       </c>
       <c r="E135" s="1">
         <v>2</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>646</v>
+        <v>634</v>
       </c>
       <c r="G135" s="32"/>
       <c r="H135" s="15" t="s">
-        <v>645</v>
+        <v>633</v>
       </c>
     </row>
     <row r="136" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5835,11 +5835,11 @@
         <v>1</v>
       </c>
       <c r="F136" s="5" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="G136" s="32"/>
       <c r="H136" s="15" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
     </row>
     <row r="137" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5853,11 +5853,11 @@
         <v>1</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="G137" s="32"/>
       <c r="H137" s="15" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
     </row>
     <row r="138" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="G138" s="32"/>
       <c r="H138" s="15" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
     </row>
     <row r="139" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="G139" s="32"/>
       <c r="H139" s="15" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
     </row>
     <row r="140" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5913,7 +5913,7 @@
         <v>14</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E140" s="1">
         <v>0</v>
@@ -5925,7 +5925,7 @@
         <v>211</v>
       </c>
       <c r="H140" s="15" t="s">
-        <v>549</v>
+        <v>540</v>
       </c>
     </row>
     <row r="141" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5933,7 +5933,7 @@
       <c r="B141" s="36"/>
       <c r="C141" s="28"/>
       <c r="D141" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E141" s="1">
         <v>0</v>
@@ -5943,7 +5943,7 @@
       </c>
       <c r="G141" s="32"/>
       <c r="H141" s="15" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
     </row>
     <row r="142" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5963,13 +5963,13 @@
         <v>1</v>
       </c>
       <c r="F142" s="5" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="G142" s="32" t="s">
-        <v>555</v>
+        <v>546</v>
       </c>
       <c r="H142" s="15" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
     </row>
     <row r="143" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5983,11 +5983,11 @@
         <v>1</v>
       </c>
       <c r="F143" s="5" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="G143" s="32"/>
       <c r="H143" s="15" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="144" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6001,17 +6001,17 @@
         <v>14</v>
       </c>
       <c r="D144" s="5" t="s">
-        <v>543</v>
+        <v>534</v>
       </c>
       <c r="E144" s="1">
         <v>1</v>
       </c>
       <c r="F144" s="5" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="G144" s="32"/>
       <c r="H144" s="15" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
     </row>
     <row r="145" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6025,11 +6025,11 @@
         <v>0</v>
       </c>
       <c r="F145" s="5" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="G145" s="32"/>
       <c r="H145" s="15" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
     </row>
     <row r="146" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6052,10 +6052,10 @@
         <v>200</v>
       </c>
       <c r="G146" s="32" t="s">
-        <v>555</v>
+        <v>546</v>
       </c>
       <c r="H146" s="15" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="147" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="G147" s="32"/>
       <c r="H147" s="15" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
     </row>
     <row r="148" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6093,11 +6093,11 @@
         <v>1</v>
       </c>
       <c r="F148" s="5" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="G148" s="32"/>
       <c r="H148" s="15" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
     </row>
     <row r="149" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6111,11 +6111,11 @@
         <v>0</v>
       </c>
       <c r="F149" s="5" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="G149" s="32"/>
       <c r="H149" s="15" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
     </row>
     <row r="150" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="G150" s="32"/>
       <c r="H150" s="15" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
     </row>
     <row r="151" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6157,7 +6157,7 @@
       </c>
       <c r="G151" s="32"/>
       <c r="H151" s="15" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
     </row>
     <row r="152" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="G152" s="32"/>
       <c r="H152" s="15" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
     </row>
     <row r="153" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6195,11 +6195,11 @@
         <v>0</v>
       </c>
       <c r="F153" s="5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="G153" s="32"/>
       <c r="H153" s="15" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
     </row>
     <row r="154" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6219,13 +6219,13 @@
         <v>0</v>
       </c>
       <c r="F154" s="5" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="G154" s="32" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="H154" s="15" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
     </row>
     <row r="155" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6239,11 +6239,11 @@
         <v>0</v>
       </c>
       <c r="F155" s="5" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="G155" s="32"/>
       <c r="H155" s="15" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
     </row>
     <row r="156" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="G156" s="32"/>
       <c r="H156" s="15" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
     </row>
     <row r="157" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6285,7 +6285,7 @@
       </c>
       <c r="G157" s="32"/>
       <c r="H157" s="15" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="158" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6305,11 +6305,11 @@
         <v>1</v>
       </c>
       <c r="F158" s="5" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="G158" s="32"/>
       <c r="H158" s="15" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
     </row>
     <row r="159" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
@@ -6323,11 +6323,11 @@
         <v>1</v>
       </c>
       <c r="F159" s="5" t="s">
-        <v>575</v>
+        <v>566</v>
       </c>
       <c r="G159" s="32"/>
       <c r="H159" s="15" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
     </row>
     <row r="160" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6347,13 +6347,13 @@
         <v>1</v>
       </c>
       <c r="F160" s="5" t="s">
-        <v>573</v>
+        <v>564</v>
       </c>
       <c r="G160" s="32" t="s">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="H160" s="15" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
     </row>
     <row r="161" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6367,11 +6367,11 @@
         <v>0</v>
       </c>
       <c r="F161" s="5" t="s">
-        <v>573</v>
+        <v>564</v>
       </c>
       <c r="G161" s="32"/>
       <c r="H161" s="15" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
     </row>
     <row r="162" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6391,13 +6391,13 @@
         <v>0</v>
       </c>
       <c r="F162" s="5" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="G162" s="32" t="s">
-        <v>560</v>
+        <v>551</v>
       </c>
       <c r="H162" s="15" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
     </row>
     <row r="163" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6411,11 +6411,11 @@
         <v>0</v>
       </c>
       <c r="F163" s="5" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="G163" s="32"/>
       <c r="H163" s="15" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
     </row>
     <row r="164" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6435,11 +6435,11 @@
         <v>0</v>
       </c>
       <c r="F164" s="5" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="G164" s="32"/>
       <c r="H164" s="15" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
     </row>
     <row r="165" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6453,11 +6453,11 @@
         <v>0</v>
       </c>
       <c r="F165" s="5" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="G165" s="32"/>
       <c r="H165" s="15" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
     </row>
     <row r="166" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6477,13 +6477,13 @@
         <v>1</v>
       </c>
       <c r="F166" s="5" t="s">
-        <v>258</v>
+        <v>656</v>
       </c>
       <c r="G166" s="32" t="s">
         <v>193</v>
       </c>
       <c r="H166" s="15" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
     </row>
     <row r="167" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6497,11 +6497,11 @@
         <v>0</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>258</v>
+        <v>656</v>
       </c>
       <c r="G167" s="32"/>
       <c r="H167" s="15" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
     </row>
     <row r="168" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6521,11 +6521,11 @@
         <v>1</v>
       </c>
       <c r="F168" s="5" t="s">
-        <v>255</v>
+        <v>657</v>
       </c>
       <c r="G168" s="32"/>
       <c r="H168" s="15" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
     </row>
     <row r="169" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6536,14 +6536,14 @@
         <v>116</v>
       </c>
       <c r="E169" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F169" s="5" t="s">
-        <v>256</v>
+        <v>658</v>
       </c>
       <c r="G169" s="32"/>
       <c r="H169" s="15" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
     </row>
     <row r="170" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6563,11 +6563,11 @@
         <v>2</v>
       </c>
       <c r="F170" s="5" t="s">
-        <v>632</v>
+        <v>621</v>
       </c>
       <c r="G170" s="32"/>
       <c r="H170" s="15" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
     </row>
     <row r="171" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6581,11 +6581,11 @@
         <v>2</v>
       </c>
       <c r="F171" s="5" t="s">
-        <v>633</v>
+        <v>622</v>
       </c>
       <c r="G171" s="32"/>
       <c r="H171" s="15" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
     </row>
     <row r="172" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6599,17 +6599,17 @@
         <v>14</v>
       </c>
       <c r="D172" s="5" t="s">
-        <v>545</v>
+        <v>536</v>
       </c>
       <c r="E172" s="1">
         <v>1</v>
       </c>
       <c r="F172" s="5" t="s">
-        <v>547</v>
+        <v>538</v>
       </c>
       <c r="G172" s="32"/>
       <c r="H172" s="15" t="s">
-        <v>546</v>
+        <v>537</v>
       </c>
     </row>
     <row r="173" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6617,17 +6617,17 @@
       <c r="B173" s="36"/>
       <c r="C173" s="43"/>
       <c r="D173" s="5" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="E173" s="1">
         <v>1</v>
       </c>
       <c r="F173" s="5" t="s">
-        <v>548</v>
+        <v>539</v>
       </c>
       <c r="G173" s="32"/>
       <c r="H173" s="15" t="s">
-        <v>546</v>
+        <v>537</v>
       </c>
     </row>
     <row r="174" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6647,13 +6647,13 @@
         <v>1</v>
       </c>
       <c r="F174" s="5" t="s">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="G174" s="32" t="s">
-        <v>595</v>
+        <v>584</v>
       </c>
       <c r="H174" s="15" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
     </row>
     <row r="175" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6667,11 +6667,11 @@
         <v>1</v>
       </c>
       <c r="F175" s="5" t="s">
-        <v>597</v>
+        <v>586</v>
       </c>
       <c r="G175" s="32"/>
       <c r="H175" s="15" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
     </row>
     <row r="176" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6691,13 +6691,13 @@
         <v>1</v>
       </c>
       <c r="F176" s="5" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="G176" s="32" t="s">
         <v>112</v>
       </c>
       <c r="H176" s="15" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
     </row>
     <row r="177" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6711,11 +6711,11 @@
         <v>1</v>
       </c>
       <c r="F177" s="5" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="G177" s="32"/>
       <c r="H177" s="15" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
     </row>
     <row r="178" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6729,17 +6729,17 @@
         <v>14</v>
       </c>
       <c r="D178" s="5" t="s">
-        <v>629</v>
+        <v>618</v>
       </c>
       <c r="E178" s="1">
         <v>1</v>
       </c>
       <c r="F178" s="5" t="s">
-        <v>628</v>
+        <v>617</v>
       </c>
       <c r="G178" s="32"/>
       <c r="H178" s="15" t="s">
-        <v>639</v>
+        <v>627</v>
       </c>
     </row>
     <row r="179" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6747,17 +6747,17 @@
       <c r="B179" s="35"/>
       <c r="C179" s="28"/>
       <c r="D179" s="5" t="s">
-        <v>630</v>
+        <v>619</v>
       </c>
       <c r="E179" s="1">
         <v>1</v>
       </c>
       <c r="F179" s="5" t="s">
-        <v>631</v>
+        <v>620</v>
       </c>
       <c r="G179" s="32"/>
       <c r="H179" s="15" t="s">
-        <v>640</v>
+        <v>628</v>
       </c>
     </row>
     <row r="180" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6777,11 +6777,11 @@
         <v>1</v>
       </c>
       <c r="F180" s="5" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="G180" s="32"/>
       <c r="H180" s="15" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
     </row>
     <row r="181" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6795,11 +6795,11 @@
         <v>1</v>
       </c>
       <c r="F181" s="5" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="G181" s="32"/>
       <c r="H181" s="15" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
     </row>
     <row r="182" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6823,7 +6823,7 @@
       </c>
       <c r="G182" s="32"/>
       <c r="H182" s="15" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
     </row>
     <row r="183" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="G183" s="32"/>
       <c r="H183" s="15" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="184" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6861,11 +6861,11 @@
         <v>3</v>
       </c>
       <c r="F184" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G184" s="32"/>
       <c r="H184" s="15" t="s">
-        <v>550</v>
+        <v>541</v>
       </c>
     </row>
     <row r="185" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6879,11 +6879,11 @@
         <v>2</v>
       </c>
       <c r="F185" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G185" s="32"/>
       <c r="H185" s="15" t="s">
-        <v>551</v>
+        <v>542</v>
       </c>
     </row>
     <row r="186" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6903,11 +6903,11 @@
         <v>3</v>
       </c>
       <c r="F186" s="5" t="s">
-        <v>662</v>
+        <v>646</v>
       </c>
       <c r="G186" s="32"/>
       <c r="H186" s="15" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
     </row>
     <row r="187" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6921,11 +6921,11 @@
         <v>2</v>
       </c>
       <c r="F187" s="5" t="s">
-        <v>662</v>
+        <v>646</v>
       </c>
       <c r="G187" s="32"/>
       <c r="H187" s="15" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
     </row>
     <row r="188" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6939,17 +6939,17 @@
         <v>14</v>
       </c>
       <c r="D188" s="5" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="E188" s="1">
         <v>0</v>
       </c>
       <c r="F188" s="5" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="G188" s="32"/>
       <c r="H188" s="15" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
     </row>
     <row r="189" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6957,17 +6957,17 @@
       <c r="B189" s="35"/>
       <c r="C189" s="37"/>
       <c r="D189" s="5" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="E189" s="1">
         <v>0</v>
       </c>
       <c r="F189" s="5" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="G189" s="32"/>
       <c r="H189" s="15" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
     </row>
     <row r="190" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6987,13 +6987,13 @@
         <v>0</v>
       </c>
       <c r="F190" s="5" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="G190" s="32" t="s">
-        <v>555</v>
+        <v>546</v>
       </c>
       <c r="H190" s="15" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
     </row>
     <row r="191" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7007,11 +7007,11 @@
         <v>0</v>
       </c>
       <c r="F191" s="5" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="G191" s="32"/>
       <c r="H191" s="15" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
     </row>
     <row r="192" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7031,11 +7031,11 @@
         <v>43</v>
       </c>
       <c r="F192" s="5" t="s">
-        <v>221</v>
+        <v>655</v>
       </c>
       <c r="G192" s="32"/>
       <c r="H192" s="15" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
     </row>
     <row r="193" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7049,11 +7049,11 @@
         <v>43</v>
       </c>
       <c r="F193" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G193" s="32"/>
       <c r="H193" s="15" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
     </row>
     <row r="194" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7073,13 +7073,13 @@
         <v>4</v>
       </c>
       <c r="F194" s="5" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="G194" s="32" t="s">
         <v>210</v>
       </c>
       <c r="H194" s="15" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
     </row>
     <row r="195" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7093,11 +7093,11 @@
         <v>4</v>
       </c>
       <c r="F195" s="5" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="G195" s="32"/>
       <c r="H195" s="15" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
     </row>
     <row r="196" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7117,13 +7117,13 @@
         <v>1</v>
       </c>
       <c r="F196" s="5" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="G196" s="32" t="s">
         <v>138</v>
       </c>
       <c r="H196" s="15" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
     </row>
     <row r="197" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7137,11 +7137,11 @@
         <v>1</v>
       </c>
       <c r="F197" s="5" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="G197" s="32"/>
       <c r="H197" s="15" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
     </row>
     <row r="198" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7161,13 +7161,13 @@
         <v>2</v>
       </c>
       <c r="F198" s="5" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="G198" s="32" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="H198" s="15" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
     </row>
     <row r="199" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7181,11 +7181,11 @@
         <v>1</v>
       </c>
       <c r="F199" s="5" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="G199" s="32"/>
       <c r="H199" s="15" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
     </row>
     <row r="200" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7211,7 +7211,7 @@
         <v>217</v>
       </c>
       <c r="H200" s="15" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
     </row>
     <row r="201" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="G201" s="32"/>
       <c r="H201" s="15" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
     </row>
     <row r="202" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7249,13 +7249,13 @@
         <v>2</v>
       </c>
       <c r="F202" s="5" t="s">
-        <v>562</v>
+        <v>553</v>
       </c>
       <c r="G202" s="32" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="H202" s="15" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
     </row>
     <row r="203" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7269,11 +7269,11 @@
         <v>2</v>
       </c>
       <c r="F203" s="5" t="s">
-        <v>563</v>
+        <v>554</v>
       </c>
       <c r="G203" s="32"/>
       <c r="H203" s="15" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
     </row>
     <row r="204" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7293,11 +7293,11 @@
         <v>1</v>
       </c>
       <c r="F204" s="5" t="s">
-        <v>593</v>
+        <v>582</v>
       </c>
       <c r="G204" s="32"/>
       <c r="H204" s="15" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
     </row>
     <row r="205" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7311,11 +7311,11 @@
         <v>1</v>
       </c>
       <c r="F205" s="5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G205" s="32"/>
       <c r="H205" s="15" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
     </row>
     <row r="206" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7335,11 +7335,11 @@
         <v>1</v>
       </c>
       <c r="F206" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G206" s="32"/>
       <c r="H206" s="15" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
     </row>
     <row r="207" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7353,11 +7353,11 @@
         <v>0</v>
       </c>
       <c r="F207" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G207" s="32"/>
       <c r="H207" s="15" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
     </row>
     <row r="208" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7377,13 +7377,13 @@
         <v>1</v>
       </c>
       <c r="F208" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G208" s="32" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H208" s="15" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
     </row>
     <row r="209" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7397,11 +7397,11 @@
         <v>1</v>
       </c>
       <c r="F209" s="5" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="G209" s="32"/>
       <c r="H209" s="15" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
     </row>
     <row r="210" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
@@ -7421,13 +7421,13 @@
         <v>1</v>
       </c>
       <c r="F210" s="5" t="s">
-        <v>613</v>
+        <v>602</v>
       </c>
       <c r="G210" s="32" t="s">
-        <v>583</v>
+        <v>574</v>
       </c>
       <c r="H210" s="15" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
     </row>
     <row r="211" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
@@ -7441,11 +7441,11 @@
         <v>1</v>
       </c>
       <c r="F211" s="5" t="s">
-        <v>614</v>
+        <v>603</v>
       </c>
       <c r="G211" s="32"/>
       <c r="H211" s="15" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
     </row>
     <row r="212" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7465,11 +7465,11 @@
         <v>1</v>
       </c>
       <c r="F212" s="5" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="G212" s="32"/>
       <c r="H212" s="15" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
     </row>
     <row r="213" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7483,11 +7483,11 @@
         <v>0</v>
       </c>
       <c r="F213" s="5" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="G213" s="32"/>
       <c r="H213" s="15" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
     </row>
     <row r="214" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7507,13 +7507,13 @@
         <v>2</v>
       </c>
       <c r="F214" s="5" t="s">
-        <v>554</v>
+        <v>545</v>
       </c>
       <c r="G214" s="32" t="s">
-        <v>586</v>
+        <v>577</v>
       </c>
       <c r="H214" s="15" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
     </row>
     <row r="215" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
@@ -7527,11 +7527,11 @@
         <v>1</v>
       </c>
       <c r="F215" s="5" t="s">
-        <v>561</v>
+        <v>552</v>
       </c>
       <c r="G215" s="32"/>
       <c r="H215" s="15" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
     </row>
     <row r="216" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
@@ -7551,13 +7551,13 @@
         <v>2</v>
       </c>
       <c r="F216" s="5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G216" s="32" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="H216" s="15" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
     </row>
     <row r="217" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
@@ -7571,11 +7571,11 @@
         <v>2</v>
       </c>
       <c r="F217" s="5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G217" s="32"/>
       <c r="H217" s="15" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
     </row>
     <row r="218" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="G218" s="32"/>
       <c r="H218" s="15" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
     </row>
     <row r="219" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
@@ -7617,7 +7617,7 @@
       </c>
       <c r="G219" s="32"/>
       <c r="H219" s="15" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
     </row>
     <row r="220" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
@@ -7641,7 +7641,7 @@
       </c>
       <c r="G220" s="32"/>
       <c r="H220" s="15" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
     </row>
     <row r="221" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
@@ -7659,7 +7659,7 @@
       </c>
       <c r="G221" s="32"/>
       <c r="H221" s="15" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
     </row>
     <row r="222" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
@@ -7679,13 +7679,13 @@
         <v>2</v>
       </c>
       <c r="F222" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G222" s="32" t="s">
-        <v>584</v>
+        <v>575</v>
       </c>
       <c r="H222" s="15" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
     </row>
     <row r="223" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
@@ -7699,11 +7699,11 @@
         <v>1</v>
       </c>
       <c r="F223" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G223" s="32"/>
       <c r="H223" s="15" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
     </row>
     <row r="224" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
@@ -7723,11 +7723,11 @@
         <v>3</v>
       </c>
       <c r="F224" s="5" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="G224" s="32"/>
       <c r="H224" s="15" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
     </row>
     <row r="225" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
@@ -7741,61 +7741,61 @@
         <v>3</v>
       </c>
       <c r="F225" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G225" s="32"/>
       <c r="H225" s="15" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A229" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A230" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A231" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A232" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A233" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A234" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A235" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A236" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A237" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="245" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A245" s="28" t="s">
-        <v>599</v>
+        <v>588</v>
       </c>
       <c r="B245" s="28"/>
       <c r="C245" s="28"/>
@@ -7810,7 +7810,7 @@
         <v>9</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="C246" s="29" t="s">
         <v>2</v>
@@ -7822,52 +7822,52 @@
         <v>3</v>
       </c>
       <c r="H246" s="1" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
     </row>
     <row r="247" spans="1:8" ht="100.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A247" s="18" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="B247" s="23" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="C247" s="25" t="s">
-        <v>608</v>
+        <v>597</v>
       </c>
       <c r="D247" s="26"/>
       <c r="E247" s="26"/>
       <c r="F247" s="27"/>
       <c r="G247" s="4" t="s">
-        <v>615</v>
+        <v>604</v>
       </c>
       <c r="H247" s="16" t="s">
-        <v>606</v>
+        <v>595</v>
       </c>
     </row>
     <row r="248" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A248" s="24" t="s">
-        <v>600</v>
+        <v>589</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="C248" s="25" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="D248" s="26"/>
       <c r="E248" s="26"/>
       <c r="F248" s="27"/>
       <c r="G248" s="4" t="s">
-        <v>603</v>
+        <v>592</v>
       </c>
       <c r="H248" s="16" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
     </row>
     <row r="253" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A253" s="28" t="s">
-        <v>601</v>
+        <v>590</v>
       </c>
       <c r="B253" s="28"/>
       <c r="C253" s="28"/>
@@ -7879,7 +7879,7 @@
     </row>
     <row r="254" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A254" s="28" t="s">
-        <v>602</v>
+        <v>591</v>
       </c>
       <c r="B254" s="28"/>
       <c r="C254" s="28"/>

--- a/src/main/resources/InesModResources/杀戮尖塔自制--伊内丝v0.2.xlsx
+++ b/src/main/resources/InesModResources/杀戮尖塔自制--伊内丝v0.2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\myMod\InesMod\InesMod\src\main\resources\InesModResources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA580072-45D6-4BD1-B98F-7912A089B7BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AE9E231-AB8E-4A70-A362-B8B82DF1E7B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{7A3E14A4-2175-4856-859A-887D335814F1}"/>
   </bookViews>
@@ -1938,10 +1938,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>需要测试影哨塞不下时是丢弃还是消耗。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>必须有1点情报才能打出。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2537,6 +2533,10 @@
   </si>
   <si>
     <t>抽3张牌。丢弃1张牌。此牌每被打出一次，抽牌数-1。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>影哨塞不下时会丢弃。（所以不会亏格挡）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3329,7 +3329,7 @@
       <c r="D10" s="30"/>
       <c r="E10" s="31"/>
       <c r="F10" s="9" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="G10" s="10"/>
       <c r="H10" s="17" t="s">
@@ -3349,7 +3349,7 @@
       <c r="D11" s="30"/>
       <c r="E11" s="31"/>
       <c r="F11" s="9" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="G11" s="10"/>
       <c r="H11" s="17" t="s">
@@ -3459,7 +3459,7 @@
         <v>461</v>
       </c>
       <c r="C20" s="25" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D20" s="26"/>
       <c r="E20" s="26"/>
@@ -3479,7 +3479,7 @@
         <v>461</v>
       </c>
       <c r="C21" s="25" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="D21" s="26"/>
       <c r="E21" s="26"/>
@@ -3519,13 +3519,13 @@
         <v>461</v>
       </c>
       <c r="C23" s="25" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D23" s="26"/>
       <c r="E23" s="26"/>
       <c r="F23" s="27"/>
       <c r="G23" s="4" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H23" s="16" t="s">
         <v>449</v>
@@ -3545,7 +3545,7 @@
       <c r="E24" s="26"/>
       <c r="F24" s="27"/>
       <c r="G24" s="5" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H24" s="16" t="s">
         <v>486</v>
@@ -3573,20 +3573,20 @@
     </row>
     <row r="26" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="20" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>463</v>
       </c>
       <c r="C26" s="25" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D26" s="26"/>
       <c r="E26" s="26"/>
       <c r="F26" s="27"/>
       <c r="G26" s="4"/>
       <c r="H26" s="16" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
@@ -3603,7 +3603,7 @@
       <c r="E27" s="26"/>
       <c r="F27" s="27"/>
       <c r="G27" s="4" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H27" s="16" t="s">
         <v>472</v>
@@ -3670,7 +3670,7 @@
         <v>461</v>
       </c>
       <c r="C34" s="25" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="D34" s="26"/>
       <c r="E34" s="26"/>
@@ -3688,7 +3688,7 @@
         <v>461</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D35" s="26"/>
       <c r="E35" s="26"/>
@@ -3700,20 +3700,20 @@
     </row>
     <row r="36" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="19" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>461</v>
       </c>
       <c r="C36" s="25" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="D36" s="26"/>
       <c r="E36" s="26"/>
       <c r="F36" s="27"/>
       <c r="G36" s="5"/>
       <c r="H36" s="16" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="37" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
@@ -3724,7 +3724,7 @@
         <v>461</v>
       </c>
       <c r="C37" s="25" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D37" s="26"/>
       <c r="E37" s="26"/>
@@ -3813,7 +3813,7 @@
     </row>
     <row r="45" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="F45" s="3" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H45" s="2"/>
     </row>
@@ -4107,7 +4107,7 @@
         <v>1</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="G59" s="32"/>
       <c r="H59" s="15" t="s">
@@ -4135,7 +4135,7 @@
         <v>0</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="G60" s="32"/>
       <c r="H60" s="15" t="s">
@@ -4157,7 +4157,7 @@
         <v>0</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="G61" s="32"/>
       <c r="H61" s="15" t="s">
@@ -4235,10 +4235,10 @@
         <v>0</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="G64" s="32" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H64" s="15" t="s">
         <v>305</v>
@@ -4259,7 +4259,7 @@
         <v>0</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="G65" s="32"/>
       <c r="H65" s="15" t="s">
@@ -4287,10 +4287,10 @@
         <v>1</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="G66" s="32" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H66" s="15" t="s">
         <v>306</v>
@@ -4307,7 +4307,7 @@
         <v>1</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="G67" s="32"/>
       <c r="H67" s="15" t="s">
@@ -4331,10 +4331,10 @@
         <v>1</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="G68" s="32" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H68" s="15" t="s">
         <v>307</v>
@@ -4355,7 +4355,7 @@
         <v>1</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="G69" s="32"/>
       <c r="H69" s="15" t="s">
@@ -4383,10 +4383,10 @@
         <v>0</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="G70" s="32" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H70" s="15" t="s">
         <v>308</v>
@@ -4407,7 +4407,7 @@
         <v>0</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="G71" s="32"/>
       <c r="H71" s="15" t="s">
@@ -4435,10 +4435,10 @@
         <v>0</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="G72" s="32" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H72" s="15" t="s">
         <v>309</v>
@@ -4459,7 +4459,7 @@
         <v>0</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="G73" s="32"/>
       <c r="H73" s="15" t="s">
@@ -4487,11 +4487,11 @@
         <v>0</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="G74" s="32"/>
       <c r="H74" s="15" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="I74" s="2"/>
       <c r="J74" s="2"/>
@@ -4509,11 +4509,11 @@
         <v>0</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="G75" s="32"/>
       <c r="H75" s="15" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="I75" s="2"/>
       <c r="J75" s="2"/>
@@ -4540,7 +4540,7 @@
         <v>474</v>
       </c>
       <c r="G76" s="32" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H76" s="15" t="s">
         <v>310</v>
@@ -4585,10 +4585,10 @@
         <v>2</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="G78" s="32" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H78" s="15" t="s">
         <v>311</v>
@@ -4605,7 +4605,7 @@
         <v>2</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="G79" s="32"/>
       <c r="H79" s="15" t="s">
@@ -4629,13 +4629,13 @@
         <v>2</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="G80" s="32" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H80" s="15" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="81" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4649,11 +4649,11 @@
         <v>2</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="G81" s="32"/>
       <c r="H81" s="15" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4673,10 +4673,10 @@
         <v>1</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="G82" s="32" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H82" s="15" t="s">
         <v>312</v>
@@ -4761,7 +4761,7 @@
         <v>1</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="G86" s="32"/>
       <c r="H86" s="15" t="s">
@@ -4779,7 +4779,7 @@
         <v>1</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="G87" s="32"/>
       <c r="H87" s="15" t="s">
@@ -4847,10 +4847,10 @@
         <v>0</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="G90" s="32" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H90" s="15" t="s">
         <v>315</v>
@@ -4867,7 +4867,7 @@
         <v>0</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="G91" s="32"/>
       <c r="H91" s="15" t="s">
@@ -4935,7 +4935,7 @@
         <v>2</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="G94" s="32" t="s">
         <v>278</v>
@@ -4955,7 +4955,7 @@
         <v>2</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="G95" s="32"/>
       <c r="H95" s="15" t="s">
@@ -4979,7 +4979,7 @@
         <v>43</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="G96" s="32" t="s">
         <v>199</v>
@@ -4999,7 +4999,7 @@
         <v>43</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="G97" s="32"/>
       <c r="H97" s="15" t="s">
@@ -5023,7 +5023,7 @@
         <v>0</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="G98" s="32"/>
       <c r="H98" s="15" t="s">
@@ -5041,7 +5041,7 @@
         <v>0</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="G99" s="32"/>
       <c r="H99" s="15" t="s">
@@ -5065,7 +5065,7 @@
         <v>1</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="G100" s="32"/>
       <c r="H100" s="15" t="s">
@@ -5083,7 +5083,7 @@
         <v>1</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="G101" s="32"/>
       <c r="H101" s="15" t="s">
@@ -5107,7 +5107,7 @@
         <v>1</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="G102" s="32"/>
       <c r="H102" s="15" t="s">
@@ -5125,7 +5125,7 @@
         <v>1</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="G103" s="32"/>
       <c r="H103" s="15" t="s">
@@ -5149,7 +5149,7 @@
         <v>1</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="G104" s="32"/>
       <c r="H104" s="15" t="s">
@@ -5167,7 +5167,7 @@
         <v>1</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="G105" s="32"/>
       <c r="H105" s="15" t="s">
@@ -5235,7 +5235,7 @@
         <v>1</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="G108" s="32" t="s">
         <v>218</v>
@@ -5255,7 +5255,7 @@
         <v>1</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="G109" s="32"/>
       <c r="H109" s="15" t="s">
@@ -5279,7 +5279,7 @@
         <v>1</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="G110" s="48" t="s">
         <v>257</v>
@@ -5299,7 +5299,7 @@
         <v>1</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="G111" s="49"/>
       <c r="H111" s="15" t="s">
@@ -5365,7 +5365,7 @@
         <v>1</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="G114" s="32"/>
       <c r="H114" s="15" t="s">
@@ -5383,7 +5383,7 @@
         <v>1</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="G115" s="32"/>
       <c r="H115" s="15" t="s">
@@ -5427,7 +5427,7 @@
         <v>0</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="G117" s="32"/>
       <c r="H117" s="15" t="s">
@@ -5457,7 +5457,7 @@
         <v>218</v>
       </c>
       <c r="H118" s="15" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="119" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5471,7 +5471,7 @@
         <v>0</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="G119" s="32"/>
       <c r="H119" s="15" t="s">
@@ -5495,7 +5495,7 @@
         <v>0</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="G120" s="32" t="s">
         <v>246</v>
@@ -5515,7 +5515,7 @@
         <v>0</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="G121" s="32"/>
       <c r="H121" s="15" t="s">
@@ -5626,10 +5626,10 @@
         <v>223</v>
       </c>
       <c r="G126" s="32" t="s">
-        <v>519</v>
+        <v>664</v>
       </c>
       <c r="H126" s="15" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="127" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5643,11 +5643,11 @@
         <v>0</v>
       </c>
       <c r="F127" s="5" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="G127" s="32"/>
       <c r="H127" s="15" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="128" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5709,7 +5709,7 @@
         <v>1</v>
       </c>
       <c r="F130" s="5" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="G130" s="32"/>
       <c r="H130" s="15" t="s">
@@ -5727,7 +5727,7 @@
         <v>1</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="G131" s="32"/>
       <c r="H131" s="15" t="s">
@@ -5751,11 +5751,11 @@
         <v>0</v>
       </c>
       <c r="F132" s="5" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="G132" s="32"/>
       <c r="H132" s="15" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="133" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5769,11 +5769,11 @@
         <v>0</v>
       </c>
       <c r="F133" s="5" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="G133" s="32"/>
       <c r="H133" s="15" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="134" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5787,17 +5787,17 @@
         <v>14</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="E134" s="1">
         <v>2</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="G134" s="32"/>
       <c r="H134" s="15" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="135" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5805,17 +5805,17 @@
       <c r="B135" s="36"/>
       <c r="C135" s="28"/>
       <c r="D135" s="5" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="E135" s="1">
         <v>2</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="G135" s="32"/>
       <c r="H135" s="15" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="136" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5925,7 +5925,7 @@
         <v>211</v>
       </c>
       <c r="H140" s="15" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="141" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5966,7 +5966,7 @@
         <v>480</v>
       </c>
       <c r="G142" s="32" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H142" s="15" t="s">
         <v>331</v>
@@ -5991,7 +5991,7 @@
       </c>
     </row>
     <row r="144" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A144" s="33">
+      <c r="A144" s="41">
         <v>48</v>
       </c>
       <c r="B144" s="36" t="s">
@@ -6001,7 +6001,7 @@
         <v>14</v>
       </c>
       <c r="D144" s="5" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E144" s="1">
         <v>1</v>
@@ -6015,7 +6015,7 @@
       </c>
     </row>
     <row r="145" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A145" s="34"/>
+      <c r="A145" s="42"/>
       <c r="B145" s="36"/>
       <c r="C145" s="28"/>
       <c r="D145" s="5" t="s">
@@ -6052,7 +6052,7 @@
         <v>200</v>
       </c>
       <c r="G146" s="32" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H146" s="15" t="s">
         <v>429</v>
@@ -6161,7 +6161,7 @@
       </c>
     </row>
     <row r="152" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A152" s="33">
+      <c r="A152" s="41">
         <v>52</v>
       </c>
       <c r="B152" s="36" t="s">
@@ -6185,7 +6185,7 @@
       </c>
     </row>
     <row r="153" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A153" s="34"/>
+      <c r="A153" s="42"/>
       <c r="B153" s="36"/>
       <c r="C153" s="28"/>
       <c r="D153" s="5" t="s">
@@ -6222,7 +6222,7 @@
         <v>255</v>
       </c>
       <c r="G154" s="32" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H154" s="15" t="s">
         <v>458</v>
@@ -6305,7 +6305,7 @@
         <v>1</v>
       </c>
       <c r="F158" s="5" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="G158" s="32"/>
       <c r="H158" s="15" t="s">
@@ -6323,7 +6323,7 @@
         <v>1</v>
       </c>
       <c r="F159" s="5" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G159" s="32"/>
       <c r="H159" s="15" t="s">
@@ -6347,10 +6347,10 @@
         <v>1</v>
       </c>
       <c r="F160" s="5" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="G160" s="32" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H160" s="15" t="s">
         <v>339</v>
@@ -6367,7 +6367,7 @@
         <v>0</v>
       </c>
       <c r="F161" s="5" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="G161" s="32"/>
       <c r="H161" s="15" t="s">
@@ -6394,7 +6394,7 @@
         <v>280</v>
       </c>
       <c r="G162" s="32" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H162" s="15" t="s">
         <v>340</v>
@@ -6477,7 +6477,7 @@
         <v>1</v>
       </c>
       <c r="F166" s="5" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="G166" s="32" t="s">
         <v>193</v>
@@ -6497,7 +6497,7 @@
         <v>0</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="G167" s="32"/>
       <c r="H167" s="15" t="s">
@@ -6521,7 +6521,7 @@
         <v>1</v>
       </c>
       <c r="F168" s="5" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G168" s="32"/>
       <c r="H168" s="15" t="s">
@@ -6539,7 +6539,7 @@
         <v>0</v>
       </c>
       <c r="F169" s="5" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="G169" s="32"/>
       <c r="H169" s="15" t="s">
@@ -6563,7 +6563,7 @@
         <v>2</v>
       </c>
       <c r="F170" s="5" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="G170" s="32"/>
       <c r="H170" s="15" t="s">
@@ -6581,7 +6581,7 @@
         <v>2</v>
       </c>
       <c r="F171" s="5" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="G171" s="32"/>
       <c r="H171" s="15" t="s">
@@ -6589,7 +6589,7 @@
       </c>
     </row>
     <row r="172" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A172" s="33">
+      <c r="A172" s="41">
         <v>62</v>
       </c>
       <c r="B172" s="36" t="s">
@@ -6599,35 +6599,35 @@
         <v>14</v>
       </c>
       <c r="D172" s="5" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="E172" s="1">
         <v>1</v>
       </c>
       <c r="F172" s="5" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="G172" s="32"/>
       <c r="H172" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="173" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A173" s="34"/>
+      <c r="A173" s="42"/>
       <c r="B173" s="36"/>
       <c r="C173" s="43"/>
       <c r="D173" s="5" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E173" s="1">
         <v>1</v>
       </c>
       <c r="F173" s="5" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="G173" s="32"/>
       <c r="H173" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="174" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6647,10 +6647,10 @@
         <v>1</v>
       </c>
       <c r="F174" s="5" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="G174" s="32" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H174" s="15" t="s">
         <v>344</v>
@@ -6667,7 +6667,7 @@
         <v>1</v>
       </c>
       <c r="F175" s="5" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="G175" s="32"/>
       <c r="H175" s="15" t="s">
@@ -6729,17 +6729,17 @@
         <v>14</v>
       </c>
       <c r="D178" s="5" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="E178" s="1">
         <v>1</v>
       </c>
       <c r="F178" s="5" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="G178" s="32"/>
       <c r="H178" s="15" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="179" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6747,17 +6747,17 @@
       <c r="B179" s="35"/>
       <c r="C179" s="28"/>
       <c r="D179" s="5" t="s">
+        <v>618</v>
+      </c>
+      <c r="E179" s="1">
+        <v>1</v>
+      </c>
+      <c r="F179" s="5" t="s">
         <v>619</v>
-      </c>
-      <c r="E179" s="1">
-        <v>1</v>
-      </c>
-      <c r="F179" s="5" t="s">
-        <v>620</v>
       </c>
       <c r="G179" s="32"/>
       <c r="H179" s="15" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="180" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6865,7 +6865,7 @@
       </c>
       <c r="G184" s="32"/>
       <c r="H184" s="15" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="185" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6883,7 +6883,7 @@
       </c>
       <c r="G185" s="32"/>
       <c r="H185" s="15" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="186" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6903,7 +6903,7 @@
         <v>3</v>
       </c>
       <c r="F186" s="5" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="G186" s="32"/>
       <c r="H186" s="15" t="s">
@@ -6921,7 +6921,7 @@
         <v>2</v>
       </c>
       <c r="F187" s="5" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="G187" s="32"/>
       <c r="H187" s="15" t="s">
@@ -6990,7 +6990,7 @@
         <v>258</v>
       </c>
       <c r="G190" s="32" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H190" s="15" t="s">
         <v>348</v>
@@ -7031,7 +7031,7 @@
         <v>43</v>
       </c>
       <c r="F192" s="5" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="G192" s="32"/>
       <c r="H192" s="15" t="s">
@@ -7164,7 +7164,7 @@
         <v>286</v>
       </c>
       <c r="G198" s="32" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H198" s="15" t="s">
         <v>437</v>
@@ -7249,10 +7249,10 @@
         <v>2</v>
       </c>
       <c r="F202" s="5" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="G202" s="32" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H202" s="15" t="s">
         <v>352</v>
@@ -7269,7 +7269,7 @@
         <v>2</v>
       </c>
       <c r="F203" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="G203" s="32"/>
       <c r="H203" s="15" t="s">
@@ -7293,7 +7293,7 @@
         <v>1</v>
       </c>
       <c r="F204" s="5" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G204" s="32"/>
       <c r="H204" s="15" t="s">
@@ -7397,7 +7397,7 @@
         <v>1</v>
       </c>
       <c r="F209" s="5" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="G209" s="32"/>
       <c r="H209" s="15" t="s">
@@ -7421,10 +7421,10 @@
         <v>1</v>
       </c>
       <c r="F210" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G210" s="32" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H210" s="15" t="s">
         <v>357</v>
@@ -7441,7 +7441,7 @@
         <v>1</v>
       </c>
       <c r="F211" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G211" s="32"/>
       <c r="H211" s="15" t="s">
@@ -7507,10 +7507,10 @@
         <v>2</v>
       </c>
       <c r="F214" s="5" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="G214" s="32" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H214" s="15" t="s">
         <v>355</v>
@@ -7527,7 +7527,7 @@
         <v>1</v>
       </c>
       <c r="F215" s="5" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G215" s="32"/>
       <c r="H215" s="15" t="s">
@@ -7682,7 +7682,7 @@
         <v>247</v>
       </c>
       <c r="G222" s="32" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H222" s="15" t="s">
         <v>359</v>
@@ -7795,7 +7795,7 @@
     </row>
     <row r="245" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A245" s="28" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B245" s="28"/>
       <c r="C245" s="28"/>
@@ -7827,47 +7827,47 @@
     </row>
     <row r="247" spans="1:8" ht="100.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A247" s="18" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B247" s="23" t="s">
         <v>461</v>
       </c>
       <c r="C247" s="25" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D247" s="26"/>
       <c r="E247" s="26"/>
       <c r="F247" s="27"/>
       <c r="G247" s="4" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H247" s="16" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="248" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A248" s="24" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B248" s="1" t="s">
         <v>461</v>
       </c>
       <c r="C248" s="25" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D248" s="26"/>
       <c r="E248" s="26"/>
       <c r="F248" s="27"/>
       <c r="G248" s="4" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H248" s="16" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="253" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A253" s="28" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B253" s="28"/>
       <c r="C253" s="28"/>
@@ -7879,7 +7879,7 @@
     </row>
     <row r="254" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A254" s="28" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B254" s="28"/>
       <c r="C254" s="28"/>

--- a/src/main/resources/InesModResources/杀戮尖塔自制--伊内丝v0.2.xlsx
+++ b/src/main/resources/InesModResources/杀戮尖塔自制--伊内丝v0.2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\myMod\InesMod\InesMod\src\main\resources\InesModResources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AE9E231-AB8E-4A70-A362-B8B82DF1E7B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F2C5F12-C203-49A8-B5DA-14D9ABBE8CB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{7A3E14A4-2175-4856-859A-887D335814F1}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="916" uniqueCount="665">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="666">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -716,10 +716,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>获得1层隐匿。消耗。虚无。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>时间差</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -994,14 +990,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>回复12点生命。消耗。虚无。这张牌每被打出1次，效果永久-1。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回复12点生命。消耗。这张牌每被打出1次，效果永久-1。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>下一次出牌时，将其一张耗能为0的复制品加入抽牌堆。消耗。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1173,10 +1161,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Darkness in Night</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Lone Return</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1567,10 +1551,6 @@
   </si>
   <si>
     <t>Shadow Ambush+</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Darkness in Night+</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1834,14 +1814,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>获得11点格挡和1点能量。本回合结束时保留所有影哨。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>获得14点格挡和1点能量。本回合结束时保留所有影哨。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>造成4点伤害。将偷取层数设置为1。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2204,10 +2176,6 @@
   </si>
   <si>
     <t>参考转经轮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>本次战斗后额外掉落一次卡牌奖励。消耗。虚无。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2343,10 +2311,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>潜伏。每次打出攻击牌，手牌中随机攻击牌在本场战斗中耗能-1。虚无。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>一个接一个</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2367,176 +2331,217 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>从卡牌中获得的格挡提升50%，但打出攻击牌后会消耗1张影哨。回合结束时，失去1层隐匿并获得1层虚影。
+    <t>自动打出。对所有敌人造成14点伤害2次。若无法自动打出则消耗。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>此牌加入手牌后，立即尝试消耗能量打出。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动打出。对所有敌人造成12点伤害2次。若无法自动打出则消耗。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>One by One</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>One by One+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>致命契机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>致命契机+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Deadly Opportunity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Deadly Opportunity+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>潜伏。攻击如果消耗了偷取，给予1层易伤。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>潜伏。攻击如果消耗了偷取，给予2层易伤。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ad Hoc Strategy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>此牌可消耗多层偷取。层数不足则全部消耗。研究药瓶动画</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Break the Shadow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Break the Shadow+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Veiled in Sight </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Veiled in Sight +</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对所有敌人造成9点伤害。获得1层隐匿。本回合你无法再打出攻击牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对所有敌人造成12点伤害。获得1层隐匿。本回合你无法再打出攻击牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当前所有手牌在本回合的耗能-2。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动打出。你打出的下2张攻击牌耗能变为0。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动打出。你打出的下3张攻击牌耗能变为0。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成10点伤害。本回合内，在隐匿下打出攻击牌改为丢弃影哨。保留。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成9点伤害。本回合内，在隐匿下打出攻击牌改为丢弃影哨。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动打出。获得10点格挡。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动打出。获得14点格挡。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>下一次丢弃牌时，将其立即打出一次。消耗。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本回合内，每抽1张牌可选择1张手牌丢弃。抽2张牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本回合内，每抽1张牌可选择1张手牌丢弃。抽3张牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得6点格挡。选择任意张手牌加入抽牌堆，丢弃其它所有手牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得8点格挡。选择任意张手牌加入抽牌堆，丢弃其它所有手牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>抽3张牌。丢弃1张牌。此牌每进入弃牌堆一次，抽牌数-1。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>抽3张牌。丢弃1张牌。此牌每被打出一次，抽牌数-1。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>影哨塞不下时会丢弃。（所以不会亏格挡）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>从卡牌中获得的格挡提升25%，但打出攻击牌后会消耗1张影哨。回合结束时，失去1层隐匿并获得1层虚影。
 虚影可抵挡一次攻击伤害或在回合开始时转为1点能量。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>自动打出。对所有敌人造成14点伤害2次。若无法自动打出则消耗。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>此牌加入手牌后，立即尝试消耗能量打出。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自动打出。对所有敌人造成12点伤害2次。若无法自动打出则消耗。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>One by One</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>One by One+</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>致命契机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>致命契机+</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>潜伏。下一张打出的攻击牌造成2倍伤害，随后失去所有格挡并结束你的回合。虚无。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Deadly Opportunity</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Deadly Opportunity+</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>潜伏。下一张打出的攻击牌造成2倍伤害，随后失去一半格挡并结束你的回合。虚无。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>潜伏。攻击如果消耗了偷取，给予1层易伤。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>潜伏。攻击如果消耗了偷取，给予2层易伤。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ad Hoc Strategy</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>此牌可消耗多层偷取。层数不足则全部消耗。研究药瓶动画</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Break the Shadow</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Break the Shadow+</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Veiled in Sight </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Veiled in Sight +</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>对所有敌人造成9点伤害。获得1层隐匿。本回合你无法再打出攻击牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>对所有敌人造成12点伤害。获得1层隐匿。本回合你无法再打出攻击牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>从卡牌中获得的格挡提升50%，但打出攻击牌后会消耗影哨。回合结束时，失去1层隐匿并获得1层虚影。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>当前所有手牌在本回合的耗能-2。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自动打出。你打出的下2张攻击牌耗能变为0。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自动打出。你打出的下3张攻击牌耗能变为0。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>造成10点伤害。本回合内，在隐匿下打出攻击牌改为丢弃影哨。保留。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>造成9点伤害。本回合内，在隐匿下打出攻击牌改为丢弃影哨。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>替换无锋绣针。你的回合开始时，获得2层偷取。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>战斗开始时，获得4层偷取。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自动打出。获得10点格挡。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自动打出。获得14点格挡。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>获得X层隐匿。消耗。虚无。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>下一次丢弃牌时，将其立即打出一次。消耗。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>本回合内，每抽1张牌可选择1张手牌丢弃。抽2张牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>本回合内，每抽1张牌可选择1张手牌丢弃。抽3张牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>获得6点格挡。选择任意张手牌加入抽牌堆，丢弃其它所有手牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>获得8点格挡。选择任意张手牌加入抽牌堆，丢弃其它所有手牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>获得等同于敌人数量的偷取。抽1张牌。在弃牌堆放入一张此牌的复制品。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>获得等同于敌人数量+1的偷取。抽1张牌。在弃牌堆放入一张此牌的复制品。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>抽3张牌。丢弃1张牌。此牌每进入弃牌堆一次，抽牌数-1。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>抽3张牌。丢弃1张牌。此牌每被打出一次，抽牌数-1。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>影哨塞不下时会丢弃。（所以不会亏格挡）</t>
+    <t>从卡牌中获得的格挡提升25%，但打出攻击牌后会消耗影哨。回合结束时，失去1层隐匿并获得1层虚影。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斗开始时，获得3层偷取。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>替换无锋绣针。战斗开始时，获得2层偷取。后续每个回合开始时，获得1层偷取。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得等同于敌人数量的偷取。在弃牌堆放入一张此牌的复制品。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得等同于敌人数量+1的偷取。在弃牌堆放入一张此牌的复制品。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得12点格挡和1点能量。本回合结束时保留所有影哨。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得9点格挡和1点能量。本回合结束时保留所有影哨。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Murky Night</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Murky Night+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果打出自己不会触发
+如果另一张牌打出时丢弃/消耗了此牌，此牌依然会触发</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>虚无。获得1层隐匿。消耗。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>虚无。本次战斗后额外掉落一次卡牌奖励。消耗。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>虚无。潜伏。每次打出攻击牌，手牌中随机攻击牌在本场战斗中耗能-1。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>虚无。获得X层隐匿。消耗。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>虚无。回复12点生命。这张牌每被打出1次，效果永久-1。消耗。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回复12点生命。这张牌每被打出1次，效果永久-1。消耗。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>下一张打出的攻击牌造成2倍伤害，随后失去所有格挡并结束你的回合。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>下一张打出的攻击牌造成2倍伤害，随后失去一半格挡并结束你的回合。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2824,6 +2829,27 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2835,46 +2861,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2883,16 +2873,31 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3228,10 +3233,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="28" t="s">
-        <v>293</v>
-      </c>
-      <c r="B1" s="28"/>
+      <c r="A1" s="29" t="s">
+        <v>290</v>
+      </c>
+      <c r="B1" s="29"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -3239,10 +3244,10 @@
     </row>
     <row r="2" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="7" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="12"/>
@@ -3253,10 +3258,10 @@
     </row>
     <row r="3" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -3283,29 +3288,29 @@
       <c r="B6" s="2"/>
     </row>
     <row r="8" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="36" t="s">
         <v>105</v>
       </c>
-      <c r="B8" s="30"/>
-      <c r="C8" s="30"/>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="30"/>
-      <c r="H8" s="31"/>
+      <c r="B8" s="37"/>
+      <c r="C8" s="37"/>
+      <c r="D8" s="37"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="38"/>
     </row>
     <row r="9" spans="1:8" ht="25.7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C9" s="36" t="s">
         <v>229</v>
       </c>
-      <c r="C9" s="29" t="s">
-        <v>230</v>
-      </c>
-      <c r="D9" s="30"/>
-      <c r="E9" s="31"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="38"/>
       <c r="F9" s="8" t="s">
         <v>2</v>
       </c>
@@ -3313,7 +3318,7 @@
         <v>3</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
@@ -3323,132 +3328,132 @@
       <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="30" t="s">
-        <v>232</v>
-      </c>
-      <c r="D10" s="30"/>
-      <c r="E10" s="31"/>
+      <c r="C10" s="37" t="s">
+        <v>231</v>
+      </c>
+      <c r="D10" s="37"/>
+      <c r="E10" s="38"/>
       <c r="F10" s="9" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="G10" s="10"/>
       <c r="H10" s="17" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="C11" s="29" t="s">
-        <v>236</v>
-      </c>
-      <c r="D11" s="30"/>
-      <c r="E11" s="31"/>
+        <v>247</v>
+      </c>
+      <c r="C11" s="36" t="s">
+        <v>235</v>
+      </c>
+      <c r="D11" s="37"/>
+      <c r="E11" s="38"/>
       <c r="F11" s="9" t="s">
         <v>650</v>
       </c>
       <c r="G11" s="10"/>
       <c r="H11" s="17" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="C12" s="29" t="s">
-        <v>471</v>
-      </c>
-      <c r="D12" s="30"/>
-      <c r="E12" s="31"/>
+        <v>247</v>
+      </c>
+      <c r="C12" s="36" t="s">
+        <v>466</v>
+      </c>
+      <c r="D12" s="37"/>
+      <c r="E12" s="38"/>
       <c r="F12" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G12" s="10"/>
       <c r="H12" s="17" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>447</v>
+      </c>
+      <c r="D13" s="37"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="9" t="s">
         <v>224</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="C13" s="25" t="s">
-        <v>452</v>
-      </c>
-      <c r="D13" s="30"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="9" t="s">
-        <v>225</v>
       </c>
       <c r="G13" s="10"/>
       <c r="H13" s="17" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="C14" s="30" t="s">
-        <v>289</v>
-      </c>
-      <c r="D14" s="30"/>
-      <c r="E14" s="31"/>
+        <v>230</v>
+      </c>
+      <c r="C14" s="37" t="s">
+        <v>286</v>
+      </c>
+      <c r="D14" s="37"/>
+      <c r="E14" s="38"/>
       <c r="F14" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G14" s="10"/>
       <c r="H14" s="17" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="16" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="17" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="28" t="s">
+      <c r="A18" s="29" t="s">
         <v>86</v>
       </c>
-      <c r="B18" s="28"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="28"/>
+      <c r="B18" s="29"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="29"/>
+      <c r="G18" s="29"/>
+      <c r="H18" s="29"/>
     </row>
     <row r="19" spans="1:8" ht="25.7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="C19" s="29" t="s">
+        <v>457</v>
+      </c>
+      <c r="C19" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="31"/>
+      <c r="D19" s="37"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="38"/>
       <c r="G19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
@@ -3456,192 +3461,192 @@
         <v>8</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="C20" s="25" t="s">
-        <v>582</v>
+        <v>575</v>
       </c>
       <c r="D20" s="26"/>
       <c r="E20" s="26"/>
       <c r="F20" s="27"/>
       <c r="G20" s="5" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
     </row>
     <row r="21" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="19" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="C21" s="25" t="s">
-        <v>622</v>
+        <v>647</v>
       </c>
       <c r="D21" s="26"/>
       <c r="E21" s="26"/>
       <c r="F21" s="27"/>
       <c r="G21" s="5" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
     </row>
     <row r="22" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="19" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="C22" s="25" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="D22" s="26"/>
       <c r="E22" s="26"/>
       <c r="F22" s="27"/>
       <c r="G22" s="5" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
     </row>
     <row r="23" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="19" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="C23" s="25" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="D23" s="26"/>
       <c r="E23" s="26"/>
       <c r="F23" s="27"/>
       <c r="G23" s="4" t="s">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="19" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="C24" s="25" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="D24" s="26"/>
       <c r="E24" s="26"/>
       <c r="F24" s="27"/>
       <c r="G24" s="5" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="20" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="C25" s="25" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="D25" s="26"/>
       <c r="E25" s="26"/>
       <c r="F25" s="27"/>
       <c r="G25" s="5" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="20" t="s">
-        <v>578</v>
+        <v>571</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="C26" s="25" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="D26" s="26"/>
       <c r="E26" s="26"/>
       <c r="F26" s="27"/>
       <c r="G26" s="4"/>
       <c r="H26" s="16" t="s">
-        <v>580</v>
+        <v>573</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="1" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="C27" s="25" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="D27" s="26"/>
       <c r="E27" s="26"/>
       <c r="F27" s="27"/>
       <c r="G27" s="4" t="s">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="H27" s="16" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="29" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="1:8" ht="21.7" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="31" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="28" t="s">
-        <v>502</v>
-      </c>
-      <c r="B31" s="28"/>
-      <c r="C31" s="28"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="28"/>
-      <c r="H31" s="28"/>
+      <c r="A31" s="29" t="s">
+        <v>495</v>
+      </c>
+      <c r="B31" s="29"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="29"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="29"/>
+      <c r="H31" s="29"/>
     </row>
     <row r="32" spans="1:8" ht="25.7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="C32" s="29" t="s">
+        <v>457</v>
+      </c>
+      <c r="C32" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="D32" s="30"/>
-      <c r="E32" s="30"/>
-      <c r="F32" s="31"/>
+      <c r="D32" s="37"/>
+      <c r="E32" s="37"/>
+      <c r="F32" s="38"/>
       <c r="G32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
@@ -3649,89 +3654,89 @@
         <v>8</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="C33" s="25" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="D33" s="26"/>
       <c r="E33" s="26"/>
       <c r="F33" s="27"/>
       <c r="G33" s="5"/>
       <c r="H33" s="16" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
     </row>
     <row r="34" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="19" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="C34" s="25" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="D34" s="26"/>
       <c r="E34" s="26"/>
       <c r="F34" s="27"/>
       <c r="G34" s="5"/>
       <c r="H34" s="16" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
     </row>
     <row r="35" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="19" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="D35" s="26"/>
       <c r="E35" s="26"/>
       <c r="F35" s="27"/>
       <c r="G35" s="5"/>
       <c r="H35" s="16" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
     </row>
     <row r="36" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="19" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="C36" s="25" t="s">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="D36" s="26"/>
       <c r="E36" s="26"/>
       <c r="F36" s="27"/>
       <c r="G36" s="5"/>
       <c r="H36" s="16" t="s">
-        <v>615</v>
+        <v>607</v>
       </c>
     </row>
     <row r="37" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="19" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="C37" s="25" t="s">
-        <v>624</v>
+        <v>614</v>
       </c>
       <c r="D37" s="26"/>
       <c r="E37" s="26"/>
       <c r="F37" s="27"/>
       <c r="G37" s="5"/>
       <c r="H37" s="16" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
@@ -3747,16 +3752,16 @@
       <c r="H40" s="11"/>
     </row>
     <row r="41" spans="1:8" s="3" customFormat="1" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="B41" s="28"/>
-      <c r="C41" s="28"/>
-      <c r="D41" s="28"/>
-      <c r="E41" s="28"/>
-      <c r="F41" s="28"/>
-      <c r="G41" s="28"/>
-      <c r="H41" s="28"/>
+      <c r="A41" s="29" t="s">
+        <v>499</v>
+      </c>
+      <c r="B41" s="29"/>
+      <c r="C41" s="29"/>
+      <c r="D41" s="29"/>
+      <c r="E41" s="29"/>
+      <c r="F41" s="29"/>
+      <c r="G41" s="29"/>
+      <c r="H41" s="29"/>
     </row>
     <row r="42" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="1" t="s">
@@ -3781,7 +3786,7 @@
         <v>3</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="43" spans="1:8" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.4">
@@ -3792,20 +3797,20 @@
         <v>17</v>
       </c>
       <c r="C43" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="D43" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="D43" s="6" t="s">
+      <c r="E43" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="F43" s="5" t="s">
         <v>205</v>
-      </c>
-      <c r="F43" s="5" t="s">
-        <v>206</v>
       </c>
       <c r="G43" s="4"/>
       <c r="H43" s="16" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="44" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -3813,7 +3818,7 @@
     </row>
     <row r="45" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="F45" s="3" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
       <c r="H45" s="2"/>
     </row>
@@ -3821,28 +3826,28 @@
       <c r="H46" s="2"/>
     </row>
     <row r="47" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="28" t="s">
+      <c r="A47" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="B47" s="28"/>
-      <c r="C47" s="28"/>
-      <c r="D47" s="28"/>
-      <c r="E47" s="28"/>
-      <c r="F47" s="28"/>
-      <c r="G47" s="28"/>
-      <c r="H47" s="28"/>
+      <c r="B47" s="29"/>
+      <c r="C47" s="29"/>
+      <c r="D47" s="29"/>
+      <c r="E47" s="29"/>
+      <c r="F47" s="29"/>
+      <c r="G47" s="29"/>
+      <c r="H47" s="29"/>
     </row>
     <row r="48" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="28" t="s">
-        <v>518</v>
-      </c>
-      <c r="B48" s="28"/>
-      <c r="C48" s="28"/>
-      <c r="D48" s="28"/>
-      <c r="E48" s="28"/>
-      <c r="F48" s="28"/>
-      <c r="G48" s="28"/>
-      <c r="H48" s="28"/>
+      <c r="A48" s="29" t="s">
+        <v>511</v>
+      </c>
+      <c r="B48" s="29"/>
+      <c r="C48" s="29"/>
+      <c r="D48" s="29"/>
+      <c r="E48" s="29"/>
+      <c r="F48" s="29"/>
+      <c r="G48" s="29"/>
+      <c r="H48" s="29"/>
     </row>
     <row r="49" spans="1:12" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="1" t="s">
@@ -3867,17 +3872,17 @@
         <v>3</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="50" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="51">
-        <v>1</v>
-      </c>
-      <c r="B50" s="50" t="s">
+      <c r="A50" s="40">
+        <v>1</v>
+      </c>
+      <c r="B50" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="C50" s="28" t="s">
+      <c r="C50" s="29" t="s">
         <v>6</v>
       </c>
       <c r="D50" s="6" t="s">
@@ -3889,15 +3894,15 @@
       <c r="F50" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G50" s="32"/>
+      <c r="G50" s="28"/>
       <c r="H50" s="15" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="51" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="51"/>
-      <c r="B51" s="50"/>
-      <c r="C51" s="28"/>
+      <c r="A51" s="40"/>
+      <c r="B51" s="39"/>
+      <c r="C51" s="29"/>
       <c r="D51" s="6" t="s">
         <v>18</v>
       </c>
@@ -3907,9 +3912,9 @@
       <c r="F51" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G51" s="32"/>
+      <c r="G51" s="28"/>
       <c r="H51" s="15" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
@@ -3917,13 +3922,13 @@
       <c r="L51" s="2"/>
     </row>
     <row r="52" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="41">
+      <c r="A52" s="34">
         <v>2</v>
       </c>
-      <c r="B52" s="50" t="s">
+      <c r="B52" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="28" t="s">
+      <c r="C52" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D52" s="6" t="s">
@@ -3935,9 +3940,9 @@
       <c r="F52" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G52" s="32"/>
+      <c r="G52" s="28"/>
       <c r="H52" s="15" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
@@ -3945,9 +3950,9 @@
       <c r="L52" s="2"/>
     </row>
     <row r="53" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="42"/>
-      <c r="B53" s="50"/>
-      <c r="C53" s="28"/>
+      <c r="A53" s="35"/>
+      <c r="B53" s="39"/>
+      <c r="C53" s="29"/>
       <c r="D53" s="6" t="s">
         <v>19</v>
       </c>
@@ -3957,9 +3962,9 @@
       <c r="F53" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G53" s="32"/>
+      <c r="G53" s="28"/>
       <c r="H53" s="15" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
@@ -3967,13 +3972,13 @@
       <c r="L53" s="2"/>
     </row>
     <row r="54" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="41">
+      <c r="A54" s="34">
         <v>3</v>
       </c>
-      <c r="B54" s="50" t="s">
+      <c r="B54" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="28" t="s">
+      <c r="C54" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D54" s="5" t="s">
@@ -3983,11 +3988,11 @@
         <v>1</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>499</v>
-      </c>
-      <c r="G54" s="32"/>
+        <v>492</v>
+      </c>
+      <c r="G54" s="28"/>
       <c r="H54" s="15" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
@@ -3995,9 +4000,9 @@
       <c r="L54" s="2"/>
     </row>
     <row r="55" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="42"/>
-      <c r="B55" s="50"/>
-      <c r="C55" s="28"/>
+      <c r="A55" s="35"/>
+      <c r="B55" s="39"/>
+      <c r="C55" s="29"/>
       <c r="D55" s="5" t="s">
         <v>20</v>
       </c>
@@ -4005,11 +4010,11 @@
         <v>1</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>516</v>
-      </c>
-      <c r="G55" s="32"/>
+        <v>509</v>
+      </c>
+      <c r="G55" s="28"/>
       <c r="H55" s="15" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
@@ -4017,13 +4022,13 @@
       <c r="L55" s="2"/>
     </row>
     <row r="56" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="41">
+      <c r="A56" s="34">
         <v>4</v>
       </c>
-      <c r="B56" s="50" t="s">
+      <c r="B56" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="C56" s="28" t="s">
+      <c r="C56" s="29" t="s">
         <v>6</v>
       </c>
       <c r="D56" s="5" t="s">
@@ -4033,11 +4038,11 @@
         <v>1</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>473</v>
-      </c>
-      <c r="G56" s="32"/>
+        <v>468</v>
+      </c>
+      <c r="G56" s="28"/>
       <c r="H56" s="15" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
@@ -4045,9 +4050,9 @@
       <c r="L56" s="2"/>
     </row>
     <row r="57" spans="1:12" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="42"/>
-      <c r="B57" s="50"/>
-      <c r="C57" s="28"/>
+      <c r="A57" s="35"/>
+      <c r="B57" s="39"/>
+      <c r="C57" s="29"/>
       <c r="D57" s="5" t="s">
         <v>25</v>
       </c>
@@ -4055,11 +4060,11 @@
         <v>1</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>514</v>
-      </c>
-      <c r="G57" s="32"/>
+        <v>507</v>
+      </c>
+      <c r="G57" s="28"/>
       <c r="H57" s="15" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
@@ -4067,13 +4072,13 @@
       <c r="L57" s="2"/>
     </row>
     <row r="58" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="41">
+      <c r="A58" s="34">
         <v>5</v>
       </c>
-      <c r="B58" s="38" t="s">
+      <c r="B58" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C58" s="28" t="s">
+      <c r="C58" s="29" t="s">
         <v>6</v>
       </c>
       <c r="D58" s="5" t="s">
@@ -4083,13 +4088,13 @@
         <v>1</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>495</v>
-      </c>
-      <c r="G58" s="32" t="s">
-        <v>496</v>
+        <v>488</v>
+      </c>
+      <c r="G58" s="28" t="s">
+        <v>489</v>
       </c>
       <c r="H58" s="15" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
@@ -4097,9 +4102,9 @@
       <c r="L58" s="2"/>
     </row>
     <row r="59" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A59" s="42"/>
-      <c r="B59" s="38"/>
-      <c r="C59" s="28"/>
+      <c r="A59" s="35"/>
+      <c r="B59" s="30"/>
+      <c r="C59" s="29"/>
       <c r="D59" s="5" t="s">
         <v>26</v>
       </c>
@@ -4107,11 +4112,11 @@
         <v>1</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="G59" s="32"/>
+        <v>525</v>
+      </c>
+      <c r="G59" s="28"/>
       <c r="H59" s="15" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
@@ -4119,13 +4124,13 @@
       <c r="L59" s="2"/>
     </row>
     <row r="60" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="41">
+      <c r="A60" s="34">
         <v>6</v>
       </c>
-      <c r="B60" s="38" t="s">
+      <c r="B60" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C60" s="28" t="s">
+      <c r="C60" s="29" t="s">
         <v>6</v>
       </c>
       <c r="D60" s="5" t="s">
@@ -4135,11 +4140,11 @@
         <v>0</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>569</v>
-      </c>
-      <c r="G60" s="32"/>
+        <v>562</v>
+      </c>
+      <c r="G60" s="28"/>
       <c r="H60" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
@@ -4147,9 +4152,9 @@
       <c r="L60" s="2"/>
     </row>
     <row r="61" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="42"/>
-      <c r="B61" s="38"/>
-      <c r="C61" s="28"/>
+      <c r="A61" s="35"/>
+      <c r="B61" s="30"/>
+      <c r="C61" s="29"/>
       <c r="D61" s="5" t="s">
         <v>28</v>
       </c>
@@ -4157,11 +4162,11 @@
         <v>0</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>568</v>
-      </c>
-      <c r="G61" s="32"/>
+        <v>561</v>
+      </c>
+      <c r="G61" s="28"/>
       <c r="H61" s="15" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
@@ -4169,13 +4174,13 @@
       <c r="L61" s="2"/>
     </row>
     <row r="62" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="41">
+      <c r="A62" s="34">
         <v>7</v>
       </c>
-      <c r="B62" s="38" t="s">
+      <c r="B62" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C62" s="28" t="s">
+      <c r="C62" s="29" t="s">
         <v>6</v>
       </c>
       <c r="D62" s="5" t="s">
@@ -4187,9 +4192,9 @@
       <c r="F62" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="G62" s="32"/>
+      <c r="G62" s="28"/>
       <c r="H62" s="15" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="I62" s="2"/>
       <c r="J62" s="2"/>
@@ -4197,9 +4202,9 @@
       <c r="L62" s="2"/>
     </row>
     <row r="63" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="42"/>
-      <c r="B63" s="38"/>
-      <c r="C63" s="28"/>
+      <c r="A63" s="35"/>
+      <c r="B63" s="30"/>
+      <c r="C63" s="29"/>
       <c r="D63" s="5" t="s">
         <v>38</v>
       </c>
@@ -4209,9 +4214,9 @@
       <c r="F63" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="G63" s="32"/>
+      <c r="G63" s="28"/>
       <c r="H63" s="15" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
@@ -4219,29 +4224,29 @@
       <c r="L63" s="2"/>
     </row>
     <row r="64" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A64" s="41">
+      <c r="A64" s="34">
         <v>8</v>
       </c>
-      <c r="B64" s="38" t="s">
+      <c r="B64" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C64" s="28" t="s">
+      <c r="C64" s="29" t="s">
         <v>6</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E64" s="1">
         <v>0</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>570</v>
-      </c>
-      <c r="G64" s="32" t="s">
-        <v>545</v>
+        <v>563</v>
+      </c>
+      <c r="G64" s="28" t="s">
+        <v>538</v>
       </c>
       <c r="H64" s="15" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="I64" s="2"/>
       <c r="J64" s="2"/>
@@ -4249,21 +4254,21 @@
       <c r="L64" s="2"/>
     </row>
     <row r="65" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A65" s="42"/>
-      <c r="B65" s="38"/>
-      <c r="C65" s="28"/>
+      <c r="A65" s="35"/>
+      <c r="B65" s="30"/>
+      <c r="C65" s="29"/>
       <c r="D65" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E65" s="1">
         <v>0</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>571</v>
-      </c>
-      <c r="G65" s="32"/>
+        <v>564</v>
+      </c>
+      <c r="G65" s="28"/>
       <c r="H65" s="15" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="I65" s="2"/>
       <c r="J65" s="2"/>
@@ -4271,13 +4276,13 @@
       <c r="L65" s="2"/>
     </row>
     <row r="66" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A66" s="41">
+      <c r="A66" s="34">
         <v>9</v>
       </c>
-      <c r="B66" s="38" t="s">
+      <c r="B66" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C66" s="28" t="s">
+      <c r="C66" s="29" t="s">
         <v>6</v>
       </c>
       <c r="D66" s="5" t="s">
@@ -4287,19 +4292,19 @@
         <v>1</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="G66" s="32" t="s">
-        <v>546</v>
+        <v>535</v>
+      </c>
+      <c r="G66" s="28" t="s">
+        <v>539</v>
       </c>
       <c r="H66" s="15" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="67" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A67" s="42"/>
-      <c r="B67" s="38"/>
-      <c r="C67" s="28"/>
+      <c r="A67" s="35"/>
+      <c r="B67" s="30"/>
+      <c r="C67" s="29"/>
       <c r="D67" s="5" t="s">
         <v>114</v>
       </c>
@@ -4307,21 +4312,21 @@
         <v>1</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>543</v>
-      </c>
-      <c r="G67" s="32"/>
+        <v>536</v>
+      </c>
+      <c r="G67" s="28"/>
       <c r="H67" s="15" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="68" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A68" s="41">
+      <c r="A68" s="34">
         <v>10</v>
       </c>
-      <c r="B68" s="38" t="s">
+      <c r="B68" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C68" s="28" t="s">
+      <c r="C68" s="29" t="s">
         <v>6</v>
       </c>
       <c r="D68" s="5" t="s">
@@ -4331,13 +4336,13 @@
         <v>1</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>524</v>
-      </c>
-      <c r="G68" s="32" t="s">
-        <v>547</v>
+        <v>517</v>
+      </c>
+      <c r="G68" s="28" t="s">
+        <v>540</v>
       </c>
       <c r="H68" s="15" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="I68" s="2"/>
       <c r="J68" s="2"/>
@@ -4345,9 +4350,9 @@
       <c r="L68" s="2"/>
     </row>
     <row r="69" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A69" s="42"/>
-      <c r="B69" s="38"/>
-      <c r="C69" s="28"/>
+      <c r="A69" s="35"/>
+      <c r="B69" s="30"/>
+      <c r="C69" s="29"/>
       <c r="D69" s="5" t="s">
         <v>156</v>
       </c>
@@ -4355,11 +4360,11 @@
         <v>1</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>523</v>
-      </c>
-      <c r="G69" s="32"/>
+        <v>516</v>
+      </c>
+      <c r="G69" s="28"/>
       <c r="H69" s="15" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="I69" s="2"/>
       <c r="J69" s="2"/>
@@ -4367,13 +4372,13 @@
       <c r="L69" s="2"/>
     </row>
     <row r="70" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A70" s="41">
+      <c r="A70" s="34">
         <v>11</v>
       </c>
-      <c r="B70" s="38" t="s">
+      <c r="B70" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C70" s="28" t="s">
+      <c r="C70" s="29" t="s">
         <v>6</v>
       </c>
       <c r="D70" s="5" t="s">
@@ -4383,13 +4388,13 @@
         <v>0</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>606</v>
-      </c>
-      <c r="G70" s="32" t="s">
-        <v>545</v>
+        <v>598</v>
+      </c>
+      <c r="G70" s="28" t="s">
+        <v>538</v>
       </c>
       <c r="H70" s="15" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="I70" s="2"/>
       <c r="J70" s="2"/>
@@ -4397,9 +4402,9 @@
       <c r="L70" s="2"/>
     </row>
     <row r="71" spans="1:12" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A71" s="42"/>
-      <c r="B71" s="38"/>
-      <c r="C71" s="28"/>
+      <c r="A71" s="35"/>
+      <c r="B71" s="30"/>
+      <c r="C71" s="29"/>
       <c r="D71" s="5" t="s">
         <v>154</v>
       </c>
@@ -4407,11 +4412,11 @@
         <v>0</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="G71" s="32"/>
+        <v>599</v>
+      </c>
+      <c r="G71" s="28"/>
       <c r="H71" s="15" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="I71" s="2"/>
       <c r="J71" s="2"/>
@@ -4419,13 +4424,13 @@
       <c r="L71" s="2"/>
     </row>
     <row r="72" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A72" s="41">
+      <c r="A72" s="34">
         <v>12</v>
       </c>
-      <c r="B72" s="36" t="s">
+      <c r="B72" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C72" s="28" t="s">
+      <c r="C72" s="29" t="s">
         <v>6</v>
       </c>
       <c r="D72" s="5" t="s">
@@ -4435,13 +4440,13 @@
         <v>0</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>604</v>
-      </c>
-      <c r="G72" s="32" t="s">
-        <v>545</v>
+        <v>596</v>
+      </c>
+      <c r="G72" s="28" t="s">
+        <v>538</v>
       </c>
       <c r="H72" s="15" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="I72" s="2"/>
       <c r="J72" s="2"/>
@@ -4449,9 +4454,9 @@
       <c r="L72" s="2"/>
     </row>
     <row r="73" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A73" s="42"/>
-      <c r="B73" s="36"/>
-      <c r="C73" s="28"/>
+      <c r="A73" s="35"/>
+      <c r="B73" s="33"/>
+      <c r="C73" s="29"/>
       <c r="D73" s="5" t="s">
         <v>36</v>
       </c>
@@ -4459,11 +4464,11 @@
         <v>0</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>605</v>
-      </c>
-      <c r="G73" s="32"/>
+        <v>597</v>
+      </c>
+      <c r="G73" s="28"/>
       <c r="H73" s="15" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="I73" s="2"/>
       <c r="J73" s="2"/>
@@ -4471,13 +4476,13 @@
       <c r="L73" s="2"/>
     </row>
     <row r="74" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A74" s="41">
+      <c r="A74" s="34">
         <v>13</v>
       </c>
-      <c r="B74" s="36" t="s">
+      <c r="B74" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C74" s="28" t="s">
+      <c r="C74" s="29" t="s">
         <v>6</v>
       </c>
       <c r="D74" s="5" t="s">
@@ -4487,11 +4492,11 @@
         <v>0</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>521</v>
-      </c>
-      <c r="G74" s="32"/>
+        <v>514</v>
+      </c>
+      <c r="G74" s="28"/>
       <c r="H74" s="15" t="s">
-        <v>638</v>
+        <v>626</v>
       </c>
       <c r="I74" s="2"/>
       <c r="J74" s="2"/>
@@ -4499,9 +4504,9 @@
       <c r="L74" s="2"/>
     </row>
     <row r="75" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A75" s="42"/>
-      <c r="B75" s="36"/>
-      <c r="C75" s="28"/>
+      <c r="A75" s="35"/>
+      <c r="B75" s="33"/>
+      <c r="C75" s="29"/>
       <c r="D75" s="5" t="s">
         <v>34</v>
       </c>
@@ -4509,11 +4514,11 @@
         <v>0</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>522</v>
-      </c>
-      <c r="G75" s="32"/>
+        <v>515</v>
+      </c>
+      <c r="G75" s="28"/>
       <c r="H75" s="15" t="s">
-        <v>639</v>
+        <v>627</v>
       </c>
       <c r="I75" s="2"/>
       <c r="J75" s="2"/>
@@ -4521,13 +4526,13 @@
       <c r="L75" s="2"/>
     </row>
     <row r="76" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A76" s="41">
+      <c r="A76" s="34">
         <v>14</v>
       </c>
-      <c r="B76" s="36" t="s">
+      <c r="B76" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C76" s="28" t="s">
+      <c r="C76" s="29" t="s">
         <v>6</v>
       </c>
       <c r="D76" s="5" t="s">
@@ -4537,13 +4542,13 @@
         <v>1</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>474</v>
-      </c>
-      <c r="G76" s="32" t="s">
-        <v>545</v>
+        <v>469</v>
+      </c>
+      <c r="G76" s="28" t="s">
+        <v>538</v>
       </c>
       <c r="H76" s="15" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="I76" s="2"/>
       <c r="J76" s="2"/>
@@ -4551,9 +4556,9 @@
       <c r="L76" s="2"/>
     </row>
     <row r="77" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A77" s="42"/>
-      <c r="B77" s="36"/>
-      <c r="C77" s="28"/>
+      <c r="A77" s="35"/>
+      <c r="B77" s="33"/>
+      <c r="C77" s="29"/>
       <c r="D77" s="5" t="s">
         <v>125</v>
       </c>
@@ -4561,21 +4566,21 @@
         <v>1</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>475</v>
-      </c>
-      <c r="G77" s="32"/>
+        <v>470</v>
+      </c>
+      <c r="G77" s="28"/>
       <c r="H77" s="15" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
     </row>
     <row r="78" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A78" s="41">
+      <c r="A78" s="34">
         <v>15</v>
       </c>
-      <c r="B78" s="36" t="s">
+      <c r="B78" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C78" s="28" t="s">
+      <c r="C78" s="29" t="s">
         <v>6</v>
       </c>
       <c r="D78" s="5" t="s">
@@ -4585,19 +4590,19 @@
         <v>2</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>599</v>
-      </c>
-      <c r="G78" s="32" t="s">
-        <v>597</v>
+        <v>591</v>
+      </c>
+      <c r="G78" s="28" t="s">
+        <v>589</v>
       </c>
       <c r="H78" s="15" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
     <row r="79" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A79" s="42"/>
-      <c r="B79" s="36"/>
-      <c r="C79" s="28"/>
+      <c r="A79" s="35"/>
+      <c r="B79" s="33"/>
+      <c r="C79" s="29"/>
       <c r="D79" s="5" t="s">
         <v>123</v>
       </c>
@@ -4605,21 +4610,21 @@
         <v>2</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>600</v>
-      </c>
-      <c r="G79" s="32"/>
+        <v>592</v>
+      </c>
+      <c r="G79" s="28"/>
       <c r="H79" s="15" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
     </row>
     <row r="80" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A80" s="41">
+      <c r="A80" s="34">
         <v>16</v>
       </c>
-      <c r="B80" s="36" t="s">
+      <c r="B80" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C80" s="39" t="s">
+      <c r="C80" s="50" t="s">
         <v>6</v>
       </c>
       <c r="D80" s="5" t="s">
@@ -4629,19 +4634,19 @@
         <v>2</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>642</v>
-      </c>
-      <c r="G80" s="32" t="s">
-        <v>520</v>
+        <v>630</v>
+      </c>
+      <c r="G80" s="28" t="s">
+        <v>513</v>
       </c>
       <c r="H80" s="15" t="s">
-        <v>640</v>
+        <v>628</v>
       </c>
     </row>
     <row r="81" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A81" s="42"/>
-      <c r="B81" s="36"/>
-      <c r="C81" s="40"/>
+      <c r="A81" s="35"/>
+      <c r="B81" s="33"/>
+      <c r="C81" s="51"/>
       <c r="D81" s="5" t="s">
         <v>121</v>
       </c>
@@ -4649,21 +4654,21 @@
         <v>2</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="G81" s="32"/>
+        <v>631</v>
+      </c>
+      <c r="G81" s="28"/>
       <c r="H81" s="15" t="s">
-        <v>641</v>
+        <v>629</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A82" s="41">
+      <c r="A82" s="34">
         <v>17</v>
       </c>
-      <c r="B82" s="36" t="s">
+      <c r="B82" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C82" s="28" t="s">
+      <c r="C82" s="29" t="s">
         <v>6</v>
       </c>
       <c r="D82" s="5" t="s">
@@ -4673,19 +4678,19 @@
         <v>1</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>598</v>
-      </c>
-      <c r="G82" s="32" t="s">
-        <v>637</v>
+        <v>590</v>
+      </c>
+      <c r="G82" s="28" t="s">
+        <v>625</v>
       </c>
       <c r="H82" s="15" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="83" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A83" s="42"/>
-      <c r="B83" s="36"/>
-      <c r="C83" s="28"/>
+      <c r="A83" s="35"/>
+      <c r="B83" s="33"/>
+      <c r="C83" s="29"/>
       <c r="D83" s="5" t="s">
         <v>40</v>
       </c>
@@ -4693,21 +4698,21 @@
         <v>1</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>488</v>
-      </c>
-      <c r="G83" s="32"/>
+        <v>483</v>
+      </c>
+      <c r="G83" s="28"/>
       <c r="H83" s="15" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
     </row>
     <row r="84" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A84" s="33">
+      <c r="A84" s="43">
         <v>18</v>
       </c>
-      <c r="B84" s="36" t="s">
+      <c r="B84" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C84" s="37" t="s">
+      <c r="C84" s="45" t="s">
         <v>6</v>
       </c>
       <c r="D84" s="5" t="s">
@@ -4717,19 +4722,19 @@
         <v>43</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>476</v>
-      </c>
-      <c r="G84" s="32" t="s">
-        <v>487</v>
+        <v>471</v>
+      </c>
+      <c r="G84" s="28" t="s">
+        <v>482</v>
       </c>
       <c r="H84" s="15" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="85" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A85" s="34"/>
-      <c r="B85" s="36"/>
-      <c r="C85" s="37"/>
+      <c r="A85" s="44"/>
+      <c r="B85" s="33"/>
+      <c r="C85" s="45"/>
       <c r="D85" s="5" t="s">
         <v>42</v>
       </c>
@@ -4737,21 +4742,21 @@
         <v>43</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>477</v>
-      </c>
-      <c r="G85" s="32"/>
+        <v>472</v>
+      </c>
+      <c r="G85" s="28"/>
       <c r="H85" s="15" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="86" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A86" s="41">
+      <c r="A86" s="34">
         <v>19</v>
       </c>
-      <c r="B86" s="36" t="s">
+      <c r="B86" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C86" s="28" t="s">
+      <c r="C86" s="29" t="s">
         <v>6</v>
       </c>
       <c r="D86" s="5" t="s">
@@ -4761,17 +4766,17 @@
         <v>1</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>649</v>
-      </c>
-      <c r="G86" s="32"/>
+        <v>636</v>
+      </c>
+      <c r="G86" s="28"/>
       <c r="H86" s="15" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
     </row>
     <row r="87" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A87" s="42"/>
-      <c r="B87" s="36"/>
-      <c r="C87" s="28"/>
+      <c r="A87" s="35"/>
+      <c r="B87" s="33"/>
+      <c r="C87" s="29"/>
       <c r="D87" s="5" t="s">
         <v>83</v>
       </c>
@@ -4779,65 +4784,65 @@
         <v>1</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>648</v>
-      </c>
-      <c r="G87" s="32"/>
+        <v>635</v>
+      </c>
+      <c r="G87" s="28"/>
       <c r="H87" s="15" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
     </row>
     <row r="88" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A88" s="33">
+      <c r="A88" s="43">
         <v>20</v>
       </c>
-      <c r="B88" s="35" t="s">
+      <c r="B88" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C88" s="28" t="s">
+      <c r="C88" s="29" t="s">
         <v>6</v>
       </c>
       <c r="D88" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="E88" s="1">
+        <v>1</v>
+      </c>
+      <c r="F88" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="E88" s="1">
-        <v>1</v>
-      </c>
-      <c r="F88" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="G88" s="32" t="s">
-        <v>263</v>
+      <c r="G88" s="28" t="s">
+        <v>260</v>
       </c>
       <c r="H88" s="15" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="89" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A89" s="34"/>
-      <c r="B89" s="35"/>
-      <c r="C89" s="28"/>
+      <c r="A89" s="44"/>
+      <c r="B89" s="31"/>
+      <c r="C89" s="29"/>
       <c r="D89" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="E89" s="1">
+        <v>1</v>
+      </c>
+      <c r="F89" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="E89" s="1">
-        <v>1</v>
-      </c>
-      <c r="F89" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="G89" s="32"/>
+      <c r="G89" s="28"/>
       <c r="H89" s="15" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
     </row>
     <row r="90" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A90" s="33">
+      <c r="A90" s="43">
         <v>21</v>
       </c>
-      <c r="B90" s="35" t="s">
+      <c r="B90" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C90" s="28" t="s">
+      <c r="C90" s="29" t="s">
         <v>6</v>
       </c>
       <c r="D90" s="5" t="s">
@@ -4847,19 +4852,19 @@
         <v>0</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>527</v>
-      </c>
-      <c r="G90" s="32" t="s">
-        <v>531</v>
+        <v>520</v>
+      </c>
+      <c r="G90" s="28" t="s">
+        <v>524</v>
       </c>
       <c r="H90" s="15" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="91" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A91" s="34"/>
-      <c r="B91" s="35"/>
-      <c r="C91" s="28"/>
+      <c r="A91" s="44"/>
+      <c r="B91" s="31"/>
+      <c r="C91" s="29"/>
       <c r="D91" s="5" t="s">
         <v>127</v>
       </c>
@@ -4867,21 +4872,21 @@
         <v>0</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>528</v>
-      </c>
-      <c r="G91" s="32"/>
+        <v>521</v>
+      </c>
+      <c r="G91" s="28"/>
       <c r="H91" s="15" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
     </row>
     <row r="92" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A92" s="41">
+      <c r="A92" s="34">
         <v>22</v>
       </c>
-      <c r="B92" s="35" t="s">
+      <c r="B92" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C92" s="28" t="s">
+      <c r="C92" s="29" t="s">
         <v>6</v>
       </c>
       <c r="D92" s="5" t="s">
@@ -4891,19 +4896,19 @@
         <v>2</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>497</v>
-      </c>
-      <c r="G92" s="32" t="s">
-        <v>491</v>
+        <v>490</v>
+      </c>
+      <c r="G92" s="28" t="s">
+        <v>486</v>
       </c>
       <c r="H92" s="15" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="93" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A93" s="42"/>
-      <c r="B93" s="35"/>
-      <c r="C93" s="28"/>
+      <c r="A93" s="35"/>
+      <c r="B93" s="31"/>
+      <c r="C93" s="29"/>
       <c r="D93" s="5" t="s">
         <v>176</v>
       </c>
@@ -4911,21 +4916,21 @@
         <v>2</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>498</v>
-      </c>
-      <c r="G93" s="32"/>
+        <v>491</v>
+      </c>
+      <c r="G93" s="28"/>
       <c r="H93" s="15" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
     </row>
     <row r="94" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A94" s="41">
+      <c r="A94" s="34">
         <v>23</v>
       </c>
-      <c r="B94" s="35" t="s">
+      <c r="B94" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C94" s="28" t="s">
+      <c r="C94" s="29" t="s">
         <v>6</v>
       </c>
       <c r="D94" s="5" t="s">
@@ -4935,19 +4940,19 @@
         <v>2</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>625</v>
-      </c>
-      <c r="G94" s="32" t="s">
-        <v>278</v>
+        <v>615</v>
+      </c>
+      <c r="G94" s="28" t="s">
+        <v>275</v>
       </c>
       <c r="H94" s="15" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
     </row>
     <row r="95" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A95" s="42"/>
-      <c r="B95" s="35"/>
-      <c r="C95" s="28"/>
+      <c r="A95" s="35"/>
+      <c r="B95" s="31"/>
+      <c r="C95" s="29"/>
       <c r="D95" s="5" t="s">
         <v>31</v>
       </c>
@@ -4955,21 +4960,21 @@
         <v>2</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>623</v>
-      </c>
-      <c r="G95" s="32"/>
+        <v>613</v>
+      </c>
+      <c r="G95" s="28"/>
       <c r="H95" s="15" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
     </row>
     <row r="96" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A96" s="33">
+      <c r="A96" s="43">
         <v>24</v>
       </c>
-      <c r="B96" s="35" t="s">
+      <c r="B96" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C96" s="28" t="s">
+      <c r="C96" s="29" t="s">
         <v>6</v>
       </c>
       <c r="D96" s="5" t="s">
@@ -4979,19 +4984,19 @@
         <v>43</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>525</v>
-      </c>
-      <c r="G96" s="32" t="s">
-        <v>199</v>
+        <v>518</v>
+      </c>
+      <c r="G96" s="28" t="s">
+        <v>198</v>
       </c>
       <c r="H96" s="15" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
     </row>
     <row r="97" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A97" s="34"/>
-      <c r="B97" s="35"/>
-      <c r="C97" s="28"/>
+      <c r="A97" s="44"/>
+      <c r="B97" s="31"/>
+      <c r="C97" s="29"/>
       <c r="D97" s="5" t="s">
         <v>166</v>
       </c>
@@ -4999,21 +5004,21 @@
         <v>43</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>526</v>
-      </c>
-      <c r="G97" s="32"/>
+        <v>519</v>
+      </c>
+      <c r="G97" s="28"/>
       <c r="H97" s="15" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
     </row>
     <row r="98" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A98" s="41">
+      <c r="A98" s="34">
         <v>25</v>
       </c>
-      <c r="B98" s="38" t="s">
+      <c r="B98" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C98" s="28" t="s">
+      <c r="C98" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D98" s="5" t="s">
@@ -5023,17 +5028,17 @@
         <v>0</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>660</v>
-      </c>
-      <c r="G98" s="32"/>
+        <v>651</v>
+      </c>
+      <c r="G98" s="28"/>
       <c r="H98" s="15" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
     <row r="99" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A99" s="42"/>
-      <c r="B99" s="38"/>
-      <c r="C99" s="28"/>
+      <c r="A99" s="35"/>
+      <c r="B99" s="30"/>
+      <c r="C99" s="29"/>
       <c r="D99" s="5" t="s">
         <v>146</v>
       </c>
@@ -5041,21 +5046,21 @@
         <v>0</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>661</v>
-      </c>
-      <c r="G99" s="32"/>
+        <v>652</v>
+      </c>
+      <c r="G99" s="28"/>
       <c r="H99" s="15" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
     </row>
     <row r="100" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A100" s="33">
+      <c r="A100" s="43">
         <v>26</v>
       </c>
-      <c r="B100" s="38" t="s">
+      <c r="B100" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C100" s="37" t="s">
+      <c r="C100" s="45" t="s">
         <v>14</v>
       </c>
       <c r="D100" s="5" t="s">
@@ -5065,17 +5070,17 @@
         <v>1</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>652</v>
-      </c>
-      <c r="G100" s="32"/>
+        <v>637</v>
+      </c>
+      <c r="G100" s="28"/>
       <c r="H100" s="15" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
     </row>
     <row r="101" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A101" s="34"/>
-      <c r="B101" s="38"/>
-      <c r="C101" s="37"/>
+      <c r="A101" s="44"/>
+      <c r="B101" s="30"/>
+      <c r="C101" s="45"/>
       <c r="D101" s="5" t="s">
         <v>158</v>
       </c>
@@ -5083,21 +5088,21 @@
         <v>1</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>653</v>
-      </c>
-      <c r="G101" s="32"/>
+        <v>638</v>
+      </c>
+      <c r="G101" s="28"/>
       <c r="H101" s="15" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
     </row>
     <row r="102" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A102" s="41">
+      <c r="A102" s="34">
         <v>27</v>
       </c>
-      <c r="B102" s="38" t="s">
+      <c r="B102" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C102" s="28" t="s">
+      <c r="C102" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D102" s="5" t="s">
@@ -5107,17 +5112,17 @@
         <v>1</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>658</v>
-      </c>
-      <c r="G102" s="32"/>
+        <v>642</v>
+      </c>
+      <c r="G102" s="28"/>
       <c r="H102" s="15" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
     <row r="103" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A103" s="42"/>
-      <c r="B103" s="38"/>
-      <c r="C103" s="28"/>
+      <c r="A103" s="35"/>
+      <c r="B103" s="30"/>
+      <c r="C103" s="29"/>
       <c r="D103" s="5" t="s">
         <v>45</v>
       </c>
@@ -5125,21 +5130,21 @@
         <v>1</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>659</v>
-      </c>
-      <c r="G103" s="32"/>
+        <v>643</v>
+      </c>
+      <c r="G103" s="28"/>
       <c r="H103" s="15" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
     </row>
     <row r="104" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A104" s="41">
+      <c r="A104" s="34">
         <v>28</v>
       </c>
-      <c r="B104" s="38" t="s">
+      <c r="B104" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C104" s="28" t="s">
+      <c r="C104" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D104" s="5" t="s">
@@ -5149,17 +5154,17 @@
         <v>1</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>566</v>
-      </c>
-      <c r="G104" s="32"/>
+        <v>559</v>
+      </c>
+      <c r="G104" s="28"/>
       <c r="H104" s="15" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
     </row>
     <row r="105" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A105" s="42"/>
-      <c r="B105" s="38"/>
-      <c r="C105" s="28"/>
+      <c r="A105" s="35"/>
+      <c r="B105" s="30"/>
+      <c r="C105" s="29"/>
       <c r="D105" s="5" t="s">
         <v>67</v>
       </c>
@@ -5167,21 +5172,21 @@
         <v>1</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>567</v>
-      </c>
-      <c r="G105" s="32"/>
+        <v>560</v>
+      </c>
+      <c r="G105" s="28"/>
       <c r="H105" s="15" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
     </row>
     <row r="106" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A106" s="33">
+      <c r="A106" s="43">
         <v>29</v>
       </c>
-      <c r="B106" s="38" t="s">
+      <c r="B106" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C106" s="28" t="s">
+      <c r="C106" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D106" s="5" t="s">
@@ -5191,19 +5196,19 @@
         <v>0</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="G106" s="32" t="s">
-        <v>517</v>
+        <v>272</v>
+      </c>
+      <c r="G106" s="28" t="s">
+        <v>510</v>
       </c>
       <c r="H106" s="15" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
     </row>
     <row r="107" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A107" s="34"/>
-      <c r="B107" s="38"/>
-      <c r="C107" s="28"/>
+      <c r="A107" s="44"/>
+      <c r="B107" s="30"/>
+      <c r="C107" s="29"/>
       <c r="D107" s="5" t="s">
         <v>152</v>
       </c>
@@ -5211,21 +5216,21 @@
         <v>0</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="G107" s="32"/>
+        <v>273</v>
+      </c>
+      <c r="G107" s="28"/>
       <c r="H107" s="15" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
     </row>
     <row r="108" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A108" s="41">
+      <c r="A108" s="34">
         <v>30</v>
       </c>
-      <c r="B108" s="38" t="s">
+      <c r="B108" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C108" s="28" t="s">
+      <c r="C108" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D108" s="5" t="s">
@@ -5235,19 +5240,19 @@
         <v>1</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>611</v>
-      </c>
-      <c r="G108" s="32" t="s">
-        <v>218</v>
+        <v>603</v>
+      </c>
+      <c r="G108" s="28" t="s">
+        <v>217</v>
       </c>
       <c r="H108" s="15" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="109" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A109" s="42"/>
-      <c r="B109" s="38"/>
-      <c r="C109" s="28"/>
+      <c r="A109" s="35"/>
+      <c r="B109" s="30"/>
+      <c r="C109" s="29"/>
       <c r="D109" s="5" t="s">
         <v>47</v>
       </c>
@@ -5255,85 +5260,85 @@
         <v>1</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>612</v>
-      </c>
-      <c r="G109" s="32"/>
+        <v>604</v>
+      </c>
+      <c r="G109" s="28"/>
       <c r="H109" s="15" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
     </row>
     <row r="110" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A110" s="41">
+      <c r="A110" s="34">
         <v>31</v>
       </c>
-      <c r="B110" s="46" t="s">
+      <c r="B110" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="C110" s="43" t="s">
+      <c r="C110" s="32" t="s">
         <v>14</v>
       </c>
       <c r="D110" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="E110" s="1">
+        <v>1</v>
+      </c>
+      <c r="F110" s="5" t="s">
+        <v>622</v>
+      </c>
+      <c r="G110" s="46" t="s">
+        <v>254</v>
+      </c>
+      <c r="H110" s="15" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A111" s="35"/>
+      <c r="B111" s="42"/>
+      <c r="C111" s="32"/>
+      <c r="D111" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="E110" s="1">
-        <v>1</v>
-      </c>
-      <c r="F110" s="5" t="s">
-        <v>634</v>
-      </c>
-      <c r="G110" s="48" t="s">
-        <v>257</v>
-      </c>
-      <c r="H110" s="15" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A111" s="42"/>
-      <c r="B111" s="47"/>
-      <c r="C111" s="43"/>
-      <c r="D111" s="5" t="s">
-        <v>189</v>
-      </c>
       <c r="E111" s="1">
         <v>1</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>635</v>
-      </c>
-      <c r="G111" s="49"/>
+        <v>623</v>
+      </c>
+      <c r="G111" s="47"/>
       <c r="H111" s="15" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
     </row>
     <row r="112" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A112" s="33">
+      <c r="A112" s="43">
         <v>32</v>
       </c>
-      <c r="B112" s="38" t="s">
+      <c r="B112" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C112" s="37" t="s">
+      <c r="C112" s="45" t="s">
         <v>14</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="G112" s="32"/>
+        <v>208</v>
+      </c>
+      <c r="G112" s="28"/>
       <c r="H112" s="15" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="113" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A113" s="34"/>
-      <c r="B113" s="38"/>
-      <c r="C113" s="37"/>
+      <c r="A113" s="44"/>
+      <c r="B113" s="30"/>
+      <c r="C113" s="45"/>
       <c r="D113" s="5" t="s">
         <v>52</v>
       </c>
@@ -5341,21 +5346,21 @@
         <v>43</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="G113" s="32"/>
+        <v>207</v>
+      </c>
+      <c r="G113" s="28"/>
       <c r="H113" s="15" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
     </row>
     <row r="114" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A114" s="41">
+      <c r="A114" s="34">
         <v>33</v>
       </c>
-      <c r="B114" s="38" t="s">
+      <c r="B114" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C114" s="28" t="s">
+      <c r="C114" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D114" s="5" t="s">
@@ -5365,17 +5370,17 @@
         <v>1</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>548</v>
-      </c>
-      <c r="G114" s="32"/>
+        <v>541</v>
+      </c>
+      <c r="G114" s="28"/>
       <c r="H114" s="15" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="115" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A115" s="42"/>
-      <c r="B115" s="38"/>
-      <c r="C115" s="28"/>
+      <c r="A115" s="35"/>
+      <c r="B115" s="30"/>
+      <c r="C115" s="29"/>
       <c r="D115" s="5" t="s">
         <v>133</v>
       </c>
@@ -5383,21 +5388,21 @@
         <v>1</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>549</v>
-      </c>
-      <c r="G115" s="32"/>
+        <v>542</v>
+      </c>
+      <c r="G115" s="28"/>
       <c r="H115" s="15" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
     </row>
     <row r="116" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A116" s="41">
+      <c r="A116" s="34">
         <v>34</v>
       </c>
-      <c r="B116" s="38" t="s">
+      <c r="B116" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C116" s="28" t="s">
+      <c r="C116" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D116" s="5" t="s">
@@ -5407,19 +5412,19 @@
         <v>0</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="G116" s="32" t="s">
-        <v>218</v>
+        <v>197</v>
+      </c>
+      <c r="G116" s="28" t="s">
+        <v>217</v>
       </c>
       <c r="H116" s="15" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
     </row>
     <row r="117" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A117" s="42"/>
-      <c r="B117" s="38"/>
-      <c r="C117" s="28"/>
+      <c r="A117" s="35"/>
+      <c r="B117" s="30"/>
+      <c r="C117" s="29"/>
       <c r="D117" s="5" t="s">
         <v>75</v>
       </c>
@@ -5427,21 +5432,21 @@
         <v>0</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>609</v>
-      </c>
-      <c r="G117" s="32"/>
+        <v>601</v>
+      </c>
+      <c r="G117" s="28"/>
       <c r="H117" s="15" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="118" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A118" s="41">
+      <c r="A118" s="34">
         <v>35</v>
       </c>
-      <c r="B118" s="38" t="s">
+      <c r="B118" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C118" s="28" t="s">
+      <c r="C118" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D118" s="5" t="s">
@@ -5451,19 +5456,19 @@
         <v>0</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="G118" s="32" t="s">
-        <v>218</v>
+        <v>196</v>
+      </c>
+      <c r="G118" s="28" t="s">
+        <v>217</v>
       </c>
       <c r="H118" s="15" t="s">
-        <v>636</v>
+        <v>624</v>
       </c>
     </row>
     <row r="119" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A119" s="42"/>
-      <c r="B119" s="38"/>
-      <c r="C119" s="28"/>
+      <c r="A119" s="35"/>
+      <c r="B119" s="30"/>
+      <c r="C119" s="29"/>
       <c r="D119" s="5" t="s">
         <v>77</v>
       </c>
@@ -5471,21 +5476,21 @@
         <v>0</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>608</v>
-      </c>
-      <c r="G119" s="32"/>
+        <v>600</v>
+      </c>
+      <c r="G119" s="28"/>
       <c r="H119" s="15" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
     </row>
     <row r="120" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A120" s="41">
+      <c r="A120" s="34">
         <v>36</v>
       </c>
-      <c r="B120" s="38" t="s">
+      <c r="B120" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C120" s="28" t="s">
+      <c r="C120" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D120" s="5" t="s">
@@ -5495,19 +5500,19 @@
         <v>0</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>662</v>
-      </c>
-      <c r="G120" s="32" t="s">
-        <v>246</v>
+        <v>644</v>
+      </c>
+      <c r="G120" s="28" t="s">
+        <v>245</v>
       </c>
       <c r="H120" s="15" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
     </row>
     <row r="121" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A121" s="42"/>
-      <c r="B121" s="38"/>
-      <c r="C121" s="28"/>
+      <c r="A121" s="35"/>
+      <c r="B121" s="30"/>
+      <c r="C121" s="29"/>
       <c r="D121" s="5" t="s">
         <v>119</v>
       </c>
@@ -5515,21 +5520,21 @@
         <v>0</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>663</v>
-      </c>
-      <c r="G121" s="32"/>
+        <v>645</v>
+      </c>
+      <c r="G121" s="28"/>
       <c r="H121" s="15" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
     </row>
     <row r="122" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A122" s="41">
+      <c r="A122" s="34">
         <v>37</v>
       </c>
-      <c r="B122" s="46" t="s">
+      <c r="B122" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="C122" s="28" t="s">
+      <c r="C122" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D122" s="5" t="s">
@@ -5539,17 +5544,17 @@
         <v>2</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="G122" s="32"/>
+        <v>658</v>
+      </c>
+      <c r="G122" s="28"/>
       <c r="H122" s="15" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="123" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A123" s="42"/>
-      <c r="B123" s="47"/>
-      <c r="C123" s="28"/>
+      <c r="A123" s="35"/>
+      <c r="B123" s="42"/>
+      <c r="C123" s="29"/>
       <c r="D123" s="5" t="s">
         <v>180</v>
       </c>
@@ -5557,21 +5562,21 @@
         <v>1</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="G123" s="32"/>
+        <v>658</v>
+      </c>
+      <c r="G123" s="28"/>
       <c r="H123" s="15" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
     </row>
     <row r="124" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A124" s="41">
+      <c r="A124" s="34">
         <v>38</v>
       </c>
-      <c r="B124" s="46" t="s">
+      <c r="B124" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="C124" s="28" t="s">
+      <c r="C124" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D124" s="5" t="s">
@@ -5581,17 +5586,17 @@
         <v>1</v>
       </c>
       <c r="F124" s="5" t="s">
-        <v>483</v>
-      </c>
-      <c r="G124" s="32"/>
+        <v>478</v>
+      </c>
+      <c r="G124" s="28"/>
       <c r="H124" s="15" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="125" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A125" s="42"/>
-      <c r="B125" s="47"/>
-      <c r="C125" s="28"/>
+      <c r="A125" s="35"/>
+      <c r="B125" s="42"/>
+      <c r="C125" s="29"/>
       <c r="D125" s="5" t="s">
         <v>54</v>
       </c>
@@ -5599,21 +5604,21 @@
         <v>1</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>484</v>
-      </c>
-      <c r="G125" s="32"/>
+        <v>479</v>
+      </c>
+      <c r="G125" s="28"/>
       <c r="H125" s="15" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="126" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A126" s="41">
+      <c r="A126" s="34">
         <v>39</v>
       </c>
-      <c r="B126" s="46" t="s">
+      <c r="B126" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="C126" s="28" t="s">
+      <c r="C126" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D126" s="5" t="s">
@@ -5623,19 +5628,19 @@
         <v>0</v>
       </c>
       <c r="F126" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="G126" s="32" t="s">
-        <v>664</v>
+        <v>222</v>
+      </c>
+      <c r="G126" s="28" t="s">
+        <v>646</v>
       </c>
       <c r="H126" s="15" t="s">
-        <v>556</v>
+        <v>549</v>
       </c>
     </row>
     <row r="127" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A127" s="42"/>
-      <c r="B127" s="47"/>
-      <c r="C127" s="28"/>
+      <c r="A127" s="35"/>
+      <c r="B127" s="42"/>
+      <c r="C127" s="29"/>
       <c r="D127" s="5" t="s">
         <v>131</v>
       </c>
@@ -5643,21 +5648,21 @@
         <v>0</v>
       </c>
       <c r="F127" s="5" t="s">
-        <v>558</v>
-      </c>
-      <c r="G127" s="32"/>
+        <v>551</v>
+      </c>
+      <c r="G127" s="28"/>
       <c r="H127" s="15" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
     </row>
     <row r="128" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A128" s="33">
+      <c r="A128" s="43">
         <v>40</v>
       </c>
-      <c r="B128" s="46" t="s">
+      <c r="B128" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="C128" s="28" t="s">
+      <c r="C128" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D128" s="5" t="s">
@@ -5667,17 +5672,17 @@
         <v>1</v>
       </c>
       <c r="F128" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="G128" s="32"/>
+        <v>244</v>
+      </c>
+      <c r="G128" s="28"/>
       <c r="H128" s="15" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
     <row r="129" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A129" s="34"/>
-      <c r="B129" s="47"/>
-      <c r="C129" s="28"/>
+      <c r="A129" s="44"/>
+      <c r="B129" s="42"/>
+      <c r="C129" s="29"/>
       <c r="D129" s="5" t="s">
         <v>79</v>
       </c>
@@ -5685,21 +5690,21 @@
         <v>1</v>
       </c>
       <c r="F129" s="5" t="s">
-        <v>492</v>
-      </c>
-      <c r="G129" s="32"/>
+        <v>487</v>
+      </c>
+      <c r="G129" s="28"/>
       <c r="H129" s="15" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
     </row>
     <row r="130" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A130" s="41">
+      <c r="A130" s="34">
         <v>41</v>
       </c>
-      <c r="B130" s="46" t="s">
+      <c r="B130" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="C130" s="43" t="s">
+      <c r="C130" s="32" t="s">
         <v>14</v>
       </c>
       <c r="D130" s="5" t="s">
@@ -5709,17 +5714,17 @@
         <v>1</v>
       </c>
       <c r="F130" s="5" t="s">
-        <v>646</v>
-      </c>
-      <c r="G130" s="32"/>
+        <v>633</v>
+      </c>
+      <c r="G130" s="28"/>
       <c r="H130" s="15" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
     </row>
     <row r="131" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A131" s="42"/>
-      <c r="B131" s="47"/>
-      <c r="C131" s="43"/>
+      <c r="A131" s="35"/>
+      <c r="B131" s="42"/>
+      <c r="C131" s="32"/>
       <c r="D131" s="5" t="s">
         <v>65</v>
       </c>
@@ -5727,21 +5732,21 @@
         <v>1</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>647</v>
-      </c>
-      <c r="G131" s="32"/>
+        <v>634</v>
+      </c>
+      <c r="G131" s="28"/>
       <c r="H131" s="15" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
     </row>
     <row r="132" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A132" s="33">
+      <c r="A132" s="34">
         <v>42</v>
       </c>
-      <c r="B132" s="36" t="s">
+      <c r="B132" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C132" s="28" t="s">
+      <c r="C132" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D132" s="5" t="s">
@@ -5751,17 +5756,17 @@
         <v>0</v>
       </c>
       <c r="F132" s="5" t="s">
-        <v>562</v>
-      </c>
-      <c r="G132" s="32"/>
+        <v>555</v>
+      </c>
+      <c r="G132" s="28"/>
       <c r="H132" s="15" t="s">
-        <v>560</v>
+        <v>553</v>
       </c>
     </row>
     <row r="133" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A133" s="34"/>
-      <c r="B133" s="36"/>
-      <c r="C133" s="28"/>
+      <c r="A133" s="35"/>
+      <c r="B133" s="33"/>
+      <c r="C133" s="29"/>
       <c r="D133" s="5" t="s">
         <v>51</v>
       </c>
@@ -5769,63 +5774,63 @@
         <v>0</v>
       </c>
       <c r="F133" s="5" t="s">
-        <v>559</v>
-      </c>
-      <c r="G133" s="32"/>
+        <v>552</v>
+      </c>
+      <c r="G133" s="28"/>
       <c r="H133" s="15" t="s">
-        <v>561</v>
+        <v>554</v>
       </c>
     </row>
     <row r="134" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A134" s="33">
+      <c r="A134" s="43">
         <v>43</v>
       </c>
-      <c r="B134" s="36" t="s">
+      <c r="B134" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C134" s="28" t="s">
+      <c r="C134" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
       <c r="E134" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>630</v>
-      </c>
-      <c r="G134" s="32"/>
+        <v>664</v>
+      </c>
+      <c r="G134" s="28"/>
       <c r="H134" s="15" t="s">
-        <v>631</v>
+        <v>620</v>
       </c>
     </row>
     <row r="135" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A135" s="34"/>
-      <c r="B135" s="36"/>
-      <c r="C135" s="28"/>
+      <c r="A135" s="44"/>
+      <c r="B135" s="33"/>
+      <c r="C135" s="29"/>
       <c r="D135" s="5" t="s">
-        <v>629</v>
+        <v>619</v>
       </c>
       <c r="E135" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>633</v>
-      </c>
-      <c r="G135" s="32"/>
+        <v>665</v>
+      </c>
+      <c r="G135" s="28"/>
       <c r="H135" s="15" t="s">
-        <v>632</v>
+        <v>621</v>
       </c>
     </row>
     <row r="136" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A136" s="33">
+      <c r="A136" s="43">
         <v>44</v>
       </c>
-      <c r="B136" s="36" t="s">
+      <c r="B136" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C136" s="28" t="s">
+      <c r="C136" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D136" s="5" t="s">
@@ -5835,17 +5840,17 @@
         <v>1</v>
       </c>
       <c r="F136" s="5" t="s">
-        <v>478</v>
-      </c>
-      <c r="G136" s="32"/>
+        <v>473</v>
+      </c>
+      <c r="G136" s="28"/>
       <c r="H136" s="15" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="137" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A137" s="34"/>
-      <c r="B137" s="36"/>
-      <c r="C137" s="28"/>
+      <c r="A137" s="44"/>
+      <c r="B137" s="33"/>
+      <c r="C137" s="29"/>
       <c r="D137" s="5" t="s">
         <v>49</v>
       </c>
@@ -5853,21 +5858,21 @@
         <v>1</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>479</v>
-      </c>
-      <c r="G137" s="32"/>
+        <v>474</v>
+      </c>
+      <c r="G137" s="28"/>
       <c r="H137" s="15" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
     </row>
     <row r="138" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A138" s="33">
+      <c r="A138" s="43">
         <v>45</v>
       </c>
-      <c r="B138" s="36" t="s">
+      <c r="B138" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C138" s="37" t="s">
+      <c r="C138" s="45" t="s">
         <v>14</v>
       </c>
       <c r="D138" s="5" t="s">
@@ -5877,17 +5882,17 @@
         <v>1</v>
       </c>
       <c r="F138" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="G138" s="32"/>
+        <v>212</v>
+      </c>
+      <c r="G138" s="28"/>
       <c r="H138" s="15" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
     </row>
     <row r="139" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A139" s="34"/>
-      <c r="B139" s="36"/>
-      <c r="C139" s="37"/>
+      <c r="A139" s="44"/>
+      <c r="B139" s="33"/>
+      <c r="C139" s="45"/>
       <c r="D139" s="5" t="s">
         <v>178</v>
       </c>
@@ -5895,25 +5900,25 @@
         <v>1</v>
       </c>
       <c r="F139" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="G139" s="32"/>
+        <v>211</v>
+      </c>
+      <c r="G139" s="28"/>
       <c r="H139" s="15" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
     </row>
     <row r="140" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A140" s="33">
+      <c r="A140" s="43">
         <v>46</v>
       </c>
-      <c r="B140" s="36" t="s">
+      <c r="B140" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C140" s="28" t="s">
+      <c r="C140" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E140" s="1">
         <v>0</v>
@@ -5921,19 +5926,19 @@
       <c r="F140" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="G140" s="32" t="s">
-        <v>211</v>
+      <c r="G140" s="28" t="s">
+        <v>210</v>
       </c>
       <c r="H140" s="15" t="s">
-        <v>539</v>
+        <v>532</v>
       </c>
     </row>
     <row r="141" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A141" s="34"/>
-      <c r="B141" s="36"/>
-      <c r="C141" s="28"/>
+      <c r="A141" s="44"/>
+      <c r="B141" s="33"/>
+      <c r="C141" s="29"/>
       <c r="D141" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E141" s="1">
         <v>0</v>
@@ -5941,19 +5946,19 @@
       <c r="F141" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="G141" s="32"/>
+      <c r="G141" s="28"/>
       <c r="H141" s="15" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
     </row>
     <row r="142" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A142" s="33">
+      <c r="A142" s="43">
         <v>47</v>
       </c>
-      <c r="B142" s="36" t="s">
+      <c r="B142" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C142" s="28" t="s">
+      <c r="C142" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D142" s="5" t="s">
@@ -5963,19 +5968,19 @@
         <v>1</v>
       </c>
       <c r="F142" s="5" t="s">
-        <v>480</v>
-      </c>
-      <c r="G142" s="32" t="s">
-        <v>545</v>
+        <v>475</v>
+      </c>
+      <c r="G142" s="28" t="s">
+        <v>538</v>
       </c>
       <c r="H142" s="15" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
     </row>
     <row r="143" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A143" s="34"/>
-      <c r="B143" s="36"/>
-      <c r="C143" s="28"/>
+      <c r="A143" s="44"/>
+      <c r="B143" s="33"/>
+      <c r="C143" s="29"/>
       <c r="D143" s="5" t="s">
         <v>165</v>
       </c>
@@ -5983,41 +5988,41 @@
         <v>1</v>
       </c>
       <c r="F143" s="5" t="s">
-        <v>481</v>
-      </c>
-      <c r="G143" s="32"/>
+        <v>476</v>
+      </c>
+      <c r="G143" s="28"/>
       <c r="H143" s="15" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
     </row>
     <row r="144" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A144" s="41">
+      <c r="A144" s="34">
         <v>48</v>
       </c>
-      <c r="B144" s="36" t="s">
+      <c r="B144" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C144" s="28" t="s">
+      <c r="C144" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D144" s="5" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="E144" s="1">
         <v>1</v>
       </c>
       <c r="F144" s="5" t="s">
-        <v>482</v>
-      </c>
-      <c r="G144" s="32"/>
+        <v>477</v>
+      </c>
+      <c r="G144" s="28"/>
       <c r="H144" s="15" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
     </row>
     <row r="145" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A145" s="42"/>
-      <c r="B145" s="36"/>
-      <c r="C145" s="28"/>
+      <c r="A145" s="35"/>
+      <c r="B145" s="33"/>
+      <c r="C145" s="29"/>
       <c r="D145" s="5" t="s">
         <v>55</v>
       </c>
@@ -6025,21 +6030,21 @@
         <v>0</v>
       </c>
       <c r="F145" s="5" t="s">
-        <v>482</v>
-      </c>
-      <c r="G145" s="32"/>
+        <v>477</v>
+      </c>
+      <c r="G145" s="28"/>
       <c r="H145" s="15" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
     </row>
     <row r="146" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A146" s="33">
+      <c r="A146" s="43">
         <v>49</v>
       </c>
-      <c r="B146" s="36" t="s">
+      <c r="B146" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C146" s="37" t="s">
+      <c r="C146" s="45" t="s">
         <v>14</v>
       </c>
       <c r="D146" s="5" t="s">
@@ -6049,19 +6054,19 @@
         <v>1</v>
       </c>
       <c r="F146" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="G146" s="32" t="s">
-        <v>545</v>
+        <v>199</v>
+      </c>
+      <c r="G146" s="28" t="s">
+        <v>538</v>
       </c>
       <c r="H146" s="15" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
     </row>
     <row r="147" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A147" s="34"/>
-      <c r="B147" s="36"/>
-      <c r="C147" s="37"/>
+      <c r="A147" s="44"/>
+      <c r="B147" s="33"/>
+      <c r="C147" s="45"/>
       <c r="D147" s="5" t="s">
         <v>57</v>
       </c>
@@ -6069,21 +6074,21 @@
         <v>0</v>
       </c>
       <c r="F147" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="G147" s="32"/>
+        <v>199</v>
+      </c>
+      <c r="G147" s="28"/>
       <c r="H147" s="15" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
     </row>
     <row r="148" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A148" s="41">
+      <c r="A148" s="34">
         <v>50</v>
       </c>
-      <c r="B148" s="36" t="s">
+      <c r="B148" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C148" s="43" t="s">
+      <c r="C148" s="32" t="s">
         <v>14</v>
       </c>
       <c r="D148" s="5" t="s">
@@ -6093,17 +6098,17 @@
         <v>1</v>
       </c>
       <c r="F148" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="G148" s="32"/>
+        <v>274</v>
+      </c>
+      <c r="G148" s="28"/>
       <c r="H148" s="15" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
     </row>
     <row r="149" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A149" s="42"/>
-      <c r="B149" s="36"/>
-      <c r="C149" s="43"/>
+      <c r="A149" s="35"/>
+      <c r="B149" s="33"/>
+      <c r="C149" s="32"/>
       <c r="D149" s="5" t="s">
         <v>59</v>
       </c>
@@ -6111,63 +6116,63 @@
         <v>0</v>
       </c>
       <c r="F149" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="G149" s="32"/>
+        <v>274</v>
+      </c>
+      <c r="G149" s="28"/>
       <c r="H149" s="15" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
     </row>
     <row r="150" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A150" s="41">
+      <c r="A150" s="34">
         <v>51</v>
       </c>
-      <c r="B150" s="36" t="s">
+      <c r="B150" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C150" s="28" t="s">
+      <c r="C150" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D150" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="E150" s="1">
+        <v>1</v>
+      </c>
+      <c r="F150" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="G150" s="28"/>
+      <c r="H150" s="15" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A151" s="35"/>
+      <c r="B151" s="33"/>
+      <c r="C151" s="29"/>
+      <c r="D151" s="5" t="s">
         <v>182</v>
-      </c>
-      <c r="E150" s="1">
-        <v>1</v>
-      </c>
-      <c r="F150" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="G150" s="32"/>
-      <c r="H150" s="15" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="151" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A151" s="42"/>
-      <c r="B151" s="36"/>
-      <c r="C151" s="28"/>
-      <c r="D151" s="5" t="s">
-        <v>183</v>
       </c>
       <c r="E151" s="1">
         <v>0</v>
       </c>
       <c r="F151" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="G151" s="32"/>
+        <v>183</v>
+      </c>
+      <c r="G151" s="28"/>
       <c r="H151" s="15" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
     </row>
     <row r="152" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A152" s="41">
+      <c r="A152" s="34">
         <v>52</v>
       </c>
-      <c r="B152" s="36" t="s">
+      <c r="B152" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C152" s="28" t="s">
+      <c r="C152" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D152" s="5" t="s">
@@ -6179,37 +6184,37 @@
       <c r="F152" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="G152" s="32"/>
+      <c r="G152" s="28"/>
       <c r="H152" s="15" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
     </row>
     <row r="153" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A153" s="42"/>
-      <c r="B153" s="36"/>
-      <c r="C153" s="28"/>
+      <c r="A153" s="35"/>
+      <c r="B153" s="33"/>
+      <c r="C153" s="29"/>
       <c r="D153" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E153" s="1">
         <v>0</v>
       </c>
       <c r="F153" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="G153" s="32"/>
+        <v>248</v>
+      </c>
+      <c r="G153" s="28"/>
       <c r="H153" s="15" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
     </row>
     <row r="154" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A154" s="33">
+      <c r="A154" s="43">
         <v>53</v>
       </c>
-      <c r="B154" s="36" t="s">
+      <c r="B154" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C154" s="28" t="s">
+      <c r="C154" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D154" s="5" t="s">
@@ -6219,19 +6224,19 @@
         <v>0</v>
       </c>
       <c r="F154" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="G154" s="32" t="s">
-        <v>610</v>
+        <v>252</v>
+      </c>
+      <c r="G154" s="28" t="s">
+        <v>602</v>
       </c>
       <c r="H154" s="15" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
     </row>
     <row r="155" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A155" s="34"/>
-      <c r="B155" s="36"/>
-      <c r="C155" s="28"/>
+      <c r="A155" s="44"/>
+      <c r="B155" s="33"/>
+      <c r="C155" s="29"/>
       <c r="D155" s="5" t="s">
         <v>63</v>
       </c>
@@ -6239,21 +6244,21 @@
         <v>0</v>
       </c>
       <c r="F155" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="G155" s="32"/>
+        <v>253</v>
+      </c>
+      <c r="G155" s="28"/>
       <c r="H155" s="15" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
     </row>
     <row r="156" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A156" s="33">
+      <c r="A156" s="43">
         <v>54</v>
       </c>
-      <c r="B156" s="36" t="s">
+      <c r="B156" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C156" s="28" t="s">
+      <c r="C156" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D156" s="5" t="s">
@@ -6265,15 +6270,15 @@
       <c r="F156" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="G156" s="32"/>
+      <c r="G156" s="28"/>
       <c r="H156" s="15" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="157" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A157" s="34"/>
-      <c r="B157" s="36"/>
-      <c r="C157" s="28"/>
+      <c r="A157" s="44"/>
+      <c r="B157" s="33"/>
+      <c r="C157" s="29"/>
       <c r="D157" s="5" t="s">
         <v>160</v>
       </c>
@@ -6283,19 +6288,19 @@
       <c r="F157" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="G157" s="32"/>
+      <c r="G157" s="28"/>
       <c r="H157" s="15" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
     </row>
     <row r="158" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A158" s="33">
+      <c r="A158" s="43">
         <v>55</v>
       </c>
-      <c r="B158" s="36" t="s">
+      <c r="B158" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C158" s="28" t="s">
+      <c r="C158" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D158" s="5" t="s">
@@ -6305,17 +6310,17 @@
         <v>1</v>
       </c>
       <c r="F158" s="5" t="s">
-        <v>564</v>
-      </c>
-      <c r="G158" s="32"/>
+        <v>557</v>
+      </c>
+      <c r="G158" s="28"/>
       <c r="H158" s="15" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
     </row>
     <row r="159" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A159" s="34"/>
-      <c r="B159" s="36"/>
-      <c r="C159" s="28"/>
+      <c r="A159" s="44"/>
+      <c r="B159" s="33"/>
+      <c r="C159" s="29"/>
       <c r="D159" s="5" t="s">
         <v>162</v>
       </c>
@@ -6323,21 +6328,21 @@
         <v>1</v>
       </c>
       <c r="F159" s="5" t="s">
-        <v>565</v>
-      </c>
-      <c r="G159" s="32"/>
+        <v>558</v>
+      </c>
+      <c r="G159" s="28"/>
       <c r="H159" s="15" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
     </row>
     <row r="160" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A160" s="33">
+      <c r="A160" s="43">
         <v>56</v>
       </c>
-      <c r="B160" s="36" t="s">
+      <c r="B160" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C160" s="28" t="s">
+      <c r="C160" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D160" s="5" t="s">
@@ -6347,19 +6352,19 @@
         <v>1</v>
       </c>
       <c r="F160" s="5" t="s">
-        <v>563</v>
-      </c>
-      <c r="G160" s="32" t="s">
-        <v>519</v>
+        <v>556</v>
+      </c>
+      <c r="G160" s="28" t="s">
+        <v>512</v>
       </c>
       <c r="H160" s="15" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
     </row>
     <row r="161" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A161" s="34"/>
-      <c r="B161" s="36"/>
-      <c r="C161" s="28"/>
+      <c r="A161" s="44"/>
+      <c r="B161" s="33"/>
+      <c r="C161" s="29"/>
       <c r="D161" s="5" t="s">
         <v>150</v>
       </c>
@@ -6367,21 +6372,21 @@
         <v>0</v>
       </c>
       <c r="F161" s="5" t="s">
-        <v>563</v>
-      </c>
-      <c r="G161" s="32"/>
+        <v>556</v>
+      </c>
+      <c r="G161" s="28"/>
       <c r="H161" s="15" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
     </row>
     <row r="162" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A162" s="33">
+      <c r="A162" s="43">
         <v>57</v>
       </c>
-      <c r="B162" s="36" t="s">
+      <c r="B162" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C162" s="28" t="s">
+      <c r="C162" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D162" s="5" t="s">
@@ -6391,19 +6396,19 @@
         <v>0</v>
       </c>
       <c r="F162" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="G162" s="32" t="s">
-        <v>550</v>
+        <v>277</v>
+      </c>
+      <c r="G162" s="28" t="s">
+        <v>543</v>
       </c>
       <c r="H162" s="15" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
     </row>
     <row r="163" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A163" s="34"/>
-      <c r="B163" s="36"/>
-      <c r="C163" s="28"/>
+      <c r="A163" s="44"/>
+      <c r="B163" s="33"/>
+      <c r="C163" s="29"/>
       <c r="D163" s="5" t="s">
         <v>170</v>
       </c>
@@ -6411,21 +6416,21 @@
         <v>0</v>
       </c>
       <c r="F163" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="G163" s="32"/>
+        <v>278</v>
+      </c>
+      <c r="G163" s="28"/>
       <c r="H163" s="15" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
     </row>
     <row r="164" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A164" s="33">
+      <c r="A164" s="43">
         <v>58</v>
       </c>
-      <c r="B164" s="36" t="s">
+      <c r="B164" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C164" s="37" t="s">
+      <c r="C164" s="45" t="s">
         <v>14</v>
       </c>
       <c r="D164" s="5" t="s">
@@ -6435,17 +6440,17 @@
         <v>0</v>
       </c>
       <c r="F164" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="G164" s="32"/>
+        <v>279</v>
+      </c>
+      <c r="G164" s="28"/>
       <c r="H164" s="15" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
     </row>
     <row r="165" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A165" s="34"/>
-      <c r="B165" s="36"/>
-      <c r="C165" s="37"/>
+      <c r="A165" s="44"/>
+      <c r="B165" s="33"/>
+      <c r="C165" s="45"/>
       <c r="D165" s="5" t="s">
         <v>172</v>
       </c>
@@ -6453,21 +6458,21 @@
         <v>0</v>
       </c>
       <c r="F165" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="G165" s="32"/>
+        <v>280</v>
+      </c>
+      <c r="G165" s="28"/>
       <c r="H165" s="15" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
     </row>
     <row r="166" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A166" s="33">
+      <c r="A166" s="43">
         <v>59</v>
       </c>
-      <c r="B166" s="36" t="s">
+      <c r="B166" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C166" s="37" t="s">
+      <c r="C166" s="45" t="s">
         <v>14</v>
       </c>
       <c r="D166" s="5" t="s">
@@ -6477,19 +6482,19 @@
         <v>1</v>
       </c>
       <c r="F166" s="5" t="s">
-        <v>655</v>
-      </c>
-      <c r="G166" s="32" t="s">
-        <v>193</v>
+        <v>639</v>
+      </c>
+      <c r="G166" s="28" t="s">
+        <v>192</v>
       </c>
       <c r="H166" s="15" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
     </row>
     <row r="167" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A167" s="34"/>
-      <c r="B167" s="36"/>
-      <c r="C167" s="37"/>
+      <c r="A167" s="44"/>
+      <c r="B167" s="33"/>
+      <c r="C167" s="45"/>
       <c r="D167" s="5" t="s">
         <v>142</v>
       </c>
@@ -6497,21 +6502,21 @@
         <v>0</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>655</v>
-      </c>
-      <c r="G167" s="32"/>
+        <v>639</v>
+      </c>
+      <c r="G167" s="28"/>
       <c r="H167" s="15" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
     </row>
     <row r="168" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A168" s="33">
+      <c r="A168" s="43">
         <v>60</v>
       </c>
-      <c r="B168" s="36" t="s">
+      <c r="B168" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C168" s="37" t="s">
+      <c r="C168" s="45" t="s">
         <v>14</v>
       </c>
       <c r="D168" s="5" t="s">
@@ -6521,17 +6526,17 @@
         <v>1</v>
       </c>
       <c r="F168" s="5" t="s">
-        <v>656</v>
-      </c>
-      <c r="G168" s="32"/>
+        <v>640</v>
+      </c>
+      <c r="G168" s="28"/>
       <c r="H168" s="15" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
     </row>
     <row r="169" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A169" s="34"/>
-      <c r="B169" s="36"/>
-      <c r="C169" s="37"/>
+      <c r="A169" s="44"/>
+      <c r="B169" s="33"/>
+      <c r="C169" s="45"/>
       <c r="D169" s="5" t="s">
         <v>116</v>
       </c>
@@ -6539,21 +6544,21 @@
         <v>0</v>
       </c>
       <c r="F169" s="5" t="s">
-        <v>657</v>
-      </c>
-      <c r="G169" s="32"/>
+        <v>641</v>
+      </c>
+      <c r="G169" s="28"/>
       <c r="H169" s="15" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
     </row>
     <row r="170" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A170" s="33">
+      <c r="A170" s="34">
         <v>61</v>
       </c>
-      <c r="B170" s="36" t="s">
+      <c r="B170" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C170" s="28" t="s">
+      <c r="C170" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D170" s="5" t="s">
@@ -6563,17 +6568,19 @@
         <v>2</v>
       </c>
       <c r="F170" s="5" t="s">
-        <v>620</v>
-      </c>
-      <c r="G170" s="32"/>
+        <v>611</v>
+      </c>
+      <c r="G170" s="28" t="s">
+        <v>657</v>
+      </c>
       <c r="H170" s="15" t="s">
-        <v>296</v>
+        <v>655</v>
       </c>
     </row>
     <row r="171" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A171" s="34"/>
-      <c r="B171" s="36"/>
-      <c r="C171" s="28"/>
+      <c r="A171" s="35"/>
+      <c r="B171" s="33"/>
+      <c r="C171" s="29"/>
       <c r="D171" s="5" t="s">
         <v>81</v>
       </c>
@@ -6581,107 +6588,107 @@
         <v>2</v>
       </c>
       <c r="F171" s="5" t="s">
-        <v>621</v>
-      </c>
-      <c r="G171" s="32"/>
+        <v>612</v>
+      </c>
+      <c r="G171" s="28"/>
       <c r="H171" s="15" t="s">
-        <v>427</v>
+        <v>656</v>
       </c>
     </row>
     <row r="172" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A172" s="41">
+      <c r="A172" s="34">
         <v>62</v>
       </c>
-      <c r="B172" s="36" t="s">
+      <c r="B172" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C172" s="43" t="s">
+      <c r="C172" s="32" t="s">
         <v>14</v>
       </c>
       <c r="D172" s="5" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="E172" s="1">
         <v>1</v>
       </c>
       <c r="F172" s="5" t="s">
-        <v>537</v>
-      </c>
-      <c r="G172" s="32"/>
+        <v>530</v>
+      </c>
+      <c r="G172" s="28"/>
       <c r="H172" s="15" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
     </row>
     <row r="173" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A173" s="42"/>
-      <c r="B173" s="36"/>
-      <c r="C173" s="43"/>
+      <c r="A173" s="35"/>
+      <c r="B173" s="33"/>
+      <c r="C173" s="32"/>
       <c r="D173" s="5" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="E173" s="1">
         <v>1</v>
       </c>
       <c r="F173" s="5" t="s">
-        <v>538</v>
-      </c>
-      <c r="G173" s="32"/>
+        <v>531</v>
+      </c>
+      <c r="G173" s="28"/>
       <c r="H173" s="15" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
     </row>
     <row r="174" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A174" s="33">
+      <c r="A174" s="43">
         <v>63</v>
       </c>
-      <c r="B174" s="36" t="s">
+      <c r="B174" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C174" s="37" t="s">
+      <c r="C174" s="45" t="s">
         <v>14</v>
       </c>
       <c r="D174" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="E174" s="1">
+        <v>1</v>
+      </c>
+      <c r="F174" s="5" t="s">
+        <v>659</v>
+      </c>
+      <c r="G174" s="28" t="s">
+        <v>576</v>
+      </c>
+      <c r="H174" s="15" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A175" s="44"/>
+      <c r="B175" s="33"/>
+      <c r="C175" s="45"/>
+      <c r="D175" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="E174" s="1">
-        <v>1</v>
-      </c>
-      <c r="F174" s="5" t="s">
-        <v>584</v>
-      </c>
-      <c r="G174" s="32" t="s">
-        <v>583</v>
-      </c>
-      <c r="H174" s="15" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="175" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A175" s="34"/>
-      <c r="B175" s="36"/>
-      <c r="C175" s="37"/>
-      <c r="D175" s="5" t="s">
-        <v>196</v>
-      </c>
       <c r="E175" s="1">
         <v>1</v>
       </c>
       <c r="F175" s="5" t="s">
-        <v>585</v>
-      </c>
-      <c r="G175" s="32"/>
+        <v>577</v>
+      </c>
+      <c r="G175" s="28"/>
       <c r="H175" s="15" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
     </row>
     <row r="176" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A176" s="33">
+      <c r="A176" s="43">
         <v>64</v>
       </c>
-      <c r="B176" s="36" t="s">
+      <c r="B176" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C176" s="28" t="s">
+      <c r="C176" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D176" s="5" t="s">
@@ -6691,19 +6698,19 @@
         <v>1</v>
       </c>
       <c r="F176" s="5" t="s">
-        <v>493</v>
-      </c>
-      <c r="G176" s="32" t="s">
+        <v>654</v>
+      </c>
+      <c r="G176" s="28" t="s">
         <v>112</v>
       </c>
       <c r="H176" s="15" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="177" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A177" s="34"/>
-      <c r="B177" s="36"/>
-      <c r="C177" s="28"/>
+      <c r="A177" s="44"/>
+      <c r="B177" s="33"/>
+      <c r="C177" s="29"/>
       <c r="D177" s="5" t="s">
         <v>111</v>
       </c>
@@ -6711,63 +6718,63 @@
         <v>1</v>
       </c>
       <c r="F177" s="5" t="s">
-        <v>494</v>
-      </c>
-      <c r="G177" s="32"/>
+        <v>653</v>
+      </c>
+      <c r="G177" s="28"/>
       <c r="H177" s="15" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
     </row>
     <row r="178" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A178" s="33">
+      <c r="A178" s="43">
         <v>65</v>
       </c>
-      <c r="B178" s="35" t="s">
+      <c r="B178" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C178" s="28" t="s">
+      <c r="C178" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D178" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="E178" s="1">
+        <v>1</v>
+      </c>
+      <c r="F178" s="5" t="s">
+        <v>660</v>
+      </c>
+      <c r="G178" s="28"/>
+      <c r="H178" s="15" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A179" s="44"/>
+      <c r="B179" s="31"/>
+      <c r="C179" s="29"/>
+      <c r="D179" s="5" t="s">
+        <v>609</v>
+      </c>
+      <c r="E179" s="1">
+        <v>1</v>
+      </c>
+      <c r="F179" s="5" t="s">
+        <v>610</v>
+      </c>
+      <c r="G179" s="28"/>
+      <c r="H179" s="15" t="s">
         <v>617</v>
       </c>
-      <c r="E178" s="1">
-        <v>1</v>
-      </c>
-      <c r="F178" s="5" t="s">
-        <v>616</v>
-      </c>
-      <c r="G178" s="32"/>
-      <c r="H178" s="15" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="179" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A179" s="34"/>
-      <c r="B179" s="35"/>
-      <c r="C179" s="28"/>
-      <c r="D179" s="5" t="s">
-        <v>618</v>
-      </c>
-      <c r="E179" s="1">
-        <v>1</v>
-      </c>
-      <c r="F179" s="5" t="s">
-        <v>619</v>
-      </c>
-      <c r="G179" s="32"/>
-      <c r="H179" s="15" t="s">
-        <v>627</v>
-      </c>
     </row>
     <row r="180" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A180" s="33">
+      <c r="A180" s="43">
         <v>66</v>
       </c>
-      <c r="B180" s="35" t="s">
+      <c r="B180" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C180" s="28" t="s">
+      <c r="C180" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D180" s="5" t="s">
@@ -6777,17 +6784,17 @@
         <v>1</v>
       </c>
       <c r="F180" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="G180" s="32"/>
+        <v>250</v>
+      </c>
+      <c r="G180" s="28"/>
       <c r="H180" s="15" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="181" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A181" s="34"/>
-      <c r="B181" s="35"/>
-      <c r="C181" s="28"/>
+      <c r="A181" s="44"/>
+      <c r="B181" s="31"/>
+      <c r="C181" s="29"/>
       <c r="D181" s="5" t="s">
         <v>61</v>
       </c>
@@ -6795,21 +6802,21 @@
         <v>1</v>
       </c>
       <c r="F181" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="G181" s="32"/>
+        <v>251</v>
+      </c>
+      <c r="G181" s="28"/>
       <c r="H181" s="15" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
     </row>
     <row r="182" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A182" s="33">
+      <c r="A182" s="43">
         <v>67</v>
       </c>
-      <c r="B182" s="35" t="s">
+      <c r="B182" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C182" s="28" t="s">
+      <c r="C182" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D182" s="5" t="s">
@@ -6819,17 +6826,17 @@
         <v>3</v>
       </c>
       <c r="F182" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="G182" s="32"/>
+        <v>200</v>
+      </c>
+      <c r="G182" s="28"/>
       <c r="H182" s="15" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
     </row>
     <row r="183" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A183" s="34"/>
-      <c r="B183" s="35"/>
-      <c r="C183" s="28"/>
+      <c r="A183" s="44"/>
+      <c r="B183" s="31"/>
+      <c r="C183" s="29"/>
       <c r="D183" s="5" t="s">
         <v>69</v>
       </c>
@@ -6837,63 +6844,63 @@
         <v>3</v>
       </c>
       <c r="F183" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="G183" s="32"/>
+        <v>201</v>
+      </c>
+      <c r="G183" s="28"/>
       <c r="H183" s="15" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
     </row>
     <row r="184" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A184" s="33">
+      <c r="A184" s="43">
         <v>68</v>
       </c>
-      <c r="B184" s="35" t="s">
+      <c r="B184" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C184" s="28" t="s">
+      <c r="C184" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D184" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E184" s="1">
         <v>3</v>
       </c>
       <c r="F184" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="G184" s="32"/>
+        <v>225</v>
+      </c>
+      <c r="G184" s="28"/>
       <c r="H184" s="15" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
     </row>
     <row r="185" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A185" s="34"/>
-      <c r="B185" s="35"/>
-      <c r="C185" s="28"/>
+      <c r="A185" s="44"/>
+      <c r="B185" s="31"/>
+      <c r="C185" s="29"/>
       <c r="D185" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E185" s="1">
         <v>2</v>
       </c>
       <c r="F185" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="G185" s="32"/>
+        <v>225</v>
+      </c>
+      <c r="G185" s="28"/>
       <c r="H185" s="15" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
     </row>
     <row r="186" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A186" s="33">
+      <c r="A186" s="43">
         <v>69</v>
       </c>
-      <c r="B186" s="35" t="s">
+      <c r="B186" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C186" s="28" t="s">
+      <c r="C186" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D186" s="5" t="s">
@@ -6903,17 +6910,17 @@
         <v>3</v>
       </c>
       <c r="F186" s="5" t="s">
-        <v>645</v>
-      </c>
-      <c r="G186" s="32"/>
+        <v>632</v>
+      </c>
+      <c r="G186" s="28"/>
       <c r="H186" s="15" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
     </row>
     <row r="187" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A187" s="34"/>
-      <c r="B187" s="35"/>
-      <c r="C187" s="28"/>
+      <c r="A187" s="44"/>
+      <c r="B187" s="31"/>
+      <c r="C187" s="29"/>
       <c r="D187" s="5" t="s">
         <v>71</v>
       </c>
@@ -6921,63 +6928,63 @@
         <v>2</v>
       </c>
       <c r="F187" s="5" t="s">
-        <v>645</v>
-      </c>
-      <c r="G187" s="32"/>
+        <v>632</v>
+      </c>
+      <c r="G187" s="28"/>
       <c r="H187" s="15" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
     </row>
     <row r="188" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A188" s="33">
+      <c r="A188" s="43">
         <v>70</v>
       </c>
-      <c r="B188" s="35" t="s">
+      <c r="B188" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C188" s="37" t="s">
+      <c r="C188" s="45" t="s">
         <v>14</v>
       </c>
       <c r="D188" s="5" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="E188" s="1">
         <v>0</v>
       </c>
       <c r="F188" s="5" t="s">
-        <v>441</v>
-      </c>
-      <c r="G188" s="32"/>
+        <v>436</v>
+      </c>
+      <c r="G188" s="28"/>
       <c r="H188" s="15" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
     </row>
     <row r="189" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A189" s="34"/>
-      <c r="B189" s="35"/>
-      <c r="C189" s="37"/>
+      <c r="A189" s="44"/>
+      <c r="B189" s="31"/>
+      <c r="C189" s="45"/>
       <c r="D189" s="5" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="E189" s="1">
         <v>0</v>
       </c>
       <c r="F189" s="5" t="s">
-        <v>442</v>
-      </c>
-      <c r="G189" s="32"/>
+        <v>437</v>
+      </c>
+      <c r="G189" s="28"/>
       <c r="H189" s="15" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
     </row>
     <row r="190" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A190" s="33">
+      <c r="A190" s="43">
         <v>71</v>
       </c>
-      <c r="B190" s="35" t="s">
+      <c r="B190" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C190" s="37" t="s">
+      <c r="C190" s="45" t="s">
         <v>14</v>
       </c>
       <c r="D190" s="5" t="s">
@@ -6987,19 +6994,19 @@
         <v>0</v>
       </c>
       <c r="F190" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="G190" s="32" t="s">
-        <v>545</v>
+        <v>255</v>
+      </c>
+      <c r="G190" s="28" t="s">
+        <v>538</v>
       </c>
       <c r="H190" s="15" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
     <row r="191" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A191" s="34"/>
-      <c r="B191" s="35"/>
-      <c r="C191" s="37"/>
+      <c r="A191" s="44"/>
+      <c r="B191" s="31"/>
+      <c r="C191" s="45"/>
       <c r="D191" s="5" t="s">
         <v>85</v>
       </c>
@@ -7007,63 +7014,63 @@
         <v>0</v>
       </c>
       <c r="F191" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="G191" s="32"/>
+        <v>256</v>
+      </c>
+      <c r="G191" s="28"/>
       <c r="H191" s="15" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
     </row>
     <row r="192" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A192" s="33">
+      <c r="A192" s="43">
         <v>72</v>
       </c>
-      <c r="B192" s="35" t="s">
+      <c r="B192" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C192" s="37" t="s">
+      <c r="C192" s="45" t="s">
         <v>14</v>
       </c>
       <c r="D192" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E192" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F192" s="5" t="s">
-        <v>654</v>
-      </c>
-      <c r="G192" s="32"/>
+        <v>661</v>
+      </c>
+      <c r="G192" s="28"/>
       <c r="H192" s="15" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
     </row>
     <row r="193" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A193" s="34"/>
-      <c r="B193" s="35"/>
-      <c r="C193" s="37"/>
+      <c r="A193" s="44"/>
+      <c r="B193" s="31"/>
+      <c r="C193" s="45"/>
       <c r="D193" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E193" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F193" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="G193" s="32"/>
+        <v>220</v>
+      </c>
+      <c r="G193" s="28"/>
       <c r="H193" s="15" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
     </row>
     <row r="194" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A194" s="33">
+      <c r="A194" s="43">
         <v>73</v>
       </c>
-      <c r="B194" s="35" t="s">
+      <c r="B194" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C194" s="28" t="s">
+      <c r="C194" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D194" s="5" t="s">
@@ -7073,19 +7080,19 @@
         <v>4</v>
       </c>
       <c r="F194" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="G194" s="32" t="s">
-        <v>210</v>
+        <v>281</v>
+      </c>
+      <c r="G194" s="28" t="s">
+        <v>209</v>
       </c>
       <c r="H194" s="15" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="195" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A195" s="34"/>
-      <c r="B195" s="35"/>
-      <c r="C195" s="28"/>
+      <c r="A195" s="44"/>
+      <c r="B195" s="31"/>
+      <c r="C195" s="29"/>
       <c r="D195" s="5" t="s">
         <v>129</v>
       </c>
@@ -7093,21 +7100,21 @@
         <v>4</v>
       </c>
       <c r="F195" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="G195" s="32"/>
+        <v>282</v>
+      </c>
+      <c r="G195" s="28"/>
       <c r="H195" s="15" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
     </row>
     <row r="196" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A196" s="33">
+      <c r="A196" s="43">
         <v>74</v>
       </c>
-      <c r="B196" s="35" t="s">
+      <c r="B196" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C196" s="28" t="s">
+      <c r="C196" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D196" s="5" t="s">
@@ -7117,19 +7124,19 @@
         <v>1</v>
       </c>
       <c r="F196" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="G196" s="32" t="s">
+        <v>662</v>
+      </c>
+      <c r="G196" s="28" t="s">
         <v>138</v>
       </c>
       <c r="H196" s="15" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
     </row>
     <row r="197" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A197" s="34"/>
-      <c r="B197" s="35"/>
-      <c r="C197" s="28"/>
+      <c r="A197" s="44"/>
+      <c r="B197" s="31"/>
+      <c r="C197" s="29"/>
       <c r="D197" s="5" t="s">
         <v>107</v>
       </c>
@@ -7137,21 +7144,21 @@
         <v>1</v>
       </c>
       <c r="F197" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="G197" s="32"/>
+        <v>663</v>
+      </c>
+      <c r="G197" s="28"/>
       <c r="H197" s="15" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
     </row>
     <row r="198" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A198" s="41">
+      <c r="A198" s="34">
         <v>75</v>
       </c>
-      <c r="B198" s="36" t="s">
+      <c r="B198" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C198" s="28" t="s">
+      <c r="C198" s="29" t="s">
         <v>86</v>
       </c>
       <c r="D198" s="5" t="s">
@@ -7161,19 +7168,19 @@
         <v>2</v>
       </c>
       <c r="F198" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="G198" s="32" t="s">
-        <v>577</v>
+        <v>283</v>
+      </c>
+      <c r="G198" s="28" t="s">
+        <v>570</v>
       </c>
       <c r="H198" s="15" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
     </row>
     <row r="199" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A199" s="42"/>
-      <c r="B199" s="36"/>
-      <c r="C199" s="28"/>
+      <c r="A199" s="35"/>
+      <c r="B199" s="33"/>
+      <c r="C199" s="29"/>
       <c r="D199" s="5" t="s">
         <v>92</v>
       </c>
@@ -7181,21 +7188,21 @@
         <v>1</v>
       </c>
       <c r="F199" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="G199" s="32"/>
+        <v>283</v>
+      </c>
+      <c r="G199" s="28"/>
       <c r="H199" s="15" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
     </row>
     <row r="200" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A200" s="33">
+      <c r="A200" s="43">
         <v>76</v>
       </c>
-      <c r="B200" s="36" t="s">
+      <c r="B200" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C200" s="28" t="s">
+      <c r="C200" s="29" t="s">
         <v>86</v>
       </c>
       <c r="D200" s="5" t="s">
@@ -7205,19 +7212,19 @@
         <v>1</v>
       </c>
       <c r="F200" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="G200" s="32" t="s">
-        <v>217</v>
+        <v>214</v>
+      </c>
+      <c r="G200" s="28" t="s">
+        <v>216</v>
       </c>
       <c r="H200" s="15" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
     </row>
     <row r="201" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A201" s="34"/>
-      <c r="B201" s="36"/>
-      <c r="C201" s="28"/>
+      <c r="A201" s="44"/>
+      <c r="B201" s="33"/>
+      <c r="C201" s="29"/>
       <c r="D201" s="5" t="s">
         <v>104</v>
       </c>
@@ -7225,21 +7232,21 @@
         <v>1</v>
       </c>
       <c r="F201" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="G201" s="32"/>
+        <v>215</v>
+      </c>
+      <c r="G201" s="28"/>
       <c r="H201" s="15" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
     </row>
     <row r="202" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A202" s="41">
+      <c r="A202" s="34">
         <v>77</v>
       </c>
-      <c r="B202" s="36" t="s">
+      <c r="B202" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C202" s="28" t="s">
+      <c r="C202" s="29" t="s">
         <v>86</v>
       </c>
       <c r="D202" s="5" t="s">
@@ -7249,19 +7256,19 @@
         <v>2</v>
       </c>
       <c r="F202" s="5" t="s">
-        <v>552</v>
-      </c>
-      <c r="G202" s="32" t="s">
-        <v>575</v>
+        <v>545</v>
+      </c>
+      <c r="G202" s="28" t="s">
+        <v>568</v>
       </c>
       <c r="H202" s="15" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
     </row>
     <row r="203" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A203" s="42"/>
-      <c r="B203" s="36"/>
-      <c r="C203" s="28"/>
+      <c r="A203" s="35"/>
+      <c r="B203" s="33"/>
+      <c r="C203" s="29"/>
       <c r="D203" s="5" t="s">
         <v>109</v>
       </c>
@@ -7269,21 +7276,21 @@
         <v>2</v>
       </c>
       <c r="F203" s="5" t="s">
-        <v>553</v>
-      </c>
-      <c r="G203" s="32"/>
+        <v>546</v>
+      </c>
+      <c r="G203" s="28"/>
       <c r="H203" s="15" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
     </row>
     <row r="204" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A204" s="33">
+      <c r="A204" s="43">
         <v>78</v>
       </c>
-      <c r="B204" s="36" t="s">
+      <c r="B204" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C204" s="28" t="s">
+      <c r="C204" s="29" t="s">
         <v>86</v>
       </c>
       <c r="D204" s="5" t="s">
@@ -7293,17 +7300,17 @@
         <v>1</v>
       </c>
       <c r="F204" s="5" t="s">
-        <v>581</v>
-      </c>
-      <c r="G204" s="32"/>
+        <v>574</v>
+      </c>
+      <c r="G204" s="28"/>
       <c r="H204" s="15" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="205" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A205" s="34"/>
-      <c r="B205" s="36"/>
-      <c r="C205" s="28"/>
+      <c r="A205" s="44"/>
+      <c r="B205" s="33"/>
+      <c r="C205" s="29"/>
       <c r="D205" s="5" t="s">
         <v>88</v>
       </c>
@@ -7311,21 +7318,21 @@
         <v>1</v>
       </c>
       <c r="F205" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="G205" s="32"/>
+        <v>238</v>
+      </c>
+      <c r="G205" s="28"/>
       <c r="H205" s="15" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
     </row>
     <row r="206" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A206" s="33">
+      <c r="A206" s="43">
         <v>79</v>
       </c>
-      <c r="B206" s="36" t="s">
+      <c r="B206" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C206" s="28" t="s">
+      <c r="C206" s="29" t="s">
         <v>86</v>
       </c>
       <c r="D206" s="5" t="s">
@@ -7335,17 +7342,17 @@
         <v>1</v>
       </c>
       <c r="F206" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="G206" s="32"/>
+        <v>239</v>
+      </c>
+      <c r="G206" s="28"/>
       <c r="H206" s="15" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
     </row>
     <row r="207" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A207" s="34"/>
-      <c r="B207" s="36"/>
-      <c r="C207" s="28"/>
+      <c r="A207" s="44"/>
+      <c r="B207" s="33"/>
+      <c r="C207" s="29"/>
       <c r="D207" s="5" t="s">
         <v>90</v>
       </c>
@@ -7353,21 +7360,21 @@
         <v>0</v>
       </c>
       <c r="F207" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="G207" s="32"/>
+        <v>239</v>
+      </c>
+      <c r="G207" s="28"/>
       <c r="H207" s="15" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
     </row>
     <row r="208" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A208" s="33">
+      <c r="A208" s="43">
         <v>80</v>
       </c>
-      <c r="B208" s="36" t="s">
+      <c r="B208" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C208" s="28" t="s">
+      <c r="C208" s="29" t="s">
         <v>86</v>
       </c>
       <c r="D208" s="5" t="s">
@@ -7377,19 +7384,19 @@
         <v>1</v>
       </c>
       <c r="F208" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="G208" s="32" t="s">
-        <v>235</v>
+        <v>226</v>
+      </c>
+      <c r="G208" s="28" t="s">
+        <v>234</v>
       </c>
       <c r="H208" s="15" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
     </row>
     <row r="209" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A209" s="34"/>
-      <c r="B209" s="36"/>
-      <c r="C209" s="28"/>
+      <c r="A209" s="44"/>
+      <c r="B209" s="33"/>
+      <c r="C209" s="29"/>
       <c r="D209" s="5" t="s">
         <v>102</v>
       </c>
@@ -7397,21 +7404,21 @@
         <v>1</v>
       </c>
       <c r="F209" s="5" t="s">
-        <v>572</v>
-      </c>
-      <c r="G209" s="32"/>
+        <v>565</v>
+      </c>
+      <c r="G209" s="28"/>
       <c r="H209" s="15" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
     </row>
     <row r="210" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A210" s="41">
+      <c r="A210" s="34">
         <v>81</v>
       </c>
-      <c r="B210" s="36" t="s">
+      <c r="B210" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C210" s="28" t="s">
+      <c r="C210" s="29" t="s">
         <v>86</v>
       </c>
       <c r="D210" s="5" t="s">
@@ -7421,19 +7428,19 @@
         <v>1</v>
       </c>
       <c r="F210" s="5" t="s">
-        <v>601</v>
-      </c>
-      <c r="G210" s="32" t="s">
-        <v>573</v>
+        <v>593</v>
+      </c>
+      <c r="G210" s="28" t="s">
+        <v>566</v>
       </c>
       <c r="H210" s="15" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
     </row>
     <row r="211" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A211" s="42"/>
-      <c r="B211" s="36"/>
-      <c r="C211" s="28"/>
+      <c r="A211" s="35"/>
+      <c r="B211" s="33"/>
+      <c r="C211" s="29"/>
       <c r="D211" s="5" t="s">
         <v>96</v>
       </c>
@@ -7441,21 +7448,21 @@
         <v>1</v>
       </c>
       <c r="F211" s="5" t="s">
-        <v>602</v>
-      </c>
-      <c r="G211" s="32"/>
+        <v>594</v>
+      </c>
+      <c r="G211" s="28"/>
       <c r="H211" s="15" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
     </row>
     <row r="212" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A212" s="33">
+      <c r="A212" s="43">
         <v>82</v>
       </c>
-      <c r="B212" s="44" t="s">
+      <c r="B212" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="C212" s="28" t="s">
+      <c r="C212" s="29" t="s">
         <v>86</v>
       </c>
       <c r="D212" s="5" t="s">
@@ -7465,17 +7472,17 @@
         <v>1</v>
       </c>
       <c r="F212" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="G212" s="32"/>
+        <v>257</v>
+      </c>
+      <c r="G212" s="28"/>
       <c r="H212" s="15" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
     </row>
     <row r="213" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A213" s="34"/>
-      <c r="B213" s="45"/>
-      <c r="C213" s="28"/>
+      <c r="A213" s="44"/>
+      <c r="B213" s="49"/>
+      <c r="C213" s="29"/>
       <c r="D213" s="5" t="s">
         <v>174</v>
       </c>
@@ -7483,21 +7490,21 @@
         <v>0</v>
       </c>
       <c r="F213" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="G213" s="32"/>
+        <v>257</v>
+      </c>
+      <c r="G213" s="28"/>
       <c r="H213" s="15" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
     </row>
     <row r="214" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A214" s="33">
+      <c r="A214" s="43">
         <v>83</v>
       </c>
-      <c r="B214" s="35" t="s">
+      <c r="B214" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C214" s="28" t="s">
+      <c r="C214" s="29" t="s">
         <v>86</v>
       </c>
       <c r="D214" s="5" t="s">
@@ -7507,19 +7514,19 @@
         <v>2</v>
       </c>
       <c r="F214" s="5" t="s">
-        <v>544</v>
-      </c>
-      <c r="G214" s="32" t="s">
-        <v>576</v>
+        <v>537</v>
+      </c>
+      <c r="G214" s="28" t="s">
+        <v>569</v>
       </c>
       <c r="H214" s="15" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
     </row>
     <row r="215" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A215" s="34"/>
-      <c r="B215" s="35"/>
-      <c r="C215" s="28"/>
+      <c r="A215" s="44"/>
+      <c r="B215" s="31"/>
+      <c r="C215" s="29"/>
       <c r="D215" s="5" t="s">
         <v>135</v>
       </c>
@@ -7527,21 +7534,21 @@
         <v>1</v>
       </c>
       <c r="F215" s="5" t="s">
-        <v>551</v>
-      </c>
-      <c r="G215" s="32"/>
+        <v>544</v>
+      </c>
+      <c r="G215" s="28"/>
       <c r="H215" s="15" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
     </row>
     <row r="216" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A216" s="33">
+      <c r="A216" s="43">
         <v>84</v>
       </c>
-      <c r="B216" s="35" t="s">
+      <c r="B216" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C216" s="28" t="s">
+      <c r="C216" s="29" t="s">
         <v>86</v>
       </c>
       <c r="D216" s="5" t="s">
@@ -7551,19 +7558,19 @@
         <v>2</v>
       </c>
       <c r="F216" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="G216" s="32" t="s">
-        <v>288</v>
+        <v>242</v>
+      </c>
+      <c r="G216" s="28" t="s">
+        <v>285</v>
       </c>
       <c r="H216" s="15" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="217" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A217" s="34"/>
-      <c r="B217" s="35"/>
-      <c r="C217" s="28"/>
+      <c r="A217" s="44"/>
+      <c r="B217" s="31"/>
+      <c r="C217" s="29"/>
       <c r="D217" s="5" t="s">
         <v>94</v>
       </c>
@@ -7571,21 +7578,21 @@
         <v>2</v>
       </c>
       <c r="F217" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="G217" s="32"/>
+        <v>243</v>
+      </c>
+      <c r="G217" s="28"/>
       <c r="H217" s="15" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
     </row>
     <row r="218" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A218" s="33">
+      <c r="A218" s="43">
         <v>85</v>
       </c>
-      <c r="B218" s="35" t="s">
+      <c r="B218" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C218" s="28" t="s">
+      <c r="C218" s="29" t="s">
         <v>86</v>
       </c>
       <c r="D218" s="5" t="s">
@@ -7595,17 +7602,17 @@
         <v>3</v>
       </c>
       <c r="F218" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="G218" s="32"/>
+        <v>213</v>
+      </c>
+      <c r="G218" s="28"/>
       <c r="H218" s="15" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="219" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A219" s="34"/>
-      <c r="B219" s="35"/>
-      <c r="C219" s="28"/>
+      <c r="A219" s="44"/>
+      <c r="B219" s="31"/>
+      <c r="C219" s="29"/>
       <c r="D219" s="5" t="s">
         <v>98</v>
       </c>
@@ -7613,21 +7620,21 @@
         <v>2</v>
       </c>
       <c r="F219" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="G219" s="32"/>
+        <v>213</v>
+      </c>
+      <c r="G219" s="28"/>
       <c r="H219" s="15" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
     </row>
     <row r="220" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A220" s="33">
+      <c r="A220" s="43">
         <v>86</v>
       </c>
-      <c r="B220" s="35" t="s">
+      <c r="B220" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C220" s="28" t="s">
+      <c r="C220" s="29" t="s">
         <v>86</v>
       </c>
       <c r="D220" s="5" t="s">
@@ -7637,17 +7644,17 @@
         <v>2</v>
       </c>
       <c r="F220" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="G220" s="32"/>
+        <v>186</v>
+      </c>
+      <c r="G220" s="28"/>
       <c r="H220" s="15" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
     </row>
     <row r="221" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A221" s="34"/>
-      <c r="B221" s="35"/>
-      <c r="C221" s="28"/>
+      <c r="A221" s="44"/>
+      <c r="B221" s="31"/>
+      <c r="C221" s="29"/>
       <c r="D221" s="5" t="s">
         <v>148</v>
       </c>
@@ -7655,21 +7662,21 @@
         <v>2</v>
       </c>
       <c r="F221" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="G221" s="32"/>
+        <v>193</v>
+      </c>
+      <c r="G221" s="28"/>
       <c r="H221" s="15" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
     </row>
     <row r="222" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A222" s="33">
+      <c r="A222" s="43">
         <v>87</v>
       </c>
-      <c r="B222" s="35" t="s">
+      <c r="B222" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C222" s="43" t="s">
+      <c r="C222" s="32" t="s">
         <v>86</v>
       </c>
       <c r="D222" s="5" t="s">
@@ -7679,19 +7686,19 @@
         <v>2</v>
       </c>
       <c r="F222" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="G222" s="32" t="s">
-        <v>574</v>
+        <v>246</v>
+      </c>
+      <c r="G222" s="28" t="s">
+        <v>567</v>
       </c>
       <c r="H222" s="15" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
     </row>
     <row r="223" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A223" s="34"/>
-      <c r="B223" s="35"/>
-      <c r="C223" s="43"/>
+      <c r="A223" s="44"/>
+      <c r="B223" s="31"/>
+      <c r="C223" s="32"/>
       <c r="D223" s="5" t="s">
         <v>100</v>
       </c>
@@ -7699,21 +7706,21 @@
         <v>1</v>
       </c>
       <c r="F223" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="G223" s="32"/>
+        <v>246</v>
+      </c>
+      <c r="G223" s="28"/>
       <c r="H223" s="15" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
     </row>
     <row r="224" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A224" s="33">
+      <c r="A224" s="43">
         <v>88</v>
       </c>
-      <c r="B224" s="35" t="s">
+      <c r="B224" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C224" s="37" t="s">
+      <c r="C224" s="45" t="s">
         <v>86</v>
       </c>
       <c r="D224" s="5" t="s">
@@ -7723,17 +7730,17 @@
         <v>3</v>
       </c>
       <c r="F224" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="G224" s="32"/>
+        <v>284</v>
+      </c>
+      <c r="G224" s="28"/>
       <c r="H224" s="15" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
     </row>
     <row r="225" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A225" s="34"/>
-      <c r="B225" s="35"/>
-      <c r="C225" s="37"/>
+      <c r="A225" s="44"/>
+      <c r="B225" s="31"/>
+      <c r="C225" s="45"/>
       <c r="D225" s="5" t="s">
         <v>140</v>
       </c>
@@ -7741,156 +7748,518 @@
         <v>3</v>
       </c>
       <c r="F225" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="G225" s="32"/>
+        <v>249</v>
+      </c>
+      <c r="G225" s="28"/>
       <c r="H225" s="15" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A229" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A230" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A231" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A232" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A233" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A234" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A235" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A236" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A237" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="245" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A245" s="28" t="s">
-        <v>587</v>
-      </c>
-      <c r="B245" s="28"/>
-      <c r="C245" s="28"/>
-      <c r="D245" s="28"/>
-      <c r="E245" s="28"/>
-      <c r="F245" s="28"/>
-      <c r="G245" s="28"/>
-      <c r="H245" s="28"/>
+      <c r="A245" s="29" t="s">
+        <v>579</v>
+      </c>
+      <c r="B245" s="29"/>
+      <c r="C245" s="29"/>
+      <c r="D245" s="29"/>
+      <c r="E245" s="29"/>
+      <c r="F245" s="29"/>
+      <c r="G245" s="29"/>
+      <c r="H245" s="29"/>
     </row>
     <row r="246" spans="1:8" ht="25.7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A246" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="C246" s="29" t="s">
+        <v>457</v>
+      </c>
+      <c r="C246" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="D246" s="30"/>
-      <c r="E246" s="30"/>
-      <c r="F246" s="31"/>
+      <c r="D246" s="37"/>
+      <c r="E246" s="37"/>
+      <c r="F246" s="38"/>
       <c r="G246" s="1" t="s">
         <v>3</v>
       </c>
       <c r="H246" s="1" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="247" spans="1:8" ht="100.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A247" s="18" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
       <c r="B247" s="23" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="C247" s="25" t="s">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="D247" s="26"/>
       <c r="E247" s="26"/>
       <c r="F247" s="27"/>
       <c r="G247" s="4" t="s">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="H247" s="16" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
     </row>
     <row r="248" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A248" s="24" t="s">
-        <v>588</v>
+        <v>580</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="C248" s="25" t="s">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="D248" s="26"/>
       <c r="E248" s="26"/>
       <c r="F248" s="27"/>
       <c r="G248" s="4" t="s">
-        <v>591</v>
+        <v>583</v>
       </c>
       <c r="H248" s="16" t="s">
-        <v>595</v>
+        <v>587</v>
       </c>
     </row>
     <row r="253" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A253" s="28" t="s">
-        <v>589</v>
-      </c>
-      <c r="B253" s="28"/>
-      <c r="C253" s="28"/>
-      <c r="D253" s="28"/>
-      <c r="E253" s="28"/>
-      <c r="F253" s="28"/>
-      <c r="G253" s="28"/>
-      <c r="H253" s="28"/>
+      <c r="A253" s="29" t="s">
+        <v>581</v>
+      </c>
+      <c r="B253" s="29"/>
+      <c r="C253" s="29"/>
+      <c r="D253" s="29"/>
+      <c r="E253" s="29"/>
+      <c r="F253" s="29"/>
+      <c r="G253" s="29"/>
+      <c r="H253" s="29"/>
     </row>
     <row r="254" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A254" s="28" t="s">
-        <v>590</v>
-      </c>
-      <c r="B254" s="28"/>
-      <c r="C254" s="28"/>
-      <c r="D254" s="28"/>
-      <c r="E254" s="28"/>
-      <c r="F254" s="28"/>
-      <c r="G254" s="28"/>
-      <c r="H254" s="28"/>
+      <c r="A254" s="29" t="s">
+        <v>582</v>
+      </c>
+      <c r="B254" s="29"/>
+      <c r="C254" s="29"/>
+      <c r="D254" s="29"/>
+      <c r="E254" s="29"/>
+      <c r="F254" s="29"/>
+      <c r="G254" s="29"/>
+      <c r="H254" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="386">
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="A245:H245"/>
+    <mergeCell ref="A253:H253"/>
+    <mergeCell ref="A254:H254"/>
+    <mergeCell ref="C246:F246"/>
+    <mergeCell ref="C247:F247"/>
+    <mergeCell ref="C248:F248"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="G62:G63"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="G202:G203"/>
+    <mergeCell ref="A194:A195"/>
+    <mergeCell ref="B194:B195"/>
+    <mergeCell ref="C194:C195"/>
+    <mergeCell ref="A200:A201"/>
+    <mergeCell ref="B200:B201"/>
+    <mergeCell ref="C200:C201"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A196:A197"/>
+    <mergeCell ref="B196:B197"/>
+    <mergeCell ref="C196:C197"/>
+    <mergeCell ref="A192:A193"/>
+    <mergeCell ref="B192:B193"/>
+    <mergeCell ref="C192:C193"/>
+    <mergeCell ref="G86:G87"/>
+    <mergeCell ref="A120:A121"/>
+    <mergeCell ref="B120:B121"/>
+    <mergeCell ref="C120:C121"/>
+    <mergeCell ref="G118:G119"/>
+    <mergeCell ref="A80:A81"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="C80:C81"/>
+    <mergeCell ref="A78:A79"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="G78:G79"/>
+    <mergeCell ref="A202:A203"/>
+    <mergeCell ref="B202:B203"/>
+    <mergeCell ref="C202:C203"/>
+    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="G64:G65"/>
+    <mergeCell ref="B106:B107"/>
+    <mergeCell ref="C106:C107"/>
+    <mergeCell ref="G104:G105"/>
+    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="G70:G71"/>
+    <mergeCell ref="A90:A91"/>
+    <mergeCell ref="G66:G67"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="B84:B85"/>
+    <mergeCell ref="C84:C85"/>
+    <mergeCell ref="A88:A89"/>
+    <mergeCell ref="B88:B89"/>
+    <mergeCell ref="C92:C93"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="G216:G217"/>
+    <mergeCell ref="B216:B217"/>
+    <mergeCell ref="B208:B209"/>
+    <mergeCell ref="A106:A107"/>
+    <mergeCell ref="A218:A219"/>
+    <mergeCell ref="B218:B219"/>
+    <mergeCell ref="C216:C217"/>
+    <mergeCell ref="G208:G209"/>
+    <mergeCell ref="A206:A207"/>
+    <mergeCell ref="B206:B207"/>
+    <mergeCell ref="C206:C207"/>
+    <mergeCell ref="G206:G207"/>
+    <mergeCell ref="A204:A205"/>
+    <mergeCell ref="B204:B205"/>
+    <mergeCell ref="C204:C205"/>
+    <mergeCell ref="G204:G205"/>
+    <mergeCell ref="G210:G211"/>
+    <mergeCell ref="A216:A217"/>
+    <mergeCell ref="G112:G113"/>
+    <mergeCell ref="G124:G125"/>
+    <mergeCell ref="B166:B167"/>
+    <mergeCell ref="C166:C167"/>
+    <mergeCell ref="B168:B169"/>
+    <mergeCell ref="C178:C179"/>
+    <mergeCell ref="A214:A215"/>
+    <mergeCell ref="G212:G213"/>
+    <mergeCell ref="G196:G197"/>
+    <mergeCell ref="C182:C183"/>
+    <mergeCell ref="G180:G181"/>
+    <mergeCell ref="A164:A165"/>
+    <mergeCell ref="B164:B165"/>
+    <mergeCell ref="C164:C165"/>
+    <mergeCell ref="G190:G191"/>
+    <mergeCell ref="A178:A179"/>
+    <mergeCell ref="B178:B179"/>
+    <mergeCell ref="G164:G165"/>
+    <mergeCell ref="G200:G201"/>
+    <mergeCell ref="A198:A199"/>
+    <mergeCell ref="B198:B199"/>
+    <mergeCell ref="C198:C199"/>
+    <mergeCell ref="G194:G195"/>
+    <mergeCell ref="A186:A187"/>
+    <mergeCell ref="B186:B187"/>
+    <mergeCell ref="C188:C189"/>
+    <mergeCell ref="B184:B185"/>
+    <mergeCell ref="C184:C185"/>
+    <mergeCell ref="G184:G185"/>
+    <mergeCell ref="G192:G193"/>
+    <mergeCell ref="C224:C225"/>
+    <mergeCell ref="G222:G223"/>
+    <mergeCell ref="G198:G199"/>
+    <mergeCell ref="A224:A225"/>
+    <mergeCell ref="G220:G221"/>
+    <mergeCell ref="A210:A211"/>
+    <mergeCell ref="B210:B211"/>
+    <mergeCell ref="C210:C211"/>
+    <mergeCell ref="G224:G225"/>
+    <mergeCell ref="B224:B225"/>
+    <mergeCell ref="A222:A223"/>
+    <mergeCell ref="B222:B223"/>
+    <mergeCell ref="C222:C223"/>
+    <mergeCell ref="G218:G219"/>
+    <mergeCell ref="A212:A213"/>
+    <mergeCell ref="B212:B213"/>
+    <mergeCell ref="C212:C213"/>
+    <mergeCell ref="B214:B215"/>
+    <mergeCell ref="C214:C215"/>
+    <mergeCell ref="A208:A209"/>
+    <mergeCell ref="A220:A221"/>
+    <mergeCell ref="B220:B221"/>
+    <mergeCell ref="C220:C221"/>
+    <mergeCell ref="C218:C219"/>
+    <mergeCell ref="G68:G69"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="G72:G73"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="G74:G75"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="G76:G77"/>
+    <mergeCell ref="C76:C77"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="C86:C87"/>
+    <mergeCell ref="A86:A87"/>
+    <mergeCell ref="B86:B87"/>
+    <mergeCell ref="G80:G81"/>
+    <mergeCell ref="C88:C89"/>
+    <mergeCell ref="C94:C95"/>
+    <mergeCell ref="G94:G95"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="A94:A95"/>
+    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="B104:B105"/>
+    <mergeCell ref="C104:C105"/>
+    <mergeCell ref="A96:A97"/>
+    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="C96:C97"/>
+    <mergeCell ref="B98:B99"/>
+    <mergeCell ref="C98:C99"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="B102:B103"/>
+    <mergeCell ref="A114:A115"/>
+    <mergeCell ref="B114:B115"/>
+    <mergeCell ref="A112:A113"/>
+    <mergeCell ref="B112:B113"/>
+    <mergeCell ref="A116:A117"/>
+    <mergeCell ref="B116:B117"/>
+    <mergeCell ref="A122:A123"/>
+    <mergeCell ref="B122:B123"/>
+    <mergeCell ref="G98:G99"/>
+    <mergeCell ref="A108:A109"/>
+    <mergeCell ref="B108:B109"/>
+    <mergeCell ref="C108:C109"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="B110:B111"/>
+    <mergeCell ref="A98:A99"/>
+    <mergeCell ref="A100:A101"/>
+    <mergeCell ref="B100:B101"/>
+    <mergeCell ref="C100:C101"/>
+    <mergeCell ref="A110:A111"/>
+    <mergeCell ref="A148:A149"/>
+    <mergeCell ref="G84:G85"/>
+    <mergeCell ref="G92:G93"/>
+    <mergeCell ref="G82:G83"/>
+    <mergeCell ref="G90:G91"/>
+    <mergeCell ref="G100:G101"/>
+    <mergeCell ref="C138:C139"/>
+    <mergeCell ref="G138:G139"/>
+    <mergeCell ref="G116:G117"/>
+    <mergeCell ref="G108:G109"/>
+    <mergeCell ref="G110:G111"/>
+    <mergeCell ref="C110:C111"/>
+    <mergeCell ref="C102:C103"/>
+    <mergeCell ref="C114:C115"/>
+    <mergeCell ref="C112:C113"/>
+    <mergeCell ref="C116:C117"/>
+    <mergeCell ref="G122:G123"/>
+    <mergeCell ref="C122:C123"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="G132:G133"/>
+    <mergeCell ref="G106:G107"/>
+    <mergeCell ref="G96:G97"/>
+    <mergeCell ref="G102:G103"/>
+    <mergeCell ref="G126:G127"/>
+    <mergeCell ref="B140:B141"/>
+    <mergeCell ref="C140:C141"/>
+    <mergeCell ref="G136:G137"/>
+    <mergeCell ref="A132:A133"/>
+    <mergeCell ref="A130:A131"/>
+    <mergeCell ref="B130:B131"/>
+    <mergeCell ref="C128:C129"/>
+    <mergeCell ref="A142:A143"/>
+    <mergeCell ref="B142:B143"/>
+    <mergeCell ref="A126:A127"/>
+    <mergeCell ref="B126:B127"/>
+    <mergeCell ref="C126:C127"/>
+    <mergeCell ref="B136:B137"/>
+    <mergeCell ref="C136:C137"/>
+    <mergeCell ref="G148:G149"/>
+    <mergeCell ref="A150:A151"/>
+    <mergeCell ref="A160:A161"/>
+    <mergeCell ref="B160:B161"/>
+    <mergeCell ref="C160:C161"/>
+    <mergeCell ref="G128:G129"/>
+    <mergeCell ref="A154:A155"/>
+    <mergeCell ref="A138:A139"/>
+    <mergeCell ref="G140:G141"/>
+    <mergeCell ref="G134:G135"/>
+    <mergeCell ref="A128:A129"/>
+    <mergeCell ref="B128:B129"/>
+    <mergeCell ref="B148:B149"/>
+    <mergeCell ref="C148:C149"/>
+    <mergeCell ref="G146:G147"/>
+    <mergeCell ref="A144:A145"/>
+    <mergeCell ref="B144:B145"/>
+    <mergeCell ref="C144:C145"/>
+    <mergeCell ref="A140:A141"/>
+    <mergeCell ref="C180:C181"/>
+    <mergeCell ref="G178:G179"/>
+    <mergeCell ref="A176:A177"/>
+    <mergeCell ref="B132:B133"/>
+    <mergeCell ref="C132:C133"/>
+    <mergeCell ref="B154:B155"/>
+    <mergeCell ref="C154:C155"/>
+    <mergeCell ref="G152:G153"/>
+    <mergeCell ref="G172:G173"/>
+    <mergeCell ref="B176:B177"/>
+    <mergeCell ref="C176:C177"/>
+    <mergeCell ref="B172:B173"/>
+    <mergeCell ref="A168:A169"/>
+    <mergeCell ref="G170:G171"/>
+    <mergeCell ref="G176:G177"/>
+    <mergeCell ref="G142:G143"/>
+    <mergeCell ref="A170:A171"/>
+    <mergeCell ref="B170:B171"/>
+    <mergeCell ref="C170:C171"/>
+    <mergeCell ref="G168:G169"/>
+    <mergeCell ref="A172:A173"/>
+    <mergeCell ref="A180:A181"/>
+    <mergeCell ref="B180:B181"/>
+    <mergeCell ref="A136:A137"/>
+    <mergeCell ref="B190:B191"/>
+    <mergeCell ref="G182:G183"/>
+    <mergeCell ref="C190:C191"/>
+    <mergeCell ref="G188:G189"/>
+    <mergeCell ref="B188:B189"/>
+    <mergeCell ref="C172:C173"/>
+    <mergeCell ref="C158:C159"/>
+    <mergeCell ref="G156:G157"/>
+    <mergeCell ref="A156:A157"/>
+    <mergeCell ref="B156:B157"/>
+    <mergeCell ref="A174:A175"/>
+    <mergeCell ref="B174:B175"/>
+    <mergeCell ref="C174:C175"/>
+    <mergeCell ref="G174:G175"/>
+    <mergeCell ref="B158:B159"/>
+    <mergeCell ref="C186:C187"/>
+    <mergeCell ref="A158:A159"/>
+    <mergeCell ref="G186:G187"/>
+    <mergeCell ref="A182:A183"/>
+    <mergeCell ref="B182:B183"/>
+    <mergeCell ref="C168:C169"/>
+    <mergeCell ref="G166:G167"/>
+    <mergeCell ref="A184:A185"/>
+    <mergeCell ref="G162:G163"/>
+    <mergeCell ref="A124:A125"/>
+    <mergeCell ref="B124:B125"/>
+    <mergeCell ref="A118:A119"/>
+    <mergeCell ref="A134:A135"/>
+    <mergeCell ref="B134:B135"/>
+    <mergeCell ref="C134:C135"/>
+    <mergeCell ref="G214:G215"/>
+    <mergeCell ref="C118:C119"/>
+    <mergeCell ref="B118:B119"/>
+    <mergeCell ref="C124:C125"/>
+    <mergeCell ref="A152:A153"/>
+    <mergeCell ref="B152:B153"/>
+    <mergeCell ref="C152:C153"/>
+    <mergeCell ref="A146:A147"/>
+    <mergeCell ref="B146:B147"/>
+    <mergeCell ref="C146:C147"/>
+    <mergeCell ref="B150:B151"/>
+    <mergeCell ref="C150:C151"/>
+    <mergeCell ref="G150:G151"/>
+    <mergeCell ref="G160:G161"/>
+    <mergeCell ref="A166:A167"/>
+    <mergeCell ref="A162:A163"/>
+    <mergeCell ref="A188:A189"/>
+    <mergeCell ref="A190:A191"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="A48:H48"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="G50:G51"/>
+    <mergeCell ref="G52:G53"/>
+    <mergeCell ref="G54:G55"/>
+    <mergeCell ref="G56:G57"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="C62:C63"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C60:C61"/>
     <mergeCell ref="C27:F27"/>
     <mergeCell ref="C34:F34"/>
     <mergeCell ref="C35:F35"/>
@@ -7915,368 +8284,6 @@
     <mergeCell ref="C142:C143"/>
     <mergeCell ref="G120:G121"/>
     <mergeCell ref="G114:G115"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="A62:A63"/>
-    <mergeCell ref="C62:C63"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="A47:H47"/>
-    <mergeCell ref="A48:H48"/>
-    <mergeCell ref="A41:H41"/>
-    <mergeCell ref="G50:G51"/>
-    <mergeCell ref="G52:G53"/>
-    <mergeCell ref="G54:G55"/>
-    <mergeCell ref="G56:G57"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="A124:A125"/>
-    <mergeCell ref="B124:B125"/>
-    <mergeCell ref="A118:A119"/>
-    <mergeCell ref="A134:A135"/>
-    <mergeCell ref="B134:B135"/>
-    <mergeCell ref="C134:C135"/>
-    <mergeCell ref="G214:G215"/>
-    <mergeCell ref="C118:C119"/>
-    <mergeCell ref="B118:B119"/>
-    <mergeCell ref="C124:C125"/>
-    <mergeCell ref="A152:A153"/>
-    <mergeCell ref="B152:B153"/>
-    <mergeCell ref="C152:C153"/>
-    <mergeCell ref="A146:A147"/>
-    <mergeCell ref="B146:B147"/>
-    <mergeCell ref="C146:C147"/>
-    <mergeCell ref="B150:B151"/>
-    <mergeCell ref="C150:C151"/>
-    <mergeCell ref="G150:G151"/>
-    <mergeCell ref="G160:G161"/>
-    <mergeCell ref="A166:A167"/>
-    <mergeCell ref="A162:A163"/>
-    <mergeCell ref="A188:A189"/>
-    <mergeCell ref="A190:A191"/>
-    <mergeCell ref="B190:B191"/>
-    <mergeCell ref="G182:G183"/>
-    <mergeCell ref="C190:C191"/>
-    <mergeCell ref="G188:G189"/>
-    <mergeCell ref="B188:B189"/>
-    <mergeCell ref="C172:C173"/>
-    <mergeCell ref="C158:C159"/>
-    <mergeCell ref="G156:G157"/>
-    <mergeCell ref="A156:A157"/>
-    <mergeCell ref="B156:B157"/>
-    <mergeCell ref="A174:A175"/>
-    <mergeCell ref="B174:B175"/>
-    <mergeCell ref="C174:C175"/>
-    <mergeCell ref="G174:G175"/>
-    <mergeCell ref="B158:B159"/>
-    <mergeCell ref="C186:C187"/>
-    <mergeCell ref="A158:A159"/>
-    <mergeCell ref="G186:G187"/>
-    <mergeCell ref="A182:A183"/>
-    <mergeCell ref="B182:B183"/>
-    <mergeCell ref="C168:C169"/>
-    <mergeCell ref="G166:G167"/>
-    <mergeCell ref="A184:A185"/>
-    <mergeCell ref="G162:G163"/>
-    <mergeCell ref="C180:C181"/>
-    <mergeCell ref="G178:G179"/>
-    <mergeCell ref="A176:A177"/>
-    <mergeCell ref="B132:B133"/>
-    <mergeCell ref="C132:C133"/>
-    <mergeCell ref="B154:B155"/>
-    <mergeCell ref="C154:C155"/>
-    <mergeCell ref="G152:G153"/>
-    <mergeCell ref="G172:G173"/>
-    <mergeCell ref="B176:B177"/>
-    <mergeCell ref="C176:C177"/>
-    <mergeCell ref="B172:B173"/>
-    <mergeCell ref="A168:A169"/>
-    <mergeCell ref="G170:G171"/>
-    <mergeCell ref="G176:G177"/>
-    <mergeCell ref="G142:G143"/>
-    <mergeCell ref="A170:A171"/>
-    <mergeCell ref="B170:B171"/>
-    <mergeCell ref="C170:C171"/>
-    <mergeCell ref="G168:G169"/>
-    <mergeCell ref="A172:A173"/>
-    <mergeCell ref="A180:A181"/>
-    <mergeCell ref="B180:B181"/>
-    <mergeCell ref="A136:A137"/>
-    <mergeCell ref="A126:A127"/>
-    <mergeCell ref="B126:B127"/>
-    <mergeCell ref="C126:C127"/>
-    <mergeCell ref="B136:B137"/>
-    <mergeCell ref="C136:C137"/>
-    <mergeCell ref="G148:G149"/>
-    <mergeCell ref="A150:A151"/>
-    <mergeCell ref="A160:A161"/>
-    <mergeCell ref="B160:B161"/>
-    <mergeCell ref="C160:C161"/>
-    <mergeCell ref="G128:G129"/>
-    <mergeCell ref="A154:A155"/>
-    <mergeCell ref="A138:A139"/>
-    <mergeCell ref="G140:G141"/>
-    <mergeCell ref="G134:G135"/>
-    <mergeCell ref="A128:A129"/>
-    <mergeCell ref="B128:B129"/>
-    <mergeCell ref="B148:B149"/>
-    <mergeCell ref="C148:C149"/>
-    <mergeCell ref="G146:G147"/>
-    <mergeCell ref="A144:A145"/>
-    <mergeCell ref="B144:B145"/>
-    <mergeCell ref="C144:C145"/>
-    <mergeCell ref="A140:A141"/>
-    <mergeCell ref="B140:B141"/>
-    <mergeCell ref="C140:C141"/>
-    <mergeCell ref="G136:G137"/>
-    <mergeCell ref="A132:A133"/>
-    <mergeCell ref="A130:A131"/>
-    <mergeCell ref="B130:B131"/>
-    <mergeCell ref="C128:C129"/>
-    <mergeCell ref="A142:A143"/>
-    <mergeCell ref="B142:B143"/>
-    <mergeCell ref="A148:A149"/>
-    <mergeCell ref="G84:G85"/>
-    <mergeCell ref="G92:G93"/>
-    <mergeCell ref="G82:G83"/>
-    <mergeCell ref="G90:G91"/>
-    <mergeCell ref="G100:G101"/>
-    <mergeCell ref="C138:C139"/>
-    <mergeCell ref="G138:G139"/>
-    <mergeCell ref="G116:G117"/>
-    <mergeCell ref="G108:G109"/>
-    <mergeCell ref="G110:G111"/>
-    <mergeCell ref="C110:C111"/>
-    <mergeCell ref="C102:C103"/>
-    <mergeCell ref="C114:C115"/>
-    <mergeCell ref="C112:C113"/>
-    <mergeCell ref="C116:C117"/>
-    <mergeCell ref="G122:G123"/>
-    <mergeCell ref="C122:C123"/>
-    <mergeCell ref="C82:C83"/>
-    <mergeCell ref="G132:G133"/>
-    <mergeCell ref="G106:G107"/>
-    <mergeCell ref="G96:G97"/>
-    <mergeCell ref="G102:G103"/>
-    <mergeCell ref="G126:G127"/>
-    <mergeCell ref="A114:A115"/>
-    <mergeCell ref="B114:B115"/>
-    <mergeCell ref="A112:A113"/>
-    <mergeCell ref="B112:B113"/>
-    <mergeCell ref="A116:A117"/>
-    <mergeCell ref="B116:B117"/>
-    <mergeCell ref="A122:A123"/>
-    <mergeCell ref="B122:B123"/>
-    <mergeCell ref="G98:G99"/>
-    <mergeCell ref="A108:A109"/>
-    <mergeCell ref="B108:B109"/>
-    <mergeCell ref="C108:C109"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="B110:B111"/>
-    <mergeCell ref="A98:A99"/>
-    <mergeCell ref="A100:A101"/>
-    <mergeCell ref="B100:B101"/>
-    <mergeCell ref="C100:C101"/>
-    <mergeCell ref="A110:A111"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="A94:A95"/>
-    <mergeCell ref="B94:B95"/>
-    <mergeCell ref="B104:B105"/>
-    <mergeCell ref="C104:C105"/>
-    <mergeCell ref="A96:A97"/>
-    <mergeCell ref="B96:B97"/>
-    <mergeCell ref="C96:C97"/>
-    <mergeCell ref="B98:B99"/>
-    <mergeCell ref="C98:C99"/>
-    <mergeCell ref="A102:A103"/>
-    <mergeCell ref="B102:B103"/>
-    <mergeCell ref="C218:C219"/>
-    <mergeCell ref="G68:G69"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="G72:G73"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="G74:G75"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="G76:G77"/>
-    <mergeCell ref="C76:C77"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="C74:C75"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="C86:C87"/>
-    <mergeCell ref="A86:A87"/>
-    <mergeCell ref="B86:B87"/>
-    <mergeCell ref="G80:G81"/>
-    <mergeCell ref="C88:C89"/>
-    <mergeCell ref="C94:C95"/>
-    <mergeCell ref="G94:G95"/>
-    <mergeCell ref="G192:G193"/>
-    <mergeCell ref="C224:C225"/>
-    <mergeCell ref="G222:G223"/>
-    <mergeCell ref="G198:G199"/>
-    <mergeCell ref="A224:A225"/>
-    <mergeCell ref="G220:G221"/>
-    <mergeCell ref="A210:A211"/>
-    <mergeCell ref="B210:B211"/>
-    <mergeCell ref="C210:C211"/>
-    <mergeCell ref="G224:G225"/>
-    <mergeCell ref="B224:B225"/>
-    <mergeCell ref="A222:A223"/>
-    <mergeCell ref="B222:B223"/>
-    <mergeCell ref="C222:C223"/>
-    <mergeCell ref="G218:G219"/>
-    <mergeCell ref="A212:A213"/>
-    <mergeCell ref="B212:B213"/>
-    <mergeCell ref="C212:C213"/>
-    <mergeCell ref="B214:B215"/>
-    <mergeCell ref="C214:C215"/>
-    <mergeCell ref="A208:A209"/>
-    <mergeCell ref="A220:A221"/>
-    <mergeCell ref="B220:B221"/>
-    <mergeCell ref="C220:C221"/>
-    <mergeCell ref="C178:C179"/>
-    <mergeCell ref="A214:A215"/>
-    <mergeCell ref="G212:G213"/>
-    <mergeCell ref="G196:G197"/>
-    <mergeCell ref="C182:C183"/>
-    <mergeCell ref="G180:G181"/>
-    <mergeCell ref="A164:A165"/>
-    <mergeCell ref="B164:B165"/>
-    <mergeCell ref="C164:C165"/>
-    <mergeCell ref="G190:G191"/>
-    <mergeCell ref="A178:A179"/>
-    <mergeCell ref="B178:B179"/>
-    <mergeCell ref="G164:G165"/>
-    <mergeCell ref="G200:G201"/>
-    <mergeCell ref="A198:A199"/>
-    <mergeCell ref="B198:B199"/>
-    <mergeCell ref="C198:C199"/>
-    <mergeCell ref="G194:G195"/>
-    <mergeCell ref="A186:A187"/>
-    <mergeCell ref="B186:B187"/>
-    <mergeCell ref="C188:C189"/>
-    <mergeCell ref="B184:B185"/>
-    <mergeCell ref="C184:C185"/>
-    <mergeCell ref="G184:G185"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="G216:G217"/>
-    <mergeCell ref="B216:B217"/>
-    <mergeCell ref="B208:B209"/>
-    <mergeCell ref="A106:A107"/>
-    <mergeCell ref="A218:A219"/>
-    <mergeCell ref="B218:B219"/>
-    <mergeCell ref="C216:C217"/>
-    <mergeCell ref="G208:G209"/>
-    <mergeCell ref="A206:A207"/>
-    <mergeCell ref="B206:B207"/>
-    <mergeCell ref="C206:C207"/>
-    <mergeCell ref="G206:G207"/>
-    <mergeCell ref="A204:A205"/>
-    <mergeCell ref="B204:B205"/>
-    <mergeCell ref="C204:C205"/>
-    <mergeCell ref="G204:G205"/>
-    <mergeCell ref="G210:G211"/>
-    <mergeCell ref="A216:A217"/>
-    <mergeCell ref="G112:G113"/>
-    <mergeCell ref="G124:G125"/>
-    <mergeCell ref="B166:B167"/>
-    <mergeCell ref="C166:C167"/>
-    <mergeCell ref="B168:B169"/>
-    <mergeCell ref="G78:G79"/>
-    <mergeCell ref="A202:A203"/>
-    <mergeCell ref="B202:B203"/>
-    <mergeCell ref="C202:C203"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="A92:A93"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="G64:G65"/>
-    <mergeCell ref="B106:B107"/>
-    <mergeCell ref="C106:C107"/>
-    <mergeCell ref="G104:G105"/>
-    <mergeCell ref="A70:A71"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="C70:C71"/>
-    <mergeCell ref="G70:G71"/>
-    <mergeCell ref="A90:A91"/>
-    <mergeCell ref="G66:G67"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="B84:B85"/>
-    <mergeCell ref="C84:C85"/>
-    <mergeCell ref="A88:A89"/>
-    <mergeCell ref="B88:B89"/>
-    <mergeCell ref="C92:C93"/>
-    <mergeCell ref="C200:C201"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="A31:H31"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A196:A197"/>
-    <mergeCell ref="B196:B197"/>
-    <mergeCell ref="C196:C197"/>
-    <mergeCell ref="A192:A193"/>
-    <mergeCell ref="B192:B193"/>
-    <mergeCell ref="C192:C193"/>
-    <mergeCell ref="G86:G87"/>
-    <mergeCell ref="A120:A121"/>
-    <mergeCell ref="B120:B121"/>
-    <mergeCell ref="C120:C121"/>
-    <mergeCell ref="G118:G119"/>
-    <mergeCell ref="A80:A81"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="C80:C81"/>
-    <mergeCell ref="A78:A79"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="A245:H245"/>
-    <mergeCell ref="A253:H253"/>
-    <mergeCell ref="A254:H254"/>
-    <mergeCell ref="C246:F246"/>
-    <mergeCell ref="C247:F247"/>
-    <mergeCell ref="C248:F248"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="G62:G63"/>
-    <mergeCell ref="C68:C69"/>
-    <mergeCell ref="G202:G203"/>
-    <mergeCell ref="A194:A195"/>
-    <mergeCell ref="B194:B195"/>
-    <mergeCell ref="C194:C195"/>
-    <mergeCell ref="A200:A201"/>
-    <mergeCell ref="B200:B201"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/main/resources/InesModResources/杀戮尖塔自制--伊内丝v0.2.xlsx
+++ b/src/main/resources/InesModResources/杀戮尖塔自制--伊内丝v0.2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\myMod\InesMod\InesMod\src\main\resources\InesModResources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F2C5F12-C203-49A8-B5DA-14D9ABBE8CB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F46C2FF3-5F69-4747-BB10-5CEB4AEF1778}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{7A3E14A4-2175-4856-859A-887D335814F1}"/>
   </bookViews>
@@ -2743,7 +2743,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2829,27 +2829,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2861,10 +2840,46 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2873,31 +2888,22 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3233,10 +3239,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="28" t="s">
         <v>290</v>
       </c>
-      <c r="B1" s="29"/>
+      <c r="B1" s="28"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -3288,16 +3294,16 @@
       <c r="B6" s="2"/>
     </row>
     <row r="8" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="36" t="s">
+      <c r="A8" s="29" t="s">
         <v>105</v>
       </c>
-      <c r="B8" s="37"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="38"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="31"/>
     </row>
     <row r="9" spans="1:8" ht="25.7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
@@ -3306,11 +3312,11 @@
       <c r="B9" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="C9" s="36" t="s">
+      <c r="C9" s="29" t="s">
         <v>229</v>
       </c>
-      <c r="D9" s="37"/>
-      <c r="E9" s="38"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="31"/>
       <c r="F9" s="8" t="s">
         <v>2</v>
       </c>
@@ -3328,11 +3334,11 @@
       <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="37" t="s">
+      <c r="C10" s="30" t="s">
         <v>231</v>
       </c>
-      <c r="D10" s="37"/>
-      <c r="E10" s="38"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="31"/>
       <c r="F10" s="9" t="s">
         <v>649</v>
       </c>
@@ -3348,11 +3354,11 @@
       <c r="B11" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="C11" s="36" t="s">
+      <c r="C11" s="29" t="s">
         <v>235</v>
       </c>
-      <c r="D11" s="37"/>
-      <c r="E11" s="38"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="31"/>
       <c r="F11" s="9" t="s">
         <v>650</v>
       </c>
@@ -3368,11 +3374,11 @@
       <c r="B12" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="C12" s="36" t="s">
+      <c r="C12" s="29" t="s">
         <v>466</v>
       </c>
-      <c r="D12" s="37"/>
-      <c r="E12" s="38"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="31"/>
       <c r="F12" s="9" t="s">
         <v>241</v>
       </c>
@@ -3391,8 +3397,8 @@
       <c r="C13" s="25" t="s">
         <v>447</v>
       </c>
-      <c r="D13" s="37"/>
-      <c r="E13" s="38"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="31"/>
       <c r="F13" s="9" t="s">
         <v>224</v>
       </c>
@@ -3408,11 +3414,11 @@
       <c r="B14" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="C14" s="37" t="s">
+      <c r="C14" s="30" t="s">
         <v>286</v>
       </c>
-      <c r="D14" s="37"/>
-      <c r="E14" s="38"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="31"/>
       <c r="F14" s="9" t="s">
         <v>240</v>
       </c>
@@ -3425,16 +3431,16 @@
     <row r="16" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="17" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="29" t="s">
+      <c r="A18" s="28" t="s">
         <v>86</v>
       </c>
-      <c r="B18" s="29"/>
-      <c r="C18" s="29"/>
-      <c r="D18" s="29"/>
-      <c r="E18" s="29"/>
-      <c r="F18" s="29"/>
-      <c r="G18" s="29"/>
-      <c r="H18" s="29"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="28"/>
     </row>
     <row r="19" spans="1:8" ht="25.7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
@@ -3443,12 +3449,12 @@
       <c r="B19" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="C19" s="36" t="s">
+      <c r="C19" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="D19" s="37"/>
-      <c r="E19" s="37"/>
-      <c r="F19" s="38"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="31"/>
       <c r="G19" s="1" t="s">
         <v>3</v>
       </c>
@@ -3618,16 +3624,16 @@
     <row r="29" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="1:8" ht="21.7" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="31" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="29" t="s">
+      <c r="A31" s="28" t="s">
         <v>495</v>
       </c>
-      <c r="B31" s="29"/>
-      <c r="C31" s="29"/>
-      <c r="D31" s="29"/>
-      <c r="E31" s="29"/>
-      <c r="F31" s="29"/>
-      <c r="G31" s="29"/>
-      <c r="H31" s="29"/>
+      <c r="B31" s="28"/>
+      <c r="C31" s="28"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="28"/>
+      <c r="G31" s="28"/>
+      <c r="H31" s="28"/>
     </row>
     <row r="32" spans="1:8" ht="25.7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="1" t="s">
@@ -3636,12 +3642,12 @@
       <c r="B32" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="C32" s="36" t="s">
+      <c r="C32" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="D32" s="37"/>
-      <c r="E32" s="37"/>
-      <c r="F32" s="38"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="31"/>
       <c r="G32" s="1" t="s">
         <v>3</v>
       </c>
@@ -3752,16 +3758,16 @@
       <c r="H40" s="11"/>
     </row>
     <row r="41" spans="1:8" s="3" customFormat="1" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="29" t="s">
+      <c r="A41" s="28" t="s">
         <v>499</v>
       </c>
-      <c r="B41" s="29"/>
-      <c r="C41" s="29"/>
-      <c r="D41" s="29"/>
-      <c r="E41" s="29"/>
-      <c r="F41" s="29"/>
-      <c r="G41" s="29"/>
-      <c r="H41" s="29"/>
+      <c r="B41" s="28"/>
+      <c r="C41" s="28"/>
+      <c r="D41" s="28"/>
+      <c r="E41" s="28"/>
+      <c r="F41" s="28"/>
+      <c r="G41" s="28"/>
+      <c r="H41" s="28"/>
     </row>
     <row r="42" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="1" t="s">
@@ -3826,28 +3832,28 @@
       <c r="H46" s="2"/>
     </row>
     <row r="47" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="29" t="s">
+      <c r="A47" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="B47" s="29"/>
-      <c r="C47" s="29"/>
-      <c r="D47" s="29"/>
-      <c r="E47" s="29"/>
-      <c r="F47" s="29"/>
-      <c r="G47" s="29"/>
-      <c r="H47" s="29"/>
+      <c r="B47" s="28"/>
+      <c r="C47" s="28"/>
+      <c r="D47" s="28"/>
+      <c r="E47" s="28"/>
+      <c r="F47" s="28"/>
+      <c r="G47" s="28"/>
+      <c r="H47" s="28"/>
     </row>
     <row r="48" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="29" t="s">
+      <c r="A48" s="28" t="s">
         <v>511</v>
       </c>
-      <c r="B48" s="29"/>
-      <c r="C48" s="29"/>
-      <c r="D48" s="29"/>
-      <c r="E48" s="29"/>
-      <c r="F48" s="29"/>
-      <c r="G48" s="29"/>
-      <c r="H48" s="29"/>
+      <c r="B48" s="28"/>
+      <c r="C48" s="28"/>
+      <c r="D48" s="28"/>
+      <c r="E48" s="28"/>
+      <c r="F48" s="28"/>
+      <c r="G48" s="28"/>
+      <c r="H48" s="28"/>
     </row>
     <row r="49" spans="1:12" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="1" t="s">
@@ -3876,13 +3882,13 @@
       </c>
     </row>
     <row r="50" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="40">
-        <v>1</v>
-      </c>
-      <c r="B50" s="39" t="s">
+      <c r="A50" s="51">
+        <v>1</v>
+      </c>
+      <c r="B50" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="C50" s="29" t="s">
+      <c r="C50" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D50" s="6" t="s">
@@ -3894,15 +3900,15 @@
       <c r="F50" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G50" s="28"/>
+      <c r="G50" s="32"/>
       <c r="H50" s="15" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="51" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="40"/>
-      <c r="B51" s="39"/>
-      <c r="C51" s="29"/>
+      <c r="A51" s="51"/>
+      <c r="B51" s="50"/>
+      <c r="C51" s="28"/>
       <c r="D51" s="6" t="s">
         <v>18</v>
       </c>
@@ -3912,7 +3918,7 @@
       <c r="F51" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G51" s="28"/>
+      <c r="G51" s="32"/>
       <c r="H51" s="15" t="s">
         <v>357</v>
       </c>
@@ -3922,13 +3928,13 @@
       <c r="L51" s="2"/>
     </row>
     <row r="52" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="34">
+      <c r="A52" s="38">
         <v>2</v>
       </c>
-      <c r="B52" s="39" t="s">
+      <c r="B52" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="29" t="s">
+      <c r="C52" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D52" s="6" t="s">
@@ -3940,7 +3946,7 @@
       <c r="F52" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G52" s="28"/>
+      <c r="G52" s="32"/>
       <c r="H52" s="15" t="s">
         <v>297</v>
       </c>
@@ -3950,9 +3956,9 @@
       <c r="L52" s="2"/>
     </row>
     <row r="53" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="35"/>
-      <c r="B53" s="39"/>
-      <c r="C53" s="29"/>
+      <c r="A53" s="39"/>
+      <c r="B53" s="50"/>
+      <c r="C53" s="28"/>
       <c r="D53" s="6" t="s">
         <v>19</v>
       </c>
@@ -3962,7 +3968,7 @@
       <c r="F53" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G53" s="28"/>
+      <c r="G53" s="32"/>
       <c r="H53" s="15" t="s">
         <v>358</v>
       </c>
@@ -3972,13 +3978,13 @@
       <c r="L53" s="2"/>
     </row>
     <row r="54" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="34">
+      <c r="A54" s="38">
         <v>3</v>
       </c>
-      <c r="B54" s="39" t="s">
+      <c r="B54" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="29" t="s">
+      <c r="C54" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D54" s="5" t="s">
@@ -3990,7 +3996,7 @@
       <c r="F54" s="5" t="s">
         <v>492</v>
       </c>
-      <c r="G54" s="28"/>
+      <c r="G54" s="32"/>
       <c r="H54" s="15" t="s">
         <v>455</v>
       </c>
@@ -4000,9 +4006,9 @@
       <c r="L54" s="2"/>
     </row>
     <row r="55" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="35"/>
-      <c r="B55" s="39"/>
-      <c r="C55" s="29"/>
+      <c r="A55" s="39"/>
+      <c r="B55" s="50"/>
+      <c r="C55" s="28"/>
       <c r="D55" s="5" t="s">
         <v>20</v>
       </c>
@@ -4012,7 +4018,7 @@
       <c r="F55" s="5" t="s">
         <v>509</v>
       </c>
-      <c r="G55" s="28"/>
+      <c r="G55" s="32"/>
       <c r="H55" s="15" t="s">
         <v>359</v>
       </c>
@@ -4022,13 +4028,13 @@
       <c r="L55" s="2"/>
     </row>
     <row r="56" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="34">
+      <c r="A56" s="38">
         <v>4</v>
       </c>
-      <c r="B56" s="39" t="s">
+      <c r="B56" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="C56" s="29" t="s">
+      <c r="C56" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D56" s="5" t="s">
@@ -4040,7 +4046,7 @@
       <c r="F56" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="G56" s="28"/>
+      <c r="G56" s="32"/>
       <c r="H56" s="15" t="s">
         <v>292</v>
       </c>
@@ -4050,9 +4056,9 @@
       <c r="L56" s="2"/>
     </row>
     <row r="57" spans="1:12" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="35"/>
-      <c r="B57" s="39"/>
-      <c r="C57" s="29"/>
+      <c r="A57" s="39"/>
+      <c r="B57" s="50"/>
+      <c r="C57" s="28"/>
       <c r="D57" s="5" t="s">
         <v>25</v>
       </c>
@@ -4062,7 +4068,7 @@
       <c r="F57" s="5" t="s">
         <v>507</v>
       </c>
-      <c r="G57" s="28"/>
+      <c r="G57" s="32"/>
       <c r="H57" s="15" t="s">
         <v>422</v>
       </c>
@@ -4072,13 +4078,13 @@
       <c r="L57" s="2"/>
     </row>
     <row r="58" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="34">
+      <c r="A58" s="38">
         <v>5</v>
       </c>
-      <c r="B58" s="30" t="s">
+      <c r="B58" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="C58" s="29" t="s">
+      <c r="C58" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D58" s="5" t="s">
@@ -4090,7 +4096,7 @@
       <c r="F58" s="5" t="s">
         <v>488</v>
       </c>
-      <c r="G58" s="28" t="s">
+      <c r="G58" s="32" t="s">
         <v>489</v>
       </c>
       <c r="H58" s="15" t="s">
@@ -4102,9 +4108,9 @@
       <c r="L58" s="2"/>
     </row>
     <row r="59" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A59" s="35"/>
-      <c r="B59" s="30"/>
-      <c r="C59" s="29"/>
+      <c r="A59" s="39"/>
+      <c r="B59" s="40"/>
+      <c r="C59" s="28"/>
       <c r="D59" s="5" t="s">
         <v>26</v>
       </c>
@@ -4114,7 +4120,7 @@
       <c r="F59" s="5" t="s">
         <v>525</v>
       </c>
-      <c r="G59" s="28"/>
+      <c r="G59" s="32"/>
       <c r="H59" s="15" t="s">
         <v>360</v>
       </c>
@@ -4124,13 +4130,13 @@
       <c r="L59" s="2"/>
     </row>
     <row r="60" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="34">
+      <c r="A60" s="38">
         <v>6</v>
       </c>
-      <c r="B60" s="30" t="s">
+      <c r="B60" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="C60" s="29" t="s">
+      <c r="C60" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D60" s="5" t="s">
@@ -4142,7 +4148,7 @@
       <c r="F60" s="5" t="s">
         <v>562</v>
       </c>
-      <c r="G60" s="28"/>
+      <c r="G60" s="32"/>
       <c r="H60" s="15" t="s">
         <v>299</v>
       </c>
@@ -4152,9 +4158,9 @@
       <c r="L60" s="2"/>
     </row>
     <row r="61" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="35"/>
-      <c r="B61" s="30"/>
-      <c r="C61" s="29"/>
+      <c r="A61" s="39"/>
+      <c r="B61" s="40"/>
+      <c r="C61" s="28"/>
       <c r="D61" s="5" t="s">
         <v>28</v>
       </c>
@@ -4164,7 +4170,7 @@
       <c r="F61" s="5" t="s">
         <v>561</v>
       </c>
-      <c r="G61" s="28"/>
+      <c r="G61" s="32"/>
       <c r="H61" s="15" t="s">
         <v>361</v>
       </c>
@@ -4174,13 +4180,13 @@
       <c r="L61" s="2"/>
     </row>
     <row r="62" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="34">
+      <c r="A62" s="38">
         <v>7</v>
       </c>
-      <c r="B62" s="30" t="s">
+      <c r="B62" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="C62" s="29" t="s">
+      <c r="C62" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D62" s="5" t="s">
@@ -4192,7 +4198,7 @@
       <c r="F62" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="G62" s="28"/>
+      <c r="G62" s="32"/>
       <c r="H62" s="15" t="s">
         <v>300</v>
       </c>
@@ -4202,9 +4208,9 @@
       <c r="L62" s="2"/>
     </row>
     <row r="63" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="35"/>
-      <c r="B63" s="30"/>
-      <c r="C63" s="29"/>
+      <c r="A63" s="39"/>
+      <c r="B63" s="40"/>
+      <c r="C63" s="28"/>
       <c r="D63" s="5" t="s">
         <v>38</v>
       </c>
@@ -4214,7 +4220,7 @@
       <c r="F63" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="G63" s="28"/>
+      <c r="G63" s="32"/>
       <c r="H63" s="15" t="s">
         <v>362</v>
       </c>
@@ -4224,13 +4230,13 @@
       <c r="L63" s="2"/>
     </row>
     <row r="64" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A64" s="34">
+      <c r="A64" s="38">
         <v>8</v>
       </c>
-      <c r="B64" s="30" t="s">
+      <c r="B64" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="C64" s="29" t="s">
+      <c r="C64" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D64" s="5" t="s">
@@ -4242,7 +4248,7 @@
       <c r="F64" s="5" t="s">
         <v>563</v>
       </c>
-      <c r="G64" s="28" t="s">
+      <c r="G64" s="32" t="s">
         <v>538</v>
       </c>
       <c r="H64" s="15" t="s">
@@ -4254,9 +4260,9 @@
       <c r="L64" s="2"/>
     </row>
     <row r="65" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A65" s="35"/>
-      <c r="B65" s="30"/>
-      <c r="C65" s="29"/>
+      <c r="A65" s="39"/>
+      <c r="B65" s="40"/>
+      <c r="C65" s="28"/>
       <c r="D65" s="5" t="s">
         <v>190</v>
       </c>
@@ -4266,7 +4272,7 @@
       <c r="F65" s="5" t="s">
         <v>564</v>
       </c>
-      <c r="G65" s="28"/>
+      <c r="G65" s="32"/>
       <c r="H65" s="15" t="s">
         <v>363</v>
       </c>
@@ -4276,13 +4282,13 @@
       <c r="L65" s="2"/>
     </row>
     <row r="66" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A66" s="34">
+      <c r="A66" s="38">
         <v>9</v>
       </c>
-      <c r="B66" s="30" t="s">
+      <c r="B66" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="C66" s="29" t="s">
+      <c r="C66" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D66" s="5" t="s">
@@ -4294,7 +4300,7 @@
       <c r="F66" s="5" t="s">
         <v>535</v>
       </c>
-      <c r="G66" s="28" t="s">
+      <c r="G66" s="32" t="s">
         <v>539</v>
       </c>
       <c r="H66" s="15" t="s">
@@ -4302,9 +4308,9 @@
       </c>
     </row>
     <row r="67" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A67" s="35"/>
-      <c r="B67" s="30"/>
-      <c r="C67" s="29"/>
+      <c r="A67" s="39"/>
+      <c r="B67" s="40"/>
+      <c r="C67" s="28"/>
       <c r="D67" s="5" t="s">
         <v>114</v>
       </c>
@@ -4314,19 +4320,19 @@
       <c r="F67" s="5" t="s">
         <v>536</v>
       </c>
-      <c r="G67" s="28"/>
+      <c r="G67" s="32"/>
       <c r="H67" s="15" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="68" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A68" s="34">
+      <c r="A68" s="38">
         <v>10</v>
       </c>
-      <c r="B68" s="30" t="s">
+      <c r="B68" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="C68" s="29" t="s">
+      <c r="C68" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D68" s="5" t="s">
@@ -4338,7 +4344,7 @@
       <c r="F68" s="5" t="s">
         <v>517</v>
       </c>
-      <c r="G68" s="28" t="s">
+      <c r="G68" s="32" t="s">
         <v>540</v>
       </c>
       <c r="H68" s="15" t="s">
@@ -4350,9 +4356,9 @@
       <c r="L68" s="2"/>
     </row>
     <row r="69" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A69" s="35"/>
-      <c r="B69" s="30"/>
-      <c r="C69" s="29"/>
+      <c r="A69" s="39"/>
+      <c r="B69" s="40"/>
+      <c r="C69" s="28"/>
       <c r="D69" s="5" t="s">
         <v>156</v>
       </c>
@@ -4362,7 +4368,7 @@
       <c r="F69" s="5" t="s">
         <v>516</v>
       </c>
-      <c r="G69" s="28"/>
+      <c r="G69" s="32"/>
       <c r="H69" s="15" t="s">
         <v>365</v>
       </c>
@@ -4372,13 +4378,13 @@
       <c r="L69" s="2"/>
     </row>
     <row r="70" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A70" s="34">
+      <c r="A70" s="38">
         <v>11</v>
       </c>
-      <c r="B70" s="30" t="s">
+      <c r="B70" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="C70" s="29" t="s">
+      <c r="C70" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D70" s="5" t="s">
@@ -4390,7 +4396,7 @@
       <c r="F70" s="5" t="s">
         <v>598</v>
       </c>
-      <c r="G70" s="28" t="s">
+      <c r="G70" s="32" t="s">
         <v>538</v>
       </c>
       <c r="H70" s="15" t="s">
@@ -4402,9 +4408,9 @@
       <c r="L70" s="2"/>
     </row>
     <row r="71" spans="1:12" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A71" s="35"/>
-      <c r="B71" s="30"/>
-      <c r="C71" s="29"/>
+      <c r="A71" s="39"/>
+      <c r="B71" s="40"/>
+      <c r="C71" s="28"/>
       <c r="D71" s="5" t="s">
         <v>154</v>
       </c>
@@ -4414,7 +4420,7 @@
       <c r="F71" s="5" t="s">
         <v>599</v>
       </c>
-      <c r="G71" s="28"/>
+      <c r="G71" s="32"/>
       <c r="H71" s="15" t="s">
         <v>366</v>
       </c>
@@ -4424,13 +4430,13 @@
       <c r="L71" s="2"/>
     </row>
     <row r="72" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A72" s="34">
+      <c r="A72" s="38">
         <v>12</v>
       </c>
-      <c r="B72" s="33" t="s">
+      <c r="B72" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C72" s="29" t="s">
+      <c r="C72" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D72" s="5" t="s">
@@ -4442,7 +4448,7 @@
       <c r="F72" s="5" t="s">
         <v>596</v>
       </c>
-      <c r="G72" s="28" t="s">
+      <c r="G72" s="32" t="s">
         <v>538</v>
       </c>
       <c r="H72" s="15" t="s">
@@ -4454,9 +4460,9 @@
       <c r="L72" s="2"/>
     </row>
     <row r="73" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A73" s="35"/>
-      <c r="B73" s="33"/>
-      <c r="C73" s="29"/>
+      <c r="A73" s="39"/>
+      <c r="B73" s="36"/>
+      <c r="C73" s="28"/>
       <c r="D73" s="5" t="s">
         <v>36</v>
       </c>
@@ -4466,7 +4472,7 @@
       <c r="F73" s="5" t="s">
         <v>597</v>
       </c>
-      <c r="G73" s="28"/>
+      <c r="G73" s="32"/>
       <c r="H73" s="15" t="s">
         <v>367</v>
       </c>
@@ -4476,13 +4482,13 @@
       <c r="L73" s="2"/>
     </row>
     <row r="74" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A74" s="34">
+      <c r="A74" s="38">
         <v>13</v>
       </c>
-      <c r="B74" s="33" t="s">
+      <c r="B74" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C74" s="29" t="s">
+      <c r="C74" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D74" s="5" t="s">
@@ -4494,7 +4500,7 @@
       <c r="F74" s="5" t="s">
         <v>514</v>
       </c>
-      <c r="G74" s="28"/>
+      <c r="G74" s="32"/>
       <c r="H74" s="15" t="s">
         <v>626</v>
       </c>
@@ -4504,9 +4510,9 @@
       <c r="L74" s="2"/>
     </row>
     <row r="75" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A75" s="35"/>
-      <c r="B75" s="33"/>
-      <c r="C75" s="29"/>
+      <c r="A75" s="39"/>
+      <c r="B75" s="36"/>
+      <c r="C75" s="28"/>
       <c r="D75" s="5" t="s">
         <v>34</v>
       </c>
@@ -4516,7 +4522,7 @@
       <c r="F75" s="5" t="s">
         <v>515</v>
       </c>
-      <c r="G75" s="28"/>
+      <c r="G75" s="32"/>
       <c r="H75" s="15" t="s">
         <v>627</v>
       </c>
@@ -4526,13 +4532,13 @@
       <c r="L75" s="2"/>
     </row>
     <row r="76" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A76" s="34">
+      <c r="A76" s="38">
         <v>14</v>
       </c>
-      <c r="B76" s="33" t="s">
+      <c r="B76" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C76" s="29" t="s">
+      <c r="C76" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D76" s="5" t="s">
@@ -4544,7 +4550,7 @@
       <c r="F76" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="G76" s="28" t="s">
+      <c r="G76" s="32" t="s">
         <v>538</v>
       </c>
       <c r="H76" s="15" t="s">
@@ -4556,9 +4562,9 @@
       <c r="L76" s="2"/>
     </row>
     <row r="77" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A77" s="35"/>
-      <c r="B77" s="33"/>
-      <c r="C77" s="29"/>
+      <c r="A77" s="39"/>
+      <c r="B77" s="36"/>
+      <c r="C77" s="28"/>
       <c r="D77" s="5" t="s">
         <v>125</v>
       </c>
@@ -4568,19 +4574,19 @@
       <c r="F77" s="5" t="s">
         <v>470</v>
       </c>
-      <c r="G77" s="28"/>
+      <c r="G77" s="32"/>
       <c r="H77" s="15" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="78" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A78" s="34">
+      <c r="A78" s="38">
         <v>15</v>
       </c>
-      <c r="B78" s="33" t="s">
+      <c r="B78" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C78" s="29" t="s">
+      <c r="C78" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D78" s="5" t="s">
@@ -4592,7 +4598,7 @@
       <c r="F78" s="5" t="s">
         <v>591</v>
       </c>
-      <c r="G78" s="28" t="s">
+      <c r="G78" s="32" t="s">
         <v>589</v>
       </c>
       <c r="H78" s="15" t="s">
@@ -4600,9 +4606,9 @@
       </c>
     </row>
     <row r="79" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A79" s="35"/>
-      <c r="B79" s="33"/>
-      <c r="C79" s="29"/>
+      <c r="A79" s="39"/>
+      <c r="B79" s="36"/>
+      <c r="C79" s="28"/>
       <c r="D79" s="5" t="s">
         <v>123</v>
       </c>
@@ -4612,19 +4618,19 @@
       <c r="F79" s="5" t="s">
         <v>592</v>
       </c>
-      <c r="G79" s="28"/>
+      <c r="G79" s="32"/>
       <c r="H79" s="15" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="80" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A80" s="34">
+      <c r="A80" s="38">
         <v>16</v>
       </c>
-      <c r="B80" s="33" t="s">
+      <c r="B80" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C80" s="50" t="s">
+      <c r="C80" s="41" t="s">
         <v>6</v>
       </c>
       <c r="D80" s="5" t="s">
@@ -4636,7 +4642,7 @@
       <c r="F80" s="5" t="s">
         <v>630</v>
       </c>
-      <c r="G80" s="28" t="s">
+      <c r="G80" s="32" t="s">
         <v>513</v>
       </c>
       <c r="H80" s="15" t="s">
@@ -4644,9 +4650,9 @@
       </c>
     </row>
     <row r="81" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A81" s="35"/>
-      <c r="B81" s="33"/>
-      <c r="C81" s="51"/>
+      <c r="A81" s="39"/>
+      <c r="B81" s="36"/>
+      <c r="C81" s="42"/>
       <c r="D81" s="5" t="s">
         <v>121</v>
       </c>
@@ -4656,19 +4662,19 @@
       <c r="F81" s="5" t="s">
         <v>631</v>
       </c>
-      <c r="G81" s="28"/>
+      <c r="G81" s="32"/>
       <c r="H81" s="15" t="s">
         <v>629</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A82" s="34">
+      <c r="A82" s="38">
         <v>17</v>
       </c>
-      <c r="B82" s="33" t="s">
+      <c r="B82" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C82" s="29" t="s">
+      <c r="C82" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D82" s="5" t="s">
@@ -4680,7 +4686,7 @@
       <c r="F82" s="5" t="s">
         <v>590</v>
       </c>
-      <c r="G82" s="28" t="s">
+      <c r="G82" s="32" t="s">
         <v>625</v>
       </c>
       <c r="H82" s="15" t="s">
@@ -4688,9 +4694,9 @@
       </c>
     </row>
     <row r="83" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A83" s="35"/>
-      <c r="B83" s="33"/>
-      <c r="C83" s="29"/>
+      <c r="A83" s="39"/>
+      <c r="B83" s="36"/>
+      <c r="C83" s="28"/>
       <c r="D83" s="5" t="s">
         <v>40</v>
       </c>
@@ -4700,19 +4706,19 @@
       <c r="F83" s="5" t="s">
         <v>483</v>
       </c>
-      <c r="G83" s="28"/>
+      <c r="G83" s="32"/>
       <c r="H83" s="15" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="84" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A84" s="43">
+      <c r="A84" s="33">
         <v>18</v>
       </c>
-      <c r="B84" s="33" t="s">
+      <c r="B84" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C84" s="45" t="s">
+      <c r="C84" s="37" t="s">
         <v>6</v>
       </c>
       <c r="D84" s="5" t="s">
@@ -4724,7 +4730,7 @@
       <c r="F84" s="5" t="s">
         <v>471</v>
       </c>
-      <c r="G84" s="28" t="s">
+      <c r="G84" s="32" t="s">
         <v>482</v>
       </c>
       <c r="H84" s="15" t="s">
@@ -4732,9 +4738,9 @@
       </c>
     </row>
     <row r="85" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A85" s="44"/>
-      <c r="B85" s="33"/>
-      <c r="C85" s="45"/>
+      <c r="A85" s="34"/>
+      <c r="B85" s="36"/>
+      <c r="C85" s="37"/>
       <c r="D85" s="5" t="s">
         <v>42</v>
       </c>
@@ -4744,19 +4750,19 @@
       <c r="F85" s="5" t="s">
         <v>472</v>
       </c>
-      <c r="G85" s="28"/>
+      <c r="G85" s="32"/>
       <c r="H85" s="15" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="86" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A86" s="34">
+      <c r="A86" s="38">
         <v>19</v>
       </c>
-      <c r="B86" s="33" t="s">
+      <c r="B86" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C86" s="29" t="s">
+      <c r="C86" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D86" s="5" t="s">
@@ -4768,15 +4774,15 @@
       <c r="F86" s="5" t="s">
         <v>636</v>
       </c>
-      <c r="G86" s="28"/>
+      <c r="G86" s="32"/>
       <c r="H86" s="15" t="s">
         <v>484</v>
       </c>
     </row>
     <row r="87" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A87" s="35"/>
-      <c r="B87" s="33"/>
-      <c r="C87" s="29"/>
+      <c r="A87" s="39"/>
+      <c r="B87" s="36"/>
+      <c r="C87" s="28"/>
       <c r="D87" s="5" t="s">
         <v>83</v>
       </c>
@@ -4786,19 +4792,19 @@
       <c r="F87" s="5" t="s">
         <v>635</v>
       </c>
-      <c r="G87" s="28"/>
+      <c r="G87" s="32"/>
       <c r="H87" s="15" t="s">
         <v>485</v>
       </c>
     </row>
     <row r="88" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A88" s="43">
+      <c r="A88" s="33">
         <v>20</v>
       </c>
-      <c r="B88" s="31" t="s">
+      <c r="B88" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C88" s="29" t="s">
+      <c r="C88" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D88" s="5" t="s">
@@ -4810,7 +4816,7 @@
       <c r="F88" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="G88" s="28" t="s">
+      <c r="G88" s="32" t="s">
         <v>260</v>
       </c>
       <c r="H88" s="15" t="s">
@@ -4818,9 +4824,9 @@
       </c>
     </row>
     <row r="89" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A89" s="44"/>
-      <c r="B89" s="31"/>
-      <c r="C89" s="29"/>
+      <c r="A89" s="34"/>
+      <c r="B89" s="35"/>
+      <c r="C89" s="28"/>
       <c r="D89" s="5" t="s">
         <v>259</v>
       </c>
@@ -4830,19 +4836,19 @@
       <c r="F89" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="G89" s="28"/>
+      <c r="G89" s="32"/>
       <c r="H89" s="15" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="90" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A90" s="43">
+      <c r="A90" s="33">
         <v>21</v>
       </c>
-      <c r="B90" s="31" t="s">
+      <c r="B90" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C90" s="29" t="s">
+      <c r="C90" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D90" s="5" t="s">
@@ -4854,7 +4860,7 @@
       <c r="F90" s="5" t="s">
         <v>520</v>
       </c>
-      <c r="G90" s="28" t="s">
+      <c r="G90" s="32" t="s">
         <v>524</v>
       </c>
       <c r="H90" s="15" t="s">
@@ -4862,9 +4868,9 @@
       </c>
     </row>
     <row r="91" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A91" s="44"/>
-      <c r="B91" s="31"/>
-      <c r="C91" s="29"/>
+      <c r="A91" s="34"/>
+      <c r="B91" s="35"/>
+      <c r="C91" s="28"/>
       <c r="D91" s="5" t="s">
         <v>127</v>
       </c>
@@ -4874,19 +4880,19 @@
       <c r="F91" s="5" t="s">
         <v>521</v>
       </c>
-      <c r="G91" s="28"/>
+      <c r="G91" s="32"/>
       <c r="H91" s="15" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="92" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A92" s="34">
+      <c r="A92" s="38">
         <v>22</v>
       </c>
-      <c r="B92" s="31" t="s">
+      <c r="B92" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C92" s="29" t="s">
+      <c r="C92" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D92" s="5" t="s">
@@ -4898,7 +4904,7 @@
       <c r="F92" s="5" t="s">
         <v>490</v>
       </c>
-      <c r="G92" s="28" t="s">
+      <c r="G92" s="32" t="s">
         <v>486</v>
       </c>
       <c r="H92" s="15" t="s">
@@ -4906,9 +4912,9 @@
       </c>
     </row>
     <row r="93" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A93" s="35"/>
-      <c r="B93" s="31"/>
-      <c r="C93" s="29"/>
+      <c r="A93" s="39"/>
+      <c r="B93" s="35"/>
+      <c r="C93" s="28"/>
       <c r="D93" s="5" t="s">
         <v>176</v>
       </c>
@@ -4918,19 +4924,19 @@
       <c r="F93" s="5" t="s">
         <v>491</v>
       </c>
-      <c r="G93" s="28"/>
+      <c r="G93" s="32"/>
       <c r="H93" s="15" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="94" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A94" s="34">
+      <c r="A94" s="38">
         <v>23</v>
       </c>
-      <c r="B94" s="31" t="s">
+      <c r="B94" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C94" s="29" t="s">
+      <c r="C94" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D94" s="5" t="s">
@@ -4942,7 +4948,7 @@
       <c r="F94" s="5" t="s">
         <v>615</v>
       </c>
-      <c r="G94" s="28" t="s">
+      <c r="G94" s="32" t="s">
         <v>275</v>
       </c>
       <c r="H94" s="15" t="s">
@@ -4950,9 +4956,9 @@
       </c>
     </row>
     <row r="95" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A95" s="35"/>
-      <c r="B95" s="31"/>
-      <c r="C95" s="29"/>
+      <c r="A95" s="39"/>
+      <c r="B95" s="35"/>
+      <c r="C95" s="28"/>
       <c r="D95" s="5" t="s">
         <v>31</v>
       </c>
@@ -4962,19 +4968,19 @@
       <c r="F95" s="5" t="s">
         <v>613</v>
       </c>
-      <c r="G95" s="28"/>
+      <c r="G95" s="32"/>
       <c r="H95" s="15" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="96" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A96" s="43">
+      <c r="A96" s="33">
         <v>24</v>
       </c>
-      <c r="B96" s="31" t="s">
+      <c r="B96" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C96" s="29" t="s">
+      <c r="C96" s="28" t="s">
         <v>6</v>
       </c>
       <c r="D96" s="5" t="s">
@@ -4986,7 +4992,7 @@
       <c r="F96" s="5" t="s">
         <v>518</v>
       </c>
-      <c r="G96" s="28" t="s">
+      <c r="G96" s="32" t="s">
         <v>198</v>
       </c>
       <c r="H96" s="15" t="s">
@@ -4994,9 +5000,9 @@
       </c>
     </row>
     <row r="97" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A97" s="44"/>
-      <c r="B97" s="31"/>
-      <c r="C97" s="29"/>
+      <c r="A97" s="34"/>
+      <c r="B97" s="35"/>
+      <c r="C97" s="28"/>
       <c r="D97" s="5" t="s">
         <v>166</v>
       </c>
@@ -5006,19 +5012,19 @@
       <c r="F97" s="5" t="s">
         <v>519</v>
       </c>
-      <c r="G97" s="28"/>
+      <c r="G97" s="32"/>
       <c r="H97" s="15" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="98" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A98" s="34">
+      <c r="A98" s="38">
         <v>25</v>
       </c>
-      <c r="B98" s="30" t="s">
+      <c r="B98" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="C98" s="29" t="s">
+      <c r="C98" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D98" s="5" t="s">
@@ -5030,15 +5036,15 @@
       <c r="F98" s="5" t="s">
         <v>651</v>
       </c>
-      <c r="G98" s="28"/>
+      <c r="G98" s="32"/>
       <c r="H98" s="15" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="99" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A99" s="35"/>
-      <c r="B99" s="30"/>
-      <c r="C99" s="29"/>
+      <c r="A99" s="39"/>
+      <c r="B99" s="40"/>
+      <c r="C99" s="28"/>
       <c r="D99" s="5" t="s">
         <v>146</v>
       </c>
@@ -5048,19 +5054,19 @@
       <c r="F99" s="5" t="s">
         <v>652</v>
       </c>
-      <c r="G99" s="28"/>
+      <c r="G99" s="32"/>
       <c r="H99" s="15" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="100" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A100" s="43">
+      <c r="A100" s="33">
         <v>26</v>
       </c>
-      <c r="B100" s="30" t="s">
+      <c r="B100" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="C100" s="45" t="s">
+      <c r="C100" s="37" t="s">
         <v>14</v>
       </c>
       <c r="D100" s="5" t="s">
@@ -5072,15 +5078,15 @@
       <c r="F100" s="5" t="s">
         <v>637</v>
       </c>
-      <c r="G100" s="28"/>
+      <c r="G100" s="32"/>
       <c r="H100" s="15" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="101" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A101" s="44"/>
-      <c r="B101" s="30"/>
-      <c r="C101" s="45"/>
+      <c r="A101" s="34"/>
+      <c r="B101" s="40"/>
+      <c r="C101" s="37"/>
       <c r="D101" s="5" t="s">
         <v>158</v>
       </c>
@@ -5090,19 +5096,19 @@
       <c r="F101" s="5" t="s">
         <v>638</v>
       </c>
-      <c r="G101" s="28"/>
+      <c r="G101" s="32"/>
       <c r="H101" s="15" t="s">
         <v>378</v>
       </c>
     </row>
     <row r="102" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A102" s="34">
+      <c r="A102" s="38">
         <v>27</v>
       </c>
-      <c r="B102" s="30" t="s">
+      <c r="B102" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="C102" s="29" t="s">
+      <c r="C102" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D102" s="5" t="s">
@@ -5114,15 +5120,15 @@
       <c r="F102" s="5" t="s">
         <v>642</v>
       </c>
-      <c r="G102" s="28"/>
+      <c r="G102" s="32"/>
       <c r="H102" s="15" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="103" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A103" s="35"/>
-      <c r="B103" s="30"/>
-      <c r="C103" s="29"/>
+      <c r="A103" s="39"/>
+      <c r="B103" s="40"/>
+      <c r="C103" s="28"/>
       <c r="D103" s="5" t="s">
         <v>45</v>
       </c>
@@ -5132,19 +5138,19 @@
       <c r="F103" s="5" t="s">
         <v>643</v>
       </c>
-      <c r="G103" s="28"/>
+      <c r="G103" s="32"/>
       <c r="H103" s="15" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="104" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A104" s="34">
+      <c r="A104" s="38">
         <v>28</v>
       </c>
-      <c r="B104" s="30" t="s">
+      <c r="B104" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="C104" s="29" t="s">
+      <c r="C104" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D104" s="5" t="s">
@@ -5156,15 +5162,15 @@
       <c r="F104" s="5" t="s">
         <v>559</v>
       </c>
-      <c r="G104" s="28"/>
+      <c r="G104" s="32"/>
       <c r="H104" s="15" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="105" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A105" s="35"/>
-      <c r="B105" s="30"/>
-      <c r="C105" s="29"/>
+      <c r="A105" s="39"/>
+      <c r="B105" s="40"/>
+      <c r="C105" s="28"/>
       <c r="D105" s="5" t="s">
         <v>67</v>
       </c>
@@ -5174,19 +5180,19 @@
       <c r="F105" s="5" t="s">
         <v>560</v>
       </c>
-      <c r="G105" s="28"/>
+      <c r="G105" s="32"/>
       <c r="H105" s="15" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="106" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A106" s="43">
+      <c r="A106" s="33">
         <v>29</v>
       </c>
-      <c r="B106" s="30" t="s">
+      <c r="B106" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="C106" s="29" t="s">
+      <c r="C106" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D106" s="5" t="s">
@@ -5198,7 +5204,7 @@
       <c r="F106" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="G106" s="28" t="s">
+      <c r="G106" s="32" t="s">
         <v>510</v>
       </c>
       <c r="H106" s="15" t="s">
@@ -5206,9 +5212,9 @@
       </c>
     </row>
     <row r="107" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A107" s="44"/>
-      <c r="B107" s="30"/>
-      <c r="C107" s="29"/>
+      <c r="A107" s="34"/>
+      <c r="B107" s="40"/>
+      <c r="C107" s="28"/>
       <c r="D107" s="5" t="s">
         <v>152</v>
       </c>
@@ -5218,19 +5224,19 @@
       <c r="F107" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="G107" s="28"/>
+      <c r="G107" s="32"/>
       <c r="H107" s="15" t="s">
         <v>381</v>
       </c>
     </row>
     <row r="108" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A108" s="34">
+      <c r="A108" s="38">
         <v>30</v>
       </c>
-      <c r="B108" s="30" t="s">
+      <c r="B108" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="C108" s="29" t="s">
+      <c r="C108" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D108" s="5" t="s">
@@ -5242,7 +5248,7 @@
       <c r="F108" s="5" t="s">
         <v>603</v>
       </c>
-      <c r="G108" s="28" t="s">
+      <c r="G108" s="32" t="s">
         <v>217</v>
       </c>
       <c r="H108" s="15" t="s">
@@ -5250,9 +5256,9 @@
       </c>
     </row>
     <row r="109" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A109" s="35"/>
-      <c r="B109" s="30"/>
-      <c r="C109" s="29"/>
+      <c r="A109" s="39"/>
+      <c r="B109" s="40"/>
+      <c r="C109" s="28"/>
       <c r="D109" s="5" t="s">
         <v>47</v>
       </c>
@@ -5262,19 +5268,19 @@
       <c r="F109" s="5" t="s">
         <v>604</v>
       </c>
-      <c r="G109" s="28"/>
+      <c r="G109" s="32"/>
       <c r="H109" s="15" t="s">
         <v>382</v>
       </c>
     </row>
     <row r="110" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A110" s="34">
+      <c r="A110" s="38">
         <v>31</v>
       </c>
-      <c r="B110" s="41" t="s">
+      <c r="B110" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="C110" s="32" t="s">
+      <c r="C110" s="43" t="s">
         <v>14</v>
       </c>
       <c r="D110" s="5" t="s">
@@ -5286,7 +5292,7 @@
       <c r="F110" s="5" t="s">
         <v>622</v>
       </c>
-      <c r="G110" s="46" t="s">
+      <c r="G110" s="48" t="s">
         <v>254</v>
       </c>
       <c r="H110" s="15" t="s">
@@ -5294,9 +5300,9 @@
       </c>
     </row>
     <row r="111" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A111" s="35"/>
-      <c r="B111" s="42"/>
-      <c r="C111" s="32"/>
+      <c r="A111" s="39"/>
+      <c r="B111" s="47"/>
+      <c r="C111" s="43"/>
       <c r="D111" s="5" t="s">
         <v>188</v>
       </c>
@@ -5306,19 +5312,19 @@
       <c r="F111" s="5" t="s">
         <v>623</v>
       </c>
-      <c r="G111" s="47"/>
+      <c r="G111" s="49"/>
       <c r="H111" s="15" t="s">
         <v>383</v>
       </c>
     </row>
     <row r="112" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A112" s="43">
+      <c r="A112" s="33">
         <v>32</v>
       </c>
-      <c r="B112" s="30" t="s">
+      <c r="B112" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="C112" s="45" t="s">
+      <c r="C112" s="37" t="s">
         <v>14</v>
       </c>
       <c r="D112" s="5" t="s">
@@ -5330,15 +5336,15 @@
       <c r="F112" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="G112" s="28"/>
+      <c r="G112" s="32"/>
       <c r="H112" s="15" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="113" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A113" s="44"/>
-      <c r="B113" s="30"/>
-      <c r="C113" s="45"/>
+      <c r="A113" s="34"/>
+      <c r="B113" s="40"/>
+      <c r="C113" s="37"/>
       <c r="D113" s="5" t="s">
         <v>52</v>
       </c>
@@ -5348,19 +5354,19 @@
       <c r="F113" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="G113" s="28"/>
+      <c r="G113" s="32"/>
       <c r="H113" s="15" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="114" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A114" s="34">
+      <c r="A114" s="38">
         <v>33</v>
       </c>
-      <c r="B114" s="30" t="s">
+      <c r="B114" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="C114" s="29" t="s">
+      <c r="C114" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D114" s="5" t="s">
@@ -5372,15 +5378,15 @@
       <c r="F114" s="5" t="s">
         <v>541</v>
       </c>
-      <c r="G114" s="28"/>
+      <c r="G114" s="32"/>
       <c r="H114" s="15" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="115" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A115" s="35"/>
-      <c r="B115" s="30"/>
-      <c r="C115" s="29"/>
+      <c r="A115" s="39"/>
+      <c r="B115" s="40"/>
+      <c r="C115" s="28"/>
       <c r="D115" s="5" t="s">
         <v>133</v>
       </c>
@@ -5390,19 +5396,19 @@
       <c r="F115" s="5" t="s">
         <v>542</v>
       </c>
-      <c r="G115" s="28"/>
+      <c r="G115" s="32"/>
       <c r="H115" s="15" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="116" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A116" s="34">
+      <c r="A116" s="38">
         <v>34</v>
       </c>
-      <c r="B116" s="30" t="s">
+      <c r="B116" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="C116" s="29" t="s">
+      <c r="C116" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D116" s="5" t="s">
@@ -5414,7 +5420,7 @@
       <c r="F116" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="G116" s="28" t="s">
+      <c r="G116" s="32" t="s">
         <v>217</v>
       </c>
       <c r="H116" s="15" t="s">
@@ -5422,9 +5428,9 @@
       </c>
     </row>
     <row r="117" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A117" s="35"/>
-      <c r="B117" s="30"/>
-      <c r="C117" s="29"/>
+      <c r="A117" s="39"/>
+      <c r="B117" s="40"/>
+      <c r="C117" s="28"/>
       <c r="D117" s="5" t="s">
         <v>75</v>
       </c>
@@ -5434,19 +5440,19 @@
       <c r="F117" s="5" t="s">
         <v>601</v>
       </c>
-      <c r="G117" s="28"/>
+      <c r="G117" s="32"/>
       <c r="H117" s="15" t="s">
         <v>429</v>
       </c>
     </row>
     <row r="118" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A118" s="34">
+      <c r="A118" s="38">
         <v>35</v>
       </c>
-      <c r="B118" s="30" t="s">
+      <c r="B118" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="C118" s="29" t="s">
+      <c r="C118" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D118" s="5" t="s">
@@ -5458,7 +5464,7 @@
       <c r="F118" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="G118" s="28" t="s">
+      <c r="G118" s="32" t="s">
         <v>217</v>
       </c>
       <c r="H118" s="15" t="s">
@@ -5466,9 +5472,9 @@
       </c>
     </row>
     <row r="119" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A119" s="35"/>
-      <c r="B119" s="30"/>
-      <c r="C119" s="29"/>
+      <c r="A119" s="39"/>
+      <c r="B119" s="40"/>
+      <c r="C119" s="28"/>
       <c r="D119" s="5" t="s">
         <v>77</v>
       </c>
@@ -5478,19 +5484,19 @@
       <c r="F119" s="5" t="s">
         <v>600</v>
       </c>
-      <c r="G119" s="28"/>
+      <c r="G119" s="32"/>
       <c r="H119" s="15" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="120" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A120" s="34">
+      <c r="A120" s="38">
         <v>36</v>
       </c>
-      <c r="B120" s="30" t="s">
+      <c r="B120" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="C120" s="29" t="s">
+      <c r="C120" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D120" s="5" t="s">
@@ -5502,7 +5508,7 @@
       <c r="F120" s="5" t="s">
         <v>644</v>
       </c>
-      <c r="G120" s="28" t="s">
+      <c r="G120" s="32" t="s">
         <v>245</v>
       </c>
       <c r="H120" s="15" t="s">
@@ -5510,9 +5516,9 @@
       </c>
     </row>
     <row r="121" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A121" s="35"/>
-      <c r="B121" s="30"/>
-      <c r="C121" s="29"/>
+      <c r="A121" s="39"/>
+      <c r="B121" s="40"/>
+      <c r="C121" s="28"/>
       <c r="D121" s="5" t="s">
         <v>119</v>
       </c>
@@ -5522,19 +5528,19 @@
       <c r="F121" s="5" t="s">
         <v>645</v>
       </c>
-      <c r="G121" s="28"/>
+      <c r="G121" s="32"/>
       <c r="H121" s="15" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="122" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A122" s="34">
+      <c r="A122" s="38">
         <v>37</v>
       </c>
-      <c r="B122" s="41" t="s">
+      <c r="B122" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="C122" s="29" t="s">
+      <c r="C122" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D122" s="5" t="s">
@@ -5546,15 +5552,15 @@
       <c r="F122" s="5" t="s">
         <v>658</v>
       </c>
-      <c r="G122" s="28"/>
+      <c r="G122" s="32"/>
       <c r="H122" s="15" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="123" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A123" s="35"/>
-      <c r="B123" s="42"/>
-      <c r="C123" s="29"/>
+      <c r="A123" s="39"/>
+      <c r="B123" s="47"/>
+      <c r="C123" s="28"/>
       <c r="D123" s="5" t="s">
         <v>180</v>
       </c>
@@ -5564,19 +5570,19 @@
       <c r="F123" s="5" t="s">
         <v>658</v>
       </c>
-      <c r="G123" s="28"/>
+      <c r="G123" s="32"/>
       <c r="H123" s="15" t="s">
         <v>388</v>
       </c>
     </row>
     <row r="124" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A124" s="34">
+      <c r="A124" s="38">
         <v>38</v>
       </c>
-      <c r="B124" s="41" t="s">
+      <c r="B124" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="C124" s="29" t="s">
+      <c r="C124" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D124" s="5" t="s">
@@ -5588,15 +5594,15 @@
       <c r="F124" s="5" t="s">
         <v>478</v>
       </c>
-      <c r="G124" s="28"/>
+      <c r="G124" s="32"/>
       <c r="H124" s="15" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="125" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A125" s="35"/>
-      <c r="B125" s="42"/>
-      <c r="C125" s="29"/>
+      <c r="A125" s="39"/>
+      <c r="B125" s="47"/>
+      <c r="C125" s="28"/>
       <c r="D125" s="5" t="s">
         <v>54</v>
       </c>
@@ -5606,19 +5612,19 @@
       <c r="F125" s="5" t="s">
         <v>479</v>
       </c>
-      <c r="G125" s="28"/>
+      <c r="G125" s="32"/>
       <c r="H125" s="15" t="s">
         <v>392</v>
       </c>
     </row>
     <row r="126" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A126" s="34">
+      <c r="A126" s="38">
         <v>39</v>
       </c>
-      <c r="B126" s="41" t="s">
+      <c r="B126" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="C126" s="29" t="s">
+      <c r="C126" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D126" s="5" t="s">
@@ -5630,7 +5636,7 @@
       <c r="F126" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="G126" s="28" t="s">
+      <c r="G126" s="32" t="s">
         <v>646</v>
       </c>
       <c r="H126" s="15" t="s">
@@ -5638,9 +5644,9 @@
       </c>
     </row>
     <row r="127" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A127" s="35"/>
-      <c r="B127" s="42"/>
-      <c r="C127" s="29"/>
+      <c r="A127" s="39"/>
+      <c r="B127" s="47"/>
+      <c r="C127" s="28"/>
       <c r="D127" s="5" t="s">
         <v>131</v>
       </c>
@@ -5650,19 +5656,19 @@
       <c r="F127" s="5" t="s">
         <v>551</v>
       </c>
-      <c r="G127" s="28"/>
+      <c r="G127" s="32"/>
       <c r="H127" s="15" t="s">
         <v>550</v>
       </c>
     </row>
     <row r="128" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A128" s="43">
+      <c r="A128" s="33">
         <v>40</v>
       </c>
-      <c r="B128" s="41" t="s">
+      <c r="B128" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="C128" s="29" t="s">
+      <c r="C128" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D128" s="5" t="s">
@@ -5674,15 +5680,15 @@
       <c r="F128" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="G128" s="28"/>
+      <c r="G128" s="32"/>
       <c r="H128" s="15" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="129" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A129" s="44"/>
-      <c r="B129" s="42"/>
-      <c r="C129" s="29"/>
+      <c r="A129" s="34"/>
+      <c r="B129" s="47"/>
+      <c r="C129" s="28"/>
       <c r="D129" s="5" t="s">
         <v>79</v>
       </c>
@@ -5692,19 +5698,19 @@
       <c r="F129" s="5" t="s">
         <v>487</v>
       </c>
-      <c r="G129" s="28"/>
+      <c r="G129" s="32"/>
       <c r="H129" s="15" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="130" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A130" s="34">
+      <c r="A130" s="38">
         <v>41</v>
       </c>
-      <c r="B130" s="41" t="s">
+      <c r="B130" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="C130" s="32" t="s">
+      <c r="C130" s="43" t="s">
         <v>14</v>
       </c>
       <c r="D130" s="5" t="s">
@@ -5716,15 +5722,15 @@
       <c r="F130" s="5" t="s">
         <v>633</v>
       </c>
-      <c r="G130" s="28"/>
+      <c r="G130" s="32"/>
       <c r="H130" s="15" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="131" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A131" s="35"/>
-      <c r="B131" s="42"/>
-      <c r="C131" s="32"/>
+      <c r="A131" s="39"/>
+      <c r="B131" s="47"/>
+      <c r="C131" s="43"/>
       <c r="D131" s="5" t="s">
         <v>65</v>
       </c>
@@ -5734,19 +5740,19 @@
       <c r="F131" s="5" t="s">
         <v>634</v>
       </c>
-      <c r="G131" s="28"/>
+      <c r="G131" s="32"/>
       <c r="H131" s="15" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="132" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A132" s="34">
+      <c r="A132" s="38">
         <v>42</v>
       </c>
-      <c r="B132" s="33" t="s">
+      <c r="B132" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C132" s="29" t="s">
+      <c r="C132" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D132" s="5" t="s">
@@ -5758,15 +5764,15 @@
       <c r="F132" s="5" t="s">
         <v>555</v>
       </c>
-      <c r="G132" s="28"/>
+      <c r="G132" s="32"/>
       <c r="H132" s="15" t="s">
         <v>553</v>
       </c>
     </row>
     <row r="133" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A133" s="35"/>
-      <c r="B133" s="33"/>
-      <c r="C133" s="29"/>
+      <c r="A133" s="39"/>
+      <c r="B133" s="36"/>
+      <c r="C133" s="28"/>
       <c r="D133" s="5" t="s">
         <v>51</v>
       </c>
@@ -5776,19 +5782,19 @@
       <c r="F133" s="5" t="s">
         <v>552</v>
       </c>
-      <c r="G133" s="28"/>
+      <c r="G133" s="32"/>
       <c r="H133" s="15" t="s">
         <v>554</v>
       </c>
     </row>
     <row r="134" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A134" s="43">
+      <c r="A134" s="38">
         <v>43</v>
       </c>
-      <c r="B134" s="33" t="s">
+      <c r="B134" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C134" s="29" t="s">
+      <c r="C134" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D134" s="5" t="s">
@@ -5800,15 +5806,15 @@
       <c r="F134" s="5" t="s">
         <v>664</v>
       </c>
-      <c r="G134" s="28"/>
+      <c r="G134" s="32"/>
       <c r="H134" s="15" t="s">
         <v>620</v>
       </c>
     </row>
     <row r="135" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A135" s="44"/>
-      <c r="B135" s="33"/>
-      <c r="C135" s="29"/>
+      <c r="A135" s="39"/>
+      <c r="B135" s="36"/>
+      <c r="C135" s="28"/>
       <c r="D135" s="5" t="s">
         <v>619</v>
       </c>
@@ -5818,19 +5824,19 @@
       <c r="F135" s="5" t="s">
         <v>665</v>
       </c>
-      <c r="G135" s="28"/>
+      <c r="G135" s="32"/>
       <c r="H135" s="15" t="s">
         <v>621</v>
       </c>
     </row>
     <row r="136" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A136" s="43">
+      <c r="A136" s="38">
         <v>44</v>
       </c>
-      <c r="B136" s="33" t="s">
+      <c r="B136" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C136" s="29" t="s">
+      <c r="C136" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D136" s="5" t="s">
@@ -5842,15 +5848,15 @@
       <c r="F136" s="5" t="s">
         <v>473</v>
       </c>
-      <c r="G136" s="28"/>
+      <c r="G136" s="32"/>
       <c r="H136" s="15" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="137" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A137" s="44"/>
-      <c r="B137" s="33"/>
-      <c r="C137" s="29"/>
+      <c r="A137" s="39"/>
+      <c r="B137" s="36"/>
+      <c r="C137" s="28"/>
       <c r="D137" s="5" t="s">
         <v>49</v>
       </c>
@@ -5860,19 +5866,19 @@
       <c r="F137" s="5" t="s">
         <v>474</v>
       </c>
-      <c r="G137" s="28"/>
+      <c r="G137" s="32"/>
       <c r="H137" s="15" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="138" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A138" s="43">
+      <c r="A138" s="33">
         <v>45</v>
       </c>
-      <c r="B138" s="33" t="s">
+      <c r="B138" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C138" s="45" t="s">
+      <c r="C138" s="37" t="s">
         <v>14</v>
       </c>
       <c r="D138" s="5" t="s">
@@ -5884,15 +5890,15 @@
       <c r="F138" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="G138" s="28"/>
+      <c r="G138" s="32"/>
       <c r="H138" s="15" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="139" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A139" s="44"/>
-      <c r="B139" s="33"/>
-      <c r="C139" s="45"/>
+      <c r="A139" s="34"/>
+      <c r="B139" s="36"/>
+      <c r="C139" s="37"/>
       <c r="D139" s="5" t="s">
         <v>178</v>
       </c>
@@ -5902,19 +5908,19 @@
       <c r="F139" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="G139" s="28"/>
+      <c r="G139" s="32"/>
       <c r="H139" s="15" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="140" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A140" s="43">
+      <c r="A140" s="33">
         <v>46</v>
       </c>
-      <c r="B140" s="33" t="s">
+      <c r="B140" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C140" s="29" t="s">
+      <c r="C140" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D140" s="5" t="s">
@@ -5926,7 +5932,7 @@
       <c r="F140" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="G140" s="28" t="s">
+      <c r="G140" s="32" t="s">
         <v>210</v>
       </c>
       <c r="H140" s="15" t="s">
@@ -5934,9 +5940,9 @@
       </c>
     </row>
     <row r="141" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A141" s="44"/>
-      <c r="B141" s="33"/>
-      <c r="C141" s="29"/>
+      <c r="A141" s="34"/>
+      <c r="B141" s="36"/>
+      <c r="C141" s="28"/>
       <c r="D141" s="5" t="s">
         <v>233</v>
       </c>
@@ -5946,19 +5952,19 @@
       <c r="F141" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="G141" s="28"/>
+      <c r="G141" s="32"/>
       <c r="H141" s="15" t="s">
         <v>390</v>
       </c>
     </row>
     <row r="142" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A142" s="43">
+      <c r="A142" s="33">
         <v>47</v>
       </c>
-      <c r="B142" s="33" t="s">
+      <c r="B142" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C142" s="29" t="s">
+      <c r="C142" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D142" s="5" t="s">
@@ -5970,7 +5976,7 @@
       <c r="F142" s="5" t="s">
         <v>475</v>
       </c>
-      <c r="G142" s="28" t="s">
+      <c r="G142" s="32" t="s">
         <v>538</v>
       </c>
       <c r="H142" s="15" t="s">
@@ -5978,9 +5984,9 @@
       </c>
     </row>
     <row r="143" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A143" s="44"/>
-      <c r="B143" s="33"/>
-      <c r="C143" s="29"/>
+      <c r="A143" s="34"/>
+      <c r="B143" s="36"/>
+      <c r="C143" s="28"/>
       <c r="D143" s="5" t="s">
         <v>165</v>
       </c>
@@ -5990,19 +5996,19 @@
       <c r="F143" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="G143" s="28"/>
+      <c r="G143" s="32"/>
       <c r="H143" s="15" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="144" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A144" s="34">
+      <c r="A144" s="38">
         <v>48</v>
       </c>
-      <c r="B144" s="33" t="s">
+      <c r="B144" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C144" s="29" t="s">
+      <c r="C144" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D144" s="5" t="s">
@@ -6014,15 +6020,15 @@
       <c r="F144" s="5" t="s">
         <v>477</v>
       </c>
-      <c r="G144" s="28"/>
+      <c r="G144" s="32"/>
       <c r="H144" s="15" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="145" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A145" s="35"/>
-      <c r="B145" s="33"/>
-      <c r="C145" s="29"/>
+      <c r="A145" s="39"/>
+      <c r="B145" s="36"/>
+      <c r="C145" s="28"/>
       <c r="D145" s="5" t="s">
         <v>55</v>
       </c>
@@ -6032,19 +6038,19 @@
       <c r="F145" s="5" t="s">
         <v>477</v>
       </c>
-      <c r="G145" s="28"/>
+      <c r="G145" s="32"/>
       <c r="H145" s="15" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="146" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A146" s="43">
+      <c r="A146" s="33">
         <v>49</v>
       </c>
-      <c r="B146" s="33" t="s">
+      <c r="B146" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C146" s="45" t="s">
+      <c r="C146" s="37" t="s">
         <v>14</v>
       </c>
       <c r="D146" s="5" t="s">
@@ -6056,7 +6062,7 @@
       <c r="F146" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="G146" s="28" t="s">
+      <c r="G146" s="32" t="s">
         <v>538</v>
       </c>
       <c r="H146" s="15" t="s">
@@ -6064,9 +6070,9 @@
       </c>
     </row>
     <row r="147" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A147" s="44"/>
-      <c r="B147" s="33"/>
-      <c r="C147" s="45"/>
+      <c r="A147" s="34"/>
+      <c r="B147" s="36"/>
+      <c r="C147" s="37"/>
       <c r="D147" s="5" t="s">
         <v>57</v>
       </c>
@@ -6076,19 +6082,19 @@
       <c r="F147" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="G147" s="28"/>
+      <c r="G147" s="32"/>
       <c r="H147" s="15" t="s">
         <v>425</v>
       </c>
     </row>
     <row r="148" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A148" s="34">
+      <c r="A148" s="38">
         <v>50</v>
       </c>
-      <c r="B148" s="33" t="s">
+      <c r="B148" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C148" s="32" t="s">
+      <c r="C148" s="43" t="s">
         <v>14</v>
       </c>
       <c r="D148" s="5" t="s">
@@ -6100,15 +6106,15 @@
       <c r="F148" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="G148" s="28"/>
+      <c r="G148" s="32"/>
       <c r="H148" s="15" t="s">
         <v>500</v>
       </c>
     </row>
     <row r="149" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A149" s="35"/>
-      <c r="B149" s="33"/>
-      <c r="C149" s="32"/>
+      <c r="A149" s="39"/>
+      <c r="B149" s="36"/>
+      <c r="C149" s="43"/>
       <c r="D149" s="5" t="s">
         <v>59</v>
       </c>
@@ -6118,19 +6124,19 @@
       <c r="F149" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="G149" s="28"/>
+      <c r="G149" s="32"/>
       <c r="H149" s="15" t="s">
         <v>501</v>
       </c>
     </row>
     <row r="150" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A150" s="34">
+      <c r="A150" s="38">
         <v>51</v>
       </c>
-      <c r="B150" s="33" t="s">
+      <c r="B150" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C150" s="29" t="s">
+      <c r="C150" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D150" s="5" t="s">
@@ -6142,15 +6148,15 @@
       <c r="F150" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="G150" s="28"/>
+      <c r="G150" s="32"/>
       <c r="H150" s="15" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="151" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A151" s="35"/>
-      <c r="B151" s="33"/>
-      <c r="C151" s="29"/>
+      <c r="A151" s="39"/>
+      <c r="B151" s="36"/>
+      <c r="C151" s="28"/>
       <c r="D151" s="5" t="s">
         <v>182</v>
       </c>
@@ -6160,19 +6166,19 @@
       <c r="F151" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="G151" s="28"/>
+      <c r="G151" s="32"/>
       <c r="H151" s="15" t="s">
         <v>394</v>
       </c>
     </row>
     <row r="152" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A152" s="34">
+      <c r="A152" s="38">
         <v>52</v>
       </c>
-      <c r="B152" s="33" t="s">
+      <c r="B152" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C152" s="29" t="s">
+      <c r="C152" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D152" s="5" t="s">
@@ -6184,15 +6190,15 @@
       <c r="F152" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="G152" s="28"/>
+      <c r="G152" s="32"/>
       <c r="H152" s="15" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="153" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A153" s="35"/>
-      <c r="B153" s="33"/>
-      <c r="C153" s="29"/>
+      <c r="A153" s="39"/>
+      <c r="B153" s="36"/>
+      <c r="C153" s="28"/>
       <c r="D153" s="5" t="s">
         <v>191</v>
       </c>
@@ -6202,19 +6208,19 @@
       <c r="F153" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="G153" s="28"/>
+      <c r="G153" s="32"/>
       <c r="H153" s="15" t="s">
         <v>427</v>
       </c>
     </row>
     <row r="154" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A154" s="43">
+      <c r="A154" s="33">
         <v>53</v>
       </c>
-      <c r="B154" s="33" t="s">
+      <c r="B154" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C154" s="29" t="s">
+      <c r="C154" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D154" s="5" t="s">
@@ -6226,7 +6232,7 @@
       <c r="F154" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="G154" s="28" t="s">
+      <c r="G154" s="32" t="s">
         <v>602</v>
       </c>
       <c r="H154" s="15" t="s">
@@ -6234,9 +6240,9 @@
       </c>
     </row>
     <row r="155" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A155" s="44"/>
-      <c r="B155" s="33"/>
-      <c r="C155" s="29"/>
+      <c r="A155" s="34"/>
+      <c r="B155" s="36"/>
+      <c r="C155" s="28"/>
       <c r="D155" s="5" t="s">
         <v>63</v>
       </c>
@@ -6246,19 +6252,19 @@
       <c r="F155" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="G155" s="28"/>
+      <c r="G155" s="32"/>
       <c r="H155" s="15" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="156" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A156" s="43">
+      <c r="A156" s="33">
         <v>54</v>
       </c>
-      <c r="B156" s="33" t="s">
+      <c r="B156" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C156" s="29" t="s">
+      <c r="C156" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D156" s="5" t="s">
@@ -6270,15 +6276,15 @@
       <c r="F156" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="G156" s="28"/>
+      <c r="G156" s="32"/>
       <c r="H156" s="15" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="157" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A157" s="44"/>
-      <c r="B157" s="33"/>
-      <c r="C157" s="29"/>
+      <c r="A157" s="34"/>
+      <c r="B157" s="36"/>
+      <c r="C157" s="28"/>
       <c r="D157" s="5" t="s">
         <v>160</v>
       </c>
@@ -6288,19 +6294,19 @@
       <c r="F157" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="G157" s="28"/>
+      <c r="G157" s="32"/>
       <c r="H157" s="15" t="s">
         <v>396</v>
       </c>
     </row>
     <row r="158" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A158" s="43">
+      <c r="A158" s="33">
         <v>55</v>
       </c>
-      <c r="B158" s="33" t="s">
+      <c r="B158" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C158" s="29" t="s">
+      <c r="C158" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D158" s="5" t="s">
@@ -6312,15 +6318,15 @@
       <c r="F158" s="5" t="s">
         <v>557</v>
       </c>
-      <c r="G158" s="28"/>
+      <c r="G158" s="32"/>
       <c r="H158" s="15" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="159" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A159" s="44"/>
-      <c r="B159" s="33"/>
-      <c r="C159" s="29"/>
+      <c r="A159" s="34"/>
+      <c r="B159" s="36"/>
+      <c r="C159" s="28"/>
       <c r="D159" s="5" t="s">
         <v>162</v>
       </c>
@@ -6330,19 +6336,19 @@
       <c r="F159" s="5" t="s">
         <v>558</v>
       </c>
-      <c r="G159" s="28"/>
+      <c r="G159" s="32"/>
       <c r="H159" s="15" t="s">
         <v>397</v>
       </c>
     </row>
     <row r="160" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A160" s="43">
+      <c r="A160" s="33">
         <v>56</v>
       </c>
-      <c r="B160" s="33" t="s">
+      <c r="B160" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C160" s="29" t="s">
+      <c r="C160" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D160" s="5" t="s">
@@ -6354,7 +6360,7 @@
       <c r="F160" s="5" t="s">
         <v>556</v>
       </c>
-      <c r="G160" s="28" t="s">
+      <c r="G160" s="32" t="s">
         <v>512</v>
       </c>
       <c r="H160" s="15" t="s">
@@ -6362,9 +6368,9 @@
       </c>
     </row>
     <row r="161" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A161" s="44"/>
-      <c r="B161" s="33"/>
-      <c r="C161" s="29"/>
+      <c r="A161" s="34"/>
+      <c r="B161" s="36"/>
+      <c r="C161" s="28"/>
       <c r="D161" s="5" t="s">
         <v>150</v>
       </c>
@@ -6374,19 +6380,19 @@
       <c r="F161" s="5" t="s">
         <v>556</v>
       </c>
-      <c r="G161" s="28"/>
+      <c r="G161" s="32"/>
       <c r="H161" s="15" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="162" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A162" s="43">
+      <c r="A162" s="33">
         <v>57</v>
       </c>
-      <c r="B162" s="33" t="s">
+      <c r="B162" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C162" s="29" t="s">
+      <c r="C162" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D162" s="5" t="s">
@@ -6398,7 +6404,7 @@
       <c r="F162" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="G162" s="28" t="s">
+      <c r="G162" s="32" t="s">
         <v>543</v>
       </c>
       <c r="H162" s="15" t="s">
@@ -6406,9 +6412,9 @@
       </c>
     </row>
     <row r="163" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A163" s="44"/>
-      <c r="B163" s="33"/>
-      <c r="C163" s="29"/>
+      <c r="A163" s="34"/>
+      <c r="B163" s="36"/>
+      <c r="C163" s="28"/>
       <c r="D163" s="5" t="s">
         <v>170</v>
       </c>
@@ -6418,19 +6424,19 @@
       <c r="F163" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="G163" s="28"/>
+      <c r="G163" s="32"/>
       <c r="H163" s="15" t="s">
         <v>400</v>
       </c>
     </row>
     <row r="164" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A164" s="43">
+      <c r="A164" s="33">
         <v>58</v>
       </c>
-      <c r="B164" s="33" t="s">
+      <c r="B164" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C164" s="45" t="s">
+      <c r="C164" s="37" t="s">
         <v>14</v>
       </c>
       <c r="D164" s="5" t="s">
@@ -6442,15 +6448,15 @@
       <c r="F164" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="G164" s="28"/>
+      <c r="G164" s="32"/>
       <c r="H164" s="15" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="165" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A165" s="44"/>
-      <c r="B165" s="33"/>
-      <c r="C165" s="45"/>
+      <c r="A165" s="34"/>
+      <c r="B165" s="36"/>
+      <c r="C165" s="37"/>
       <c r="D165" s="5" t="s">
         <v>172</v>
       </c>
@@ -6460,19 +6466,19 @@
       <c r="F165" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="G165" s="28"/>
+      <c r="G165" s="32"/>
       <c r="H165" s="15" t="s">
         <v>401</v>
       </c>
     </row>
     <row r="166" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A166" s="43">
+      <c r="A166" s="33">
         <v>59</v>
       </c>
-      <c r="B166" s="33" t="s">
+      <c r="B166" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C166" s="45" t="s">
+      <c r="C166" s="37" t="s">
         <v>14</v>
       </c>
       <c r="D166" s="5" t="s">
@@ -6484,7 +6490,7 @@
       <c r="F166" s="5" t="s">
         <v>639</v>
       </c>
-      <c r="G166" s="28" t="s">
+      <c r="G166" s="32" t="s">
         <v>192</v>
       </c>
       <c r="H166" s="15" t="s">
@@ -6492,9 +6498,9 @@
       </c>
     </row>
     <row r="167" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A167" s="44"/>
-      <c r="B167" s="33"/>
-      <c r="C167" s="45"/>
+      <c r="A167" s="34"/>
+      <c r="B167" s="36"/>
+      <c r="C167" s="37"/>
       <c r="D167" s="5" t="s">
         <v>142</v>
       </c>
@@ -6504,19 +6510,19 @@
       <c r="F167" s="5" t="s">
         <v>639</v>
       </c>
-      <c r="G167" s="28"/>
+      <c r="G167" s="32"/>
       <c r="H167" s="15" t="s">
         <v>402</v>
       </c>
     </row>
     <row r="168" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A168" s="43">
+      <c r="A168" s="33">
         <v>60</v>
       </c>
-      <c r="B168" s="33" t="s">
+      <c r="B168" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C168" s="45" t="s">
+      <c r="C168" s="37" t="s">
         <v>14</v>
       </c>
       <c r="D168" s="5" t="s">
@@ -6528,15 +6534,15 @@
       <c r="F168" s="5" t="s">
         <v>640</v>
       </c>
-      <c r="G168" s="28"/>
+      <c r="G168" s="32"/>
       <c r="H168" s="15" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="169" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A169" s="44"/>
-      <c r="B169" s="33"/>
-      <c r="C169" s="45"/>
+      <c r="A169" s="34"/>
+      <c r="B169" s="36"/>
+      <c r="C169" s="37"/>
       <c r="D169" s="5" t="s">
         <v>116</v>
       </c>
@@ -6546,19 +6552,19 @@
       <c r="F169" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="G169" s="28"/>
+      <c r="G169" s="32"/>
       <c r="H169" s="15" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="170" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A170" s="34">
+      <c r="A170" s="38">
         <v>61</v>
       </c>
-      <c r="B170" s="33" t="s">
+      <c r="B170" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C170" s="29" t="s">
+      <c r="C170" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D170" s="5" t="s">
@@ -6570,7 +6576,7 @@
       <c r="F170" s="5" t="s">
         <v>611</v>
       </c>
-      <c r="G170" s="28" t="s">
+      <c r="G170" s="32" t="s">
         <v>657</v>
       </c>
       <c r="H170" s="15" t="s">
@@ -6578,9 +6584,9 @@
       </c>
     </row>
     <row r="171" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A171" s="35"/>
-      <c r="B171" s="33"/>
-      <c r="C171" s="29"/>
+      <c r="A171" s="39"/>
+      <c r="B171" s="36"/>
+      <c r="C171" s="28"/>
       <c r="D171" s="5" t="s">
         <v>81</v>
       </c>
@@ -6590,19 +6596,19 @@
       <c r="F171" s="5" t="s">
         <v>612</v>
       </c>
-      <c r="G171" s="28"/>
+      <c r="G171" s="32"/>
       <c r="H171" s="15" t="s">
         <v>656</v>
       </c>
     </row>
     <row r="172" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A172" s="34">
+      <c r="A172" s="38">
         <v>62</v>
       </c>
-      <c r="B172" s="33" t="s">
+      <c r="B172" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C172" s="32" t="s">
+      <c r="C172" s="43" t="s">
         <v>14</v>
       </c>
       <c r="D172" s="5" t="s">
@@ -6614,15 +6620,15 @@
       <c r="F172" s="5" t="s">
         <v>530</v>
       </c>
-      <c r="G172" s="28"/>
+      <c r="G172" s="32"/>
       <c r="H172" s="15" t="s">
         <v>529</v>
       </c>
     </row>
     <row r="173" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A173" s="35"/>
-      <c r="B173" s="33"/>
-      <c r="C173" s="32"/>
+      <c r="A173" s="39"/>
+      <c r="B173" s="36"/>
+      <c r="C173" s="43"/>
       <c r="D173" s="5" t="s">
         <v>527</v>
       </c>
@@ -6632,19 +6638,19 @@
       <c r="F173" s="5" t="s">
         <v>531</v>
       </c>
-      <c r="G173" s="28"/>
+      <c r="G173" s="32"/>
       <c r="H173" s="15" t="s">
         <v>529</v>
       </c>
     </row>
     <row r="174" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A174" s="43">
+      <c r="A174" s="33">
         <v>63</v>
       </c>
-      <c r="B174" s="33" t="s">
+      <c r="B174" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C174" s="45" t="s">
+      <c r="C174" s="37" t="s">
         <v>14</v>
       </c>
       <c r="D174" s="5" t="s">
@@ -6656,7 +6662,7 @@
       <c r="F174" s="5" t="s">
         <v>659</v>
       </c>
-      <c r="G174" s="28" t="s">
+      <c r="G174" s="32" t="s">
         <v>576</v>
       </c>
       <c r="H174" s="15" t="s">
@@ -6664,9 +6670,9 @@
       </c>
     </row>
     <row r="175" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A175" s="44"/>
-      <c r="B175" s="33"/>
-      <c r="C175" s="45"/>
+      <c r="A175" s="34"/>
+      <c r="B175" s="36"/>
+      <c r="C175" s="37"/>
       <c r="D175" s="5" t="s">
         <v>195</v>
       </c>
@@ -6676,19 +6682,19 @@
       <c r="F175" s="5" t="s">
         <v>577</v>
       </c>
-      <c r="G175" s="28"/>
+      <c r="G175" s="32"/>
       <c r="H175" s="15" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="176" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A176" s="43">
+      <c r="A176" s="33">
         <v>64</v>
       </c>
-      <c r="B176" s="33" t="s">
+      <c r="B176" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C176" s="29" t="s">
+      <c r="C176" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D176" s="5" t="s">
@@ -6700,7 +6706,7 @@
       <c r="F176" s="5" t="s">
         <v>654</v>
       </c>
-      <c r="G176" s="28" t="s">
+      <c r="G176" s="32" t="s">
         <v>112</v>
       </c>
       <c r="H176" s="15" t="s">
@@ -6708,9 +6714,9 @@
       </c>
     </row>
     <row r="177" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A177" s="44"/>
-      <c r="B177" s="33"/>
-      <c r="C177" s="29"/>
+      <c r="A177" s="34"/>
+      <c r="B177" s="36"/>
+      <c r="C177" s="28"/>
       <c r="D177" s="5" t="s">
         <v>111</v>
       </c>
@@ -6720,19 +6726,19 @@
       <c r="F177" s="5" t="s">
         <v>653</v>
       </c>
-      <c r="G177" s="28"/>
+      <c r="G177" s="32"/>
       <c r="H177" s="15" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="178" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A178" s="43">
+      <c r="A178" s="33">
         <v>65</v>
       </c>
-      <c r="B178" s="31" t="s">
+      <c r="B178" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C178" s="29" t="s">
+      <c r="C178" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D178" s="5" t="s">
@@ -6744,15 +6750,15 @@
       <c r="F178" s="5" t="s">
         <v>660</v>
       </c>
-      <c r="G178" s="28"/>
+      <c r="G178" s="32"/>
       <c r="H178" s="15" t="s">
         <v>616</v>
       </c>
     </row>
     <row r="179" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A179" s="44"/>
-      <c r="B179" s="31"/>
-      <c r="C179" s="29"/>
+      <c r="A179" s="34"/>
+      <c r="B179" s="35"/>
+      <c r="C179" s="28"/>
       <c r="D179" s="5" t="s">
         <v>609</v>
       </c>
@@ -6762,19 +6768,19 @@
       <c r="F179" s="5" t="s">
         <v>610</v>
       </c>
-      <c r="G179" s="28"/>
+      <c r="G179" s="32"/>
       <c r="H179" s="15" t="s">
         <v>617</v>
       </c>
     </row>
     <row r="180" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A180" s="43">
+      <c r="A180" s="33">
         <v>66</v>
       </c>
-      <c r="B180" s="31" t="s">
+      <c r="B180" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C180" s="29" t="s">
+      <c r="C180" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D180" s="5" t="s">
@@ -6786,15 +6792,15 @@
       <c r="F180" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="G180" s="28"/>
+      <c r="G180" s="32"/>
       <c r="H180" s="15" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="181" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A181" s="44"/>
-      <c r="B181" s="31"/>
-      <c r="C181" s="29"/>
+      <c r="A181" s="34"/>
+      <c r="B181" s="35"/>
+      <c r="C181" s="28"/>
       <c r="D181" s="5" t="s">
         <v>61</v>
       </c>
@@ -6804,19 +6810,19 @@
       <c r="F181" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="G181" s="28"/>
+      <c r="G181" s="32"/>
       <c r="H181" s="15" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="182" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A182" s="43">
+      <c r="A182" s="33">
         <v>67</v>
       </c>
-      <c r="B182" s="31" t="s">
+      <c r="B182" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C182" s="29" t="s">
+      <c r="C182" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D182" s="5" t="s">
@@ -6828,15 +6834,15 @@
       <c r="F182" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="G182" s="28"/>
+      <c r="G182" s="32"/>
       <c r="H182" s="15" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="183" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A183" s="44"/>
-      <c r="B183" s="31"/>
-      <c r="C183" s="29"/>
+      <c r="A183" s="34"/>
+      <c r="B183" s="35"/>
+      <c r="C183" s="28"/>
       <c r="D183" s="5" t="s">
         <v>69</v>
       </c>
@@ -6846,19 +6852,19 @@
       <c r="F183" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="G183" s="28"/>
+      <c r="G183" s="32"/>
       <c r="H183" s="15" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="184" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A184" s="43">
+      <c r="A184" s="33">
         <v>68</v>
       </c>
-      <c r="B184" s="31" t="s">
+      <c r="B184" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C184" s="29" t="s">
+      <c r="C184" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D184" s="5" t="s">
@@ -6870,15 +6876,15 @@
       <c r="F184" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="G184" s="28"/>
+      <c r="G184" s="32"/>
       <c r="H184" s="15" t="s">
         <v>533</v>
       </c>
     </row>
     <row r="185" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A185" s="44"/>
-      <c r="B185" s="31"/>
-      <c r="C185" s="29"/>
+      <c r="A185" s="34"/>
+      <c r="B185" s="35"/>
+      <c r="C185" s="28"/>
       <c r="D185" s="5" t="s">
         <v>219</v>
       </c>
@@ -6888,19 +6894,19 @@
       <c r="F185" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="G185" s="28"/>
+      <c r="G185" s="32"/>
       <c r="H185" s="15" t="s">
         <v>534</v>
       </c>
     </row>
     <row r="186" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A186" s="43">
+      <c r="A186" s="52">
         <v>69</v>
       </c>
-      <c r="B186" s="31" t="s">
+      <c r="B186" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C186" s="29" t="s">
+      <c r="C186" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D186" s="5" t="s">
@@ -6912,15 +6918,15 @@
       <c r="F186" s="5" t="s">
         <v>632</v>
       </c>
-      <c r="G186" s="28"/>
+      <c r="G186" s="32"/>
       <c r="H186" s="15" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="187" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A187" s="44"/>
-      <c r="B187" s="31"/>
-      <c r="C187" s="29"/>
+      <c r="A187" s="53"/>
+      <c r="B187" s="35"/>
+      <c r="C187" s="28"/>
       <c r="D187" s="5" t="s">
         <v>71</v>
       </c>
@@ -6930,19 +6936,19 @@
       <c r="F187" s="5" t="s">
         <v>632</v>
       </c>
-      <c r="G187" s="28"/>
+      <c r="G187" s="32"/>
       <c r="H187" s="15" t="s">
         <v>431</v>
       </c>
     </row>
     <row r="188" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A188" s="43">
+      <c r="A188" s="33">
         <v>70</v>
       </c>
-      <c r="B188" s="31" t="s">
+      <c r="B188" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C188" s="45" t="s">
+      <c r="C188" s="37" t="s">
         <v>14</v>
       </c>
       <c r="D188" s="5" t="s">
@@ -6954,15 +6960,15 @@
       <c r="F188" s="5" t="s">
         <v>436</v>
       </c>
-      <c r="G188" s="28"/>
+      <c r="G188" s="32"/>
       <c r="H188" s="15" t="s">
         <v>440</v>
       </c>
     </row>
     <row r="189" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A189" s="44"/>
-      <c r="B189" s="31"/>
-      <c r="C189" s="45"/>
+      <c r="A189" s="34"/>
+      <c r="B189" s="35"/>
+      <c r="C189" s="37"/>
       <c r="D189" s="5" t="s">
         <v>438</v>
       </c>
@@ -6972,19 +6978,19 @@
       <c r="F189" s="5" t="s">
         <v>437</v>
       </c>
-      <c r="G189" s="28"/>
+      <c r="G189" s="32"/>
       <c r="H189" s="15" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="190" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A190" s="43">
+      <c r="A190" s="33">
         <v>71</v>
       </c>
-      <c r="B190" s="31" t="s">
+      <c r="B190" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C190" s="45" t="s">
+      <c r="C190" s="37" t="s">
         <v>14</v>
       </c>
       <c r="D190" s="5" t="s">
@@ -6996,7 +7002,7 @@
       <c r="F190" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="G190" s="28" t="s">
+      <c r="G190" s="32" t="s">
         <v>538</v>
       </c>
       <c r="H190" s="15" t="s">
@@ -7004,9 +7010,9 @@
       </c>
     </row>
     <row r="191" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A191" s="44"/>
-      <c r="B191" s="31"/>
-      <c r="C191" s="45"/>
+      <c r="A191" s="34"/>
+      <c r="B191" s="35"/>
+      <c r="C191" s="37"/>
       <c r="D191" s="5" t="s">
         <v>85</v>
       </c>
@@ -7016,19 +7022,19 @@
       <c r="F191" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="G191" s="28"/>
+      <c r="G191" s="32"/>
       <c r="H191" s="15" t="s">
         <v>408</v>
       </c>
     </row>
     <row r="192" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A192" s="43">
+      <c r="A192" s="33">
         <v>72</v>
       </c>
-      <c r="B192" s="31" t="s">
+      <c r="B192" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C192" s="45" t="s">
+      <c r="C192" s="37" t="s">
         <v>14</v>
       </c>
       <c r="D192" s="5" t="s">
@@ -7040,15 +7046,15 @@
       <c r="F192" s="5" t="s">
         <v>661</v>
       </c>
-      <c r="G192" s="28"/>
+      <c r="G192" s="32"/>
       <c r="H192" s="15" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="193" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A193" s="44"/>
-      <c r="B193" s="31"/>
-      <c r="C193" s="45"/>
+      <c r="A193" s="34"/>
+      <c r="B193" s="35"/>
+      <c r="C193" s="37"/>
       <c r="D193" s="5" t="s">
         <v>185</v>
       </c>
@@ -7058,19 +7064,19 @@
       <c r="F193" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="G193" s="28"/>
+      <c r="G193" s="32"/>
       <c r="H193" s="15" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="194" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A194" s="43">
+      <c r="A194" s="33">
         <v>73</v>
       </c>
-      <c r="B194" s="31" t="s">
+      <c r="B194" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C194" s="29" t="s">
+      <c r="C194" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D194" s="5" t="s">
@@ -7082,7 +7088,7 @@
       <c r="F194" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="G194" s="28" t="s">
+      <c r="G194" s="32" t="s">
         <v>209</v>
       </c>
       <c r="H194" s="15" t="s">
@@ -7090,9 +7096,9 @@
       </c>
     </row>
     <row r="195" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A195" s="44"/>
-      <c r="B195" s="31"/>
-      <c r="C195" s="29"/>
+      <c r="A195" s="34"/>
+      <c r="B195" s="35"/>
+      <c r="C195" s="28"/>
       <c r="D195" s="5" t="s">
         <v>129</v>
       </c>
@@ -7102,19 +7108,19 @@
       <c r="F195" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="G195" s="28"/>
+      <c r="G195" s="32"/>
       <c r="H195" s="15" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="196" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A196" s="43">
+      <c r="A196" s="33">
         <v>74</v>
       </c>
-      <c r="B196" s="31" t="s">
+      <c r="B196" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C196" s="29" t="s">
+      <c r="C196" s="28" t="s">
         <v>14</v>
       </c>
       <c r="D196" s="5" t="s">
@@ -7126,7 +7132,7 @@
       <c r="F196" s="5" t="s">
         <v>662</v>
       </c>
-      <c r="G196" s="28" t="s">
+      <c r="G196" s="32" t="s">
         <v>138</v>
       </c>
       <c r="H196" s="15" t="s">
@@ -7134,9 +7140,9 @@
       </c>
     </row>
     <row r="197" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A197" s="44"/>
-      <c r="B197" s="31"/>
-      <c r="C197" s="29"/>
+      <c r="A197" s="34"/>
+      <c r="B197" s="35"/>
+      <c r="C197" s="28"/>
       <c r="D197" s="5" t="s">
         <v>107</v>
       </c>
@@ -7146,19 +7152,19 @@
       <c r="F197" s="5" t="s">
         <v>663</v>
       </c>
-      <c r="G197" s="28"/>
+      <c r="G197" s="32"/>
       <c r="H197" s="15" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="198" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A198" s="34">
+      <c r="A198" s="38">
         <v>75</v>
       </c>
-      <c r="B198" s="33" t="s">
+      <c r="B198" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C198" s="29" t="s">
+      <c r="C198" s="28" t="s">
         <v>86</v>
       </c>
       <c r="D198" s="5" t="s">
@@ -7170,7 +7176,7 @@
       <c r="F198" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="G198" s="28" t="s">
+      <c r="G198" s="32" t="s">
         <v>570</v>
       </c>
       <c r="H198" s="15" t="s">
@@ -7178,9 +7184,9 @@
       </c>
     </row>
     <row r="199" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A199" s="35"/>
-      <c r="B199" s="33"/>
-      <c r="C199" s="29"/>
+      <c r="A199" s="39"/>
+      <c r="B199" s="36"/>
+      <c r="C199" s="28"/>
       <c r="D199" s="5" t="s">
         <v>92</v>
       </c>
@@ -7190,19 +7196,19 @@
       <c r="F199" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="G199" s="28"/>
+      <c r="G199" s="32"/>
       <c r="H199" s="15" t="s">
         <v>433</v>
       </c>
     </row>
     <row r="200" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A200" s="43">
+      <c r="A200" s="33">
         <v>76</v>
       </c>
-      <c r="B200" s="33" t="s">
+      <c r="B200" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C200" s="29" t="s">
+      <c r="C200" s="28" t="s">
         <v>86</v>
       </c>
       <c r="D200" s="5" t="s">
@@ -7214,7 +7220,7 @@
       <c r="F200" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="G200" s="28" t="s">
+      <c r="G200" s="32" t="s">
         <v>216</v>
       </c>
       <c r="H200" s="15" t="s">
@@ -7222,9 +7228,9 @@
       </c>
     </row>
     <row r="201" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A201" s="44"/>
-      <c r="B201" s="33"/>
-      <c r="C201" s="29"/>
+      <c r="A201" s="34"/>
+      <c r="B201" s="36"/>
+      <c r="C201" s="28"/>
       <c r="D201" s="5" t="s">
         <v>104</v>
       </c>
@@ -7234,19 +7240,19 @@
       <c r="F201" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="G201" s="28"/>
+      <c r="G201" s="32"/>
       <c r="H201" s="15" t="s">
         <v>435</v>
       </c>
     </row>
     <row r="202" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A202" s="34">
+      <c r="A202" s="38">
         <v>77</v>
       </c>
-      <c r="B202" s="33" t="s">
+      <c r="B202" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C202" s="29" t="s">
+      <c r="C202" s="28" t="s">
         <v>86</v>
       </c>
       <c r="D202" s="5" t="s">
@@ -7258,7 +7264,7 @@
       <c r="F202" s="5" t="s">
         <v>545</v>
       </c>
-      <c r="G202" s="28" t="s">
+      <c r="G202" s="32" t="s">
         <v>568</v>
       </c>
       <c r="H202" s="15" t="s">
@@ -7266,9 +7272,9 @@
       </c>
     </row>
     <row r="203" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A203" s="35"/>
-      <c r="B203" s="33"/>
-      <c r="C203" s="29"/>
+      <c r="A203" s="39"/>
+      <c r="B203" s="36"/>
+      <c r="C203" s="28"/>
       <c r="D203" s="5" t="s">
         <v>109</v>
       </c>
@@ -7278,19 +7284,19 @@
       <c r="F203" s="5" t="s">
         <v>546</v>
       </c>
-      <c r="G203" s="28"/>
+      <c r="G203" s="32"/>
       <c r="H203" s="15" t="s">
         <v>412</v>
       </c>
     </row>
     <row r="204" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A204" s="43">
+      <c r="A204" s="33">
         <v>78</v>
       </c>
-      <c r="B204" s="33" t="s">
+      <c r="B204" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C204" s="29" t="s">
+      <c r="C204" s="28" t="s">
         <v>86</v>
       </c>
       <c r="D204" s="5" t="s">
@@ -7302,15 +7308,15 @@
       <c r="F204" s="5" t="s">
         <v>574</v>
       </c>
-      <c r="G204" s="28"/>
+      <c r="G204" s="32"/>
       <c r="H204" s="15" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="205" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A205" s="44"/>
-      <c r="B205" s="33"/>
-      <c r="C205" s="29"/>
+      <c r="A205" s="34"/>
+      <c r="B205" s="36"/>
+      <c r="C205" s="28"/>
       <c r="D205" s="5" t="s">
         <v>88</v>
       </c>
@@ -7320,19 +7326,19 @@
       <c r="F205" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="G205" s="28"/>
+      <c r="G205" s="32"/>
       <c r="H205" s="15" t="s">
         <v>423</v>
       </c>
     </row>
     <row r="206" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A206" s="43">
+      <c r="A206" s="33">
         <v>79</v>
       </c>
-      <c r="B206" s="33" t="s">
+      <c r="B206" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C206" s="29" t="s">
+      <c r="C206" s="28" t="s">
         <v>86</v>
       </c>
       <c r="D206" s="5" t="s">
@@ -7344,15 +7350,15 @@
       <c r="F206" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="G206" s="28"/>
+      <c r="G206" s="32"/>
       <c r="H206" s="15" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="207" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A207" s="44"/>
-      <c r="B207" s="33"/>
-      <c r="C207" s="29"/>
+      <c r="A207" s="34"/>
+      <c r="B207" s="36"/>
+      <c r="C207" s="28"/>
       <c r="D207" s="5" t="s">
         <v>90</v>
       </c>
@@ -7362,19 +7368,19 @@
       <c r="F207" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="G207" s="28"/>
+      <c r="G207" s="32"/>
       <c r="H207" s="15" t="s">
         <v>413</v>
       </c>
     </row>
     <row r="208" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A208" s="43">
+      <c r="A208" s="33">
         <v>80</v>
       </c>
-      <c r="B208" s="33" t="s">
+      <c r="B208" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C208" s="29" t="s">
+      <c r="C208" s="28" t="s">
         <v>86</v>
       </c>
       <c r="D208" s="5" t="s">
@@ -7386,7 +7392,7 @@
       <c r="F208" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="G208" s="28" t="s">
+      <c r="G208" s="32" t="s">
         <v>234</v>
       </c>
       <c r="H208" s="15" t="s">
@@ -7394,9 +7400,9 @@
       </c>
     </row>
     <row r="209" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A209" s="44"/>
-      <c r="B209" s="33"/>
-      <c r="C209" s="29"/>
+      <c r="A209" s="34"/>
+      <c r="B209" s="36"/>
+      <c r="C209" s="28"/>
       <c r="D209" s="5" t="s">
         <v>102</v>
       </c>
@@ -7406,19 +7412,19 @@
       <c r="F209" s="5" t="s">
         <v>565</v>
       </c>
-      <c r="G209" s="28"/>
+      <c r="G209" s="32"/>
       <c r="H209" s="15" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="210" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A210" s="34">
+      <c r="A210" s="38">
         <v>81</v>
       </c>
-      <c r="B210" s="33" t="s">
+      <c r="B210" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C210" s="29" t="s">
+      <c r="C210" s="28" t="s">
         <v>86</v>
       </c>
       <c r="D210" s="5" t="s">
@@ -7430,7 +7436,7 @@
       <c r="F210" s="5" t="s">
         <v>593</v>
       </c>
-      <c r="G210" s="28" t="s">
+      <c r="G210" s="32" t="s">
         <v>566</v>
       </c>
       <c r="H210" s="15" t="s">
@@ -7438,9 +7444,9 @@
       </c>
     </row>
     <row r="211" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A211" s="35"/>
-      <c r="B211" s="33"/>
-      <c r="C211" s="29"/>
+      <c r="A211" s="39"/>
+      <c r="B211" s="36"/>
+      <c r="C211" s="28"/>
       <c r="D211" s="5" t="s">
         <v>96</v>
       </c>
@@ -7450,19 +7456,19 @@
       <c r="F211" s="5" t="s">
         <v>594</v>
       </c>
-      <c r="G211" s="28"/>
+      <c r="G211" s="32"/>
       <c r="H211" s="15" t="s">
         <v>418</v>
       </c>
     </row>
     <row r="212" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A212" s="43">
+      <c r="A212" s="33">
         <v>82</v>
       </c>
-      <c r="B212" s="48" t="s">
+      <c r="B212" s="44" t="s">
         <v>29</v>
       </c>
-      <c r="C212" s="29" t="s">
+      <c r="C212" s="28" t="s">
         <v>86</v>
       </c>
       <c r="D212" s="5" t="s">
@@ -7474,15 +7480,15 @@
       <c r="F212" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="G212" s="28"/>
+      <c r="G212" s="32"/>
       <c r="H212" s="15" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="213" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A213" s="44"/>
-      <c r="B213" s="49"/>
-      <c r="C213" s="29"/>
+      <c r="A213" s="34"/>
+      <c r="B213" s="45"/>
+      <c r="C213" s="28"/>
       <c r="D213" s="5" t="s">
         <v>174</v>
       </c>
@@ -7492,19 +7498,19 @@
       <c r="F213" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="G213" s="28"/>
+      <c r="G213" s="32"/>
       <c r="H213" s="15" t="s">
         <v>415</v>
       </c>
     </row>
     <row r="214" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A214" s="43">
+      <c r="A214" s="33">
         <v>83</v>
       </c>
-      <c r="B214" s="31" t="s">
+      <c r="B214" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C214" s="29" t="s">
+      <c r="C214" s="28" t="s">
         <v>86</v>
       </c>
       <c r="D214" s="5" t="s">
@@ -7516,7 +7522,7 @@
       <c r="F214" s="5" t="s">
         <v>537</v>
       </c>
-      <c r="G214" s="28" t="s">
+      <c r="G214" s="32" t="s">
         <v>569</v>
       </c>
       <c r="H214" s="15" t="s">
@@ -7524,9 +7530,9 @@
       </c>
     </row>
     <row r="215" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A215" s="44"/>
-      <c r="B215" s="31"/>
-      <c r="C215" s="29"/>
+      <c r="A215" s="34"/>
+      <c r="B215" s="35"/>
+      <c r="C215" s="28"/>
       <c r="D215" s="5" t="s">
         <v>135</v>
       </c>
@@ -7536,19 +7542,19 @@
       <c r="F215" s="5" t="s">
         <v>544</v>
       </c>
-      <c r="G215" s="28"/>
+      <c r="G215" s="32"/>
       <c r="H215" s="15" t="s">
         <v>416</v>
       </c>
     </row>
     <row r="216" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A216" s="43">
+      <c r="A216" s="33">
         <v>84</v>
       </c>
-      <c r="B216" s="31" t="s">
+      <c r="B216" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C216" s="29" t="s">
+      <c r="C216" s="28" t="s">
         <v>86</v>
       </c>
       <c r="D216" s="5" t="s">
@@ -7560,7 +7566,7 @@
       <c r="F216" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="G216" s="28" t="s">
+      <c r="G216" s="32" t="s">
         <v>285</v>
       </c>
       <c r="H216" s="15" t="s">
@@ -7568,9 +7574,9 @@
       </c>
     </row>
     <row r="217" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A217" s="44"/>
-      <c r="B217" s="31"/>
-      <c r="C217" s="29"/>
+      <c r="A217" s="34"/>
+      <c r="B217" s="35"/>
+      <c r="C217" s="28"/>
       <c r="D217" s="5" t="s">
         <v>94</v>
       </c>
@@ -7580,19 +7586,19 @@
       <c r="F217" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="G217" s="28"/>
+      <c r="G217" s="32"/>
       <c r="H217" s="15" t="s">
         <v>417</v>
       </c>
     </row>
     <row r="218" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A218" s="43">
+      <c r="A218" s="33">
         <v>85</v>
       </c>
-      <c r="B218" s="31" t="s">
+      <c r="B218" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C218" s="29" t="s">
+      <c r="C218" s="28" t="s">
         <v>86</v>
       </c>
       <c r="D218" s="5" t="s">
@@ -7604,15 +7610,15 @@
       <c r="F218" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="G218" s="28"/>
+      <c r="G218" s="32"/>
       <c r="H218" s="15" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="219" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A219" s="44"/>
-      <c r="B219" s="31"/>
-      <c r="C219" s="29"/>
+      <c r="A219" s="34"/>
+      <c r="B219" s="35"/>
+      <c r="C219" s="28"/>
       <c r="D219" s="5" t="s">
         <v>98</v>
       </c>
@@ -7622,19 +7628,19 @@
       <c r="F219" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="G219" s="28"/>
+      <c r="G219" s="32"/>
       <c r="H219" s="15" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="220" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A220" s="43">
+      <c r="A220" s="33">
         <v>86</v>
       </c>
-      <c r="B220" s="31" t="s">
+      <c r="B220" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C220" s="29" t="s">
+      <c r="C220" s="28" t="s">
         <v>86</v>
       </c>
       <c r="D220" s="5" t="s">
@@ -7646,15 +7652,15 @@
       <c r="F220" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="G220" s="28"/>
+      <c r="G220" s="32"/>
       <c r="H220" s="15" t="s">
         <v>442</v>
       </c>
     </row>
     <row r="221" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A221" s="44"/>
-      <c r="B221" s="31"/>
-      <c r="C221" s="29"/>
+      <c r="A221" s="34"/>
+      <c r="B221" s="35"/>
+      <c r="C221" s="28"/>
       <c r="D221" s="5" t="s">
         <v>148</v>
       </c>
@@ -7664,19 +7670,19 @@
       <c r="F221" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="G221" s="28"/>
+      <c r="G221" s="32"/>
       <c r="H221" s="15" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="222" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A222" s="43">
+      <c r="A222" s="33">
         <v>87</v>
       </c>
-      <c r="B222" s="31" t="s">
+      <c r="B222" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C222" s="32" t="s">
+      <c r="C222" s="43" t="s">
         <v>86</v>
       </c>
       <c r="D222" s="5" t="s">
@@ -7688,7 +7694,7 @@
       <c r="F222" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="G222" s="28" t="s">
+      <c r="G222" s="32" t="s">
         <v>567</v>
       </c>
       <c r="H222" s="15" t="s">
@@ -7696,9 +7702,9 @@
       </c>
     </row>
     <row r="223" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A223" s="44"/>
-      <c r="B223" s="31"/>
-      <c r="C223" s="32"/>
+      <c r="A223" s="34"/>
+      <c r="B223" s="35"/>
+      <c r="C223" s="43"/>
       <c r="D223" s="5" t="s">
         <v>100</v>
       </c>
@@ -7708,19 +7714,19 @@
       <c r="F223" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="G223" s="28"/>
+      <c r="G223" s="32"/>
       <c r="H223" s="15" t="s">
         <v>420</v>
       </c>
     </row>
     <row r="224" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A224" s="43">
+      <c r="A224" s="33">
         <v>88</v>
       </c>
-      <c r="B224" s="31" t="s">
+      <c r="B224" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C224" s="45" t="s">
+      <c r="C224" s="37" t="s">
         <v>86</v>
       </c>
       <c r="D224" s="5" t="s">
@@ -7732,15 +7738,15 @@
       <c r="F224" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="G224" s="28"/>
+      <c r="G224" s="32"/>
       <c r="H224" s="15" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="225" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A225" s="44"/>
-      <c r="B225" s="31"/>
-      <c r="C225" s="45"/>
+      <c r="A225" s="34"/>
+      <c r="B225" s="35"/>
+      <c r="C225" s="37"/>
       <c r="D225" s="5" t="s">
         <v>140</v>
       </c>
@@ -7750,7 +7756,7 @@
       <c r="F225" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="G225" s="28"/>
+      <c r="G225" s="32"/>
       <c r="H225" s="15" t="s">
         <v>421</v>
       </c>
@@ -7801,16 +7807,16 @@
       </c>
     </row>
     <row r="245" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A245" s="29" t="s">
+      <c r="A245" s="28" t="s">
         <v>579</v>
       </c>
-      <c r="B245" s="29"/>
-      <c r="C245" s="29"/>
-      <c r="D245" s="29"/>
-      <c r="E245" s="29"/>
-      <c r="F245" s="29"/>
-      <c r="G245" s="29"/>
-      <c r="H245" s="29"/>
+      <c r="B245" s="28"/>
+      <c r="C245" s="28"/>
+      <c r="D245" s="28"/>
+      <c r="E245" s="28"/>
+      <c r="F245" s="28"/>
+      <c r="G245" s="28"/>
+      <c r="H245" s="28"/>
     </row>
     <row r="246" spans="1:8" ht="25.7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A246" s="1" t="s">
@@ -7819,12 +7825,12 @@
       <c r="B246" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="C246" s="36" t="s">
+      <c r="C246" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="D246" s="37"/>
-      <c r="E246" s="37"/>
-      <c r="F246" s="38"/>
+      <c r="D246" s="30"/>
+      <c r="E246" s="30"/>
+      <c r="F246" s="31"/>
       <c r="G246" s="1" t="s">
         <v>3</v>
       </c>
@@ -7873,31 +7879,393 @@
       </c>
     </row>
     <row r="253" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A253" s="29" t="s">
+      <c r="A253" s="28" t="s">
         <v>581</v>
       </c>
-      <c r="B253" s="29"/>
-      <c r="C253" s="29"/>
-      <c r="D253" s="29"/>
-      <c r="E253" s="29"/>
-      <c r="F253" s="29"/>
-      <c r="G253" s="29"/>
-      <c r="H253" s="29"/>
+      <c r="B253" s="28"/>
+      <c r="C253" s="28"/>
+      <c r="D253" s="28"/>
+      <c r="E253" s="28"/>
+      <c r="F253" s="28"/>
+      <c r="G253" s="28"/>
+      <c r="H253" s="28"/>
     </row>
     <row r="254" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A254" s="29" t="s">
+      <c r="A254" s="28" t="s">
         <v>582</v>
       </c>
-      <c r="B254" s="29"/>
-      <c r="C254" s="29"/>
-      <c r="D254" s="29"/>
-      <c r="E254" s="29"/>
-      <c r="F254" s="29"/>
-      <c r="G254" s="29"/>
-      <c r="H254" s="29"/>
+      <c r="B254" s="28"/>
+      <c r="C254" s="28"/>
+      <c r="D254" s="28"/>
+      <c r="E254" s="28"/>
+      <c r="F254" s="28"/>
+      <c r="G254" s="28"/>
+      <c r="H254" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="386">
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="G60:G61"/>
+    <mergeCell ref="C208:C209"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="B92:B93"/>
+    <mergeCell ref="G88:G89"/>
+    <mergeCell ref="C90:C91"/>
+    <mergeCell ref="G130:G131"/>
+    <mergeCell ref="C130:C131"/>
+    <mergeCell ref="G144:G145"/>
+    <mergeCell ref="B162:B163"/>
+    <mergeCell ref="C162:C163"/>
+    <mergeCell ref="B138:B139"/>
+    <mergeCell ref="G154:G155"/>
+    <mergeCell ref="G158:G159"/>
+    <mergeCell ref="C156:C157"/>
+    <mergeCell ref="C142:C143"/>
+    <mergeCell ref="G120:G121"/>
+    <mergeCell ref="G114:G115"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="C62:C63"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="A48:H48"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="G50:G51"/>
+    <mergeCell ref="G52:G53"/>
+    <mergeCell ref="G54:G55"/>
+    <mergeCell ref="G56:G57"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="A124:A125"/>
+    <mergeCell ref="B124:B125"/>
+    <mergeCell ref="A118:A119"/>
+    <mergeCell ref="A134:A135"/>
+    <mergeCell ref="B134:B135"/>
+    <mergeCell ref="C134:C135"/>
+    <mergeCell ref="G214:G215"/>
+    <mergeCell ref="C118:C119"/>
+    <mergeCell ref="B118:B119"/>
+    <mergeCell ref="C124:C125"/>
+    <mergeCell ref="A152:A153"/>
+    <mergeCell ref="B152:B153"/>
+    <mergeCell ref="C152:C153"/>
+    <mergeCell ref="A146:A147"/>
+    <mergeCell ref="B146:B147"/>
+    <mergeCell ref="C146:C147"/>
+    <mergeCell ref="B150:B151"/>
+    <mergeCell ref="C150:C151"/>
+    <mergeCell ref="G150:G151"/>
+    <mergeCell ref="G160:G161"/>
+    <mergeCell ref="A166:A167"/>
+    <mergeCell ref="A162:A163"/>
+    <mergeCell ref="A188:A189"/>
+    <mergeCell ref="A190:A191"/>
+    <mergeCell ref="B190:B191"/>
+    <mergeCell ref="G182:G183"/>
+    <mergeCell ref="C190:C191"/>
+    <mergeCell ref="G188:G189"/>
+    <mergeCell ref="B188:B189"/>
+    <mergeCell ref="C172:C173"/>
+    <mergeCell ref="C158:C159"/>
+    <mergeCell ref="G156:G157"/>
+    <mergeCell ref="A156:A157"/>
+    <mergeCell ref="B156:B157"/>
+    <mergeCell ref="A174:A175"/>
+    <mergeCell ref="B174:B175"/>
+    <mergeCell ref="C174:C175"/>
+    <mergeCell ref="G174:G175"/>
+    <mergeCell ref="B158:B159"/>
+    <mergeCell ref="C186:C187"/>
+    <mergeCell ref="A158:A159"/>
+    <mergeCell ref="G186:G187"/>
+    <mergeCell ref="A182:A183"/>
+    <mergeCell ref="B182:B183"/>
+    <mergeCell ref="C168:C169"/>
+    <mergeCell ref="G166:G167"/>
+    <mergeCell ref="A184:A185"/>
+    <mergeCell ref="G162:G163"/>
+    <mergeCell ref="C180:C181"/>
+    <mergeCell ref="G178:G179"/>
+    <mergeCell ref="A176:A177"/>
+    <mergeCell ref="B132:B133"/>
+    <mergeCell ref="C132:C133"/>
+    <mergeCell ref="B154:B155"/>
+    <mergeCell ref="C154:C155"/>
+    <mergeCell ref="G152:G153"/>
+    <mergeCell ref="G172:G173"/>
+    <mergeCell ref="B176:B177"/>
+    <mergeCell ref="C176:C177"/>
+    <mergeCell ref="B172:B173"/>
+    <mergeCell ref="A168:A169"/>
+    <mergeCell ref="G170:G171"/>
+    <mergeCell ref="G176:G177"/>
+    <mergeCell ref="G142:G143"/>
+    <mergeCell ref="A170:A171"/>
+    <mergeCell ref="B170:B171"/>
+    <mergeCell ref="C170:C171"/>
+    <mergeCell ref="G168:G169"/>
+    <mergeCell ref="A172:A173"/>
+    <mergeCell ref="A180:A181"/>
+    <mergeCell ref="B180:B181"/>
+    <mergeCell ref="A136:A137"/>
+    <mergeCell ref="A126:A127"/>
+    <mergeCell ref="B126:B127"/>
+    <mergeCell ref="C126:C127"/>
+    <mergeCell ref="B136:B137"/>
+    <mergeCell ref="C136:C137"/>
+    <mergeCell ref="G148:G149"/>
+    <mergeCell ref="A150:A151"/>
+    <mergeCell ref="A160:A161"/>
+    <mergeCell ref="B160:B161"/>
+    <mergeCell ref="C160:C161"/>
+    <mergeCell ref="G128:G129"/>
+    <mergeCell ref="A154:A155"/>
+    <mergeCell ref="A138:A139"/>
+    <mergeCell ref="G140:G141"/>
+    <mergeCell ref="G134:G135"/>
+    <mergeCell ref="A128:A129"/>
+    <mergeCell ref="B128:B129"/>
+    <mergeCell ref="B148:B149"/>
+    <mergeCell ref="C148:C149"/>
+    <mergeCell ref="G146:G147"/>
+    <mergeCell ref="A144:A145"/>
+    <mergeCell ref="B144:B145"/>
+    <mergeCell ref="C144:C145"/>
+    <mergeCell ref="A140:A141"/>
+    <mergeCell ref="B140:B141"/>
+    <mergeCell ref="C140:C141"/>
+    <mergeCell ref="G136:G137"/>
+    <mergeCell ref="A132:A133"/>
+    <mergeCell ref="A130:A131"/>
+    <mergeCell ref="B130:B131"/>
+    <mergeCell ref="C128:C129"/>
+    <mergeCell ref="A142:A143"/>
+    <mergeCell ref="B142:B143"/>
+    <mergeCell ref="A148:A149"/>
+    <mergeCell ref="G84:G85"/>
+    <mergeCell ref="G92:G93"/>
+    <mergeCell ref="G82:G83"/>
+    <mergeCell ref="G90:G91"/>
+    <mergeCell ref="G100:G101"/>
+    <mergeCell ref="C138:C139"/>
+    <mergeCell ref="G138:G139"/>
+    <mergeCell ref="G116:G117"/>
+    <mergeCell ref="G108:G109"/>
+    <mergeCell ref="G110:G111"/>
+    <mergeCell ref="C110:C111"/>
+    <mergeCell ref="C102:C103"/>
+    <mergeCell ref="C114:C115"/>
+    <mergeCell ref="C112:C113"/>
+    <mergeCell ref="C116:C117"/>
+    <mergeCell ref="G122:G123"/>
+    <mergeCell ref="C122:C123"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="G132:G133"/>
+    <mergeCell ref="G106:G107"/>
+    <mergeCell ref="G96:G97"/>
+    <mergeCell ref="G102:G103"/>
+    <mergeCell ref="G126:G127"/>
+    <mergeCell ref="A114:A115"/>
+    <mergeCell ref="B114:B115"/>
+    <mergeCell ref="A112:A113"/>
+    <mergeCell ref="B112:B113"/>
+    <mergeCell ref="A116:A117"/>
+    <mergeCell ref="B116:B117"/>
+    <mergeCell ref="A122:A123"/>
+    <mergeCell ref="B122:B123"/>
+    <mergeCell ref="G98:G99"/>
+    <mergeCell ref="A108:A109"/>
+    <mergeCell ref="B108:B109"/>
+    <mergeCell ref="C108:C109"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="B110:B111"/>
+    <mergeCell ref="A98:A99"/>
+    <mergeCell ref="A100:A101"/>
+    <mergeCell ref="B100:B101"/>
+    <mergeCell ref="C100:C101"/>
+    <mergeCell ref="A110:A111"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="A94:A95"/>
+    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="B104:B105"/>
+    <mergeCell ref="C104:C105"/>
+    <mergeCell ref="A96:A97"/>
+    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="C96:C97"/>
+    <mergeCell ref="B98:B99"/>
+    <mergeCell ref="C98:C99"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="B102:B103"/>
+    <mergeCell ref="C218:C219"/>
+    <mergeCell ref="G68:G69"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="G72:G73"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="G74:G75"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="G76:G77"/>
+    <mergeCell ref="C76:C77"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="C86:C87"/>
+    <mergeCell ref="A86:A87"/>
+    <mergeCell ref="B86:B87"/>
+    <mergeCell ref="G80:G81"/>
+    <mergeCell ref="C88:C89"/>
+    <mergeCell ref="C94:C95"/>
+    <mergeCell ref="G94:G95"/>
+    <mergeCell ref="G192:G193"/>
+    <mergeCell ref="C224:C225"/>
+    <mergeCell ref="G222:G223"/>
+    <mergeCell ref="G198:G199"/>
+    <mergeCell ref="A224:A225"/>
+    <mergeCell ref="G220:G221"/>
+    <mergeCell ref="A210:A211"/>
+    <mergeCell ref="B210:B211"/>
+    <mergeCell ref="C210:C211"/>
+    <mergeCell ref="G224:G225"/>
+    <mergeCell ref="B224:B225"/>
+    <mergeCell ref="A222:A223"/>
+    <mergeCell ref="B222:B223"/>
+    <mergeCell ref="C222:C223"/>
+    <mergeCell ref="G218:G219"/>
+    <mergeCell ref="A212:A213"/>
+    <mergeCell ref="B212:B213"/>
+    <mergeCell ref="C212:C213"/>
+    <mergeCell ref="B214:B215"/>
+    <mergeCell ref="C214:C215"/>
+    <mergeCell ref="A208:A209"/>
+    <mergeCell ref="A220:A221"/>
+    <mergeCell ref="B220:B221"/>
+    <mergeCell ref="C220:C221"/>
+    <mergeCell ref="C178:C179"/>
+    <mergeCell ref="A214:A215"/>
+    <mergeCell ref="G212:G213"/>
+    <mergeCell ref="G196:G197"/>
+    <mergeCell ref="C182:C183"/>
+    <mergeCell ref="G180:G181"/>
+    <mergeCell ref="A164:A165"/>
+    <mergeCell ref="B164:B165"/>
+    <mergeCell ref="C164:C165"/>
+    <mergeCell ref="G190:G191"/>
+    <mergeCell ref="A178:A179"/>
+    <mergeCell ref="B178:B179"/>
+    <mergeCell ref="G164:G165"/>
+    <mergeCell ref="G200:G201"/>
+    <mergeCell ref="A198:A199"/>
+    <mergeCell ref="B198:B199"/>
+    <mergeCell ref="C198:C199"/>
+    <mergeCell ref="G194:G195"/>
+    <mergeCell ref="A186:A187"/>
+    <mergeCell ref="B186:B187"/>
+    <mergeCell ref="C188:C189"/>
+    <mergeCell ref="B184:B185"/>
+    <mergeCell ref="C184:C185"/>
+    <mergeCell ref="G184:G185"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="G216:G217"/>
+    <mergeCell ref="B216:B217"/>
+    <mergeCell ref="B208:B209"/>
+    <mergeCell ref="A106:A107"/>
+    <mergeCell ref="A218:A219"/>
+    <mergeCell ref="B218:B219"/>
+    <mergeCell ref="C216:C217"/>
+    <mergeCell ref="G208:G209"/>
+    <mergeCell ref="A206:A207"/>
+    <mergeCell ref="B206:B207"/>
+    <mergeCell ref="C206:C207"/>
+    <mergeCell ref="G206:G207"/>
+    <mergeCell ref="A204:A205"/>
+    <mergeCell ref="B204:B205"/>
+    <mergeCell ref="C204:C205"/>
+    <mergeCell ref="G204:G205"/>
+    <mergeCell ref="G210:G211"/>
+    <mergeCell ref="A216:A217"/>
+    <mergeCell ref="G112:G113"/>
+    <mergeCell ref="G124:G125"/>
+    <mergeCell ref="B166:B167"/>
+    <mergeCell ref="C166:C167"/>
+    <mergeCell ref="B168:B169"/>
+    <mergeCell ref="G78:G79"/>
+    <mergeCell ref="A202:A203"/>
+    <mergeCell ref="B202:B203"/>
+    <mergeCell ref="C202:C203"/>
+    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="G64:G65"/>
+    <mergeCell ref="B106:B107"/>
+    <mergeCell ref="C106:C107"/>
+    <mergeCell ref="G104:G105"/>
+    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="G70:G71"/>
+    <mergeCell ref="A90:A91"/>
+    <mergeCell ref="G66:G67"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="B84:B85"/>
+    <mergeCell ref="C84:C85"/>
+    <mergeCell ref="A88:A89"/>
+    <mergeCell ref="B88:B89"/>
+    <mergeCell ref="C92:C93"/>
+    <mergeCell ref="C200:C201"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A196:A197"/>
+    <mergeCell ref="B196:B197"/>
+    <mergeCell ref="C196:C197"/>
+    <mergeCell ref="A192:A193"/>
+    <mergeCell ref="B192:B193"/>
+    <mergeCell ref="C192:C193"/>
+    <mergeCell ref="G86:G87"/>
+    <mergeCell ref="A120:A121"/>
+    <mergeCell ref="B120:B121"/>
+    <mergeCell ref="C120:C121"/>
+    <mergeCell ref="G118:G119"/>
+    <mergeCell ref="A80:A81"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="C80:C81"/>
+    <mergeCell ref="A78:A79"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
     <mergeCell ref="C36:F36"/>
     <mergeCell ref="A245:H245"/>
     <mergeCell ref="A253:H253"/>
@@ -7922,368 +8290,6 @@
     <mergeCell ref="C194:C195"/>
     <mergeCell ref="A200:A201"/>
     <mergeCell ref="B200:B201"/>
-    <mergeCell ref="C200:C201"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="A31:H31"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A196:A197"/>
-    <mergeCell ref="B196:B197"/>
-    <mergeCell ref="C196:C197"/>
-    <mergeCell ref="A192:A193"/>
-    <mergeCell ref="B192:B193"/>
-    <mergeCell ref="C192:C193"/>
-    <mergeCell ref="G86:G87"/>
-    <mergeCell ref="A120:A121"/>
-    <mergeCell ref="B120:B121"/>
-    <mergeCell ref="C120:C121"/>
-    <mergeCell ref="G118:G119"/>
-    <mergeCell ref="A80:A81"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="C80:C81"/>
-    <mergeCell ref="A78:A79"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="G78:G79"/>
-    <mergeCell ref="A202:A203"/>
-    <mergeCell ref="B202:B203"/>
-    <mergeCell ref="C202:C203"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="A92:A93"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="G64:G65"/>
-    <mergeCell ref="B106:B107"/>
-    <mergeCell ref="C106:C107"/>
-    <mergeCell ref="G104:G105"/>
-    <mergeCell ref="A70:A71"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="C70:C71"/>
-    <mergeCell ref="G70:G71"/>
-    <mergeCell ref="A90:A91"/>
-    <mergeCell ref="G66:G67"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="B84:B85"/>
-    <mergeCell ref="C84:C85"/>
-    <mergeCell ref="A88:A89"/>
-    <mergeCell ref="B88:B89"/>
-    <mergeCell ref="C92:C93"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="G216:G217"/>
-    <mergeCell ref="B216:B217"/>
-    <mergeCell ref="B208:B209"/>
-    <mergeCell ref="A106:A107"/>
-    <mergeCell ref="A218:A219"/>
-    <mergeCell ref="B218:B219"/>
-    <mergeCell ref="C216:C217"/>
-    <mergeCell ref="G208:G209"/>
-    <mergeCell ref="A206:A207"/>
-    <mergeCell ref="B206:B207"/>
-    <mergeCell ref="C206:C207"/>
-    <mergeCell ref="G206:G207"/>
-    <mergeCell ref="A204:A205"/>
-    <mergeCell ref="B204:B205"/>
-    <mergeCell ref="C204:C205"/>
-    <mergeCell ref="G204:G205"/>
-    <mergeCell ref="G210:G211"/>
-    <mergeCell ref="A216:A217"/>
-    <mergeCell ref="G112:G113"/>
-    <mergeCell ref="G124:G125"/>
-    <mergeCell ref="B166:B167"/>
-    <mergeCell ref="C166:C167"/>
-    <mergeCell ref="B168:B169"/>
-    <mergeCell ref="C178:C179"/>
-    <mergeCell ref="A214:A215"/>
-    <mergeCell ref="G212:G213"/>
-    <mergeCell ref="G196:G197"/>
-    <mergeCell ref="C182:C183"/>
-    <mergeCell ref="G180:G181"/>
-    <mergeCell ref="A164:A165"/>
-    <mergeCell ref="B164:B165"/>
-    <mergeCell ref="C164:C165"/>
-    <mergeCell ref="G190:G191"/>
-    <mergeCell ref="A178:A179"/>
-    <mergeCell ref="B178:B179"/>
-    <mergeCell ref="G164:G165"/>
-    <mergeCell ref="G200:G201"/>
-    <mergeCell ref="A198:A199"/>
-    <mergeCell ref="B198:B199"/>
-    <mergeCell ref="C198:C199"/>
-    <mergeCell ref="G194:G195"/>
-    <mergeCell ref="A186:A187"/>
-    <mergeCell ref="B186:B187"/>
-    <mergeCell ref="C188:C189"/>
-    <mergeCell ref="B184:B185"/>
-    <mergeCell ref="C184:C185"/>
-    <mergeCell ref="G184:G185"/>
-    <mergeCell ref="G192:G193"/>
-    <mergeCell ref="C224:C225"/>
-    <mergeCell ref="G222:G223"/>
-    <mergeCell ref="G198:G199"/>
-    <mergeCell ref="A224:A225"/>
-    <mergeCell ref="G220:G221"/>
-    <mergeCell ref="A210:A211"/>
-    <mergeCell ref="B210:B211"/>
-    <mergeCell ref="C210:C211"/>
-    <mergeCell ref="G224:G225"/>
-    <mergeCell ref="B224:B225"/>
-    <mergeCell ref="A222:A223"/>
-    <mergeCell ref="B222:B223"/>
-    <mergeCell ref="C222:C223"/>
-    <mergeCell ref="G218:G219"/>
-    <mergeCell ref="A212:A213"/>
-    <mergeCell ref="B212:B213"/>
-    <mergeCell ref="C212:C213"/>
-    <mergeCell ref="B214:B215"/>
-    <mergeCell ref="C214:C215"/>
-    <mergeCell ref="A208:A209"/>
-    <mergeCell ref="A220:A221"/>
-    <mergeCell ref="B220:B221"/>
-    <mergeCell ref="C220:C221"/>
-    <mergeCell ref="C218:C219"/>
-    <mergeCell ref="G68:G69"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="G72:G73"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="G74:G75"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="G76:G77"/>
-    <mergeCell ref="C76:C77"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="C74:C75"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="C86:C87"/>
-    <mergeCell ref="A86:A87"/>
-    <mergeCell ref="B86:B87"/>
-    <mergeCell ref="G80:G81"/>
-    <mergeCell ref="C88:C89"/>
-    <mergeCell ref="C94:C95"/>
-    <mergeCell ref="G94:G95"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="A94:A95"/>
-    <mergeCell ref="B94:B95"/>
-    <mergeCell ref="B104:B105"/>
-    <mergeCell ref="C104:C105"/>
-    <mergeCell ref="A96:A97"/>
-    <mergeCell ref="B96:B97"/>
-    <mergeCell ref="C96:C97"/>
-    <mergeCell ref="B98:B99"/>
-    <mergeCell ref="C98:C99"/>
-    <mergeCell ref="A102:A103"/>
-    <mergeCell ref="B102:B103"/>
-    <mergeCell ref="A114:A115"/>
-    <mergeCell ref="B114:B115"/>
-    <mergeCell ref="A112:A113"/>
-    <mergeCell ref="B112:B113"/>
-    <mergeCell ref="A116:A117"/>
-    <mergeCell ref="B116:B117"/>
-    <mergeCell ref="A122:A123"/>
-    <mergeCell ref="B122:B123"/>
-    <mergeCell ref="G98:G99"/>
-    <mergeCell ref="A108:A109"/>
-    <mergeCell ref="B108:B109"/>
-    <mergeCell ref="C108:C109"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="B110:B111"/>
-    <mergeCell ref="A98:A99"/>
-    <mergeCell ref="A100:A101"/>
-    <mergeCell ref="B100:B101"/>
-    <mergeCell ref="C100:C101"/>
-    <mergeCell ref="A110:A111"/>
-    <mergeCell ref="A148:A149"/>
-    <mergeCell ref="G84:G85"/>
-    <mergeCell ref="G92:G93"/>
-    <mergeCell ref="G82:G83"/>
-    <mergeCell ref="G90:G91"/>
-    <mergeCell ref="G100:G101"/>
-    <mergeCell ref="C138:C139"/>
-    <mergeCell ref="G138:G139"/>
-    <mergeCell ref="G116:G117"/>
-    <mergeCell ref="G108:G109"/>
-    <mergeCell ref="G110:G111"/>
-    <mergeCell ref="C110:C111"/>
-    <mergeCell ref="C102:C103"/>
-    <mergeCell ref="C114:C115"/>
-    <mergeCell ref="C112:C113"/>
-    <mergeCell ref="C116:C117"/>
-    <mergeCell ref="G122:G123"/>
-    <mergeCell ref="C122:C123"/>
-    <mergeCell ref="C82:C83"/>
-    <mergeCell ref="G132:G133"/>
-    <mergeCell ref="G106:G107"/>
-    <mergeCell ref="G96:G97"/>
-    <mergeCell ref="G102:G103"/>
-    <mergeCell ref="G126:G127"/>
-    <mergeCell ref="B140:B141"/>
-    <mergeCell ref="C140:C141"/>
-    <mergeCell ref="G136:G137"/>
-    <mergeCell ref="A132:A133"/>
-    <mergeCell ref="A130:A131"/>
-    <mergeCell ref="B130:B131"/>
-    <mergeCell ref="C128:C129"/>
-    <mergeCell ref="A142:A143"/>
-    <mergeCell ref="B142:B143"/>
-    <mergeCell ref="A126:A127"/>
-    <mergeCell ref="B126:B127"/>
-    <mergeCell ref="C126:C127"/>
-    <mergeCell ref="B136:B137"/>
-    <mergeCell ref="C136:C137"/>
-    <mergeCell ref="G148:G149"/>
-    <mergeCell ref="A150:A151"/>
-    <mergeCell ref="A160:A161"/>
-    <mergeCell ref="B160:B161"/>
-    <mergeCell ref="C160:C161"/>
-    <mergeCell ref="G128:G129"/>
-    <mergeCell ref="A154:A155"/>
-    <mergeCell ref="A138:A139"/>
-    <mergeCell ref="G140:G141"/>
-    <mergeCell ref="G134:G135"/>
-    <mergeCell ref="A128:A129"/>
-    <mergeCell ref="B128:B129"/>
-    <mergeCell ref="B148:B149"/>
-    <mergeCell ref="C148:C149"/>
-    <mergeCell ref="G146:G147"/>
-    <mergeCell ref="A144:A145"/>
-    <mergeCell ref="B144:B145"/>
-    <mergeCell ref="C144:C145"/>
-    <mergeCell ref="A140:A141"/>
-    <mergeCell ref="C180:C181"/>
-    <mergeCell ref="G178:G179"/>
-    <mergeCell ref="A176:A177"/>
-    <mergeCell ref="B132:B133"/>
-    <mergeCell ref="C132:C133"/>
-    <mergeCell ref="B154:B155"/>
-    <mergeCell ref="C154:C155"/>
-    <mergeCell ref="G152:G153"/>
-    <mergeCell ref="G172:G173"/>
-    <mergeCell ref="B176:B177"/>
-    <mergeCell ref="C176:C177"/>
-    <mergeCell ref="B172:B173"/>
-    <mergeCell ref="A168:A169"/>
-    <mergeCell ref="G170:G171"/>
-    <mergeCell ref="G176:G177"/>
-    <mergeCell ref="G142:G143"/>
-    <mergeCell ref="A170:A171"/>
-    <mergeCell ref="B170:B171"/>
-    <mergeCell ref="C170:C171"/>
-    <mergeCell ref="G168:G169"/>
-    <mergeCell ref="A172:A173"/>
-    <mergeCell ref="A180:A181"/>
-    <mergeCell ref="B180:B181"/>
-    <mergeCell ref="A136:A137"/>
-    <mergeCell ref="B190:B191"/>
-    <mergeCell ref="G182:G183"/>
-    <mergeCell ref="C190:C191"/>
-    <mergeCell ref="G188:G189"/>
-    <mergeCell ref="B188:B189"/>
-    <mergeCell ref="C172:C173"/>
-    <mergeCell ref="C158:C159"/>
-    <mergeCell ref="G156:G157"/>
-    <mergeCell ref="A156:A157"/>
-    <mergeCell ref="B156:B157"/>
-    <mergeCell ref="A174:A175"/>
-    <mergeCell ref="B174:B175"/>
-    <mergeCell ref="C174:C175"/>
-    <mergeCell ref="G174:G175"/>
-    <mergeCell ref="B158:B159"/>
-    <mergeCell ref="C186:C187"/>
-    <mergeCell ref="A158:A159"/>
-    <mergeCell ref="G186:G187"/>
-    <mergeCell ref="A182:A183"/>
-    <mergeCell ref="B182:B183"/>
-    <mergeCell ref="C168:C169"/>
-    <mergeCell ref="G166:G167"/>
-    <mergeCell ref="A184:A185"/>
-    <mergeCell ref="G162:G163"/>
-    <mergeCell ref="A124:A125"/>
-    <mergeCell ref="B124:B125"/>
-    <mergeCell ref="A118:A119"/>
-    <mergeCell ref="A134:A135"/>
-    <mergeCell ref="B134:B135"/>
-    <mergeCell ref="C134:C135"/>
-    <mergeCell ref="G214:G215"/>
-    <mergeCell ref="C118:C119"/>
-    <mergeCell ref="B118:B119"/>
-    <mergeCell ref="C124:C125"/>
-    <mergeCell ref="A152:A153"/>
-    <mergeCell ref="B152:B153"/>
-    <mergeCell ref="C152:C153"/>
-    <mergeCell ref="A146:A147"/>
-    <mergeCell ref="B146:B147"/>
-    <mergeCell ref="C146:C147"/>
-    <mergeCell ref="B150:B151"/>
-    <mergeCell ref="C150:C151"/>
-    <mergeCell ref="G150:G151"/>
-    <mergeCell ref="G160:G161"/>
-    <mergeCell ref="A166:A167"/>
-    <mergeCell ref="A162:A163"/>
-    <mergeCell ref="A188:A189"/>
-    <mergeCell ref="A190:A191"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="A47:H47"/>
-    <mergeCell ref="A48:H48"/>
-    <mergeCell ref="A41:H41"/>
-    <mergeCell ref="G50:G51"/>
-    <mergeCell ref="G52:G53"/>
-    <mergeCell ref="G54:G55"/>
-    <mergeCell ref="G56:G57"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="A62:A63"/>
-    <mergeCell ref="C62:C63"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="G58:G59"/>
-    <mergeCell ref="G60:G61"/>
-    <mergeCell ref="C208:C209"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="C64:C65"/>
-    <mergeCell ref="B92:B93"/>
-    <mergeCell ref="G88:G89"/>
-    <mergeCell ref="C90:C91"/>
-    <mergeCell ref="G130:G131"/>
-    <mergeCell ref="C130:C131"/>
-    <mergeCell ref="G144:G145"/>
-    <mergeCell ref="B162:B163"/>
-    <mergeCell ref="C162:C163"/>
-    <mergeCell ref="B138:B139"/>
-    <mergeCell ref="G154:G155"/>
-    <mergeCell ref="G158:G159"/>
-    <mergeCell ref="C156:C157"/>
-    <mergeCell ref="C142:C143"/>
-    <mergeCell ref="G120:G121"/>
-    <mergeCell ref="G114:G115"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/main/resources/InesModResources/杀戮尖塔自制--伊内丝v0.2.xlsx
+++ b/src/main/resources/InesModResources/杀戮尖塔自制--伊内丝v0.2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\myMod\InesMod\InesMod\src\main\resources\InesModResources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F46C2FF3-5F69-4747-BB10-5CEB4AEF1778}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AF26BEE-EA13-4749-B32D-9578877E3C3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{7A3E14A4-2175-4856-859A-887D335814F1}"/>
   </bookViews>
@@ -2407,10 +2407,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>当前所有手牌在本回合的耗能-2。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>自动打出。你打出的下2张攻击牌耗能变为0。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2542,6 +2538,10 @@
   </si>
   <si>
     <t>下一张打出的攻击牌造成2倍伤害，随后失去一半格挡并结束你的回合。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当前所有手牌在本回合的耗能-2。消耗。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2595,7 +2595,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2647,6 +2647,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2900,10 +2906,10 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3340,7 +3346,7 @@
       <c r="D10" s="30"/>
       <c r="E10" s="31"/>
       <c r="F10" s="9" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="G10" s="10"/>
       <c r="H10" s="17" t="s">
@@ -3360,7 +3366,7 @@
       <c r="D11" s="30"/>
       <c r="E11" s="31"/>
       <c r="F11" s="9" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="G11" s="10"/>
       <c r="H11" s="17" t="s">
@@ -3490,7 +3496,7 @@
         <v>456</v>
       </c>
       <c r="C21" s="25" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D21" s="26"/>
       <c r="E21" s="26"/>
@@ -3681,7 +3687,7 @@
         <v>456</v>
       </c>
       <c r="C34" s="25" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D34" s="26"/>
       <c r="E34" s="26"/>
@@ -4772,7 +4778,7 @@
         <v>1</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="G86" s="32"/>
       <c r="H86" s="15" t="s">
@@ -4790,7 +4796,7 @@
         <v>1</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="G87" s="32"/>
       <c r="H87" s="15" t="s">
@@ -5034,7 +5040,7 @@
         <v>0</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="G98" s="32"/>
       <c r="H98" s="15" t="s">
@@ -5052,7 +5058,7 @@
         <v>0</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="G99" s="32"/>
       <c r="H99" s="15" t="s">
@@ -5076,7 +5082,7 @@
         <v>1</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="G100" s="32"/>
       <c r="H100" s="15" t="s">
@@ -5094,7 +5100,7 @@
         <v>1</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="G101" s="32"/>
       <c r="H101" s="15" t="s">
@@ -5118,7 +5124,7 @@
         <v>1</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="G102" s="32"/>
       <c r="H102" s="15" t="s">
@@ -5136,7 +5142,7 @@
         <v>1</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="G103" s="32"/>
       <c r="H103" s="15" t="s">
@@ -5506,7 +5512,7 @@
         <v>0</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="G120" s="32" t="s">
         <v>245</v>
@@ -5526,7 +5532,7 @@
         <v>0</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="G121" s="32"/>
       <c r="H121" s="15" t="s">
@@ -5550,7 +5556,7 @@
         <v>2</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="G122" s="32"/>
       <c r="H122" s="15" t="s">
@@ -5568,7 +5574,7 @@
         <v>1</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="G123" s="32"/>
       <c r="H123" s="15" t="s">
@@ -5637,7 +5643,7 @@
         <v>222</v>
       </c>
       <c r="G126" s="32" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H126" s="15" t="s">
         <v>549</v>
@@ -5720,7 +5726,7 @@
         <v>1</v>
       </c>
       <c r="F130" s="5" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="G130" s="32"/>
       <c r="H130" s="15" t="s">
@@ -5738,7 +5744,7 @@
         <v>1</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="G131" s="32"/>
       <c r="H131" s="15" t="s">
@@ -5804,7 +5810,7 @@
         <v>0</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="G134" s="32"/>
       <c r="H134" s="15" t="s">
@@ -5822,7 +5828,7 @@
         <v>0</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="G135" s="32"/>
       <c r="H135" s="15" t="s">
@@ -6488,7 +6494,7 @@
         <v>1</v>
       </c>
       <c r="F166" s="5" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="G166" s="32" t="s">
         <v>192</v>
@@ -6508,7 +6514,7 @@
         <v>0</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="G167" s="32"/>
       <c r="H167" s="15" t="s">
@@ -6532,7 +6538,7 @@
         <v>1</v>
       </c>
       <c r="F168" s="5" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="G168" s="32"/>
       <c r="H168" s="15" t="s">
@@ -6550,7 +6556,7 @@
         <v>0</v>
       </c>
       <c r="F169" s="5" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="G169" s="32"/>
       <c r="H169" s="15" t="s">
@@ -6577,10 +6583,10 @@
         <v>611</v>
       </c>
       <c r="G170" s="32" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H170" s="15" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="171" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6598,7 +6604,7 @@
       </c>
       <c r="G171" s="32"/>
       <c r="H171" s="15" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="172" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6660,7 +6666,7 @@
         <v>1</v>
       </c>
       <c r="F174" s="5" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="G174" s="32" t="s">
         <v>576</v>
@@ -6704,7 +6710,7 @@
         <v>1</v>
       </c>
       <c r="F176" s="5" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="G176" s="32" t="s">
         <v>112</v>
@@ -6724,7 +6730,7 @@
         <v>1</v>
       </c>
       <c r="F177" s="5" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="G177" s="32"/>
       <c r="H177" s="15" t="s">
@@ -6748,7 +6754,7 @@
         <v>1</v>
       </c>
       <c r="F178" s="5" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="G178" s="32"/>
       <c r="H178" s="15" t="s">
@@ -6858,7 +6864,7 @@
       </c>
     </row>
     <row r="184" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A184" s="33">
+      <c r="A184" s="52">
         <v>68</v>
       </c>
       <c r="B184" s="35" t="s">
@@ -6882,7 +6888,7 @@
       </c>
     </row>
     <row r="185" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A185" s="34"/>
+      <c r="A185" s="53"/>
       <c r="B185" s="35"/>
       <c r="C185" s="28"/>
       <c r="D185" s="5" t="s">
@@ -6916,7 +6922,7 @@
         <v>3</v>
       </c>
       <c r="F186" s="5" t="s">
-        <v>632</v>
+        <v>665</v>
       </c>
       <c r="G186" s="32"/>
       <c r="H186" s="15" t="s">
@@ -6934,7 +6940,7 @@
         <v>2</v>
       </c>
       <c r="F187" s="5" t="s">
-        <v>632</v>
+        <v>665</v>
       </c>
       <c r="G187" s="32"/>
       <c r="H187" s="15" t="s">
@@ -7044,7 +7050,7 @@
         <v>43</v>
       </c>
       <c r="F192" s="5" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="G192" s="32"/>
       <c r="H192" s="15" t="s">
@@ -7130,7 +7136,7 @@
         <v>1</v>
       </c>
       <c r="F196" s="5" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="G196" s="32" t="s">
         <v>138</v>
@@ -7150,7 +7156,7 @@
         <v>1</v>
       </c>
       <c r="F197" s="5" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="G197" s="32"/>
       <c r="H197" s="15" t="s">

--- a/src/main/resources/InesModResources/杀戮尖塔自制--伊内丝v0.2.xlsx
+++ b/src/main/resources/InesModResources/杀戮尖塔自制--伊内丝v0.2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\myMod\InesMod\InesMod\src\main\resources\InesModResources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AF26BEE-EA13-4749-B32D-9578877E3C3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE0E11B3-35A7-4BB4-9F9F-4B402D9C97D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{7A3E14A4-2175-4856-859A-887D335814F1}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="666">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="668">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2542,6 +2542,15 @@
   </si>
   <si>
     <t>当前所有手牌在本回合的耗能-2。消耗。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同上。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>实际为获得1层同名buff（效果可叠加，可跨回合），达到条件时触发。
+正在结束回合时，不触发。（下）回合抽牌前，触发。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2595,7 +2604,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2647,12 +2656,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2749,7 +2752,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2835,6 +2838,27 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2846,46 +2870,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2894,22 +2882,31 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3245,10 +3242,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="29" t="s">
         <v>290</v>
       </c>
-      <c r="B1" s="28"/>
+      <c r="B1" s="29"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -3300,16 +3297,16 @@
       <c r="B6" s="2"/>
     </row>
     <row r="8" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="36" t="s">
         <v>105</v>
       </c>
-      <c r="B8" s="30"/>
-      <c r="C8" s="30"/>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="30"/>
-      <c r="H8" s="31"/>
+      <c r="B8" s="37"/>
+      <c r="C8" s="37"/>
+      <c r="D8" s="37"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="38"/>
     </row>
     <row r="9" spans="1:8" ht="25.7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
@@ -3318,11 +3315,11 @@
       <c r="B9" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" s="36" t="s">
         <v>229</v>
       </c>
-      <c r="D9" s="30"/>
-      <c r="E9" s="31"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="38"/>
       <c r="F9" s="8" t="s">
         <v>2</v>
       </c>
@@ -3340,11 +3337,11 @@
       <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="30" t="s">
+      <c r="C10" s="37" t="s">
         <v>231</v>
       </c>
-      <c r="D10" s="30"/>
-      <c r="E10" s="31"/>
+      <c r="D10" s="37"/>
+      <c r="E10" s="38"/>
       <c r="F10" s="9" t="s">
         <v>648</v>
       </c>
@@ -3360,11 +3357,11 @@
       <c r="B11" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="C11" s="29" t="s">
+      <c r="C11" s="36" t="s">
         <v>235</v>
       </c>
-      <c r="D11" s="30"/>
-      <c r="E11" s="31"/>
+      <c r="D11" s="37"/>
+      <c r="E11" s="38"/>
       <c r="F11" s="9" t="s">
         <v>649</v>
       </c>
@@ -3380,11 +3377,11 @@
       <c r="B12" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="C12" s="29" t="s">
+      <c r="C12" s="36" t="s">
         <v>466</v>
       </c>
-      <c r="D12" s="30"/>
-      <c r="E12" s="31"/>
+      <c r="D12" s="37"/>
+      <c r="E12" s="38"/>
       <c r="F12" s="9" t="s">
         <v>241</v>
       </c>
@@ -3403,8 +3400,8 @@
       <c r="C13" s="25" t="s">
         <v>447</v>
       </c>
-      <c r="D13" s="30"/>
-      <c r="E13" s="31"/>
+      <c r="D13" s="37"/>
+      <c r="E13" s="38"/>
       <c r="F13" s="9" t="s">
         <v>224</v>
       </c>
@@ -3420,11 +3417,11 @@
       <c r="B14" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="C14" s="30" t="s">
+      <c r="C14" s="37" t="s">
         <v>286</v>
       </c>
-      <c r="D14" s="30"/>
-      <c r="E14" s="31"/>
+      <c r="D14" s="37"/>
+      <c r="E14" s="38"/>
       <c r="F14" s="9" t="s">
         <v>240</v>
       </c>
@@ -3437,16 +3434,16 @@
     <row r="16" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="17" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="28" t="s">
+      <c r="A18" s="29" t="s">
         <v>86</v>
       </c>
-      <c r="B18" s="28"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="28"/>
+      <c r="B18" s="29"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="29"/>
+      <c r="G18" s="29"/>
+      <c r="H18" s="29"/>
     </row>
     <row r="19" spans="1:8" ht="25.7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
@@ -3455,12 +3452,12 @@
       <c r="B19" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="C19" s="29" t="s">
+      <c r="C19" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="31"/>
+      <c r="D19" s="37"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="38"/>
       <c r="G19" s="1" t="s">
         <v>3</v>
       </c>
@@ -3630,16 +3627,16 @@
     <row r="29" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="1:8" ht="21.7" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="31" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="28" t="s">
+      <c r="A31" s="29" t="s">
         <v>495</v>
       </c>
-      <c r="B31" s="28"/>
-      <c r="C31" s="28"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="28"/>
-      <c r="H31" s="28"/>
+      <c r="B31" s="29"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="29"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="29"/>
+      <c r="H31" s="29"/>
     </row>
     <row r="32" spans="1:8" ht="25.7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="1" t="s">
@@ -3648,12 +3645,12 @@
       <c r="B32" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="C32" s="29" t="s">
+      <c r="C32" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="D32" s="30"/>
-      <c r="E32" s="30"/>
-      <c r="F32" s="31"/>
+      <c r="D32" s="37"/>
+      <c r="E32" s="37"/>
+      <c r="F32" s="38"/>
       <c r="G32" s="1" t="s">
         <v>3</v>
       </c>
@@ -3764,16 +3761,16 @@
       <c r="H40" s="11"/>
     </row>
     <row r="41" spans="1:8" s="3" customFormat="1" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="28" t="s">
+      <c r="A41" s="29" t="s">
         <v>499</v>
       </c>
-      <c r="B41" s="28"/>
-      <c r="C41" s="28"/>
-      <c r="D41" s="28"/>
-      <c r="E41" s="28"/>
-      <c r="F41" s="28"/>
-      <c r="G41" s="28"/>
-      <c r="H41" s="28"/>
+      <c r="B41" s="29"/>
+      <c r="C41" s="29"/>
+      <c r="D41" s="29"/>
+      <c r="E41" s="29"/>
+      <c r="F41" s="29"/>
+      <c r="G41" s="29"/>
+      <c r="H41" s="29"/>
     </row>
     <row r="42" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="1" t="s">
@@ -3838,28 +3835,28 @@
       <c r="H46" s="2"/>
     </row>
     <row r="47" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="28" t="s">
+      <c r="A47" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="B47" s="28"/>
-      <c r="C47" s="28"/>
-      <c r="D47" s="28"/>
-      <c r="E47" s="28"/>
-      <c r="F47" s="28"/>
-      <c r="G47" s="28"/>
-      <c r="H47" s="28"/>
+      <c r="B47" s="29"/>
+      <c r="C47" s="29"/>
+      <c r="D47" s="29"/>
+      <c r="E47" s="29"/>
+      <c r="F47" s="29"/>
+      <c r="G47" s="29"/>
+      <c r="H47" s="29"/>
     </row>
     <row r="48" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="28" t="s">
+      <c r="A48" s="29" t="s">
         <v>511</v>
       </c>
-      <c r="B48" s="28"/>
-      <c r="C48" s="28"/>
-      <c r="D48" s="28"/>
-      <c r="E48" s="28"/>
-      <c r="F48" s="28"/>
-      <c r="G48" s="28"/>
-      <c r="H48" s="28"/>
+      <c r="B48" s="29"/>
+      <c r="C48" s="29"/>
+      <c r="D48" s="29"/>
+      <c r="E48" s="29"/>
+      <c r="F48" s="29"/>
+      <c r="G48" s="29"/>
+      <c r="H48" s="29"/>
     </row>
     <row r="49" spans="1:12" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="1" t="s">
@@ -3888,13 +3885,13 @@
       </c>
     </row>
     <row r="50" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="51">
-        <v>1</v>
-      </c>
-      <c r="B50" s="50" t="s">
+      <c r="A50" s="40">
+        <v>1</v>
+      </c>
+      <c r="B50" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="C50" s="28" t="s">
+      <c r="C50" s="29" t="s">
         <v>6</v>
       </c>
       <c r="D50" s="6" t="s">
@@ -3906,15 +3903,15 @@
       <c r="F50" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G50" s="32"/>
+      <c r="G50" s="28"/>
       <c r="H50" s="15" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="51" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="51"/>
-      <c r="B51" s="50"/>
-      <c r="C51" s="28"/>
+      <c r="A51" s="40"/>
+      <c r="B51" s="39"/>
+      <c r="C51" s="29"/>
       <c r="D51" s="6" t="s">
         <v>18</v>
       </c>
@@ -3924,7 +3921,7 @@
       <c r="F51" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G51" s="32"/>
+      <c r="G51" s="28"/>
       <c r="H51" s="15" t="s">
         <v>357</v>
       </c>
@@ -3934,13 +3931,13 @@
       <c r="L51" s="2"/>
     </row>
     <row r="52" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="38">
+      <c r="A52" s="34">
         <v>2</v>
       </c>
-      <c r="B52" s="50" t="s">
+      <c r="B52" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="28" t="s">
+      <c r="C52" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D52" s="6" t="s">
@@ -3952,7 +3949,7 @@
       <c r="F52" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G52" s="32"/>
+      <c r="G52" s="28"/>
       <c r="H52" s="15" t="s">
         <v>297</v>
       </c>
@@ -3962,9 +3959,9 @@
       <c r="L52" s="2"/>
     </row>
     <row r="53" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="39"/>
-      <c r="B53" s="50"/>
-      <c r="C53" s="28"/>
+      <c r="A53" s="35"/>
+      <c r="B53" s="39"/>
+      <c r="C53" s="29"/>
       <c r="D53" s="6" t="s">
         <v>19</v>
       </c>
@@ -3974,7 +3971,7 @@
       <c r="F53" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G53" s="32"/>
+      <c r="G53" s="28"/>
       <c r="H53" s="15" t="s">
         <v>358</v>
       </c>
@@ -3984,13 +3981,13 @@
       <c r="L53" s="2"/>
     </row>
     <row r="54" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="38">
+      <c r="A54" s="34">
         <v>3</v>
       </c>
-      <c r="B54" s="50" t="s">
+      <c r="B54" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="28" t="s">
+      <c r="C54" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D54" s="5" t="s">
@@ -4002,7 +3999,7 @@
       <c r="F54" s="5" t="s">
         <v>492</v>
       </c>
-      <c r="G54" s="32"/>
+      <c r="G54" s="28"/>
       <c r="H54" s="15" t="s">
         <v>455</v>
       </c>
@@ -4012,9 +4009,9 @@
       <c r="L54" s="2"/>
     </row>
     <row r="55" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="39"/>
-      <c r="B55" s="50"/>
-      <c r="C55" s="28"/>
+      <c r="A55" s="35"/>
+      <c r="B55" s="39"/>
+      <c r="C55" s="29"/>
       <c r="D55" s="5" t="s">
         <v>20</v>
       </c>
@@ -4024,7 +4021,7 @@
       <c r="F55" s="5" t="s">
         <v>509</v>
       </c>
-      <c r="G55" s="32"/>
+      <c r="G55" s="28"/>
       <c r="H55" s="15" t="s">
         <v>359</v>
       </c>
@@ -4034,13 +4031,13 @@
       <c r="L55" s="2"/>
     </row>
     <row r="56" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="38">
+      <c r="A56" s="34">
         <v>4</v>
       </c>
-      <c r="B56" s="50" t="s">
+      <c r="B56" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="C56" s="28" t="s">
+      <c r="C56" s="29" t="s">
         <v>6</v>
       </c>
       <c r="D56" s="5" t="s">
@@ -4052,7 +4049,7 @@
       <c r="F56" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="G56" s="32"/>
+      <c r="G56" s="28"/>
       <c r="H56" s="15" t="s">
         <v>292</v>
       </c>
@@ -4062,9 +4059,9 @@
       <c r="L56" s="2"/>
     </row>
     <row r="57" spans="1:12" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="39"/>
-      <c r="B57" s="50"/>
-      <c r="C57" s="28"/>
+      <c r="A57" s="35"/>
+      <c r="B57" s="39"/>
+      <c r="C57" s="29"/>
       <c r="D57" s="5" t="s">
         <v>25</v>
       </c>
@@ -4074,7 +4071,7 @@
       <c r="F57" s="5" t="s">
         <v>507</v>
       </c>
-      <c r="G57" s="32"/>
+      <c r="G57" s="28"/>
       <c r="H57" s="15" t="s">
         <v>422</v>
       </c>
@@ -4084,13 +4081,13 @@
       <c r="L57" s="2"/>
     </row>
     <row r="58" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="38">
+      <c r="A58" s="34">
         <v>5</v>
       </c>
-      <c r="B58" s="40" t="s">
+      <c r="B58" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C58" s="28" t="s">
+      <c r="C58" s="29" t="s">
         <v>6</v>
       </c>
       <c r="D58" s="5" t="s">
@@ -4102,7 +4099,7 @@
       <c r="F58" s="5" t="s">
         <v>488</v>
       </c>
-      <c r="G58" s="32" t="s">
+      <c r="G58" s="28" t="s">
         <v>489</v>
       </c>
       <c r="H58" s="15" t="s">
@@ -4114,9 +4111,9 @@
       <c r="L58" s="2"/>
     </row>
     <row r="59" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A59" s="39"/>
-      <c r="B59" s="40"/>
-      <c r="C59" s="28"/>
+      <c r="A59" s="35"/>
+      <c r="B59" s="30"/>
+      <c r="C59" s="29"/>
       <c r="D59" s="5" t="s">
         <v>26</v>
       </c>
@@ -4126,7 +4123,7 @@
       <c r="F59" s="5" t="s">
         <v>525</v>
       </c>
-      <c r="G59" s="32"/>
+      <c r="G59" s="28"/>
       <c r="H59" s="15" t="s">
         <v>360</v>
       </c>
@@ -4136,13 +4133,13 @@
       <c r="L59" s="2"/>
     </row>
     <row r="60" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="38">
+      <c r="A60" s="34">
         <v>6</v>
       </c>
-      <c r="B60" s="40" t="s">
+      <c r="B60" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C60" s="28" t="s">
+      <c r="C60" s="29" t="s">
         <v>6</v>
       </c>
       <c r="D60" s="5" t="s">
@@ -4154,7 +4151,7 @@
       <c r="F60" s="5" t="s">
         <v>562</v>
       </c>
-      <c r="G60" s="32"/>
+      <c r="G60" s="28"/>
       <c r="H60" s="15" t="s">
         <v>299</v>
       </c>
@@ -4164,9 +4161,9 @@
       <c r="L60" s="2"/>
     </row>
     <row r="61" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="39"/>
-      <c r="B61" s="40"/>
-      <c r="C61" s="28"/>
+      <c r="A61" s="35"/>
+      <c r="B61" s="30"/>
+      <c r="C61" s="29"/>
       <c r="D61" s="5" t="s">
         <v>28</v>
       </c>
@@ -4176,7 +4173,7 @@
       <c r="F61" s="5" t="s">
         <v>561</v>
       </c>
-      <c r="G61" s="32"/>
+      <c r="G61" s="28"/>
       <c r="H61" s="15" t="s">
         <v>361</v>
       </c>
@@ -4186,13 +4183,13 @@
       <c r="L61" s="2"/>
     </row>
     <row r="62" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="38">
+      <c r="A62" s="34">
         <v>7</v>
       </c>
-      <c r="B62" s="40" t="s">
+      <c r="B62" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C62" s="28" t="s">
+      <c r="C62" s="29" t="s">
         <v>6</v>
       </c>
       <c r="D62" s="5" t="s">
@@ -4204,7 +4201,7 @@
       <c r="F62" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="G62" s="32"/>
+      <c r="G62" s="28"/>
       <c r="H62" s="15" t="s">
         <v>300</v>
       </c>
@@ -4214,9 +4211,9 @@
       <c r="L62" s="2"/>
     </row>
     <row r="63" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="39"/>
-      <c r="B63" s="40"/>
-      <c r="C63" s="28"/>
+      <c r="A63" s="35"/>
+      <c r="B63" s="30"/>
+      <c r="C63" s="29"/>
       <c r="D63" s="5" t="s">
         <v>38</v>
       </c>
@@ -4226,7 +4223,7 @@
       <c r="F63" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="G63" s="32"/>
+      <c r="G63" s="28"/>
       <c r="H63" s="15" t="s">
         <v>362</v>
       </c>
@@ -4236,13 +4233,13 @@
       <c r="L63" s="2"/>
     </row>
     <row r="64" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A64" s="38">
+      <c r="A64" s="34">
         <v>8</v>
       </c>
-      <c r="B64" s="40" t="s">
+      <c r="B64" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C64" s="28" t="s">
+      <c r="C64" s="29" t="s">
         <v>6</v>
       </c>
       <c r="D64" s="5" t="s">
@@ -4254,7 +4251,7 @@
       <c r="F64" s="5" t="s">
         <v>563</v>
       </c>
-      <c r="G64" s="32" t="s">
+      <c r="G64" s="28" t="s">
         <v>538</v>
       </c>
       <c r="H64" s="15" t="s">
@@ -4266,9 +4263,9 @@
       <c r="L64" s="2"/>
     </row>
     <row r="65" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A65" s="39"/>
-      <c r="B65" s="40"/>
-      <c r="C65" s="28"/>
+      <c r="A65" s="35"/>
+      <c r="B65" s="30"/>
+      <c r="C65" s="29"/>
       <c r="D65" s="5" t="s">
         <v>190</v>
       </c>
@@ -4278,7 +4275,7 @@
       <c r="F65" s="5" t="s">
         <v>564</v>
       </c>
-      <c r="G65" s="32"/>
+      <c r="G65" s="28"/>
       <c r="H65" s="15" t="s">
         <v>363</v>
       </c>
@@ -4288,13 +4285,13 @@
       <c r="L65" s="2"/>
     </row>
     <row r="66" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A66" s="38">
+      <c r="A66" s="34">
         <v>9</v>
       </c>
-      <c r="B66" s="40" t="s">
+      <c r="B66" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C66" s="28" t="s">
+      <c r="C66" s="29" t="s">
         <v>6</v>
       </c>
       <c r="D66" s="5" t="s">
@@ -4306,7 +4303,7 @@
       <c r="F66" s="5" t="s">
         <v>535</v>
       </c>
-      <c r="G66" s="32" t="s">
+      <c r="G66" s="28" t="s">
         <v>539</v>
       </c>
       <c r="H66" s="15" t="s">
@@ -4314,9 +4311,9 @@
       </c>
     </row>
     <row r="67" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A67" s="39"/>
-      <c r="B67" s="40"/>
-      <c r="C67" s="28"/>
+      <c r="A67" s="35"/>
+      <c r="B67" s="30"/>
+      <c r="C67" s="29"/>
       <c r="D67" s="5" t="s">
         <v>114</v>
       </c>
@@ -4326,19 +4323,19 @@
       <c r="F67" s="5" t="s">
         <v>536</v>
       </c>
-      <c r="G67" s="32"/>
+      <c r="G67" s="28"/>
       <c r="H67" s="15" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="68" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A68" s="38">
+      <c r="A68" s="34">
         <v>10</v>
       </c>
-      <c r="B68" s="40" t="s">
+      <c r="B68" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C68" s="28" t="s">
+      <c r="C68" s="29" t="s">
         <v>6</v>
       </c>
       <c r="D68" s="5" t="s">
@@ -4350,7 +4347,7 @@
       <c r="F68" s="5" t="s">
         <v>517</v>
       </c>
-      <c r="G68" s="32" t="s">
+      <c r="G68" s="28" t="s">
         <v>540</v>
       </c>
       <c r="H68" s="15" t="s">
@@ -4362,9 +4359,9 @@
       <c r="L68" s="2"/>
     </row>
     <row r="69" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A69" s="39"/>
-      <c r="B69" s="40"/>
-      <c r="C69" s="28"/>
+      <c r="A69" s="35"/>
+      <c r="B69" s="30"/>
+      <c r="C69" s="29"/>
       <c r="D69" s="5" t="s">
         <v>156</v>
       </c>
@@ -4374,7 +4371,7 @@
       <c r="F69" s="5" t="s">
         <v>516</v>
       </c>
-      <c r="G69" s="32"/>
+      <c r="G69" s="28"/>
       <c r="H69" s="15" t="s">
         <v>365</v>
       </c>
@@ -4384,13 +4381,13 @@
       <c r="L69" s="2"/>
     </row>
     <row r="70" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A70" s="38">
+      <c r="A70" s="34">
         <v>11</v>
       </c>
-      <c r="B70" s="40" t="s">
+      <c r="B70" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C70" s="28" t="s">
+      <c r="C70" s="29" t="s">
         <v>6</v>
       </c>
       <c r="D70" s="5" t="s">
@@ -4402,7 +4399,7 @@
       <c r="F70" s="5" t="s">
         <v>598</v>
       </c>
-      <c r="G70" s="32" t="s">
+      <c r="G70" s="28" t="s">
         <v>538</v>
       </c>
       <c r="H70" s="15" t="s">
@@ -4414,9 +4411,9 @@
       <c r="L70" s="2"/>
     </row>
     <row r="71" spans="1:12" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A71" s="39"/>
-      <c r="B71" s="40"/>
-      <c r="C71" s="28"/>
+      <c r="A71" s="35"/>
+      <c r="B71" s="30"/>
+      <c r="C71" s="29"/>
       <c r="D71" s="5" t="s">
         <v>154</v>
       </c>
@@ -4426,7 +4423,7 @@
       <c r="F71" s="5" t="s">
         <v>599</v>
       </c>
-      <c r="G71" s="32"/>
+      <c r="G71" s="28"/>
       <c r="H71" s="15" t="s">
         <v>366</v>
       </c>
@@ -4436,13 +4433,13 @@
       <c r="L71" s="2"/>
     </row>
     <row r="72" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A72" s="38">
+      <c r="A72" s="34">
         <v>12</v>
       </c>
-      <c r="B72" s="36" t="s">
+      <c r="B72" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C72" s="28" t="s">
+      <c r="C72" s="29" t="s">
         <v>6</v>
       </c>
       <c r="D72" s="5" t="s">
@@ -4454,7 +4451,7 @@
       <c r="F72" s="5" t="s">
         <v>596</v>
       </c>
-      <c r="G72" s="32" t="s">
+      <c r="G72" s="28" t="s">
         <v>538</v>
       </c>
       <c r="H72" s="15" t="s">
@@ -4466,9 +4463,9 @@
       <c r="L72" s="2"/>
     </row>
     <row r="73" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A73" s="39"/>
-      <c r="B73" s="36"/>
-      <c r="C73" s="28"/>
+      <c r="A73" s="35"/>
+      <c r="B73" s="33"/>
+      <c r="C73" s="29"/>
       <c r="D73" s="5" t="s">
         <v>36</v>
       </c>
@@ -4478,7 +4475,7 @@
       <c r="F73" s="5" t="s">
         <v>597</v>
       </c>
-      <c r="G73" s="32"/>
+      <c r="G73" s="28"/>
       <c r="H73" s="15" t="s">
         <v>367</v>
       </c>
@@ -4488,13 +4485,13 @@
       <c r="L73" s="2"/>
     </row>
     <row r="74" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A74" s="38">
+      <c r="A74" s="34">
         <v>13</v>
       </c>
-      <c r="B74" s="36" t="s">
+      <c r="B74" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C74" s="28" t="s">
+      <c r="C74" s="29" t="s">
         <v>6</v>
       </c>
       <c r="D74" s="5" t="s">
@@ -4506,7 +4503,7 @@
       <c r="F74" s="5" t="s">
         <v>514</v>
       </c>
-      <c r="G74" s="32"/>
+      <c r="G74" s="28"/>
       <c r="H74" s="15" t="s">
         <v>626</v>
       </c>
@@ -4516,9 +4513,9 @@
       <c r="L74" s="2"/>
     </row>
     <row r="75" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A75" s="39"/>
-      <c r="B75" s="36"/>
-      <c r="C75" s="28"/>
+      <c r="A75" s="35"/>
+      <c r="B75" s="33"/>
+      <c r="C75" s="29"/>
       <c r="D75" s="5" t="s">
         <v>34</v>
       </c>
@@ -4528,7 +4525,7 @@
       <c r="F75" s="5" t="s">
         <v>515</v>
       </c>
-      <c r="G75" s="32"/>
+      <c r="G75" s="28"/>
       <c r="H75" s="15" t="s">
         <v>627</v>
       </c>
@@ -4538,13 +4535,13 @@
       <c r="L75" s="2"/>
     </row>
     <row r="76" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A76" s="38">
+      <c r="A76" s="34">
         <v>14</v>
       </c>
-      <c r="B76" s="36" t="s">
+      <c r="B76" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C76" s="28" t="s">
+      <c r="C76" s="29" t="s">
         <v>6</v>
       </c>
       <c r="D76" s="5" t="s">
@@ -4556,7 +4553,7 @@
       <c r="F76" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="G76" s="32" t="s">
+      <c r="G76" s="28" t="s">
         <v>538</v>
       </c>
       <c r="H76" s="15" t="s">
@@ -4568,9 +4565,9 @@
       <c r="L76" s="2"/>
     </row>
     <row r="77" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A77" s="39"/>
-      <c r="B77" s="36"/>
-      <c r="C77" s="28"/>
+      <c r="A77" s="35"/>
+      <c r="B77" s="33"/>
+      <c r="C77" s="29"/>
       <c r="D77" s="5" t="s">
         <v>125</v>
       </c>
@@ -4580,19 +4577,19 @@
       <c r="F77" s="5" t="s">
         <v>470</v>
       </c>
-      <c r="G77" s="32"/>
+      <c r="G77" s="28"/>
       <c r="H77" s="15" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="78" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A78" s="38">
+      <c r="A78" s="34">
         <v>15</v>
       </c>
-      <c r="B78" s="36" t="s">
+      <c r="B78" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C78" s="28" t="s">
+      <c r="C78" s="29" t="s">
         <v>6</v>
       </c>
       <c r="D78" s="5" t="s">
@@ -4604,7 +4601,7 @@
       <c r="F78" s="5" t="s">
         <v>591</v>
       </c>
-      <c r="G78" s="32" t="s">
+      <c r="G78" s="28" t="s">
         <v>589</v>
       </c>
       <c r="H78" s="15" t="s">
@@ -4612,9 +4609,9 @@
       </c>
     </row>
     <row r="79" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A79" s="39"/>
-      <c r="B79" s="36"/>
-      <c r="C79" s="28"/>
+      <c r="A79" s="35"/>
+      <c r="B79" s="33"/>
+      <c r="C79" s="29"/>
       <c r="D79" s="5" t="s">
         <v>123</v>
       </c>
@@ -4624,19 +4621,19 @@
       <c r="F79" s="5" t="s">
         <v>592</v>
       </c>
-      <c r="G79" s="32"/>
+      <c r="G79" s="28"/>
       <c r="H79" s="15" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="80" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A80" s="38">
+      <c r="A80" s="34">
         <v>16</v>
       </c>
-      <c r="B80" s="36" t="s">
+      <c r="B80" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C80" s="41" t="s">
+      <c r="C80" s="50" t="s">
         <v>6</v>
       </c>
       <c r="D80" s="5" t="s">
@@ -4648,7 +4645,7 @@
       <c r="F80" s="5" t="s">
         <v>630</v>
       </c>
-      <c r="G80" s="32" t="s">
+      <c r="G80" s="28" t="s">
         <v>513</v>
       </c>
       <c r="H80" s="15" t="s">
@@ -4656,9 +4653,9 @@
       </c>
     </row>
     <row r="81" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A81" s="39"/>
-      <c r="B81" s="36"/>
-      <c r="C81" s="42"/>
+      <c r="A81" s="35"/>
+      <c r="B81" s="33"/>
+      <c r="C81" s="51"/>
       <c r="D81" s="5" t="s">
         <v>121</v>
       </c>
@@ -4668,19 +4665,19 @@
       <c r="F81" s="5" t="s">
         <v>631</v>
       </c>
-      <c r="G81" s="32"/>
+      <c r="G81" s="28"/>
       <c r="H81" s="15" t="s">
         <v>629</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A82" s="38">
+      <c r="A82" s="34">
         <v>17</v>
       </c>
-      <c r="B82" s="36" t="s">
+      <c r="B82" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C82" s="28" t="s">
+      <c r="C82" s="29" t="s">
         <v>6</v>
       </c>
       <c r="D82" s="5" t="s">
@@ -4692,7 +4689,7 @@
       <c r="F82" s="5" t="s">
         <v>590</v>
       </c>
-      <c r="G82" s="32" t="s">
+      <c r="G82" s="28" t="s">
         <v>625</v>
       </c>
       <c r="H82" s="15" t="s">
@@ -4700,9 +4697,9 @@
       </c>
     </row>
     <row r="83" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A83" s="39"/>
-      <c r="B83" s="36"/>
-      <c r="C83" s="28"/>
+      <c r="A83" s="35"/>
+      <c r="B83" s="33"/>
+      <c r="C83" s="29"/>
       <c r="D83" s="5" t="s">
         <v>40</v>
       </c>
@@ -4712,19 +4709,19 @@
       <c r="F83" s="5" t="s">
         <v>483</v>
       </c>
-      <c r="G83" s="32"/>
+      <c r="G83" s="28"/>
       <c r="H83" s="15" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="84" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A84" s="33">
+      <c r="A84" s="43">
         <v>18</v>
       </c>
-      <c r="B84" s="36" t="s">
+      <c r="B84" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C84" s="37" t="s">
+      <c r="C84" s="45" t="s">
         <v>6</v>
       </c>
       <c r="D84" s="5" t="s">
@@ -4736,7 +4733,7 @@
       <c r="F84" s="5" t="s">
         <v>471</v>
       </c>
-      <c r="G84" s="32" t="s">
+      <c r="G84" s="28" t="s">
         <v>482</v>
       </c>
       <c r="H84" s="15" t="s">
@@ -4744,9 +4741,9 @@
       </c>
     </row>
     <row r="85" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A85" s="34"/>
-      <c r="B85" s="36"/>
-      <c r="C85" s="37"/>
+      <c r="A85" s="44"/>
+      <c r="B85" s="33"/>
+      <c r="C85" s="45"/>
       <c r="D85" s="5" t="s">
         <v>42</v>
       </c>
@@ -4756,19 +4753,19 @@
       <c r="F85" s="5" t="s">
         <v>472</v>
       </c>
-      <c r="G85" s="32"/>
+      <c r="G85" s="28"/>
       <c r="H85" s="15" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="86" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A86" s="38">
+      <c r="A86" s="34">
         <v>19</v>
       </c>
-      <c r="B86" s="36" t="s">
+      <c r="B86" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C86" s="28" t="s">
+      <c r="C86" s="29" t="s">
         <v>6</v>
       </c>
       <c r="D86" s="5" t="s">
@@ -4780,15 +4777,15 @@
       <c r="F86" s="5" t="s">
         <v>635</v>
       </c>
-      <c r="G86" s="32"/>
+      <c r="G86" s="28"/>
       <c r="H86" s="15" t="s">
         <v>484</v>
       </c>
     </row>
     <row r="87" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A87" s="39"/>
-      <c r="B87" s="36"/>
-      <c r="C87" s="28"/>
+      <c r="A87" s="35"/>
+      <c r="B87" s="33"/>
+      <c r="C87" s="29"/>
       <c r="D87" s="5" t="s">
         <v>83</v>
       </c>
@@ -4798,19 +4795,19 @@
       <c r="F87" s="5" t="s">
         <v>634</v>
       </c>
-      <c r="G87" s="32"/>
+      <c r="G87" s="28"/>
       <c r="H87" s="15" t="s">
         <v>485</v>
       </c>
     </row>
     <row r="88" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A88" s="33">
+      <c r="A88" s="43">
         <v>20</v>
       </c>
-      <c r="B88" s="35" t="s">
+      <c r="B88" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C88" s="28" t="s">
+      <c r="C88" s="29" t="s">
         <v>6</v>
       </c>
       <c r="D88" s="5" t="s">
@@ -4822,7 +4819,7 @@
       <c r="F88" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="G88" s="32" t="s">
+      <c r="G88" s="28" t="s">
         <v>260</v>
       </c>
       <c r="H88" s="15" t="s">
@@ -4830,9 +4827,9 @@
       </c>
     </row>
     <row r="89" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A89" s="34"/>
-      <c r="B89" s="35"/>
-      <c r="C89" s="28"/>
+      <c r="A89" s="44"/>
+      <c r="B89" s="31"/>
+      <c r="C89" s="29"/>
       <c r="D89" s="5" t="s">
         <v>259</v>
       </c>
@@ -4842,19 +4839,19 @@
       <c r="F89" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="G89" s="32"/>
+      <c r="G89" s="28"/>
       <c r="H89" s="15" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="90" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A90" s="33">
+      <c r="A90" s="43">
         <v>21</v>
       </c>
-      <c r="B90" s="35" t="s">
+      <c r="B90" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C90" s="28" t="s">
+      <c r="C90" s="29" t="s">
         <v>6</v>
       </c>
       <c r="D90" s="5" t="s">
@@ -4866,7 +4863,7 @@
       <c r="F90" s="5" t="s">
         <v>520</v>
       </c>
-      <c r="G90" s="32" t="s">
+      <c r="G90" s="28" t="s">
         <v>524</v>
       </c>
       <c r="H90" s="15" t="s">
@@ -4874,9 +4871,9 @@
       </c>
     </row>
     <row r="91" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A91" s="34"/>
-      <c r="B91" s="35"/>
-      <c r="C91" s="28"/>
+      <c r="A91" s="44"/>
+      <c r="B91" s="31"/>
+      <c r="C91" s="29"/>
       <c r="D91" s="5" t="s">
         <v>127</v>
       </c>
@@ -4886,19 +4883,19 @@
       <c r="F91" s="5" t="s">
         <v>521</v>
       </c>
-      <c r="G91" s="32"/>
+      <c r="G91" s="28"/>
       <c r="H91" s="15" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="92" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A92" s="38">
+      <c r="A92" s="34">
         <v>22</v>
       </c>
-      <c r="B92" s="35" t="s">
+      <c r="B92" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C92" s="28" t="s">
+      <c r="C92" s="29" t="s">
         <v>6</v>
       </c>
       <c r="D92" s="5" t="s">
@@ -4910,7 +4907,7 @@
       <c r="F92" s="5" t="s">
         <v>490</v>
       </c>
-      <c r="G92" s="32" t="s">
+      <c r="G92" s="28" t="s">
         <v>486</v>
       </c>
       <c r="H92" s="15" t="s">
@@ -4918,9 +4915,9 @@
       </c>
     </row>
     <row r="93" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A93" s="39"/>
-      <c r="B93" s="35"/>
-      <c r="C93" s="28"/>
+      <c r="A93" s="35"/>
+      <c r="B93" s="31"/>
+      <c r="C93" s="29"/>
       <c r="D93" s="5" t="s">
         <v>176</v>
       </c>
@@ -4930,19 +4927,19 @@
       <c r="F93" s="5" t="s">
         <v>491</v>
       </c>
-      <c r="G93" s="32"/>
+      <c r="G93" s="28"/>
       <c r="H93" s="15" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="94" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A94" s="38">
+      <c r="A94" s="34">
         <v>23</v>
       </c>
-      <c r="B94" s="35" t="s">
+      <c r="B94" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C94" s="28" t="s">
+      <c r="C94" s="29" t="s">
         <v>6</v>
       </c>
       <c r="D94" s="5" t="s">
@@ -4954,7 +4951,7 @@
       <c r="F94" s="5" t="s">
         <v>615</v>
       </c>
-      <c r="G94" s="32" t="s">
+      <c r="G94" s="28" t="s">
         <v>275</v>
       </c>
       <c r="H94" s="15" t="s">
@@ -4962,9 +4959,9 @@
       </c>
     </row>
     <row r="95" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A95" s="39"/>
-      <c r="B95" s="35"/>
-      <c r="C95" s="28"/>
+      <c r="A95" s="35"/>
+      <c r="B95" s="31"/>
+      <c r="C95" s="29"/>
       <c r="D95" s="5" t="s">
         <v>31</v>
       </c>
@@ -4974,19 +4971,19 @@
       <c r="F95" s="5" t="s">
         <v>613</v>
       </c>
-      <c r="G95" s="32"/>
+      <c r="G95" s="28"/>
       <c r="H95" s="15" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="96" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A96" s="33">
+      <c r="A96" s="43">
         <v>24</v>
       </c>
-      <c r="B96" s="35" t="s">
+      <c r="B96" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C96" s="28" t="s">
+      <c r="C96" s="29" t="s">
         <v>6</v>
       </c>
       <c r="D96" s="5" t="s">
@@ -4998,7 +4995,7 @@
       <c r="F96" s="5" t="s">
         <v>518</v>
       </c>
-      <c r="G96" s="32" t="s">
+      <c r="G96" s="28" t="s">
         <v>198</v>
       </c>
       <c r="H96" s="15" t="s">
@@ -5006,9 +5003,9 @@
       </c>
     </row>
     <row r="97" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A97" s="34"/>
-      <c r="B97" s="35"/>
-      <c r="C97" s="28"/>
+      <c r="A97" s="44"/>
+      <c r="B97" s="31"/>
+      <c r="C97" s="29"/>
       <c r="D97" s="5" t="s">
         <v>166</v>
       </c>
@@ -5018,19 +5015,19 @@
       <c r="F97" s="5" t="s">
         <v>519</v>
       </c>
-      <c r="G97" s="32"/>
+      <c r="G97" s="28"/>
       <c r="H97" s="15" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="98" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A98" s="38">
+      <c r="A98" s="34">
         <v>25</v>
       </c>
-      <c r="B98" s="40" t="s">
+      <c r="B98" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C98" s="28" t="s">
+      <c r="C98" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D98" s="5" t="s">
@@ -5042,15 +5039,15 @@
       <c r="F98" s="5" t="s">
         <v>650</v>
       </c>
-      <c r="G98" s="32"/>
+      <c r="G98" s="28"/>
       <c r="H98" s="15" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="99" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A99" s="39"/>
-      <c r="B99" s="40"/>
-      <c r="C99" s="28"/>
+      <c r="A99" s="35"/>
+      <c r="B99" s="30"/>
+      <c r="C99" s="29"/>
       <c r="D99" s="5" t="s">
         <v>146</v>
       </c>
@@ -5060,19 +5057,19 @@
       <c r="F99" s="5" t="s">
         <v>651</v>
       </c>
-      <c r="G99" s="32"/>
+      <c r="G99" s="28"/>
       <c r="H99" s="15" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="100" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A100" s="33">
+      <c r="A100" s="43">
         <v>26</v>
       </c>
-      <c r="B100" s="40" t="s">
+      <c r="B100" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C100" s="37" t="s">
+      <c r="C100" s="45" t="s">
         <v>14</v>
       </c>
       <c r="D100" s="5" t="s">
@@ -5084,15 +5081,15 @@
       <c r="F100" s="5" t="s">
         <v>636</v>
       </c>
-      <c r="G100" s="32"/>
+      <c r="G100" s="28"/>
       <c r="H100" s="15" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="101" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A101" s="34"/>
-      <c r="B101" s="40"/>
-      <c r="C101" s="37"/>
+      <c r="A101" s="44"/>
+      <c r="B101" s="30"/>
+      <c r="C101" s="45"/>
       <c r="D101" s="5" t="s">
         <v>158</v>
       </c>
@@ -5102,19 +5099,19 @@
       <c r="F101" s="5" t="s">
         <v>637</v>
       </c>
-      <c r="G101" s="32"/>
+      <c r="G101" s="28"/>
       <c r="H101" s="15" t="s">
         <v>378</v>
       </c>
     </row>
     <row r="102" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A102" s="38">
+      <c r="A102" s="34">
         <v>27</v>
       </c>
-      <c r="B102" s="40" t="s">
+      <c r="B102" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C102" s="28" t="s">
+      <c r="C102" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D102" s="5" t="s">
@@ -5126,15 +5123,15 @@
       <c r="F102" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="G102" s="32"/>
+      <c r="G102" s="28"/>
       <c r="H102" s="15" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="103" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A103" s="39"/>
-      <c r="B103" s="40"/>
-      <c r="C103" s="28"/>
+      <c r="A103" s="35"/>
+      <c r="B103" s="30"/>
+      <c r="C103" s="29"/>
       <c r="D103" s="5" t="s">
         <v>45</v>
       </c>
@@ -5144,19 +5141,19 @@
       <c r="F103" s="5" t="s">
         <v>642</v>
       </c>
-      <c r="G103" s="32"/>
+      <c r="G103" s="28"/>
       <c r="H103" s="15" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="104" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A104" s="38">
+      <c r="A104" s="34">
         <v>28</v>
       </c>
-      <c r="B104" s="40" t="s">
+      <c r="B104" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C104" s="28" t="s">
+      <c r="C104" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D104" s="5" t="s">
@@ -5168,15 +5165,15 @@
       <c r="F104" s="5" t="s">
         <v>559</v>
       </c>
-      <c r="G104" s="32"/>
+      <c r="G104" s="28"/>
       <c r="H104" s="15" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="105" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A105" s="39"/>
-      <c r="B105" s="40"/>
-      <c r="C105" s="28"/>
+      <c r="A105" s="35"/>
+      <c r="B105" s="30"/>
+      <c r="C105" s="29"/>
       <c r="D105" s="5" t="s">
         <v>67</v>
       </c>
@@ -5186,19 +5183,19 @@
       <c r="F105" s="5" t="s">
         <v>560</v>
       </c>
-      <c r="G105" s="32"/>
+      <c r="G105" s="28"/>
       <c r="H105" s="15" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="106" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A106" s="33">
+      <c r="A106" s="43">
         <v>29</v>
       </c>
-      <c r="B106" s="40" t="s">
+      <c r="B106" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C106" s="28" t="s">
+      <c r="C106" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D106" s="5" t="s">
@@ -5210,7 +5207,7 @@
       <c r="F106" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="G106" s="32" t="s">
+      <c r="G106" s="28" t="s">
         <v>510</v>
       </c>
       <c r="H106" s="15" t="s">
@@ -5218,9 +5215,9 @@
       </c>
     </row>
     <row r="107" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A107" s="34"/>
-      <c r="B107" s="40"/>
-      <c r="C107" s="28"/>
+      <c r="A107" s="44"/>
+      <c r="B107" s="30"/>
+      <c r="C107" s="29"/>
       <c r="D107" s="5" t="s">
         <v>152</v>
       </c>
@@ -5230,19 +5227,19 @@
       <c r="F107" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="G107" s="32"/>
+      <c r="G107" s="28"/>
       <c r="H107" s="15" t="s">
         <v>381</v>
       </c>
     </row>
     <row r="108" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A108" s="38">
+      <c r="A108" s="34">
         <v>30</v>
       </c>
-      <c r="B108" s="40" t="s">
+      <c r="B108" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C108" s="28" t="s">
+      <c r="C108" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D108" s="5" t="s">
@@ -5254,7 +5251,7 @@
       <c r="F108" s="5" t="s">
         <v>603</v>
       </c>
-      <c r="G108" s="32" t="s">
+      <c r="G108" s="28" t="s">
         <v>217</v>
       </c>
       <c r="H108" s="15" t="s">
@@ -5262,9 +5259,9 @@
       </c>
     </row>
     <row r="109" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A109" s="39"/>
-      <c r="B109" s="40"/>
-      <c r="C109" s="28"/>
+      <c r="A109" s="35"/>
+      <c r="B109" s="30"/>
+      <c r="C109" s="29"/>
       <c r="D109" s="5" t="s">
         <v>47</v>
       </c>
@@ -5274,19 +5271,19 @@
       <c r="F109" s="5" t="s">
         <v>604</v>
       </c>
-      <c r="G109" s="32"/>
+      <c r="G109" s="28"/>
       <c r="H109" s="15" t="s">
         <v>382</v>
       </c>
     </row>
     <row r="110" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A110" s="38">
+      <c r="A110" s="34">
         <v>31</v>
       </c>
-      <c r="B110" s="46" t="s">
+      <c r="B110" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="C110" s="43" t="s">
+      <c r="C110" s="32" t="s">
         <v>14</v>
       </c>
       <c r="D110" s="5" t="s">
@@ -5298,7 +5295,7 @@
       <c r="F110" s="5" t="s">
         <v>622</v>
       </c>
-      <c r="G110" s="48" t="s">
+      <c r="G110" s="46" t="s">
         <v>254</v>
       </c>
       <c r="H110" s="15" t="s">
@@ -5306,9 +5303,9 @@
       </c>
     </row>
     <row r="111" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A111" s="39"/>
-      <c r="B111" s="47"/>
-      <c r="C111" s="43"/>
+      <c r="A111" s="35"/>
+      <c r="B111" s="42"/>
+      <c r="C111" s="32"/>
       <c r="D111" s="5" t="s">
         <v>188</v>
       </c>
@@ -5318,19 +5315,19 @@
       <c r="F111" s="5" t="s">
         <v>623</v>
       </c>
-      <c r="G111" s="49"/>
+      <c r="G111" s="47"/>
       <c r="H111" s="15" t="s">
         <v>383</v>
       </c>
     </row>
     <row r="112" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A112" s="33">
+      <c r="A112" s="43">
         <v>32</v>
       </c>
-      <c r="B112" s="40" t="s">
+      <c r="B112" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C112" s="37" t="s">
+      <c r="C112" s="45" t="s">
         <v>14</v>
       </c>
       <c r="D112" s="5" t="s">
@@ -5342,15 +5339,15 @@
       <c r="F112" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="G112" s="32"/>
+      <c r="G112" s="28"/>
       <c r="H112" s="15" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="113" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A113" s="34"/>
-      <c r="B113" s="40"/>
-      <c r="C113" s="37"/>
+      <c r="A113" s="44"/>
+      <c r="B113" s="30"/>
+      <c r="C113" s="45"/>
       <c r="D113" s="5" t="s">
         <v>52</v>
       </c>
@@ -5360,19 +5357,19 @@
       <c r="F113" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="G113" s="32"/>
+      <c r="G113" s="28"/>
       <c r="H113" s="15" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="114" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A114" s="38">
+      <c r="A114" s="34">
         <v>33</v>
       </c>
-      <c r="B114" s="40" t="s">
+      <c r="B114" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C114" s="28" t="s">
+      <c r="C114" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D114" s="5" t="s">
@@ -5384,15 +5381,15 @@
       <c r="F114" s="5" t="s">
         <v>541</v>
       </c>
-      <c r="G114" s="32"/>
+      <c r="G114" s="28"/>
       <c r="H114" s="15" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="115" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A115" s="39"/>
-      <c r="B115" s="40"/>
-      <c r="C115" s="28"/>
+      <c r="A115" s="35"/>
+      <c r="B115" s="30"/>
+      <c r="C115" s="29"/>
       <c r="D115" s="5" t="s">
         <v>133</v>
       </c>
@@ -5402,19 +5399,19 @@
       <c r="F115" s="5" t="s">
         <v>542</v>
       </c>
-      <c r="G115" s="32"/>
+      <c r="G115" s="28"/>
       <c r="H115" s="15" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="116" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A116" s="38">
+      <c r="A116" s="34">
         <v>34</v>
       </c>
-      <c r="B116" s="40" t="s">
+      <c r="B116" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C116" s="28" t="s">
+      <c r="C116" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D116" s="5" t="s">
@@ -5426,17 +5423,17 @@
       <c r="F116" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="G116" s="32" t="s">
-        <v>217</v>
+      <c r="G116" s="28" t="s">
+        <v>667</v>
       </c>
       <c r="H116" s="15" t="s">
         <v>428</v>
       </c>
     </row>
     <row r="117" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A117" s="39"/>
-      <c r="B117" s="40"/>
-      <c r="C117" s="28"/>
+      <c r="A117" s="35"/>
+      <c r="B117" s="30"/>
+      <c r="C117" s="29"/>
       <c r="D117" s="5" t="s">
         <v>75</v>
       </c>
@@ -5446,19 +5443,19 @@
       <c r="F117" s="5" t="s">
         <v>601</v>
       </c>
-      <c r="G117" s="32"/>
+      <c r="G117" s="28"/>
       <c r="H117" s="15" t="s">
         <v>429</v>
       </c>
     </row>
     <row r="118" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A118" s="38">
+      <c r="A118" s="34">
         <v>35</v>
       </c>
-      <c r="B118" s="40" t="s">
+      <c r="B118" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C118" s="28" t="s">
+      <c r="C118" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D118" s="5" t="s">
@@ -5470,17 +5467,17 @@
       <c r="F118" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="G118" s="32" t="s">
-        <v>217</v>
+      <c r="G118" s="28" t="s">
+        <v>666</v>
       </c>
       <c r="H118" s="15" t="s">
         <v>624</v>
       </c>
     </row>
     <row r="119" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A119" s="39"/>
-      <c r="B119" s="40"/>
-      <c r="C119" s="28"/>
+      <c r="A119" s="35"/>
+      <c r="B119" s="30"/>
+      <c r="C119" s="29"/>
       <c r="D119" s="5" t="s">
         <v>77</v>
       </c>
@@ -5490,19 +5487,19 @@
       <c r="F119" s="5" t="s">
         <v>600</v>
       </c>
-      <c r="G119" s="32"/>
+      <c r="G119" s="28"/>
       <c r="H119" s="15" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="120" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A120" s="38">
+      <c r="A120" s="34">
         <v>36</v>
       </c>
-      <c r="B120" s="40" t="s">
+      <c r="B120" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C120" s="28" t="s">
+      <c r="C120" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D120" s="5" t="s">
@@ -5514,7 +5511,7 @@
       <c r="F120" s="5" t="s">
         <v>643</v>
       </c>
-      <c r="G120" s="32" t="s">
+      <c r="G120" s="28" t="s">
         <v>245</v>
       </c>
       <c r="H120" s="15" t="s">
@@ -5522,9 +5519,9 @@
       </c>
     </row>
     <row r="121" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A121" s="39"/>
-      <c r="B121" s="40"/>
-      <c r="C121" s="28"/>
+      <c r="A121" s="35"/>
+      <c r="B121" s="30"/>
+      <c r="C121" s="29"/>
       <c r="D121" s="5" t="s">
         <v>119</v>
       </c>
@@ -5534,19 +5531,19 @@
       <c r="F121" s="5" t="s">
         <v>644</v>
       </c>
-      <c r="G121" s="32"/>
+      <c r="G121" s="28"/>
       <c r="H121" s="15" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="122" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A122" s="38">
+      <c r="A122" s="34">
         <v>37</v>
       </c>
-      <c r="B122" s="46" t="s">
+      <c r="B122" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="C122" s="28" t="s">
+      <c r="C122" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D122" s="5" t="s">
@@ -5558,15 +5555,15 @@
       <c r="F122" s="5" t="s">
         <v>657</v>
       </c>
-      <c r="G122" s="32"/>
+      <c r="G122" s="28"/>
       <c r="H122" s="15" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="123" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A123" s="39"/>
-      <c r="B123" s="47"/>
-      <c r="C123" s="28"/>
+      <c r="A123" s="35"/>
+      <c r="B123" s="42"/>
+      <c r="C123" s="29"/>
       <c r="D123" s="5" t="s">
         <v>180</v>
       </c>
@@ -5576,19 +5573,19 @@
       <c r="F123" s="5" t="s">
         <v>657</v>
       </c>
-      <c r="G123" s="32"/>
+      <c r="G123" s="28"/>
       <c r="H123" s="15" t="s">
         <v>388</v>
       </c>
     </row>
     <row r="124" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A124" s="38">
+      <c r="A124" s="34">
         <v>38</v>
       </c>
-      <c r="B124" s="46" t="s">
+      <c r="B124" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="C124" s="28" t="s">
+      <c r="C124" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D124" s="5" t="s">
@@ -5600,15 +5597,15 @@
       <c r="F124" s="5" t="s">
         <v>478</v>
       </c>
-      <c r="G124" s="32"/>
+      <c r="G124" s="28"/>
       <c r="H124" s="15" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="125" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A125" s="39"/>
-      <c r="B125" s="47"/>
-      <c r="C125" s="28"/>
+      <c r="A125" s="35"/>
+      <c r="B125" s="42"/>
+      <c r="C125" s="29"/>
       <c r="D125" s="5" t="s">
         <v>54</v>
       </c>
@@ -5618,19 +5615,19 @@
       <c r="F125" s="5" t="s">
         <v>479</v>
       </c>
-      <c r="G125" s="32"/>
+      <c r="G125" s="28"/>
       <c r="H125" s="15" t="s">
         <v>392</v>
       </c>
     </row>
     <row r="126" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A126" s="38">
+      <c r="A126" s="34">
         <v>39</v>
       </c>
-      <c r="B126" s="46" t="s">
+      <c r="B126" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="C126" s="28" t="s">
+      <c r="C126" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D126" s="5" t="s">
@@ -5642,7 +5639,7 @@
       <c r="F126" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="G126" s="32" t="s">
+      <c r="G126" s="28" t="s">
         <v>645</v>
       </c>
       <c r="H126" s="15" t="s">
@@ -5650,9 +5647,9 @@
       </c>
     </row>
     <row r="127" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A127" s="39"/>
-      <c r="B127" s="47"/>
-      <c r="C127" s="28"/>
+      <c r="A127" s="35"/>
+      <c r="B127" s="42"/>
+      <c r="C127" s="29"/>
       <c r="D127" s="5" t="s">
         <v>131</v>
       </c>
@@ -5662,19 +5659,19 @@
       <c r="F127" s="5" t="s">
         <v>551</v>
       </c>
-      <c r="G127" s="32"/>
+      <c r="G127" s="28"/>
       <c r="H127" s="15" t="s">
         <v>550</v>
       </c>
     </row>
     <row r="128" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A128" s="33">
+      <c r="A128" s="43">
         <v>40</v>
       </c>
-      <c r="B128" s="46" t="s">
+      <c r="B128" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="C128" s="28" t="s">
+      <c r="C128" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D128" s="5" t="s">
@@ -5686,15 +5683,15 @@
       <c r="F128" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="G128" s="32"/>
+      <c r="G128" s="28"/>
       <c r="H128" s="15" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="129" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A129" s="34"/>
-      <c r="B129" s="47"/>
-      <c r="C129" s="28"/>
+      <c r="A129" s="44"/>
+      <c r="B129" s="42"/>
+      <c r="C129" s="29"/>
       <c r="D129" s="5" t="s">
         <v>79</v>
       </c>
@@ -5704,19 +5701,19 @@
       <c r="F129" s="5" t="s">
         <v>487</v>
       </c>
-      <c r="G129" s="32"/>
+      <c r="G129" s="28"/>
       <c r="H129" s="15" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="130" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A130" s="38">
+      <c r="A130" s="34">
         <v>41</v>
       </c>
-      <c r="B130" s="46" t="s">
+      <c r="B130" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="C130" s="43" t="s">
+      <c r="C130" s="32" t="s">
         <v>14</v>
       </c>
       <c r="D130" s="5" t="s">
@@ -5728,15 +5725,15 @@
       <c r="F130" s="5" t="s">
         <v>632</v>
       </c>
-      <c r="G130" s="32"/>
+      <c r="G130" s="28"/>
       <c r="H130" s="15" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="131" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A131" s="39"/>
-      <c r="B131" s="47"/>
-      <c r="C131" s="43"/>
+      <c r="A131" s="35"/>
+      <c r="B131" s="42"/>
+      <c r="C131" s="32"/>
       <c r="D131" s="5" t="s">
         <v>65</v>
       </c>
@@ -5746,19 +5743,19 @@
       <c r="F131" s="5" t="s">
         <v>633</v>
       </c>
-      <c r="G131" s="32"/>
+      <c r="G131" s="28"/>
       <c r="H131" s="15" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="132" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A132" s="38">
+      <c r="A132" s="34">
         <v>42</v>
       </c>
-      <c r="B132" s="36" t="s">
+      <c r="B132" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C132" s="28" t="s">
+      <c r="C132" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D132" s="5" t="s">
@@ -5770,15 +5767,15 @@
       <c r="F132" s="5" t="s">
         <v>555</v>
       </c>
-      <c r="G132" s="32"/>
+      <c r="G132" s="28"/>
       <c r="H132" s="15" t="s">
         <v>553</v>
       </c>
     </row>
     <row r="133" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A133" s="39"/>
-      <c r="B133" s="36"/>
-      <c r="C133" s="28"/>
+      <c r="A133" s="35"/>
+      <c r="B133" s="33"/>
+      <c r="C133" s="29"/>
       <c r="D133" s="5" t="s">
         <v>51</v>
       </c>
@@ -5788,19 +5785,19 @@
       <c r="F133" s="5" t="s">
         <v>552</v>
       </c>
-      <c r="G133" s="32"/>
+      <c r="G133" s="28"/>
       <c r="H133" s="15" t="s">
         <v>554</v>
       </c>
     </row>
     <row r="134" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A134" s="38">
+      <c r="A134" s="34">
         <v>43</v>
       </c>
-      <c r="B134" s="36" t="s">
+      <c r="B134" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C134" s="28" t="s">
+      <c r="C134" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D134" s="5" t="s">
@@ -5812,15 +5809,15 @@
       <c r="F134" s="5" t="s">
         <v>663</v>
       </c>
-      <c r="G134" s="32"/>
+      <c r="G134" s="28"/>
       <c r="H134" s="15" t="s">
         <v>620</v>
       </c>
     </row>
     <row r="135" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A135" s="39"/>
-      <c r="B135" s="36"/>
-      <c r="C135" s="28"/>
+      <c r="A135" s="35"/>
+      <c r="B135" s="33"/>
+      <c r="C135" s="29"/>
       <c r="D135" s="5" t="s">
         <v>619</v>
       </c>
@@ -5830,19 +5827,19 @@
       <c r="F135" s="5" t="s">
         <v>664</v>
       </c>
-      <c r="G135" s="32"/>
+      <c r="G135" s="28"/>
       <c r="H135" s="15" t="s">
         <v>621</v>
       </c>
     </row>
     <row r="136" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A136" s="38">
+      <c r="A136" s="34">
         <v>44</v>
       </c>
-      <c r="B136" s="36" t="s">
+      <c r="B136" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C136" s="28" t="s">
+      <c r="C136" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D136" s="5" t="s">
@@ -5854,15 +5851,15 @@
       <c r="F136" s="5" t="s">
         <v>473</v>
       </c>
-      <c r="G136" s="32"/>
+      <c r="G136" s="28"/>
       <c r="H136" s="15" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="137" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A137" s="39"/>
-      <c r="B137" s="36"/>
-      <c r="C137" s="28"/>
+      <c r="A137" s="35"/>
+      <c r="B137" s="33"/>
+      <c r="C137" s="29"/>
       <c r="D137" s="5" t="s">
         <v>49</v>
       </c>
@@ -5872,19 +5869,19 @@
       <c r="F137" s="5" t="s">
         <v>474</v>
       </c>
-      <c r="G137" s="32"/>
+      <c r="G137" s="28"/>
       <c r="H137" s="15" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="138" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A138" s="33">
+      <c r="A138" s="43">
         <v>45</v>
       </c>
-      <c r="B138" s="36" t="s">
+      <c r="B138" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C138" s="37" t="s">
+      <c r="C138" s="45" t="s">
         <v>14</v>
       </c>
       <c r="D138" s="5" t="s">
@@ -5896,15 +5893,15 @@
       <c r="F138" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="G138" s="32"/>
+      <c r="G138" s="28"/>
       <c r="H138" s="15" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="139" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A139" s="34"/>
-      <c r="B139" s="36"/>
-      <c r="C139" s="37"/>
+      <c r="A139" s="44"/>
+      <c r="B139" s="33"/>
+      <c r="C139" s="45"/>
       <c r="D139" s="5" t="s">
         <v>178</v>
       </c>
@@ -5914,19 +5911,19 @@
       <c r="F139" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="G139" s="32"/>
+      <c r="G139" s="28"/>
       <c r="H139" s="15" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="140" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A140" s="33">
+      <c r="A140" s="43">
         <v>46</v>
       </c>
-      <c r="B140" s="36" t="s">
+      <c r="B140" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C140" s="28" t="s">
+      <c r="C140" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D140" s="5" t="s">
@@ -5938,7 +5935,7 @@
       <c r="F140" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="G140" s="32" t="s">
+      <c r="G140" s="28" t="s">
         <v>210</v>
       </c>
       <c r="H140" s="15" t="s">
@@ -5946,9 +5943,9 @@
       </c>
     </row>
     <row r="141" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A141" s="34"/>
-      <c r="B141" s="36"/>
-      <c r="C141" s="28"/>
+      <c r="A141" s="44"/>
+      <c r="B141" s="33"/>
+      <c r="C141" s="29"/>
       <c r="D141" s="5" t="s">
         <v>233</v>
       </c>
@@ -5958,19 +5955,19 @@
       <c r="F141" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="G141" s="32"/>
+      <c r="G141" s="28"/>
       <c r="H141" s="15" t="s">
         <v>390</v>
       </c>
     </row>
     <row r="142" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A142" s="33">
+      <c r="A142" s="43">
         <v>47</v>
       </c>
-      <c r="B142" s="36" t="s">
+      <c r="B142" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C142" s="28" t="s">
+      <c r="C142" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D142" s="5" t="s">
@@ -5982,7 +5979,7 @@
       <c r="F142" s="5" t="s">
         <v>475</v>
       </c>
-      <c r="G142" s="32" t="s">
+      <c r="G142" s="28" t="s">
         <v>538</v>
       </c>
       <c r="H142" s="15" t="s">
@@ -5990,9 +5987,9 @@
       </c>
     </row>
     <row r="143" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A143" s="34"/>
-      <c r="B143" s="36"/>
-      <c r="C143" s="28"/>
+      <c r="A143" s="44"/>
+      <c r="B143" s="33"/>
+      <c r="C143" s="29"/>
       <c r="D143" s="5" t="s">
         <v>165</v>
       </c>
@@ -6002,19 +5999,19 @@
       <c r="F143" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="G143" s="32"/>
+      <c r="G143" s="28"/>
       <c r="H143" s="15" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="144" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A144" s="38">
+      <c r="A144" s="34">
         <v>48</v>
       </c>
-      <c r="B144" s="36" t="s">
+      <c r="B144" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C144" s="28" t="s">
+      <c r="C144" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D144" s="5" t="s">
@@ -6026,15 +6023,15 @@
       <c r="F144" s="5" t="s">
         <v>477</v>
       </c>
-      <c r="G144" s="32"/>
+      <c r="G144" s="28"/>
       <c r="H144" s="15" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="145" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A145" s="39"/>
-      <c r="B145" s="36"/>
-      <c r="C145" s="28"/>
+      <c r="A145" s="35"/>
+      <c r="B145" s="33"/>
+      <c r="C145" s="29"/>
       <c r="D145" s="5" t="s">
         <v>55</v>
       </c>
@@ -6044,19 +6041,19 @@
       <c r="F145" s="5" t="s">
         <v>477</v>
       </c>
-      <c r="G145" s="32"/>
+      <c r="G145" s="28"/>
       <c r="H145" s="15" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="146" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A146" s="33">
+      <c r="A146" s="43">
         <v>49</v>
       </c>
-      <c r="B146" s="36" t="s">
+      <c r="B146" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C146" s="37" t="s">
+      <c r="C146" s="45" t="s">
         <v>14</v>
       </c>
       <c r="D146" s="5" t="s">
@@ -6068,7 +6065,7 @@
       <c r="F146" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="G146" s="32" t="s">
+      <c r="G146" s="28" t="s">
         <v>538</v>
       </c>
       <c r="H146" s="15" t="s">
@@ -6076,9 +6073,9 @@
       </c>
     </row>
     <row r="147" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A147" s="34"/>
-      <c r="B147" s="36"/>
-      <c r="C147" s="37"/>
+      <c r="A147" s="44"/>
+      <c r="B147" s="33"/>
+      <c r="C147" s="45"/>
       <c r="D147" s="5" t="s">
         <v>57</v>
       </c>
@@ -6088,19 +6085,19 @@
       <c r="F147" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="G147" s="32"/>
+      <c r="G147" s="28"/>
       <c r="H147" s="15" t="s">
         <v>425</v>
       </c>
     </row>
     <row r="148" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A148" s="38">
+      <c r="A148" s="34">
         <v>50</v>
       </c>
-      <c r="B148" s="36" t="s">
+      <c r="B148" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C148" s="43" t="s">
+      <c r="C148" s="32" t="s">
         <v>14</v>
       </c>
       <c r="D148" s="5" t="s">
@@ -6112,15 +6109,15 @@
       <c r="F148" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="G148" s="32"/>
+      <c r="G148" s="28"/>
       <c r="H148" s="15" t="s">
         <v>500</v>
       </c>
     </row>
     <row r="149" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A149" s="39"/>
-      <c r="B149" s="36"/>
-      <c r="C149" s="43"/>
+      <c r="A149" s="35"/>
+      <c r="B149" s="33"/>
+      <c r="C149" s="32"/>
       <c r="D149" s="5" t="s">
         <v>59</v>
       </c>
@@ -6130,19 +6127,19 @@
       <c r="F149" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="G149" s="32"/>
+      <c r="G149" s="28"/>
       <c r="H149" s="15" t="s">
         <v>501</v>
       </c>
     </row>
     <row r="150" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A150" s="38">
+      <c r="A150" s="34">
         <v>51</v>
       </c>
-      <c r="B150" s="36" t="s">
+      <c r="B150" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C150" s="28" t="s">
+      <c r="C150" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D150" s="5" t="s">
@@ -6154,15 +6151,15 @@
       <c r="F150" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="G150" s="32"/>
+      <c r="G150" s="28"/>
       <c r="H150" s="15" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="151" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A151" s="39"/>
-      <c r="B151" s="36"/>
-      <c r="C151" s="28"/>
+      <c r="A151" s="35"/>
+      <c r="B151" s="33"/>
+      <c r="C151" s="29"/>
       <c r="D151" s="5" t="s">
         <v>182</v>
       </c>
@@ -6172,19 +6169,19 @@
       <c r="F151" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="G151" s="32"/>
+      <c r="G151" s="28"/>
       <c r="H151" s="15" t="s">
         <v>394</v>
       </c>
     </row>
     <row r="152" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A152" s="38">
+      <c r="A152" s="34">
         <v>52</v>
       </c>
-      <c r="B152" s="36" t="s">
+      <c r="B152" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C152" s="28" t="s">
+      <c r="C152" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D152" s="5" t="s">
@@ -6196,15 +6193,15 @@
       <c r="F152" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="G152" s="32"/>
+      <c r="G152" s="28"/>
       <c r="H152" s="15" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="153" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A153" s="39"/>
-      <c r="B153" s="36"/>
-      <c r="C153" s="28"/>
+      <c r="A153" s="35"/>
+      <c r="B153" s="33"/>
+      <c r="C153" s="29"/>
       <c r="D153" s="5" t="s">
         <v>191</v>
       </c>
@@ -6214,19 +6211,19 @@
       <c r="F153" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="G153" s="32"/>
+      <c r="G153" s="28"/>
       <c r="H153" s="15" t="s">
         <v>427</v>
       </c>
     </row>
     <row r="154" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A154" s="33">
+      <c r="A154" s="43">
         <v>53</v>
       </c>
-      <c r="B154" s="36" t="s">
+      <c r="B154" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C154" s="28" t="s">
+      <c r="C154" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D154" s="5" t="s">
@@ -6238,7 +6235,7 @@
       <c r="F154" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="G154" s="32" t="s">
+      <c r="G154" s="28" t="s">
         <v>602</v>
       </c>
       <c r="H154" s="15" t="s">
@@ -6246,9 +6243,9 @@
       </c>
     </row>
     <row r="155" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A155" s="34"/>
-      <c r="B155" s="36"/>
-      <c r="C155" s="28"/>
+      <c r="A155" s="44"/>
+      <c r="B155" s="33"/>
+      <c r="C155" s="29"/>
       <c r="D155" s="5" t="s">
         <v>63</v>
       </c>
@@ -6258,19 +6255,19 @@
       <c r="F155" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="G155" s="32"/>
+      <c r="G155" s="28"/>
       <c r="H155" s="15" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="156" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A156" s="33">
+      <c r="A156" s="43">
         <v>54</v>
       </c>
-      <c r="B156" s="36" t="s">
+      <c r="B156" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C156" s="28" t="s">
+      <c r="C156" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D156" s="5" t="s">
@@ -6282,15 +6279,15 @@
       <c r="F156" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="G156" s="32"/>
+      <c r="G156" s="28"/>
       <c r="H156" s="15" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="157" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A157" s="34"/>
-      <c r="B157" s="36"/>
-      <c r="C157" s="28"/>
+      <c r="A157" s="44"/>
+      <c r="B157" s="33"/>
+      <c r="C157" s="29"/>
       <c r="D157" s="5" t="s">
         <v>160</v>
       </c>
@@ -6300,19 +6297,19 @@
       <c r="F157" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="G157" s="32"/>
+      <c r="G157" s="28"/>
       <c r="H157" s="15" t="s">
         <v>396</v>
       </c>
     </row>
     <row r="158" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A158" s="33">
+      <c r="A158" s="43">
         <v>55</v>
       </c>
-      <c r="B158" s="36" t="s">
+      <c r="B158" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C158" s="28" t="s">
+      <c r="C158" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D158" s="5" t="s">
@@ -6324,15 +6321,15 @@
       <c r="F158" s="5" t="s">
         <v>557</v>
       </c>
-      <c r="G158" s="32"/>
+      <c r="G158" s="28"/>
       <c r="H158" s="15" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="159" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A159" s="34"/>
-      <c r="B159" s="36"/>
-      <c r="C159" s="28"/>
+      <c r="A159" s="44"/>
+      <c r="B159" s="33"/>
+      <c r="C159" s="29"/>
       <c r="D159" s="5" t="s">
         <v>162</v>
       </c>
@@ -6342,19 +6339,19 @@
       <c r="F159" s="5" t="s">
         <v>558</v>
       </c>
-      <c r="G159" s="32"/>
+      <c r="G159" s="28"/>
       <c r="H159" s="15" t="s">
         <v>397</v>
       </c>
     </row>
     <row r="160" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A160" s="33">
+      <c r="A160" s="43">
         <v>56</v>
       </c>
-      <c r="B160" s="36" t="s">
+      <c r="B160" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C160" s="28" t="s">
+      <c r="C160" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D160" s="5" t="s">
@@ -6366,7 +6363,7 @@
       <c r="F160" s="5" t="s">
         <v>556</v>
       </c>
-      <c r="G160" s="32" t="s">
+      <c r="G160" s="28" t="s">
         <v>512</v>
       </c>
       <c r="H160" s="15" t="s">
@@ -6374,9 +6371,9 @@
       </c>
     </row>
     <row r="161" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A161" s="34"/>
-      <c r="B161" s="36"/>
-      <c r="C161" s="28"/>
+      <c r="A161" s="44"/>
+      <c r="B161" s="33"/>
+      <c r="C161" s="29"/>
       <c r="D161" s="5" t="s">
         <v>150</v>
       </c>
@@ -6386,19 +6383,19 @@
       <c r="F161" s="5" t="s">
         <v>556</v>
       </c>
-      <c r="G161" s="32"/>
+      <c r="G161" s="28"/>
       <c r="H161" s="15" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="162" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A162" s="33">
+      <c r="A162" s="43">
         <v>57</v>
       </c>
-      <c r="B162" s="36" t="s">
+      <c r="B162" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C162" s="28" t="s">
+      <c r="C162" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D162" s="5" t="s">
@@ -6410,7 +6407,7 @@
       <c r="F162" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="G162" s="32" t="s">
+      <c r="G162" s="28" t="s">
         <v>543</v>
       </c>
       <c r="H162" s="15" t="s">
@@ -6418,9 +6415,9 @@
       </c>
     </row>
     <row r="163" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A163" s="34"/>
-      <c r="B163" s="36"/>
-      <c r="C163" s="28"/>
+      <c r="A163" s="44"/>
+      <c r="B163" s="33"/>
+      <c r="C163" s="29"/>
       <c r="D163" s="5" t="s">
         <v>170</v>
       </c>
@@ -6430,19 +6427,19 @@
       <c r="F163" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="G163" s="32"/>
+      <c r="G163" s="28"/>
       <c r="H163" s="15" t="s">
         <v>400</v>
       </c>
     </row>
     <row r="164" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A164" s="33">
+      <c r="A164" s="43">
         <v>58</v>
       </c>
-      <c r="B164" s="36" t="s">
+      <c r="B164" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C164" s="37" t="s">
+      <c r="C164" s="45" t="s">
         <v>14</v>
       </c>
       <c r="D164" s="5" t="s">
@@ -6454,15 +6451,15 @@
       <c r="F164" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="G164" s="32"/>
+      <c r="G164" s="28"/>
       <c r="H164" s="15" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="165" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A165" s="34"/>
-      <c r="B165" s="36"/>
-      <c r="C165" s="37"/>
+      <c r="A165" s="44"/>
+      <c r="B165" s="33"/>
+      <c r="C165" s="45"/>
       <c r="D165" s="5" t="s">
         <v>172</v>
       </c>
@@ -6472,19 +6469,19 @@
       <c r="F165" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="G165" s="32"/>
+      <c r="G165" s="28"/>
       <c r="H165" s="15" t="s">
         <v>401</v>
       </c>
     </row>
     <row r="166" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A166" s="33">
+      <c r="A166" s="43">
         <v>59</v>
       </c>
-      <c r="B166" s="36" t="s">
+      <c r="B166" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C166" s="37" t="s">
+      <c r="C166" s="45" t="s">
         <v>14</v>
       </c>
       <c r="D166" s="5" t="s">
@@ -6496,7 +6493,7 @@
       <c r="F166" s="5" t="s">
         <v>638</v>
       </c>
-      <c r="G166" s="32" t="s">
+      <c r="G166" s="28" t="s">
         <v>192</v>
       </c>
       <c r="H166" s="15" t="s">
@@ -6504,9 +6501,9 @@
       </c>
     </row>
     <row r="167" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A167" s="34"/>
-      <c r="B167" s="36"/>
-      <c r="C167" s="37"/>
+      <c r="A167" s="44"/>
+      <c r="B167" s="33"/>
+      <c r="C167" s="45"/>
       <c r="D167" s="5" t="s">
         <v>142</v>
       </c>
@@ -6516,19 +6513,19 @@
       <c r="F167" s="5" t="s">
         <v>638</v>
       </c>
-      <c r="G167" s="32"/>
+      <c r="G167" s="28"/>
       <c r="H167" s="15" t="s">
         <v>402</v>
       </c>
     </row>
     <row r="168" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A168" s="33">
+      <c r="A168" s="43">
         <v>60</v>
       </c>
-      <c r="B168" s="36" t="s">
+      <c r="B168" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C168" s="37" t="s">
+      <c r="C168" s="45" t="s">
         <v>14</v>
       </c>
       <c r="D168" s="5" t="s">
@@ -6540,15 +6537,15 @@
       <c r="F168" s="5" t="s">
         <v>639</v>
       </c>
-      <c r="G168" s="32"/>
+      <c r="G168" s="28"/>
       <c r="H168" s="15" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="169" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A169" s="34"/>
-      <c r="B169" s="36"/>
-      <c r="C169" s="37"/>
+      <c r="A169" s="44"/>
+      <c r="B169" s="33"/>
+      <c r="C169" s="45"/>
       <c r="D169" s="5" t="s">
         <v>116</v>
       </c>
@@ -6558,19 +6555,19 @@
       <c r="F169" s="5" t="s">
         <v>640</v>
       </c>
-      <c r="G169" s="32"/>
+      <c r="G169" s="28"/>
       <c r="H169" s="15" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="170" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A170" s="38">
+      <c r="A170" s="34">
         <v>61</v>
       </c>
-      <c r="B170" s="36" t="s">
+      <c r="B170" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C170" s="28" t="s">
+      <c r="C170" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D170" s="5" t="s">
@@ -6582,7 +6579,7 @@
       <c r="F170" s="5" t="s">
         <v>611</v>
       </c>
-      <c r="G170" s="32" t="s">
+      <c r="G170" s="28" t="s">
         <v>656</v>
       </c>
       <c r="H170" s="15" t="s">
@@ -6590,9 +6587,9 @@
       </c>
     </row>
     <row r="171" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A171" s="39"/>
-      <c r="B171" s="36"/>
-      <c r="C171" s="28"/>
+      <c r="A171" s="35"/>
+      <c r="B171" s="33"/>
+      <c r="C171" s="29"/>
       <c r="D171" s="5" t="s">
         <v>81</v>
       </c>
@@ -6602,19 +6599,19 @@
       <c r="F171" s="5" t="s">
         <v>612</v>
       </c>
-      <c r="G171" s="32"/>
+      <c r="G171" s="28"/>
       <c r="H171" s="15" t="s">
         <v>655</v>
       </c>
     </row>
     <row r="172" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A172" s="38">
+      <c r="A172" s="34">
         <v>62</v>
       </c>
-      <c r="B172" s="36" t="s">
+      <c r="B172" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C172" s="43" t="s">
+      <c r="C172" s="32" t="s">
         <v>14</v>
       </c>
       <c r="D172" s="5" t="s">
@@ -6626,15 +6623,15 @@
       <c r="F172" s="5" t="s">
         <v>530</v>
       </c>
-      <c r="G172" s="32"/>
+      <c r="G172" s="28"/>
       <c r="H172" s="15" t="s">
         <v>529</v>
       </c>
     </row>
     <row r="173" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A173" s="39"/>
-      <c r="B173" s="36"/>
-      <c r="C173" s="43"/>
+      <c r="A173" s="35"/>
+      <c r="B173" s="33"/>
+      <c r="C173" s="32"/>
       <c r="D173" s="5" t="s">
         <v>527</v>
       </c>
@@ -6644,19 +6641,19 @@
       <c r="F173" s="5" t="s">
         <v>531</v>
       </c>
-      <c r="G173" s="32"/>
+      <c r="G173" s="28"/>
       <c r="H173" s="15" t="s">
         <v>529</v>
       </c>
     </row>
     <row r="174" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A174" s="33">
+      <c r="A174" s="43">
         <v>63</v>
       </c>
-      <c r="B174" s="36" t="s">
+      <c r="B174" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C174" s="37" t="s">
+      <c r="C174" s="45" t="s">
         <v>14</v>
       </c>
       <c r="D174" s="5" t="s">
@@ -6668,7 +6665,7 @@
       <c r="F174" s="5" t="s">
         <v>658</v>
       </c>
-      <c r="G174" s="32" t="s">
+      <c r="G174" s="28" t="s">
         <v>576</v>
       </c>
       <c r="H174" s="15" t="s">
@@ -6676,9 +6673,9 @@
       </c>
     </row>
     <row r="175" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A175" s="34"/>
-      <c r="B175" s="36"/>
-      <c r="C175" s="37"/>
+      <c r="A175" s="44"/>
+      <c r="B175" s="33"/>
+      <c r="C175" s="45"/>
       <c r="D175" s="5" t="s">
         <v>195</v>
       </c>
@@ -6688,19 +6685,19 @@
       <c r="F175" s="5" t="s">
         <v>577</v>
       </c>
-      <c r="G175" s="32"/>
+      <c r="G175" s="28"/>
       <c r="H175" s="15" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="176" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A176" s="33">
+      <c r="A176" s="43">
         <v>64</v>
       </c>
-      <c r="B176" s="36" t="s">
+      <c r="B176" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C176" s="28" t="s">
+      <c r="C176" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D176" s="5" t="s">
@@ -6712,7 +6709,7 @@
       <c r="F176" s="5" t="s">
         <v>653</v>
       </c>
-      <c r="G176" s="32" t="s">
+      <c r="G176" s="28" t="s">
         <v>112</v>
       </c>
       <c r="H176" s="15" t="s">
@@ -6720,9 +6717,9 @@
       </c>
     </row>
     <row r="177" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A177" s="34"/>
-      <c r="B177" s="36"/>
-      <c r="C177" s="28"/>
+      <c r="A177" s="44"/>
+      <c r="B177" s="33"/>
+      <c r="C177" s="29"/>
       <c r="D177" s="5" t="s">
         <v>111</v>
       </c>
@@ -6732,19 +6729,19 @@
       <c r="F177" s="5" t="s">
         <v>652</v>
       </c>
-      <c r="G177" s="32"/>
+      <c r="G177" s="28"/>
       <c r="H177" s="15" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="178" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A178" s="33">
+      <c r="A178" s="43">
         <v>65</v>
       </c>
-      <c r="B178" s="35" t="s">
+      <c r="B178" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C178" s="28" t="s">
+      <c r="C178" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D178" s="5" t="s">
@@ -6756,15 +6753,15 @@
       <c r="F178" s="5" t="s">
         <v>659</v>
       </c>
-      <c r="G178" s="32"/>
+      <c r="G178" s="28"/>
       <c r="H178" s="15" t="s">
         <v>616</v>
       </c>
     </row>
     <row r="179" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A179" s="34"/>
-      <c r="B179" s="35"/>
-      <c r="C179" s="28"/>
+      <c r="A179" s="44"/>
+      <c r="B179" s="31"/>
+      <c r="C179" s="29"/>
       <c r="D179" s="5" t="s">
         <v>609</v>
       </c>
@@ -6774,19 +6771,19 @@
       <c r="F179" s="5" t="s">
         <v>610</v>
       </c>
-      <c r="G179" s="32"/>
+      <c r="G179" s="28"/>
       <c r="H179" s="15" t="s">
         <v>617</v>
       </c>
     </row>
     <row r="180" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A180" s="33">
+      <c r="A180" s="43">
         <v>66</v>
       </c>
-      <c r="B180" s="35" t="s">
+      <c r="B180" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C180" s="28" t="s">
+      <c r="C180" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D180" s="5" t="s">
@@ -6798,15 +6795,15 @@
       <c r="F180" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="G180" s="32"/>
+      <c r="G180" s="28"/>
       <c r="H180" s="15" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="181" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A181" s="34"/>
-      <c r="B181" s="35"/>
-      <c r="C181" s="28"/>
+      <c r="A181" s="44"/>
+      <c r="B181" s="31"/>
+      <c r="C181" s="29"/>
       <c r="D181" s="5" t="s">
         <v>61</v>
       </c>
@@ -6816,19 +6813,19 @@
       <c r="F181" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="G181" s="32"/>
+      <c r="G181" s="28"/>
       <c r="H181" s="15" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="182" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A182" s="33">
+      <c r="A182" s="43">
         <v>67</v>
       </c>
-      <c r="B182" s="35" t="s">
+      <c r="B182" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C182" s="28" t="s">
+      <c r="C182" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D182" s="5" t="s">
@@ -6840,15 +6837,15 @@
       <c r="F182" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="G182" s="32"/>
+      <c r="G182" s="28"/>
       <c r="H182" s="15" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="183" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A183" s="34"/>
-      <c r="B183" s="35"/>
-      <c r="C183" s="28"/>
+      <c r="A183" s="44"/>
+      <c r="B183" s="31"/>
+      <c r="C183" s="29"/>
       <c r="D183" s="5" t="s">
         <v>69</v>
       </c>
@@ -6858,19 +6855,19 @@
       <c r="F183" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="G183" s="32"/>
+      <c r="G183" s="28"/>
       <c r="H183" s="15" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="184" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A184" s="52">
+      <c r="A184" s="34">
         <v>68</v>
       </c>
-      <c r="B184" s="35" t="s">
+      <c r="B184" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C184" s="28" t="s">
+      <c r="C184" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D184" s="5" t="s">
@@ -6882,15 +6879,15 @@
       <c r="F184" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="G184" s="32"/>
+      <c r="G184" s="28"/>
       <c r="H184" s="15" t="s">
         <v>533</v>
       </c>
     </row>
     <row r="185" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A185" s="53"/>
-      <c r="B185" s="35"/>
-      <c r="C185" s="28"/>
+      <c r="A185" s="35"/>
+      <c r="B185" s="31"/>
+      <c r="C185" s="29"/>
       <c r="D185" s="5" t="s">
         <v>219</v>
       </c>
@@ -6900,19 +6897,19 @@
       <c r="F185" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="G185" s="32"/>
+      <c r="G185" s="28"/>
       <c r="H185" s="15" t="s">
         <v>534</v>
       </c>
     </row>
     <row r="186" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A186" s="52">
+      <c r="A186" s="34">
         <v>69</v>
       </c>
-      <c r="B186" s="35" t="s">
+      <c r="B186" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C186" s="28" t="s">
+      <c r="C186" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D186" s="5" t="s">
@@ -6924,15 +6921,15 @@
       <c r="F186" s="5" t="s">
         <v>665</v>
       </c>
-      <c r="G186" s="32"/>
+      <c r="G186" s="28"/>
       <c r="H186" s="15" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="187" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A187" s="53"/>
-      <c r="B187" s="35"/>
-      <c r="C187" s="28"/>
+      <c r="A187" s="35"/>
+      <c r="B187" s="31"/>
+      <c r="C187" s="29"/>
       <c r="D187" s="5" t="s">
         <v>71</v>
       </c>
@@ -6942,19 +6939,19 @@
       <c r="F187" s="5" t="s">
         <v>665</v>
       </c>
-      <c r="G187" s="32"/>
+      <c r="G187" s="28"/>
       <c r="H187" s="15" t="s">
         <v>431</v>
       </c>
     </row>
     <row r="188" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A188" s="33">
+      <c r="A188" s="43">
         <v>70</v>
       </c>
-      <c r="B188" s="35" t="s">
+      <c r="B188" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C188" s="37" t="s">
+      <c r="C188" s="45" t="s">
         <v>14</v>
       </c>
       <c r="D188" s="5" t="s">
@@ -6966,15 +6963,15 @@
       <c r="F188" s="5" t="s">
         <v>436</v>
       </c>
-      <c r="G188" s="32"/>
+      <c r="G188" s="28"/>
       <c r="H188" s="15" t="s">
         <v>440</v>
       </c>
     </row>
     <row r="189" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A189" s="34"/>
-      <c r="B189" s="35"/>
-      <c r="C189" s="37"/>
+      <c r="A189" s="44"/>
+      <c r="B189" s="31"/>
+      <c r="C189" s="45"/>
       <c r="D189" s="5" t="s">
         <v>438</v>
       </c>
@@ -6984,19 +6981,19 @@
       <c r="F189" s="5" t="s">
         <v>437</v>
       </c>
-      <c r="G189" s="32"/>
+      <c r="G189" s="28"/>
       <c r="H189" s="15" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="190" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A190" s="33">
+      <c r="A190" s="43">
         <v>71</v>
       </c>
-      <c r="B190" s="35" t="s">
+      <c r="B190" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C190" s="37" t="s">
+      <c r="C190" s="45" t="s">
         <v>14</v>
       </c>
       <c r="D190" s="5" t="s">
@@ -7008,7 +7005,7 @@
       <c r="F190" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="G190" s="32" t="s">
+      <c r="G190" s="28" t="s">
         <v>538</v>
       </c>
       <c r="H190" s="15" t="s">
@@ -7016,9 +7013,9 @@
       </c>
     </row>
     <row r="191" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A191" s="34"/>
-      <c r="B191" s="35"/>
-      <c r="C191" s="37"/>
+      <c r="A191" s="44"/>
+      <c r="B191" s="31"/>
+      <c r="C191" s="45"/>
       <c r="D191" s="5" t="s">
         <v>85</v>
       </c>
@@ -7028,19 +7025,19 @@
       <c r="F191" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="G191" s="32"/>
+      <c r="G191" s="28"/>
       <c r="H191" s="15" t="s">
         <v>408</v>
       </c>
     </row>
     <row r="192" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A192" s="33">
+      <c r="A192" s="43">
         <v>72</v>
       </c>
-      <c r="B192" s="35" t="s">
+      <c r="B192" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C192" s="37" t="s">
+      <c r="C192" s="45" t="s">
         <v>14</v>
       </c>
       <c r="D192" s="5" t="s">
@@ -7052,15 +7049,15 @@
       <c r="F192" s="5" t="s">
         <v>660</v>
       </c>
-      <c r="G192" s="32"/>
+      <c r="G192" s="28"/>
       <c r="H192" s="15" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="193" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A193" s="34"/>
-      <c r="B193" s="35"/>
-      <c r="C193" s="37"/>
+      <c r="A193" s="44"/>
+      <c r="B193" s="31"/>
+      <c r="C193" s="45"/>
       <c r="D193" s="5" t="s">
         <v>185</v>
       </c>
@@ -7070,19 +7067,19 @@
       <c r="F193" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="G193" s="32"/>
+      <c r="G193" s="28"/>
       <c r="H193" s="15" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="194" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A194" s="33">
+      <c r="A194" s="43">
         <v>73</v>
       </c>
-      <c r="B194" s="35" t="s">
+      <c r="B194" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C194" s="28" t="s">
+      <c r="C194" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D194" s="5" t="s">
@@ -7094,7 +7091,7 @@
       <c r="F194" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="G194" s="32" t="s">
+      <c r="G194" s="28" t="s">
         <v>209</v>
       </c>
       <c r="H194" s="15" t="s">
@@ -7102,9 +7099,9 @@
       </c>
     </row>
     <row r="195" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A195" s="34"/>
-      <c r="B195" s="35"/>
-      <c r="C195" s="28"/>
+      <c r="A195" s="44"/>
+      <c r="B195" s="31"/>
+      <c r="C195" s="29"/>
       <c r="D195" s="5" t="s">
         <v>129</v>
       </c>
@@ -7114,19 +7111,19 @@
       <c r="F195" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="G195" s="32"/>
+      <c r="G195" s="28"/>
       <c r="H195" s="15" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="196" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A196" s="33">
+      <c r="A196" s="43">
         <v>74</v>
       </c>
-      <c r="B196" s="35" t="s">
+      <c r="B196" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C196" s="28" t="s">
+      <c r="C196" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D196" s="5" t="s">
@@ -7138,7 +7135,7 @@
       <c r="F196" s="5" t="s">
         <v>661</v>
       </c>
-      <c r="G196" s="32" t="s">
+      <c r="G196" s="28" t="s">
         <v>138</v>
       </c>
       <c r="H196" s="15" t="s">
@@ -7146,9 +7143,9 @@
       </c>
     </row>
     <row r="197" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A197" s="34"/>
-      <c r="B197" s="35"/>
-      <c r="C197" s="28"/>
+      <c r="A197" s="44"/>
+      <c r="B197" s="31"/>
+      <c r="C197" s="29"/>
       <c r="D197" s="5" t="s">
         <v>107</v>
       </c>
@@ -7158,19 +7155,19 @@
       <c r="F197" s="5" t="s">
         <v>662</v>
       </c>
-      <c r="G197" s="32"/>
+      <c r="G197" s="28"/>
       <c r="H197" s="15" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="198" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A198" s="38">
+      <c r="A198" s="34">
         <v>75</v>
       </c>
-      <c r="B198" s="36" t="s">
+      <c r="B198" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C198" s="28" t="s">
+      <c r="C198" s="29" t="s">
         <v>86</v>
       </c>
       <c r="D198" s="5" t="s">
@@ -7182,7 +7179,7 @@
       <c r="F198" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="G198" s="32" t="s">
+      <c r="G198" s="28" t="s">
         <v>570</v>
       </c>
       <c r="H198" s="15" t="s">
@@ -7190,9 +7187,9 @@
       </c>
     </row>
     <row r="199" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A199" s="39"/>
-      <c r="B199" s="36"/>
-      <c r="C199" s="28"/>
+      <c r="A199" s="35"/>
+      <c r="B199" s="33"/>
+      <c r="C199" s="29"/>
       <c r="D199" s="5" t="s">
         <v>92</v>
       </c>
@@ -7202,19 +7199,19 @@
       <c r="F199" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="G199" s="32"/>
+      <c r="G199" s="28"/>
       <c r="H199" s="15" t="s">
         <v>433</v>
       </c>
     </row>
     <row r="200" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A200" s="33">
+      <c r="A200" s="43">
         <v>76</v>
       </c>
-      <c r="B200" s="36" t="s">
+      <c r="B200" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C200" s="28" t="s">
+      <c r="C200" s="29" t="s">
         <v>86</v>
       </c>
       <c r="D200" s="5" t="s">
@@ -7226,7 +7223,7 @@
       <c r="F200" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="G200" s="32" t="s">
+      <c r="G200" s="28" t="s">
         <v>216</v>
       </c>
       <c r="H200" s="15" t="s">
@@ -7234,9 +7231,9 @@
       </c>
     </row>
     <row r="201" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A201" s="34"/>
-      <c r="B201" s="36"/>
-      <c r="C201" s="28"/>
+      <c r="A201" s="44"/>
+      <c r="B201" s="33"/>
+      <c r="C201" s="29"/>
       <c r="D201" s="5" t="s">
         <v>104</v>
       </c>
@@ -7246,19 +7243,19 @@
       <c r="F201" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="G201" s="32"/>
+      <c r="G201" s="28"/>
       <c r="H201" s="15" t="s">
         <v>435</v>
       </c>
     </row>
     <row r="202" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A202" s="38">
+      <c r="A202" s="34">
         <v>77</v>
       </c>
-      <c r="B202" s="36" t="s">
+      <c r="B202" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C202" s="28" t="s">
+      <c r="C202" s="29" t="s">
         <v>86</v>
       </c>
       <c r="D202" s="5" t="s">
@@ -7270,7 +7267,7 @@
       <c r="F202" s="5" t="s">
         <v>545</v>
       </c>
-      <c r="G202" s="32" t="s">
+      <c r="G202" s="28" t="s">
         <v>568</v>
       </c>
       <c r="H202" s="15" t="s">
@@ -7278,9 +7275,9 @@
       </c>
     </row>
     <row r="203" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A203" s="39"/>
-      <c r="B203" s="36"/>
-      <c r="C203" s="28"/>
+      <c r="A203" s="35"/>
+      <c r="B203" s="33"/>
+      <c r="C203" s="29"/>
       <c r="D203" s="5" t="s">
         <v>109</v>
       </c>
@@ -7290,19 +7287,19 @@
       <c r="F203" s="5" t="s">
         <v>546</v>
       </c>
-      <c r="G203" s="32"/>
+      <c r="G203" s="28"/>
       <c r="H203" s="15" t="s">
         <v>412</v>
       </c>
     </row>
     <row r="204" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A204" s="33">
+      <c r="A204" s="43">
         <v>78</v>
       </c>
-      <c r="B204" s="36" t="s">
+      <c r="B204" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C204" s="28" t="s">
+      <c r="C204" s="29" t="s">
         <v>86</v>
       </c>
       <c r="D204" s="5" t="s">
@@ -7314,15 +7311,15 @@
       <c r="F204" s="5" t="s">
         <v>574</v>
       </c>
-      <c r="G204" s="32"/>
+      <c r="G204" s="28"/>
       <c r="H204" s="15" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="205" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A205" s="34"/>
-      <c r="B205" s="36"/>
-      <c r="C205" s="28"/>
+      <c r="A205" s="44"/>
+      <c r="B205" s="33"/>
+      <c r="C205" s="29"/>
       <c r="D205" s="5" t="s">
         <v>88</v>
       </c>
@@ -7332,19 +7329,19 @@
       <c r="F205" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="G205" s="32"/>
+      <c r="G205" s="28"/>
       <c r="H205" s="15" t="s">
         <v>423</v>
       </c>
     </row>
     <row r="206" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A206" s="33">
+      <c r="A206" s="43">
         <v>79</v>
       </c>
-      <c r="B206" s="36" t="s">
+      <c r="B206" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C206" s="28" t="s">
+      <c r="C206" s="29" t="s">
         <v>86</v>
       </c>
       <c r="D206" s="5" t="s">
@@ -7356,15 +7353,15 @@
       <c r="F206" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="G206" s="32"/>
+      <c r="G206" s="28"/>
       <c r="H206" s="15" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="207" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A207" s="34"/>
-      <c r="B207" s="36"/>
-      <c r="C207" s="28"/>
+      <c r="A207" s="44"/>
+      <c r="B207" s="33"/>
+      <c r="C207" s="29"/>
       <c r="D207" s="5" t="s">
         <v>90</v>
       </c>
@@ -7374,19 +7371,19 @@
       <c r="F207" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="G207" s="32"/>
+      <c r="G207" s="28"/>
       <c r="H207" s="15" t="s">
         <v>413</v>
       </c>
     </row>
     <row r="208" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A208" s="33">
+      <c r="A208" s="43">
         <v>80</v>
       </c>
-      <c r="B208" s="36" t="s">
+      <c r="B208" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C208" s="28" t="s">
+      <c r="C208" s="29" t="s">
         <v>86</v>
       </c>
       <c r="D208" s="5" t="s">
@@ -7398,7 +7395,7 @@
       <c r="F208" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="G208" s="32" t="s">
+      <c r="G208" s="28" t="s">
         <v>234</v>
       </c>
       <c r="H208" s="15" t="s">
@@ -7406,9 +7403,9 @@
       </c>
     </row>
     <row r="209" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A209" s="34"/>
-      <c r="B209" s="36"/>
-      <c r="C209" s="28"/>
+      <c r="A209" s="44"/>
+      <c r="B209" s="33"/>
+      <c r="C209" s="29"/>
       <c r="D209" s="5" t="s">
         <v>102</v>
       </c>
@@ -7418,19 +7415,19 @@
       <c r="F209" s="5" t="s">
         <v>565</v>
       </c>
-      <c r="G209" s="32"/>
+      <c r="G209" s="28"/>
       <c r="H209" s="15" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="210" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A210" s="38">
+      <c r="A210" s="34">
         <v>81</v>
       </c>
-      <c r="B210" s="36" t="s">
+      <c r="B210" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C210" s="28" t="s">
+      <c r="C210" s="29" t="s">
         <v>86</v>
       </c>
       <c r="D210" s="5" t="s">
@@ -7442,7 +7439,7 @@
       <c r="F210" s="5" t="s">
         <v>593</v>
       </c>
-      <c r="G210" s="32" t="s">
+      <c r="G210" s="28" t="s">
         <v>566</v>
       </c>
       <c r="H210" s="15" t="s">
@@ -7450,9 +7447,9 @@
       </c>
     </row>
     <row r="211" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A211" s="39"/>
-      <c r="B211" s="36"/>
-      <c r="C211" s="28"/>
+      <c r="A211" s="35"/>
+      <c r="B211" s="33"/>
+      <c r="C211" s="29"/>
       <c r="D211" s="5" t="s">
         <v>96</v>
       </c>
@@ -7462,19 +7459,19 @@
       <c r="F211" s="5" t="s">
         <v>594</v>
       </c>
-      <c r="G211" s="32"/>
+      <c r="G211" s="28"/>
       <c r="H211" s="15" t="s">
         <v>418</v>
       </c>
     </row>
     <row r="212" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A212" s="33">
+      <c r="A212" s="43">
         <v>82</v>
       </c>
-      <c r="B212" s="44" t="s">
+      <c r="B212" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="C212" s="28" t="s">
+      <c r="C212" s="29" t="s">
         <v>86</v>
       </c>
       <c r="D212" s="5" t="s">
@@ -7486,15 +7483,15 @@
       <c r="F212" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="G212" s="32"/>
+      <c r="G212" s="28"/>
       <c r="H212" s="15" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="213" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A213" s="34"/>
-      <c r="B213" s="45"/>
-      <c r="C213" s="28"/>
+      <c r="A213" s="44"/>
+      <c r="B213" s="49"/>
+      <c r="C213" s="29"/>
       <c r="D213" s="5" t="s">
         <v>174</v>
       </c>
@@ -7504,19 +7501,19 @@
       <c r="F213" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="G213" s="32"/>
+      <c r="G213" s="28"/>
       <c r="H213" s="15" t="s">
         <v>415</v>
       </c>
     </row>
     <row r="214" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A214" s="33">
+      <c r="A214" s="43">
         <v>83</v>
       </c>
-      <c r="B214" s="35" t="s">
+      <c r="B214" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C214" s="28" t="s">
+      <c r="C214" s="29" t="s">
         <v>86</v>
       </c>
       <c r="D214" s="5" t="s">
@@ -7528,7 +7525,7 @@
       <c r="F214" s="5" t="s">
         <v>537</v>
       </c>
-      <c r="G214" s="32" t="s">
+      <c r="G214" s="28" t="s">
         <v>569</v>
       </c>
       <c r="H214" s="15" t="s">
@@ -7536,9 +7533,9 @@
       </c>
     </row>
     <row r="215" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A215" s="34"/>
-      <c r="B215" s="35"/>
-      <c r="C215" s="28"/>
+      <c r="A215" s="44"/>
+      <c r="B215" s="31"/>
+      <c r="C215" s="29"/>
       <c r="D215" s="5" t="s">
         <v>135</v>
       </c>
@@ -7548,19 +7545,19 @@
       <c r="F215" s="5" t="s">
         <v>544</v>
       </c>
-      <c r="G215" s="32"/>
+      <c r="G215" s="28"/>
       <c r="H215" s="15" t="s">
         <v>416</v>
       </c>
     </row>
     <row r="216" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A216" s="33">
+      <c r="A216" s="43">
         <v>84</v>
       </c>
-      <c r="B216" s="35" t="s">
+      <c r="B216" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C216" s="28" t="s">
+      <c r="C216" s="29" t="s">
         <v>86</v>
       </c>
       <c r="D216" s="5" t="s">
@@ -7572,7 +7569,7 @@
       <c r="F216" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="G216" s="32" t="s">
+      <c r="G216" s="28" t="s">
         <v>285</v>
       </c>
       <c r="H216" s="15" t="s">
@@ -7580,9 +7577,9 @@
       </c>
     </row>
     <row r="217" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A217" s="34"/>
-      <c r="B217" s="35"/>
-      <c r="C217" s="28"/>
+      <c r="A217" s="44"/>
+      <c r="B217" s="31"/>
+      <c r="C217" s="29"/>
       <c r="D217" s="5" t="s">
         <v>94</v>
       </c>
@@ -7592,19 +7589,19 @@
       <c r="F217" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="G217" s="32"/>
+      <c r="G217" s="28"/>
       <c r="H217" s="15" t="s">
         <v>417</v>
       </c>
     </row>
     <row r="218" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A218" s="33">
+      <c r="A218" s="43">
         <v>85</v>
       </c>
-      <c r="B218" s="35" t="s">
+      <c r="B218" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C218" s="28" t="s">
+      <c r="C218" s="29" t="s">
         <v>86</v>
       </c>
       <c r="D218" s="5" t="s">
@@ -7616,15 +7613,15 @@
       <c r="F218" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="G218" s="32"/>
+      <c r="G218" s="28"/>
       <c r="H218" s="15" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="219" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A219" s="34"/>
-      <c r="B219" s="35"/>
-      <c r="C219" s="28"/>
+      <c r="A219" s="44"/>
+      <c r="B219" s="31"/>
+      <c r="C219" s="29"/>
       <c r="D219" s="5" t="s">
         <v>98</v>
       </c>
@@ -7634,19 +7631,19 @@
       <c r="F219" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="G219" s="32"/>
+      <c r="G219" s="28"/>
       <c r="H219" s="15" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="220" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A220" s="33">
+      <c r="A220" s="43">
         <v>86</v>
       </c>
-      <c r="B220" s="35" t="s">
+      <c r="B220" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C220" s="28" t="s">
+      <c r="C220" s="29" t="s">
         <v>86</v>
       </c>
       <c r="D220" s="5" t="s">
@@ -7658,15 +7655,15 @@
       <c r="F220" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="G220" s="32"/>
+      <c r="G220" s="28"/>
       <c r="H220" s="15" t="s">
         <v>442</v>
       </c>
     </row>
     <row r="221" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A221" s="34"/>
-      <c r="B221" s="35"/>
-      <c r="C221" s="28"/>
+      <c r="A221" s="44"/>
+      <c r="B221" s="31"/>
+      <c r="C221" s="29"/>
       <c r="D221" s="5" t="s">
         <v>148</v>
       </c>
@@ -7676,19 +7673,19 @@
       <c r="F221" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="G221" s="32"/>
+      <c r="G221" s="28"/>
       <c r="H221" s="15" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="222" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A222" s="33">
+      <c r="A222" s="43">
         <v>87</v>
       </c>
-      <c r="B222" s="35" t="s">
+      <c r="B222" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C222" s="43" t="s">
+      <c r="C222" s="32" t="s">
         <v>86</v>
       </c>
       <c r="D222" s="5" t="s">
@@ -7700,7 +7697,7 @@
       <c r="F222" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="G222" s="32" t="s">
+      <c r="G222" s="28" t="s">
         <v>567</v>
       </c>
       <c r="H222" s="15" t="s">
@@ -7708,9 +7705,9 @@
       </c>
     </row>
     <row r="223" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A223" s="34"/>
-      <c r="B223" s="35"/>
-      <c r="C223" s="43"/>
+      <c r="A223" s="44"/>
+      <c r="B223" s="31"/>
+      <c r="C223" s="32"/>
       <c r="D223" s="5" t="s">
         <v>100</v>
       </c>
@@ -7720,19 +7717,19 @@
       <c r="F223" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="G223" s="32"/>
+      <c r="G223" s="28"/>
       <c r="H223" s="15" t="s">
         <v>420</v>
       </c>
     </row>
     <row r="224" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A224" s="33">
+      <c r="A224" s="43">
         <v>88</v>
       </c>
-      <c r="B224" s="35" t="s">
+      <c r="B224" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C224" s="37" t="s">
+      <c r="C224" s="45" t="s">
         <v>86</v>
       </c>
       <c r="D224" s="5" t="s">
@@ -7744,15 +7741,15 @@
       <c r="F224" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="G224" s="32"/>
+      <c r="G224" s="28"/>
       <c r="H224" s="15" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="225" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A225" s="34"/>
-      <c r="B225" s="35"/>
-      <c r="C225" s="37"/>
+      <c r="A225" s="44"/>
+      <c r="B225" s="31"/>
+      <c r="C225" s="45"/>
       <c r="D225" s="5" t="s">
         <v>140</v>
       </c>
@@ -7762,7 +7759,7 @@
       <c r="F225" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="G225" s="32"/>
+      <c r="G225" s="28"/>
       <c r="H225" s="15" t="s">
         <v>421</v>
       </c>
@@ -7813,16 +7810,16 @@
       </c>
     </row>
     <row r="245" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A245" s="28" t="s">
+      <c r="A245" s="29" t="s">
         <v>579</v>
       </c>
-      <c r="B245" s="28"/>
-      <c r="C245" s="28"/>
-      <c r="D245" s="28"/>
-      <c r="E245" s="28"/>
-      <c r="F245" s="28"/>
-      <c r="G245" s="28"/>
-      <c r="H245" s="28"/>
+      <c r="B245" s="29"/>
+      <c r="C245" s="29"/>
+      <c r="D245" s="29"/>
+      <c r="E245" s="29"/>
+      <c r="F245" s="29"/>
+      <c r="G245" s="29"/>
+      <c r="H245" s="29"/>
     </row>
     <row r="246" spans="1:8" ht="25.7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A246" s="1" t="s">
@@ -7831,12 +7828,12 @@
       <c r="B246" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="C246" s="29" t="s">
+      <c r="C246" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="D246" s="30"/>
-      <c r="E246" s="30"/>
-      <c r="F246" s="31"/>
+      <c r="D246" s="37"/>
+      <c r="E246" s="37"/>
+      <c r="F246" s="38"/>
       <c r="G246" s="1" t="s">
         <v>3</v>
       </c>
@@ -7885,31 +7882,393 @@
       </c>
     </row>
     <row r="253" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A253" s="28" t="s">
+      <c r="A253" s="29" t="s">
         <v>581</v>
       </c>
-      <c r="B253" s="28"/>
-      <c r="C253" s="28"/>
-      <c r="D253" s="28"/>
-      <c r="E253" s="28"/>
-      <c r="F253" s="28"/>
-      <c r="G253" s="28"/>
-      <c r="H253" s="28"/>
+      <c r="B253" s="29"/>
+      <c r="C253" s="29"/>
+      <c r="D253" s="29"/>
+      <c r="E253" s="29"/>
+      <c r="F253" s="29"/>
+      <c r="G253" s="29"/>
+      <c r="H253" s="29"/>
     </row>
     <row r="254" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A254" s="28" t="s">
+      <c r="A254" s="29" t="s">
         <v>582</v>
       </c>
-      <c r="B254" s="28"/>
-      <c r="C254" s="28"/>
-      <c r="D254" s="28"/>
-      <c r="E254" s="28"/>
-      <c r="F254" s="28"/>
-      <c r="G254" s="28"/>
-      <c r="H254" s="28"/>
+      <c r="B254" s="29"/>
+      <c r="C254" s="29"/>
+      <c r="D254" s="29"/>
+      <c r="E254" s="29"/>
+      <c r="F254" s="29"/>
+      <c r="G254" s="29"/>
+      <c r="H254" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="386">
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="A245:H245"/>
+    <mergeCell ref="A253:H253"/>
+    <mergeCell ref="A254:H254"/>
+    <mergeCell ref="C246:F246"/>
+    <mergeCell ref="C247:F247"/>
+    <mergeCell ref="C248:F248"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="G62:G63"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="G202:G203"/>
+    <mergeCell ref="A194:A195"/>
+    <mergeCell ref="B194:B195"/>
+    <mergeCell ref="C194:C195"/>
+    <mergeCell ref="A200:A201"/>
+    <mergeCell ref="B200:B201"/>
+    <mergeCell ref="C200:C201"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A196:A197"/>
+    <mergeCell ref="B196:B197"/>
+    <mergeCell ref="C196:C197"/>
+    <mergeCell ref="A192:A193"/>
+    <mergeCell ref="B192:B193"/>
+    <mergeCell ref="C192:C193"/>
+    <mergeCell ref="G86:G87"/>
+    <mergeCell ref="A120:A121"/>
+    <mergeCell ref="B120:B121"/>
+    <mergeCell ref="C120:C121"/>
+    <mergeCell ref="G118:G119"/>
+    <mergeCell ref="A80:A81"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="C80:C81"/>
+    <mergeCell ref="A78:A79"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="G78:G79"/>
+    <mergeCell ref="A202:A203"/>
+    <mergeCell ref="B202:B203"/>
+    <mergeCell ref="C202:C203"/>
+    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="G64:G65"/>
+    <mergeCell ref="B106:B107"/>
+    <mergeCell ref="C106:C107"/>
+    <mergeCell ref="G104:G105"/>
+    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="G70:G71"/>
+    <mergeCell ref="A90:A91"/>
+    <mergeCell ref="G66:G67"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="B84:B85"/>
+    <mergeCell ref="C84:C85"/>
+    <mergeCell ref="A88:A89"/>
+    <mergeCell ref="B88:B89"/>
+    <mergeCell ref="C92:C93"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="G216:G217"/>
+    <mergeCell ref="B216:B217"/>
+    <mergeCell ref="B208:B209"/>
+    <mergeCell ref="A106:A107"/>
+    <mergeCell ref="A218:A219"/>
+    <mergeCell ref="B218:B219"/>
+    <mergeCell ref="C216:C217"/>
+    <mergeCell ref="G208:G209"/>
+    <mergeCell ref="A206:A207"/>
+    <mergeCell ref="B206:B207"/>
+    <mergeCell ref="C206:C207"/>
+    <mergeCell ref="G206:G207"/>
+    <mergeCell ref="A204:A205"/>
+    <mergeCell ref="B204:B205"/>
+    <mergeCell ref="C204:C205"/>
+    <mergeCell ref="G204:G205"/>
+    <mergeCell ref="G210:G211"/>
+    <mergeCell ref="A216:A217"/>
+    <mergeCell ref="G112:G113"/>
+    <mergeCell ref="G124:G125"/>
+    <mergeCell ref="B166:B167"/>
+    <mergeCell ref="C166:C167"/>
+    <mergeCell ref="B168:B169"/>
+    <mergeCell ref="C178:C179"/>
+    <mergeCell ref="A214:A215"/>
+    <mergeCell ref="G212:G213"/>
+    <mergeCell ref="G196:G197"/>
+    <mergeCell ref="C182:C183"/>
+    <mergeCell ref="G180:G181"/>
+    <mergeCell ref="A164:A165"/>
+    <mergeCell ref="B164:B165"/>
+    <mergeCell ref="C164:C165"/>
+    <mergeCell ref="G190:G191"/>
+    <mergeCell ref="A178:A179"/>
+    <mergeCell ref="B178:B179"/>
+    <mergeCell ref="G164:G165"/>
+    <mergeCell ref="G200:G201"/>
+    <mergeCell ref="A198:A199"/>
+    <mergeCell ref="B198:B199"/>
+    <mergeCell ref="C198:C199"/>
+    <mergeCell ref="G194:G195"/>
+    <mergeCell ref="A186:A187"/>
+    <mergeCell ref="B186:B187"/>
+    <mergeCell ref="C188:C189"/>
+    <mergeCell ref="B184:B185"/>
+    <mergeCell ref="C184:C185"/>
+    <mergeCell ref="G184:G185"/>
+    <mergeCell ref="G192:G193"/>
+    <mergeCell ref="C224:C225"/>
+    <mergeCell ref="G222:G223"/>
+    <mergeCell ref="G198:G199"/>
+    <mergeCell ref="A224:A225"/>
+    <mergeCell ref="G220:G221"/>
+    <mergeCell ref="A210:A211"/>
+    <mergeCell ref="B210:B211"/>
+    <mergeCell ref="C210:C211"/>
+    <mergeCell ref="G224:G225"/>
+    <mergeCell ref="B224:B225"/>
+    <mergeCell ref="A222:A223"/>
+    <mergeCell ref="B222:B223"/>
+    <mergeCell ref="C222:C223"/>
+    <mergeCell ref="G218:G219"/>
+    <mergeCell ref="A212:A213"/>
+    <mergeCell ref="B212:B213"/>
+    <mergeCell ref="C212:C213"/>
+    <mergeCell ref="B214:B215"/>
+    <mergeCell ref="C214:C215"/>
+    <mergeCell ref="A208:A209"/>
+    <mergeCell ref="A220:A221"/>
+    <mergeCell ref="B220:B221"/>
+    <mergeCell ref="C220:C221"/>
+    <mergeCell ref="C218:C219"/>
+    <mergeCell ref="G68:G69"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="G72:G73"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="G74:G75"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="G76:G77"/>
+    <mergeCell ref="C76:C77"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="C86:C87"/>
+    <mergeCell ref="A86:A87"/>
+    <mergeCell ref="B86:B87"/>
+    <mergeCell ref="G80:G81"/>
+    <mergeCell ref="C88:C89"/>
+    <mergeCell ref="C94:C95"/>
+    <mergeCell ref="G94:G95"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="A94:A95"/>
+    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="B104:B105"/>
+    <mergeCell ref="C104:C105"/>
+    <mergeCell ref="A96:A97"/>
+    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="C96:C97"/>
+    <mergeCell ref="B98:B99"/>
+    <mergeCell ref="C98:C99"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="B102:B103"/>
+    <mergeCell ref="A114:A115"/>
+    <mergeCell ref="B114:B115"/>
+    <mergeCell ref="A112:A113"/>
+    <mergeCell ref="B112:B113"/>
+    <mergeCell ref="A116:A117"/>
+    <mergeCell ref="B116:B117"/>
+    <mergeCell ref="A122:A123"/>
+    <mergeCell ref="B122:B123"/>
+    <mergeCell ref="G98:G99"/>
+    <mergeCell ref="A108:A109"/>
+    <mergeCell ref="B108:B109"/>
+    <mergeCell ref="C108:C109"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="B110:B111"/>
+    <mergeCell ref="A98:A99"/>
+    <mergeCell ref="A100:A101"/>
+    <mergeCell ref="B100:B101"/>
+    <mergeCell ref="C100:C101"/>
+    <mergeCell ref="A110:A111"/>
+    <mergeCell ref="A148:A149"/>
+    <mergeCell ref="G84:G85"/>
+    <mergeCell ref="G92:G93"/>
+    <mergeCell ref="G82:G83"/>
+    <mergeCell ref="G90:G91"/>
+    <mergeCell ref="G100:G101"/>
+    <mergeCell ref="C138:C139"/>
+    <mergeCell ref="G138:G139"/>
+    <mergeCell ref="G116:G117"/>
+    <mergeCell ref="G108:G109"/>
+    <mergeCell ref="G110:G111"/>
+    <mergeCell ref="C110:C111"/>
+    <mergeCell ref="C102:C103"/>
+    <mergeCell ref="C114:C115"/>
+    <mergeCell ref="C112:C113"/>
+    <mergeCell ref="C116:C117"/>
+    <mergeCell ref="G122:G123"/>
+    <mergeCell ref="C122:C123"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="G132:G133"/>
+    <mergeCell ref="G106:G107"/>
+    <mergeCell ref="G96:G97"/>
+    <mergeCell ref="G102:G103"/>
+    <mergeCell ref="G126:G127"/>
+    <mergeCell ref="B140:B141"/>
+    <mergeCell ref="C140:C141"/>
+    <mergeCell ref="G136:G137"/>
+    <mergeCell ref="A132:A133"/>
+    <mergeCell ref="A130:A131"/>
+    <mergeCell ref="B130:B131"/>
+    <mergeCell ref="C128:C129"/>
+    <mergeCell ref="A142:A143"/>
+    <mergeCell ref="B142:B143"/>
+    <mergeCell ref="A126:A127"/>
+    <mergeCell ref="B126:B127"/>
+    <mergeCell ref="C126:C127"/>
+    <mergeCell ref="B136:B137"/>
+    <mergeCell ref="C136:C137"/>
+    <mergeCell ref="G148:G149"/>
+    <mergeCell ref="A150:A151"/>
+    <mergeCell ref="A160:A161"/>
+    <mergeCell ref="B160:B161"/>
+    <mergeCell ref="C160:C161"/>
+    <mergeCell ref="G128:G129"/>
+    <mergeCell ref="A154:A155"/>
+    <mergeCell ref="A138:A139"/>
+    <mergeCell ref="G140:G141"/>
+    <mergeCell ref="G134:G135"/>
+    <mergeCell ref="A128:A129"/>
+    <mergeCell ref="B128:B129"/>
+    <mergeCell ref="B148:B149"/>
+    <mergeCell ref="C148:C149"/>
+    <mergeCell ref="G146:G147"/>
+    <mergeCell ref="A144:A145"/>
+    <mergeCell ref="B144:B145"/>
+    <mergeCell ref="C144:C145"/>
+    <mergeCell ref="A140:A141"/>
+    <mergeCell ref="C180:C181"/>
+    <mergeCell ref="G178:G179"/>
+    <mergeCell ref="A176:A177"/>
+    <mergeCell ref="B132:B133"/>
+    <mergeCell ref="C132:C133"/>
+    <mergeCell ref="B154:B155"/>
+    <mergeCell ref="C154:C155"/>
+    <mergeCell ref="G152:G153"/>
+    <mergeCell ref="G172:G173"/>
+    <mergeCell ref="B176:B177"/>
+    <mergeCell ref="C176:C177"/>
+    <mergeCell ref="B172:B173"/>
+    <mergeCell ref="A168:A169"/>
+    <mergeCell ref="G170:G171"/>
+    <mergeCell ref="G176:G177"/>
+    <mergeCell ref="G142:G143"/>
+    <mergeCell ref="A170:A171"/>
+    <mergeCell ref="B170:B171"/>
+    <mergeCell ref="C170:C171"/>
+    <mergeCell ref="G168:G169"/>
+    <mergeCell ref="A172:A173"/>
+    <mergeCell ref="A180:A181"/>
+    <mergeCell ref="B180:B181"/>
+    <mergeCell ref="A136:A137"/>
+    <mergeCell ref="B190:B191"/>
+    <mergeCell ref="G182:G183"/>
+    <mergeCell ref="C190:C191"/>
+    <mergeCell ref="G188:G189"/>
+    <mergeCell ref="B188:B189"/>
+    <mergeCell ref="C172:C173"/>
+    <mergeCell ref="C158:C159"/>
+    <mergeCell ref="G156:G157"/>
+    <mergeCell ref="A156:A157"/>
+    <mergeCell ref="B156:B157"/>
+    <mergeCell ref="A174:A175"/>
+    <mergeCell ref="B174:B175"/>
+    <mergeCell ref="C174:C175"/>
+    <mergeCell ref="G174:G175"/>
+    <mergeCell ref="B158:B159"/>
+    <mergeCell ref="C186:C187"/>
+    <mergeCell ref="A158:A159"/>
+    <mergeCell ref="G186:G187"/>
+    <mergeCell ref="A182:A183"/>
+    <mergeCell ref="B182:B183"/>
+    <mergeCell ref="C168:C169"/>
+    <mergeCell ref="G166:G167"/>
+    <mergeCell ref="A184:A185"/>
+    <mergeCell ref="G162:G163"/>
+    <mergeCell ref="A124:A125"/>
+    <mergeCell ref="B124:B125"/>
+    <mergeCell ref="A118:A119"/>
+    <mergeCell ref="A134:A135"/>
+    <mergeCell ref="B134:B135"/>
+    <mergeCell ref="C134:C135"/>
+    <mergeCell ref="G214:G215"/>
+    <mergeCell ref="C118:C119"/>
+    <mergeCell ref="B118:B119"/>
+    <mergeCell ref="C124:C125"/>
+    <mergeCell ref="A152:A153"/>
+    <mergeCell ref="B152:B153"/>
+    <mergeCell ref="C152:C153"/>
+    <mergeCell ref="A146:A147"/>
+    <mergeCell ref="B146:B147"/>
+    <mergeCell ref="C146:C147"/>
+    <mergeCell ref="B150:B151"/>
+    <mergeCell ref="C150:C151"/>
+    <mergeCell ref="G150:G151"/>
+    <mergeCell ref="G160:G161"/>
+    <mergeCell ref="A166:A167"/>
+    <mergeCell ref="A162:A163"/>
+    <mergeCell ref="A188:A189"/>
+    <mergeCell ref="A190:A191"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="A48:H48"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="G50:G51"/>
+    <mergeCell ref="G52:G53"/>
+    <mergeCell ref="G54:G55"/>
+    <mergeCell ref="G56:G57"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="C62:C63"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C60:C61"/>
     <mergeCell ref="C27:F27"/>
     <mergeCell ref="C34:F34"/>
     <mergeCell ref="C35:F35"/>
@@ -7934,368 +8293,6 @@
     <mergeCell ref="C142:C143"/>
     <mergeCell ref="G120:G121"/>
     <mergeCell ref="G114:G115"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="A62:A63"/>
-    <mergeCell ref="C62:C63"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="A47:H47"/>
-    <mergeCell ref="A48:H48"/>
-    <mergeCell ref="A41:H41"/>
-    <mergeCell ref="G50:G51"/>
-    <mergeCell ref="G52:G53"/>
-    <mergeCell ref="G54:G55"/>
-    <mergeCell ref="G56:G57"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="A124:A125"/>
-    <mergeCell ref="B124:B125"/>
-    <mergeCell ref="A118:A119"/>
-    <mergeCell ref="A134:A135"/>
-    <mergeCell ref="B134:B135"/>
-    <mergeCell ref="C134:C135"/>
-    <mergeCell ref="G214:G215"/>
-    <mergeCell ref="C118:C119"/>
-    <mergeCell ref="B118:B119"/>
-    <mergeCell ref="C124:C125"/>
-    <mergeCell ref="A152:A153"/>
-    <mergeCell ref="B152:B153"/>
-    <mergeCell ref="C152:C153"/>
-    <mergeCell ref="A146:A147"/>
-    <mergeCell ref="B146:B147"/>
-    <mergeCell ref="C146:C147"/>
-    <mergeCell ref="B150:B151"/>
-    <mergeCell ref="C150:C151"/>
-    <mergeCell ref="G150:G151"/>
-    <mergeCell ref="G160:G161"/>
-    <mergeCell ref="A166:A167"/>
-    <mergeCell ref="A162:A163"/>
-    <mergeCell ref="A188:A189"/>
-    <mergeCell ref="A190:A191"/>
-    <mergeCell ref="B190:B191"/>
-    <mergeCell ref="G182:G183"/>
-    <mergeCell ref="C190:C191"/>
-    <mergeCell ref="G188:G189"/>
-    <mergeCell ref="B188:B189"/>
-    <mergeCell ref="C172:C173"/>
-    <mergeCell ref="C158:C159"/>
-    <mergeCell ref="G156:G157"/>
-    <mergeCell ref="A156:A157"/>
-    <mergeCell ref="B156:B157"/>
-    <mergeCell ref="A174:A175"/>
-    <mergeCell ref="B174:B175"/>
-    <mergeCell ref="C174:C175"/>
-    <mergeCell ref="G174:G175"/>
-    <mergeCell ref="B158:B159"/>
-    <mergeCell ref="C186:C187"/>
-    <mergeCell ref="A158:A159"/>
-    <mergeCell ref="G186:G187"/>
-    <mergeCell ref="A182:A183"/>
-    <mergeCell ref="B182:B183"/>
-    <mergeCell ref="C168:C169"/>
-    <mergeCell ref="G166:G167"/>
-    <mergeCell ref="A184:A185"/>
-    <mergeCell ref="G162:G163"/>
-    <mergeCell ref="C180:C181"/>
-    <mergeCell ref="G178:G179"/>
-    <mergeCell ref="A176:A177"/>
-    <mergeCell ref="B132:B133"/>
-    <mergeCell ref="C132:C133"/>
-    <mergeCell ref="B154:B155"/>
-    <mergeCell ref="C154:C155"/>
-    <mergeCell ref="G152:G153"/>
-    <mergeCell ref="G172:G173"/>
-    <mergeCell ref="B176:B177"/>
-    <mergeCell ref="C176:C177"/>
-    <mergeCell ref="B172:B173"/>
-    <mergeCell ref="A168:A169"/>
-    <mergeCell ref="G170:G171"/>
-    <mergeCell ref="G176:G177"/>
-    <mergeCell ref="G142:G143"/>
-    <mergeCell ref="A170:A171"/>
-    <mergeCell ref="B170:B171"/>
-    <mergeCell ref="C170:C171"/>
-    <mergeCell ref="G168:G169"/>
-    <mergeCell ref="A172:A173"/>
-    <mergeCell ref="A180:A181"/>
-    <mergeCell ref="B180:B181"/>
-    <mergeCell ref="A136:A137"/>
-    <mergeCell ref="A126:A127"/>
-    <mergeCell ref="B126:B127"/>
-    <mergeCell ref="C126:C127"/>
-    <mergeCell ref="B136:B137"/>
-    <mergeCell ref="C136:C137"/>
-    <mergeCell ref="G148:G149"/>
-    <mergeCell ref="A150:A151"/>
-    <mergeCell ref="A160:A161"/>
-    <mergeCell ref="B160:B161"/>
-    <mergeCell ref="C160:C161"/>
-    <mergeCell ref="G128:G129"/>
-    <mergeCell ref="A154:A155"/>
-    <mergeCell ref="A138:A139"/>
-    <mergeCell ref="G140:G141"/>
-    <mergeCell ref="G134:G135"/>
-    <mergeCell ref="A128:A129"/>
-    <mergeCell ref="B128:B129"/>
-    <mergeCell ref="B148:B149"/>
-    <mergeCell ref="C148:C149"/>
-    <mergeCell ref="G146:G147"/>
-    <mergeCell ref="A144:A145"/>
-    <mergeCell ref="B144:B145"/>
-    <mergeCell ref="C144:C145"/>
-    <mergeCell ref="A140:A141"/>
-    <mergeCell ref="B140:B141"/>
-    <mergeCell ref="C140:C141"/>
-    <mergeCell ref="G136:G137"/>
-    <mergeCell ref="A132:A133"/>
-    <mergeCell ref="A130:A131"/>
-    <mergeCell ref="B130:B131"/>
-    <mergeCell ref="C128:C129"/>
-    <mergeCell ref="A142:A143"/>
-    <mergeCell ref="B142:B143"/>
-    <mergeCell ref="A148:A149"/>
-    <mergeCell ref="G84:G85"/>
-    <mergeCell ref="G92:G93"/>
-    <mergeCell ref="G82:G83"/>
-    <mergeCell ref="G90:G91"/>
-    <mergeCell ref="G100:G101"/>
-    <mergeCell ref="C138:C139"/>
-    <mergeCell ref="G138:G139"/>
-    <mergeCell ref="G116:G117"/>
-    <mergeCell ref="G108:G109"/>
-    <mergeCell ref="G110:G111"/>
-    <mergeCell ref="C110:C111"/>
-    <mergeCell ref="C102:C103"/>
-    <mergeCell ref="C114:C115"/>
-    <mergeCell ref="C112:C113"/>
-    <mergeCell ref="C116:C117"/>
-    <mergeCell ref="G122:G123"/>
-    <mergeCell ref="C122:C123"/>
-    <mergeCell ref="C82:C83"/>
-    <mergeCell ref="G132:G133"/>
-    <mergeCell ref="G106:G107"/>
-    <mergeCell ref="G96:G97"/>
-    <mergeCell ref="G102:G103"/>
-    <mergeCell ref="G126:G127"/>
-    <mergeCell ref="A114:A115"/>
-    <mergeCell ref="B114:B115"/>
-    <mergeCell ref="A112:A113"/>
-    <mergeCell ref="B112:B113"/>
-    <mergeCell ref="A116:A117"/>
-    <mergeCell ref="B116:B117"/>
-    <mergeCell ref="A122:A123"/>
-    <mergeCell ref="B122:B123"/>
-    <mergeCell ref="G98:G99"/>
-    <mergeCell ref="A108:A109"/>
-    <mergeCell ref="B108:B109"/>
-    <mergeCell ref="C108:C109"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="B110:B111"/>
-    <mergeCell ref="A98:A99"/>
-    <mergeCell ref="A100:A101"/>
-    <mergeCell ref="B100:B101"/>
-    <mergeCell ref="C100:C101"/>
-    <mergeCell ref="A110:A111"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="A94:A95"/>
-    <mergeCell ref="B94:B95"/>
-    <mergeCell ref="B104:B105"/>
-    <mergeCell ref="C104:C105"/>
-    <mergeCell ref="A96:A97"/>
-    <mergeCell ref="B96:B97"/>
-    <mergeCell ref="C96:C97"/>
-    <mergeCell ref="B98:B99"/>
-    <mergeCell ref="C98:C99"/>
-    <mergeCell ref="A102:A103"/>
-    <mergeCell ref="B102:B103"/>
-    <mergeCell ref="C218:C219"/>
-    <mergeCell ref="G68:G69"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="G72:G73"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="G74:G75"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="G76:G77"/>
-    <mergeCell ref="C76:C77"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="C74:C75"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="C86:C87"/>
-    <mergeCell ref="A86:A87"/>
-    <mergeCell ref="B86:B87"/>
-    <mergeCell ref="G80:G81"/>
-    <mergeCell ref="C88:C89"/>
-    <mergeCell ref="C94:C95"/>
-    <mergeCell ref="G94:G95"/>
-    <mergeCell ref="G192:G193"/>
-    <mergeCell ref="C224:C225"/>
-    <mergeCell ref="G222:G223"/>
-    <mergeCell ref="G198:G199"/>
-    <mergeCell ref="A224:A225"/>
-    <mergeCell ref="G220:G221"/>
-    <mergeCell ref="A210:A211"/>
-    <mergeCell ref="B210:B211"/>
-    <mergeCell ref="C210:C211"/>
-    <mergeCell ref="G224:G225"/>
-    <mergeCell ref="B224:B225"/>
-    <mergeCell ref="A222:A223"/>
-    <mergeCell ref="B222:B223"/>
-    <mergeCell ref="C222:C223"/>
-    <mergeCell ref="G218:G219"/>
-    <mergeCell ref="A212:A213"/>
-    <mergeCell ref="B212:B213"/>
-    <mergeCell ref="C212:C213"/>
-    <mergeCell ref="B214:B215"/>
-    <mergeCell ref="C214:C215"/>
-    <mergeCell ref="A208:A209"/>
-    <mergeCell ref="A220:A221"/>
-    <mergeCell ref="B220:B221"/>
-    <mergeCell ref="C220:C221"/>
-    <mergeCell ref="C178:C179"/>
-    <mergeCell ref="A214:A215"/>
-    <mergeCell ref="G212:G213"/>
-    <mergeCell ref="G196:G197"/>
-    <mergeCell ref="C182:C183"/>
-    <mergeCell ref="G180:G181"/>
-    <mergeCell ref="A164:A165"/>
-    <mergeCell ref="B164:B165"/>
-    <mergeCell ref="C164:C165"/>
-    <mergeCell ref="G190:G191"/>
-    <mergeCell ref="A178:A179"/>
-    <mergeCell ref="B178:B179"/>
-    <mergeCell ref="G164:G165"/>
-    <mergeCell ref="G200:G201"/>
-    <mergeCell ref="A198:A199"/>
-    <mergeCell ref="B198:B199"/>
-    <mergeCell ref="C198:C199"/>
-    <mergeCell ref="G194:G195"/>
-    <mergeCell ref="A186:A187"/>
-    <mergeCell ref="B186:B187"/>
-    <mergeCell ref="C188:C189"/>
-    <mergeCell ref="B184:B185"/>
-    <mergeCell ref="C184:C185"/>
-    <mergeCell ref="G184:G185"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="G216:G217"/>
-    <mergeCell ref="B216:B217"/>
-    <mergeCell ref="B208:B209"/>
-    <mergeCell ref="A106:A107"/>
-    <mergeCell ref="A218:A219"/>
-    <mergeCell ref="B218:B219"/>
-    <mergeCell ref="C216:C217"/>
-    <mergeCell ref="G208:G209"/>
-    <mergeCell ref="A206:A207"/>
-    <mergeCell ref="B206:B207"/>
-    <mergeCell ref="C206:C207"/>
-    <mergeCell ref="G206:G207"/>
-    <mergeCell ref="A204:A205"/>
-    <mergeCell ref="B204:B205"/>
-    <mergeCell ref="C204:C205"/>
-    <mergeCell ref="G204:G205"/>
-    <mergeCell ref="G210:G211"/>
-    <mergeCell ref="A216:A217"/>
-    <mergeCell ref="G112:G113"/>
-    <mergeCell ref="G124:G125"/>
-    <mergeCell ref="B166:B167"/>
-    <mergeCell ref="C166:C167"/>
-    <mergeCell ref="B168:B169"/>
-    <mergeCell ref="G78:G79"/>
-    <mergeCell ref="A202:A203"/>
-    <mergeCell ref="B202:B203"/>
-    <mergeCell ref="C202:C203"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="A92:A93"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="G64:G65"/>
-    <mergeCell ref="B106:B107"/>
-    <mergeCell ref="C106:C107"/>
-    <mergeCell ref="G104:G105"/>
-    <mergeCell ref="A70:A71"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="C70:C71"/>
-    <mergeCell ref="G70:G71"/>
-    <mergeCell ref="A90:A91"/>
-    <mergeCell ref="G66:G67"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="B84:B85"/>
-    <mergeCell ref="C84:C85"/>
-    <mergeCell ref="A88:A89"/>
-    <mergeCell ref="B88:B89"/>
-    <mergeCell ref="C92:C93"/>
-    <mergeCell ref="C200:C201"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="A31:H31"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A196:A197"/>
-    <mergeCell ref="B196:B197"/>
-    <mergeCell ref="C196:C197"/>
-    <mergeCell ref="A192:A193"/>
-    <mergeCell ref="B192:B193"/>
-    <mergeCell ref="C192:C193"/>
-    <mergeCell ref="G86:G87"/>
-    <mergeCell ref="A120:A121"/>
-    <mergeCell ref="B120:B121"/>
-    <mergeCell ref="C120:C121"/>
-    <mergeCell ref="G118:G119"/>
-    <mergeCell ref="A80:A81"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="C80:C81"/>
-    <mergeCell ref="A78:A79"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="A245:H245"/>
-    <mergeCell ref="A253:H253"/>
-    <mergeCell ref="A254:H254"/>
-    <mergeCell ref="C246:F246"/>
-    <mergeCell ref="C247:F247"/>
-    <mergeCell ref="C248:F248"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="G62:G63"/>
-    <mergeCell ref="C68:C69"/>
-    <mergeCell ref="G202:G203"/>
-    <mergeCell ref="A194:A195"/>
-    <mergeCell ref="B194:B195"/>
-    <mergeCell ref="C194:C195"/>
-    <mergeCell ref="A200:A201"/>
-    <mergeCell ref="B200:B201"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/main/resources/InesModResources/杀戮尖塔自制--伊内丝v0.2.xlsx
+++ b/src/main/resources/InesModResources/杀戮尖塔自制--伊内丝v0.2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\myMod\InesMod\InesMod\src\main\resources\InesModResources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE0E11B3-35A7-4BB4-9F9F-4B402D9C97D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A701F195-1DC5-4C3F-BB71-46DAB5EADBDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{7A3E14A4-2175-4856-859A-887D335814F1}"/>
   </bookViews>

--- a/src/main/resources/InesModResources/杀戮尖塔自制--伊内丝v0.2.xlsx
+++ b/src/main/resources/InesModResources/杀戮尖塔自制--伊内丝v0.2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\myMod\InesMod\InesMod\src\main\resources\InesModResources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A701F195-1DC5-4C3F-BB71-46DAB5EADBDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{835FC10C-B651-4740-9049-EA8938DB6888}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{7A3E14A4-2175-4856-859A-887D335814F1}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="668">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="668">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1898,19 +1898,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>抽2张牌。获得2层偷取和1点能量。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>从列表中删除此牌并使用一个能力记录一个copy，下回合将copy加入手牌。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>*种类为深灰色的是额外卡组，大后期再考虑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>必须有1点情报才能打出。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2090,23 +2082,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>消耗1点情报打出。增加随机1张能力牌到你的手牌，使其耗能变为0。消耗。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>给予1层虚弱。如果目标的意图不为攻击，额外给予1层虚弱。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>给予1层虚弱。如果目标的意图不为攻击，额外给予2层虚弱。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>现在与接下来3个回合开始时，增加1张小刀到你的手牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>现在与接下来5个回合开始时，增加1张小刀到你的手牌。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2551,6 +2531,26 @@
   <si>
     <t>实际为获得1层同名buff（效果可叠加，可跨回合），达到条件时触发。
 正在结束回合时，不触发。（下）回合抽牌前，触发。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>抽2张牌。获得1层偷取和1点能量。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以触发 临时补给 和 临时战略</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>消耗1张牌以打出。增加随机1张能力牌到你的手牌，使其耗能变为0。消耗。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>现在与接下来3个回合开始时，增加2张小刀到你的手牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>现在与接下来5个回合开始时，增加2张小刀到你的手牌。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2752,7 +2752,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2871,9 +2871,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3230,7 +3227,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42CD751D-9911-4397-9269-1058B93A73AF}">
-  <dimension ref="A1:L254"/>
+  <dimension ref="A1:K254"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="3" width="9.1328125" customWidth="1"/>
@@ -3343,7 +3340,7 @@
       <c r="D10" s="37"/>
       <c r="E10" s="38"/>
       <c r="F10" s="9" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="G10" s="10"/>
       <c r="H10" s="17" t="s">
@@ -3363,7 +3360,7 @@
       <c r="D11" s="37"/>
       <c r="E11" s="38"/>
       <c r="F11" s="9" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="G11" s="10"/>
       <c r="H11" s="17" t="s">
@@ -3473,7 +3470,7 @@
         <v>456</v>
       </c>
       <c r="C20" s="25" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="D20" s="26"/>
       <c r="E20" s="26"/>
@@ -3493,7 +3490,7 @@
         <v>456</v>
       </c>
       <c r="C21" s="25" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="D21" s="26"/>
       <c r="E21" s="26"/>
@@ -3533,13 +3530,13 @@
         <v>456</v>
       </c>
       <c r="C23" s="25" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="D23" s="26"/>
       <c r="E23" s="26"/>
       <c r="F23" s="27"/>
       <c r="G23" s="4" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="H23" s="16" t="s">
         <v>444</v>
@@ -3559,7 +3556,7 @@
       <c r="E24" s="26"/>
       <c r="F24" s="27"/>
       <c r="G24" s="5" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="H24" s="16" t="s">
         <v>481</v>
@@ -3587,20 +3584,20 @@
     </row>
     <row r="26" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="20" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>458</v>
       </c>
       <c r="C26" s="25" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="D26" s="26"/>
       <c r="E26" s="26"/>
       <c r="F26" s="27"/>
       <c r="G26" s="4"/>
       <c r="H26" s="16" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
@@ -3617,7 +3614,7 @@
       <c r="E27" s="26"/>
       <c r="F27" s="27"/>
       <c r="G27" s="4" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="H27" s="16" t="s">
         <v>467</v>
@@ -3684,7 +3681,7 @@
         <v>456</v>
       </c>
       <c r="C34" s="25" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
       <c r="D34" s="26"/>
       <c r="E34" s="26"/>
@@ -3702,7 +3699,7 @@
         <v>456</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="D35" s="26"/>
       <c r="E35" s="26"/>
@@ -3714,20 +3711,20 @@
     </row>
     <row r="36" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="19" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>456</v>
       </c>
       <c r="C36" s="25" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="D36" s="26"/>
       <c r="E36" s="26"/>
       <c r="F36" s="27"/>
       <c r="G36" s="5"/>
       <c r="H36" s="16" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
     </row>
     <row r="37" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
@@ -3738,7 +3735,7 @@
         <v>456</v>
       </c>
       <c r="C37" s="25" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="D37" s="26"/>
       <c r="E37" s="26"/>
@@ -3827,7 +3824,7 @@
     </row>
     <row r="45" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="F45" s="3" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="H45" s="2"/>
     </row>
@@ -3848,7 +3845,7 @@
     </row>
     <row r="48" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="29" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B48" s="29"/>
       <c r="C48" s="29"/>
@@ -3858,7 +3855,7 @@
       <c r="G48" s="29"/>
       <c r="H48" s="29"/>
     </row>
-    <row r="49" spans="1:12" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:11" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="1" t="s">
         <v>0</v>
       </c>
@@ -3884,8 +3881,8 @@
         <v>287</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="40">
+    <row r="50" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A50" s="34">
         <v>1</v>
       </c>
       <c r="B50" s="39" t="s">
@@ -3908,8 +3905,8 @@
         <v>296</v>
       </c>
     </row>
-    <row r="51" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="40"/>
+    <row r="51" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A51" s="35"/>
       <c r="B51" s="39"/>
       <c r="C51" s="29"/>
       <c r="D51" s="6" t="s">
@@ -3928,9 +3925,8 @@
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
       <c r="K51" s="2"/>
-      <c r="L51" s="2"/>
-    </row>
-    <row r="52" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="52" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="34">
         <v>2</v>
       </c>
@@ -3956,9 +3952,8 @@
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
-      <c r="L52" s="2"/>
-    </row>
-    <row r="53" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="53" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="35"/>
       <c r="B53" s="39"/>
       <c r="C53" s="29"/>
@@ -3978,9 +3973,8 @@
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
-      <c r="L53" s="2"/>
-    </row>
-    <row r="54" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="54" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="34">
         <v>3</v>
       </c>
@@ -4006,9 +4000,8 @@
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
-      <c r="L54" s="2"/>
-    </row>
-    <row r="55" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="55" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="35"/>
       <c r="B55" s="39"/>
       <c r="C55" s="29"/>
@@ -4019,7 +4012,7 @@
         <v>1</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>509</v>
+        <v>663</v>
       </c>
       <c r="G55" s="28"/>
       <c r="H55" s="15" t="s">
@@ -4028,9 +4021,8 @@
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
       <c r="K55" s="2"/>
-      <c r="L55" s="2"/>
-    </row>
-    <row r="56" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="56" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="34">
         <v>4</v>
       </c>
@@ -4056,9 +4048,8 @@
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
       <c r="K56" s="2"/>
-      <c r="L56" s="2"/>
-    </row>
-    <row r="57" spans="1:12" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="57" spans="1:11" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="35"/>
       <c r="B57" s="39"/>
       <c r="C57" s="29"/>
@@ -4078,9 +4069,8 @@
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
       <c r="K57" s="2"/>
-      <c r="L57" s="2"/>
-    </row>
-    <row r="58" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="58" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="34">
         <v>5</v>
       </c>
@@ -4108,9 +4098,8 @@
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
       <c r="K58" s="2"/>
-      <c r="L58" s="2"/>
-    </row>
-    <row r="59" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="59" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="35"/>
       <c r="B59" s="30"/>
       <c r="C59" s="29"/>
@@ -4121,7 +4110,7 @@
         <v>1</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="G59" s="28"/>
       <c r="H59" s="15" t="s">
@@ -4130,9 +4119,8 @@
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
       <c r="K59" s="2"/>
-      <c r="L59" s="2"/>
-    </row>
-    <row r="60" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="60" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="34">
         <v>6</v>
       </c>
@@ -4149,7 +4137,7 @@
         <v>0</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="G60" s="28"/>
       <c r="H60" s="15" t="s">
@@ -4158,9 +4146,8 @@
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
       <c r="K60" s="2"/>
-      <c r="L60" s="2"/>
-    </row>
-    <row r="61" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="61" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="35"/>
       <c r="B61" s="30"/>
       <c r="C61" s="29"/>
@@ -4171,7 +4158,7 @@
         <v>0</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="G61" s="28"/>
       <c r="H61" s="15" t="s">
@@ -4180,9 +4167,8 @@
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
       <c r="K61" s="2"/>
-      <c r="L61" s="2"/>
-    </row>
-    <row r="62" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="62" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="34">
         <v>7</v>
       </c>
@@ -4208,9 +4194,8 @@
       <c r="I62" s="2"/>
       <c r="J62" s="2"/>
       <c r="K62" s="2"/>
-      <c r="L62" s="2"/>
-    </row>
-    <row r="63" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="63" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="35"/>
       <c r="B63" s="30"/>
       <c r="C63" s="29"/>
@@ -4230,9 +4215,8 @@
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
       <c r="K63" s="2"/>
-      <c r="L63" s="2"/>
-    </row>
-    <row r="64" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="64" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="34">
         <v>8</v>
       </c>
@@ -4249,10 +4233,10 @@
         <v>0</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="G64" s="28" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="H64" s="15" t="s">
         <v>301</v>
@@ -4260,9 +4244,8 @@
       <c r="I64" s="2"/>
       <c r="J64" s="2"/>
       <c r="K64" s="2"/>
-      <c r="L64" s="2"/>
-    </row>
-    <row r="65" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="65" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="35"/>
       <c r="B65" s="30"/>
       <c r="C65" s="29"/>
@@ -4273,7 +4256,7 @@
         <v>0</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="G65" s="28"/>
       <c r="H65" s="15" t="s">
@@ -4282,9 +4265,8 @@
       <c r="I65" s="2"/>
       <c r="J65" s="2"/>
       <c r="K65" s="2"/>
-      <c r="L65" s="2"/>
-    </row>
-    <row r="66" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="66" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="34">
         <v>9</v>
       </c>
@@ -4301,16 +4283,16 @@
         <v>1</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="G66" s="28" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="H66" s="15" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="35"/>
       <c r="B67" s="30"/>
       <c r="C67" s="29"/>
@@ -4321,14 +4303,14 @@
         <v>1</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="G67" s="28"/>
       <c r="H67" s="15" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="34">
         <v>10</v>
       </c>
@@ -4345,10 +4327,10 @@
         <v>1</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="G68" s="28" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="H68" s="15" t="s">
         <v>303</v>
@@ -4356,9 +4338,8 @@
       <c r="I68" s="2"/>
       <c r="J68" s="2"/>
       <c r="K68" s="2"/>
-      <c r="L68" s="2"/>
-    </row>
-    <row r="69" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="69" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="35"/>
       <c r="B69" s="30"/>
       <c r="C69" s="29"/>
@@ -4369,7 +4350,7 @@
         <v>1</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="G69" s="28"/>
       <c r="H69" s="15" t="s">
@@ -4378,9 +4359,8 @@
       <c r="I69" s="2"/>
       <c r="J69" s="2"/>
       <c r="K69" s="2"/>
-      <c r="L69" s="2"/>
-    </row>
-    <row r="70" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="70" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="34">
         <v>11</v>
       </c>
@@ -4397,10 +4377,10 @@
         <v>0</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="G70" s="28" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="H70" s="15" t="s">
         <v>304</v>
@@ -4408,9 +4388,8 @@
       <c r="I70" s="2"/>
       <c r="J70" s="2"/>
       <c r="K70" s="2"/>
-      <c r="L70" s="2"/>
-    </row>
-    <row r="71" spans="1:12" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="71" spans="1:11" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="35"/>
       <c r="B71" s="30"/>
       <c r="C71" s="29"/>
@@ -4421,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="G71" s="28"/>
       <c r="H71" s="15" t="s">
@@ -4430,9 +4409,8 @@
       <c r="I71" s="2"/>
       <c r="J71" s="2"/>
       <c r="K71" s="2"/>
-      <c r="L71" s="2"/>
-    </row>
-    <row r="72" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="72" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="34">
         <v>12</v>
       </c>
@@ -4449,10 +4427,10 @@
         <v>0</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="G72" s="28" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="H72" s="15" t="s">
         <v>305</v>
@@ -4460,9 +4438,8 @@
       <c r="I72" s="2"/>
       <c r="J72" s="2"/>
       <c r="K72" s="2"/>
-      <c r="L72" s="2"/>
-    </row>
-    <row r="73" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="73" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="35"/>
       <c r="B73" s="33"/>
       <c r="C73" s="29"/>
@@ -4473,7 +4450,7 @@
         <v>0</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="G73" s="28"/>
       <c r="H73" s="15" t="s">
@@ -4482,9 +4459,8 @@
       <c r="I73" s="2"/>
       <c r="J73" s="2"/>
       <c r="K73" s="2"/>
-      <c r="L73" s="2"/>
-    </row>
-    <row r="74" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="74" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="34">
         <v>13</v>
       </c>
@@ -4501,18 +4477,17 @@
         <v>0</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="G74" s="28"/>
       <c r="H74" s="15" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="I74" s="2"/>
       <c r="J74" s="2"/>
       <c r="K74" s="2"/>
-      <c r="L74" s="2"/>
-    </row>
-    <row r="75" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="75" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="35"/>
       <c r="B75" s="33"/>
       <c r="C75" s="29"/>
@@ -4523,18 +4498,17 @@
         <v>0</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="G75" s="28"/>
       <c r="H75" s="15" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="I75" s="2"/>
       <c r="J75" s="2"/>
       <c r="K75" s="2"/>
-      <c r="L75" s="2"/>
-    </row>
-    <row r="76" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="76" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="34">
         <v>14</v>
       </c>
@@ -4554,7 +4528,7 @@
         <v>469</v>
       </c>
       <c r="G76" s="28" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="H76" s="15" t="s">
         <v>306</v>
@@ -4562,9 +4536,8 @@
       <c r="I76" s="2"/>
       <c r="J76" s="2"/>
       <c r="K76" s="2"/>
-      <c r="L76" s="2"/>
-    </row>
-    <row r="77" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="77" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="35"/>
       <c r="B77" s="33"/>
       <c r="C77" s="29"/>
@@ -4582,7 +4555,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="34">
         <v>15</v>
       </c>
@@ -4599,16 +4572,16 @@
         <v>2</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="G78" s="28" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="H78" s="15" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="35"/>
       <c r="B79" s="33"/>
       <c r="C79" s="29"/>
@@ -4619,21 +4592,21 @@
         <v>2</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="G79" s="28"/>
       <c r="H79" s="15" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="34">
         <v>16</v>
       </c>
       <c r="B80" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C80" s="50" t="s">
+      <c r="C80" s="49" t="s">
         <v>6</v>
       </c>
       <c r="D80" s="5" t="s">
@@ -4643,19 +4616,19 @@
         <v>2</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="G80" s="28" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="H80" s="15" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
     </row>
     <row r="81" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="35"/>
       <c r="B81" s="33"/>
-      <c r="C81" s="51"/>
+      <c r="C81" s="50"/>
       <c r="D81" s="5" t="s">
         <v>121</v>
       </c>
@@ -4663,11 +4636,11 @@
         <v>2</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="G81" s="28"/>
       <c r="H81" s="15" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4687,10 +4660,10 @@
         <v>1</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="G82" s="28" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="H82" s="15" t="s">
         <v>308</v>
@@ -4715,13 +4688,13 @@
       </c>
     </row>
     <row r="84" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A84" s="43">
+      <c r="A84" s="42">
         <v>18</v>
       </c>
       <c r="B84" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C84" s="45" t="s">
+      <c r="C84" s="44" t="s">
         <v>6</v>
       </c>
       <c r="D84" s="5" t="s">
@@ -4741,9 +4714,9 @@
       </c>
     </row>
     <row r="85" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A85" s="44"/>
+      <c r="A85" s="43"/>
       <c r="B85" s="33"/>
-      <c r="C85" s="45"/>
+      <c r="C85" s="44"/>
       <c r="D85" s="5" t="s">
         <v>42</v>
       </c>
@@ -4775,7 +4748,7 @@
         <v>1</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="G86" s="28"/>
       <c r="H86" s="15" t="s">
@@ -4793,7 +4766,7 @@
         <v>1</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="G87" s="28"/>
       <c r="H87" s="15" t="s">
@@ -4801,7 +4774,7 @@
       </c>
     </row>
     <row r="88" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A88" s="43">
+      <c r="A88" s="42">
         <v>20</v>
       </c>
       <c r="B88" s="31" t="s">
@@ -4827,7 +4800,7 @@
       </c>
     </row>
     <row r="89" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A89" s="44"/>
+      <c r="A89" s="43"/>
       <c r="B89" s="31"/>
       <c r="C89" s="29"/>
       <c r="D89" s="5" t="s">
@@ -4845,7 +4818,7 @@
       </c>
     </row>
     <row r="90" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A90" s="43">
+      <c r="A90" s="42">
         <v>21</v>
       </c>
       <c r="B90" s="31" t="s">
@@ -4861,17 +4834,17 @@
         <v>0</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="G90" s="28" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H90" s="15" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="91" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A91" s="44"/>
+      <c r="A91" s="43"/>
       <c r="B91" s="31"/>
       <c r="C91" s="29"/>
       <c r="D91" s="5" t="s">
@@ -4881,7 +4854,7 @@
         <v>0</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="G91" s="28"/>
       <c r="H91" s="15" t="s">
@@ -4949,7 +4922,7 @@
         <v>2</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="G94" s="28" t="s">
         <v>275</v>
@@ -4969,7 +4942,7 @@
         <v>2</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="G95" s="28"/>
       <c r="H95" s="15" t="s">
@@ -4977,7 +4950,7 @@
       </c>
     </row>
     <row r="96" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A96" s="43">
+      <c r="A96" s="42">
         <v>24</v>
       </c>
       <c r="B96" s="31" t="s">
@@ -4993,7 +4966,7 @@
         <v>43</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="G96" s="28" t="s">
         <v>198</v>
@@ -5003,7 +4976,7 @@
       </c>
     </row>
     <row r="97" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A97" s="44"/>
+      <c r="A97" s="43"/>
       <c r="B97" s="31"/>
       <c r="C97" s="29"/>
       <c r="D97" s="5" t="s">
@@ -5013,7 +4986,7 @@
         <v>43</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="G97" s="28"/>
       <c r="H97" s="15" t="s">
@@ -5037,7 +5010,7 @@
         <v>0</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="G98" s="28"/>
       <c r="H98" s="15" t="s">
@@ -5055,7 +5028,7 @@
         <v>0</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="G99" s="28"/>
       <c r="H99" s="15" t="s">
@@ -5063,13 +5036,13 @@
       </c>
     </row>
     <row r="100" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A100" s="43">
+      <c r="A100" s="42">
         <v>26</v>
       </c>
       <c r="B100" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C100" s="45" t="s">
+      <c r="C100" s="44" t="s">
         <v>14</v>
       </c>
       <c r="D100" s="5" t="s">
@@ -5079,7 +5052,7 @@
         <v>1</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="G100" s="28"/>
       <c r="H100" s="15" t="s">
@@ -5087,9 +5060,9 @@
       </c>
     </row>
     <row r="101" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A101" s="44"/>
+      <c r="A101" s="43"/>
       <c r="B101" s="30"/>
-      <c r="C101" s="45"/>
+      <c r="C101" s="44"/>
       <c r="D101" s="5" t="s">
         <v>158</v>
       </c>
@@ -5097,7 +5070,7 @@
         <v>1</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="G101" s="28"/>
       <c r="H101" s="15" t="s">
@@ -5121,7 +5094,7 @@
         <v>1</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="G102" s="28"/>
       <c r="H102" s="15" t="s">
@@ -5139,7 +5112,7 @@
         <v>1</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="G103" s="28"/>
       <c r="H103" s="15" t="s">
@@ -5157,17 +5130,17 @@
         <v>14</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>66</v>
+        <v>149</v>
       </c>
       <c r="E104" s="1">
         <v>1</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>559</v>
+        <v>665</v>
       </c>
       <c r="G104" s="28"/>
       <c r="H104" s="15" t="s">
-        <v>318</v>
+        <v>335</v>
       </c>
     </row>
     <row r="105" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5175,21 +5148,21 @@
       <c r="B105" s="30"/>
       <c r="C105" s="29"/>
       <c r="D105" s="5" t="s">
-        <v>67</v>
+        <v>150</v>
       </c>
       <c r="E105" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>560</v>
+        <v>665</v>
       </c>
       <c r="G105" s="28"/>
       <c r="H105" s="15" t="s">
-        <v>380</v>
+        <v>399</v>
       </c>
     </row>
     <row r="106" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A106" s="43">
+      <c r="A106" s="42">
         <v>29</v>
       </c>
       <c r="B106" s="30" t="s">
@@ -5208,14 +5181,14 @@
         <v>272</v>
       </c>
       <c r="G106" s="28" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H106" s="15" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="107" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A107" s="44"/>
+      <c r="A107" s="43"/>
       <c r="B107" s="30"/>
       <c r="C107" s="29"/>
       <c r="D107" s="5" t="s">
@@ -5249,7 +5222,7 @@
         <v>1</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="G108" s="28" t="s">
         <v>217</v>
@@ -5269,7 +5242,7 @@
         <v>1</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="G109" s="28"/>
       <c r="H109" s="15" t="s">
@@ -5280,7 +5253,7 @@
       <c r="A110" s="34">
         <v>31</v>
       </c>
-      <c r="B110" s="41" t="s">
+      <c r="B110" s="40" t="s">
         <v>17</v>
       </c>
       <c r="C110" s="32" t="s">
@@ -5293,9 +5266,9 @@
         <v>1</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>622</v>
-      </c>
-      <c r="G110" s="46" t="s">
+        <v>617</v>
+      </c>
+      <c r="G110" s="45" t="s">
         <v>254</v>
       </c>
       <c r="H110" s="15" t="s">
@@ -5304,7 +5277,7 @@
     </row>
     <row r="111" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="35"/>
-      <c r="B111" s="42"/>
+      <c r="B111" s="41"/>
       <c r="C111" s="32"/>
       <c r="D111" s="5" t="s">
         <v>188</v>
@@ -5313,21 +5286,21 @@
         <v>1</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>623</v>
-      </c>
-      <c r="G111" s="47"/>
+        <v>618</v>
+      </c>
+      <c r="G111" s="46"/>
       <c r="H111" s="15" t="s">
         <v>383</v>
       </c>
     </row>
     <row r="112" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A112" s="43">
+      <c r="A112" s="42">
         <v>32</v>
       </c>
       <c r="B112" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C112" s="45" t="s">
+      <c r="C112" s="44" t="s">
         <v>14</v>
       </c>
       <c r="D112" s="5" t="s">
@@ -5345,9 +5318,9 @@
       </c>
     </row>
     <row r="113" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A113" s="44"/>
+      <c r="A113" s="43"/>
       <c r="B113" s="30"/>
-      <c r="C113" s="45"/>
+      <c r="C113" s="44"/>
       <c r="D113" s="5" t="s">
         <v>52</v>
       </c>
@@ -5379,7 +5352,7 @@
         <v>1</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="G114" s="28"/>
       <c r="H114" s="15" t="s">
@@ -5397,7 +5370,7 @@
         <v>1</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="G115" s="28"/>
       <c r="H115" s="15" t="s">
@@ -5424,7 +5397,7 @@
         <v>197</v>
       </c>
       <c r="G116" s="28" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="H116" s="15" t="s">
         <v>428</v>
@@ -5441,7 +5414,7 @@
         <v>0</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="G117" s="28"/>
       <c r="H117" s="15" t="s">
@@ -5468,10 +5441,10 @@
         <v>196</v>
       </c>
       <c r="G118" s="28" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="H118" s="15" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
     </row>
     <row r="119" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5485,7 +5458,7 @@
         <v>0</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="G119" s="28"/>
       <c r="H119" s="15" t="s">
@@ -5509,7 +5482,7 @@
         <v>0</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="G120" s="28" t="s">
         <v>245</v>
@@ -5529,7 +5502,7 @@
         <v>0</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="G121" s="28"/>
       <c r="H121" s="15" t="s">
@@ -5540,7 +5513,7 @@
       <c r="A122" s="34">
         <v>37</v>
       </c>
-      <c r="B122" s="41" t="s">
+      <c r="B122" s="40" t="s">
         <v>17</v>
       </c>
       <c r="C122" s="29" t="s">
@@ -5553,7 +5526,7 @@
         <v>2</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="G122" s="28"/>
       <c r="H122" s="15" t="s">
@@ -5562,7 +5535,7 @@
     </row>
     <row r="123" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="35"/>
-      <c r="B123" s="42"/>
+      <c r="B123" s="41"/>
       <c r="C123" s="29"/>
       <c r="D123" s="5" t="s">
         <v>180</v>
@@ -5571,7 +5544,7 @@
         <v>1</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="G123" s="28"/>
       <c r="H123" s="15" t="s">
@@ -5582,7 +5555,7 @@
       <c r="A124" s="34">
         <v>38</v>
       </c>
-      <c r="B124" s="41" t="s">
+      <c r="B124" s="40" t="s">
         <v>17</v>
       </c>
       <c r="C124" s="29" t="s">
@@ -5597,14 +5570,16 @@
       <c r="F124" s="5" t="s">
         <v>478</v>
       </c>
-      <c r="G124" s="28"/>
+      <c r="G124" s="28" t="s">
+        <v>664</v>
+      </c>
       <c r="H124" s="15" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="125" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="35"/>
-      <c r="B125" s="42"/>
+      <c r="B125" s="41"/>
       <c r="C125" s="29"/>
       <c r="D125" s="5" t="s">
         <v>54</v>
@@ -5624,7 +5599,7 @@
       <c r="A126" s="34">
         <v>39</v>
       </c>
-      <c r="B126" s="41" t="s">
+      <c r="B126" s="40" t="s">
         <v>17</v>
       </c>
       <c r="C126" s="29" t="s">
@@ -5640,15 +5615,15 @@
         <v>222</v>
       </c>
       <c r="G126" s="28" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="H126" s="15" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="127" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="35"/>
-      <c r="B127" s="42"/>
+      <c r="B127" s="41"/>
       <c r="C127" s="29"/>
       <c r="D127" s="5" t="s">
         <v>131</v>
@@ -5657,18 +5632,18 @@
         <v>0</v>
       </c>
       <c r="F127" s="5" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="G127" s="28"/>
       <c r="H127" s="15" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="128" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A128" s="43">
+      <c r="A128" s="42">
         <v>40</v>
       </c>
-      <c r="B128" s="41" t="s">
+      <c r="B128" s="40" t="s">
         <v>17</v>
       </c>
       <c r="C128" s="29" t="s">
@@ -5689,8 +5664,8 @@
       </c>
     </row>
     <row r="129" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A129" s="44"/>
-      <c r="B129" s="42"/>
+      <c r="A129" s="43"/>
+      <c r="B129" s="41"/>
       <c r="C129" s="29"/>
       <c r="D129" s="5" t="s">
         <v>79</v>
@@ -5710,7 +5685,7 @@
       <c r="A130" s="34">
         <v>41</v>
       </c>
-      <c r="B130" s="41" t="s">
+      <c r="B130" s="40" t="s">
         <v>17</v>
       </c>
       <c r="C130" s="32" t="s">
@@ -5723,7 +5698,7 @@
         <v>1</v>
       </c>
       <c r="F130" s="5" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="G130" s="28"/>
       <c r="H130" s="15" t="s">
@@ -5732,7 +5707,7 @@
     </row>
     <row r="131" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="35"/>
-      <c r="B131" s="42"/>
+      <c r="B131" s="41"/>
       <c r="C131" s="32"/>
       <c r="D131" s="5" t="s">
         <v>65</v>
@@ -5741,7 +5716,7 @@
         <v>1</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="G131" s="28"/>
       <c r="H131" s="15" t="s">
@@ -5749,7 +5724,7 @@
       </c>
     </row>
     <row r="132" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A132" s="34">
+      <c r="A132" s="42">
         <v>42</v>
       </c>
       <c r="B132" s="33" t="s">
@@ -5759,35 +5734,35 @@
         <v>14</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="E132" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F132" s="5" t="s">
-        <v>555</v>
+        <v>666</v>
       </c>
       <c r="G132" s="28"/>
       <c r="H132" s="15" t="s">
-        <v>553</v>
+        <v>318</v>
       </c>
     </row>
     <row r="133" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A133" s="35"/>
+      <c r="A133" s="43"/>
       <c r="B133" s="33"/>
       <c r="C133" s="29"/>
       <c r="D133" s="5" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="E133" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F133" s="5" t="s">
-        <v>552</v>
+        <v>667</v>
       </c>
       <c r="G133" s="28"/>
       <c r="H133" s="15" t="s">
-        <v>554</v>
+        <v>380</v>
       </c>
     </row>
     <row r="134" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5801,17 +5776,19 @@
         <v>14</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>618</v>
+        <v>50</v>
       </c>
       <c r="E134" s="1">
         <v>0</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>663</v>
-      </c>
-      <c r="G134" s="28"/>
+        <v>553</v>
+      </c>
+      <c r="G134" s="28" t="s">
+        <v>664</v>
+      </c>
       <c r="H134" s="15" t="s">
-        <v>620</v>
+        <v>551</v>
       </c>
     </row>
     <row r="135" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5819,17 +5796,17 @@
       <c r="B135" s="33"/>
       <c r="C135" s="29"/>
       <c r="D135" s="5" t="s">
-        <v>619</v>
+        <v>51</v>
       </c>
       <c r="E135" s="1">
         <v>0</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>664</v>
+        <v>550</v>
       </c>
       <c r="G135" s="28"/>
       <c r="H135" s="15" t="s">
-        <v>621</v>
+        <v>552</v>
       </c>
     </row>
     <row r="136" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5843,17 +5820,17 @@
         <v>14</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>48</v>
+        <v>613</v>
       </c>
       <c r="E136" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F136" s="5" t="s">
-        <v>473</v>
+        <v>658</v>
       </c>
       <c r="G136" s="28"/>
       <c r="H136" s="15" t="s">
-        <v>326</v>
+        <v>615</v>
       </c>
     </row>
     <row r="137" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5861,107 +5838,105 @@
       <c r="B137" s="33"/>
       <c r="C137" s="29"/>
       <c r="D137" s="5" t="s">
-        <v>49</v>
+        <v>614</v>
       </c>
       <c r="E137" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>474</v>
+        <v>659</v>
       </c>
       <c r="G137" s="28"/>
       <c r="H137" s="15" t="s">
-        <v>389</v>
+        <v>616</v>
       </c>
     </row>
     <row r="138" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A138" s="43">
+      <c r="A138" s="34">
         <v>45</v>
       </c>
       <c r="B138" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C138" s="45" t="s">
+      <c r="C138" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>177</v>
+        <v>48</v>
       </c>
       <c r="E138" s="1">
         <v>1</v>
       </c>
       <c r="F138" s="5" t="s">
-        <v>212</v>
+        <v>473</v>
       </c>
       <c r="G138" s="28"/>
       <c r="H138" s="15" t="s">
-        <v>451</v>
+        <v>326</v>
       </c>
     </row>
     <row r="139" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A139" s="44"/>
+      <c r="A139" s="35"/>
       <c r="B139" s="33"/>
-      <c r="C139" s="45"/>
+      <c r="C139" s="29"/>
       <c r="D139" s="5" t="s">
-        <v>178</v>
+        <v>49</v>
       </c>
       <c r="E139" s="1">
         <v>1</v>
       </c>
       <c r="F139" s="5" t="s">
-        <v>211</v>
+        <v>474</v>
       </c>
       <c r="G139" s="28"/>
       <c r="H139" s="15" t="s">
-        <v>452</v>
+        <v>389</v>
       </c>
     </row>
     <row r="140" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A140" s="43">
+      <c r="A140" s="42">
         <v>46</v>
       </c>
       <c r="B140" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C140" s="29" t="s">
+      <c r="C140" s="44" t="s">
         <v>14</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>232</v>
+        <v>177</v>
       </c>
       <c r="E140" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F140" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="G140" s="28" t="s">
-        <v>210</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="G140" s="28"/>
       <c r="H140" s="15" t="s">
-        <v>532</v>
+        <v>451</v>
       </c>
     </row>
     <row r="141" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A141" s="44"/>
+      <c r="A141" s="43"/>
       <c r="B141" s="33"/>
-      <c r="C141" s="29"/>
+      <c r="C141" s="44"/>
       <c r="D141" s="5" t="s">
-        <v>233</v>
+        <v>178</v>
       </c>
       <c r="E141" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F141" s="5" t="s">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="G141" s="28"/>
       <c r="H141" s="15" t="s">
-        <v>390</v>
+        <v>452</v>
       </c>
     </row>
     <row r="142" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A142" s="43">
+      <c r="A142" s="42">
         <v>47</v>
       </c>
       <c r="B142" s="33" t="s">
@@ -5971,37 +5946,37 @@
         <v>14</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>164</v>
+        <v>232</v>
       </c>
       <c r="E142" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F142" s="5" t="s">
-        <v>475</v>
+        <v>136</v>
       </c>
       <c r="G142" s="28" t="s">
-        <v>538</v>
+        <v>210</v>
       </c>
       <c r="H142" s="15" t="s">
-        <v>327</v>
+        <v>530</v>
       </c>
     </row>
     <row r="143" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A143" s="44"/>
+      <c r="A143" s="43"/>
       <c r="B143" s="33"/>
       <c r="C143" s="29"/>
       <c r="D143" s="5" t="s">
-        <v>165</v>
+        <v>233</v>
       </c>
       <c r="E143" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F143" s="5" t="s">
-        <v>476</v>
+        <v>137</v>
       </c>
       <c r="G143" s="28"/>
       <c r="H143" s="15" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="144" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6015,17 +5990,19 @@
         <v>14</v>
       </c>
       <c r="D144" s="5" t="s">
-        <v>526</v>
+        <v>164</v>
       </c>
       <c r="E144" s="1">
         <v>1</v>
       </c>
       <c r="F144" s="5" t="s">
-        <v>477</v>
-      </c>
-      <c r="G144" s="28"/>
+        <v>475</v>
+      </c>
+      <c r="G144" s="28" t="s">
+        <v>536</v>
+      </c>
       <c r="H144" s="15" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="145" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6033,103 +6010,103 @@
       <c r="B145" s="33"/>
       <c r="C145" s="29"/>
       <c r="D145" s="5" t="s">
-        <v>55</v>
+        <v>165</v>
       </c>
       <c r="E145" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F145" s="5" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="G145" s="28"/>
       <c r="H145" s="15" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="146" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A146" s="43">
+      <c r="A146" s="34">
         <v>49</v>
       </c>
       <c r="B146" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C146" s="45" t="s">
+      <c r="C146" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>56</v>
+        <v>524</v>
       </c>
       <c r="E146" s="1">
         <v>1</v>
       </c>
       <c r="F146" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="G146" s="28" t="s">
-        <v>538</v>
-      </c>
+        <v>477</v>
+      </c>
+      <c r="G146" s="28"/>
       <c r="H146" s="15" t="s">
-        <v>424</v>
+        <v>329</v>
       </c>
     </row>
     <row r="147" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A147" s="44"/>
+      <c r="A147" s="35"/>
       <c r="B147" s="33"/>
-      <c r="C147" s="45"/>
+      <c r="C147" s="29"/>
       <c r="D147" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E147" s="1">
         <v>0</v>
       </c>
       <c r="F147" s="5" t="s">
-        <v>199</v>
+        <v>477</v>
       </c>
       <c r="G147" s="28"/>
       <c r="H147" s="15" t="s">
-        <v>425</v>
+        <v>393</v>
       </c>
     </row>
     <row r="148" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A148" s="34">
+      <c r="A148" s="42">
         <v>50</v>
       </c>
       <c r="B148" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C148" s="32" t="s">
+      <c r="C148" s="44" t="s">
         <v>14</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E148" s="1">
         <v>1</v>
       </c>
       <c r="F148" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="G148" s="28"/>
+        <v>199</v>
+      </c>
+      <c r="G148" s="28" t="s">
+        <v>536</v>
+      </c>
       <c r="H148" s="15" t="s">
-        <v>500</v>
+        <v>424</v>
       </c>
     </row>
     <row r="149" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A149" s="35"/>
+      <c r="A149" s="43"/>
       <c r="B149" s="33"/>
-      <c r="C149" s="32"/>
+      <c r="C149" s="44"/>
       <c r="D149" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E149" s="1">
         <v>0</v>
       </c>
       <c r="F149" s="5" t="s">
-        <v>274</v>
+        <v>199</v>
       </c>
       <c r="G149" s="28"/>
       <c r="H149" s="15" t="s">
-        <v>501</v>
+        <v>425</v>
       </c>
     </row>
     <row r="150" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6139,39 +6116,39 @@
       <c r="B150" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C150" s="29" t="s">
+      <c r="C150" s="32" t="s">
         <v>14</v>
       </c>
       <c r="D150" s="5" t="s">
-        <v>181</v>
+        <v>58</v>
       </c>
       <c r="E150" s="1">
         <v>1</v>
       </c>
       <c r="F150" s="5" t="s">
-        <v>183</v>
+        <v>274</v>
       </c>
       <c r="G150" s="28"/>
       <c r="H150" s="15" t="s">
-        <v>330</v>
+        <v>500</v>
       </c>
     </row>
     <row r="151" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A151" s="35"/>
       <c r="B151" s="33"/>
-      <c r="C151" s="29"/>
+      <c r="C151" s="32"/>
       <c r="D151" s="5" t="s">
-        <v>182</v>
+        <v>59</v>
       </c>
       <c r="E151" s="1">
         <v>0</v>
       </c>
       <c r="F151" s="5" t="s">
-        <v>183</v>
+        <v>274</v>
       </c>
       <c r="G151" s="28"/>
       <c r="H151" s="15" t="s">
-        <v>394</v>
+        <v>501</v>
       </c>
     </row>
     <row r="152" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6185,17 +6162,17 @@
         <v>14</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>72</v>
+        <v>181</v>
       </c>
       <c r="E152" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F152" s="5" t="s">
-        <v>73</v>
+        <v>183</v>
       </c>
       <c r="G152" s="28"/>
       <c r="H152" s="15" t="s">
-        <v>426</v>
+        <v>330</v>
       </c>
     </row>
     <row r="153" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6203,21 +6180,21 @@
       <c r="B153" s="33"/>
       <c r="C153" s="29"/>
       <c r="D153" s="5" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="E153" s="1">
         <v>0</v>
       </c>
       <c r="F153" s="5" t="s">
-        <v>248</v>
+        <v>183</v>
       </c>
       <c r="G153" s="28"/>
       <c r="H153" s="15" t="s">
-        <v>427</v>
+        <v>394</v>
       </c>
     </row>
     <row r="154" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A154" s="43">
+      <c r="A154" s="34">
         <v>53</v>
       </c>
       <c r="B154" s="33" t="s">
@@ -6227,41 +6204,39 @@
         <v>14</v>
       </c>
       <c r="D154" s="5" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="E154" s="1">
         <v>0</v>
       </c>
       <c r="F154" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="G154" s="28" t="s">
-        <v>602</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="G154" s="28"/>
       <c r="H154" s="15" t="s">
-        <v>453</v>
+        <v>426</v>
       </c>
     </row>
     <row r="155" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A155" s="44"/>
+      <c r="A155" s="35"/>
       <c r="B155" s="33"/>
       <c r="C155" s="29"/>
       <c r="D155" s="5" t="s">
-        <v>63</v>
+        <v>191</v>
       </c>
       <c r="E155" s="1">
         <v>0</v>
       </c>
       <c r="F155" s="5" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="G155" s="28"/>
       <c r="H155" s="15" t="s">
-        <v>454</v>
+        <v>427</v>
       </c>
     </row>
     <row r="156" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A156" s="43">
+      <c r="A156" s="42">
         <v>54</v>
       </c>
       <c r="B156" s="33" t="s">
@@ -6271,39 +6246,41 @@
         <v>14</v>
       </c>
       <c r="D156" s="5" t="s">
-        <v>159</v>
+        <v>62</v>
       </c>
       <c r="E156" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F156" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="G156" s="28"/>
+        <v>252</v>
+      </c>
+      <c r="G156" s="28" t="s">
+        <v>597</v>
+      </c>
       <c r="H156" s="15" t="s">
-        <v>332</v>
+        <v>453</v>
       </c>
     </row>
     <row r="157" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A157" s="44"/>
+      <c r="A157" s="43"/>
       <c r="B157" s="33"/>
       <c r="C157" s="29"/>
       <c r="D157" s="5" t="s">
-        <v>160</v>
+        <v>63</v>
       </c>
       <c r="E157" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F157" s="5" t="s">
-        <v>168</v>
+        <v>253</v>
       </c>
       <c r="G157" s="28"/>
       <c r="H157" s="15" t="s">
-        <v>396</v>
+        <v>454</v>
       </c>
     </row>
     <row r="158" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A158" s="43">
+      <c r="A158" s="42">
         <v>55</v>
       </c>
       <c r="B158" s="33" t="s">
@@ -6313,39 +6290,39 @@
         <v>14</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E158" s="1">
         <v>1</v>
       </c>
       <c r="F158" s="5" t="s">
-        <v>557</v>
+        <v>167</v>
       </c>
       <c r="G158" s="28"/>
       <c r="H158" s="15" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="159" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A159" s="44"/>
+        <v>332</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A159" s="43"/>
       <c r="B159" s="33"/>
       <c r="C159" s="29"/>
       <c r="D159" s="5" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E159" s="1">
         <v>1</v>
       </c>
       <c r="F159" s="5" t="s">
-        <v>558</v>
+        <v>168</v>
       </c>
       <c r="G159" s="28"/>
       <c r="H159" s="15" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="160" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A160" s="43">
+      <c r="A160" s="42">
         <v>56</v>
       </c>
       <c r="B160" s="33" t="s">
@@ -6355,41 +6332,39 @@
         <v>14</v>
       </c>
       <c r="D160" s="5" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="E160" s="1">
         <v>1</v>
       </c>
       <c r="F160" s="5" t="s">
-        <v>556</v>
-      </c>
-      <c r="G160" s="28" t="s">
-        <v>512</v>
-      </c>
+        <v>554</v>
+      </c>
+      <c r="G160" s="28"/>
       <c r="H160" s="15" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="161" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A161" s="44"/>
+        <v>333</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A161" s="43"/>
       <c r="B161" s="33"/>
       <c r="C161" s="29"/>
       <c r="D161" s="5" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="E161" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F161" s="5" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="G161" s="28"/>
       <c r="H161" s="15" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="162" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A162" s="43">
+      <c r="A162" s="42">
         <v>57</v>
       </c>
       <c r="B162" s="33" t="s">
@@ -6408,14 +6383,14 @@
         <v>277</v>
       </c>
       <c r="G162" s="28" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="H162" s="15" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="163" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A163" s="44"/>
+      <c r="A163" s="43"/>
       <c r="B163" s="33"/>
       <c r="C163" s="29"/>
       <c r="D163" s="5" t="s">
@@ -6433,13 +6408,13 @@
       </c>
     </row>
     <row r="164" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A164" s="43">
+      <c r="A164" s="42">
         <v>58</v>
       </c>
       <c r="B164" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C164" s="45" t="s">
+      <c r="C164" s="44" t="s">
         <v>14</v>
       </c>
       <c r="D164" s="5" t="s">
@@ -6457,9 +6432,9 @@
       </c>
     </row>
     <row r="165" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A165" s="44"/>
+      <c r="A165" s="43"/>
       <c r="B165" s="33"/>
-      <c r="C165" s="45"/>
+      <c r="C165" s="44"/>
       <c r="D165" s="5" t="s">
         <v>172</v>
       </c>
@@ -6475,13 +6450,13 @@
       </c>
     </row>
     <row r="166" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A166" s="43">
+      <c r="A166" s="42">
         <v>59</v>
       </c>
       <c r="B166" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C166" s="45" t="s">
+      <c r="C166" s="44" t="s">
         <v>14</v>
       </c>
       <c r="D166" s="5" t="s">
@@ -6491,7 +6466,7 @@
         <v>1</v>
       </c>
       <c r="F166" s="5" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="G166" s="28" t="s">
         <v>192</v>
@@ -6501,9 +6476,9 @@
       </c>
     </row>
     <row r="167" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A167" s="44"/>
+      <c r="A167" s="43"/>
       <c r="B167" s="33"/>
-      <c r="C167" s="45"/>
+      <c r="C167" s="44"/>
       <c r="D167" s="5" t="s">
         <v>142</v>
       </c>
@@ -6511,7 +6486,7 @@
         <v>0</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="G167" s="28"/>
       <c r="H167" s="15" t="s">
@@ -6519,13 +6494,13 @@
       </c>
     </row>
     <row r="168" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A168" s="43">
+      <c r="A168" s="42">
         <v>60</v>
       </c>
       <c r="B168" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C168" s="45" t="s">
+      <c r="C168" s="44" t="s">
         <v>14</v>
       </c>
       <c r="D168" s="5" t="s">
@@ -6535,7 +6510,7 @@
         <v>1</v>
       </c>
       <c r="F168" s="5" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="G168" s="28"/>
       <c r="H168" s="15" t="s">
@@ -6543,9 +6518,9 @@
       </c>
     </row>
     <row r="169" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A169" s="44"/>
+      <c r="A169" s="43"/>
       <c r="B169" s="33"/>
-      <c r="C169" s="45"/>
+      <c r="C169" s="44"/>
       <c r="D169" s="5" t="s">
         <v>116</v>
       </c>
@@ -6553,7 +6528,7 @@
         <v>0</v>
       </c>
       <c r="F169" s="5" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="G169" s="28"/>
       <c r="H169" s="15" t="s">
@@ -6577,13 +6552,13 @@
         <v>2</v>
       </c>
       <c r="F170" s="5" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="G170" s="28" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="H170" s="15" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
     </row>
     <row r="171" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6597,11 +6572,11 @@
         <v>2</v>
       </c>
       <c r="F171" s="5" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="G171" s="28"/>
       <c r="H171" s="15" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
     </row>
     <row r="172" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6615,17 +6590,17 @@
         <v>14</v>
       </c>
       <c r="D172" s="5" t="s">
+        <v>526</v>
+      </c>
+      <c r="E172" s="1">
+        <v>1</v>
+      </c>
+      <c r="F172" s="5" t="s">
         <v>528</v>
-      </c>
-      <c r="E172" s="1">
-        <v>1</v>
-      </c>
-      <c r="F172" s="5" t="s">
-        <v>530</v>
       </c>
       <c r="G172" s="28"/>
       <c r="H172" s="15" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="173" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6633,27 +6608,27 @@
       <c r="B173" s="33"/>
       <c r="C173" s="32"/>
       <c r="D173" s="5" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="E173" s="1">
         <v>1</v>
       </c>
       <c r="F173" s="5" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="G173" s="28"/>
       <c r="H173" s="15" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="174" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A174" s="43">
+      <c r="A174" s="42">
         <v>63</v>
       </c>
       <c r="B174" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C174" s="45" t="s">
+      <c r="C174" s="44" t="s">
         <v>14</v>
       </c>
       <c r="D174" s="5" t="s">
@@ -6663,19 +6638,19 @@
         <v>1</v>
       </c>
       <c r="F174" s="5" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="G174" s="28" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="H174" s="15" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="175" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A175" s="44"/>
+      <c r="A175" s="43"/>
       <c r="B175" s="33"/>
-      <c r="C175" s="45"/>
+      <c r="C175" s="44"/>
       <c r="D175" s="5" t="s">
         <v>195</v>
       </c>
@@ -6683,7 +6658,7 @@
         <v>1</v>
       </c>
       <c r="F175" s="5" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="G175" s="28"/>
       <c r="H175" s="15" t="s">
@@ -6691,7 +6666,7 @@
       </c>
     </row>
     <row r="176" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A176" s="43">
+      <c r="A176" s="42">
         <v>64</v>
       </c>
       <c r="B176" s="33" t="s">
@@ -6707,7 +6682,7 @@
         <v>1</v>
       </c>
       <c r="F176" s="5" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
       <c r="G176" s="28" t="s">
         <v>112</v>
@@ -6717,7 +6692,7 @@
       </c>
     </row>
     <row r="177" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A177" s="44"/>
+      <c r="A177" s="43"/>
       <c r="B177" s="33"/>
       <c r="C177" s="29"/>
       <c r="D177" s="5" t="s">
@@ -6727,7 +6702,7 @@
         <v>1</v>
       </c>
       <c r="F177" s="5" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="G177" s="28"/>
       <c r="H177" s="15" t="s">
@@ -6735,7 +6710,7 @@
       </c>
     </row>
     <row r="178" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A178" s="43">
+      <c r="A178" s="42">
         <v>65</v>
       </c>
       <c r="B178" s="31" t="s">
@@ -6745,39 +6720,39 @@
         <v>14</v>
       </c>
       <c r="D178" s="5" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="E178" s="1">
         <v>1</v>
       </c>
       <c r="F178" s="5" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="G178" s="28"/>
       <c r="H178" s="15" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
     </row>
     <row r="179" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A179" s="44"/>
+      <c r="A179" s="43"/>
       <c r="B179" s="31"/>
       <c r="C179" s="29"/>
       <c r="D179" s="5" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="E179" s="1">
         <v>1</v>
       </c>
       <c r="F179" s="5" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="G179" s="28"/>
       <c r="H179" s="15" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
     </row>
     <row r="180" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A180" s="43">
+      <c r="A180" s="42">
         <v>66</v>
       </c>
       <c r="B180" s="31" t="s">
@@ -6801,7 +6776,7 @@
       </c>
     </row>
     <row r="181" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A181" s="44"/>
+      <c r="A181" s="43"/>
       <c r="B181" s="31"/>
       <c r="C181" s="29"/>
       <c r="D181" s="5" t="s">
@@ -6819,7 +6794,7 @@
       </c>
     </row>
     <row r="182" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A182" s="43">
+      <c r="A182" s="42">
         <v>67</v>
       </c>
       <c r="B182" s="31" t="s">
@@ -6843,7 +6818,7 @@
       </c>
     </row>
     <row r="183" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A183" s="44"/>
+      <c r="A183" s="43"/>
       <c r="B183" s="31"/>
       <c r="C183" s="29"/>
       <c r="D183" s="5" t="s">
@@ -6881,7 +6856,7 @@
       </c>
       <c r="G184" s="28"/>
       <c r="H184" s="15" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="185" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6899,7 +6874,7 @@
       </c>
       <c r="G185" s="28"/>
       <c r="H185" s="15" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="186" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6919,7 +6894,7 @@
         <v>3</v>
       </c>
       <c r="F186" s="5" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="G186" s="28"/>
       <c r="H186" s="15" t="s">
@@ -6937,7 +6912,7 @@
         <v>2</v>
       </c>
       <c r="F187" s="5" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="G187" s="28"/>
       <c r="H187" s="15" t="s">
@@ -6945,13 +6920,13 @@
       </c>
     </row>
     <row r="188" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A188" s="43">
+      <c r="A188" s="42">
         <v>70</v>
       </c>
       <c r="B188" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C188" s="45" t="s">
+      <c r="C188" s="44" t="s">
         <v>14</v>
       </c>
       <c r="D188" s="5" t="s">
@@ -6969,9 +6944,9 @@
       </c>
     </row>
     <row r="189" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A189" s="44"/>
+      <c r="A189" s="43"/>
       <c r="B189" s="31"/>
-      <c r="C189" s="45"/>
+      <c r="C189" s="44"/>
       <c r="D189" s="5" t="s">
         <v>438</v>
       </c>
@@ -6987,13 +6962,13 @@
       </c>
     </row>
     <row r="190" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A190" s="43">
+      <c r="A190" s="42">
         <v>71</v>
       </c>
       <c r="B190" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C190" s="45" t="s">
+      <c r="C190" s="44" t="s">
         <v>14</v>
       </c>
       <c r="D190" s="5" t="s">
@@ -7006,16 +6981,16 @@
         <v>255</v>
       </c>
       <c r="G190" s="28" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="H190" s="15" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="191" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A191" s="44"/>
+      <c r="A191" s="43"/>
       <c r="B191" s="31"/>
-      <c r="C191" s="45"/>
+      <c r="C191" s="44"/>
       <c r="D191" s="5" t="s">
         <v>85</v>
       </c>
@@ -7031,13 +7006,13 @@
       </c>
     </row>
     <row r="192" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A192" s="43">
+      <c r="A192" s="42">
         <v>72</v>
       </c>
       <c r="B192" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C192" s="45" t="s">
+      <c r="C192" s="44" t="s">
         <v>14</v>
       </c>
       <c r="D192" s="5" t="s">
@@ -7047,7 +7022,7 @@
         <v>43</v>
       </c>
       <c r="F192" s="5" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="G192" s="28"/>
       <c r="H192" s="15" t="s">
@@ -7055,9 +7030,9 @@
       </c>
     </row>
     <row r="193" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A193" s="44"/>
+      <c r="A193" s="43"/>
       <c r="B193" s="31"/>
-      <c r="C193" s="45"/>
+      <c r="C193" s="44"/>
       <c r="D193" s="5" t="s">
         <v>185</v>
       </c>
@@ -7073,7 +7048,7 @@
       </c>
     </row>
     <row r="194" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A194" s="43">
+      <c r="A194" s="42">
         <v>73</v>
       </c>
       <c r="B194" s="31" t="s">
@@ -7099,7 +7074,7 @@
       </c>
     </row>
     <row r="195" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A195" s="44"/>
+      <c r="A195" s="43"/>
       <c r="B195" s="31"/>
       <c r="C195" s="29"/>
       <c r="D195" s="5" t="s">
@@ -7117,7 +7092,7 @@
       </c>
     </row>
     <row r="196" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A196" s="43">
+      <c r="A196" s="42">
         <v>74</v>
       </c>
       <c r="B196" s="31" t="s">
@@ -7133,7 +7108,7 @@
         <v>1</v>
       </c>
       <c r="F196" s="5" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="G196" s="28" t="s">
         <v>138</v>
@@ -7143,7 +7118,7 @@
       </c>
     </row>
     <row r="197" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A197" s="44"/>
+      <c r="A197" s="43"/>
       <c r="B197" s="31"/>
       <c r="C197" s="29"/>
       <c r="D197" s="5" t="s">
@@ -7153,7 +7128,7 @@
         <v>1</v>
       </c>
       <c r="F197" s="5" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="G197" s="28"/>
       <c r="H197" s="15" t="s">
@@ -7180,7 +7155,7 @@
         <v>283</v>
       </c>
       <c r="G198" s="28" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="H198" s="15" t="s">
         <v>432</v>
@@ -7205,7 +7180,7 @@
       </c>
     </row>
     <row r="200" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A200" s="43">
+      <c r="A200" s="42">
         <v>76</v>
       </c>
       <c r="B200" s="33" t="s">
@@ -7231,7 +7206,7 @@
       </c>
     </row>
     <row r="201" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A201" s="44"/>
+      <c r="A201" s="43"/>
       <c r="B201" s="33"/>
       <c r="C201" s="29"/>
       <c r="D201" s="5" t="s">
@@ -7265,10 +7240,10 @@
         <v>2</v>
       </c>
       <c r="F202" s="5" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="G202" s="28" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="H202" s="15" t="s">
         <v>348</v>
@@ -7285,7 +7260,7 @@
         <v>2</v>
       </c>
       <c r="F203" s="5" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="G203" s="28"/>
       <c r="H203" s="15" t="s">
@@ -7293,7 +7268,7 @@
       </c>
     </row>
     <row r="204" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A204" s="43">
+      <c r="A204" s="42">
         <v>78</v>
       </c>
       <c r="B204" s="33" t="s">
@@ -7309,7 +7284,7 @@
         <v>1</v>
       </c>
       <c r="F204" s="5" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="G204" s="28"/>
       <c r="H204" s="15" t="s">
@@ -7317,7 +7292,7 @@
       </c>
     </row>
     <row r="205" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A205" s="44"/>
+      <c r="A205" s="43"/>
       <c r="B205" s="33"/>
       <c r="C205" s="29"/>
       <c r="D205" s="5" t="s">
@@ -7335,7 +7310,7 @@
       </c>
     </row>
     <row r="206" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A206" s="43">
+      <c r="A206" s="42">
         <v>79</v>
       </c>
       <c r="B206" s="33" t="s">
@@ -7359,7 +7334,7 @@
       </c>
     </row>
     <row r="207" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A207" s="44"/>
+      <c r="A207" s="43"/>
       <c r="B207" s="33"/>
       <c r="C207" s="29"/>
       <c r="D207" s="5" t="s">
@@ -7377,7 +7352,7 @@
       </c>
     </row>
     <row r="208" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A208" s="43">
+      <c r="A208" s="42">
         <v>80</v>
       </c>
       <c r="B208" s="33" t="s">
@@ -7403,7 +7378,7 @@
       </c>
     </row>
     <row r="209" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A209" s="44"/>
+      <c r="A209" s="43"/>
       <c r="B209" s="33"/>
       <c r="C209" s="29"/>
       <c r="D209" s="5" t="s">
@@ -7413,7 +7388,7 @@
         <v>1</v>
       </c>
       <c r="F209" s="5" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="G209" s="28"/>
       <c r="H209" s="15" t="s">
@@ -7437,10 +7412,10 @@
         <v>1</v>
       </c>
       <c r="F210" s="5" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="G210" s="28" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="H210" s="15" t="s">
         <v>353</v>
@@ -7457,7 +7432,7 @@
         <v>1</v>
       </c>
       <c r="F211" s="5" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="G211" s="28"/>
       <c r="H211" s="15" t="s">
@@ -7465,10 +7440,10 @@
       </c>
     </row>
     <row r="212" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A212" s="43">
+      <c r="A212" s="42">
         <v>82</v>
       </c>
-      <c r="B212" s="48" t="s">
+      <c r="B212" s="47" t="s">
         <v>29</v>
       </c>
       <c r="C212" s="29" t="s">
@@ -7489,8 +7464,8 @@
       </c>
     </row>
     <row r="213" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A213" s="44"/>
-      <c r="B213" s="49"/>
+      <c r="A213" s="43"/>
+      <c r="B213" s="48"/>
       <c r="C213" s="29"/>
       <c r="D213" s="5" t="s">
         <v>174</v>
@@ -7507,7 +7482,7 @@
       </c>
     </row>
     <row r="214" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A214" s="43">
+      <c r="A214" s="42">
         <v>83</v>
       </c>
       <c r="B214" s="31" t="s">
@@ -7523,17 +7498,17 @@
         <v>2</v>
       </c>
       <c r="F214" s="5" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="G214" s="28" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="H214" s="15" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="215" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A215" s="44"/>
+      <c r="A215" s="43"/>
       <c r="B215" s="31"/>
       <c r="C215" s="29"/>
       <c r="D215" s="5" t="s">
@@ -7543,7 +7518,7 @@
         <v>1</v>
       </c>
       <c r="F215" s="5" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="G215" s="28"/>
       <c r="H215" s="15" t="s">
@@ -7551,7 +7526,7 @@
       </c>
     </row>
     <row r="216" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A216" s="43">
+      <c r="A216" s="42">
         <v>84</v>
       </c>
       <c r="B216" s="31" t="s">
@@ -7577,7 +7552,7 @@
       </c>
     </row>
     <row r="217" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A217" s="44"/>
+      <c r="A217" s="43"/>
       <c r="B217" s="31"/>
       <c r="C217" s="29"/>
       <c r="D217" s="5" t="s">
@@ -7595,7 +7570,7 @@
       </c>
     </row>
     <row r="218" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A218" s="43">
+      <c r="A218" s="42">
         <v>85</v>
       </c>
       <c r="B218" s="31" t="s">
@@ -7619,7 +7594,7 @@
       </c>
     </row>
     <row r="219" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A219" s="44"/>
+      <c r="A219" s="43"/>
       <c r="B219" s="31"/>
       <c r="C219" s="29"/>
       <c r="D219" s="5" t="s">
@@ -7637,7 +7612,7 @@
       </c>
     </row>
     <row r="220" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A220" s="43">
+      <c r="A220" s="42">
         <v>86</v>
       </c>
       <c r="B220" s="31" t="s">
@@ -7661,7 +7636,7 @@
       </c>
     </row>
     <row r="221" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A221" s="44"/>
+      <c r="A221" s="43"/>
       <c r="B221" s="31"/>
       <c r="C221" s="29"/>
       <c r="D221" s="5" t="s">
@@ -7679,7 +7654,7 @@
       </c>
     </row>
     <row r="222" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A222" s="43">
+      <c r="A222" s="42">
         <v>87</v>
       </c>
       <c r="B222" s="31" t="s">
@@ -7698,14 +7673,14 @@
         <v>246</v>
       </c>
       <c r="G222" s="28" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="H222" s="15" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="223" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A223" s="44"/>
+      <c r="A223" s="43"/>
       <c r="B223" s="31"/>
       <c r="C223" s="32"/>
       <c r="D223" s="5" t="s">
@@ -7723,13 +7698,13 @@
       </c>
     </row>
     <row r="224" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A224" s="43">
+      <c r="A224" s="42">
         <v>88</v>
       </c>
       <c r="B224" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C224" s="45" t="s">
+      <c r="C224" s="44" t="s">
         <v>86</v>
       </c>
       <c r="D224" s="5" t="s">
@@ -7747,9 +7722,9 @@
       </c>
     </row>
     <row r="225" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A225" s="44"/>
+      <c r="A225" s="43"/>
       <c r="B225" s="31"/>
-      <c r="C225" s="45"/>
+      <c r="C225" s="44"/>
       <c r="D225" s="5" t="s">
         <v>140</v>
       </c>
@@ -7811,7 +7786,7 @@
     </row>
     <row r="245" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A245" s="29" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="B245" s="29"/>
       <c r="C245" s="29"/>
@@ -7843,47 +7818,47 @@
     </row>
     <row r="247" spans="1:8" ht="100.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A247" s="18" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="B247" s="23" t="s">
         <v>456</v>
       </c>
       <c r="C247" s="25" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="D247" s="26"/>
       <c r="E247" s="26"/>
       <c r="F247" s="27"/>
       <c r="G247" s="4" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="H247" s="16" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
     </row>
     <row r="248" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A248" s="24" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="B248" s="1" t="s">
         <v>456</v>
       </c>
       <c r="C248" s="25" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="D248" s="26"/>
       <c r="E248" s="26"/>
       <c r="F248" s="27"/>
       <c r="G248" s="4" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="H248" s="16" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
     </row>
     <row r="253" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A253" s="29" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="B253" s="29"/>
       <c r="C253" s="29"/>
@@ -7895,7 +7870,7 @@
     </row>
     <row r="254" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A254" s="29" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="B254" s="29"/>
       <c r="C254" s="29"/>
@@ -7907,6 +7882,9 @@
     </row>
   </sheetData>
   <mergeCells count="386">
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="B104:B105"/>
+    <mergeCell ref="C104:C105"/>
     <mergeCell ref="C36:F36"/>
     <mergeCell ref="A245:H245"/>
     <mergeCell ref="A253:H253"/>
@@ -7965,7 +7943,7 @@
     <mergeCell ref="G64:G65"/>
     <mergeCell ref="B106:B107"/>
     <mergeCell ref="C106:C107"/>
-    <mergeCell ref="G104:G105"/>
+    <mergeCell ref="G132:G133"/>
     <mergeCell ref="A70:A71"/>
     <mergeCell ref="B70:B71"/>
     <mergeCell ref="C70:C71"/>
@@ -8078,8 +8056,6 @@
     <mergeCell ref="B82:B83"/>
     <mergeCell ref="A94:A95"/>
     <mergeCell ref="B94:B95"/>
-    <mergeCell ref="B104:B105"/>
-    <mergeCell ref="C104:C105"/>
     <mergeCell ref="A96:A97"/>
     <mergeCell ref="B96:B97"/>
     <mergeCell ref="C96:C97"/>
@@ -8099,21 +8075,20 @@
     <mergeCell ref="A108:A109"/>
     <mergeCell ref="B108:B109"/>
     <mergeCell ref="C108:C109"/>
-    <mergeCell ref="A104:A105"/>
     <mergeCell ref="B110:B111"/>
     <mergeCell ref="A98:A99"/>
     <mergeCell ref="A100:A101"/>
     <mergeCell ref="B100:B101"/>
     <mergeCell ref="C100:C101"/>
     <mergeCell ref="A110:A111"/>
-    <mergeCell ref="A148:A149"/>
+    <mergeCell ref="A150:A151"/>
     <mergeCell ref="G84:G85"/>
     <mergeCell ref="G92:G93"/>
     <mergeCell ref="G82:G83"/>
     <mergeCell ref="G90:G91"/>
     <mergeCell ref="G100:G101"/>
-    <mergeCell ref="C138:C139"/>
-    <mergeCell ref="G138:G139"/>
+    <mergeCell ref="C140:C141"/>
+    <mergeCell ref="G140:G141"/>
     <mergeCell ref="G116:G117"/>
     <mergeCell ref="G108:G109"/>
     <mergeCell ref="G110:G111"/>
@@ -8125,52 +8100,52 @@
     <mergeCell ref="G122:G123"/>
     <mergeCell ref="C122:C123"/>
     <mergeCell ref="C82:C83"/>
-    <mergeCell ref="G132:G133"/>
+    <mergeCell ref="G134:G135"/>
     <mergeCell ref="G106:G107"/>
     <mergeCell ref="G96:G97"/>
     <mergeCell ref="G102:G103"/>
     <mergeCell ref="G126:G127"/>
-    <mergeCell ref="B140:B141"/>
-    <mergeCell ref="C140:C141"/>
-    <mergeCell ref="G136:G137"/>
-    <mergeCell ref="A132:A133"/>
+    <mergeCell ref="B142:B143"/>
+    <mergeCell ref="C142:C143"/>
+    <mergeCell ref="G138:G139"/>
+    <mergeCell ref="A134:A135"/>
     <mergeCell ref="A130:A131"/>
     <mergeCell ref="B130:B131"/>
     <mergeCell ref="C128:C129"/>
-    <mergeCell ref="A142:A143"/>
-    <mergeCell ref="B142:B143"/>
+    <mergeCell ref="A144:A145"/>
+    <mergeCell ref="B144:B145"/>
     <mergeCell ref="A126:A127"/>
     <mergeCell ref="B126:B127"/>
     <mergeCell ref="C126:C127"/>
-    <mergeCell ref="B136:B137"/>
-    <mergeCell ref="C136:C137"/>
-    <mergeCell ref="G148:G149"/>
-    <mergeCell ref="A150:A151"/>
-    <mergeCell ref="A160:A161"/>
-    <mergeCell ref="B160:B161"/>
-    <mergeCell ref="C160:C161"/>
+    <mergeCell ref="B138:B139"/>
+    <mergeCell ref="C138:C139"/>
+    <mergeCell ref="G150:G151"/>
+    <mergeCell ref="A152:A153"/>
+    <mergeCell ref="A132:A133"/>
+    <mergeCell ref="B132:B133"/>
+    <mergeCell ref="C132:C133"/>
     <mergeCell ref="G128:G129"/>
-    <mergeCell ref="A154:A155"/>
-    <mergeCell ref="A138:A139"/>
-    <mergeCell ref="G140:G141"/>
-    <mergeCell ref="G134:G135"/>
+    <mergeCell ref="A156:A157"/>
+    <mergeCell ref="A140:A141"/>
+    <mergeCell ref="G142:G143"/>
+    <mergeCell ref="G136:G137"/>
     <mergeCell ref="A128:A129"/>
     <mergeCell ref="B128:B129"/>
-    <mergeCell ref="B148:B149"/>
-    <mergeCell ref="C148:C149"/>
-    <mergeCell ref="G146:G147"/>
-    <mergeCell ref="A144:A145"/>
-    <mergeCell ref="B144:B145"/>
-    <mergeCell ref="C144:C145"/>
-    <mergeCell ref="A140:A141"/>
+    <mergeCell ref="B150:B151"/>
+    <mergeCell ref="C150:C151"/>
+    <mergeCell ref="G148:G149"/>
+    <mergeCell ref="A146:A147"/>
+    <mergeCell ref="B146:B147"/>
+    <mergeCell ref="C146:C147"/>
+    <mergeCell ref="A142:A143"/>
     <mergeCell ref="C180:C181"/>
     <mergeCell ref="G178:G179"/>
     <mergeCell ref="A176:A177"/>
-    <mergeCell ref="B132:B133"/>
-    <mergeCell ref="C132:C133"/>
-    <mergeCell ref="B154:B155"/>
-    <mergeCell ref="C154:C155"/>
-    <mergeCell ref="G152:G153"/>
+    <mergeCell ref="B134:B135"/>
+    <mergeCell ref="C134:C135"/>
+    <mergeCell ref="B156:B157"/>
+    <mergeCell ref="C156:C157"/>
+    <mergeCell ref="G154:G155"/>
     <mergeCell ref="G172:G173"/>
     <mergeCell ref="B176:B177"/>
     <mergeCell ref="C176:C177"/>
@@ -8178,7 +8153,7 @@
     <mergeCell ref="A168:A169"/>
     <mergeCell ref="G170:G171"/>
     <mergeCell ref="G176:G177"/>
-    <mergeCell ref="G142:G143"/>
+    <mergeCell ref="G144:G145"/>
     <mergeCell ref="A170:A171"/>
     <mergeCell ref="B170:B171"/>
     <mergeCell ref="C170:C171"/>
@@ -8186,24 +8161,24 @@
     <mergeCell ref="A172:A173"/>
     <mergeCell ref="A180:A181"/>
     <mergeCell ref="B180:B181"/>
-    <mergeCell ref="A136:A137"/>
+    <mergeCell ref="A138:A139"/>
     <mergeCell ref="B190:B191"/>
     <mergeCell ref="G182:G183"/>
     <mergeCell ref="C190:C191"/>
     <mergeCell ref="G188:G189"/>
     <mergeCell ref="B188:B189"/>
     <mergeCell ref="C172:C173"/>
-    <mergeCell ref="C158:C159"/>
-    <mergeCell ref="G156:G157"/>
-    <mergeCell ref="A156:A157"/>
-    <mergeCell ref="B156:B157"/>
+    <mergeCell ref="C160:C161"/>
+    <mergeCell ref="G158:G159"/>
+    <mergeCell ref="A158:A159"/>
+    <mergeCell ref="B158:B159"/>
     <mergeCell ref="A174:A175"/>
     <mergeCell ref="B174:B175"/>
     <mergeCell ref="C174:C175"/>
     <mergeCell ref="G174:G175"/>
-    <mergeCell ref="B158:B159"/>
+    <mergeCell ref="B160:B161"/>
     <mergeCell ref="C186:C187"/>
-    <mergeCell ref="A158:A159"/>
+    <mergeCell ref="A160:A161"/>
     <mergeCell ref="G186:G187"/>
     <mergeCell ref="A182:A183"/>
     <mergeCell ref="B182:B183"/>
@@ -8214,23 +8189,23 @@
     <mergeCell ref="A124:A125"/>
     <mergeCell ref="B124:B125"/>
     <mergeCell ref="A118:A119"/>
-    <mergeCell ref="A134:A135"/>
-    <mergeCell ref="B134:B135"/>
-    <mergeCell ref="C134:C135"/>
+    <mergeCell ref="A136:A137"/>
+    <mergeCell ref="B136:B137"/>
+    <mergeCell ref="C136:C137"/>
     <mergeCell ref="G214:G215"/>
     <mergeCell ref="C118:C119"/>
     <mergeCell ref="B118:B119"/>
     <mergeCell ref="C124:C125"/>
-    <mergeCell ref="A152:A153"/>
+    <mergeCell ref="A154:A155"/>
+    <mergeCell ref="B154:B155"/>
+    <mergeCell ref="C154:C155"/>
+    <mergeCell ref="A148:A149"/>
+    <mergeCell ref="B148:B149"/>
+    <mergeCell ref="C148:C149"/>
     <mergeCell ref="B152:B153"/>
     <mergeCell ref="C152:C153"/>
-    <mergeCell ref="A146:A147"/>
-    <mergeCell ref="B146:B147"/>
-    <mergeCell ref="C146:C147"/>
-    <mergeCell ref="B150:B151"/>
-    <mergeCell ref="C150:C151"/>
-    <mergeCell ref="G150:G151"/>
-    <mergeCell ref="G160:G161"/>
+    <mergeCell ref="G152:G153"/>
+    <mergeCell ref="G104:G105"/>
     <mergeCell ref="A166:A167"/>
     <mergeCell ref="A162:A163"/>
     <mergeCell ref="A188:A189"/>
@@ -8283,14 +8258,14 @@
     <mergeCell ref="C90:C91"/>
     <mergeCell ref="G130:G131"/>
     <mergeCell ref="C130:C131"/>
-    <mergeCell ref="G144:G145"/>
+    <mergeCell ref="G146:G147"/>
     <mergeCell ref="B162:B163"/>
     <mergeCell ref="C162:C163"/>
-    <mergeCell ref="B138:B139"/>
-    <mergeCell ref="G154:G155"/>
-    <mergeCell ref="G158:G159"/>
-    <mergeCell ref="C156:C157"/>
-    <mergeCell ref="C142:C143"/>
+    <mergeCell ref="B140:B141"/>
+    <mergeCell ref="G156:G157"/>
+    <mergeCell ref="G160:G161"/>
+    <mergeCell ref="C158:C159"/>
+    <mergeCell ref="C144:C145"/>
     <mergeCell ref="G120:G121"/>
     <mergeCell ref="G114:G115"/>
   </mergeCells>

--- a/src/main/resources/InesModResources/杀戮尖塔自制--伊内丝v0.2.xlsx
+++ b/src/main/resources/InesModResources/杀戮尖塔自制--伊内丝v0.2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\myMod\InesMod\InesMod\src\main\resources\InesModResources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{835FC10C-B651-4740-9049-EA8938DB6888}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{857233E3-6BA4-42FC-9F62-8BE5DCC8B83B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{7A3E14A4-2175-4856-859A-887D335814F1}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="668">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="919" uniqueCount="669">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -995,14 +995,6 @@
   </si>
   <si>
     <t>下一次出牌时，将其一张耗能为0的复制品加入抽牌堆。消耗。保留。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>选择最多1张牌在本回合保留，丢弃其它所有手牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>选择最多2张牌在本回合保留，丢弃其它所有手牌。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1773,14 +1765,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>丢弃所有手牌。向手牌中加入3张影哨。虚无。消耗。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>丢弃所有手牌。向手牌中加入3张影哨。虚无。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Strength Stolen</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2087,6 +2071,14 @@
   </si>
   <si>
     <t>给予1层虚弱。如果目标的意图不为攻击，额外给予2层虚弱。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>现在与接下来3个回合开始时，增加1张小刀到你的手牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>现在与接下来5个回合开始时，增加1张小刀到你的手牌。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2529,28 +2521,40 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>抽2张牌。获得1层偷取和1点能量。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以触发 临时补给 和 临时战略</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>消耗1张牌以打出。增加随机1张能力牌到你的手牌，使其耗能变为0。消耗。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>比刀刃之舞的优势是技能牌可以多次打出</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>虚无。丢弃所有手牌。向手牌中加入3张影哨。消耗。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>虚无。丢弃所有手牌。向手牌中加入3张影哨。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>实际为获得1层同名buff（效果可叠加，可跨回合），达到条件时触发。
-正在结束回合时，不触发。（下）回合抽牌前，触发。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>抽2张牌。获得1层偷取和1点能量。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>可以触发 临时补给 和 临时战略</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>消耗1张牌以打出。增加随机1张能力牌到你的手牌，使其耗能变为0。消耗。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>现在与接下来3个回合开始时，增加2张小刀到你的手牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>现在与接下来5个回合开始时，增加2张小刀到你的手牌。</t>
+正在结束回合时，不触发。（下）回合抽牌前，触发（不能保留大于1张牌）。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择最多1张手牌在本回合保留，丢弃其它所有手牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择最多2张手牌在本回合保留，丢弃其它所有手牌。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2752,7 +2756,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2904,6 +2908,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3240,7 +3250,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="29" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B1" s="29"/>
       <c r="D1" s="2"/>
@@ -3250,10 +3260,10 @@
     </row>
     <row r="2" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="7" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="12"/>
@@ -3264,10 +3274,10 @@
     </row>
     <row r="3" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -3324,7 +3334,7 @@
         <v>3</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
@@ -3340,11 +3350,11 @@
       <c r="D10" s="37"/>
       <c r="E10" s="38"/>
       <c r="F10" s="9" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="G10" s="10"/>
       <c r="H10" s="17" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
@@ -3360,11 +3370,11 @@
       <c r="D11" s="37"/>
       <c r="E11" s="38"/>
       <c r="F11" s="9" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="G11" s="10"/>
       <c r="H11" s="17" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
@@ -3375,7 +3385,7 @@
         <v>247</v>
       </c>
       <c r="C12" s="36" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D12" s="37"/>
       <c r="E12" s="38"/>
@@ -3384,7 +3394,7 @@
       </c>
       <c r="G12" s="10"/>
       <c r="H12" s="17" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
@@ -3395,7 +3405,7 @@
         <v>230</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D13" s="37"/>
       <c r="E13" s="38"/>
@@ -3404,7 +3414,7 @@
       </c>
       <c r="G13" s="10"/>
       <c r="H13" s="17" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
@@ -3415,7 +3425,7 @@
         <v>230</v>
       </c>
       <c r="C14" s="37" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D14" s="37"/>
       <c r="E14" s="38"/>
@@ -3424,7 +3434,7 @@
       </c>
       <c r="G14" s="10"/>
       <c r="H14" s="17" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
@@ -3447,7 +3457,7 @@
         <v>9</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C19" s="36" t="s">
         <v>2</v>
@@ -3459,7 +3469,7 @@
         <v>3</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
@@ -3467,19 +3477,19 @@
         <v>8</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C20" s="25" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="D20" s="26"/>
       <c r="E20" s="26"/>
       <c r="F20" s="27"/>
       <c r="G20" s="5" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="21" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
@@ -3487,137 +3497,137 @@
         <v>206</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C21" s="25" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D21" s="26"/>
       <c r="E21" s="26"/>
       <c r="F21" s="27"/>
       <c r="G21" s="5" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="22" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="19" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C22" s="25" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="D22" s="26"/>
       <c r="E22" s="26"/>
       <c r="F22" s="27"/>
       <c r="G22" s="5" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
     </row>
     <row r="23" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="19" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C23" s="25" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="D23" s="26"/>
       <c r="E23" s="26"/>
       <c r="F23" s="27"/>
       <c r="G23" s="4" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="19" t="s">
+        <v>457</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="C24" s="25" t="s">
         <v>459</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>461</v>
       </c>
       <c r="D24" s="26"/>
       <c r="E24" s="26"/>
       <c r="F24" s="27"/>
       <c r="G24" s="5" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="20" t="s">
+        <v>458</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="C25" s="25" t="s">
         <v>460</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="C25" s="25" t="s">
-        <v>462</v>
       </c>
       <c r="D25" s="26"/>
       <c r="E25" s="26"/>
       <c r="F25" s="27"/>
       <c r="G25" s="5" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="20" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C26" s="25" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="D26" s="26"/>
       <c r="E26" s="26"/>
       <c r="F26" s="27"/>
       <c r="G26" s="4"/>
       <c r="H26" s="16" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="1" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C27" s="25" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D27" s="26"/>
       <c r="E27" s="26"/>
       <c r="F27" s="27"/>
       <c r="G27" s="4" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="H27" s="16" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
@@ -3625,7 +3635,7 @@
     <row r="30" spans="1:8" ht="21.7" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="31" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="29" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="B31" s="29"/>
       <c r="C31" s="29"/>
@@ -3640,7 +3650,7 @@
         <v>9</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C32" s="36" t="s">
         <v>2</v>
@@ -3652,7 +3662,7 @@
         <v>3</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
@@ -3660,17 +3670,17 @@
         <v>8</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C33" s="25" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="D33" s="26"/>
       <c r="E33" s="26"/>
       <c r="F33" s="27"/>
       <c r="G33" s="5"/>
       <c r="H33" s="16" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="34" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
@@ -3678,71 +3688,71 @@
         <v>206</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C34" s="25" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="D34" s="26"/>
       <c r="E34" s="26"/>
       <c r="F34" s="27"/>
       <c r="G34" s="5"/>
       <c r="H34" s="16" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="35" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="19" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="D35" s="26"/>
       <c r="E35" s="26"/>
       <c r="F35" s="27"/>
       <c r="G35" s="5"/>
       <c r="H35" s="16" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="36" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="19" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C36" s="25" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="D36" s="26"/>
       <c r="E36" s="26"/>
       <c r="F36" s="27"/>
       <c r="G36" s="5"/>
       <c r="H36" s="16" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="37" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="19" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C37" s="25" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="D37" s="26"/>
       <c r="E37" s="26"/>
       <c r="F37" s="27"/>
       <c r="G37" s="5"/>
       <c r="H37" s="16" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
@@ -3759,7 +3769,7 @@
     </row>
     <row r="41" spans="1:8" s="3" customFormat="1" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="29" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="B41" s="29"/>
       <c r="C41" s="29"/>
@@ -3792,7 +3802,7 @@
         <v>3</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="43" spans="1:8" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.4">
@@ -3816,7 +3826,7 @@
       </c>
       <c r="G43" s="4"/>
       <c r="H43" s="16" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="44" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -3824,7 +3834,7 @@
     </row>
     <row r="45" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="F45" s="3" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="H45" s="2"/>
     </row>
@@ -3845,7 +3855,7 @@
     </row>
     <row r="48" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="29" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="B48" s="29"/>
       <c r="C48" s="29"/>
@@ -3878,7 +3888,7 @@
         <v>3</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="50" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -3902,7 +3912,7 @@
       </c>
       <c r="G50" s="28"/>
       <c r="H50" s="15" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="51" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -3920,7 +3930,7 @@
       </c>
       <c r="G51" s="28"/>
       <c r="H51" s="15" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
@@ -3947,7 +3957,7 @@
       </c>
       <c r="G52" s="28"/>
       <c r="H52" s="15" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
@@ -3968,7 +3978,7 @@
       </c>
       <c r="G53" s="28"/>
       <c r="H53" s="15" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
@@ -3991,11 +4001,11 @@
         <v>1</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="G54" s="28"/>
       <c r="H54" s="15" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
@@ -4012,11 +4022,11 @@
         <v>1</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="G55" s="28"/>
       <c r="H55" s="15" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
@@ -4039,11 +4049,11 @@
         <v>1</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G56" s="28"/>
       <c r="H56" s="15" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
@@ -4060,11 +4070,11 @@
         <v>1</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="G57" s="28"/>
       <c r="H57" s="15" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
@@ -4087,13 +4097,13 @@
         <v>1</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="G58" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="H58" s="15" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
@@ -4110,11 +4120,11 @@
         <v>1</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="G59" s="28"/>
       <c r="H59" s="15" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
@@ -4137,11 +4147,11 @@
         <v>0</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="G60" s="28"/>
       <c r="H60" s="15" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
@@ -4158,11 +4168,11 @@
         <v>0</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="G61" s="28"/>
       <c r="H61" s="15" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
@@ -4189,7 +4199,7 @@
       </c>
       <c r="G62" s="28"/>
       <c r="H62" s="15" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="I62" s="2"/>
       <c r="J62" s="2"/>
@@ -4210,7 +4220,7 @@
       </c>
       <c r="G63" s="28"/>
       <c r="H63" s="15" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
@@ -4233,13 +4243,13 @@
         <v>0</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="G64" s="28" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="H64" s="15" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="I64" s="2"/>
       <c r="J64" s="2"/>
@@ -4256,11 +4266,11 @@
         <v>0</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="G65" s="28"/>
       <c r="H65" s="15" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="I65" s="2"/>
       <c r="J65" s="2"/>
@@ -4283,13 +4293,13 @@
         <v>1</v>
       </c>
       <c r="F66" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="G66" s="28" t="s">
         <v>533</v>
       </c>
-      <c r="G66" s="28" t="s">
-        <v>537</v>
-      </c>
       <c r="H66" s="15" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="67" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4303,11 +4313,11 @@
         <v>1</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="G67" s="28"/>
       <c r="H67" s="15" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="68" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4327,13 +4337,13 @@
         <v>1</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="G68" s="28" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="H68" s="15" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="I68" s="2"/>
       <c r="J68" s="2"/>
@@ -4350,11 +4360,11 @@
         <v>1</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="G69" s="28"/>
       <c r="H69" s="15" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="I69" s="2"/>
       <c r="J69" s="2"/>
@@ -4377,13 +4387,13 @@
         <v>0</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="G70" s="28" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="H70" s="15" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="I70" s="2"/>
       <c r="J70" s="2"/>
@@ -4400,11 +4410,11 @@
         <v>0</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="G71" s="28"/>
       <c r="H71" s="15" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="I71" s="2"/>
       <c r="J71" s="2"/>
@@ -4427,13 +4437,13 @@
         <v>0</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="G72" s="28" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="H72" s="15" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="I72" s="2"/>
       <c r="J72" s="2"/>
@@ -4450,11 +4460,11 @@
         <v>0</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="G73" s="28"/>
       <c r="H73" s="15" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="I73" s="2"/>
       <c r="J73" s="2"/>
@@ -4477,11 +4487,11 @@
         <v>0</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="G74" s="28"/>
       <c r="H74" s="15" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="I74" s="2"/>
       <c r="J74" s="2"/>
@@ -4498,11 +4508,11 @@
         <v>0</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="G75" s="28"/>
       <c r="H75" s="15" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="I75" s="2"/>
       <c r="J75" s="2"/>
@@ -4525,13 +4535,13 @@
         <v>1</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="G76" s="28" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="H76" s="15" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="I76" s="2"/>
       <c r="J76" s="2"/>
@@ -4548,11 +4558,11 @@
         <v>1</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="G77" s="28"/>
       <c r="H77" s="15" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="78" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4572,13 +4582,13 @@
         <v>2</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="G78" s="28" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="H78" s="15" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="79" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4592,11 +4602,11 @@
         <v>2</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="G79" s="28"/>
       <c r="H79" s="15" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="80" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4616,13 +4626,13 @@
         <v>2</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G80" s="28" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="H80" s="15" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="81" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4636,11 +4646,11 @@
         <v>2</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="G81" s="28"/>
       <c r="H81" s="15" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4660,13 +4670,13 @@
         <v>1</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="G82" s="28" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="H82" s="15" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="83" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4680,11 +4690,11 @@
         <v>1</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="G83" s="28"/>
       <c r="H83" s="15" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="84" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4704,13 +4714,13 @@
         <v>43</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="G84" s="28" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="H84" s="15" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="85" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4724,11 +4734,11 @@
         <v>43</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="G85" s="28"/>
       <c r="H85" s="15" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="86" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4748,11 +4758,11 @@
         <v>1</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="G86" s="28"/>
       <c r="H86" s="15" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
     </row>
     <row r="87" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4766,11 +4776,11 @@
         <v>1</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="G87" s="28"/>
       <c r="H87" s="15" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
     </row>
     <row r="88" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4784,19 +4794,19 @@
         <v>6</v>
       </c>
       <c r="D88" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="E88" s="1">
+        <v>1</v>
+      </c>
+      <c r="F88" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="G88" s="28" t="s">
         <v>258</v>
       </c>
-      <c r="E88" s="1">
-        <v>1</v>
-      </c>
-      <c r="F88" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="G88" s="28" t="s">
-        <v>260</v>
-      </c>
       <c r="H88" s="15" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="89" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4804,17 +4814,17 @@
       <c r="B89" s="31"/>
       <c r="C89" s="29"/>
       <c r="D89" s="5" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E89" s="1">
         <v>1</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G89" s="28"/>
       <c r="H89" s="15" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="90" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4834,13 +4844,13 @@
         <v>0</v>
       </c>
       <c r="F90" s="5" t="s">
+        <v>514</v>
+      </c>
+      <c r="G90" s="28" t="s">
         <v>518</v>
       </c>
-      <c r="G90" s="28" t="s">
-        <v>522</v>
-      </c>
       <c r="H90" s="15" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="91" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4854,11 +4864,11 @@
         <v>0</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="G91" s="28"/>
       <c r="H91" s="15" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="92" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4878,13 +4888,13 @@
         <v>2</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="G92" s="28" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="H92" s="15" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="93" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4898,11 +4908,11 @@
         <v>2</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="G93" s="28"/>
       <c r="H93" s="15" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="94" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4922,13 +4932,13 @@
         <v>2</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="G94" s="28" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="H94" s="15" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="95" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4942,11 +4952,11 @@
         <v>2</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="G95" s="28"/>
       <c r="H95" s="15" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="96" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4966,13 +4976,13 @@
         <v>43</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="G96" s="28" t="s">
         <v>198</v>
       </c>
       <c r="H96" s="15" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="97" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4986,11 +4996,11 @@
         <v>43</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="G97" s="28"/>
       <c r="H97" s="15" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="98" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5010,11 +5020,11 @@
         <v>0</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="G98" s="28"/>
       <c r="H98" s="15" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="99" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5028,11 +5038,11 @@
         <v>0</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="G99" s="28"/>
       <c r="H99" s="15" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="100" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5052,11 +5062,11 @@
         <v>1</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G100" s="28"/>
       <c r="H100" s="15" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="101" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5070,11 +5080,11 @@
         <v>1</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="G101" s="28"/>
       <c r="H101" s="15" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="102" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5094,11 +5104,11 @@
         <v>1</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="G102" s="28"/>
       <c r="H102" s="15" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="103" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5112,53 +5122,55 @@
         <v>1</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="G103" s="28"/>
       <c r="H103" s="15" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="104" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="34">
         <v>28</v>
       </c>
-      <c r="B104" s="30" t="s">
+      <c r="B104" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="C104" s="29" t="s">
+      <c r="C104" s="51" t="s">
         <v>14</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>149</v>
+        <v>66</v>
       </c>
       <c r="E104" s="1">
         <v>1</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>665</v>
-      </c>
-      <c r="G104" s="28"/>
+        <v>552</v>
+      </c>
+      <c r="G104" s="28" t="s">
+        <v>663</v>
+      </c>
       <c r="H104" s="15" t="s">
-        <v>335</v>
+        <v>316</v>
       </c>
     </row>
     <row r="105" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="35"/>
-      <c r="B105" s="30"/>
-      <c r="C105" s="29"/>
+      <c r="B105" s="41"/>
+      <c r="C105" s="52"/>
       <c r="D105" s="5" t="s">
-        <v>150</v>
+        <v>67</v>
       </c>
       <c r="E105" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>665</v>
+        <v>553</v>
       </c>
       <c r="G105" s="28"/>
       <c r="H105" s="15" t="s">
-        <v>399</v>
+        <v>378</v>
       </c>
     </row>
     <row r="106" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5178,13 +5190,13 @@
         <v>0</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="G106" s="28" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="H106" s="15" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="107" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5198,11 +5210,11 @@
         <v>0</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G107" s="28"/>
       <c r="H107" s="15" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="108" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5222,13 +5234,13 @@
         <v>1</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="G108" s="28" t="s">
         <v>217</v>
       </c>
       <c r="H108" s="15" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="109" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5242,11 +5254,11 @@
         <v>1</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="G109" s="28"/>
       <c r="H109" s="15" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="110" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5266,13 +5278,13 @@
         <v>1</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="G110" s="45" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="H110" s="15" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="111" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5286,11 +5298,11 @@
         <v>1</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="G111" s="46"/>
       <c r="H111" s="15" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="112" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5314,7 +5326,7 @@
       </c>
       <c r="G112" s="28"/>
       <c r="H112" s="15" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="113" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5332,7 +5344,7 @@
       </c>
       <c r="G113" s="28"/>
       <c r="H113" s="15" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="114" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5352,11 +5364,11 @@
         <v>1</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="G114" s="28"/>
       <c r="H114" s="15" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="115" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5370,11 +5382,11 @@
         <v>1</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="G115" s="28"/>
       <c r="H115" s="15" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="116" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5397,10 +5409,10 @@
         <v>197</v>
       </c>
       <c r="G116" s="28" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="H116" s="15" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="117" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5414,11 +5426,11 @@
         <v>0</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="G117" s="28"/>
       <c r="H117" s="15" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="118" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5441,10 +5453,10 @@
         <v>196</v>
       </c>
       <c r="G118" s="28" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="H118" s="15" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="119" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5458,11 +5470,11 @@
         <v>0</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="G119" s="28"/>
       <c r="H119" s="15" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5482,13 +5494,13 @@
         <v>0</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="G120" s="28" t="s">
         <v>245</v>
       </c>
       <c r="H120" s="15" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="121" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5502,11 +5514,11 @@
         <v>0</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="G121" s="28"/>
       <c r="H121" s="15" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="122" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
@@ -5526,11 +5538,11 @@
         <v>2</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G122" s="28"/>
       <c r="H122" s="15" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="123" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5544,11 +5556,11 @@
         <v>1</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G123" s="28"/>
       <c r="H123" s="15" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="124" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5568,13 +5580,13 @@
         <v>1</v>
       </c>
       <c r="F124" s="5" t="s">
-        <v>478</v>
+        <v>664</v>
       </c>
       <c r="G124" s="28" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="H124" s="15" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="125" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5588,11 +5600,11 @@
         <v>1</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>479</v>
+        <v>665</v>
       </c>
       <c r="G125" s="28"/>
       <c r="H125" s="15" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5615,10 +5627,10 @@
         <v>222</v>
       </c>
       <c r="G126" s="28" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="H126" s="15" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
     </row>
     <row r="127" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5632,11 +5644,11 @@
         <v>0</v>
       </c>
       <c r="F127" s="5" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="G127" s="28"/>
       <c r="H127" s="15" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
     </row>
     <row r="128" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5660,7 +5672,7 @@
       </c>
       <c r="G128" s="28"/>
       <c r="H128" s="15" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="129" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5674,11 +5686,11 @@
         <v>1</v>
       </c>
       <c r="F129" s="5" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="G129" s="28"/>
       <c r="H129" s="15" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="130" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5698,11 +5710,11 @@
         <v>1</v>
       </c>
       <c r="F130" s="5" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="G130" s="28"/>
       <c r="H130" s="15" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="131" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5716,53 +5728,53 @@
         <v>1</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="G131" s="28"/>
       <c r="H131" s="15" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="132" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="42">
         <v>42</v>
       </c>
-      <c r="B132" s="33" t="s">
-        <v>32</v>
+      <c r="B132" s="40" t="s">
+        <v>17</v>
       </c>
       <c r="C132" s="29" t="s">
         <v>14</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>66</v>
+        <v>149</v>
       </c>
       <c r="E132" s="1">
         <v>1</v>
       </c>
       <c r="F132" s="5" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="G132" s="28"/>
       <c r="H132" s="15" t="s">
-        <v>318</v>
+        <v>333</v>
       </c>
     </row>
     <row r="133" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A133" s="43"/>
-      <c r="B133" s="33"/>
+      <c r="B133" s="41"/>
       <c r="C133" s="29"/>
       <c r="D133" s="5" t="s">
-        <v>67</v>
+        <v>150</v>
       </c>
       <c r="E133" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F133" s="5" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="G133" s="28"/>
       <c r="H133" s="15" t="s">
-        <v>380</v>
+        <v>397</v>
       </c>
     </row>
     <row r="134" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5782,13 +5794,13 @@
         <v>0</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="G134" s="28" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="H134" s="15" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
     </row>
     <row r="135" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5802,11 +5814,11 @@
         <v>0</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="G135" s="28"/>
       <c r="H135" s="15" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="136" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5820,17 +5832,17 @@
         <v>14</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="E136" s="1">
         <v>0</v>
       </c>
       <c r="F136" s="5" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="G136" s="28"/>
       <c r="H136" s="15" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="137" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5838,17 +5850,17 @@
       <c r="B137" s="33"/>
       <c r="C137" s="29"/>
       <c r="D137" s="5" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="E137" s="1">
         <v>0</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="G137" s="28"/>
       <c r="H137" s="15" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="138" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5868,11 +5880,11 @@
         <v>1</v>
       </c>
       <c r="F138" s="5" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="G138" s="28"/>
       <c r="H138" s="15" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="139" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5886,11 +5898,11 @@
         <v>1</v>
       </c>
       <c r="F139" s="5" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="G139" s="28"/>
       <c r="H139" s="15" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="140" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5914,7 +5926,7 @@
       </c>
       <c r="G140" s="28"/>
       <c r="H140" s="15" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="141" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5932,7 +5944,7 @@
       </c>
       <c r="G141" s="28"/>
       <c r="H141" s="15" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="142" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5958,7 +5970,7 @@
         <v>210</v>
       </c>
       <c r="H142" s="15" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
     </row>
     <row r="143" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5976,7 +5988,7 @@
       </c>
       <c r="G143" s="28"/>
       <c r="H143" s="15" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="144" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5996,13 +6008,13 @@
         <v>1</v>
       </c>
       <c r="F144" s="5" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="G144" s="28" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="H144" s="15" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="145" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6016,11 +6028,11 @@
         <v>1</v>
       </c>
       <c r="F145" s="5" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="G145" s="28"/>
       <c r="H145" s="15" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="146" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6034,17 +6046,17 @@
         <v>14</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="E146" s="1">
         <v>1</v>
       </c>
       <c r="F146" s="5" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G146" s="28"/>
       <c r="H146" s="15" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="147" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6058,11 +6070,11 @@
         <v>0</v>
       </c>
       <c r="F147" s="5" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G147" s="28"/>
       <c r="H147" s="15" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="148" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6085,10 +6097,10 @@
         <v>199</v>
       </c>
       <c r="G148" s="28" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="H148" s="15" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="149" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6106,7 +6118,7 @@
       </c>
       <c r="G149" s="28"/>
       <c r="H149" s="15" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="150" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6126,11 +6138,11 @@
         <v>1</v>
       </c>
       <c r="F150" s="5" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="G150" s="28"/>
       <c r="H150" s="15" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="151" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6144,11 +6156,11 @@
         <v>0</v>
       </c>
       <c r="F151" s="5" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="G151" s="28"/>
       <c r="H151" s="15" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
     </row>
     <row r="152" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6172,7 +6184,7 @@
       </c>
       <c r="G152" s="28"/>
       <c r="H152" s="15" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="153" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6190,7 +6202,7 @@
       </c>
       <c r="G153" s="28"/>
       <c r="H153" s="15" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="154" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6214,7 +6226,7 @@
       </c>
       <c r="G154" s="28"/>
       <c r="H154" s="15" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="155" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6232,7 +6244,7 @@
       </c>
       <c r="G155" s="28"/>
       <c r="H155" s="15" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="156" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6252,13 +6264,13 @@
         <v>0</v>
       </c>
       <c r="F156" s="5" t="s">
-        <v>252</v>
+        <v>667</v>
       </c>
       <c r="G156" s="28" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="H156" s="15" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="157" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6272,11 +6284,11 @@
         <v>0</v>
       </c>
       <c r="F157" s="5" t="s">
-        <v>253</v>
+        <v>668</v>
       </c>
       <c r="G157" s="28"/>
       <c r="H157" s="15" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="158" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6300,7 +6312,7 @@
       </c>
       <c r="G158" s="28"/>
       <c r="H158" s="15" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="159" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6318,7 +6330,7 @@
       </c>
       <c r="G159" s="28"/>
       <c r="H159" s="15" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="160" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6338,11 +6350,11 @@
         <v>1</v>
       </c>
       <c r="F160" s="5" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="G160" s="28"/>
       <c r="H160" s="15" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="161" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
@@ -6356,11 +6368,11 @@
         <v>1</v>
       </c>
       <c r="F161" s="5" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="G161" s="28"/>
       <c r="H161" s="15" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="162" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6380,13 +6392,13 @@
         <v>0</v>
       </c>
       <c r="F162" s="5" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G162" s="28" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="H162" s="15" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="163" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6400,11 +6412,11 @@
         <v>0</v>
       </c>
       <c r="F163" s="5" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G163" s="28"/>
       <c r="H163" s="15" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="164" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6424,11 +6436,11 @@
         <v>0</v>
       </c>
       <c r="F164" s="5" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G164" s="28"/>
       <c r="H164" s="15" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="165" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6442,11 +6454,11 @@
         <v>0</v>
       </c>
       <c r="F165" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G165" s="28"/>
       <c r="H165" s="15" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="166" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6466,13 +6478,13 @@
         <v>1</v>
       </c>
       <c r="F166" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="G166" s="28" t="s">
         <v>192</v>
       </c>
       <c r="H166" s="15" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="167" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6486,11 +6498,11 @@
         <v>0</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="G167" s="28"/>
       <c r="H167" s="15" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="168" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6510,11 +6522,11 @@
         <v>1</v>
       </c>
       <c r="F168" s="5" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="G168" s="28"/>
       <c r="H168" s="15" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="169" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6528,11 +6540,11 @@
         <v>0</v>
       </c>
       <c r="F169" s="5" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="G169" s="28"/>
       <c r="H169" s="15" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="170" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6552,13 +6564,13 @@
         <v>2</v>
       </c>
       <c r="F170" s="5" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="G170" s="28" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="H170" s="15" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
     </row>
     <row r="171" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6572,11 +6584,11 @@
         <v>2</v>
       </c>
       <c r="F171" s="5" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="G171" s="28"/>
       <c r="H171" s="15" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="172" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6590,17 +6602,17 @@
         <v>14</v>
       </c>
       <c r="D172" s="5" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="E172" s="1">
         <v>1</v>
       </c>
       <c r="F172" s="5" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="G172" s="28"/>
       <c r="H172" s="15" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
     </row>
     <row r="173" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6608,17 +6620,17 @@
       <c r="B173" s="33"/>
       <c r="C173" s="32"/>
       <c r="D173" s="5" t="s">
+        <v>521</v>
+      </c>
+      <c r="E173" s="1">
+        <v>1</v>
+      </c>
+      <c r="F173" s="5" t="s">
         <v>525</v>
-      </c>
-      <c r="E173" s="1">
-        <v>1</v>
-      </c>
-      <c r="F173" s="5" t="s">
-        <v>529</v>
       </c>
       <c r="G173" s="28"/>
       <c r="H173" s="15" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
     </row>
     <row r="174" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6638,13 +6650,13 @@
         <v>1</v>
       </c>
       <c r="F174" s="5" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="G174" s="28" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="H174" s="15" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="175" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6658,15 +6670,15 @@
         <v>1</v>
       </c>
       <c r="F175" s="5" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="G175" s="28"/>
       <c r="H175" s="15" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="176" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A176" s="42">
+      <c r="A176" s="34">
         <v>64</v>
       </c>
       <c r="B176" s="33" t="s">
@@ -6682,17 +6694,17 @@
         <v>1</v>
       </c>
       <c r="F176" s="5" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="G176" s="28" t="s">
         <v>112</v>
       </c>
       <c r="H176" s="15" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="177" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A177" s="43"/>
+      <c r="A177" s="35"/>
       <c r="B177" s="33"/>
       <c r="C177" s="29"/>
       <c r="D177" s="5" t="s">
@@ -6702,11 +6714,11 @@
         <v>1</v>
       </c>
       <c r="F177" s="5" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="G177" s="28"/>
       <c r="H177" s="15" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="178" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6720,17 +6732,17 @@
         <v>14</v>
       </c>
       <c r="D178" s="5" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E178" s="1">
         <v>1</v>
       </c>
       <c r="F178" s="5" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="G178" s="28"/>
       <c r="H178" s="15" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="179" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6738,17 +6750,17 @@
       <c r="B179" s="31"/>
       <c r="C179" s="29"/>
       <c r="D179" s="5" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="E179" s="1">
         <v>1</v>
       </c>
       <c r="F179" s="5" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="G179" s="28"/>
       <c r="H179" s="15" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="180" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6772,7 +6784,7 @@
       </c>
       <c r="G180" s="28"/>
       <c r="H180" s="15" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="181" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6790,7 +6802,7 @@
       </c>
       <c r="G181" s="28"/>
       <c r="H181" s="15" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="182" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6814,7 +6826,7 @@
       </c>
       <c r="G182" s="28"/>
       <c r="H182" s="15" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="183" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6832,7 +6844,7 @@
       </c>
       <c r="G183" s="28"/>
       <c r="H183" s="15" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="184" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6856,7 +6868,7 @@
       </c>
       <c r="G184" s="28"/>
       <c r="H184" s="15" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
     </row>
     <row r="185" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6874,7 +6886,7 @@
       </c>
       <c r="G185" s="28"/>
       <c r="H185" s="15" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
     </row>
     <row r="186" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6894,11 +6906,11 @@
         <v>3</v>
       </c>
       <c r="F186" s="5" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="G186" s="28"/>
       <c r="H186" s="15" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="187" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6912,11 +6924,11 @@
         <v>2</v>
       </c>
       <c r="F187" s="5" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="G187" s="28"/>
       <c r="H187" s="15" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="188" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6930,17 +6942,17 @@
         <v>14</v>
       </c>
       <c r="D188" s="5" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E188" s="1">
         <v>0</v>
       </c>
       <c r="F188" s="5" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="G188" s="28"/>
       <c r="H188" s="15" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="189" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6948,17 +6960,17 @@
       <c r="B189" s="31"/>
       <c r="C189" s="44"/>
       <c r="D189" s="5" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E189" s="1">
         <v>0</v>
       </c>
       <c r="F189" s="5" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="G189" s="28"/>
       <c r="H189" s="15" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="190" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6978,13 +6990,13 @@
         <v>0</v>
       </c>
       <c r="F190" s="5" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="G190" s="28" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="H190" s="15" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="191" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6998,11 +7010,11 @@
         <v>0</v>
       </c>
       <c r="F191" s="5" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G191" s="28"/>
       <c r="H191" s="15" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="192" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7022,11 +7034,11 @@
         <v>43</v>
       </c>
       <c r="F192" s="5" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="G192" s="28"/>
       <c r="H192" s="15" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="193" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7044,7 +7056,7 @@
       </c>
       <c r="G193" s="28"/>
       <c r="H193" s="15" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="194" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7064,13 +7076,13 @@
         <v>4</v>
       </c>
       <c r="F194" s="5" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G194" s="28" t="s">
         <v>209</v>
       </c>
       <c r="H194" s="15" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="195" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7084,11 +7096,11 @@
         <v>4</v>
       </c>
       <c r="F195" s="5" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G195" s="28"/>
       <c r="H195" s="15" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="196" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7108,13 +7120,13 @@
         <v>1</v>
       </c>
       <c r="F196" s="5" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="G196" s="28" t="s">
         <v>138</v>
       </c>
       <c r="H196" s="15" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="197" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7128,11 +7140,11 @@
         <v>1</v>
       </c>
       <c r="F197" s="5" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="G197" s="28"/>
       <c r="H197" s="15" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="198" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7152,13 +7164,13 @@
         <v>2</v>
       </c>
       <c r="F198" s="5" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G198" s="28" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="H198" s="15" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="199" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7172,11 +7184,11 @@
         <v>1</v>
       </c>
       <c r="F199" s="5" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G199" s="28"/>
       <c r="H199" s="15" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="200" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7202,7 +7214,7 @@
         <v>216</v>
       </c>
       <c r="H200" s="15" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="201" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7220,7 +7232,7 @@
       </c>
       <c r="G201" s="28"/>
       <c r="H201" s="15" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="202" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7240,13 +7252,13 @@
         <v>2</v>
       </c>
       <c r="F202" s="5" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="G202" s="28" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="H202" s="15" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="203" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7260,11 +7272,11 @@
         <v>2</v>
       </c>
       <c r="F203" s="5" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="G203" s="28"/>
       <c r="H203" s="15" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="204" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7284,11 +7296,11 @@
         <v>1</v>
       </c>
       <c r="F204" s="5" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="G204" s="28"/>
       <c r="H204" s="15" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="205" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7306,7 +7318,7 @@
       </c>
       <c r="G205" s="28"/>
       <c r="H205" s="15" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="206" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7330,7 +7342,7 @@
       </c>
       <c r="G206" s="28"/>
       <c r="H206" s="15" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="207" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7348,7 +7360,7 @@
       </c>
       <c r="G207" s="28"/>
       <c r="H207" s="15" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="208" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7374,7 +7386,7 @@
         <v>234</v>
       </c>
       <c r="H208" s="15" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="209" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7388,11 +7400,11 @@
         <v>1</v>
       </c>
       <c r="F209" s="5" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="G209" s="28"/>
       <c r="H209" s="15" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="210" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
@@ -7412,13 +7424,13 @@
         <v>1</v>
       </c>
       <c r="F210" s="5" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="G210" s="28" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="H210" s="15" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="211" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
@@ -7432,11 +7444,11 @@
         <v>1</v>
       </c>
       <c r="F211" s="5" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="G211" s="28"/>
       <c r="H211" s="15" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="212" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7456,11 +7468,11 @@
         <v>1</v>
       </c>
       <c r="F212" s="5" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="G212" s="28"/>
       <c r="H212" s="15" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="213" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7474,11 +7486,11 @@
         <v>0</v>
       </c>
       <c r="F213" s="5" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="G213" s="28"/>
       <c r="H213" s="15" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="214" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7498,13 +7510,13 @@
         <v>2</v>
       </c>
       <c r="F214" s="5" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="G214" s="28" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="H214" s="15" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="215" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
@@ -7518,11 +7530,11 @@
         <v>1</v>
       </c>
       <c r="F215" s="5" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="G215" s="28"/>
       <c r="H215" s="15" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="216" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
@@ -7545,10 +7557,10 @@
         <v>242</v>
       </c>
       <c r="G216" s="28" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H216" s="15" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="217" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
@@ -7566,7 +7578,7 @@
       </c>
       <c r="G217" s="28"/>
       <c r="H217" s="15" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="218" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
@@ -7590,7 +7602,7 @@
       </c>
       <c r="G218" s="28"/>
       <c r="H218" s="15" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="219" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
@@ -7608,7 +7620,7 @@
       </c>
       <c r="G219" s="28"/>
       <c r="H219" s="15" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="220" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
@@ -7632,7 +7644,7 @@
       </c>
       <c r="G220" s="28"/>
       <c r="H220" s="15" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="221" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
@@ -7650,7 +7662,7 @@
       </c>
       <c r="G221" s="28"/>
       <c r="H221" s="15" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="222" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
@@ -7673,10 +7685,10 @@
         <v>246</v>
       </c>
       <c r="G222" s="28" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="H222" s="15" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="223" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
@@ -7694,7 +7706,7 @@
       </c>
       <c r="G223" s="28"/>
       <c r="H223" s="15" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="224" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
@@ -7714,11 +7726,11 @@
         <v>3</v>
       </c>
       <c r="F224" s="5" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G224" s="28"/>
       <c r="H224" s="15" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="225" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
@@ -7736,57 +7748,57 @@
       </c>
       <c r="G225" s="28"/>
       <c r="H225" s="15" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A229" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A230" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A231" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A232" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A233" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A234" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A235" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A236" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A237" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="245" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A245" s="29" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B245" s="29"/>
       <c r="C245" s="29"/>
@@ -7801,7 +7813,7 @@
         <v>9</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C246" s="36" t="s">
         <v>2</v>
@@ -7813,52 +7825,52 @@
         <v>3</v>
       </c>
       <c r="H246" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="247" spans="1:8" ht="100.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A247" s="18" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B247" s="23" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C247" s="25" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D247" s="26"/>
       <c r="E247" s="26"/>
       <c r="F247" s="27"/>
       <c r="G247" s="4" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="H247" s="16" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
     <row r="248" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A248" s="24" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C248" s="25" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="D248" s="26"/>
       <c r="E248" s="26"/>
       <c r="F248" s="27"/>
       <c r="G248" s="4" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H248" s="16" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="253" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A253" s="29" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B253" s="29"/>
       <c r="C253" s="29"/>
@@ -7870,7 +7882,7 @@
     </row>
     <row r="254" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A254" s="29" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B254" s="29"/>
       <c r="C254" s="29"/>
@@ -7882,9 +7894,8 @@
     </row>
   </sheetData>
   <mergeCells count="386">
-    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="C104:C105"/>
     <mergeCell ref="B104:B105"/>
-    <mergeCell ref="C104:C105"/>
     <mergeCell ref="C36:F36"/>
     <mergeCell ref="A245:H245"/>
     <mergeCell ref="A253:H253"/>
@@ -7943,7 +7954,7 @@
     <mergeCell ref="G64:G65"/>
     <mergeCell ref="B106:B107"/>
     <mergeCell ref="C106:C107"/>
-    <mergeCell ref="G132:G133"/>
+    <mergeCell ref="G104:G105"/>
     <mergeCell ref="A70:A71"/>
     <mergeCell ref="B70:B71"/>
     <mergeCell ref="C70:C71"/>
@@ -8075,6 +8086,7 @@
     <mergeCell ref="A108:A109"/>
     <mergeCell ref="B108:B109"/>
     <mergeCell ref="C108:C109"/>
+    <mergeCell ref="A104:A105"/>
     <mergeCell ref="B110:B111"/>
     <mergeCell ref="A98:A99"/>
     <mergeCell ref="A100:A101"/>
@@ -8205,7 +8217,7 @@
     <mergeCell ref="B152:B153"/>
     <mergeCell ref="C152:C153"/>
     <mergeCell ref="G152:G153"/>
-    <mergeCell ref="G104:G105"/>
+    <mergeCell ref="G132:G133"/>
     <mergeCell ref="A166:A167"/>
     <mergeCell ref="A162:A163"/>
     <mergeCell ref="A188:A189"/>

--- a/src/main/resources/InesModResources/杀戮尖塔自制--伊内丝v0.2.xlsx
+++ b/src/main/resources/InesModResources/杀戮尖塔自制--伊内丝v0.2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\myMod\InesMod\InesMod\src\main\resources\InesModResources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{857233E3-6BA4-42FC-9F62-8BE5DCC8B83B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BFF4C35-B788-442B-8C41-127C954D7776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{7A3E14A4-2175-4856-859A-887D335814F1}"/>
   </bookViews>
@@ -6248,7 +6248,7 @@
       </c>
     </row>
     <row r="156" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A156" s="42">
+      <c r="A156" s="34">
         <v>54</v>
       </c>
       <c r="B156" s="33" t="s">
@@ -6274,7 +6274,7 @@
       </c>
     </row>
     <row r="157" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A157" s="43"/>
+      <c r="A157" s="35"/>
       <c r="B157" s="33"/>
       <c r="C157" s="29"/>
       <c r="D157" s="5" t="s">
@@ -7507,7 +7507,7 @@
         <v>134</v>
       </c>
       <c r="E214" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F214" s="5" t="s">
         <v>531</v>
@@ -7527,7 +7527,7 @@
         <v>135</v>
       </c>
       <c r="E215" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F215" s="5" t="s">
         <v>538</v>

--- a/src/main/resources/InesModResources/杀戮尖塔自制--伊内丝v0.2.xlsx
+++ b/src/main/resources/InesModResources/杀戮尖塔自制--伊内丝v0.2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\myMod\InesMod\InesMod\src\main\resources\InesModResources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BFF4C35-B788-442B-8C41-127C954D7776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4D905BA-5D5E-4F2D-BFD4-EDDAC21C481A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{7A3E14A4-2175-4856-859A-887D335814F1}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="919" uniqueCount="669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="976" uniqueCount="676">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -928,10 +928,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>打出后，影哨进入弃牌堆，正常获得格挡。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>更如她那不断掩埋的往事。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -962,10 +958,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>偷取的力量效果+1。固有。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>下回合开始时，抽2张牌且这些牌在1回合内耗能变为0。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -986,10 +978,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>每消耗10张影哨，对所有敌人造成50点伤害。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>下一次出牌时，将其一张耗能为0的复制品加入抽牌堆。消耗。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1117,10 +1105,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>每消耗10张影哨，对所有敌人造成32点伤害。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>即额外+1力量和-1力量</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1216,9 +1200,6 @@
   </si>
   <si>
     <t>Top Secret Operation</t>
-  </si>
-  <si>
-    <t>Necessary Cost</t>
   </si>
   <si>
     <t>Infiltration</t>
@@ -2557,12 +2538,60 @@
     <t>选择最多2张手牌在本回合保留，丢弃其它所有手牌。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>是否完成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卡图</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>✓</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Necessary Cost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pid：107221536（有改编）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pid：123415298</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>手牌中每有1张影哨，使攻击伤害+2。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>手牌中每有1张影哨，使攻击伤害+3。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你的回合结束时，如果处于隐匿，获得2点力量。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每消耗1张影哨，获得1层偷取。固有。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pid：106920382</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pid：128952340</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2607,8 +2636,14 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2660,6 +2695,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2756,7 +2803,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2910,10 +2957,40 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3246,11 +3323,13 @@
     <col min="6" max="6" width="84.53125" customWidth="1"/>
     <col min="7" max="7" width="71.46484375" customWidth="1"/>
     <col min="8" max="8" width="28" style="2" customWidth="1"/>
+    <col min="9" max="9" width="9.06640625" customWidth="1"/>
+    <col min="10" max="10" width="27.59765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="29" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B1" s="29"/>
       <c r="D1" s="2"/>
@@ -3260,10 +3339,10 @@
     </row>
     <row r="2" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="7" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="12"/>
@@ -3274,10 +3353,10 @@
     </row>
     <row r="3" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -3334,7 +3413,7 @@
         <v>3</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
@@ -3350,51 +3429,51 @@
       <c r="D10" s="37"/>
       <c r="E10" s="38"/>
       <c r="F10" s="9" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="G10" s="10"/>
       <c r="H10" s="17" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D11" s="37"/>
       <c r="E11" s="38"/>
       <c r="F11" s="9" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="G11" s="10"/>
       <c r="H11" s="17" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C12" s="36" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="D12" s="37"/>
       <c r="E12" s="38"/>
       <c r="F12" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G12" s="10"/>
       <c r="H12" s="17" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
@@ -3405,7 +3484,7 @@
         <v>230</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="D13" s="37"/>
       <c r="E13" s="38"/>
@@ -3414,7 +3493,7 @@
       </c>
       <c r="G13" s="10"/>
       <c r="H13" s="17" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
@@ -3425,16 +3504,16 @@
         <v>230</v>
       </c>
       <c r="C14" s="37" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="D14" s="37"/>
       <c r="E14" s="38"/>
       <c r="F14" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G14" s="10"/>
       <c r="H14" s="17" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
@@ -3457,7 +3536,7 @@
         <v>9</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="C19" s="36" t="s">
         <v>2</v>
@@ -3469,7 +3548,7 @@
         <v>3</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
@@ -3477,19 +3556,19 @@
         <v>8</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="C20" s="25" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="D20" s="26"/>
       <c r="E20" s="26"/>
       <c r="F20" s="27"/>
       <c r="G20" s="5" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
     </row>
     <row r="21" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
@@ -3497,137 +3576,137 @@
         <v>206</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="C21" s="25" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="D21" s="26"/>
       <c r="E21" s="26"/>
       <c r="F21" s="27"/>
       <c r="G21" s="5" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
     </row>
     <row r="22" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="19" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="C22" s="25" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="D22" s="26"/>
       <c r="E22" s="26"/>
       <c r="F22" s="27"/>
       <c r="G22" s="5" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
     </row>
     <row r="23" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="19" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="C23" s="25" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="D23" s="26"/>
       <c r="E23" s="26"/>
       <c r="F23" s="27"/>
       <c r="G23" s="4" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="19" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="C24" s="25" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="D24" s="26"/>
       <c r="E24" s="26"/>
       <c r="F24" s="27"/>
       <c r="G24" s="5" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="20" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="C25" s="25" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="D25" s="26"/>
       <c r="E25" s="26"/>
       <c r="F25" s="27"/>
       <c r="G25" s="5" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="20" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="C26" s="25" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="D26" s="26"/>
       <c r="E26" s="26"/>
       <c r="F26" s="27"/>
       <c r="G26" s="4"/>
       <c r="H26" s="16" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="1" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="C27" s="25" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="D27" s="26"/>
       <c r="E27" s="26"/>
       <c r="F27" s="27"/>
       <c r="G27" s="4" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="H27" s="16" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
@@ -3635,7 +3714,7 @@
     <row r="30" spans="1:8" ht="21.7" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="31" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="29" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="B31" s="29"/>
       <c r="C31" s="29"/>
@@ -3650,7 +3729,7 @@
         <v>9</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="C32" s="36" t="s">
         <v>2</v>
@@ -3662,102 +3741,102 @@
         <v>3</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="19" t="s">
         <v>8</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="C33" s="25" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="D33" s="26"/>
       <c r="E33" s="26"/>
       <c r="F33" s="27"/>
       <c r="G33" s="5"/>
       <c r="H33" s="16" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="19" t="s">
         <v>206</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="C34" s="25" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="D34" s="26"/>
       <c r="E34" s="26"/>
       <c r="F34" s="27"/>
       <c r="G34" s="5"/>
       <c r="H34" s="16" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="19" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="D35" s="26"/>
       <c r="E35" s="26"/>
       <c r="F35" s="27"/>
       <c r="G35" s="5"/>
       <c r="H35" s="16" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="19" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="C36" s="25" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="D36" s="26"/>
       <c r="E36" s="26"/>
       <c r="F36" s="27"/>
       <c r="G36" s="5"/>
       <c r="H36" s="16" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" s="3" customFormat="1" ht="39.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="19" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="C37" s="25" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="D37" s="26"/>
       <c r="E37" s="26"/>
       <c r="F37" s="27"/>
       <c r="G37" s="5"/>
       <c r="H37" s="16" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="39" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="40" spans="1:8" s="3" customFormat="1" ht="23.35" customHeight="1" x14ac:dyDescent="0.4">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="39" spans="1:10" ht="19.7" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="40" spans="1:10" s="3" customFormat="1" ht="23.35" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40"/>
       <c r="B40"/>
       <c r="C40"/>
@@ -3767,9 +3846,9 @@
       <c r="G40"/>
       <c r="H40" s="11"/>
     </row>
-    <row r="41" spans="1:8" s="3" customFormat="1" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:10" s="3" customFormat="1" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="29" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="B41" s="29"/>
       <c r="C41" s="29"/>
@@ -3779,7 +3858,7 @@
       <c r="G41" s="29"/>
       <c r="H41" s="29"/>
     </row>
-    <row r="42" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:10" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="1" t="s">
         <v>0</v>
       </c>
@@ -3802,10 +3881,10 @@
         <v>3</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="22">
         <v>1</v>
       </c>
@@ -3826,22 +3905,22 @@
       </c>
       <c r="G43" s="4"/>
       <c r="H43" s="16" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="H44" s="2"/>
     </row>
-    <row r="45" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:10" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="F45" s="3" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="H45" s="2"/>
     </row>
-    <row r="46" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:10" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="H46" s="2"/>
     </row>
-    <row r="47" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:10" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="29" t="s">
         <v>7</v>
       </c>
@@ -3852,18 +3931,24 @@
       <c r="F47" s="29"/>
       <c r="G47" s="29"/>
       <c r="H47" s="29"/>
-    </row>
-    <row r="48" spans="1:8" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="29" t="s">
-        <v>506</v>
-      </c>
-      <c r="B48" s="29"/>
-      <c r="C48" s="29"/>
-      <c r="D48" s="29"/>
-      <c r="E48" s="29"/>
-      <c r="F48" s="29"/>
-      <c r="G48" s="29"/>
-      <c r="H48" s="29"/>
+      <c r="I47" s="29" t="s">
+        <v>665</v>
+      </c>
+      <c r="J47" s="29"/>
+    </row>
+    <row r="48" spans="1:10" s="3" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="36" t="s">
+        <v>501</v>
+      </c>
+      <c r="B48" s="37"/>
+      <c r="C48" s="37"/>
+      <c r="D48" s="37"/>
+      <c r="E48" s="37"/>
+      <c r="F48" s="37"/>
+      <c r="G48" s="37"/>
+      <c r="H48" s="38"/>
+      <c r="I48" s="29"/>
+      <c r="J48" s="29"/>
     </row>
     <row r="49" spans="1:11" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="1" t="s">
@@ -3888,7 +3973,13 @@
         <v>3</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>285</v>
+        <v>281</v>
+      </c>
+      <c r="I49" s="55" t="s">
+        <v>664</v>
+      </c>
+      <c r="J49" s="55" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="50" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -3912,8 +4003,12 @@
       </c>
       <c r="G50" s="28"/>
       <c r="H50" s="15" t="s">
-        <v>294</v>
-      </c>
+        <v>290</v>
+      </c>
+      <c r="I50" s="56" t="s">
+        <v>666</v>
+      </c>
+      <c r="J50" s="51"/>
     </row>
     <row r="51" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="35"/>
@@ -3930,10 +4025,10 @@
       </c>
       <c r="G51" s="28"/>
       <c r="H51" s="15" t="s">
-        <v>355</v>
-      </c>
-      <c r="I51" s="2"/>
-      <c r="J51" s="2"/>
+        <v>350</v>
+      </c>
+      <c r="I51" s="57"/>
+      <c r="J51" s="52"/>
       <c r="K51" s="2"/>
     </row>
     <row r="52" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -3957,10 +4052,12 @@
       </c>
       <c r="G52" s="28"/>
       <c r="H52" s="15" t="s">
-        <v>295</v>
-      </c>
-      <c r="I52" s="2"/>
-      <c r="J52" s="2"/>
+        <v>291</v>
+      </c>
+      <c r="I52" s="56" t="s">
+        <v>666</v>
+      </c>
+      <c r="J52" s="51"/>
       <c r="K52" s="2"/>
     </row>
     <row r="53" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -3978,10 +4075,10 @@
       </c>
       <c r="G53" s="28"/>
       <c r="H53" s="15" t="s">
-        <v>356</v>
-      </c>
-      <c r="I53" s="2"/>
-      <c r="J53" s="2"/>
+        <v>351</v>
+      </c>
+      <c r="I53" s="57"/>
+      <c r="J53" s="52"/>
       <c r="K53" s="2"/>
     </row>
     <row r="54" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4001,14 +4098,14 @@
         <v>1</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="G54" s="28"/>
       <c r="H54" s="15" t="s">
-        <v>453</v>
-      </c>
-      <c r="I54" s="2"/>
-      <c r="J54" s="2"/>
+        <v>448</v>
+      </c>
+      <c r="I54" s="51"/>
+      <c r="J54" s="51"/>
       <c r="K54" s="2"/>
     </row>
     <row r="55" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4022,14 +4119,14 @@
         <v>1</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="G55" s="28"/>
       <c r="H55" s="15" t="s">
-        <v>357</v>
-      </c>
-      <c r="I55" s="2"/>
-      <c r="J55" s="2"/>
+        <v>352</v>
+      </c>
+      <c r="I55" s="52"/>
+      <c r="J55" s="52"/>
       <c r="K55" s="2"/>
     </row>
     <row r="56" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4049,14 +4146,16 @@
         <v>1</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="G56" s="28"/>
       <c r="H56" s="15" t="s">
-        <v>290</v>
-      </c>
-      <c r="I56" s="2"/>
-      <c r="J56" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="I56" s="56" t="s">
+        <v>666</v>
+      </c>
+      <c r="J56" s="51"/>
       <c r="K56" s="2"/>
     </row>
     <row r="57" spans="1:11" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
@@ -4070,14 +4169,14 @@
         <v>1</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="G57" s="28"/>
       <c r="H57" s="15" t="s">
-        <v>420</v>
-      </c>
-      <c r="I57" s="2"/>
-      <c r="J57" s="2"/>
+        <v>415</v>
+      </c>
+      <c r="I57" s="57"/>
+      <c r="J57" s="52"/>
       <c r="K57" s="2"/>
     </row>
     <row r="58" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4097,16 +4196,18 @@
         <v>1</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="G58" s="28" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="H58" s="15" t="s">
-        <v>296</v>
-      </c>
-      <c r="I58" s="2"/>
-      <c r="J58" s="2"/>
+        <v>292</v>
+      </c>
+      <c r="I58" s="56" t="s">
+        <v>666</v>
+      </c>
+      <c r="J58" s="51"/>
       <c r="K58" s="2"/>
     </row>
     <row r="59" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4120,14 +4221,14 @@
         <v>1</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G59" s="28"/>
       <c r="H59" s="15" t="s">
-        <v>358</v>
-      </c>
-      <c r="I59" s="2"/>
-      <c r="J59" s="2"/>
+        <v>353</v>
+      </c>
+      <c r="I59" s="57"/>
+      <c r="J59" s="52"/>
       <c r="K59" s="2"/>
     </row>
     <row r="60" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4147,14 +4248,14 @@
         <v>0</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="G60" s="28"/>
       <c r="H60" s="15" t="s">
-        <v>297</v>
-      </c>
-      <c r="I60" s="2"/>
-      <c r="J60" s="2"/>
+        <v>293</v>
+      </c>
+      <c r="I60" s="51"/>
+      <c r="J60" s="51"/>
       <c r="K60" s="2"/>
     </row>
     <row r="61" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4168,14 +4269,14 @@
         <v>0</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="G61" s="28"/>
       <c r="H61" s="15" t="s">
-        <v>359</v>
-      </c>
-      <c r="I61" s="2"/>
-      <c r="J61" s="2"/>
+        <v>354</v>
+      </c>
+      <c r="I61" s="52"/>
+      <c r="J61" s="52"/>
       <c r="K61" s="2"/>
     </row>
     <row r="62" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4199,10 +4300,10 @@
       </c>
       <c r="G62" s="28"/>
       <c r="H62" s="15" t="s">
-        <v>298</v>
-      </c>
-      <c r="I62" s="2"/>
-      <c r="J62" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="I62" s="51"/>
+      <c r="J62" s="51"/>
       <c r="K62" s="2"/>
     </row>
     <row r="63" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4220,10 +4321,10 @@
       </c>
       <c r="G63" s="28"/>
       <c r="H63" s="15" t="s">
-        <v>360</v>
-      </c>
-      <c r="I63" s="2"/>
-      <c r="J63" s="2"/>
+        <v>355</v>
+      </c>
+      <c r="I63" s="52"/>
+      <c r="J63" s="52"/>
       <c r="K63" s="2"/>
     </row>
     <row r="64" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4243,16 +4344,18 @@
         <v>0</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="G64" s="28" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="H64" s="15" t="s">
-        <v>299</v>
-      </c>
-      <c r="I64" s="2"/>
-      <c r="J64" s="2"/>
+        <v>295</v>
+      </c>
+      <c r="I64" s="56" t="s">
+        <v>666</v>
+      </c>
+      <c r="J64" s="51"/>
       <c r="K64" s="2"/>
     </row>
     <row r="65" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4266,14 +4369,14 @@
         <v>0</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="G65" s="28"/>
       <c r="H65" s="15" t="s">
-        <v>361</v>
-      </c>
-      <c r="I65" s="2"/>
-      <c r="J65" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="I65" s="57"/>
+      <c r="J65" s="52"/>
       <c r="K65" s="2"/>
     </row>
     <row r="66" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4293,14 +4396,18 @@
         <v>1</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="G66" s="28" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="H66" s="15" t="s">
-        <v>300</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="I66" s="56" t="s">
+        <v>666</v>
+      </c>
+      <c r="J66" s="51"/>
     </row>
     <row r="67" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="35"/>
@@ -4313,12 +4420,14 @@
         <v>1</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="G67" s="28"/>
       <c r="H67" s="15" t="s">
-        <v>362</v>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="I67" s="57"/>
+      <c r="J67" s="52"/>
     </row>
     <row r="68" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="34">
@@ -4337,16 +4446,16 @@
         <v>1</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="G68" s="28" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="H68" s="15" t="s">
-        <v>301</v>
-      </c>
-      <c r="I68" s="2"/>
-      <c r="J68" s="2"/>
+        <v>297</v>
+      </c>
+      <c r="I68" s="51"/>
+      <c r="J68" s="51"/>
       <c r="K68" s="2"/>
     </row>
     <row r="69" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4360,14 +4469,14 @@
         <v>1</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="G69" s="28"/>
       <c r="H69" s="15" t="s">
-        <v>363</v>
-      </c>
-      <c r="I69" s="2"/>
-      <c r="J69" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="I69" s="52"/>
+      <c r="J69" s="52"/>
       <c r="K69" s="2"/>
     </row>
     <row r="70" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4387,16 +4496,18 @@
         <v>0</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="G70" s="28" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="H70" s="15" t="s">
-        <v>302</v>
-      </c>
-      <c r="I70" s="2"/>
-      <c r="J70" s="2"/>
+        <v>298</v>
+      </c>
+      <c r="I70" s="56" t="s">
+        <v>666</v>
+      </c>
+      <c r="J70" s="51"/>
       <c r="K70" s="2"/>
     </row>
     <row r="71" spans="1:11" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
@@ -4410,14 +4521,14 @@
         <v>0</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="G71" s="28"/>
       <c r="H71" s="15" t="s">
-        <v>364</v>
-      </c>
-      <c r="I71" s="2"/>
-      <c r="J71" s="2"/>
+        <v>359</v>
+      </c>
+      <c r="I71" s="57"/>
+      <c r="J71" s="52"/>
       <c r="K71" s="2"/>
     </row>
     <row r="72" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4437,16 +4548,18 @@
         <v>0</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="G72" s="28" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="H72" s="15" t="s">
-        <v>303</v>
-      </c>
-      <c r="I72" s="2"/>
-      <c r="J72" s="2"/>
+        <v>299</v>
+      </c>
+      <c r="I72" s="56" t="s">
+        <v>666</v>
+      </c>
+      <c r="J72" s="51"/>
       <c r="K72" s="2"/>
     </row>
     <row r="73" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4460,14 +4573,14 @@
         <v>0</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="G73" s="28"/>
       <c r="H73" s="15" t="s">
-        <v>365</v>
-      </c>
-      <c r="I73" s="2"/>
-      <c r="J73" s="2"/>
+        <v>360</v>
+      </c>
+      <c r="I73" s="57"/>
+      <c r="J73" s="52"/>
       <c r="K73" s="2"/>
     </row>
     <row r="74" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4487,14 +4600,16 @@
         <v>0</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="G74" s="28"/>
       <c r="H74" s="15" t="s">
-        <v>619</v>
-      </c>
-      <c r="I74" s="2"/>
-      <c r="J74" s="2"/>
+        <v>614</v>
+      </c>
+      <c r="I74" s="56" t="s">
+        <v>666</v>
+      </c>
+      <c r="J74" s="51"/>
       <c r="K74" s="2"/>
     </row>
     <row r="75" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4508,14 +4623,14 @@
         <v>0</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="G75" s="28"/>
       <c r="H75" s="15" t="s">
-        <v>620</v>
-      </c>
-      <c r="I75" s="2"/>
-      <c r="J75" s="2"/>
+        <v>615</v>
+      </c>
+      <c r="I75" s="57"/>
+      <c r="J75" s="52"/>
       <c r="K75" s="2"/>
     </row>
     <row r="76" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4535,16 +4650,18 @@
         <v>1</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="G76" s="28" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="H76" s="15" t="s">
-        <v>304</v>
-      </c>
-      <c r="I76" s="2"/>
-      <c r="J76" s="2"/>
+        <v>300</v>
+      </c>
+      <c r="I76" s="56" t="s">
+        <v>666</v>
+      </c>
+      <c r="J76" s="51"/>
       <c r="K76" s="2"/>
     </row>
     <row r="77" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4558,12 +4675,14 @@
         <v>1</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="G77" s="28"/>
       <c r="H77" s="15" t="s">
-        <v>366</v>
-      </c>
+        <v>361</v>
+      </c>
+      <c r="I77" s="57"/>
+      <c r="J77" s="52"/>
     </row>
     <row r="78" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="34">
@@ -4582,14 +4701,16 @@
         <v>2</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="G78" s="28" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="H78" s="15" t="s">
-        <v>305</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="I78" s="51"/>
+      <c r="J78" s="51"/>
     </row>
     <row r="79" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="35"/>
@@ -4602,12 +4723,14 @@
         <v>2</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="G79" s="28"/>
       <c r="H79" s="15" t="s">
-        <v>367</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="I79" s="52"/>
+      <c r="J79" s="52"/>
     </row>
     <row r="80" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="34">
@@ -4626,16 +4749,18 @@
         <v>2</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="G80" s="28" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="H80" s="15" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>616</v>
+      </c>
+      <c r="I80" s="51"/>
+      <c r="J80" s="51"/>
+    </row>
+    <row r="81" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="35"/>
       <c r="B81" s="33"/>
       <c r="C81" s="50"/>
@@ -4646,14 +4771,16 @@
         <v>2</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="G81" s="28"/>
       <c r="H81" s="15" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>617</v>
+      </c>
+      <c r="I81" s="52"/>
+      <c r="J81" s="52"/>
+    </row>
+    <row r="82" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="34">
         <v>17</v>
       </c>
@@ -4670,16 +4797,18 @@
         <v>1</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="G82" s="28" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="H82" s="15" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>302</v>
+      </c>
+      <c r="I82" s="51"/>
+      <c r="J82" s="51"/>
+    </row>
+    <row r="83" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="35"/>
       <c r="B83" s="33"/>
       <c r="C83" s="29"/>
@@ -4690,14 +4819,16 @@
         <v>1</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="G83" s="28"/>
       <c r="H83" s="15" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>363</v>
+      </c>
+      <c r="I83" s="52"/>
+      <c r="J83" s="52"/>
+    </row>
+    <row r="84" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="42">
         <v>18</v>
       </c>
@@ -4714,16 +4845,18 @@
         <v>43</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="G84" s="28" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="H84" s="15" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>303</v>
+      </c>
+      <c r="I84" s="51"/>
+      <c r="J84" s="51"/>
+    </row>
+    <row r="85" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="43"/>
       <c r="B85" s="33"/>
       <c r="C85" s="44"/>
@@ -4734,14 +4867,16 @@
         <v>43</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="G85" s="28"/>
       <c r="H85" s="15" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>364</v>
+      </c>
+      <c r="I85" s="52"/>
+      <c r="J85" s="52"/>
+    </row>
+    <row r="86" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="34">
         <v>19</v>
       </c>
@@ -4758,14 +4893,18 @@
         <v>1</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="G86" s="28"/>
       <c r="H86" s="15" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>475</v>
+      </c>
+      <c r="I86" s="56" t="s">
+        <v>666</v>
+      </c>
+      <c r="J86" s="51"/>
+    </row>
+    <row r="87" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="35"/>
       <c r="B87" s="33"/>
       <c r="C87" s="29"/>
@@ -4776,14 +4915,16 @@
         <v>1</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="G87" s="28"/>
       <c r="H87" s="15" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>476</v>
+      </c>
+      <c r="I87" s="57"/>
+      <c r="J87" s="52"/>
+    </row>
+    <row r="88" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="42">
         <v>20</v>
       </c>
@@ -4794,40 +4935,46 @@
         <v>6</v>
       </c>
       <c r="D88" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="E88" s="1">
+        <v>1</v>
+      </c>
+      <c r="F88" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="E88" s="1">
-        <v>1</v>
-      </c>
-      <c r="F88" s="5" t="s">
-        <v>259</v>
-      </c>
       <c r="G88" s="28" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="H88" s="15" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>304</v>
+      </c>
+      <c r="I88" s="56" t="s">
+        <v>666</v>
+      </c>
+      <c r="J88" s="51"/>
+    </row>
+    <row r="89" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="43"/>
       <c r="B89" s="31"/>
       <c r="C89" s="29"/>
       <c r="D89" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="E89" s="1">
+        <v>1</v>
+      </c>
+      <c r="F89" s="5" t="s">
         <v>257</v>
-      </c>
-      <c r="E89" s="1">
-        <v>1</v>
-      </c>
-      <c r="F89" s="5" t="s">
-        <v>260</v>
       </c>
       <c r="G89" s="28"/>
       <c r="H89" s="15" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>365</v>
+      </c>
+      <c r="I89" s="57"/>
+      <c r="J89" s="52"/>
+    </row>
+    <row r="90" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="42">
         <v>21</v>
       </c>
@@ -4844,16 +4991,18 @@
         <v>0</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="G90" s="28" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="H90" s="15" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>305</v>
+      </c>
+      <c r="I90" s="51"/>
+      <c r="J90" s="51"/>
+    </row>
+    <row r="91" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="43"/>
       <c r="B91" s="31"/>
       <c r="C91" s="29"/>
@@ -4864,14 +5013,16 @@
         <v>0</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="G91" s="28"/>
       <c r="H91" s="15" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>366</v>
+      </c>
+      <c r="I91" s="52"/>
+      <c r="J91" s="52"/>
+    </row>
+    <row r="92" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="34">
         <v>22</v>
       </c>
@@ -4888,16 +5039,20 @@
         <v>2</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="G92" s="28" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="H92" s="15" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>306</v>
+      </c>
+      <c r="I92" s="56" t="s">
+        <v>666</v>
+      </c>
+      <c r="J92" s="51"/>
+    </row>
+    <row r="93" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="35"/>
       <c r="B93" s="31"/>
       <c r="C93" s="29"/>
@@ -4908,14 +5063,16 @@
         <v>2</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="G93" s="28"/>
       <c r="H93" s="15" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>367</v>
+      </c>
+      <c r="I93" s="57"/>
+      <c r="J93" s="52"/>
+    </row>
+    <row r="94" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="34">
         <v>23</v>
       </c>
@@ -4932,16 +5089,18 @@
         <v>2</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="G94" s="28" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="H94" s="15" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>307</v>
+      </c>
+      <c r="I94" s="51"/>
+      <c r="J94" s="51"/>
+    </row>
+    <row r="95" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="35"/>
       <c r="B95" s="31"/>
       <c r="C95" s="29"/>
@@ -4952,14 +5111,16 @@
         <v>2</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="G95" s="28"/>
       <c r="H95" s="15" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>368</v>
+      </c>
+      <c r="I95" s="52"/>
+      <c r="J95" s="52"/>
+    </row>
+    <row r="96" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="42">
         <v>24</v>
       </c>
@@ -4976,16 +5137,22 @@
         <v>43</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="G96" s="28" t="s">
         <v>198</v>
       </c>
       <c r="H96" s="15" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>667</v>
+      </c>
+      <c r="I96" s="56" t="s">
+        <v>666</v>
+      </c>
+      <c r="J96" s="51" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="43"/>
       <c r="B97" s="31"/>
       <c r="C97" s="29"/>
@@ -4996,14 +5163,16 @@
         <v>43</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="G97" s="28"/>
       <c r="H97" s="15" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>369</v>
+      </c>
+      <c r="I97" s="57"/>
+      <c r="J97" s="52"/>
+    </row>
+    <row r="98" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="34">
         <v>25</v>
       </c>
@@ -5020,14 +5189,18 @@
         <v>0</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="G98" s="28"/>
       <c r="H98" s="15" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>308</v>
+      </c>
+      <c r="I98" s="56" t="s">
+        <v>666</v>
+      </c>
+      <c r="J98" s="51"/>
+    </row>
+    <row r="99" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="35"/>
       <c r="B99" s="30"/>
       <c r="C99" s="29"/>
@@ -5038,14 +5211,16 @@
         <v>0</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="G99" s="28"/>
       <c r="H99" s="15" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>370</v>
+      </c>
+      <c r="I99" s="57"/>
+      <c r="J99" s="52"/>
+    </row>
+    <row r="100" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="42">
         <v>26</v>
       </c>
@@ -5062,14 +5237,16 @@
         <v>1</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="G100" s="28"/>
       <c r="H100" s="15" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>309</v>
+      </c>
+      <c r="I100" s="51"/>
+      <c r="J100" s="51"/>
+    </row>
+    <row r="101" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="43"/>
       <c r="B101" s="30"/>
       <c r="C101" s="44"/>
@@ -5080,14 +5257,16 @@
         <v>1</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="G101" s="28"/>
       <c r="H101" s="15" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>371</v>
+      </c>
+      <c r="I101" s="52"/>
+      <c r="J101" s="52"/>
+    </row>
+    <row r="102" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="34">
         <v>27</v>
       </c>
@@ -5104,14 +5283,18 @@
         <v>1</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="G102" s="28"/>
       <c r="H102" s="15" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>310</v>
+      </c>
+      <c r="I102" s="56" t="s">
+        <v>666</v>
+      </c>
+      <c r="J102" s="51"/>
+    </row>
+    <row r="103" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="35"/>
       <c r="B103" s="30"/>
       <c r="C103" s="29"/>
@@ -5122,21 +5305,23 @@
         <v>1</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="G103" s="28"/>
       <c r="H103" s="15" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>372</v>
+      </c>
+      <c r="I103" s="57"/>
+      <c r="J103" s="52"/>
+    </row>
+    <row r="104" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="34">
         <v>28</v>
       </c>
       <c r="B104" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="C104" s="51" t="s">
+      <c r="C104" s="53" t="s">
         <v>14</v>
       </c>
       <c r="D104" s="5" t="s">
@@ -5146,19 +5331,23 @@
         <v>1</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="G104" s="28" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="H104" s="15" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>311</v>
+      </c>
+      <c r="I104" s="56" t="s">
+        <v>666</v>
+      </c>
+      <c r="J104" s="51"/>
+    </row>
+    <row r="105" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="35"/>
       <c r="B105" s="41"/>
-      <c r="C105" s="52"/>
+      <c r="C105" s="54"/>
       <c r="D105" s="5" t="s">
         <v>67</v>
       </c>
@@ -5166,14 +5355,16 @@
         <v>1</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="G105" s="28"/>
       <c r="H105" s="15" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>373</v>
+      </c>
+      <c r="I105" s="57"/>
+      <c r="J105" s="52"/>
+    </row>
+    <row r="106" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="42">
         <v>29</v>
       </c>
@@ -5190,16 +5381,18 @@
         <v>0</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G106" s="28" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="H106" s="15" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>312</v>
+      </c>
+      <c r="I106" s="51"/>
+      <c r="J106" s="51"/>
+    </row>
+    <row r="107" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="43"/>
       <c r="B107" s="30"/>
       <c r="C107" s="29"/>
@@ -5210,14 +5403,16 @@
         <v>0</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="G107" s="28"/>
       <c r="H107" s="15" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>374</v>
+      </c>
+      <c r="I107" s="52"/>
+      <c r="J107" s="52"/>
+    </row>
+    <row r="108" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="34">
         <v>30</v>
       </c>
@@ -5234,16 +5429,20 @@
         <v>1</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="G108" s="28" t="s">
         <v>217</v>
       </c>
       <c r="H108" s="15" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>313</v>
+      </c>
+      <c r="I108" s="56" t="s">
+        <v>666</v>
+      </c>
+      <c r="J108" s="51"/>
+    </row>
+    <row r="109" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="35"/>
       <c r="B109" s="30"/>
       <c r="C109" s="29"/>
@@ -5254,14 +5453,16 @@
         <v>1</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="G109" s="28"/>
       <c r="H109" s="15" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>375</v>
+      </c>
+      <c r="I109" s="57"/>
+      <c r="J109" s="52"/>
+    </row>
+    <row r="110" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="34">
         <v>31</v>
       </c>
@@ -5278,16 +5479,20 @@
         <v>1</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="G110" s="45" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H110" s="15" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>314</v>
+      </c>
+      <c r="I110" s="56" t="s">
+        <v>666</v>
+      </c>
+      <c r="J110" s="51"/>
+    </row>
+    <row r="111" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="35"/>
       <c r="B111" s="41"/>
       <c r="C111" s="32"/>
@@ -5298,14 +5503,16 @@
         <v>1</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="G111" s="46"/>
       <c r="H111" s="15" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>376</v>
+      </c>
+      <c r="I111" s="57"/>
+      <c r="J111" s="52"/>
+    </row>
+    <row r="112" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="42">
         <v>32</v>
       </c>
@@ -5326,10 +5533,12 @@
       </c>
       <c r="G112" s="28"/>
       <c r="H112" s="15" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>315</v>
+      </c>
+      <c r="I112" s="51"/>
+      <c r="J112" s="51"/>
+    </row>
+    <row r="113" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="43"/>
       <c r="B113" s="30"/>
       <c r="C113" s="44"/>
@@ -5344,10 +5553,12 @@
       </c>
       <c r="G113" s="28"/>
       <c r="H113" s="15" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>377</v>
+      </c>
+      <c r="I113" s="52"/>
+      <c r="J113" s="52"/>
+    </row>
+    <row r="114" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="34">
         <v>33</v>
       </c>
@@ -5364,14 +5575,18 @@
         <v>1</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="G114" s="28"/>
       <c r="H114" s="15" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>316</v>
+      </c>
+      <c r="I114" s="56" t="s">
+        <v>666</v>
+      </c>
+      <c r="J114" s="51"/>
+    </row>
+    <row r="115" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="35"/>
       <c r="B115" s="30"/>
       <c r="C115" s="29"/>
@@ -5382,14 +5597,16 @@
         <v>1</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="G115" s="28"/>
       <c r="H115" s="15" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>378</v>
+      </c>
+      <c r="I115" s="57"/>
+      <c r="J115" s="52"/>
+    </row>
+    <row r="116" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="34">
         <v>34</v>
       </c>
@@ -5409,13 +5626,17 @@
         <v>197</v>
       </c>
       <c r="G116" s="28" t="s">
+        <v>661</v>
+      </c>
+      <c r="H116" s="15" t="s">
+        <v>421</v>
+      </c>
+      <c r="I116" s="56" t="s">
         <v>666</v>
       </c>
-      <c r="H116" s="15" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="J116" s="51"/>
+    </row>
+    <row r="117" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="35"/>
       <c r="B117" s="30"/>
       <c r="C117" s="29"/>
@@ -5426,14 +5647,16 @@
         <v>0</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="G117" s="28"/>
       <c r="H117" s="15" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>422</v>
+      </c>
+      <c r="I117" s="57"/>
+      <c r="J117" s="52"/>
+    </row>
+    <row r="118" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="34">
         <v>35</v>
       </c>
@@ -5453,13 +5676,17 @@
         <v>196</v>
       </c>
       <c r="G118" s="28" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="H118" s="15" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="119" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>612</v>
+      </c>
+      <c r="I118" s="56" t="s">
+        <v>666</v>
+      </c>
+      <c r="J118" s="51"/>
+    </row>
+    <row r="119" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="35"/>
       <c r="B119" s="30"/>
       <c r="C119" s="29"/>
@@ -5470,14 +5697,16 @@
         <v>0</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="G119" s="28"/>
       <c r="H119" s="15" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="120" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>379</v>
+      </c>
+      <c r="I119" s="57"/>
+      <c r="J119" s="52"/>
+    </row>
+    <row r="120" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="34">
         <v>36</v>
       </c>
@@ -5494,16 +5723,18 @@
         <v>0</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="G120" s="28" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="H120" s="15" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>317</v>
+      </c>
+      <c r="I120" s="51"/>
+      <c r="J120" s="51"/>
+    </row>
+    <row r="121" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="35"/>
       <c r="B121" s="30"/>
       <c r="C121" s="29"/>
@@ -5514,14 +5745,16 @@
         <v>0</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="G121" s="28"/>
       <c r="H121" s="15" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
+        <v>380</v>
+      </c>
+      <c r="I121" s="52"/>
+      <c r="J121" s="52"/>
+    </row>
+    <row r="122" spans="1:10" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="34">
         <v>37</v>
       </c>
@@ -5538,14 +5771,18 @@
         <v>2</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="G122" s="28"/>
       <c r="H122" s="15" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>318</v>
+      </c>
+      <c r="I122" s="56" t="s">
+        <v>666</v>
+      </c>
+      <c r="J122" s="51"/>
+    </row>
+    <row r="123" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="35"/>
       <c r="B123" s="41"/>
       <c r="C123" s="29"/>
@@ -5556,14 +5793,16 @@
         <v>1</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="G123" s="28"/>
       <c r="H123" s="15" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>381</v>
+      </c>
+      <c r="I123" s="57"/>
+      <c r="J123" s="52"/>
+    </row>
+    <row r="124" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="34">
         <v>38</v>
       </c>
@@ -5580,16 +5819,18 @@
         <v>1</v>
       </c>
       <c r="F124" s="5" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="G124" s="28" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="H124" s="15" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>321</v>
+      </c>
+      <c r="I124" s="51"/>
+      <c r="J124" s="51"/>
+    </row>
+    <row r="125" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="35"/>
       <c r="B125" s="41"/>
       <c r="C125" s="29"/>
@@ -5600,14 +5841,16 @@
         <v>1</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="G125" s="28"/>
       <c r="H125" s="15" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>385</v>
+      </c>
+      <c r="I125" s="52"/>
+      <c r="J125" s="52"/>
+    </row>
+    <row r="126" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="34">
         <v>39</v>
       </c>
@@ -5627,13 +5870,17 @@
         <v>222</v>
       </c>
       <c r="G126" s="28" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="H126" s="15" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>538</v>
+      </c>
+      <c r="I126" s="56" t="s">
+        <v>666</v>
+      </c>
+      <c r="J126" s="51"/>
+    </row>
+    <row r="127" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="35"/>
       <c r="B127" s="41"/>
       <c r="C127" s="29"/>
@@ -5644,14 +5891,16 @@
         <v>0</v>
       </c>
       <c r="F127" s="5" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="G127" s="28"/>
       <c r="H127" s="15" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>539</v>
+      </c>
+      <c r="I127" s="57"/>
+      <c r="J127" s="52"/>
+    </row>
+    <row r="128" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="42">
         <v>40</v>
       </c>
@@ -5668,14 +5917,16 @@
         <v>1</v>
       </c>
       <c r="F128" s="5" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="G128" s="28"/>
       <c r="H128" s="15" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>327</v>
+      </c>
+      <c r="I128" s="51"/>
+      <c r="J128" s="51"/>
+    </row>
+    <row r="129" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="43"/>
       <c r="B129" s="41"/>
       <c r="C129" s="29"/>
@@ -5686,14 +5937,16 @@
         <v>1</v>
       </c>
       <c r="F129" s="5" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="G129" s="28"/>
       <c r="H129" s="15" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>391</v>
+      </c>
+      <c r="I129" s="52"/>
+      <c r="J129" s="52"/>
+    </row>
+    <row r="130" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="34">
         <v>41</v>
       </c>
@@ -5710,14 +5963,16 @@
         <v>1</v>
       </c>
       <c r="F130" s="5" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="G130" s="28"/>
       <c r="H130" s="15" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="131" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>324</v>
+      </c>
+      <c r="I130" s="51"/>
+      <c r="J130" s="51"/>
+    </row>
+    <row r="131" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="35"/>
       <c r="B131" s="41"/>
       <c r="C131" s="32"/>
@@ -5728,14 +5983,16 @@
         <v>1</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="G131" s="28"/>
       <c r="H131" s="15" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="132" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>388</v>
+      </c>
+      <c r="I131" s="52"/>
+      <c r="J131" s="52"/>
+    </row>
+    <row r="132" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="42">
         <v>42</v>
       </c>
@@ -5752,14 +6009,16 @@
         <v>1</v>
       </c>
       <c r="F132" s="5" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="G132" s="28"/>
       <c r="H132" s="15" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>328</v>
+      </c>
+      <c r="I132" s="51"/>
+      <c r="J132" s="51"/>
+    </row>
+    <row r="133" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A133" s="43"/>
       <c r="B133" s="41"/>
       <c r="C133" s="29"/>
@@ -5770,14 +6029,16 @@
         <v>0</v>
       </c>
       <c r="F133" s="5" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="G133" s="28"/>
       <c r="H133" s="15" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="134" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>392</v>
+      </c>
+      <c r="I133" s="52"/>
+      <c r="J133" s="52"/>
+    </row>
+    <row r="134" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A134" s="34">
         <v>43</v>
       </c>
@@ -5794,16 +6055,20 @@
         <v>0</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="G134" s="28" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="H134" s="15" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="135" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>542</v>
+      </c>
+      <c r="I134" s="56" t="s">
+        <v>666</v>
+      </c>
+      <c r="J134" s="51"/>
+    </row>
+    <row r="135" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A135" s="35"/>
       <c r="B135" s="33"/>
       <c r="C135" s="29"/>
@@ -5814,14 +6079,16 @@
         <v>0</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="G135" s="28"/>
       <c r="H135" s="15" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="136" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>543</v>
+      </c>
+      <c r="I135" s="57"/>
+      <c r="J135" s="52"/>
+    </row>
+    <row r="136" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A136" s="34">
         <v>44</v>
       </c>
@@ -5832,38 +6099,44 @@
         <v>14</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="E136" s="1">
         <v>0</v>
       </c>
       <c r="F136" s="5" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="G136" s="28"/>
       <c r="H136" s="15" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>608</v>
+      </c>
+      <c r="I136" s="56" t="s">
+        <v>666</v>
+      </c>
+      <c r="J136" s="51"/>
+    </row>
+    <row r="137" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A137" s="35"/>
       <c r="B137" s="33"/>
       <c r="C137" s="29"/>
       <c r="D137" s="5" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="E137" s="1">
         <v>0</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="G137" s="28"/>
       <c r="H137" s="15" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="138" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>609</v>
+      </c>
+      <c r="I137" s="57"/>
+      <c r="J137" s="52"/>
+    </row>
+    <row r="138" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A138" s="34">
         <v>45</v>
       </c>
@@ -5880,14 +6153,16 @@
         <v>1</v>
       </c>
       <c r="F138" s="5" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="G138" s="28"/>
       <c r="H138" s="15" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="139" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>319</v>
+      </c>
+      <c r="I138" s="51"/>
+      <c r="J138" s="51"/>
+    </row>
+    <row r="139" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A139" s="35"/>
       <c r="B139" s="33"/>
       <c r="C139" s="29"/>
@@ -5898,14 +6173,16 @@
         <v>1</v>
       </c>
       <c r="F139" s="5" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="G139" s="28"/>
       <c r="H139" s="15" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="140" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>382</v>
+      </c>
+      <c r="I139" s="52"/>
+      <c r="J139" s="52"/>
+    </row>
+    <row r="140" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A140" s="42">
         <v>46</v>
       </c>
@@ -5926,10 +6203,12 @@
       </c>
       <c r="G140" s="28"/>
       <c r="H140" s="15" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="141" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>444</v>
+      </c>
+      <c r="I140" s="51"/>
+      <c r="J140" s="51"/>
+    </row>
+    <row r="141" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A141" s="43"/>
       <c r="B141" s="33"/>
       <c r="C141" s="44"/>
@@ -5944,10 +6223,12 @@
       </c>
       <c r="G141" s="28"/>
       <c r="H141" s="15" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="142" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>445</v>
+      </c>
+      <c r="I141" s="52"/>
+      <c r="J141" s="52"/>
+    </row>
+    <row r="142" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A142" s="42">
         <v>47</v>
       </c>
@@ -5970,10 +6251,14 @@
         <v>210</v>
       </c>
       <c r="H142" s="15" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="143" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>521</v>
+      </c>
+      <c r="I142" s="56" t="s">
+        <v>666</v>
+      </c>
+      <c r="J142" s="51"/>
+    </row>
+    <row r="143" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A143" s="43"/>
       <c r="B143" s="33"/>
       <c r="C143" s="29"/>
@@ -5988,10 +6273,12 @@
       </c>
       <c r="G143" s="28"/>
       <c r="H143" s="15" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="144" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>383</v>
+      </c>
+      <c r="I143" s="57"/>
+      <c r="J143" s="52"/>
+    </row>
+    <row r="144" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A144" s="34">
         <v>48</v>
       </c>
@@ -6008,16 +6295,18 @@
         <v>1</v>
       </c>
       <c r="F144" s="5" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="G144" s="28" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="H144" s="15" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>320</v>
+      </c>
+      <c r="I144" s="51"/>
+      <c r="J144" s="51"/>
+    </row>
+    <row r="145" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A145" s="35"/>
       <c r="B145" s="33"/>
       <c r="C145" s="29"/>
@@ -6028,14 +6317,16 @@
         <v>1</v>
       </c>
       <c r="F145" s="5" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="G145" s="28"/>
       <c r="H145" s="15" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="146" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>384</v>
+      </c>
+      <c r="I145" s="52"/>
+      <c r="J145" s="52"/>
+    </row>
+    <row r="146" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A146" s="34">
         <v>49</v>
       </c>
@@ -6046,20 +6337,24 @@
         <v>14</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="E146" s="1">
         <v>1</v>
       </c>
       <c r="F146" s="5" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="G146" s="28"/>
       <c r="H146" s="15" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="147" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>322</v>
+      </c>
+      <c r="I146" s="56" t="s">
+        <v>666</v>
+      </c>
+      <c r="J146" s="51"/>
+    </row>
+    <row r="147" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A147" s="35"/>
       <c r="B147" s="33"/>
       <c r="C147" s="29"/>
@@ -6070,14 +6365,16 @@
         <v>0</v>
       </c>
       <c r="F147" s="5" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="G147" s="28"/>
       <c r="H147" s="15" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="148" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>386</v>
+      </c>
+      <c r="I147" s="57"/>
+      <c r="J147" s="52"/>
+    </row>
+    <row r="148" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A148" s="42">
         <v>50</v>
       </c>
@@ -6097,13 +6394,15 @@
         <v>199</v>
       </c>
       <c r="G148" s="28" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="H148" s="15" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="149" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>417</v>
+      </c>
+      <c r="I148" s="51"/>
+      <c r="J148" s="51"/>
+    </row>
+    <row r="149" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A149" s="43"/>
       <c r="B149" s="33"/>
       <c r="C149" s="44"/>
@@ -6118,10 +6417,12 @@
       </c>
       <c r="G149" s="28"/>
       <c r="H149" s="15" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="150" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>418</v>
+      </c>
+      <c r="I149" s="52"/>
+      <c r="J149" s="52"/>
+    </row>
+    <row r="150" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A150" s="34">
         <v>51</v>
       </c>
@@ -6138,14 +6439,18 @@
         <v>1</v>
       </c>
       <c r="F150" s="5" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="G150" s="28"/>
       <c r="H150" s="15" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="151" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>491</v>
+      </c>
+      <c r="I150" s="56" t="s">
+        <v>666</v>
+      </c>
+      <c r="J150" s="51"/>
+    </row>
+    <row r="151" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A151" s="35"/>
       <c r="B151" s="33"/>
       <c r="C151" s="32"/>
@@ -6156,14 +6461,16 @@
         <v>0</v>
       </c>
       <c r="F151" s="5" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="G151" s="28"/>
       <c r="H151" s="15" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="152" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>492</v>
+      </c>
+      <c r="I151" s="57"/>
+      <c r="J151" s="52"/>
+    </row>
+    <row r="152" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A152" s="34">
         <v>52</v>
       </c>
@@ -6184,10 +6491,14 @@
       </c>
       <c r="G152" s="28"/>
       <c r="H152" s="15" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="153" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>323</v>
+      </c>
+      <c r="I152" s="56" t="s">
+        <v>666</v>
+      </c>
+      <c r="J152" s="51"/>
+    </row>
+    <row r="153" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A153" s="35"/>
       <c r="B153" s="33"/>
       <c r="C153" s="29"/>
@@ -6202,10 +6513,12 @@
       </c>
       <c r="G153" s="28"/>
       <c r="H153" s="15" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="154" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>387</v>
+      </c>
+      <c r="I153" s="57"/>
+      <c r="J153" s="52"/>
+    </row>
+    <row r="154" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A154" s="34">
         <v>53</v>
       </c>
@@ -6226,10 +6539,12 @@
       </c>
       <c r="G154" s="28"/>
       <c r="H154" s="15" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="155" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>419</v>
+      </c>
+      <c r="I154" s="51"/>
+      <c r="J154" s="51"/>
+    </row>
+    <row r="155" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A155" s="35"/>
       <c r="B155" s="33"/>
       <c r="C155" s="29"/>
@@ -6240,14 +6555,16 @@
         <v>0</v>
       </c>
       <c r="F155" s="5" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="G155" s="28"/>
       <c r="H155" s="15" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="156" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>420</v>
+      </c>
+      <c r="I155" s="52"/>
+      <c r="J155" s="52"/>
+    </row>
+    <row r="156" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A156" s="34">
         <v>54</v>
       </c>
@@ -6264,16 +6581,20 @@
         <v>0</v>
       </c>
       <c r="F156" s="5" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="G156" s="28" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="H156" s="15" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="157" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>446</v>
+      </c>
+      <c r="I156" s="56" t="s">
+        <v>666</v>
+      </c>
+      <c r="J156" s="51"/>
+    </row>
+    <row r="157" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A157" s="35"/>
       <c r="B157" s="33"/>
       <c r="C157" s="29"/>
@@ -6284,14 +6605,16 @@
         <v>0</v>
       </c>
       <c r="F157" s="5" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="G157" s="28"/>
       <c r="H157" s="15" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="158" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>447</v>
+      </c>
+      <c r="I157" s="57"/>
+      <c r="J157" s="52"/>
+    </row>
+    <row r="158" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A158" s="42">
         <v>55</v>
       </c>
@@ -6312,10 +6635,12 @@
       </c>
       <c r="G158" s="28"/>
       <c r="H158" s="15" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="159" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>325</v>
+      </c>
+      <c r="I158" s="51"/>
+      <c r="J158" s="51"/>
+    </row>
+    <row r="159" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A159" s="43"/>
       <c r="B159" s="33"/>
       <c r="C159" s="29"/>
@@ -6330,10 +6655,12 @@
       </c>
       <c r="G159" s="28"/>
       <c r="H159" s="15" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="160" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>389</v>
+      </c>
+      <c r="I159" s="52"/>
+      <c r="J159" s="52"/>
+    </row>
+    <row r="160" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A160" s="42">
         <v>56</v>
       </c>
@@ -6350,14 +6677,16 @@
         <v>1</v>
       </c>
       <c r="F160" s="5" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="G160" s="28"/>
       <c r="H160" s="15" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="161" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
+        <v>326</v>
+      </c>
+      <c r="I160" s="51"/>
+      <c r="J160" s="51"/>
+    </row>
+    <row r="161" spans="1:10" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A161" s="43"/>
       <c r="B161" s="33"/>
       <c r="C161" s="29"/>
@@ -6368,14 +6697,16 @@
         <v>1</v>
       </c>
       <c r="F161" s="5" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="G161" s="28"/>
       <c r="H161" s="15" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="162" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>390</v>
+      </c>
+      <c r="I161" s="52"/>
+      <c r="J161" s="52"/>
+    </row>
+    <row r="162" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A162" s="42">
         <v>57</v>
       </c>
@@ -6392,16 +6723,18 @@
         <v>0</v>
       </c>
       <c r="F162" s="5" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="G162" s="28" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="H162" s="15" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="163" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>329</v>
+      </c>
+      <c r="I162" s="51"/>
+      <c r="J162" s="51"/>
+    </row>
+    <row r="163" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A163" s="43"/>
       <c r="B163" s="33"/>
       <c r="C163" s="29"/>
@@ -6412,14 +6745,16 @@
         <v>0</v>
       </c>
       <c r="F163" s="5" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="G163" s="28"/>
       <c r="H163" s="15" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="164" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>393</v>
+      </c>
+      <c r="I163" s="52"/>
+      <c r="J163" s="52"/>
+    </row>
+    <row r="164" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A164" s="42">
         <v>58</v>
       </c>
@@ -6436,14 +6771,16 @@
         <v>0</v>
       </c>
       <c r="F164" s="5" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="G164" s="28"/>
       <c r="H164" s="15" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="165" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>330</v>
+      </c>
+      <c r="I164" s="51"/>
+      <c r="J164" s="51"/>
+    </row>
+    <row r="165" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A165" s="43"/>
       <c r="B165" s="33"/>
       <c r="C165" s="44"/>
@@ -6454,14 +6791,16 @@
         <v>0</v>
       </c>
       <c r="F165" s="5" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="G165" s="28"/>
       <c r="H165" s="15" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="166" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>394</v>
+      </c>
+      <c r="I165" s="52"/>
+      <c r="J165" s="52"/>
+    </row>
+    <row r="166" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A166" s="42">
         <v>59</v>
       </c>
@@ -6478,16 +6817,18 @@
         <v>1</v>
       </c>
       <c r="F166" s="5" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="G166" s="28" t="s">
         <v>192</v>
       </c>
       <c r="H166" s="15" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="167" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>331</v>
+      </c>
+      <c r="I166" s="51"/>
+      <c r="J166" s="51"/>
+    </row>
+    <row r="167" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A167" s="43"/>
       <c r="B167" s="33"/>
       <c r="C167" s="44"/>
@@ -6498,14 +6839,16 @@
         <v>0</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="G167" s="28"/>
       <c r="H167" s="15" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="168" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>395</v>
+      </c>
+      <c r="I167" s="52"/>
+      <c r="J167" s="52"/>
+    </row>
+    <row r="168" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A168" s="42">
         <v>60</v>
       </c>
@@ -6522,14 +6865,16 @@
         <v>1</v>
       </c>
       <c r="F168" s="5" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="G168" s="28"/>
       <c r="H168" s="15" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="169" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>332</v>
+      </c>
+      <c r="I168" s="51"/>
+      <c r="J168" s="51"/>
+    </row>
+    <row r="169" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A169" s="43"/>
       <c r="B169" s="33"/>
       <c r="C169" s="44"/>
@@ -6540,14 +6885,16 @@
         <v>0</v>
       </c>
       <c r="F169" s="5" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="G169" s="28"/>
       <c r="H169" s="15" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="170" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>396</v>
+      </c>
+      <c r="I169" s="52"/>
+      <c r="J169" s="52"/>
+    </row>
+    <row r="170" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A170" s="34">
         <v>61</v>
       </c>
@@ -6564,16 +6911,18 @@
         <v>2</v>
       </c>
       <c r="F170" s="5" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="G170" s="28" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="H170" s="15" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="171" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>642</v>
+      </c>
+      <c r="I170" s="51"/>
+      <c r="J170" s="51"/>
+    </row>
+    <row r="171" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A171" s="35"/>
       <c r="B171" s="33"/>
       <c r="C171" s="29"/>
@@ -6584,14 +6933,16 @@
         <v>2</v>
       </c>
       <c r="F171" s="5" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="G171" s="28"/>
       <c r="H171" s="15" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="172" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>643</v>
+      </c>
+      <c r="I171" s="52"/>
+      <c r="J171" s="52"/>
+    </row>
+    <row r="172" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A172" s="34">
         <v>62</v>
       </c>
@@ -6602,38 +6953,44 @@
         <v>14</v>
       </c>
       <c r="D172" s="5" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="E172" s="1">
         <v>1</v>
       </c>
       <c r="F172" s="5" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="G172" s="28"/>
       <c r="H172" s="15" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="173" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>518</v>
+      </c>
+      <c r="I172" s="56" t="s">
+        <v>666</v>
+      </c>
+      <c r="J172" s="51"/>
+    </row>
+    <row r="173" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A173" s="35"/>
       <c r="B173" s="33"/>
       <c r="C173" s="32"/>
       <c r="D173" s="5" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="E173" s="1">
         <v>1</v>
       </c>
       <c r="F173" s="5" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="G173" s="28"/>
       <c r="H173" s="15" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="174" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>518</v>
+      </c>
+      <c r="I173" s="57"/>
+      <c r="J173" s="52"/>
+    </row>
+    <row r="174" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A174" s="42">
         <v>63</v>
       </c>
@@ -6650,16 +7007,18 @@
         <v>1</v>
       </c>
       <c r="F174" s="5" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="G174" s="28" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="H174" s="15" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="175" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>333</v>
+      </c>
+      <c r="I174" s="51"/>
+      <c r="J174" s="51"/>
+    </row>
+    <row r="175" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A175" s="43"/>
       <c r="B175" s="33"/>
       <c r="C175" s="44"/>
@@ -6670,14 +7029,16 @@
         <v>1</v>
       </c>
       <c r="F175" s="5" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="G175" s="28"/>
       <c r="H175" s="15" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="176" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>397</v>
+      </c>
+      <c r="I175" s="52"/>
+      <c r="J175" s="52"/>
+    </row>
+    <row r="176" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A176" s="34">
         <v>64</v>
       </c>
@@ -6694,16 +7055,20 @@
         <v>1</v>
       </c>
       <c r="F176" s="5" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="G176" s="28" t="s">
         <v>112</v>
       </c>
       <c r="H176" s="15" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="177" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>334</v>
+      </c>
+      <c r="I176" s="56" t="s">
+        <v>666</v>
+      </c>
+      <c r="J176" s="51"/>
+    </row>
+    <row r="177" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A177" s="35"/>
       <c r="B177" s="33"/>
       <c r="C177" s="29"/>
@@ -6714,14 +7079,16 @@
         <v>1</v>
       </c>
       <c r="F177" s="5" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="G177" s="28"/>
       <c r="H177" s="15" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="178" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>398</v>
+      </c>
+      <c r="I177" s="57"/>
+      <c r="J177" s="52"/>
+    </row>
+    <row r="178" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A178" s="42">
         <v>65</v>
       </c>
@@ -6732,38 +7099,44 @@
         <v>14</v>
       </c>
       <c r="D178" s="5" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="E178" s="1">
         <v>1</v>
       </c>
       <c r="F178" s="5" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="G178" s="28"/>
       <c r="H178" s="15" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="179" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>604</v>
+      </c>
+      <c r="I178" s="56" t="s">
+        <v>666</v>
+      </c>
+      <c r="J178" s="51"/>
+    </row>
+    <row r="179" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A179" s="43"/>
       <c r="B179" s="31"/>
       <c r="C179" s="29"/>
       <c r="D179" s="5" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="E179" s="1">
         <v>1</v>
       </c>
       <c r="F179" s="5" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="G179" s="28"/>
       <c r="H179" s="15" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="180" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>605</v>
+      </c>
+      <c r="I179" s="57"/>
+      <c r="J179" s="52"/>
+    </row>
+    <row r="180" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A180" s="42">
         <v>66</v>
       </c>
@@ -6780,14 +7153,18 @@
         <v>1</v>
       </c>
       <c r="F180" s="5" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G180" s="28"/>
       <c r="H180" s="15" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="181" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>335</v>
+      </c>
+      <c r="I180" s="56" t="s">
+        <v>666</v>
+      </c>
+      <c r="J180" s="51"/>
+    </row>
+    <row r="181" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A181" s="43"/>
       <c r="B181" s="31"/>
       <c r="C181" s="29"/>
@@ -6798,14 +7175,16 @@
         <v>1</v>
       </c>
       <c r="F181" s="5" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="G181" s="28"/>
       <c r="H181" s="15" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="182" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>399</v>
+      </c>
+      <c r="I181" s="57"/>
+      <c r="J181" s="52"/>
+    </row>
+    <row r="182" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A182" s="42">
         <v>67</v>
       </c>
@@ -6826,10 +7205,14 @@
       </c>
       <c r="G182" s="28"/>
       <c r="H182" s="15" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="183" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>336</v>
+      </c>
+      <c r="I182" s="56" t="s">
+        <v>666</v>
+      </c>
+      <c r="J182" s="51"/>
+    </row>
+    <row r="183" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A183" s="43"/>
       <c r="B183" s="31"/>
       <c r="C183" s="29"/>
@@ -6844,10 +7227,12 @@
       </c>
       <c r="G183" s="28"/>
       <c r="H183" s="15" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="184" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>400</v>
+      </c>
+      <c r="I183" s="57"/>
+      <c r="J183" s="52"/>
+    </row>
+    <row r="184" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A184" s="34">
         <v>68</v>
       </c>
@@ -6868,10 +7253,14 @@
       </c>
       <c r="G184" s="28"/>
       <c r="H184" s="15" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="185" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>522</v>
+      </c>
+      <c r="I184" s="56" t="s">
+        <v>666</v>
+      </c>
+      <c r="J184" s="51"/>
+    </row>
+    <row r="185" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A185" s="35"/>
       <c r="B185" s="31"/>
       <c r="C185" s="29"/>
@@ -6886,10 +7275,12 @@
       </c>
       <c r="G185" s="28"/>
       <c r="H185" s="15" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="186" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>523</v>
+      </c>
+      <c r="I185" s="57"/>
+      <c r="J185" s="52"/>
+    </row>
+    <row r="186" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A186" s="34">
         <v>69</v>
       </c>
@@ -6906,14 +7297,18 @@
         <v>3</v>
       </c>
       <c r="F186" s="5" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="G186" s="28"/>
       <c r="H186" s="15" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="187" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>423</v>
+      </c>
+      <c r="I186" s="58" t="s">
+        <v>666</v>
+      </c>
+      <c r="J186" s="51"/>
+    </row>
+    <row r="187" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A187" s="35"/>
       <c r="B187" s="31"/>
       <c r="C187" s="29"/>
@@ -6924,14 +7319,16 @@
         <v>2</v>
       </c>
       <c r="F187" s="5" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="G187" s="28"/>
       <c r="H187" s="15" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="188" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>424</v>
+      </c>
+      <c r="I187" s="59"/>
+      <c r="J187" s="52"/>
+    </row>
+    <row r="188" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A188" s="42">
         <v>70</v>
       </c>
@@ -6942,38 +7339,42 @@
         <v>14</v>
       </c>
       <c r="D188" s="5" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="E188" s="1">
         <v>0</v>
       </c>
       <c r="F188" s="5" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="G188" s="28"/>
       <c r="H188" s="15" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="189" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>433</v>
+      </c>
+      <c r="I188" s="51"/>
+      <c r="J188" s="51"/>
+    </row>
+    <row r="189" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A189" s="43"/>
       <c r="B189" s="31"/>
       <c r="C189" s="44"/>
       <c r="D189" s="5" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="E189" s="1">
         <v>0</v>
       </c>
       <c r="F189" s="5" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="G189" s="28"/>
       <c r="H189" s="15" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="190" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>434</v>
+      </c>
+      <c r="I189" s="52"/>
+      <c r="J189" s="52"/>
+    </row>
+    <row r="190" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A190" s="42">
         <v>71</v>
       </c>
@@ -6990,16 +7391,18 @@
         <v>0</v>
       </c>
       <c r="F190" s="5" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="G190" s="28" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="H190" s="15" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="191" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>337</v>
+      </c>
+      <c r="I190" s="51"/>
+      <c r="J190" s="51"/>
+    </row>
+    <row r="191" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A191" s="43"/>
       <c r="B191" s="31"/>
       <c r="C191" s="44"/>
@@ -7010,14 +7413,16 @@
         <v>0</v>
       </c>
       <c r="F191" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="G191" s="28"/>
       <c r="H191" s="15" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="192" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>401</v>
+      </c>
+      <c r="I191" s="52"/>
+      <c r="J191" s="52"/>
+    </row>
+    <row r="192" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A192" s="42">
         <v>72</v>
       </c>
@@ -7034,14 +7439,16 @@
         <v>43</v>
       </c>
       <c r="F192" s="5" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
       <c r="G192" s="28"/>
       <c r="H192" s="15" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="193" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>338</v>
+      </c>
+      <c r="I192" s="51"/>
+      <c r="J192" s="51"/>
+    </row>
+    <row r="193" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A193" s="43"/>
       <c r="B193" s="31"/>
       <c r="C193" s="44"/>
@@ -7056,10 +7463,12 @@
       </c>
       <c r="G193" s="28"/>
       <c r="H193" s="15" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="194" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>402</v>
+      </c>
+      <c r="I193" s="52"/>
+      <c r="J193" s="52"/>
+    </row>
+    <row r="194" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A194" s="42">
         <v>73</v>
       </c>
@@ -7076,16 +7485,20 @@
         <v>4</v>
       </c>
       <c r="F194" s="5" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="G194" s="28" t="s">
         <v>209</v>
       </c>
       <c r="H194" s="15" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="195" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>339</v>
+      </c>
+      <c r="I194" s="56" t="s">
+        <v>666</v>
+      </c>
+      <c r="J194" s="51"/>
+    </row>
+    <row r="195" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A195" s="43"/>
       <c r="B195" s="31"/>
       <c r="C195" s="29"/>
@@ -7096,14 +7509,16 @@
         <v>4</v>
       </c>
       <c r="F195" s="5" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="G195" s="28"/>
       <c r="H195" s="15" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="196" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>403</v>
+      </c>
+      <c r="I195" s="57"/>
+      <c r="J195" s="52"/>
+    </row>
+    <row r="196" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A196" s="42">
         <v>74</v>
       </c>
@@ -7120,16 +7535,20 @@
         <v>1</v>
       </c>
       <c r="F196" s="5" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="G196" s="28" t="s">
         <v>138</v>
       </c>
       <c r="H196" s="15" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="197" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>340</v>
+      </c>
+      <c r="I196" s="58" t="s">
+        <v>666</v>
+      </c>
+      <c r="J196" s="51"/>
+    </row>
+    <row r="197" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A197" s="43"/>
       <c r="B197" s="31"/>
       <c r="C197" s="29"/>
@@ -7140,14 +7559,16 @@
         <v>1</v>
       </c>
       <c r="F197" s="5" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="G197" s="28"/>
       <c r="H197" s="15" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="198" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>404</v>
+      </c>
+      <c r="I197" s="59"/>
+      <c r="J197" s="52"/>
+    </row>
+    <row r="198" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A198" s="34">
         <v>75</v>
       </c>
@@ -7164,16 +7585,20 @@
         <v>2</v>
       </c>
       <c r="F198" s="5" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="G198" s="28" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="H198" s="15" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="199" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>425</v>
+      </c>
+      <c r="I198" s="56" t="s">
+        <v>666</v>
+      </c>
+      <c r="J198" s="51"/>
+    </row>
+    <row r="199" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A199" s="35"/>
       <c r="B199" s="33"/>
       <c r="C199" s="29"/>
@@ -7184,14 +7609,16 @@
         <v>1</v>
       </c>
       <c r="F199" s="5" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="G199" s="28"/>
       <c r="H199" s="15" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="200" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>426</v>
+      </c>
+      <c r="I199" s="57"/>
+      <c r="J199" s="52"/>
+    </row>
+    <row r="200" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A200" s="42">
         <v>76</v>
       </c>
@@ -7214,10 +7641,12 @@
         <v>216</v>
       </c>
       <c r="H200" s="15" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="201" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>427</v>
+      </c>
+      <c r="I200" s="51"/>
+      <c r="J200" s="51"/>
+    </row>
+    <row r="201" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A201" s="43"/>
       <c r="B201" s="33"/>
       <c r="C201" s="29"/>
@@ -7232,10 +7661,12 @@
       </c>
       <c r="G201" s="28"/>
       <c r="H201" s="15" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="202" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>428</v>
+      </c>
+      <c r="I201" s="52"/>
+      <c r="J201" s="52"/>
+    </row>
+    <row r="202" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A202" s="34">
         <v>77</v>
       </c>
@@ -7252,16 +7683,20 @@
         <v>2</v>
       </c>
       <c r="F202" s="5" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="G202" s="28" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="H202" s="15" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="203" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>341</v>
+      </c>
+      <c r="I202" s="56" t="s">
+        <v>666</v>
+      </c>
+      <c r="J202" s="51"/>
+    </row>
+    <row r="203" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A203" s="35"/>
       <c r="B203" s="33"/>
       <c r="C203" s="29"/>
@@ -7272,14 +7707,16 @@
         <v>2</v>
       </c>
       <c r="F203" s="5" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="G203" s="28"/>
       <c r="H203" s="15" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="204" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>405</v>
+      </c>
+      <c r="I203" s="57"/>
+      <c r="J203" s="52"/>
+    </row>
+    <row r="204" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A204" s="42">
         <v>78</v>
       </c>
@@ -7296,14 +7733,18 @@
         <v>1</v>
       </c>
       <c r="F204" s="5" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="G204" s="28"/>
       <c r="H204" s="15" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="205" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>287</v>
+      </c>
+      <c r="I204" s="56" t="s">
+        <v>666</v>
+      </c>
+      <c r="J204" s="51"/>
+    </row>
+    <row r="205" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A205" s="43"/>
       <c r="B205" s="33"/>
       <c r="C205" s="29"/>
@@ -7314,14 +7755,16 @@
         <v>1</v>
       </c>
       <c r="F205" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G205" s="28"/>
       <c r="H205" s="15" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="206" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>416</v>
+      </c>
+      <c r="I205" s="57"/>
+      <c r="J205" s="52"/>
+    </row>
+    <row r="206" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A206" s="42">
         <v>79</v>
       </c>
@@ -7338,14 +7781,20 @@
         <v>1</v>
       </c>
       <c r="F206" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G206" s="28"/>
       <c r="H206" s="15" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="207" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>289</v>
+      </c>
+      <c r="I206" s="56" t="s">
+        <v>666</v>
+      </c>
+      <c r="J206" s="51" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="207" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A207" s="43"/>
       <c r="B207" s="33"/>
       <c r="C207" s="29"/>
@@ -7356,21 +7805,23 @@
         <v>0</v>
       </c>
       <c r="F207" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G207" s="28"/>
       <c r="H207" s="15" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="208" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>406</v>
+      </c>
+      <c r="I207" s="57"/>
+      <c r="J207" s="52"/>
+    </row>
+    <row r="208" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A208" s="42">
         <v>80</v>
       </c>
       <c r="B208" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C208" s="29" t="s">
+      <c r="C208" s="62" t="s">
         <v>86</v>
       </c>
       <c r="D208" s="5" t="s">
@@ -7382,17 +7833,17 @@
       <c r="F208" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="G208" s="28" t="s">
-        <v>234</v>
-      </c>
+      <c r="G208" s="28"/>
       <c r="H208" s="15" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="209" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>342</v>
+      </c>
+      <c r="I208" s="51"/>
+      <c r="J208" s="51"/>
+    </row>
+    <row r="209" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A209" s="43"/>
       <c r="B209" s="33"/>
-      <c r="C209" s="29"/>
+      <c r="C209" s="62"/>
       <c r="D209" s="5" t="s">
         <v>102</v>
       </c>
@@ -7400,14 +7851,16 @@
         <v>1</v>
       </c>
       <c r="F209" s="5" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="G209" s="28"/>
       <c r="H209" s="15" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="210" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
+        <v>407</v>
+      </c>
+      <c r="I209" s="52"/>
+      <c r="J209" s="52"/>
+    </row>
+    <row r="210" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A210" s="34">
         <v>81</v>
       </c>
@@ -7424,16 +7877,20 @@
         <v>1</v>
       </c>
       <c r="F210" s="5" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="G210" s="28" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="H210" s="15" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="211" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
+        <v>346</v>
+      </c>
+      <c r="I210" s="56" t="s">
+        <v>666</v>
+      </c>
+      <c r="J210" s="51"/>
+    </row>
+    <row r="211" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A211" s="35"/>
       <c r="B211" s="33"/>
       <c r="C211" s="29"/>
@@ -7444,57 +7901,67 @@
         <v>1</v>
       </c>
       <c r="F211" s="5" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="G211" s="28"/>
       <c r="H211" s="15" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="212" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>411</v>
+      </c>
+      <c r="I211" s="57"/>
+      <c r="J211" s="52"/>
+    </row>
+    <row r="212" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A212" s="42">
         <v>82</v>
       </c>
-      <c r="B212" s="47" t="s">
-        <v>29</v>
-      </c>
-      <c r="C212" s="29" t="s">
+      <c r="B212" s="60" t="s">
+        <v>32</v>
+      </c>
+      <c r="C212" s="53" t="s">
         <v>86</v>
       </c>
       <c r="D212" s="5" t="s">
-        <v>173</v>
+        <v>93</v>
       </c>
       <c r="E212" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F212" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="G212" s="28"/>
+        <v>241</v>
+      </c>
+      <c r="G212" s="45" t="s">
+        <v>279</v>
+      </c>
       <c r="H212" s="15" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="213" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>345</v>
+      </c>
+      <c r="I212" s="56" t="s">
+        <v>666</v>
+      </c>
+      <c r="J212" s="51"/>
+    </row>
+    <row r="213" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A213" s="43"/>
-      <c r="B213" s="48"/>
-      <c r="C213" s="29"/>
+      <c r="B213" s="61"/>
+      <c r="C213" s="54"/>
       <c r="D213" s="5" t="s">
-        <v>174</v>
+        <v>94</v>
       </c>
       <c r="E213" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F213" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="G213" s="28"/>
+        <v>241</v>
+      </c>
+      <c r="G213" s="46"/>
       <c r="H213" s="15" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="214" spans="1:8" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A214" s="42">
+        <v>410</v>
+      </c>
+      <c r="I213" s="57"/>
+      <c r="J213" s="52"/>
+    </row>
+    <row r="214" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A214" s="34">
         <v>83</v>
       </c>
       <c r="B214" s="31" t="s">
@@ -7510,17 +7977,21 @@
         <v>1</v>
       </c>
       <c r="F214" s="5" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="G214" s="28" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="H214" s="15" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="215" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A215" s="43"/>
+        <v>344</v>
+      </c>
+      <c r="I214" s="56" t="s">
+        <v>666</v>
+      </c>
+      <c r="J214" s="51"/>
+    </row>
+    <row r="215" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A215" s="35"/>
       <c r="B215" s="31"/>
       <c r="C215" s="29"/>
       <c r="D215" s="5" t="s">
@@ -7530,58 +8001,62 @@
         <v>0</v>
       </c>
       <c r="F215" s="5" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="G215" s="28"/>
       <c r="H215" s="15" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="216" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
+        <v>409</v>
+      </c>
+      <c r="I215" s="57"/>
+      <c r="J215" s="52"/>
+    </row>
+    <row r="216" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A216" s="42">
         <v>84</v>
       </c>
-      <c r="B216" s="31" t="s">
+      <c r="B216" s="47" t="s">
         <v>29</v>
       </c>
       <c r="C216" s="29" t="s">
         <v>86</v>
       </c>
       <c r="D216" s="5" t="s">
-        <v>93</v>
+        <v>173</v>
       </c>
       <c r="E216" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F216" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="G216" s="28" t="s">
-        <v>283</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="G216" s="28"/>
       <c r="H216" s="15" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="217" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
+        <v>343</v>
+      </c>
+      <c r="I216" s="51"/>
+      <c r="J216" s="51"/>
+    </row>
+    <row r="217" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A217" s="43"/>
-      <c r="B217" s="31"/>
+      <c r="B217" s="48"/>
       <c r="C217" s="29"/>
       <c r="D217" s="5" t="s">
-        <v>94</v>
+        <v>174</v>
       </c>
       <c r="E217" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F217" s="5" t="s">
-        <v>243</v>
+        <v>672</v>
       </c>
       <c r="G217" s="28"/>
       <c r="H217" s="15" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="218" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
+        <v>408</v>
+      </c>
+      <c r="I217" s="52"/>
+      <c r="J217" s="52"/>
+    </row>
+    <row r="218" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A218" s="42">
         <v>85</v>
       </c>
@@ -7595,17 +8070,21 @@
         <v>97</v>
       </c>
       <c r="E218" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F218" s="5" t="s">
         <v>213</v>
       </c>
       <c r="G218" s="28"/>
       <c r="H218" s="15" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="219" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
+        <v>347</v>
+      </c>
+      <c r="I218" s="56" t="s">
+        <v>666</v>
+      </c>
+      <c r="J218" s="51"/>
+    </row>
+    <row r="219" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A219" s="43"/>
       <c r="B219" s="31"/>
       <c r="C219" s="29"/>
@@ -7613,17 +8092,19 @@
         <v>98</v>
       </c>
       <c r="E219" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F219" s="5" t="s">
-        <v>213</v>
+        <v>673</v>
       </c>
       <c r="G219" s="28"/>
       <c r="H219" s="15" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="220" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
+        <v>412</v>
+      </c>
+      <c r="I219" s="57"/>
+      <c r="J219" s="52"/>
+    </row>
+    <row r="220" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A220" s="42">
         <v>86</v>
       </c>
@@ -7644,10 +8125,14 @@
       </c>
       <c r="G220" s="28"/>
       <c r="H220" s="15" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="221" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
+        <v>435</v>
+      </c>
+      <c r="I220" s="58" t="s">
+        <v>666</v>
+      </c>
+      <c r="J220" s="51"/>
+    </row>
+    <row r="221" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A221" s="43"/>
       <c r="B221" s="31"/>
       <c r="C221" s="29"/>
@@ -7662,10 +8147,12 @@
       </c>
       <c r="G221" s="28"/>
       <c r="H221" s="15" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="222" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
+        <v>436</v>
+      </c>
+      <c r="I221" s="59"/>
+      <c r="J221" s="52"/>
+    </row>
+    <row r="222" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A222" s="42">
         <v>87</v>
       </c>
@@ -7682,16 +8169,22 @@
         <v>2</v>
       </c>
       <c r="F222" s="5" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="G222" s="28" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="H222" s="15" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="223" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
+        <v>348</v>
+      </c>
+      <c r="I222" s="56" t="s">
+        <v>666</v>
+      </c>
+      <c r="J222" s="51" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="223" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A223" s="43"/>
       <c r="B223" s="31"/>
       <c r="C223" s="32"/>
@@ -7702,21 +8195,23 @@
         <v>1</v>
       </c>
       <c r="F223" s="5" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="G223" s="28"/>
       <c r="H223" s="15" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="224" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.4">
+        <v>413</v>
+      </c>
+      <c r="I223" s="57"/>
+      <c r="J223" s="52"/>
+    </row>
+    <row r="224" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A224" s="42">
         <v>88</v>
       </c>
       <c r="B224" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C224" s="44" t="s">
+      <c r="C224" s="32" t="s">
         <v>86</v>
       </c>
       <c r="D224" s="5" t="s">
@@ -77